--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K266"/>
+  <dimension ref="A1:K276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17833,6 +17833,690 @@
         </is>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】超強力！完全体ジェラールの本気！！唯一無二性能で無尽塔46.47階を破壊してしまう💥白薔薇＆背水無し攻略解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>完全体ジェラールで無尽塔46/47階を攻略する戦法を解説。
+最終皇帝女のカラツカ山＋フォールンレガリアの自傷でHP非満タン維持し回避確定発動。
+ビューネ・ネメシス・ジェラール・最終皇帝女・カタリナでダメブロ4枚＋回避を重ねる構成。</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>・最終皇帝女カラツカ山とフォールンレガリアの相性が最高
+・JRが検品持ちで偉すぎる
+・カタリナの挑発＋硬さでヘイト管理が優秀
+・ビューネのBP支援でBP切れず安定戦闘
+・白薔薇なしでも代用可能でお得</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>・フォールンレガリア2回使うと自傷加速で崩壊する
+・オールポーション使うとHP満タンで回避不発になり危険
+・JR自身は自傷ないのでHP管理がやや手間
+・直接攻撃キャラはゼラスマターに通らず連れていけない</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔46/47階攻略
+・カラツカ山＋自傷シナジー
+・フォールンレガリア活用
+・回避4枚重ね編成
+・白薔薇なし攻略</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RvuCxt1f4dU</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>RvuCxt1f4dU</t>
+        </is>
+      </c>
+      <c r="K267" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】大番狂わせ！最新キャラランキング★アビス厄軍団が環境破壊する【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>火力インフレを受けてキャラ評価基準を見直し最新ランキングを公開。
+サラ闇落ちはSSS、ジェラール闇落ちもSSS、ビクトール闇落ちはSSに調整。
+ウィルをトリプルSへ昇格、ルビーはS、レオニード／レオン／トーマスはA評価に。</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>・ジェラール闇落ちは2倍オーバードライブが偉くサポート性能が高い
+・サラはステ盛り＋エクストラフォース3倍で超火力
+・ビクトールは周回適正が非常に高くレイドで大活躍
+・ウィルは万能でボード値・HP回復・継承技も優秀
+・ジェラル＋リラの組み合わせが強力</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>・レオンは継承なしだと軽減49%で致命的に低い
+・トーマスは支援が飛び抜けず使い道が明確すぎてA止まり
+・ビクトールはヒット数がブレて高難度の安定性は低い
+・ルビーは1ターン目に使えず看板適正が弱い
+・レオニードは刺さる場面が少なく汎用性低め</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>・最新キャラランキング
+・火力インフレと評価基準調整
+・アビス厄軍団3体評価
+・ウィル昇格
+・アニバ前の引き判断</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cKC66JCk-uE</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>cKC66JCk-uE</t>
+        </is>
+      </c>
+      <c r="K268" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】闇堕ちガチャ後半戦が始まる！次はまさかのあのキャラ！？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>5/15開始の暦読み編第4話後編ガチャを予想する動画。
+シングルガチャ3体構成と読み、主役は苦人士・オアイブ・少年と予想。
+ロマサガ2親子組の対決を盛り上げる絡みに期待を寄せる。</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>・暦読み編のストーリーが興味深く面白い
+・ジェラール・レオン・ビクトールの親子絡みが熱い
+・闇落ちジェラールのキャラ描写が良かった
+・シングルガチャは引きやすく優しい仕様</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>・ジェラール戦がリフレクト一辺倒で消化不良
+・レオンとビクトールが一言も喋っていない
+・キャットの直近実装で再登場が難しい状況
+・アニバ前で石貯めの判断に悩ましい時期</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>・5/15新ガチャ予想
+・暦読み編第4話後編
+・シングルガチャ3体
+・苦人士・オアイブ・少年
+・ロマサガ2親子組</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=N92Pv2G_B1w</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>N92Pv2G_B1w</t>
+        </is>
+      </c>
+      <c r="K269" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】これはマジで後悔！どうしても欲しい理由があったので闇堕ちジェラール編ガチャを引いた結果...【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>闇落ちジェラール編ガチャに天井まで突撃した結果報告動画。
+本命のビクトールが最後まで出ず、レオン被りでフレニッシュ。
+天井交換でビクトールをコンプし「もう後悔した」と振り返る。</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>・闇落ちジェラールがイケメンで超かっこいい
+・ビクトールのエフェクト速度に期待大で強そう
+・ジェラルアビス（イケメン版）の演出が良い
+・ロマサガ2親子3人組の絡みが熱くて楽しみ</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>・本命ビクトールが天井まで出ず後悔
+・レオンが大量生産枠でひたすら被る
+・ビクトールが流し切りばかり実装される運営いじり
+・コ玉（願掛け）は結局効果なし
+・天井15000ジェル＋無償3万消費でしんどい</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>・闇落ちジェラール編ガチャ
+・天井150連
+・ビクトール狙い
+・親子3人組（ジェラル/レオン/ビクトル）
+・コ玉（願掛け）検証</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fhG--UnQNco</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>fhG--UnQNco</t>
+        </is>
+      </c>
+      <c r="K270" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【ガチャ動画】やらかし ばちばち ギリギリ【No.607】</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>ノエル編ガチャの期限ギリギリでウィル狙い50連を実施。
+ウィルとルビーをゲットして4万5000円温存で撤退成功。
+タコさんが咳で肋骨にヒビが入った近況も雑談として語る。</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>・ウィルが取れて満足の結果
+・ルビーも一緒に引けて両親ゲット
+・4万5000ジェル温存できてお得
+・ドラクエタクトコラボのストーリーが良かった</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>・残り11時間というギリギリで焦った
+・ノエルは諦めて撤退する形に
+・肋骨にヒビが入って咳が痛い
+・ペット2匹演出は当てにならない</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>・ノエル編ガチャ50連
+・ウィル狙い引き
+・ギリギリ期限消化
+・ドラクエタクトコラボ
+・肋骨ヒビ雑談</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B1umK_8iu54</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>B1umK_8iu54</t>
+        </is>
+      </c>
+      <c r="K271" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「闇堕ちミルザ」厄…第2弾中編!!めがみもやってきててんやわんやの前夜祭前の大注目ガチャ!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>ガチャ予想でドロレスをピンポイント的中、感謝
+ジェラール・サラに続きミルザも闇堕ち登場
+ミルザのカブト報酬は控えめ、復刻日程も考察</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ予想でドロレスをピンポイント的中できた
+・復刻の最終皇帝女は便利で揃えてるなら狙える</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザのカブト報酬がかなり控えめ
+・ハーフアニバが6月にずれ込む可能性あり</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>・闇堕ちミルザ
+・ガチャ予想的中
+・ハーフアニバ日程
+・復刻ガチャ
+・連達技</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C7Xni8fygMI</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr">
+        <is>
+          <t>C7Xni8fygMI</t>
+        </is>
+      </c>
+      <c r="K272" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15T02:30:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ミルザ闇堕ち！5月15日更新情報まとめ 【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>5/15から暦み編第4話中編、ミルザ闇堕ち登場
+ミルザアビス編と女神編のダブルガチャ開催
+投稿者は女神ドロレス最優先で両方狙う方針</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>・闇堕ちミルザが退術で武器が変わるのが面白い
+・女神ドロレスは絶対取る案件で楽しみ
+・ログインボーナスで3000ジュエル配布</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>・コラボ含めガチャが多く出費がかさむので手心が欲しい</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>・暦み編第4話中編
+・ミルザアビス編
+・女神編
+・詩人ドロレス
+・復刻アドラー編
+・螺旋回廊更新</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dvprjPrgJ-w</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr">
+        <is>
+          <t>dvprjPrgJ-w</t>
+        </is>
+      </c>
+      <c r="K273" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15T02:30:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】発狂ミルザ⁉️闇堕ちの連鎖が止まらない、、公式先行情報確認【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>公式先行情報でミルザ闇堕ち（アビス化）を確認
+女神・詩人ドロレス編と復刻アドラー編も同時開催
+闇堕ちキャラ量産のルーティン化を予想</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>・召喚時の回廊で演出が変わる仕掛けが面白い
+・復刻の最終皇帝女は強く今でも使える
+・久々の斧キャラ・詩人ドロレスが嬉しい</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ続きで課金が限界突破して厳しい
+・ミルザは光術関係があり回すか悩ましい
+・レオンは出番が少なく継承目的でも取る必要薄い</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>・闇堕ちミルザ
+・召喚回廊で演出変化
+・女神編
+・復刻アドラー編
+・最終皇帝女
+・闇堕ち量産予想</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zgjqVhXgvvg</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr">
+        <is>
+          <t>zgjqVhXgvvg</t>
+        </is>
+      </c>
+      <c r="K274" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15T02:30:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】主役は闇堕ちミルザ！次のガチャの内容に驚愕！？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>5/15から暦み編第4話中辺、闇堕ちミルザが主役
+ミルザアビス編・女神編・復刻アドラー編の3ガチャ
+1週間刻みの更新でハーフアニバへ、出費に戦々恐々</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザアビスで武器違いが増えるのは純粋に嬉しい
+・アビスキャラは強い傾向で注目
+・久々の斧キャラ詩人ドロレスが嬉しい</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザが退術化で継承がめんどくさい・できない
+・女神も闇落ちさせた方がイラスト人気が出たのでは
+・3ガチャ実装＋1週間刻みで出費が恐ろしい
+・復刻にジュエルを回すより新ガチャの方が幸せ</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>・闇堕ちミルザアビス
+・退術キャラ
+・女神編
+・復刻アドラー編
+・3ガチャ実装
+・ハーフアニバ予想</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Hs5XV44vU8s</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr">
+        <is>
+          <t>Hs5XV44vU8s</t>
+        </is>
+      </c>
+      <c r="K275" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15T02:30:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新規・復帰勢必見！ドラクエコラボノエルで闘者武器強化&amp;育成しながら高速周回する方法【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>ドラクエコラボのノエルで闘者の関門を高速周回
+育成と関門武器強化を同時にこなす方法を解説
+お気に入り登録と上級パス自動再戦で効率化</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>・関門武器は高威力で周回・高難度・レイドで使え強化価値大
+・ノエルソロでも因リラ編成と10秒未満差で十分速い
+・上級パス加入で1日3000回自動再戦でき効率的</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>・過去の関門は復刻されず自動再戦チケットが手に入りにくい
+・イベントタブからバトルを選ぶと時間ロスする</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>・ノエル高速周回
+・闘者の関門
+・関門武器強化
+・育成枠編成
+・お気に入りクエスト登録
+・上級パス自動再戦</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=eg-Wl7x9YU8</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr">
+        <is>
+          <t>eg-Wl7x9YU8</t>
+        </is>
+      </c>
+      <c r="K276" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15T02:30:27Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K276"/>
+  <dimension ref="A1:K289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18517,6 +18517,903 @@
         </is>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「無限バフ&amp;ダメブロ」詩人が無尽塔に参戦!!小回りの聞く性能を分析&amp;古き良き良き性能の術を持つホーリーオーダー女バルバラ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>無限バフ&amp;ダメブロ詩人が無尽塔に参戦の性能分析
+詩人は無限バフ型に加えダメブロ1回で無人島活躍が期待
+ホーリーオーダー女バルバラはリキャスト2ターン術が強いが現状はE評価</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>・詩人はディフェンス75%ばら巻きで便利
+・ダメブロ1回付与で無人島での優先度が上がった
+・BPプラス15で自己完結し20重スタート
+・カンスト状態が安すく毒性統一編成の究極
+・バルバラのリキャスト2ターン術は強い</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>・詩人は時間がかかり1度のミスも許されない繊細さ
+・5体全員がやり続けるシチュエーションがない
+・バルバラは個人と防御どちらかしか伸ばせない典型的な役立てづらいスタイル
+・バルバラ総合評価Eで玄関手前の古いスタイル</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>・詩人スタイル
+・ダメブロ継承
+・無限バフ
+・バルバラ性能
+・無人島運用
+・ホーリーオーダー女</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=O54d6XM-g5s</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr">
+        <is>
+          <t>O54d6XM-g5s</t>
+        </is>
+      </c>
+      <c r="K277" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16T01:06:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「最強は?」厄ガチャランキング!!マイスが時代に追いついた…アルドラと徹底比較!!&amp;横の時代が来るのか!?回復過剰のドロレスの使い方　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>厄ガチャランキング！マイス時代のアルドラと回復過剰ドロレス分析
+アルドラはマイス劣化版でダメブロ周りが惜しくフレーバー化
+ドロレスは横を殴って回復するだけで総合C評価</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>・アルドラはマイス並みの火力を出せる可能性
+・アルドラはステバフ大きく行動回数多い
+・ドロレスはセフィルマルカーの回復対策に良さそう
+・横を殴って全体回復は便利</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>・アルドラはマイスのデメリットを遥かに超える面倒くささ
+・マイスがすでにいるとアルドラは介護感
+・ドロレスはやれることが少ない
+・ミルザとの相性は悪い
+・味方全体への火力補正値が10ターンで切れる</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>・厄ガチャランキング
+・アルドラ評価
+・ドロレス評価
+・マイス比較
+・横アタッカー
+・AJ検定</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QxdwV0h5DBo</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr">
+        <is>
+          <t>QxdwV0h5DBo</t>
+        </is>
+      </c>
+      <c r="K278" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16T01:06:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「A.J.と重ねる」厄ミルザの陰単体EXの役割とは!?&amp;その闇を吸い付くし味方に還元するめがみの強さを紐解く　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>厄ミルザの陰単体EXの役割と闇を還元するめがみの強さを紐解く
+めがみは全員陰攻撃が必須で制約が厳しい割に効果が限定的
+ミルザは陰単体EX 1.5倍永続が便利で置き物として活躍可能</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>・めがみの防御面は最高峰の91-92%
+・ミルザの陰単体エクストラフォース2.25倍は便利
+・ミルザは要無効という特攻性を持つ
+・ミルザは5行動以上確定で行える
+・ダメブロ蓄積の補助として有効</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>・めがみは全員がマイターン陰攻撃必中というのが破に難しい
+・めがみは制約が厳しい割に強くない
+・めがみは複産物的にしか取れない
+・ミルザは突出した強さの数値はない
+・AAも乗せづらく狙って取るものではない</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>・厄ミルザ性能
+・めがみ評価
+・陰単体EX
+・AJ重ね
+・エクストラフォース</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XzQGs14KaIo</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr">
+        <is>
+          <t>XzQGs14KaIo</t>
+        </is>
+      </c>
+      <c r="K279" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16T01:06:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　めがみ　何ターン生き残る？　この技継承、実質”背水”です</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>めがみの技継承で実質背水運用、何ターン生き残るか検証
+ゼラチナスマター戦でめがみが236ターン耐え続け勝利
+置き物性能が高く一数を取れて良かった案件</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>・めがみが236ターン耐えて勝利
+・ポテンシャルがやばい
+・置き物性能が高い
+・アビリティのバフが強すぎる
+・取って良かった、今回のガチャで1番かも
+・エクストラフォース熱用が奥物性能相当</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>・サポーターのため火力がもう少し欲しい
+・BPやODエクストラフォース補助が必要
+・BPが重い
+・メインアタッカーとしては厳しい
+・高すぎるがゆえに火力が出ない</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>・めがみ検証
+・背水運用
+・236ターン耐久
+・置き物性能
+・ゼラチナスマター</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5iIUiLDkJ5g</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr">
+        <is>
+          <t>5iIUiLDkJ5g</t>
+        </is>
+      </c>
+      <c r="K280" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16T01:06:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ドロレス､めがみ狙いでガチャ！『こよみ編 第4話 中編 公開記念 Romancing祭 めがみ編＆ミルザ【厄】編』【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>ドロレス・めがみ狙いでRomancing祭めがみ編＆ミルザ厄編ガチャ
+詩人ばかり出てお目当てがピンポイントで出ないガチャ運
+ドロレスは何とか取れたがめがみは取れず、ミルザ編に課金切替</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>・ドロレスは絶対取りたかったので取れて良かった
+・ミルザはアタッカーでカウンターもできる
+・ピックが出ただけマシ
+・ドロレスは闇落ちキャラとして魅力的</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>・最近ピンポイントでお目当てが出ない
+・詩人ばかり出る偏り
+・すり抜けばかり
+・ハーフアニバ前なのにひどい
+・ジュエルが溜まっていない
+・バルバラは闇落ちキャラじゃない</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>・ドロレス狙い
+・詩人すり抜け
+・ガチャ運
+・ロマフェス
+・キャラ愛</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2ZRDT-0aVUg</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr">
+        <is>
+          <t>2ZRDT-0aVUg</t>
+        </is>
+      </c>
+      <c r="K281" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16T01:06:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】最速で6人全員性能確認！光と闇の邂逅【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>最速で光と闇の邂逅ガチャ6人全員性能確認
+ミルザは陰属性パーティリーダーでアルドラはマイス似だが補助必須
+女神は陰属性特攻で刺さる場所では有効、欲しいのはアルドラとミルザ</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザはレアアビリティ持ちでアリ
+・ミルザはエクストラフォース単体陰中が便利で被らない
+・ディフェンスアップ超極大で固い
+・アルドラはOD直進コンボが強い
+・バルバラはルミエルエテルネルが強い
+・女神は陰属性特攻で刺さると強い
+・ドロレスはHP回復スーパーマンで便利</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>・アルドラはHP管理が狭くフルスペック発動条件が厳しい
+・アルドラはマイスでよくね感がある
+・女神は要属性使うと味方が弱くなる縛り
+・詩人はあんま強くなくしょぼい
+・ドロレスはエクストラフォース系もなく抜けてる
+・ミルザはトリプルSまでは行かない</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>・6人性能確認
+・ミルザ陰パ
+・アルドラ運用
+・女神特攻
+・ドロレス回復
+・AJ検定</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4YwtRzrskw8</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr">
+        <is>
+          <t>4YwtRzrskw8</t>
+        </is>
+      </c>
+      <c r="K282" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16T01:06:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】特攻深夜Wガチャ！！私は引かぬ媚びぬ省みぬ！！！！！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>特攻深夜Wガチャ、ミルザ闇落ち編に絞って引く決意
+まさかの神引きでアルドラとミルザ両方ゲットしクワールド復刻も
+89連で大満足、もう一方の女神編も無償分で爆発しドロレス引き</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザとアルドラ両方確保できた
+・クワールド復刻も来てびっくり
+・こっちのガチャは最高
+・6連で爆発
+・神引きで先週の痛みが超心できた
+・ドロレスも引けて女神編も大処理</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>・ボルカばっか出る
+・同じ詩人が連続で出る偏り
+・優勝ジュエルが20で1しかない
+・こっちはすり抜けばかり
+・ジェラール出ない
+・89連は普段の半分以下</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>・深夜ガチャ
+・神引き
+・ミルザ確保
+・アルドラ確保
+・クワールド復刻</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bifLT_-jlbk</t>
+        </is>
+      </c>
+      <c r="J283" s="2" t="inlineStr">
+        <is>
+          <t>bifLT_-jlbk</t>
+        </is>
+      </c>
+      <c r="K283" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16T01:06:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみ編 第4話 中編 公開記念 ガチャガチャ</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>こよみ編第4話中編公開記念ガチャ、雑談多めで運悪く外しまくり
+バルバラ・アルドラ・ミルザ各性能を確認しアルドラを評価
+80連回しても何も当たらず設定1扱いのレイガ続き</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>・バルバラのルミエレテルネルは強い
+・アルドラはダメブロ貼りつつイグナイトラッシュで強い
+・アルドラはAJ検定通り使いやすさUP
+・ミルザのマリスロードはアタッカーに優秀
+・ドロレスはAJ検定合格でリッチと組み合わせ良し
+・バルバラは幻統では最強</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>・80連回しても何も当たらない
+・ジェラール出ない
+・詩人は3年前のスタイルみたいで弱い
+・ドロレスは性能微妙、HP回復だけ
+・アルドラはエクストラフォースなくて物足りない
+・すり抜け祭り、設定1のレイガ</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ編中編
+・キャラ性能解説
+・ガチャ回し雑談
+・AJ検定
+・ストーリー要素</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=g1PSrk2lHKM</t>
+        </is>
+      </c>
+      <c r="J284" s="2" t="inlineStr">
+        <is>
+          <t>g1PSrk2lHKM</t>
+        </is>
+      </c>
+      <c r="K284" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16T01:06:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今回1番の当たりガチャ？ミルザ編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>今回1番の当たりガチャ？ミルザ編3キャラ性能チェック
+アルドラがマイス上位互換でドライブチェーン持ちで強い
+バルバラはエクスフォース無しで微妙、ミルザは陰属性編成向け</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>・アルドラはマイスの上位互換的性能
+・アルドラのフリップフレームでOD1.75倍+ドライブチェーン
+・アルドラはAJとの相性抜群
+・ミルザは5行動17ヒットで陰属性編成のリーダー
+・ミルザはマリスロードで2倍フォース2ターン
+・バルバラはセットエクラのループで永続活用</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>・バルバラはエクスフォース付与を持たない超サポーター
+・バルバラはほぼ会話で来そうな性能
+・アルドラはHP代償管理が必須で難しい
+・ミルザは要属性キャラと共存できない
+・ミルザは無理する必要はない、他に強いアタッカー多い
+・アビスキャラはピンポイントが多い</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザ編評価
+・アルドラ性能
+・バルバラ性能
+・陰属性編成
+・AJ相性
+・ドライブチェーン</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=b2dETnFf1Zc</t>
+        </is>
+      </c>
+      <c r="J285" s="2" t="inlineStr">
+        <is>
+          <t>b2dETnFf1Zc</t>
+        </is>
+      </c>
+      <c r="K285" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16T01:06:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭ミルザ厄編ガチャ評価 #ロマサガRS #shorts #ガチャ</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭ミルザ厄編ガチャ評価のショート動画
+字幕は実質取得できておらず内容情報が不足
+ショート動画でガチャ評価を伝える形式</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr"/>
+      <c r="F286" s="2" t="inlineStr"/>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザ厄編
+・ショート動画
+・ガチャ評価</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=41X5_IDq_UU</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="inlineStr">
+        <is>
+          <t>41X5_IDq_UU</t>
+        </is>
+      </c>
+      <c r="K286" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16T01:06:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭めがみ編ガチャ評価 #ロマサガRS #shorts #ガチャ</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭めがみ編ガチャ評価のショート動画
+字幕は実質取得できておらず内容情報が不足
+ショート動画でガチャ評価を伝える形式</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr"/>
+      <c r="F287" s="2" t="inlineStr"/>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>・めがみ編
+・ショート動画
+・ガチャ評価</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=M4Gp43M3grw</t>
+        </is>
+      </c>
+      <c r="J287" s="2" t="inlineStr">
+        <is>
+          <t>M4Gp43M3grw</t>
+        </is>
+      </c>
+      <c r="K287" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16T01:06:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】ミルザ〔厄〕能力値早見表~純黒の魔戦士~漆黒の~SSS30ヒット以上~陰フォース2.75倍スーパーアタッカー</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>ミルザ厄能力値早見表、純黒の魔戦士陰フォース2.75倍SSSアタッカー
+陰特化スーパーアタッカーで33ヒット以上、カウンター性能も完備
+置き物性能は単体陰1.5倍で活躍判断悩む、雪だるまの前例あり</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザはトリプルS以上33ヒットの破の火力
+・エクストラフォース陰2.75倍は強力
+・5回直接攻撃を受ければ43ヒット
+・カウンター性能も完備で味方サポート可能
+・マリスロード使用時にフォース合計2倍付与
+・味方全体に単体陰1.5倍永続付与</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>・陰属性に縛られる
+・直接攻撃を受ける前提
+・色で使う場合は他の攻撃強化系が弱い
+・マリスロードはバトル中2回までの制限が痛い
+・すぐに陰1.75倍キャラ来る可能性で取りどき悩む
+・雪だるまも同様の問題で活躍が難しかった</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザ厄性能
+・陰フォース2.75倍
+・33ヒット
+・能力値早見表
+・カウンター性能</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XIpysgvmChE</t>
+        </is>
+      </c>
+      <c r="J288" s="2" t="inlineStr">
+        <is>
+          <t>XIpysgvmChE</t>
+        </is>
+      </c>
+      <c r="K288" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16T01:06:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベント解説、周回編成の紹介【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>新イベント解説、こよみ編メブリアイの周回編成紹介
+交換所アイテムは月影の紅花、装備進化機晶、進化の軌跡を集める
+5月20日に鍛錬道場と螺旋回廊の追加が来るので技ランク上げを</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>・交換所で必要なものを交換して終わりにできる
+・5/20に鍛錬道場と螺旋回廊追加でやり込み増える
+・最近の追加キャラは属性武器を使う場合が増えてきた
+・イベント自体は焦ってやる内容ではない</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>・今回のイベントでは11秒の技が12秒になってしまう環境
+・育成上限プラスでHP5330から5360と微増のみ</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ編イベント
+・周回編成
+・交換所アイテム
+・5/20螺旋更新
+・装備進化</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=678N7rVToBA</t>
+        </is>
+      </c>
+      <c r="J289" s="2" t="inlineStr">
+        <is>
+          <t>678N7rVToBA</t>
+        </is>
+      </c>
+      <c r="K289" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16T01:06:50Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K289"/>
+  <dimension ref="A1:K299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19414,6 +19414,693 @@
         </is>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「ハーフアニバ目前」実は強い厄ガチャ!!無尽塔メンツを刷新せよ!!12体4ガチャランキング!!最新スタイル比較検討会→2026年5月17日版　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>ハーフアニバ目前の厄ガチャ12体を比較検討。
+アルドラ・女神は無人島でダメブロ要員として再評価。
+ジェラール／ビクトールは確保、サラ天井は見送りが安全。</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>・アルドラはダメブロ3ターンで無人島に刺さる
+・女神は天品アタッカー＋ダメブロでタフに戦える
+・サラは大償ダメージ持ちで皇帝女と相性◎
+・ビクトール・ジェラールは汎用性が高く必須級
+・トールは女神／サラより頭一つ抜けた火力サポート</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>・トーマスはダメブロ環境で居場所が無い
+・バルバラは継承前提で活躍させづらい
+・ミルザはカウンター必須でやられやすい
+・サラ天井は消費ジュエル的に重く見送り推奨</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>・厄ガチャ評価
+・無人島環境
+・ダメブロ運用
+・サラ天井判断
+・ジェラール推奨</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4s55E45n4GU</t>
+        </is>
+      </c>
+      <c r="J290" s="2" t="inlineStr">
+        <is>
+          <t>4s55E45n4GU</t>
+        </is>
+      </c>
+      <c r="K290" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17T01:09:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　ミルザ　陰パ、止まらん　頼れる男始動</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>ミルザ＋サラ＋ジェラール＋ターミンの陰パで実戦テスト。
+単体攻撃に乗るエクストラフォースと反撃で火力が伸びる。
+ミルザはサブアタッカー兼サポーターとして優秀との結論。</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザのカウンターと反撃が安定して刺さる
+・サラの火力が3億超えで圧巻
+・偶数ターンのジェラール効果で火力が一段伸びる
+・ミルザのインバフは被らず汎用的に乗る</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザのバフは単体攻撃にしか乗らない点に注意
+・陰パは防御の高いキャラが少なく耐久に不安</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザ陰パ検証
+・単体イン強化
+・カウンター運用
+・AJ連携
+・実戦バトル</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EDsXmDiTrRs</t>
+        </is>
+      </c>
+      <c r="J291" s="2" t="inlineStr">
+        <is>
+          <t>EDsXmDiTrRs</t>
+        </is>
+      </c>
+      <c r="K291" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17T01:09:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】5大ガチャランキング！引くべき優先度考察★激突アビス軍団【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>5大ガチャをジェラール＞ミルザ＞女神＞サラ＞最終皇帝女で順位付け。
+ジェラールは2T毎にOD2倍を撒ける環境支配級と評価。
+他は基本温存、ジェラールだけは引いて損なしとの結論。</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>・ジェラールはOD2倍と全体防御75%で必須級
+・ミルザは竜王と組ませると2倍火力が出る
+・女神は赤ネサス継承でSサブアタッカー化
+・最終皇帝女のルクスOEは未だ環境最強級
+・ビクトールは火力サポートと回避で汎用的</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>・アルドラはHP満タン維持が難しくマイス劣化気味
+・トーマスは火力不足で使い場面に困る
+・レオンは継承なしだと軽減50%で出番が少ない
+・ドロレスは防御軽減ゼロで穴になりやすい</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>・5大ガチャ比較
+・ジェラール1位
+・ミルザ将来性
+・女神運用
+・最終皇帝女復刻</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1mLcaVxCYms</t>
+        </is>
+      </c>
+      <c r="J292" s="2" t="inlineStr">
+        <is>
+          <t>1mLcaVxCYms</t>
+        </is>
+      </c>
+      <c r="K292" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17T01:09:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】まさかのSSS判定有！思わぬ伏兵現る★最新キャラランキング！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>最終皇帝女はトリプルSで未だ環境支配と再評価。
+女神はSS判定で行動回数＋赤ネサス継承が強力。
+ジェラールはインフラ級、他は温存推奨との結論。</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>・最終皇帝女のルクスOEは今も最前線で活躍
+・女神は8回行動＋赤ネサスで防御91%まで盛れる
+・ジェラールは2Tに1度OD2倍の破格性能
+・詩人は導きシリーズで要属性編成が一気に強化
+・バルバラは爆裂で火力サポートが楽になる</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>・アルドラはマイス比で平成難易度が高すぎる
+・ミルザは現状デス、将来性のみ評価
+・バルバラはエクストラフォース無くSS届かず
+・ドロレスはデスメタルソウル無しだと素材待ち
+・ハーフアニバ前のため引きすぎは危険</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>・最終皇帝女SSS
+・女神SS判定
+・ジェラール推奨
+・アルドラ評価
+・ハーフアニバ温存</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KbuXKYr6LRs</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="inlineStr">
+        <is>
+          <t>KbuXKYr6LRs</t>
+        </is>
+      </c>
+      <c r="K293" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17T01:09:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>＃ロマサガRS アルドラ編成紹介と使ってみた所感</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>アルドラ編成は先制攻撃でHPが削れる構造が課題。
+防御軽減を上げる、ターン終了時回復で対策可能。
+個人的にはマイスの方が扱いやすいとの所感。</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>・アイス・ウィルは編成に組み込みやすい
+・反撃回復のターミンが安定枠になる
+・防御軽減で大償ダメージを火ダメ依存にできる</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>・アルドラはマイスより明確に使いづらい
+・先制攻撃後にHPを返す手段の確保が必須</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>・アルドラ編成
+・HP満タン維持
+・回復スタイル
+・ターミン採用
+・マイス比較</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=N0ALUKHgMOk</t>
+        </is>
+      </c>
+      <c r="J294" s="2" t="inlineStr">
+        <is>
+          <t>N0ALUKHgMOk</t>
+        </is>
+      </c>
+      <c r="K294" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17T01:09:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>＃ロマサガRS  完全体めがみ思ったより強かった</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>女神は赤ネサス継承で行動回数を活かしバフ撒き役に。
+敵が陰属性攻撃するとエクストラフォースが大量に乗る。
+完全体なら陰属性以外の敵にも汎用性高く戦える。</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>・行動回数の多さでステバフと防御強化を全体に配れる
+・陰属性攻撃時のエクスフォで大幅に火力貢献
+・継承完全体なら汎用性が一段アップ
+・特殊攻撃を避けられる
+・実際に使ってみて非常に使いやすい</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr"/>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>・女神性能
+・赤ネサス継承
+・ステバフ撒き
+・防御強化
+・特殊攻撃回避</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTxCm2hbKto</t>
+        </is>
+      </c>
+      <c r="J295" s="2" t="inlineStr">
+        <is>
+          <t>XTxCm2hbKto</t>
+        </is>
+      </c>
+      <c r="K295" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17T01:09:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今度のめがみは守り最強！？めがみ編の3人をチェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>女神編ドロレス／詩人／女神の3名を性能チェック。
+ドロレスはHP回復特化、詩人は要属性編成専用バッファー。
+女神は条件次第で軽減91%超、陰属性敵相手に化ける。</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>・女神は火ダメ軽減91%超でトップクラスの硬さ
+・女神は本人火力も高く太陽落とし＋紀煙三人で連撃
+・詩人は導きシリーズで要属性編成を底上げ可能
+・ドロレスは継承デスメタルコードで全体88%軽減
+・女神は今後の陰属性敵相手に活躍が期待できる</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>・ドロレスはHP回復特化すぎて出番が限定的
+・詩人は要属性編成限定でピンポイント運用
+・女神は陰属性攻撃を持つ敵にしか真価が出ない
+・ハーフアニバ直前で温存判断が無難</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>・女神編考察
+・ドロレス回復特化
+・詩人要編成
+・女神火ダメ軽減
+・ハーフアニバ判断</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7x3cueP_smc</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="inlineStr">
+        <is>
+          <t>7x3cueP_smc</t>
+        </is>
+      </c>
+      <c r="K296" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17T01:09:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第120回~アルラウネたちの井戸~最適解パーティ徹底考察~👊ランク上位を目指そう👊〜📻TYAMU RADIO📻</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>5/18開幕「アルラウネたちの井戸」最適解パーティを徹底考察。
+弱点は大員属性、9体2Rで範囲アタッカーが本命。
+本命は神＋ガチャん＋アレツ＋ユト＋イシスの編成。</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>・神は全体アタッカーとして安定して候補入り
+・リラ・イシスは置物枠として継続採用
+・ガーネットは大員属性強化で適性高い
+・サラ・ターミンはセカンドアタッカーで火力貢献
+・雪だるまは9体カスト前提で輝く可能性</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャんアレツの天番技がまだ揃っていない
+・サラは単体攻撃で9体ステージとは相性悪い
+・ミルザは強化系が弱く井戸での活躍は未数
+・テスト運用ができないため当日の調整が必要</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>・アルラウネの井戸
+・大員属性弱点
+・範囲アタッカー
+・本命編成
+・セカンドアタッカー</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qR7yxGVL5gI</t>
+        </is>
+      </c>
+      <c r="J297" s="2" t="inlineStr">
+        <is>
+          <t>qR7yxGVL5gI</t>
+        </is>
+      </c>
+      <c r="K297" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17T01:09:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみ編 第4話 中編ガチャ考察配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>暦読み編第4話中編ガチャをミルザ／アルドラ／バルバラを生配信で考察。
+ミルザのマリスロードは2回限定で短期決戦向きと評価。
+視聴者と雑談しつつ無人島やドラクエタクト話題で盛り上がる。</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザ本人の火力はカウンター込みで担保されている
+・ミルザの陰属性無効は特定バトルで刺さる可能性
+・復刻のアドラー編で最終皇帝女が狙えるのは魅力
+・視聴者と無人島攻略の知見を共有できた</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザのマリスロードは2回限定で長期戦に弱い
+・アルドラはHP管理が難しく扱いづらい
+・バルバラは特徴薄く優先度低め
+・ハーフアニバ直前で温存判断が無難</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ考察配信
+・ミルザ評価
+・マリスロード制限
+・視聴者交流
+・ハーフアニバ温存</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=60sB2yrDbL0</t>
+        </is>
+      </c>
+      <c r="J298" s="2" t="inlineStr">
+        <is>
+          <t>60sB2yrDbL0</t>
+        </is>
+      </c>
+      <c r="K298" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17T01:09:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「ミルザ[厄] 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>ロマンシング祭ミルザ[厄]編3体のスタイル考察。
+ミルザB、アルドラB+、バルバラB-の評価。
+マイス未所持ならアルドラ検討、新規には不向きとの結論。</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザはエクスフォ単体イン1.5倍が被らず強力
+・ミルザの直接攻撃カウンター4S5ヒットが優秀
+・アルドラはOD攻撃1.75倍とウィーク80%上昇が高火力
+・アルドラの火ダメ軽減75%は高難度でも採用しやすい
+・バルバラはバフ／デバフの効果量が高い</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>・マリスロードは2回制限で長期戦に向かない
+・アルドラはHP満タン維持のハードルが高く新規向きでない
+・アルドラは自前のOD上昇手段が無く編成が縛られる
+・バルバラは特徴が薄く取得優先度は低い
+・バルバラのカ問武器装備不可は痛い</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザ厄編考察
+・ランク付け
+・マリスロード評価
+・アルドラHP運用
+・バルバラ判断</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6wT_Qu4QHi8</t>
+        </is>
+      </c>
+      <c r="J299" s="2" t="inlineStr">
+        <is>
+          <t>6wT_Qu4QHi8</t>
+        </is>
+      </c>
+      <c r="K299" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17T01:09:01Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K299"/>
+  <dimension ref="A1:K309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20101,6 +20101,673 @@
         </is>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「引くべし」厄ガチャ!!ハーフアニバ前にジュエルの消費!?我々は良いスタイルだけを集めるガチャ厳選勢なのだ…!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>厄ガチャでビクトール・ジェラールを早期回収狙い
+ムくちゃ確定で2枚抜き含む豪華結果
+さらに女神・詩人ガチャの引き判断を考察</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>・早期撤退コンプで運が良かった
+・ムくちゃ第3規模からの2枚抜き
+・ジェラール最終皇帝女と相性良し</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>・すり抜けで余計なジュエル消費
+・ジェラール代償ダメージはマイターン外で扱いづらい
+・さら追加はアタッカー更新で迷いどころ</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>・厄ガチャ
+・ビクトール
+・ジェラール
+・ムくちゃ確定
+・すり抜け
+・女神ガチャ判断</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=885IFH-UUMA</t>
+        </is>
+      </c>
+      <c r="J300" s="2" t="inlineStr">
+        <is>
+          <t>885IFH-UUMA</t>
+        </is>
+      </c>
+      <c r="K300" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】無尽塔48階から　過去の自分を乗り越えろ！【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔48階に挑戦するも排水なしでは耐えきれず
+アルドラの運用法を試行錯誤、回復連携が課題
+アーミック試用で2ターン目以降の火力上昇を確認</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>・赤ネサス女神は防御軽減でほぼ無敵
+・アーミックは2ターン目以降の火力が優秀
+・ミルザは思った以上に強かった</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>・48階は排水なしだと攻撃回数多くて耐えられない
+・アルドラはBP像攻撃でHPがきつい
+・セフェルマルカーは合う合わないが激しい</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔48階
+・排水ひらめき
+・アルドラ運用
+・アーミック検証
+・赤ネサス女神
+・セフェルマルカー対策</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BGp3qAhtZSQ</t>
+        </is>
+      </c>
+      <c r="J301" s="2" t="inlineStr">
+        <is>
+          <t>BGp3qAhtZSQ</t>
+        </is>
+      </c>
+      <c r="K301" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　アルドラ　この性能、どう活かす？　使いこなす運用法考察</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>アルドラのターミン戦用編成を試行錯誤で考察
+ウィルやアイスで回復を挟む構成が必要
+本来は1番初手で動かすのがベストと結論</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>・アルドラは原営との相性は良い
+・ウィルの原影が強力で使いやすい
+・アイス・ターミンの回復量があれば編成可能</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>・1番初手で動かさないと火力カストしきれない
+・ターン終了時回復量が不足してメイン火力が出ない
+・BP像攻撃を撃つ敵だと戦法が破綻</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>・アルドラ運用考察
+・ターミン戦編成
+・HP回復連携
+・セフェルマルカー対策
+・BP補助</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HgQ74jU0qJ8</t>
+        </is>
+      </c>
+      <c r="J302" s="2" t="inlineStr">
+        <is>
+          <t>HgQ74jU0qJ8</t>
+        </is>
+      </c>
+      <c r="K302" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>ガンダム50周年について色々話す 【Gジェネエターナル】『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>ガンダム50周年でシードフリーダム0劇場公開決定
+実写映画やファースト リマスター計画も発表
+ウイングガンダム新規映像でGジェネへの参戦に期待</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>・シードフリーダム0の制作は順調
+・ウイング系の本格参戦が望める
+・実写は監督が原作リスペクト発言で安心</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>・実写化はドラゴンボール的失敗の不安が残る
+・リマスターはゲーム側に大きな動きが期待しにくい
+・ファースト実写化の可能性で評価が割れそう</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>・ガンダム50周年
+・シードフリーダム0
+・ガンダム実写映画
+・ファーストリマスター
+・ウイング新規映像</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SLAO1CCQX-A</t>
+        </is>
+      </c>
+      <c r="J303" s="2" t="inlineStr">
+        <is>
+          <t>SLAO1CCQX-A</t>
+        </is>
+      </c>
+      <c r="K303" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>#ロマサガRS　完全体めがみあかねさすで超鉄壁で敵涙目</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>女神に赤ネサスを継承して防御軽減率91%到達
+パーティ全員80%超でセフェルマルカー無効化
+最終ゲージは全力オートでクリア完遂</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>・8回行動で防御軽減91%は驚異的
+・セフェルマルカーの攻撃が全く通じない
+・最終ゲージを全力オートで攻略可能</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr"/>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>・女神スタイル
+・赤ネサス継承
+・防御軽減率91%
+・セフェルマルカー攻略
+・鉄壁編成</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8rwFJn-JvGE</t>
+        </is>
+      </c>
+      <c r="J304" s="2" t="inlineStr">
+        <is>
+          <t>8rwFJn-JvGE</t>
+        </is>
+      </c>
+      <c r="K304" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】なぜ今「陰属性」なのか？ダメージ＆軽減率のグラフが示す強みと課題【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>陰属性キャラの火力と防御軽減をグラフで可視化
+サラ・ノエル・サルインが100億級のアタッカー
+ターミン・ジェラールが防御軽減で必須級と分析</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>・サラの火力100億級は他属性比でも飛び抜けている
+・ターミン・ジェラールはほぼ必須級の防御性能
+・ノエルは自前バフで使いやすい</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>・陰属性は防御軽減役と火力役の両立が難しい
+・サブアタッカー枠が弱く穴になる
+・サラはAJ系継承を受けられないのが弱点</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>・陰属性考察
+・火力グラフ
+・防御軽減率
+・ジェラル必須級
+・ノエル評価</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tJXTUQtjVPY</t>
+        </is>
+      </c>
+      <c r="J305" s="2" t="inlineStr">
+        <is>
+          <t>tJXTUQtjVPY</t>
+        </is>
+      </c>
+      <c r="K305" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ガチャ絶不調...絶対に欲しいと思っていたキャラを追った結果...【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>アルドラ狙いで闇落ちミルザ編ガチャに突撃
+ステップ5まで爆死し優勝ジュエル4万円分投入
+結局150連天井までアルドラは出ず交換に</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>・バルバラのソフィア似イラストは好印象
+・ペット2匹引き当てた点は嬉しい
+・ミルザ・バルバラはコンプ達成</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>・ステップ5までピックアップ1体も出ず爆死
+・4万円課金しても本命アルドラはすり抜け
+・ガチャ周期が悪く調子最悪、ハフ前にジュエル枯渇懸念</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>・闇落ちミルザガチャ
+・アルドラ狙い
+・天井突破
+・課金優勝ジュエル
+・ガチャ調子の波</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=T_AY900cA7o</t>
+        </is>
+      </c>
+      <c r="J306" s="2" t="inlineStr">
+        <is>
+          <t>T_AY900cA7o</t>
+        </is>
+      </c>
+      <c r="K306" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】条件次第では特効性能⁉︎ミルザ厄・めがみガチャ性能チェック&amp;キャラランク評価【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>ミルザ厄・女神編4キャラの性能を詳細解説
+陰特攻の女神とミルザ陽デバフ注意キャラと評価
+注目は条件で本領発揮する女神スタイル</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>・アビスミルザは陰行で全体火力バフ強力
+・女神はライトオブポラリスで味方サポート優秀
+・詩人は陽攻撃続けることでバフ重複し優秀</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>・アルドラはHP満タ条件と代償ダメで編成テクニック必要
+・ミルザは陽攻撃でデバフ入る注意点あり
+・ドロレスは全体火ダメ軽減なく防御面手薄</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>・アビスミルザ
+・アルドラ性能
+・女神スタイル
+・詩人陽バフ
+・ドロレス回復
+・キャラランク評価</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sXkzNiNbZFI</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr">
+        <is>
+          <t>sXkzNiNbZFI</t>
+        </is>
+      </c>
+      <c r="K307" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「めがみ 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>ロマフェス女神編 女神・詩人・ドロレスを考察
+女神は陰特攻、詩人は陽パキースタイル評価
+3体ともB+評価で尖った性能と判定</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>・女神は陰属性敵相手に高い余ダメ・能力バフが優秀
+・詩人は陽攻撃継続で重複バフが強力
+・ドロレスはマイターン6回HP回復でヒーラー性能高い</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>・女神は陰属性敵限定でピンポイント運用
+・詩人は陽属性編成必須で運用条件が分かりづらい
+・ドロレスは継承前提でロマパス所持者向け</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>・ロマフェス女神編
+・女神スタイル考察
+・詩人陽パキー
+・ドロレス横範囲火力
+・継承候補</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=syqP9jhcL14</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="inlineStr">
+        <is>
+          <t>syqP9jhcL14</t>
+        </is>
+      </c>
+      <c r="K308" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】現行イベントが2R制の時の過ごし方で差が開く!?微課金プレイヤー向けの過ごし方【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>現行イベ2R制時は当社の看門を周回が効率的
+ロマパス上級必須だが育成ブースト同等で時短
+ビクトール・ノエル等の青龍向け編成を紹介</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>・看門周回はイベント育成プラスと同じブースト適用
+・ビクトール技さで青龍を高速周回可能
+・魂レベル次第で技に時短も可能</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>・ロマパス上級必須で微課金以下は恩恵薄い
+・1日3000周しかできない上限がきつい
+・現行イベが2R制だと育成プラスは最短11秒で非効率</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>・2R制イベ攻略
+・当社の看門周回
+・ロマパス上級活用
+・青龍周回編成
+・微課金向け効率</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EuVZnMex4bE</t>
+        </is>
+      </c>
+      <c r="J309" s="2" t="inlineStr">
+        <is>
+          <t>EuVZnMex4bE</t>
+        </is>
+      </c>
+      <c r="K309" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K309"/>
+  <dimension ref="A1:K315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20768,6 +20768,426 @@
         </is>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】無尽塔最上層「崩れない壁」ハイレベル耐久の立ち回りと編成→46層樹の将魔&amp;47層ゼラチナスマター突破!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔46層「樹の将魔」と47層「ゼラチナスマター」の立ち回りと編成解説。
+ノエル超火力短期決戦案や、ベア+ゲラール+皇帝女+ネメシスのダメブロ耐久案を提示。
+排水なし手持ちで200ターン耐久してクリア可能と確認、ただし運要素が強い構成。</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>・ノエル使用なら20〜40ターンで撃破可能
+・ベアのパリーで単体攻撃をほぼ受け切れる
+・ネメシスは状態低下なら12%回避を確保
+・魂アビリティなしでもやりくり可能で再現度高い
+・皇帝女の確定回避でフラワーサンクチュアリと連携</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>・46層は直接攻撃ではダメ通らずアタッカー選択が狭い
+・200ターンかかりタイムは長く何度は低め
+・魂アビなしだとデバフ蓄積が必要で運要素強い
+・ゲラールはステルス継承前提で被弾事故リスクあり
+・BP管理と白皇帝女の打ち直しタイミングが事故要因</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔46層攻略
+・47層ゼラチナスマター
+・魂アビリティ運用
+・ダメブロ耐久編成
+・ベア/ネメシス活用
+・フラワーサンクチュアリ</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gEcpNvioSrA</t>
+        </is>
+      </c>
+      <c r="J310" s="2" t="inlineStr">
+        <is>
+          <t>gEcpNvioSrA</t>
+        </is>
+      </c>
+      <c r="K310" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19T01:07:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】無尽塔45階から　過去の自分を乗り越えろ！【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>ミルザ編・女神編ガチャ配信→無尽塔45層挑戦のロング配信。
+ミルザ・女神を運良く確保しアルドラはHP満タン制約で扱いにくいと評価。
+女神に「打続のハニアボール」を継承させて排水なしで236ターン耐久撃破。</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザの追撃カウンターが想定以上に強力
+・女神は防御強化＋ハニアボールで実質排水級の耐久
+・無尽塔45層を排水なしで撃破できた発見
+・ビクトールは集会・レイドで時短性能が抜群
+・アルベルトのBP回復継承が編成の鍵に</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>・アルドラはHP満タン連マ縛りで実戦は使いにくい
+・アルドラはBP15要求で1ターン目しかフリップが撃てない
+・バルバラは活躍場所が見えず使い道が不明
+・ハニアボール編成は1戦200ターン超で動画映え悪い
+・女神は火力が低く弱点突かないと厳しい</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザ編/女神編ガチャ
+・アルドラ使用感検証
+・無尽塔45層挑戦
+・女神＋ハニアボール耐久
+・ビクトール集会適正</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Fjj4lFr-2QY</t>
+        </is>
+      </c>
+      <c r="J311" s="2" t="inlineStr">
+        <is>
+          <t>Fjj4lFr-2QY</t>
+        </is>
+      </c>
+      <c r="K311" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19T01:07:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】本番　優秀なキャラはいるのか？新キャラチェックしよう！【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS本番(終盤)配信、新キャラの優秀さをチェックする雑談ライブ。
+ミルザ編・女神編のガチャ性能と運用感を雑談ベースで紹介。
+配信者は新キャラを軽く触り使用感を述べる構成。</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>・新キャラの性能傾向を初見にもわかりやすく解説
+・女神は無尽塔含めて汎用性が高そう</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>・本番（終盤）ガチャは引き渋りされやすい時期</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>・新キャラチェック
+・ミルザ編評価
+・女神編評価
+・初見歓迎ライブ</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=u8IRZcIYgec</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="inlineStr">
+        <is>
+          <t>u8IRZcIYgec</t>
+        </is>
+      </c>
+      <c r="K312" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19T01:07:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】無尽塔44　アン・ルー　倒す</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔44層アンルーの撃破配信、雪だるま継承が思わぬキーマンに。
+単発バラ撒きガチャでバルバラのみ確保、女神は引けず嘆く。
+アンルー戦は全員オバドラ化のフローズンキャンディ戦法で攻略成功。</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>・フローズンキャンディの全体オバドラが想像以上に強力
+・雪だるま継承で全員オバドラ化が実現
+・バルバラを編成すると火力が体感アップ
+・ターミンのBP援護で火力面が安定
+・AJ+リラ+最終皇帝女の組み合わせが幻闘場で機能</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ単発バラ撒きで女神を引けず
+・アルドラ未所持でアンルー戦が苦戦
+・アルベルト未所持で他コンテンツも詰みやすい
+・螺旋回廊のロマパス報酬が労力に見合わない
+・サルーイン神刊は手持ちが揃わず攻略難航</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔44層攻略
+・アンルー戦
+・フローズンキャンディ戦法
+・雪だるま継承
+・バルバラ単独確保
+・サルーイン神刊挑戦</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fPnphT0bbYM</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="inlineStr">
+        <is>
+          <t>fPnphT0bbYM</t>
+        </is>
+      </c>
+      <c r="K313" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19T01:07:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今の1位はやはりあのキャラ！最新版ガチャ確保ランキング【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>最新版ガチャ確保優先度ランキング（17スタイル）を発表する解説動画。
+1位はジェラールアビス、続いてサラ、ビクトール、復刻最終皇帝女、女神。
+現状コンテンツ不足で「無理して引かなくてもいい」と冷静な助言も。</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>・ジェラールアビスはOD2倍ばら撒きで2位リラ超え
+・サラは1ターン目から最強級アタッカー火力
+・ビクトールは集会・レイドで唯一無二の時短性能
+・最終皇帝女＋完全体ミドで96%軽減を達成
+・女神は赤刺し前提で98%軽減のトップクラス耐久</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>・ジェラールアビスはLP消費でセフェルマルカーと相性悪
+・アルドラはHP満タン制約でセフェルマルカー適性低
+・今は新規高難度がなく強キャラを取っても使い所がない
+・主人/詩人は陽属性編成専用でピンポイント過ぎる
+・コンテンツが記憶再戦の更新だけで満足度が低い</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ確保優先度
+・ジェラールアビス
+・ビクトールお兄様
+・復刻最終皇帝女
+・女神編評価
+・アルドラ評価</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Acc0X-VZy1k</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="inlineStr">
+        <is>
+          <t>Acc0X-VZy1k</t>
+        </is>
+      </c>
+      <c r="K314" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19T01:07:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】アビスキャラは引くべき？ジェラール厄・サラ厄ガチャキャラランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>アビスジェラール/サラ編ガチャの最終評価ショート動画。
+アビスジェラールを星3、ビクトールを特機戦力に評価。
+汎用火力バッファーとしてアビスジェラールが筆頭のおすすめ。</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>・アビスジェラールはOD満タン＋エクストラフォース1.75倍が強力
+・ビクトールはエフェクト速度＋40ヒットで周回・レイドに最適
+・アビスジェラールの技を継承して無尽塔で最終皇帝女と強相性
+・集会キャラ未所持ならビクトールは強くおすすめ
+・サラはアビス落ち後の火力が高水準で攻撃枠として使える</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>・レオンは打突軽減率が低く新鮮味に欠ける
+・レオニードはリラ同様無尽塔以外で出番が薄い
+・トーマスは攻防バランス型で振り切り不足
+・サラは代償ダメージで高難度では味方への負担あり
+・アビスジェラールはLP消費でキャラ選びを要求される</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ最終評価
+・アビスジェラール星3
+・ビクトール特機戦力
+・無人島継承活用</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cVAYRyjOCz0</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="inlineStr">
+        <is>
+          <t>cVAYRyjOCz0</t>
+        </is>
+      </c>
+      <c r="K315" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19T01:07:29Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K315"/>
+  <dimension ref="A1:K322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21188,6 +21188,478 @@
         </is>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋560階「ギミック解明速報」!!〇〇無効!?カウンター!?強烈コンボで全滅…その対策はサガドラクエタクトコラボ!?VSジュエルビースト　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>螺旋560階「ジュエルビースト」のギミック解明速報。
+属性攻撃を吸って火力アップ＋4ターン目強烈コンボに注意。
+短期決戦＋エレメント系不採用＋ノエル添えで攻略可能。</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>・3ターン以内の短期決戦が一番簡単
+・AAすみれ・源などエレメント系不採用スタイルが有効
+・ノエルを添えればもっとスッキリ倒せる
+・カタリナ・最終皇帝男のカウンターは連撃を止められる
+・イバラチョコレートのコンティニュー仕様で攻略可能</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>・4ターン目のコンボで個人防御低い者がやられる
+・敵のメインウェポンが属性攻撃を吸って強化されてくる
+・ファイナルカタストロフを撃たれると無理くり収めるしかない
+・属性削減すると火力が下がり採用しづらい</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋560階
+・ジュエルビースト
+・ギミック解明
+・属性吸収
+・短期決戦</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5r249xT2xgg</t>
+        </is>
+      </c>
+      <c r="J316" s="2" t="inlineStr">
+        <is>
+          <t>5r249xT2xgg</t>
+        </is>
+      </c>
+      <c r="K316" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20T01:07:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始229日目　黎明　未来を見据えた施策</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣プレイ229日目の進捗報告。
+新キャラ3体獲得・徳川/毛利編成を中心に強化中。
+列伝イベは反省、次回に向け経験値を貯めて備える。</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>・毛利元清は毛利家強化の要として強そう
+・蒲生氏郷で織田・豊臣の複合タイプを強化できる
+・本多忠勝は壁役として重宝（無効化が大きい）
+・視聴者コメントが非常に勉強になった（特別史跡・四天王採用など）
+・全国制圧率3.4％まで到達し順調に拡大中</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>・列伝イベ13399位と振るわず毛利育成が遅かった
+・戦力が前回15万6000から14万2000に低下
+・覚醒できないキャラ（村上武吉・羽柴秀吉など）が多い
+・九州・近畿・北陸・大阪が取れておらず制圧率が伸び悩み
+・毛利照元の弓は範囲は広いが感覚が長く扱いづらい</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>・信長の野望出陣
+・プレイ進捗
+・毛利元就育成
+・列伝イベ反省
+・経験値温存</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_mib8Yye4Zg</t>
+        </is>
+      </c>
+      <c r="J317" s="2" t="inlineStr">
+        <is>
+          <t>_mib8Yye4Zg</t>
+        </is>
+      </c>
+      <c r="K317" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20T01:07:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>＃ロマサガRS ヴィクトール無限流し斬り集</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>ヴィクトールの新スタイル「無限流し斬り」連撃集動画。
+超高速モーションと多段ヒットの演出を披露。
+短尺で技演出を見せるだけの紹介クリップ。</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>・ヴィクトール新スタイルの連撃モーションが映える</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr"/>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>・ヴィクトール
+・新スタイル
+・流し斬り
+・連撃演出
+・クリップ集</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=08DvSAdiSyw</t>
+        </is>
+      </c>
+      <c r="J318" s="2" t="inlineStr">
+        <is>
+          <t>08DvSAdiSyw</t>
+        </is>
+      </c>
+      <c r="K318" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20T01:07:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】決着をつけよう・・ドラクエVS闇落ちロマサガ軍団！！4大ガチャランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>ドラクエタクト2種＋闇落ちロマサガの4大ガチャランキング。
+1位ノエル編、2位カタリナ編、3位ジェラール編、4位サラ編。
+復刻ない闇落ち軍団を確保推奨、サラは復刻待ちでOK。</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>・ノエルはダークドレアの圧倒的火力＋37ヒットで超アタッカー
+・カタリナは反撃スタイル最高クラスで継承元としても優秀
+・ミド君は技4回行動＋EX3倍で性能・継承ともに最強級
+・トールは9回行動＋防御90％超で過去最高のオールラウンダー
+・ジェラールは2体にEXフォース2倍配布で配信中サブアタッカー以上
+・ビクトールはレイドで1分10秒台を狙える超大当たり
+・ヌビーはEXボス1.62倍＋直接/間接攻撃の希少枠で優秀</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>・サラは避弾必要で初ターン全力できず全体防御権0が穴
+・ジェラールはLPダメ等のデメリット盛り
+・ビクトールの自己バフ重視型は全体防御49％しか出ず穴
+・レオニードは刺さる場所が限定的で活躍場面が狭い
+・サラ天井は復刻あるためジュエル消費的に見送り推奨</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>・4大ガチャランキング
+・ノエル
+・カタリナ
+・ジェラール
+・ビクトール
+・復刻判断</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=H6ouVfbhW7Q</t>
+        </is>
+      </c>
+      <c r="J319" s="2" t="inlineStr">
+        <is>
+          <t>H6ouVfbhW7Q</t>
+        </is>
+      </c>
+      <c r="K319" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20T01:07:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】危険閲覧注意！7年間ガチャを引き続けた結果、遂に攻略法を見つけました【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>ミルザアビス編ガチャ後半戦の実況レポート。
+5万ジュエル課金からスタートし女神＋ドロレスを確保。
+ステップ7到達前にコンプ達成、節約ガチャで大勝利。</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>・ステップ6到達前にコンプ達成、節約ガチャ大勝利
+・女神スタイルの翼イラストが魅力的で確保できて嬉しい
+・ドロレスは闇属性周りで面白い運用が見込める
+・ステップ5以内でドロレス・女神・バニー等が引き当てに成功
+・光・闇の対立環境で女神を確保できたのは大きい</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>・直近のガチャ調子が悪く5万ジュエル課金で補填
+・ドロレスは性能的に強いとは言えない
+・ドロレスは毎ターン自身HP70％消費が痛体
+・前回ミルザアビスでアルドラを最後まで引けず物欲センサー</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザアビスガチャ
+・女神スタイル
+・ドロレス
+・ステップガチャ
+・節約コンプ</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6qcqG8LxPCM</t>
+        </is>
+      </c>
+      <c r="J320" s="2" t="inlineStr">
+        <is>
+          <t>6qcqG8LxPCM</t>
+        </is>
+      </c>
+      <c r="K320" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20T01:07:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】ジェラール能力値早見表~今すぐゲットせよ‼️めちゃ強い！(◎_◎;)まだ間に合う！！</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>ジェラール（アビス版）の能力値早見表まとめ。
+自身火力＋偶数ターン全体EXフォースODが破格性能。
+締切間近、スルー気味の人も急いで確保推奨。</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>・攻撃強化3000％＋EXフォース4倍＋火力バフ2800％で破格火力
+・偶数ターンに地震以外の味方全体へEXフォースOD2倍配布が強力
+・クワトロS＋ダS2回で8回行動と高い手数
+・AJ（オートジェネレーター）との相性が良い
+・実装から日が経った今も大活躍中の性能</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>・技攻撃時の代償ダメージ＋代償LPが痛体
+・技さんは自身LP2消費でLP上限から2回しか打てない
+・デスのLP回復補助術が地震以外しか効かず代用不可</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>・ジェラール早見表
+・アビス版
+・EXフォースOD2倍
+・8回行動
+・確保推奨</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B3ml9LiqYH8</t>
+        </is>
+      </c>
+      <c r="J321" s="2" t="inlineStr">
+        <is>
+          <t>B3ml9LiqYH8</t>
+        </is>
+      </c>
+      <c r="K321" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20T01:07:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋回廊560階「ジュエルビースト」を攻略！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>螺旋回廊560階「ジュエルビースト」の攻略動画。
+ヒート連打を中心とした編成でクリアを確認。
+BGM中心の実プレイ映像で立ち回りを共有。</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋回廊560階ジュエルビーストの攻略に成功
+・ヒート火力で押し切る編成例を提示</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr"/>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋560階
+・ジュエルビースト
+・クリア報告
+・ヒート編成</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jX788MbebfM</t>
+        </is>
+      </c>
+      <c r="J322" s="2" t="inlineStr">
+        <is>
+          <t>jX788MbebfM</t>
+        </is>
+      </c>
+      <c r="K322" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20T01:07:55Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K322"/>
+  <dimension ref="A1:K330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21660,6 +21660,556 @@
         </is>
       </c>
     </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ハーフアニバ前夜祭!!「闇堕ち」ラストは!?やはり〇〇様…からのオトモはこの子たち　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>ハーフアニバ前夜祭の暦読み編4話ガチャを予想。
+前中後編で1コンセプト、闇堕ち＆光の傾向が継続。
+最有力はサラ、ジュディ＆セルマ、西王の3体を提示。</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>・過去主人公の重複出現を抑える運営方針を評価
+・ラストガチャの譲渡ターミン仕様に期待感</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>・昨年型の主人公差し込みは不評だったと指摘</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>・ハーフアニバ前夜祭
+・暦読み編ガチャ予想
+・闇堕ちキャラ
+・サラ予想
+・ジュディ&amp;セルマ
+・西王</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_KQ0DkAopQY</t>
+        </is>
+      </c>
+      <c r="J323" s="2" t="inlineStr">
+        <is>
+          <t>_KQ0DkAopQY</t>
+        </is>
+      </c>
+      <c r="K323" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21T01:30:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　螺旋回廊560　AJなし編成の可能性　DOコラボ限定編成で突撃</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>螺旋回廊560をAJなしDOコラボ限定編成で攻略。
+編成はカタリナ・ウィル・ノエル・コテ男・ルビーで挑戦。
+運要素ありつつも6ターン前後で勝利、ノエル補助技推奨。</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>・カタリナ・ウィルのカウンターと火力が高く2億超え
+・DOコラボ限定編成でも6ターンで勝利可能
+・スイートローズヒール装備が事実上必須でほぼ確実
+・幻統武器でもベルの火力は十分強力</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>・ジュエルブラスターが異常に強く壊滅しがち
+・ポーション/コーションのタイミングがランダムで読みづらい
+・ノエル無補助だと火力不足になりやすい
+・1ターン目はOD溜まりにくく構成が苦しい</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋回廊560攻略
+・AJなし編成
+・DOコラボキャラ
+・ジュエルブラスター対策
+・ポーション運ゲ
+・ノエル補助技</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rBr0UJhWjoU</t>
+        </is>
+      </c>
+      <c r="J324" s="2" t="inlineStr">
+        <is>
+          <t>rBr0UJhWjoU</t>
+        </is>
+      </c>
+      <c r="K324" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21T01:30:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】あの組み合わせがつよい！AJ＆ノエル抜き編成もあり！螺旋560階攻略【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>螺旋560をAJ・ノエル抜き編成4種で攻略紹介。
+AJ代替にロックブーケ＆ジェラール組が刺さると解説。
+4ターン討伐ペースで、ロック武器のレプテ重ねが鍵。</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>・AJ&amp;ノエル軸は依然として最強で4ターン討伐可能
+・ロックブーケ&amp;ジェラルでもAJ無し攻略が成立
+・最終コテ男のレディアントセイバーが反撃で優秀
+・難易度が手応えあって楽しいバトル</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>・ファイナルカタストロフは状態異常対策しても通用しない
+・ジュエルブラスターは防御強化必須レベルに痛い
+・AJ無し編成はターン火力が露骨に厳しくなる</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋560階攻略
+・AJ&amp;ノエル抜き編成
+・ロックブーケ&amp;ジェラール
+・ジュエルウォール対策
+・5ターン本気化
+・弱点1.75倍バフ</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=L0ifGo2TM3U</t>
+        </is>
+      </c>
+      <c r="J325" s="2" t="inlineStr">
+        <is>
+          <t>L0ifGo2TM3U</t>
+        </is>
+      </c>
+      <c r="K325" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21T01:30:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋 560 攻略　その後　無尽塔45　倒す</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>螺旋560を運も味方に「やおち」気味にクリア報告。
+その後無尽塔45階に挑戦するが火力不足で討伐失敗。
+排水アビリティ持ちキャラ育成と22日ガチャを展望。</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋560はギミック理解前でも勝ててしまう作り
+・ハニュアウォール&amp;排水持ちは女神級に強い
+・ノエルに排水が付けば無敵級と評価
+・ミドが現状ナンバー1アタッカーと推す</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔45階はHP多すぎ・火力不足で実質討伐不可
+・ロックブーケ系の無敵級耐久に打開策なし
+・技道場の初回ひらめき率が低くストレス
+・レオニードは性能的に使いどころが薄い印象</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋560攻略後雑談
+・無尽塔45階挑戦
+・排水アビリティ育成
+・22日ガチャ予想
+・ジュエルビースト考察
+・技道場</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0waC6TelIMY</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="inlineStr">
+        <is>
+          <t>0waC6TelIMY</t>
+        </is>
+      </c>
+      <c r="K326" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21T01:30:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】最強火力軍団結成？螺旋回廊560階を初回攻略！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>螺旋回廊560をAJ・ノエル・ミド等で初回火力攻略。
+4ターン以内討伐で本気化前に倒す押し切り戦法を解説。
+前半は手加減し3〜4ターン目に火力集中が成功の鍵。</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>・7415ジュエルの月給に喜び、運営の継続的に給料アップ
+・カタリナはギミック相性が良すぎる接待性能
+・ミドが自己強化型で実質アタッカー級の火力
+・ジェラールのバフが火力底上げに大貢献</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>・熱・冷・雷・陽属性は攻撃するほど敵バフが入る罠仕様
+・ジュエルブラスターが非常に厄介
+・OD連打で本気化が早まる制約あり
+・4ターン目の攻撃を食らうと確実に全滅</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋560初回攻略
+・火力ゴリ押し編成
+・本気化タイム制限
+・ジュエルブラスター
+・OD回数で発動タイミング変化
+・カタリナ&amp;カウンター</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5UIL_C5y9ZY</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="inlineStr">
+        <is>
+          <t>5UIL_C5y9ZY</t>
+        </is>
+      </c>
+      <c r="K327" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21T01:30:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】遂にくるぞ！闇堕ちガチャ後編の主役はあの大本命キャラ！？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>暦読み編第4話後編ガチャを大予想する企画動画。
+陽属性持ち＆魔王設定から本命は「西王アビス」と断言。
+お供はパウルスバッサーとロアールでSS3体シングル予想。</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>・闇堕ちアビス系キャラは性能盛られて強い傾向
+・西王のイラストに大期待でジュエル全ベット価値あり
+・ハーフアニバ前は運営が課金を引き出す豪華ガチャを出す</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>・メインストーリー絡みでガチャ予想がここ最近全然当たらない
+・ロマサガ運営に「全野祭ガチャ」が無くなりつつある流れ
+・イベントごとのストーリー展開が読みづらい</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>・暦読み編第4話後編予想
+・西王アビス本命
+・陽属性闇堕ち法則
+・ハーフアニバ前ガチャ
+・SS3体シングル予想
+・パウルスバッサー&amp;ロアール</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B9Ujuc3fA_8</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="inlineStr">
+        <is>
+          <t>B9Ujuc3fA_8</t>
+        </is>
+      </c>
+      <c r="K328" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21T01:30:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはり闇堕ちキャラは強キャラ確定！？サラ編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>闇堕ちサラ編ガチャの新SS3体の性能チェック動画。
+サラはA威力32ヒットの純アタッカーで陽残熱に強い。
+レオニード・トーマスは器用貧乏でハーフアニバ前は様子見。</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>・闇堕ちサラはA威力32ヒットでカンスト火力出しやすい
+・サラの本気化後は陽残熱の3属性弱点を取りやすい
+・ジェラール&amp;サラのアビス系は陰耐性+15%の恩恵あり
+・トーマスは打突列7発全体強化で打突編成では便利</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>・レオニードはエクスフォース倍率低く接待戦以外は活躍薄め
+・トーマスは器用貧乏で防御も火力も上位互換が存在
+・サラはAJと2コス被りで併用できないのが残念
+・サラの本気化は5発受けないと発動せず待機型で噛み合い悪い
+・ハーフアニバ前なのでダブルガチャは引きづらく見送り推奨</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>・サラ闇堕ち編ガチャ
+・サラ性能評価
+・レオニード白爵
+・トーマス槍サポーター
+・ハーフアニバ前の貯金
+・看貫武器運用</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=t50N7M8PRFo</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="inlineStr">
+        <is>
+          <t>t50N7M8PRFo</t>
+        </is>
+      </c>
+      <c r="K329" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21T01:30:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【ガチャ動画】めがみじゃない！？【No.608】</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>暦読み編女神ガチャを150連覚悟で気合い回し。
+途中で詩人やイスカンダール等のすり抜けを引きつつ進行。
+約90〜100連で本命の女神を引き当て大満足の結果。</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>・女神を約90連で引けて大満足
+・詩人やイスカンダールのすり抜けがイラスト含めかっこいい
+・GB持ちなので女神は絶対確保ラインの神性能</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>・詩人は性能イメージが薄く採用に困る
+・ハーフアニバ前で残ジュエルが心許なく追いガチャは厳しい
+・ミルザを追加で引きたいが2万5千ジュエルで足踏み</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>・女神ガチャ150連
+・暦読み編GB
+・すり抜け詩人
+・ハーフアニバ前貯金
+・ミルザ追加検討</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jUB2fs4JneY</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="inlineStr">
+        <is>
+          <t>jUB2fs4JneY</t>
+        </is>
+      </c>
+      <c r="K330" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21T01:30:00Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K330"/>
+  <dimension ref="A1:K346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22210,6 +22210,1082 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】引くべき「陰時代の軸」3体分の強さ聖王厄!!ハーフアニバ前にとんでもなスタイルをぶち込んで来た…!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>聖王厄は陰時代の軸となるぶっ壊れ性能
+無限バフ+デバフ+ODB補填の2.5人分働き
+ハーフアニバ前に過去最強級のSS降臨</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>・聖王厄は2.5人分の働きをするぶっ壊れ性能
+・デバフ性能が過去最強級で前捨て1000%が見える
+・ODやBPを5ターン補填できる
+・陰時代の主軸として確保必須
+・10ターンで火力補正1.5万%級</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>・過去の楽院持ちはどれもいまい
+・他2体が片々の性能の可能性が高い</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>・聖王厄
+・陰時代の軸
+・無限バフ
+・デバフ性能
+・ハーフアニバ</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=J46kAxVUOZU</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="inlineStr">
+        <is>
+          <t>J46kAxVUOZU</t>
+        </is>
+      </c>
+      <c r="K331" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「※修正版」3体最終ランク付け!!陰強化の申し子!!状態異常解除がプラスされた最新ヴァンパイアレディの使い勝手を考える　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>ヴァンパイアレディは状態異常解除付き
+汎用A・特攻Sだが個人火力はそこそこ
+3体ガチャは陰時代主軸として石吸われる</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>・状態異常解除持ちで唯一無二の活用
+・ダークミラージュで全体極勝回復+BP+5
+・防御87%と最高峰に迫る伸び
+・全ステバフ解除&amp;回数限定回避が優秀
+・5ターン丸ごと回避はぶっ壊れ性能</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>・味方全体への火力補正値はラウンドまたがず超いまい
+・全体へのサポートは超いまいで低評価
+・特化した強さがなく使いどに困る
+・追撃が出ないように対策されて残念
+・個人火力のパンチは弱め</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>・ヴァンパイアレディ
+・状態異常解除
+・陰時代
+・オールラウンダー
+・ハーフアニバ</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=a2qBNoxt9lw</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="inlineStr">
+        <is>
+          <t>a2qBNoxt9lw</t>
+        </is>
+      </c>
+      <c r="K332" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「全部やる」だがエクストラ2倍!!ロロの使い勝手はどこ!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>ロロはエクストラ2倍&amp;BP+15の支援猫
+防御86%&amp;全体サポート充実の便利キャラ
+副産物としては取っておきたい優秀SS</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>・エクストラウィーク1.25倍を永続維持
+・最大BP+15と1ターン+11のBP補給
+・防御81-90%と環境最高峰
+・全体サポートが充実し複数役割こなす
+・サービスガチャで石を集めやすい</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>・自身の火力はほぼゼロ
+・エクストラ項目が最近のスタイルと被りやすい
+・パンチが弱く火力中心の打線討伐では使いづらい
+・無人島適正がない
+・スロースターターでエクストラ2倍を活かしにくい</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>・ロロ
+・エクストラ2倍
+・全体サポート
+・防御性能
+・BP増加</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=o9fU28PthrM</t>
+        </is>
+      </c>
+      <c r="J333" s="2" t="inlineStr">
+        <is>
+          <t>o9fU28PthrM</t>
+        </is>
+      </c>
+      <c r="K333" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「聖王厄降臨」黒猫も組み合わせてセーラー〇〇ンコラボ開始!?いやいやハーフアニバ前夜祭で限定〇〇配布だと!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>聖王厄降臨速報・黒猫ロロも組み合わせ実装
+セーラー○○ンコラボ風の予想動画
+ハーフアニバ前夜祭で限定配布の話題</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>・ハーフアニバ前夜祭で限定配布の期待</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr"/>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>・聖王厄降臨
+・黒猫ロロ
+・ハーフアニバ前夜祭
+・限定配布
+・コラボ予想</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=u4hAyTsoymw</t>
+        </is>
+      </c>
+      <c r="J334" s="2" t="inlineStr">
+        <is>
+          <t>u4hAyTsoymw</t>
+        </is>
+      </c>
+      <c r="K334" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】引きたい奴が俺にはいる！　ガチャ　今から引きに行こうか！【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>ジェラール狙いでガチャ実施・絵がかっこいい
+サラの火力が異常に強いと話題
+聖王厄イベ周回をビクトール等で高速化</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>・サラの火力がぶっ壊れで異常に強い
+・ジェラールの絵がかっこいい
+・ビクトールのモーションが早く周回向き
+・アレツ・ニセギュス共にワンパン可能
+・サラはSSとして単純に強い</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>・ジェラールは自称ダメージが気になる
+・ジェラールは無人島・HP満タに合わない
+・新しいレオンは微妙な性能
+・トーマスは火力があまりなさそう
+・防御強化量が低めで今後きつい</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ実施
+・ジェラール
+・サラ火力
+・周回検証
+・ビクトール</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OPXyBa41cck</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="inlineStr">
+        <is>
+          <t>OPXyBa41cck</t>
+        </is>
+      </c>
+      <c r="K335" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】無尽塔48階から　過去の自分を乗り越えろ！【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔48階と螺旋560階のギミック挑戦
+聖王1点狙いガチャ予定&amp;AJ周回紹介
+配信終盤は酔った視聴者との雑談に脱線</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>・聖王1点狙いでいて困ったことがない
+・AJを使うと螺旋がかなり楽になる
+・加藤を記憶再戦にぶっ込んで活用</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋560階のギミックが分かりづらい
+・ジュエルアビスが2ターン目に来ると厄介
+・コラボキャラだけで周回するとかなりきつい</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔48階
+・螺旋560階
+・聖王1点狙い
+・AJ周回
+・ハーフアニバ</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qw-YVoUzxiQ</t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="inlineStr">
+        <is>
+          <t>qw-YVoUzxiQ</t>
+        </is>
+      </c>
+      <c r="K336" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】聖王が闇堕ち！？5月22日更新情報まとめ 【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>5月22日からこよみ編4話後編キャンペ
+聖王アビス・ロロ・ヴァンパイアレディ実装
+7.5周年63連チケットも事前集めへ</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>・聖王闇落ち姿が興奮する性能
+・聖王アビスは絶対取りに行きたい
+・63連チケットガチャ2回実行可能
+・ドレインアクス+連達追加で使える期待</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr"/>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ編後編
+・聖王アビス
+・ガチャ更新
+・7.5周年
+・63連チケット</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TrlGn_SUpPw</t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="inlineStr">
+        <is>
+          <t>TrlGn_SUpPw</t>
+        </is>
+      </c>
+      <c r="K337" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】聖王【厄】は絶対欲しい！＋オマケ有 『こよみ編 第4話 後編 公開記念 Romancing祭 聖王厄編』【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>聖王アビス編ガチャを60連回して挑戦
+ピック爆死もヴァンパイアレディは確保
+おまけのドラクエタクトアセルス1凸成功</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>・['ヴァンパイアレディが確保できた', 'アセルスは1凸できた', '聖王アビスは絶対取る案件', 'ヴァンパイアレディはイラストパワーが高い']</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>・60連でピック0でへこむ爆死
+・最近ガチャ引きが本当に良くない
+・聖王アビス本命取れず
+・ステップ7天井しないと困る展開
+・下ぶれすぎで爆死パターン</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビスガチャ
+・ヴァンパイアレディ確保
+・爆死
+・ドラクエタクトコラボ
+・アセルス</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YLq0l5g5OeI</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="inlineStr">
+        <is>
+          <t>YLq0l5g5OeI</t>
+        </is>
+      </c>
+      <c r="K338" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】絶対ヤバいアビス聖王爆誕！驚愕の公式先行情報確認！ハーフアニバ目前【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>螺旋560階のジュエルアビス攻略解説
+聖王アビス・ロロ・ヴァンパイアレディ実装
+陰の3体パーティ完成で次回が楽しみ</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>・3属性攻撃のロロは現環境に刺さる
+・ヴァンパイアレディはオールラウンダー期待
+・陰の3体パーティで完成度が高い
+・63連SS3体確定チケットが楽しみ
+・聖王アビスの闇落ち演出が良い</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋560階は歯ボがないと火力ゴリ押し以外難しい
+・5ターン以内のODが5回超えると発狂</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋560階攻略
+・聖王アビス
+・ロロ性能
+・ヴァンパイアレディ
+・ハーフアニバ</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=49VgDsGyb6c</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="inlineStr">
+        <is>
+          <t>49VgDsGyb6c</t>
+        </is>
+      </c>
+      <c r="K339" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】陰の時代来る！？性能詰め込みすぎ聖王＆鉄壁ロロに万能ヴァンパイアレディ！ハーフアニバーサリー前に強烈すぎる件【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>聖王ロロヴァンパイアレディの性能解析
+陰3体は環境必須級ではないが優秀
+ハーフアニバ被るので即引きせず様子見</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>・ロロは防御90%超で殺人ドロー使える
+・ロロはODBサポート充実で優秀
+・聖王は連続性時代来た時にハマる可能性
+・ヴァンパイアレディは継承で防御極大化
+・陰3体パーティでジュエルアビス対応可能</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>・聖王は使いづらそうな印象
+・ロロは7回避弾できるか未確定
+・ヴァンパイアレディは火力が低め(20億)
+・ハーフアニバと期間被るので即引き非推奨
+・聖王の防御は30%しかなく硬くない</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビス
+・ロロ性能
+・ヴァンパイアレディ
+・陰属性編成
+・ジュエルアビス対策</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Uh8rpzNaUd4</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr">
+        <is>
+          <t>Uh8rpzNaUd4</t>
+        </is>
+      </c>
+      <c r="K340" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】それでも手に入れたい闇落ちスタイルがあるんだぁぁぁぁーーー！！まさに災厄編ダブルガチャ課金限界突破【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>災厄編ダブルガチャを課金で限界突破
+ビクトール・レオン・サラはなんとか確保
+ジェラール狙いで追加課金してジェラ確保</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトールとレオンの親子が早めに確保
+・追加課金でジェラールを無事確保
+・サラはまだ天井圏内で交換可能
+・サラはSSとして単純に強い
+・30連で2体引けて引きは良い方</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>・大目当てジェラールが当初出ずに苦戦
+・ピックアップから抜ける確率が高い
+・ノーピック演出が連発で爆死気味
+・追加課金はきつい
+・180連使ってもサラは取れず</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>・災厄編ダブルガチャ
+・ジェラール狙い
+・課金限界突破
+・サラ確保
+・ビクトール</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=alhSU2tfB1k</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr">
+        <is>
+          <t>alhSU2tfB1k</t>
+        </is>
+      </c>
+      <c r="K341" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】超やりこんだ完全攻略螺旋560階！簡単クリア方法解説全７編成【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>螺旋560階ジュエルアビス攻略解説
+奇数偶数ODの行動回数ギミック紹介
+短期/中期/長期7編成のクリア例提示</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>・AGは最高の特攻で本当にあるとなんとかなる
+・ノエルがいれば押しできる
+・カタリナも押しの上で良かった
+・ルビー軸ロックブーケ軸は使いやすい
+・ビクトール+ジェラール編成は早くて落ちない</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>・ファイナルカタストロフでほぼ落ちる鬼畜仕様
+・AGやノエル無いと5ターン以下クリア困難
+・ジュエルブラスターで大体何か落ちる
+・OD回数の累計ターン差がギミックで難しい
+・アタッカーで防御権0は取らない傾向で対策しづらい</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋560階
+・ジュエルアビス攻略
+・OD回数ギミック
+・AG特攻
+・編成例7種</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nIXpywulgus</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="inlineStr">
+        <is>
+          <t>nIXpywulgus</t>
+        </is>
+      </c>
+      <c r="K342" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】周年直前に覇権キャラ実装！？闇落ち聖王が遂にきてしまった...【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>5月22日聖王アビス・ロロ・ヴァンパイア実装
+7.5周年直前の闇落ち聖王に大注目
+予想動画で聖王アビス的中の発表会</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>・闇落ち聖王が遂に実装され注目
+・新武器闇斧で強キャラ感が漂う
+・周年直前ガチャは強い説あり
+・63連SS3体確定チケット最大3回引ける
+・予想動画で聖王アビスを的中</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>・ジュエルをかさいに来ている告知の流れ
+・63連チケットは期間限定で集めにくい</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビス実装
+・7.5周年直前
+・闇斧新武器
+・63連チケット
+・予想発表会</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=s6_maWLT_78</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="inlineStr">
+        <is>
+          <t>s6_maWLT_78</t>
+        </is>
+      </c>
+      <c r="K343" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭聖王厄編ガチャ評価 #ロマサガRS #shorts #ガチャ</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭聖王厄編ガチャ評価shorts
+動画は音楽中心で字幕は取得不可
+タイトルから聖王厄ガチャ評価動画と推測</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr"/>
+      <c r="F344" s="2" t="inlineStr"/>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>・Romancing祭
+・聖王厄編
+・ガチャ評価
+・ショート動画</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dnUiIHs7M0M</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="inlineStr">
+        <is>
+          <t>dnUiIHs7M0M</t>
+        </is>
+      </c>
+      <c r="K344" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】ヴァンパイアレディ能力値早見表〜これは…アントニウスで活躍⁉️推しキャラ＋陰属性フォース付与キャラ降臨✨</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>ヴァンパイアレディ能力値早見表を解説
+全体運用と単体運用の違いを紹介
+陰属性フォース1.62倍は過去最強級</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>・技術系1.62倍フォースは過去最強級の付与
+・軽減75%でターン状態解除あり
+・陰属性弱点の移動戦で活躍可能
+・全体運用なら攻撃強化3555%
+・ライバルがいない汎用性の高いフォース</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>・単体20ヒット運用より全体10ヒット運用優位
+・AJほどの活躍は難しい
+・1.75倍ではなく1.62倍で控えめ</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>・ヴァンパイアレディ
+・能力値早見表
+・陰属性フォース
+・全体/単体運用
+・アントニウス活躍予想</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=z7WB1EMhPBk</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="inlineStr">
+        <is>
+          <t>z7WB1EMhPBk</t>
+        </is>
+      </c>
+      <c r="K345" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベント解説、要注意点有り‼️、ダメチャレ全力オート編成の紹介、周回編成の紹介【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>暦読み編4話後編ブラインド閉ざされた光
+63連ガチャチケット63枚集める注意点
+ダメチャレ300億全力オート編成紹介</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>・63連ガチャ最大3回引けるチャンス
+・祈りの血実でフィールド効果が強化される
+・ダメチャレ300億は救済難易度
+・AJ継承+ノエル編成で全力オート可能</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>・63連ガチャチケットを期間内63枚集めないと引けない
+・稀ドロップで集めにくい
+・上限集めないと天井交換も難しい</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>・新イベント解説
+・63連ガチャチケット
+・ダメチャレ300億
+・全力オート編成
+・祈りの血実</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QefC6wj5i2Q</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr">
+        <is>
+          <t>QefC6wj5i2Q</t>
+        </is>
+      </c>
+      <c r="K346" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22T13:15:00Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K346"/>
+  <dimension ref="A1:K357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23286,6 +23286,764 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「聖王【厄】引く」厄ランク総決算!!更なる無尽塔対応スタイルたち!!9体3ガチャランキング!!最新スタイル比較検討会→2026年5月23日版　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>ハーフアニバ前の聖王厄含む9体ランキング解説
+詩人と女神は無尽塔適性高く確保推奨
+ミルザは仕上がっておらず微妙との判断</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>・詩人は無尽塔適性が高くお得
+・女神はワントップアタッカー精度が高い
+・聖王はイン継承で唯一無二
+・石人の全体火力底上げが強い
+・ビューネイは天稟更新で回避力高い</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>・バルバラは継承だけ強く性能ガタガタ
+・ミルザは仕上がっておらず使いづらい
+・ゲラールは離脱早く戦力にならない
+・ドロレスの横範囲回復は実用性薄い
+・レディは追撃できず火力貢献低い</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>・聖王厄評価
+・無尽塔適性
+・詩人と女神
+・ミルザ評価
+・キャラランキング</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KRi_XRdD2ag</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr">
+        <is>
+          <t>KRi_XRdD2ag</t>
+        </is>
+      </c>
+      <c r="K347" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「引く決意」ハーフアニバ前なのに引くぞ!!俺は無尽塔を遊びたいんだ!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>ハーフアニバ前に詩人と女神狙いガチャ実施
+天井到達で詩人と女神を確保、ドロレス断念
+ステップ踏まず無償石を温存して撤退判断</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>・無償石を節約して撤退判断良好
+・詩人と女神を確保できた
+・聖王はすり抜けで取得ラッキー</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>・詩人ばかり被って効率悪い
+・ドロレス確保はコスパ悪く諦め
+・バンパイアレディも撤退対象</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ実況
+・詩人と女神確保
+・天井到達
+・ステップ判断
+・ハーフアニバ前</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=s6a4Lm32NZs</t>
+        </is>
+      </c>
+      <c r="J348" s="2" t="inlineStr">
+        <is>
+          <t>s6a4Lm32NZs</t>
+        </is>
+      </c>
+      <c r="K348" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　ロロ　万能か、中途半端か？　実際にパーティに入れて見た結果・・・</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>ロロをセフィルマルカ戦で実戦テスト
+7回避弾の条件達成は難しいが3回までは強力
+火力貢献は低いがBP・OD回復は優秀</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>・BP回復とODゲージ上昇が優秀
+・ロロの防御強化量は高い
+・AJ検定合格で火力大幅上昇
+・ODゲージ取れた時の恩恵がでかい</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>・ロロは火力貢献が低く中途半端
+・7回避弾の発動条件が厳しすぎる
+・編成的に組みづらい
+・余ダメージが低くアタッカーには不向き</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>・ロロ実戦検証
+・セフィルマルカ戦
+・7回避弾条件
+・BP回復
+・ODゲージ</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2u_5O_Mwx78</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="inlineStr">
+        <is>
+          <t>2u_5O_Mwx78</t>
+        </is>
+      </c>
+      <c r="K349" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　聖王　強敵が骨抜きに・・・　美しき吸血鬼と挑む！</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>聖王とバンパイアレディでセフィルマルカ攻略
+デバフが強烈でセフィルマルカがミスを起こす
+3ゲージ目は連携で発狂するため2連携が安定</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>・聖王のデバフ量が圧倒的
+・セフィルマルカがミスするレベルのデバフ
+・バンパイアレディがアタッカー級の火力
+・聖王の自己回復量が大きい
+・LP攻撃をミスさせられる</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>・3ゲージ目は連携で発狂しやすい
+・聖王の継承技の選択肢が乏しい
+・ダメージ量の調整が難しい
+・序盤の仕上がりが遅い</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビス検証
+・バンパイアレディ
+・セフィルマルカ戦
+・デバフ過多でミス発生
+・回避が最大の防御</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LVNDTdVUTQU</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="inlineStr">
+        <is>
+          <t>LVNDTdVUTQU</t>
+        </is>
+      </c>
+      <c r="K350" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今引くべきか・・三大ガチャランキング！ハーフアニバーサリー前に選択を迫られる【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>ハーフアニバ前3ガチャ評価、1位は聖王編
+聖王はインパ極めるなら必須クラスの性能
+基本は温存推奨、主人公インド軍団確認後検討</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>・聖王は環境支配級の可能性あり
+・ロロは超高難度向け超優秀
+・バンパイアレディの1.62倍付与が貴重
+・ミルザはインパに刺さる
+・詩人は導きシリーズで強い</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>・ロロの7回避弾条件は今の図鑑では難しい
+・ミルザは編成柔軟性が低い
+・女神はデスメタルソウル継承ほぼ必須
+・今すぐ引かず温存推奨
+・ミルザは脱げないのが弱点</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>・三大ガチャランキング
+・聖王1位評価
+・インパ編成
+・ハーフアニバ前温存
+・ロロ評価</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WlMn5pJTee0</t>
+        </is>
+      </c>
+      <c r="J351" s="2" t="inlineStr">
+        <is>
+          <t>WlMn5pJTee0</t>
+        </is>
+      </c>
+      <c r="K351" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ロロ、教えてくれ。私は後何度ガチャを回せばいい？ガチャは私に、何も言ってはくれない。【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>聖王アビスガチャを爆引き
+聖王・ロロ・バンパイアレディの3体狙い
+天井近くまで使うが配布石でコンプ確定</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>・3体コンプ確定で勝ち
+・螺旋回廊報酬で無償石が膨れた
+・5/29からハーフアニバ生放送決定で楽しみ
+・聖王神引きで取得できた</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>・演出薄いのに高レアばかりですり抜け多発
+・ロロ3連続で被るなど運悪い
+・土日に新スタイル使えないのは残念
+・石の消耗が想定以上</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>・聖王ガチャ実況
+・天井到達
+・コンプ確定
+・5/29ハーフアニバ生放送</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=smx7UIDnILc</t>
+        </is>
+      </c>
+      <c r="J352" s="2" t="inlineStr">
+        <is>
+          <t>smx7UIDnILc</t>
+        </is>
+      </c>
+      <c r="K352" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】超重要お知らせもチェック！イベント周回とスコアバトル【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>新イベント「ブラインドされた光」攻略解説
+スコアバトル300億で聖王アビスマント獲得
+5/29ハーフアニバ生放送決定で盛り上がる</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>・聖王闇落ちストーリーが面白い
+・スコア300億は手持ちでも余裕
+・ハーフアニバ生放送決定でテンション上昇
+・ゲスト発表が嬉しい
+・湧き出す魔獣8で11秒周回可能</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>・イベント自体はいつも通りでつなぎ感
+・新規プレイヤーには300億ハードル高め
+・ハーフアニバ前で本番ではない</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>・イベント周回
+・スコアバトル
+・聖王アビスマント
+・ハーフアニバ生放送
+・ストーリー考察</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SDPaqjX4VEE</t>
+        </is>
+      </c>
+      <c r="J353" s="2" t="inlineStr">
+        <is>
+          <t>SDPaqjX4VEE</t>
+        </is>
+      </c>
+      <c r="K353" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>友情崩壊の危機？収録後にサンゾーとFUMIYAが大喧嘩！？【TARLESS NEXT2】</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>ドローム社案件、TARLESS NEXT2新フレーバー紹介
+ヘーゼルナッツジェラートとチョコレート塩を試飲
+30%割引クーポン「サンゾネクスト」配布</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>・チョコレート塩が濃厚で美味しい
+・ヘーゼルナッツジェラートも好評
+・ニコチン・タール0で安心
+・自動吸引でコスパ良い
+・感謝祭で30%OFFクーポン提供</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr"/>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>・TARLESS NEXT2
+・新フレーバー試飲
+・ニコチンタール0
+・30%割引クーポン
+・感謝祭</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tuRW9Q2LwFo</t>
+        </is>
+      </c>
+      <c r="J354" s="2" t="inlineStr">
+        <is>
+          <t>tuRW9Q2LwFo</t>
+        </is>
+      </c>
+      <c r="K354" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはりあのキャラは確保必須⁉︎聖王厄ガチャ性能チェック&amp;キャラランク評価【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>聖王厄ガチャ3体の性能とランク評価
+聖王アビスはインパ編成のリーダー枠で確保推奨
+大週ハーフアニバ控えステイ推奨</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビスはインパ編成のリーダー枠
+・デバフ量がお手本のような邪魔
+・バンパイアレディは火力バフが豊富
+・ロロはBP・OD回復強力
+・聖王はバフ解除&amp;デバフ付与が貴重</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>・ロロは7回避弾条件が厳しい
+・ハーフアニバ前なのでステイ推奨
+・ヒット系アビリティの条件難易度高め
+・バフが少ない場面では出番少なめ</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビス性能評価
+・バンパイアレディ性能
+・ロロ評価
+・ハーフアニバ前ステイ</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xslvo54TnLk</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="inlineStr">
+        <is>
+          <t>xslvo54TnLk</t>
+        </is>
+      </c>
+      <c r="K355" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第121回アントニウスの井戸〜最適解パーティ徹底考察‼️〜👊ランク上位を目指そう👊</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>第121回アントニウスの井戸最適解編成考察
+残属性無効のため陰属性アタッカー中心
+聖王アビスのデバフが高HP敵で大活躍見込み</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビスはデバフで大活躍可能性
+・サラのアビスバージョンが強い
+・新女神は2ターン戦で88%軽減が優秀
+・バンパイアレディは1.6倍フォースバフが貴重
+・ターミン・飯はまるかは継続活躍見込み</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>・剣の最角で残属性が全く通用しない
+・属性体制盛り以上の厄介ギミック
+・アントニウス本体HPが螺旋の3倍想定
+・雪だるまも置物気味の運用</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>・アントニウスの井戸
+・剣の最角
+・陰属性編成
+・聖王アビス活躍予想
+・螺旋510回</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MJwxcI1daBc</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr">
+        <is>
+          <t>MJwxcI1daBc</t>
+        </is>
+      </c>
+      <c r="K356" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「聖王[厄] 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>聖王アビス編3体のスタイル徹底考察
+聖王はA-、ロロはA-、バンパイアレディはB評価
+ハーフアニバ前で温存もアリ、見極め推奨</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>・聖王は2スタイル分の能力で過去最高クラス
+・ロロは超高難度で攻撃倍率2倍まで上昇
+・聖王の術参断光の効果が強力
+・バンパイアレディのBP+15は便利
+・陰属性に追い風の環境</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>・聖王の火ダメ軽減30%は心もとない
+・バンパイアレディは別スタイルで代替可能
+・ロロは7回攻撃前提でないと本領発揮できず
+・術参断光は通常聖王に継承不可
+・今すぐ入手の必要性は薄い</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビス考察
+・バンパイアレディ評価
+・ロロ評価
+・ランク付け
+・ハーフアニバ前判断</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=f34LMyPVoVo</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="inlineStr">
+        <is>
+          <t>f34LMyPVoVo</t>
+        </is>
+      </c>
+      <c r="K357" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K357"/>
+  <dimension ref="A1:K368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24044,6 +24044,763 @@
         </is>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ハーフアニバ「ぶっ壊れ」は来る!?過去の傾向から来る可能性を徹底予測!!周年のガチャ回し立ち回りを考える会　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>過去の傾向からハーフアニバの「ぶっ壊れ」を予測する回。
+結論：周年でも環境変化スタイルは2体程度、毎月コンスタント。
+貯めても意味薄く、来たタイミングで都度狙うのが基本。</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>・エスパー女の棒立ち75%で防御の積み上げ不要に
+・ストーミー/フロスティが防御の幅を広げた
+・司令やアーニャが現環境の基礎を築いた
+・毎月コンスタントに肝になるスタイルが来る環境</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>・ハーフアニバまで石を貯める意味はあまりない
+・執年スタイル全部取る昔の遊び方は不要
+・ノエルにカウンターは付かないので無理狙いは禁物</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>・ハーフアニバ予測
+・ぶっ壊れ傾向
+・ガチャ厳選術
+・周年立ち回り
+・過去スタイル整理</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B13ZXsf6lCc</t>
+        </is>
+      </c>
+      <c r="J358" s="2" t="inlineStr">
+        <is>
+          <t>B13ZXsf6lCc</t>
+        </is>
+      </c>
+      <c r="K358" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26T01:08:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】まずは倒して満額狙え!!「井戸アントニウス」ギミック詳細!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>井戸アントニウスのギミック詳細解説と編成披露。
+残属性排除＋OD連打、または間接攻撃編成が要点。
+今回80万止まりでランクインは厳しいとの所感。</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>・ジェラールはOD2倍要因として有効
+・イシス/マイスのEFばら撒きが便利
+・ターミトでBP配って動きやすい
+・ブーケのデバフで被ダメ抑制可能</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>・手持ち的に2ターンには収まらない
+・80万点ではランクイン難しい
+・ジェラルの代償ダメージが大きい</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>・井戸アントニウス
+・ギミック解説
+・残属性排除
+・間接攻撃編成
+・OD連打</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_K3IHlf5OYY</t>
+        </is>
+      </c>
+      <c r="J359" s="2" t="inlineStr">
+        <is>
+          <t>_K3IHlf5OYY</t>
+        </is>
+      </c>
+      <c r="K359" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26T01:08:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始235日目　鍛錬　名刀を追い求めて</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣プレイ235日目の進捗ライブ。
+新キャラ3体入手、戦力15.9万、Lv88、制圧率3.5%。
+名刀鍛錬を本田忠勝に集中、低レベル武将育成方針へ転換。</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>・本田小松は回復持ちで耐久編成に強そう
+・名刀鍛錬は歩く分だけ稼げて面白い
+・視聴者助言で低レベル枠育成に変えて楽に
+・プレイヤーLvが順調に1週1上昇ペース</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>・天下争覇の柿崎軍が強すぎて伸び悩み
+・前回の列伝イベは育成遅れで失敗
+・九州方面の制圧率が低く0%が多い
+・巻物18万ボーダーはきつめ</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>・信長の野望出陣
+・名刀鍛錬
+・天下争覇
+・制圧率
+・武将育成
+・コメント返信</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=q5J4yI2HkQo</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr">
+        <is>
+          <t>q5J4yI2HkQo</t>
+        </is>
+      </c>
+      <c r="K360" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26T01:08:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】イベントの告知来ねぇ、、 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナルの月末告知が来ない件の雑談動画。
+CDW0079ストーリーかタワーイベントが来るはずと予想。
+31日更新で今のガチャ/イベが終わるので何かしらは確実。</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>・アップデートでタワー階層スキップ可能に
+・大規模攻略戦・強敵集来も既に実装済
+・月末は限定ユニット実装が恒例</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>・5月末予定のCDW0079ストーリーが告知無し
+・サンダーボルト第1回もずれ込んだ前例あり
+・運営の動きが見えず不安</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・月末告知遅延
+・クロスディメンション
+・タワーイベント
+・限定ユニット予想</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QnypnvZykik</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="inlineStr">
+        <is>
+          <t>QnypnvZykik</t>
+        </is>
+      </c>
+      <c r="K361" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26T01:08:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】超激早！もう待てない！7.5周年セレチケ交換予習【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年セレチケ交換の予習（精査中シート公開）。
+直近1年実装の継承軸スタイルをS〜B評価で多数紹介。
+デコレーションツリー/Vチョコ/聖王継承などをS級に。</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>・デコレーションツリー継承はターミシでS級
+・Vチョコレートメロトセロイは最前線でS
+・フリーデンシュベルトで軽減率81%まで上昇
+・聖王の継承先「勝利の小墓」が一択級
+・リアンセイバー継承新工程男はSランク
+・パートランド双剣劣化はフィニッシャー級</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>・アルティメットミドは1月実装で交換不可
+・リラは最近性能が飲まれ気味で優先度低下
+・グランドクロスは継承制限で交換無意味
+・クリスマスキャッチは個人的には未使用</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>・セレチケ予習
+・継承推奨
+・ロマパス併用
+・Sランク継承
+・周年立ち回り</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pi7VSQk87G4</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr">
+        <is>
+          <t>pi7VSQk87G4</t>
+        </is>
+      </c>
+      <c r="K362" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26T01:08:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>【スマグロ】ひたすら鍛えるのみ　27日のドラクエ発表楽しみ♪</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>スマグロ（ドラクエ系スマホゲー）育成配信の雑談回。
+27日のドラクエ新情報・巨人阿部監督逮捕などコメント返信。
+締めのガチャ40連はロト3が出ず大爆死で打ち切り。</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>・ロト装備が揃うと完璧で楽しみ
+・レモンスライムはドロップが強い
+・スタミナ消化で着実にレベルアップ</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ40連で星7が1個も出ず爆死
+・スマホがフリーズ気味で動作が重い
+・ドラクエ12の発表は厳しそうな雰囲気
+・ガチャ7%表記が体感より渋い</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>・スマグロ周回
+・ドラクエ12発表期待
+・雑談配信
+・ロト装備集め
+・ガチャ爆死</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=88Ti5jhIsOw</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="inlineStr">
+        <is>
+          <t>88Ti5jhIsOw</t>
+        </is>
+      </c>
+      <c r="K363" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26T01:08:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】最優先案件アリ！最新版ガチャ確保優先度【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年直前、最新版ガチャ確保優先度ランキング。
+聖王アビスを最優先、メガロ・アルドラを優先度高に。
+他は中以下、29日の周年発表まで待つのが基本方針。</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビスはデバフ量が異常で最優先
+・陰属性編成で使うと火力底上げが凄い
+・アルドラはOD1.75倍で便利屋として優先度高
+・メガロは敵攻撃回数次第で高難度に刺さる</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>・アルドラはセフェルマルカー戦と相性最悪
+・ドロレスは無理して取る必要なし
+・ミルザは陰特化で汎用性低め
+・周年前なのでガチャ全般に石を使いにくい</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>・確保優先度
+・聖王アビス評価
+・ハーフアニバ前判断
+・陰属性編成
+・ガチャ厳選</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=20QKVH10zvE</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr">
+        <is>
+          <t>20QKVH10zvE</t>
+        </is>
+      </c>
+      <c r="K364" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26T01:08:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】時代の覇者が復活！？新聖王が率いる新生陰属性編成【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>聖王アビスを軸にした新生陰属性編成で螺旋560回攻略。
+ミルザ/ジェラル/バートランド/聖王/ロックブウブゲ編成。
+AJ無しでも余裕クリア、聖王アビスのデバフが圧倒的。</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビスのデバフがバグレベルで強烈
+・AJ無しでも陰属性編成は十分火力出る
+・バートランド継承双剣劣化が化け物火力
+・ミルザのカウンターでダメージ稼げる
+・6ターン程度でフィニッシュ可能</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>・聖王だけ弱体破りで大ダメージを受ける謎挙動
+・ジュエルビーストは奇数ターン火力が通りにくい
+・聖王の闇斧はこのボスでは意味なし</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>・陰属性編成
+・螺旋回廊560回
+・ジュエルビースト
+・聖王アビス検証
+・AJなしクリア</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ynqs-8PHpMQ</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr">
+        <is>
+          <t>ynqs-8PHpMQ</t>
+        </is>
+      </c>
+      <c r="K365" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26T01:08:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年前ガチャ引くべき？ミルザ厄・めがみガチャキャラランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年前ガチャのキャラランキング動画。
+1番おすすめは女神、サポーター注目はバルバラ。
+ドロレスは星1、他のミルザ/詩人/アルドラ等は星2。</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>・女神は陰特攻＆置物バフで万能に活躍
+・バルバラはステバフ・デバフの総合力が高い
+・ミルザアビスは陰アタッカー＆カウンター持ち
+・詩人は陽の導きバフで陽編成で活躍</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>・ドロレスはHP回復以外目立たず星1止まり
+・アルドラは代償ダメージが重く扱いにくい
+・詩人は属性編成必須で汎用性低い
+・ミルザアビスは陽攻撃でデバフ反転の事故あり</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャランキング
+・女神おすすめ
+・バルバラ評価
+・ミルザアビス考察
+・アルドラ運用</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=X8jmH-yKaRw</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr">
+        <is>
+          <t>X8jmH-yKaRw</t>
+        </is>
+      </c>
+      <c r="K366" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26T01:08:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】2026年5月下旬ガチャ総まとめ！全12スタイル引くべきスタイルランキング！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>5月下旬実装ガチャ全12スタイルのティアランク総評。
+最優先該当なし、有用ランクに女神と聖王アビスを配置。
+ハーフアニバ前で全体的に控えめ評価との見立て。</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>・女神は陰特攻バッファーで最有用ランク
+・聖王アビスは欲張りスタイルで邪魔様要素強い
+・ドロレスは記憶再戦ヒーラーとして使える
+・ロロは超高難度適性が高いサポーター</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>・今回最優先該当なしで全体的に地味
+・バルバラは欠点ないが明確な長所も無い
+・バンパイアレディはEF付与スタイルに代替され気味
+・ミルザは2回制限と条件が厳しい
+・アルドラは70%代償ダメで万人向けでない</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>・ティアランク
+・ガチャ総まとめ
+・聖王アビス有用
+・女神有用
+・ハーフアニバ前</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_5knwzpHlvo</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr">
+        <is>
+          <t>_5knwzpHlvo</t>
+        </is>
+      </c>
+      <c r="K367" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26T01:08:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【スコアバトル】聖王[厄] 300億完全無課金編成、2,100億編成の紹介【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>スコアバトル聖王アビス、300億無課金編成と2100億編成紹介。
+祈りの血実5000個でフィールドアビリティ全解放が鍵。
+残攻撃メインで火耐性を上げ、防御バフ漏らさず維持。</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>・祈りの血実5000個で火力バフ1000%が解放
+・300億達成で副防具報酬が必ず取れる
+・ロマンシングショップ装備だけで無課金達成可能
+・AJにグレン撃継承で火力底上げ</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>・残耐性マイナスだと普通に壊滅する
+・新規・復帰勢には300億のハードルが高め
+・フィールド効果は被ダメ無効ではなく不便</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>・スコアバトル
+・聖王アビス攻略
+・祈りの血実
+・無課金編成
+・2100億編成</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=egSXxQdiwnA</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr">
+        <is>
+          <t>egSXxQdiwnA</t>
+        </is>
+      </c>
+      <c r="K368" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26T01:08:38Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K368"/>
+  <dimension ref="A1:K373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24801,6 +24801,343 @@
         </is>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】汎用めがみテンプレで「毒」を完封しセフェルマルカーを完結する!!詩人含めた陽シナジーの最高峰　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>女神編成（陽シナジー）でセフェルマルカーを12ターン完封。
+10ターン目から1000%超のステバフが自動発動し毒も防ぐ。
+女神は無人島アタッカーとしても最適と紹介。</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>・女神は無人島アタッカーとしても最適で爆発力より安定型
+・10ターン目から1000%超のステバフが自動発動して安定
+・メガミ＋ミドのバランスで12ターン安定クリア
+・詩人ターミンの固定値防御75%で鉄壁火力に
+・同じ行動しかしない敵なので何度でも勝てるテンプレ編成</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>・爆発力はなく現実的かつ確実な強さに留まる</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>・女神編成
+・セフェルマルカー
+・陽シナジー
+・無人島
+・ダメブロ蓄積</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LqwER8IMJgA</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr">
+        <is>
+          <t>LqwER8IMJgA</t>
+        </is>
+      </c>
+      <c r="K369" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27T01:05:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】やっと来た！5月31日イベント予告 #SDガンダムGジェネレーションエターナル ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>5月31日12時よりクロスディメンションW79が開催。
+報酬はガンダムPixie&amp;イフリートの2体1組コンビユニット。
+SR枠グラハムは物理射撃支援に最大射程アップが付く。</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>・コンビユニットは攻撃型でマップ兵器持ち
+・グラハムは物理射撃支援で射程6〜7まで届く可能性</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>・SSRの報酬ユニットがコンビ1組のみで寂しい
+・GJエタで早くもコンビユニット実装は意外</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・クロスディメンションW79
+・コンビユニット
+・グラハム
+・マップ兵器</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=39Lje8-Hsmo</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr">
+        <is>
+          <t>39Lje8-Hsmo</t>
+        </is>
+      </c>
+      <c r="K370" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27T01:05:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】やっと来た！5月31日イベント予告 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>5月31日からクロスディメンションW79開催を解説。
+報酬PixieEイフリートは2体1組のコンビユニットで攻撃型。
+ガチャの新限定枠の可能性に触れ29日30日の発表に期待。</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>・コンビユニットは攻撃型でマップ兵器持ち
+・グラハムを支援に乗せれば物理射撃の射程アップが優秀</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>・SSR報酬がコンビユニット1組のみで寂しい構成
+・PixieやイフリートをすでにメダルにしてしまったユーザーはイベントBで稼ぎづらい</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・クロスディメンションW79
+・コンビユニット
+・グラハム支援
+・ガチャ予想</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hgdk2ZVYeao</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr">
+        <is>
+          <t>hgdk2ZVYeao</t>
+        </is>
+      </c>
+      <c r="K371" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27T01:05:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>【スマグロ】ひたすら鍛えるのみ　27日のドラクエ発表楽しみ♪</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>スマグロ生配信で雑談しつつ女神と聖王ガチャを単発で引く。
+防具強化や30億ダメミッション、アントニウスの井戸を周回。
+5/27のドラクエ発表、5/29の公式生放送、5/31の聖王関連にも言及。</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>・単発ガチャで女神が引けて満足、女神編成は強い
+・フィールド効果で1465億ダメージまで一気に伸びた
+・女神のハニーアタックとダメブロ蓄積の組み合わせが優秀
+・聖王は唯一無二系で将来的に取っておくと良い
+・低課金で楽しめるのがロマサガRSの良い点</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>・アントニウスの井戸3段が硬く2段で妥協しがち
+・防具最大強化に必要な素材が周回1万2000個と過大
+・パチンコで桃鉄スロットを触り2万円負け
+・聖王の技マシンが術なので次の聖王に継承できなさそう
+・63連チケットなど告知不足で取り逃しそうになる</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>・スマグロ生配信
+・女神/聖王ガチャ
+・防具強化周回
+・アントニウスの井戸
+・30億ダメージミッション</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AMfRploz7fo</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr">
+        <is>
+          <t>AMfRploz7fo</t>
+        </is>
+      </c>
+      <c r="K372" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27T01:05:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第121回アントニウスの井戸〜‼️攻略‼️100位以内の~編成・立ち回り~👊全てお見せ致します👊</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>第121回アントニウスの井戸を50位以内の編成と立ち回りで攻略。
+マリス・ターミン・はまるか・AJ・サラビスイシスでベスト編成を紹介。
+メルティハートハットでアントニウスの一撃を防ぎ24手で38位達成。</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>・メルティハートハットが防具で被弾を防ぐ大活躍アイテム
+・23日の考察動画と同じ編成で1番の順位を更新
+・マリス＋ターミンの編成は50〜100位を安定して狙える
+・クリーミーリボンドレスの装着でさらに安定</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>・上位プレイヤーの編成はガラっと違うらしく未把握
+・今回の編成は作者のベストではない
+・カウンターを誘発しないようターミンの被弾位置に要注意
+・メルティハートハットは持っている人がかなり少ない</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>・アントニウスの井戸121回
+・メルティハートハット
+・50位以内攻略
+・クラウドシフト人系
+・魂のアビリティ</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Wasw68Zer8A</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr">
+        <is>
+          <t>Wasw68Zer8A</t>
+        </is>
+      </c>
+      <c r="K373" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27T01:05:16Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K373"/>
+  <dimension ref="A1:K376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25138,6 +25138,222 @@
         </is>
       </c>
     </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】確定!?7.5周年第1弾「はいネタバレ」さらにハーフアニバの日程を全予測しつつ八歌仙の実装スケジュールまで　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年生放送ゲストは江島さん、第1弾で黒エ確定予想。
+例年通り第5弾まで、毎週ダブルガチャ＋シングルで八歌仙8人実装と想定。
+主人公祭り化に不満が溜まり、ハフバはバランス重視で歴代主人公ちょい混ぜ予測。</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>・第1弾は黒エが確定濃厚で読みやすい
+・歴代RS主人公ローテで人気キャラ調整あり
+・例年通り第5弾まで続く豪華構成
+・シングル含むダブルガチャで八歌仙網羅</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>・主人公祭り化でユーザーの不満がじわじわ溜まっている
+・リアム実装のための祭りになっている感
+・当たらないキャラへの売上偏重が極端
+・暦読みは進行上来ないと予想され物足りない</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年ガチャ予測
+・八歌仙実装
+・黒エ確定
+・歴代主人公ローテ
+・主人公祭り不満
+・ダブルガチャ</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1p6RBIpfE-U</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr">
+        <is>
+          <t>1p6RBIpfE-U</t>
+        </is>
+      </c>
+      <c r="K374" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】技上　周回雑談【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>技揚げ道場終了でガチャプールがスカスカに、ハフバ前で減少が激しい。
+井戸戦メタルブラック対策、雷弱点でミルフィ不在を補う編成探しに苦戦。
+ビクトール・ノエル・気アチ・カタリナを試し、気アチ＋AJ＋ターミン構成が有力。</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>・気アチは連続攻撃回数が多く火力出る
+・ビクトールはゴルノバ系で雷ダメ伸びる
+・ノエル火力が断然高い
+・ホルネウスはカタリナと並んで井戸で良い
+・ハフバはダブル4連で盛り上がりそう
+・復帰勢が増えて活気がある
+・記憶再戦は毎日やる価値あり</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>・技揚げ道場がなくなって周回がしんどい
+・ガチャプールがスカスカで3体しか引けない
+・ミルフィ不在で井戸の編成が組みづらい
+・メタルアルカイザーHP600億予想で1ターン突破が必要
+・アルベルトは全体火力が乗らず厳しい
+・最新ディーバ未所持で詰む場面がある</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>・井戸戦予想
+・メタルブラック対策
+・雷弱点編成
+・ガチャプール激減
+・技揚げ道場終了
+・ハフバ準備</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Iu2UexVSicc</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr">
+        <is>
+          <t>Iu2UexVSicc</t>
+        </is>
+      </c>
+      <c r="K375" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】あと数日で激アツのハーフアニバが始まる！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年直前、アルベルト声優・浦田さん＋ふみさん3人で盛り上げ収録。
+ドラクエコラボでアルベルト＝ロト装備に感動、マーニャ予想やバンパイアアルディ愛も。
+第1弾は江島さん＝クロエ確定予想、新キャラ3人を1発実装も予測。</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>・ドラクエコラボのアルベルト＝ロト装備のイラストが最高
+・アビス編キャラの目下ペイントとビジュアルが素晴らしい
+・バンパイアアルディのイラストが毎回神懸かっている
+・アビス版ジェラール・サラが強い
+・公式生放送に江島さん登場で盛り上がる
+・ハフバは新キャラ3人一気実装で豪華になる可能性</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>・レリック連の周回が終わらず5個ずつではなく500個ずつにして欲しい
+・アビス編のガチャ間隔が短く財布が厳しい
+・猫アレルギーでローラの闇落ち版が引きにくい</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年期待
+・ドラクエコラボ感想
+・アビス編予想
+・第1弾ガチャ予想
+・声優トーク
+・公式生放送ゲスト</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=96qvFLk-9I4</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr">
+        <is>
+          <t>96qvFLk-9I4</t>
+        </is>
+      </c>
+      <c r="K376" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28T01:05:00Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K376"/>
+  <dimension ref="A1:K385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25354,6 +25354,611 @@
         </is>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】技上　周回雑談【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>技上残の最大火力挑戦、編成試行錯誤で2080億達成
+7.5周年公式生放送への期待、セレチケ予想と注意喚起
+家電雑談・井戸19手の凄さ・強化解除回避アビ評価</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>・ノエル軸の編成で2080億の最高記録達成
+・ビクトールが全てを解決する強力キャラ
+・強化解除回避アビは螺旋でも便利
+・井戸の19手到達は本当に凄い
+・セレチケがもらえるだけでありがたい</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>・セレチケ失敗で運営にごねるのはやめよう
+・マイスの代替が浮かばず変えづらい
+・DCモーター扇風機もモーター音が気になる商品あり</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>・技上残最大火力
+・7.5周年生放送
+・セレチケ予想
+・編成試行錯誤
+・強化解除回避アビ</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TWP2vdu7Hu4</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr">
+        <is>
+          <t>TWP2vdu7Hu4</t>
+        </is>
+      </c>
+      <c r="K377" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29T11:02:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始239日目　育成　眠りし力を呼び覚ます</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>信長出陣239日目、武将165体、新規6体追加
+列伝22到達、武田手持ち8体で後半は厳しい予想
+名感ボーナス30→40を目指す育成方針に切替</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>・神社で遠征移転免がもらえてかなり大きい
+・千鳥（始末さん）は対象タイプで悪くない性能
+・ご証3個取り目指せる手応え
+・天下波の補助コメで戦略改善の糸口</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>・武田武将が8体しかおらず後半きつい
+・第2第3編成の戦力不足で天下波順位伸びず
+・意縮付与の効果がよく分からない
+・勢力が単発単体だけでは上がりにくい</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>・239日経過
+・武田列伝22到達
+・九州茶室解放
+・名感ボーナス育成
+・神社遠征免</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Y5ZLNxJ7AKs</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr">
+        <is>
+          <t>Y5ZLNxJ7AKs</t>
+        </is>
+      </c>
+      <c r="K378" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29T11:02:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】イベント全然関係ないｗ 5月31日ガシャ予告！ 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>5/31ガチャはナイチンゲール限定支援型予告
+ニューガンダムWフィンファンネル装備型も追加
+開催中イベントとは一切関係ない逆襲のシャアMSV</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>・逆者MSVだけで攻撃・支援・耐久型が全部揃う
+・ハイニュー所持なのでナイチンゲールも揃えたい</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>・タワーイベントとガチャ内容が一切関係ない
+・ハイニュー復刻はなさそうで残念
+・アトラスやグレートジヨングで石を消費中</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>・5/31ガチャ予告
+・ナイチンゲール
+・ニューガンダムWFF
+・逆者MSV
+・100連回す予定</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3CdBQEdIAXU</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr">
+        <is>
+          <t>3CdBQEdIAXU</t>
+        </is>
+      </c>
+      <c r="K379" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29T11:02:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】イベント全然関係ないｗ 5月31日ガシャ予告！ #SDガンダムGジェネレーションエターナル ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>5/31ガチャはナイチンゲール限定支援型予告
+ニューガンダムWフィンファンネル装備型も追加
+開催中イベントとは一切関係ない逆襲のシャアMSV</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>・逆者MSVだけで攻撃・支援・耐久型が全部揃う
+・ハイニュー所持なのでナイチンゲールも欲しい</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>・タワーイベントとガチャ内容が一切関係ない
+・ハイニュー復刻はなさそうで残念</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>・5/31ガチャ予告
+・ナイチンゲール
+・ニューガンダムWFF
+・逆者MSV
+・ショート版</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=m03KquHcim4</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr">
+        <is>
+          <t>m03KquHcim4</t>
+        </is>
+      </c>
+      <c r="K380" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29T11:02:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】リリーナが報酬！タワーイベント開催予告！ 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>6/4からウエストタワー16-20回が開催予告
+報酬はURリリーナ（範囲回復スキル持ち）
+攻略済み階層をスキップできる神アップデート</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>・スキップ機能追加は異常に助かる神アプデ
+・範囲回復のリリーナは使いどころ多い
+・ダイヤ報酬がめちゃめちゃもらえる
+・報酬確認画面で何階で何貰えるか分かる
+・スキップでもちゃんと報酬がもらえる</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>・クロスディメンションだけで新規2枠は考えづらい</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>・タワーイベント16-20回
+・URリリーナ報酬
+・スキップ機能追加
+・範囲回復スキル
+・ウイング系参戦予想</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=n6YDKe5WN9A</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr">
+        <is>
+          <t>n6YDKe5WN9A</t>
+        </is>
+      </c>
+      <c r="K381" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29T11:02:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】報酬はリリーナ！タワーイベント開催予告！ #SDガンダムGジェネレーションエターナル ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>6/4からウエストタワー16-20回が開催予告
+報酬はURリリーナ（範囲回復スキル持ち）
+攻略済み階層をスキップできる神アップデート</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>・スキップ機能追加は本当に紙アップデート
+・範囲回復のリリーナは使いどころ多い
+・ダイヤ報酬がめちゃめちゃもらえる</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>・クロスディメンションだけで新規2枠は考えづらい</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>・タワーイベント16-20回
+・URリリーナ報酬
+・スキップ機能追加
+・範囲回復
+・ショート版</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wdC9B0ppenk</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr">
+        <is>
+          <t>wdC9B0ppenk</t>
+        </is>
+      </c>
+      <c r="K382" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29T11:02:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>【スマグロ】ラダトームの王女ガチャとりゅうおうマルチ</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>竜王マルチチャレンジが強すぎてソロは厳しい
+ロト剣極めれば新ガチャ不要、フレマルチで突破
+ドラクエ12の豪体システムと夢見る少女予想雑談</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>・ロト剣を極めれば新ガチャより全然強い
+・メタル剣あればメタル系狩りが楽になる
+・フレマルチで助けてもらえてクリア成功
+・ドラクエ12にダーク路線が来るのも面白い</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>・竜王マルチチャレンジが素人には難易度高すぎ
+・雑魚スライムでも20ダメ食らう敵火力
+・ジェムが足りずガチャを十分回せない
+・回復薬がないと罪なほど消費が激しい</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>・竜王マルチ
+・ロト剣強化
+・ラダトーム王女ガチャ
+・ドラクエ12豪体
+・フレンドマルチ</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-fmVy-C7kQs</t>
+        </is>
+      </c>
+      <c r="J383" s="2" t="inlineStr">
+        <is>
+          <t>-fmVy-C7kQs</t>
+        </is>
+      </c>
+      <c r="K383" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29T11:02:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはり大本命はこよみ！？激アツの7.5周年の内容を徹底予想【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>5/29メンテ後の7.5周年生放送と開幕ガチャを予想
+フーミン予想は暦読み新6人SS6体ガチャ
+サゾー予想はSS8体8%すり抜けなし祭り仕様</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>・ハーフアニバはジュエル配布も豪華で楽しみ
+・暦読みちゃんは大本命で性能注目
+・新主人公8人同時開幕なら祭り感あり
+・メンテ明けにライブ配信で盛り上げる予定</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>・今のRSは優しくなく第4弾まで分散の懸念
+・ありきたりなガチャは祭りらしくなくつまらない
+・メンテが23時までだと配信時間が削られる</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年生放送
+・暦読み編6人
+・SS8体ガチャ予想
+・すり抜けなし願望
+・開幕ライブ配信</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RQuwSadm-20</t>
+        </is>
+      </c>
+      <c r="J384" s="2" t="inlineStr">
+        <is>
+          <t>RQuwSadm-20</t>
+        </is>
+      </c>
+      <c r="K384" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29T11:02:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【ガチャ動画】7.5周年前に尽きる…！？【No.610】</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>暦読み4話後編記念ガチャを単発30連で挑戦
+たこ→ロロ狙い、くん→星王（セ王）狙い
+SS3体（バンパイアレディ等）出るが本命は来ず</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>・バンパイアレディは人外可愛いキャラで好き
+・SS3体出てよくも悪くも普通の相性
+・ハーフアニバ開始分のジュエルも当ガチャに使える</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>・本命のロロ/星王が出ず手応え薄い
+・ミルザはガチャ期限切れ間近で間に合わない
+・ジュエル残量がやばい状況</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>・単発30連
+・ロロ狙い
+・星王狙い
+・バンパイアレディ
+・7.5周年前ガチャ</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HFQiWwffrqU</t>
+        </is>
+      </c>
+      <c r="J385" s="2" t="inlineStr">
+        <is>
+          <t>HFQiWwffrqU</t>
+        </is>
+      </c>
+      <c r="K385" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29T11:02:33Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K385"/>
+  <dimension ref="A1:K397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25959,6 +25959,792 @@
         </is>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】関門速報「OD駆使したい!?」ゴールデンバウムを最速でぶっ倒したい6月の闘者の関門　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>6月闘者の関門ゴールデンバウム最速攻略の検証
+OD編成は12秒だが演出重く、8秒最速は不安定
+安定狙いは雪だるま+育成枠で見手戻しが無難</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>・雪だるま入れた育成枠でも安定して攻略可能
+・置き物編成はゴリゴリ揃えれば成立</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>・オーバードライブ編成は演出が重い
+・8秒最速のイシス無編成は安定しない
+・技には全然向かない難易度</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>・関門速報
+・ゴールデンバウム
+・OD編成検証
+・雪だるま編成
+・育成枠</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ffkzwy4Epg8</t>
+        </is>
+      </c>
+      <c r="J386" s="2" t="inlineStr">
+        <is>
+          <t>ffkzwy4Epg8</t>
+        </is>
+      </c>
+      <c r="K386" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:07:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年速報!!「待望のセレチケ配布&amp;63連ガチャ」厳選勢的獲得スタイルオススメ!!今選ぶならコレ!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年セレチケと63連の獲得優先解説
+唯一無二スタイル（白姫ハロウィン・ジェラール等）が最優先
+継承運用組も無人島で価値が再評価される</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>・白姫の闇は現状唯一無二の蓄積型ダメブロ
+・ジェラール無人島後半きつめで最優先
+・女神は最新ビクトール継承で避弾ダメブロ強化
+・ハニアボール継承で最新女神がダメブロ蓄積可能
+・リラお団子継承は今のリラに必須級</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>・お玉以下の古いスタイルは上昇ガチャすり抜け交換不可で注意
+・竿は魂ガチャ常駐外で確認必要</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>・セレチケ
+・63連ガチャ
+・白姫ハロウィン
+・無人島
+・継承運用</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lcMbW3VucQw</t>
+        </is>
+      </c>
+      <c r="J387" s="2" t="inlineStr">
+        <is>
+          <t>lcMbW3VucQw</t>
+        </is>
+      </c>
+      <c r="K387" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:07:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】引かない!?大注目「陰主人公」飯綱こよみ!!エクストラ3.75倍を武器に環境に君臨するかどうかを確認　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>陰主人公こよみの性能解説、エクストラ3.75倍が武器
+29ヒット技と便利系オールラウンダー性能
+強さは無難で爆裂感はなく総合評価Sの便利枠</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>・エクストラ3.75倍と高数値で安心感あり
+・1回限定29ヒット技に破壊力あり
+・全攻撃強化4050%・防御強化81%とサポート優秀
+・BPやLP回復も継承で対応可能で便利</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>・SSが1つもなく爆裂強くはない
+・ターミンと同じく便利止まりで突出ウリ不在
+・サポートと火力の両立が継承の柱で立てづらい</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>・飯綱こよみ
+・陰主人公
+・エクストラ3.75倍
+・29ヒット技
+・ターミン枠</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qNornXpd6Q4</t>
+        </is>
+      </c>
+      <c r="J388" s="2" t="inlineStr">
+        <is>
+          <t>qNornXpd6Q4</t>
+        </is>
+      </c>
+      <c r="K388" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:07:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　関門：ゴールデンバウム　10秒未満3体アタッカー紹介</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>ゴールデンバウム10秒未満アタッカー3体の紹介
+ハルウィン・サライン・サイバを編成例で実演
+サルの連達が強く陰属性弱点で安定周回可能</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>・サライン今回の連達がかなり強力
+・陰属性弱点で攻撃が通りやすい
+・8秒・7秒・6秒の周回がサクっと成立
+・AJ・ミルザのサポートでバフ十分</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr"/>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>・ゴールデンバウム関門
+・ハルウィン
+・サライン連達
+・サイバ
+・10秒未満周回</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BkOCssZH40Y</t>
+        </is>
+      </c>
+      <c r="J389" s="2" t="inlineStr">
+        <is>
+          <t>BkOCssZH40Y</t>
+        </is>
+      </c>
+      <c r="K389" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:07:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】もうぶっちぎりの陰属性！7.5周年6人全員性能確認【【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年新6人全員の性能を生で確認
+こよみ・サイバ・代々が突出で陰属性が環境制圧
+ストライフ・シレは尖り弱めで補助が必要</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>・こよみはサルイン仕様で4億超え技も継承
+・サイバは1.75倍全体バフのぶっ壊れサポーター
+・代々はオーバードライブ満タンと回避軽減で強烈
+・サラは1.75倍バトル開始バフと15ヒット全体が優秀
+・陰属性が環境的に押されており火力底上げ</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>・ストライフはエクストラフォース自前必要で補助前提
+・シレはサポート寄りで継承低勝ほぼ確定
+・暦み単体狙いはきつくAJ検定も乗りにくい</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年6人考察
+・陰属性インフレ
+・サイバ1.75倍
+・代々アタッカー
+・暦み狙い目</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BUOT34OOD5I</t>
+        </is>
+      </c>
+      <c r="J390" s="2" t="inlineStr">
+        <is>
+          <t>BUOT34OOD5I</t>
+        </is>
+      </c>
+      <c r="K390" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:07:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】大当たりはこれ！６３連ガチャ解説★いまでもSSS級多数あり【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>63連ガチャの当たり優先度を解説
+ダイナマイト・キングタイバー・メロトセロイ等を推奨
+環境に残る神スタイル多数で新規にも有用</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>・ダイナマイトは味方エクストラフォース付与で刺さる
+・キングタイバーは回避と継承で今でも強い
+・最終工程男は成功15戦継承で軽出可能
+・メロトセロイは1.75倍オーバーライドが熱い
+・ファイアブリンガーは全体BP上げで現役
+・マイスはドライブチェイン2枚ばら撒きで優秀</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>・フェリーラントは最近のインフレに飲まれた
+・ホロデスは強くなくウェイカー継承も微妙
+・デュエルビストは対面少なく出番限定的</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>・63連ガチャ
+・当たり優先度
+・キングタイバー
+・ファイアブリンガー
+・最終コテオン</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kH5zUaTcuLc</t>
+        </is>
+      </c>
+      <c r="J391" s="2" t="inlineStr">
+        <is>
+          <t>kH5zUaTcuLc</t>
+        </is>
+      </c>
+      <c r="K391" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:07:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年記念ガチャ</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年ガチャ生配信、コメビュー不調と格闘
+3000・6000・9000円課金で暦み・サイバコンプ
+暦み・サイバ両方欲しいが課金沼に自覚あり</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>・暦みとサイバを最終的にコンプ達成
+・サイバの武器全体エクホ1.875倍は強い
+・暦みのダーク仕様に40ヒット級の伸びしろ</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>・コメントビューア9.0仕様変更でログイン必須化が面倒
+・ガチャ仕様が損な配置で課金誘導感が強い
+・1/5・1/3確率で当たる気がしない引き味</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年ガチャ
+・暦み
+・サイバ
+・課金コンプ
+・コメビュー不調</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lM3WyqcmtWo</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr">
+        <is>
+          <t>lM3WyqcmtWo</t>
+        </is>
+      </c>
+      <c r="K392" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:07:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年開幕！公式生放送直後にライブ配信【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>公式生放送直後ライブで7.5周年開幕を祝う
+暦みの邪心仕様とサイバの破壊神性能に大興奮
+連携オンオフとオートOD回避選択は神アプデ</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>・連携オンオフがついに実装され神アプデ
+・オートODの発動回避が選べてオート復権
+・暦みは邪心宿しサルインの絆で強烈
+・サイバは太鼓の破壊神でプレイアブル化
+・サライグラキスのイラストが特に良い</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>・ヴァンパイアレディが結局出てくる引き味で複雑</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年開幕
+・公式生放送振り返り
+・連携オンオフ
+・オートOD
+・サイバ親キャラ</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-cWTcPBMN3Q</t>
+        </is>
+      </c>
+      <c r="J393" s="2" t="inlineStr">
+        <is>
+          <t>-cWTcPBMN3Q</t>
+        </is>
+      </c>
+      <c r="K393" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:07:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】待望の機能実装！ユーザー大歓喜の神アプデで始まる7.5周年！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年開幕お知らせ総まとめ動画
+ガチャ・セレチケ3枚・神アプデ・新コンテンツ盛り
+連携オンオフとオートOD回避が最大の目玉</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>・セレチケ3枚配布で過去スタイル補完できる
+・連携オンオフ実装は念願の神アプデ
+・オートOD発動回避選択でオート攻略復権
+・1.5万ジュエル+各種ログボでジュエル潤沢
+・死亡具・副防具の超進化対応で防具強化
+・アビス化レイド（白バラ等）が原作勢に刺さる</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>・ジュエルセール12個12万円は流石に考える
+・井戸の報酬が週末限定クエへ移動し井戸はトロフィー化
+・湘断試験の難易度が大幅上昇する見込み</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年まとめ
+・セレチケ3枚
+・神アプデ
+・アビス制圧戦
+・週末限定クエ</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=L2Im9nUb-eI</t>
+        </is>
+      </c>
+      <c r="J394" s="2" t="inlineStr">
+        <is>
+          <t>L2Im9nUb-eI</t>
+        </is>
+      </c>
+      <c r="K394" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:07:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年Romancing祭飯綱こよみ編ガチャ評価 #ロマサガRS #shorts #ガチャ</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年Romancing祭こよみ編のガチャ評価ショート
+字幕は音楽のみで具体的解説なし
+タイトルから飯綱こよみガチャの評価動画</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr"/>
+      <c r="F395" s="2" t="inlineStr"/>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ編ガチャ
+・Romancing祭
+・shorts</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6PUyjRjMk4E</t>
+        </is>
+      </c>
+      <c r="J395" s="2" t="inlineStr">
+        <is>
+          <t>6PUyjRjMk4E</t>
+        </is>
+      </c>
+      <c r="K395" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:07:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年Romancing祭サイヴァ編ガチャ評価 #ロマサガRS #shorts #ガチャ</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年Romancing祭サイヴァ編ガチャ評価ショート
+字幕は音楽のみで具体的解説なし
+タイトルからサイバ編ガチャの評価動画</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr"/>
+      <c r="F396" s="2" t="inlineStr"/>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>・サイヴァ編ガチャ
+・Romancing祭
+・shorts</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mHWPlTIiWDw</t>
+        </is>
+      </c>
+      <c r="J396" s="2" t="inlineStr">
+        <is>
+          <t>mHWPlTIiWDw</t>
+        </is>
+      </c>
+      <c r="K396" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:07:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年記念SSスタイル交換チケットで交換したいオススメスタイルは？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年セレチケおすすめ交換スタイルを紹介
+現役運用組と継承候補組に分けて解説
+幻闘場特化スタイル群も今年中盤まで現役級</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>・ハロウィンディーバは霊属性サポでターミン継承可
+・ロードライポルカは無人島で短期サポ強力
+・ロードライギュスターブは術完全無効で特殊枠
+・バレンタインお玉のチョコ贈り物で無人島が楽に
+・制圧戦女神の赤ネサスは暦み編女神に必須継承
+・ドロレスのデスメタルコード継承で原環境対応
+・最終工程男の現実先行は火力補填に有用
+・ノエル極炎交差継承でAJ検定常時1.75倍
+・幻闘場特化スタイル群は今年上期まで現役級</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>・4/10復刻ガチャ5体（白姫含む）が対象外で残念
+・事前告知なしで白姫狙い勢には肩透かし
+・インフレで過去スタイルと現行の差が大きい</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>・セレチケおすすめ
+・継承候補
+・幻闘場特化
+・ハロウィンディーバ
+・ノエル極炎交差</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EdKe1WBJn4o</t>
+        </is>
+      </c>
+      <c r="J397" s="2" t="inlineStr">
+        <is>
+          <t>EdKe1WBJn4o</t>
+        </is>
+      </c>
+      <c r="K397" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:07:11Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K397"/>
+  <dimension ref="A1:K402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26745,6 +26745,337 @@
         </is>
       </c>
     </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「引くべし」サイヴァ!!A.J.時代の終わりを告げるエクストラフォース1.75倍無差別ばら撒き!!ほか使い勝手を徹底考察　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>サイヴァ(裁判)はバトル開始時から無条件で全形態エクストラ1.75倍
+サブアタッカーとして火力・置き物・バフも充実し防御面も担保
+高難度評価SS、「とにかく引くべき」と高評価</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>・無条件1.75倍エクストラが全攻撃形態に乗り強力
+・サブアタッカーとして火力が十分出る
+・置き物効果・バフ系サポートも充実
+・防御面もある程度担保で邪魔にならない
+・高難度評価SS、とにかく引くべき</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>・防御周りはステバフ含めいまいち
+・マフ系80%のみで立ち位置はサブアタッカー止まり
+・過去のAA単体1.75倍ばら撒きスタイルは効果が薄くなる</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>・サイヴァ性能
+・エクストラ1.75倍
+・AJ時代終了
+・置き物効果
+・高難度SS
+・引くべき</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9FdvrxEPw2Q</t>
+        </is>
+      </c>
+      <c r="J398" s="2" t="inlineStr">
+        <is>
+          <t>9FdvrxEPw2Q</t>
+        </is>
+      </c>
+      <c r="K398" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31T01:06:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　ジェラール厄　500億満額育成枠1体周回　コヨーミン入り２編成で挑む</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>ジェラール厄レイドを育成枠1体の2編成で500億満額周回
+直接攻撃99%カットのため間接攻撃+斬弱点で火力を確保
+1編成目は冥王リッチ型、2編成目はODオート活用型を紹介</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>・育成枠1体でも500億満額が取れる
+・間接攻撃+斬弱点で火力を確保できる
+・ODオート周回でアタッカーも育成可能
+・ルビー採用でODが溜まりやすくBPも取れる</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>・2編成目(OD型)は1編成目より周回が遅い
+・ODが2ターン目で切れて溜めにくい点に注意</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>・ジェラール厄レイド
+・500億満額
+・育成枠1体
+・2編成紹介
+・ODオート周回</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0mzMnpjv5gE</t>
+        </is>
+      </c>
+      <c r="J399" s="2" t="inlineStr">
+        <is>
+          <t>0mzMnpjv5gE</t>
+        </is>
+      </c>
+      <c r="K399" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31T01:06:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】遂に環境支配級SSS現る！最新キャラランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>5月最終ランキング、暦読みとサイバ(裁判)が環境支配級SSS
+暦読みは火力・防御・回復・バフ万能、サイバは無条件1.82倍ばら撒き
+一方シレは防御率30%台、ミニオンは評価を上げづらくやや厳しめ</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>・暦読みは火力・防御・HP回復・バフ全部こなす環境支配級SSS
+・サイバ(裁判)は無条件1.82倍ばら撒き+20ヒットで環境最強SSS
+・暦読みは100億も簡単に超える圧倒的火力
+・大はザンエクストラ1.75倍でAJと相性最高(SS)
+・サは防御強化・状態回復が優秀(SS)</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>・シレは防御系率が30%台と低くサポートとして致命的(AA)
+・ミニオンは自己以外のエクストラが少なく外部補助必要(A)
+・暦読み・サイバは防御低率50%が明確なデメリット</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>・最新キャラランキング
+・環境支配級SSS
+・暦読み
+・サイバ(裁判)
+・大/サ評価
+・シレ/ミニオン低評価</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nmHCdPWhH-c</t>
+        </is>
+      </c>
+      <c r="J400" s="2" t="inlineStr">
+        <is>
+          <t>nmHCdPWhH-c</t>
+        </is>
+      </c>
+      <c r="K400" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31T01:06:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年制圧戦レイドジェラール厄満額500億周回 #ロマサガrs #shorts</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年制圧戦レイド「ジェラール厄」満額500億周回のショート
+自動生成字幕が文字化けで内容を取得できず詳細不明
+タイトルからジェラール厄の500億周回紹介と推測</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr"/>
+      <c r="F401" s="2" t="inlineStr"/>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>・ジェラール厄
+・500億周回
+・7.5周年制圧戦
+・ショート動画</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ovw48NqqgpE</t>
+        </is>
+      </c>
+      <c r="J401" s="2" t="inlineStr">
+        <is>
+          <t>ovw48NqqgpE</t>
+        </is>
+      </c>
+      <c r="K401" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31T01:06:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第122回メタルアルカイザーの井戸〜最適解パーティ徹底考察〜👊ランク上位を目指そう👊~📻TYAMU RADIO 📻~</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>6月1日実装メタルアルカイザーの井戸(螺旋1520回元)の予想考察
+雷属性弱点だが強アタッカー不在で陰属性2体含むベスト編成を提案
+HP約870億・3〜4ターン長期戦予想、ビクトールと暦みの火力が突出</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>・今後の井戸は高難度より強く遊び応えがあり歓迎
+・ビクトールと暦みの火力がえぐい
+・サイバは置き物+アタッカー両立の万能キャラ
+・被弾時BP回復が長期戦に好相性</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>・雷属性のスーパーアタッカーが不在
+・引属性は体勢+125で活躍しづらい
+・メタルアルカイザーの雷防御弱化アビリは効果が薄く感じた
+・未動の火力がさほど出ず枠変更を検討
+・軽減キャラ未配置で長期戦は不安が残る</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>・メタルアルカイザーの井戸
+・雷属性弱点
+・ベスト編成考察
+・HP870億予想
+・暦み/ビクトール火力</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LOvHq11m28Q</t>
+        </is>
+      </c>
+      <c r="J402" s="2" t="inlineStr">
+        <is>
+          <t>LOvHq11m28Q</t>
+        </is>
+      </c>
+      <c r="K402" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31T01:06:29Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K402"/>
+  <dimension ref="A1:K414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27076,6 +27076,815 @@
         </is>
       </c>
     </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「対応自在」アマゾネス!!属性を自在に使い分け直接&amp;間接までコントロールするロマンシングパス配布!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>配布アマゾネスのロマンシングパス性能を評価
+直接/関節を使い分け幅広い敵に対応するが火力は半端
+総合評価C、今月はスルーで限定ガチャ優先推奨</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>・直接禁止ギミックに使い分けで対応できる
+・副属性2種で幅広い敵に対応可能
+・リキャスト4ターン技でBP自己完結できる
+・女性編成ならそこそこやれる</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>・パンチが弱くプラチナより弱そう
+・女性縛りで起用条件が整わない
+・レイドでも出番なさそう
+・総合評価C、今月はスルー推奨</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>・ロマンシングパス
+・アマゾネス
+・複属性1.5倍
+・女性編成
+・総合評価C</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NdWx58YMKu0</t>
+        </is>
+      </c>
+      <c r="J403" s="2" t="inlineStr">
+        <is>
+          <t>NdWx58YMKu0</t>
+        </is>
+      </c>
+      <c r="K403" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:06:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「ギミック解明速報」追憶の幻闘場デス!!予告通り〇〇が手がかりに…小剣&amp;剣　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>追憶の幻闘場デスのギミック解明速報
+オーディ5連携が必須、満タン系を揃えれば中期戦で撃破
+天流は残体性35以上で発動簡単、武器種まとめは後日</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>・OD満タン系を揃えれば中期戦で倒せる
+・武器種リンク持ちがいればかなり簡単
+・天流は残体性35以上で発動が簡単
+・プラチナ新キャラがODゲージを巻いて便利</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>・火力低くOD満タン系いないと積む
+・4連携は無駄になる
+・LP回避の運ゲ要素がある</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場デス
+・オーディ5連携
+・OD満タン系
+・天流
+・小剣・剣</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YhTdtltKTqk</t>
+        </is>
+      </c>
+      <c r="J404" s="2" t="inlineStr">
+        <is>
+          <t>YhTdtltKTqk</t>
+        </is>
+      </c>
+      <c r="K404" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:06:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新キャラ無し「ランクイン全力オート」で楽チン満額井戸!!サイヴァ!?居ねぇんだよぉ!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>新キャラ無し既存スタイルで満額井戸ランクイン
+オートでODまで回り井戸のリトライが楽になった
+毎週高難イド級になる井戸、やり込めばランクインしやすい</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>・オートで井戸が楽になった
+・新キャラ無しでもランクインできる
+・やり込めば毎週ランクインしやすい</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>・3ターンで倒すには裁判が必要
+・ダメージを受けるので体勢は必要</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>・井戸
+・全力オート
+・ランクイン
+・魂アビリティ
+・既存スタイル</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_kibvKgAcec</t>
+        </is>
+      </c>
+      <c r="J405" s="2" t="inlineStr">
+        <is>
+          <t>_kibvKgAcec</t>
+        </is>
+      </c>
+      <c r="K405" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:06:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】サライ無しの「満額最短」は!?500億を余裕で取りながらギリギリを目指せ!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>サライ無しのサラレイド満額最短編成に挑戦
+再来と詩人が稼ぎの鍵、500億を余裕で確保
+世界記録との差は90秒、サライがいれば3人遊べる</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>・再来がいるとかなり稼げる
+・詩人が肝で外せない重要枠
+・500億は余裕で確保できる
+・サライがいれば3人分稼げる</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>・手持ち不足で遅いギラを使用
+・世界記録との差が90秒ある</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>・サラレイド
+・満額最短
+・500億
+・再来
+・詩人</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fEyvzbw5NSM</t>
+        </is>
+      </c>
+      <c r="J406" s="2" t="inlineStr">
+        <is>
+          <t>fEyvzbw5NSM</t>
+        </is>
+      </c>
+      <c r="K406" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:06:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】手持ちで試してみて！サラレイド2分20台～3分満額500億編成！役割別代用なども解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>サラレイド2分20台〜3分の満額500億編成を解説
+再来がMVP特攻、サラ・ビクトールが今回のギミックに刺さる
+メインアタッカー候補とサポーター・代用キャラを役割別紹介</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>・再来がMVP特攻で強い
+・サラの評価が高くレイドで活躍
+・ビクトールが関節攻撃ギミックに刺さる
+・ルビーの補助性能が高い
+・雪だるまのOD75倍で火力が伸びる</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトールは運ゲになりがち
+・2分20秒を切るのは難しい
+・イシスは関節攻撃で火力が出ない</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>・サラレイド
+・500億編成
+・再来特攻
+・関節攻撃ギミック
+・役割別代用</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7DXVPJ2wulY</t>
+        </is>
+      </c>
+      <c r="J407" s="2" t="inlineStr">
+        <is>
+          <t>7DXVPJ2wulY</t>
+        </is>
+      </c>
+      <c r="K407" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:06:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>＃ロマサガRS サラレイド50億2:31</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>サラレイドで50億を2分31秒で達成したショート動画
+字幕がほぼ無く詳細解説なし、プレイ映像中心
+タイムアタック系の実走記録と思われる</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr"/>
+      <c r="F408" s="2" t="inlineStr"/>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>・サラレイド
+・タイムアタック
+・50億
+・ショート動画</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aRzkR5oGDVs</t>
+        </is>
+      </c>
+      <c r="J408" s="2" t="inlineStr">
+        <is>
+          <t>aRzkR5oGDVs</t>
+        </is>
+      </c>
+      <c r="K408" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:06:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】5000ジュエル確保する為の決断・・SSS防具進化私はこれにした！全進化考察【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>5000ジュエル確保のためSSS防具超進化を緊急考察
+投稿者はパワーチャージ目当てでセオマウントを選択
+各防具を比較、ハルモニア・セオマント系を推す</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>・セオマウントのパワーチャージ3が強い
+・ゴーレムオーブの精神付与が偉い
+・ハルモニアスーツの行動補正低下が偉い</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>・続巻きは優先度が低い
+・セオの鎧の軽減はそこそこ止まり
+・超心が貴重で進化先に悩む</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>・SSS防具進化
+・セオマウント
+・パワーチャージ
+・ゴーレムオーブ
+・ハルモニアスーツ</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gwhOADYCWn4</t>
+        </is>
+      </c>
+      <c r="J409" s="2" t="inlineStr">
+        <is>
+          <t>gwhOADYCWn4</t>
+        </is>
+      </c>
+      <c r="K409" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:06:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】超進化防具おすすめランキングベスト3！圧倒的におすすなのは！？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>超進化防具のおすすめベスト3を発表
+1位西王マント(BP+3)、2位ハルモニアスーツ、3位ゴールデンローブ
+アビリティ最優先で選べ、ステや状態異常体制は気にしなくてよい</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>・西王マントのBP+3は戦略が変わるほど強い
+・ハルモニアの行動順補正低下が唯一無二
+・火ダメ軽減20%が大きい
+・ゴールデンローブの精神上昇が優秀
+・超進化で別物レベルに強化される</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>・マスタリーグラブが一番微妙(火軽減無し)
+・属の8巻き50%上昇はEFでなく微妙
+・クイックシルバーは3000個に貧弱
+・西王の鎧+マントは天属性キャラ使いづらい
+・状態異常体制はほぼ意味がない</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>・超進化防具
+・西王マント
+・ハルモニアスーツ
+・ゴールデンローブ
+・BP+3</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HhlxMv7DREk</t>
+        </is>
+      </c>
+      <c r="J410" s="2" t="inlineStr">
+        <is>
+          <t>HhlxMv7DREk</t>
+        </is>
+      </c>
+      <c r="K410" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:06:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】買い得？スルー？６月のロマンシングパスの内容をチェック！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>6月のロマンシングパスの内容をチェック
+キャラはブコ、女性編成でOD常時使える絶妙な調整
+ジュエル等の特典付きで買って損なし、槍のダメブロも注目</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>・ブコは絶妙にいい調整
+・女性編成でODを常時使える
+・ジュエル・ソウルピース付きで買って損なし
+・槍のダメージブロック1回が無人島で強い
+・今月のパスは相当いい</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>・ブコはぶっ壊れではない
+・EF女性1.12倍は効果が高くない
+・ガチャキャラの方がはるかに強い
+・武器が槍限定でピンポイント</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>・ロマンシングパス
+・ブコ
+・女性編成
+・ダメージブロック
+・無人島</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QZEVpLURSmA</t>
+        </is>
+      </c>
+      <c r="J411" s="2" t="inlineStr">
+        <is>
+          <t>QZEVpLURSmA</t>
+        </is>
+      </c>
+      <c r="K411" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:06:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】取らないと後悔レベルが存在！？最新版ガチャ確保ランキング！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>最新版ガチャ確保優先度ランキングを発表
+最優先はサイバと絆暦み、頭2つ抜けて強い
+7.5周年で勢力図が一変、サライ・代々・聖王が優先高</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>・サイバは環境を作る最強で欠点なし
+・絆暦みは主人公として強く味方強化も高い
+・サライは火力高くサポートも貴重
+・代々の火ダメ軽減が高い
+・アビス聖王はインパで活躍</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>・ロドラはインフレで優先中に落ちた
+・復刻西王編は確保優先度が最も低い
+・ストライフは熱パ需要なく無理しない
+・シーレは過去主人公で壊れてはいない</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>・確保優先度
+・サイバ
+・絆暦み
+・サライグラキエス
+・7.5周年</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Qj0fdrcMQL0</t>
+        </is>
+      </c>
+      <c r="J412" s="2" t="inlineStr">
+        <is>
+          <t>Qj0fdrcMQL0</t>
+        </is>
+      </c>
+      <c r="K412" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:06:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ガチャの闇に恐怖？新しくなったプラチナガチャの性能を確認してコンプを狙う！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>リニューアルしたプラチナチケットガチャの性能チェック
+新3スタイルではジーンムーアが当たりでOD加速が優秀
+11万枚から5000連でコンプ達成、運悪めの結果に</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>・ジーンムーアが当たりでOD加速90%が優秀
+・シルバードラゴンは全体攻撃継承で面白い
+・ジーンムーアは追撃アタッカーとしても悪くない</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>・フランシスはプラガチャキャラで微妙
+・シルバー親は全体攻撃継承ないと微妙
+・コンプに5000連もかかった
+・最新時代では強くはない</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>・プラチナガチャ
+・ジーンムーア
+・シルバー親
+・OD加速
+・コンプ</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VizYMvEfpMM</t>
+        </is>
+      </c>
+      <c r="J413" s="2" t="inlineStr">
+        <is>
+          <t>VizYMvEfpMM</t>
+        </is>
+      </c>
+      <c r="K413" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:06:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】そのセレチケ交換ちょっと待った！おすすめランキングと超重要を解説！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年セレクトチケットのおすすめスタイルを紹介
+基本はギリギリまで待ち、63連チケットを先に使うべき
+1位女神2位バトランド3位ノエル、無人島用キャラも解説</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>・女神は赤ネサスで性能が変わる最優先
+・バトランドは強力なアタッカー
+・DQコラボノエルは必須級
+・ネメシスは無人島で必須
+・中達の熱冷無効が唯一無二</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>・1年前のスタイルでそんなに使わない
+・急がずギリギリまで待つべき
+・無人島以外で使わないキャラが多い
+・150連で交換できるものは優先度が下がる</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>・セレクトチケット
+・女神
+・バトランド
+・無人島
+・幻闘場特化</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sQ-deM5HRWM</t>
+        </is>
+      </c>
+      <c r="J414" s="2" t="inlineStr">
+        <is>
+          <t>sQ-deM5HRWM</t>
+        </is>
+      </c>
+      <c r="K414" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:06:27Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K414"/>
+  <dimension ref="A1:K418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27885,6 +27885,255 @@
         </is>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　7.5周年セレチケ　後悔しない3体...誰選ぶ？　独断と偏見で厳選！</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年SSセレチケの厳選おすすめを独断で解説
+螺旋回廊・無人島向けの置き物/防御/OD要員を紹介
+最有力はリンク系・女神と赤ネサス系の継承技</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>・オアイーブは置き物バフ&amp;BPサポートが優秀
+・ビューネは無人島で防具弱化が刺さる
+・ポルカはダメブロ3回+リバイバルが強力
+・エミリーは縦横全体火力で希少枠
+・赤ネサス継承は永続防御バフで最有力</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>・ロリカリアは防御が低く周りの補助が必須
+・エミリーの縦横技は術なので風武器が必要
+・対象外SS(ロックブーケ等)があり要注意</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>・セレチケ厳選
+・螺旋回廊向け
+・無人島向け
+・リンク系女神
+・OD/EFサポート
+・継承技要員</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=axRDXZqeHiw</t>
+        </is>
+      </c>
+      <c r="J415" s="2" t="inlineStr">
+        <is>
+          <t>axRDXZqeHiw</t>
+        </is>
+      </c>
+      <c r="K415" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04T01:06:10Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】飯綱こよみ・サイヴァ能力値早見表〜Half Anniversary〜注目のブッ壊れ性能を堪能せよ‼️</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年第1弾 飯綱こよみ・サイヴァの能力値早見表を公開
+こよみは1ターン目から弱点無視級の超火力
+サイヴァは置き物バフ300-400%で2体とも確保推奨</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>・こよみは1ターン目から弱点無視級の超火力
+・サイヴァは体力精神バフ300-400%の置き物性能
+・サイヴァは火力もデバフも持ち汎用性抜群
+・2体とも確保優先度が高い</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr"/>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ能力値
+・サイヴァ能力値
+・ハーフアニバ
+・置き物バフ
+・確保推奨</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TfsIzGj-7Aw</t>
+        </is>
+      </c>
+      <c r="J416" s="2" t="inlineStr">
+        <is>
+          <t>TfsIzGj-7Aw</t>
+        </is>
+      </c>
+      <c r="K416" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04T01:06:10Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】サラ〔厄〕レイド~井戸キャラ~3:09~</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>サラ〔厄〕レイドの井戸キャラ攻略プレイ動画
+ナレーションなしの実戦バトル映像(3:09〜)
+井戸キャラ編成での立ち回りを実演</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr"/>
+      <c r="F417" s="2" t="inlineStr"/>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>・サラ〔厄〕レイド
+・井戸キャラ
+・実戦プレイ</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=q-SwcHa8n_4</t>
+        </is>
+      </c>
+      <c r="J417" s="2" t="inlineStr">
+        <is>
+          <t>q-SwcHa8n_4</t>
+        </is>
+      </c>
+      <c r="K417" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04T01:06:10Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第122回 ~メタルアルカイザーの井戸〜攻略〜目指せ！！100位‼️〜全てお見せ致しますᕦ(ò_óˇ)ᕤ</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>メタルアルカイザーの井戸 100位以内を狙う攻略動画
+初日朝に自作したオリジナル編成を実演
+100位ボーダーは約85.4万点、白蓮未強化で伸び代あり</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>・仲間と協力できるコミュニティが楽しく有意義
+・白蓮が手抜き状態でまだ伸び代がある
+・高難度コンテンツが毎週続いて好調</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>・トップとはかなり点差がある</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>・メタルアルカイザー井戸
+・100位攻略
+・オリジナル編成
+・高難度立ち回り</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rAi4YTnvF0k</t>
+        </is>
+      </c>
+      <c r="J418" s="2" t="inlineStr">
+        <is>
+          <t>rAi4YTnvF0k</t>
+        </is>
+      </c>
+      <c r="K418" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04T01:06:10Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K418"/>
+  <dimension ref="A1:K441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28134,6 +28134,1504 @@
         </is>
       </c>
     </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「唯一無二」引くべき無尽塔対応サライ!!その圧倒的火力と両立させる対応力　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔対応サライ・グラキエスのスタイル評価。
+全体攻撃を打ち続ける破壊力と状態異常解除が唯一無二。
+無人島適性に加えダメブロ要素も持つ優秀タイル。</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>・全体攻撃を打ち続ける破壊力が高い
+・ターン終了時の状態異常解除がレア性能
+・無人島でのダメブロ自己付与で組みやすい
+・個人火力と火力サポートを両立</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
+        <is>
+          <t>・ダメブロ面はあまり強くない
+・防御し戦うと各種恩恵が消える割り切りが必要</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>・サライ・グラキエス
+・無尽塔/無人島適性
+・全体攻撃火力
+・状態異常解除
+・ダメブロ</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3gUTEaNTQZ8</t>
+        </is>
+      </c>
+      <c r="J419" s="2" t="inlineStr">
+        <is>
+          <t>3gUTEaNTQZ8</t>
+        </is>
+      </c>
+      <c r="K419" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「天井不可避」聖王…サイヴァ…サライ…そしてこよみ!!どこまで引くかの超決戦!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>聖王・サイヴァ・サライ・こよみを巡るガチャ実況回。
+コンプを狙うも天井不可避ですり抜け連発の沼展開。
+ネタ寄りのガチャドラマでオチは神引きの二択。</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr"/>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>・天井不可避ですり抜けが連発
+・コンプの必然性がないガチャが多い不満</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ実況
+・天井突破
+・すり抜け
+・7.5周年ガチャ
+・コンプ狙い</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5iXfQ17DV4E</t>
+        </is>
+      </c>
+      <c r="J420" s="2" t="inlineStr">
+        <is>
+          <t>5iXfQ17DV4E</t>
+        </is>
+      </c>
+      <c r="K420" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】残りのガチャ「判明」いつものリアム生誕祭という名の7.5周年当日!!後半戦に来るイベントは!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>残りのガチャ判明、いつものリアム生誕祭という名の当日。
+継続制圧戦で魂アビリティを稼ぐ一週間になる。
+11日に8線揃い編ストーリー序盤終了と予想。</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>・カウントダウンやパネル交換でジュエル配布がある
+・制圧戦で魂アビリティをしっかり集められる</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>・継続制圧戦の報酬がしょぼい
+・後半戦の中身が見えず不安</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年日程
+・制圧戦
+・魂アビリティ
+・ガチャ予想
+・ハーフアニバ後半戦</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LSrDhOyZVSI</t>
+        </is>
+      </c>
+      <c r="J421" s="2" t="inlineStr">
+        <is>
+          <t>LSrDhOyZVSI</t>
+        </is>
+      </c>
+      <c r="K421" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「緊急」終了前…聖王VSこよみ比較検討会!!&amp;ダイ・ダイ+ストライフ+シィレイ性能詳細のガチャ厳選勢ダブルヘッダー!!ガチャごとの引き方と評価を網羅　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>聖王VSこよみ比較とダイダイ・ストライフ・シィレイ性能評価。
+こよみは買えが効くが上位クラスの仕上がり。
+裁編コンプ推奨、シィレイは課金が惜しい性能。</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>・こよみは買えが効く中でもかなり上位の強さ
+・フォーナンドは攻防底上げが得意で雑に混ぜられる
+・聖王は無人島適性とバフデバフが唯一無二</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>・こよみは唯一無二の強さはなく買えが効く
+・ストライフは1ターン潰す行動で使いにくい
+・シィレイは意味不明な仕様でロクな数値が出ず継承価値も皆無</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ評価
+・聖王比較
+・ストライフ
+・シィレイ
+・ガチャ厳選</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dGbS1g384q8</t>
+        </is>
+      </c>
+      <c r="J422" s="2" t="inlineStr">
+        <is>
+          <t>dGbS1g384q8</t>
+        </is>
+      </c>
+      <c r="K422" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】8種防具ランキング「超危険」超進化防具それ取っちゃダメ!!それぞれの特徴を解説しつつ古参プレイヤー垂涎の防具オススメ!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>8種超進化防具をランキングで厳選紹介。
+ゴールデンローブは精神ばら撒き2枚重ねが優秀。
+どれを取っても勝敗に大きな影響はない注意点も。</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>・ゴールデンローブ精神15%ばら撒き2枚が高難度で有効
+・パワーチャージ3聖王マントは継承時のBP不足を補える
+・低リスクで好きなものを選べる</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>・ある防具を除きどれを取っても勝敗に影響しない
+・ステ+100や+200はステバフ前ではほぼ無意味</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>・超進化防具
+・ゴールデンローブ
+・パワーチャージ3
+・ジュエル5000
+・優先度ランキング</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=el9k81iis9U</t>
+        </is>
+      </c>
+      <c r="J423" s="2" t="inlineStr">
+        <is>
+          <t>el9k81iis9U</t>
+        </is>
+      </c>
+      <c r="K423" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ここで!?「7.5周年当日」のガチャネタバレキター!!本当に厄の出番なのかそれともいつもの…　#ロマサガrs</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年当日6月6日のガチャネタバレ予想回。
+リアム終年祭は避けられ主人公絡みは控えめと予測。
+以降8.5周年まで全部土日開催の見込み。</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>・土日開催で記念日感のあるお祝いガチャになる</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>・バナーやドット流用で新スタイル無しのキャラがいる
+・リアム終年祭は避けられ盛り上げ要素が読みにくい</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年ガチャ予想
+・6月6日当日
+・主人公ガチャ
+・制圧戦レイド
+・ダブルガチャ</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=njs4Dz1tgM8</t>
+        </is>
+      </c>
+      <c r="J424" s="2" t="inlineStr">
+        <is>
+          <t>njs4Dz1tgM8</t>
+        </is>
+      </c>
+      <c r="K424" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】幻闘場デス全武器種クリアするまで終われません！！普段話さない事を話す雑談回【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場デスを全武器種クリアするまで終われない雑談回。
+ウェポンシステムやAJ、裁判が圧倒的に強くサクサク突破。
+朝昼の食事ネタやサルイン考察も交えた長尺配信。</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>・ウェポンシステムが幻闘場上で凄まじく強い
+・裁判やAJがいると術ダメージ0で余裕の突破
+・リラやファティーマ、ミド君が1人無双級</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>・銃など最近のアタッカーがおらず火力が出ない
+・地雷ギミックでLPダメージ発狂し銃と10は撤退</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場デス全武器種
+・雑談配信
+・ウェポンシステム
+・裁判/AJ
+・サルイン考察</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NcfPdOy8ljU</t>
+        </is>
+      </c>
+      <c r="J425" s="2" t="inlineStr">
+        <is>
+          <t>NcfPdOy8ljU</t>
+        </is>
+      </c>
+      <c r="K425" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】白薔薇姫＆T260Gレイドまとめて解説★プラガチャまさかの大活躍！！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>白薔薇姫とT260Gレイドをまとめて解説。
+物理ビクトール編成と無限流し切りで黒バラ攻略。
+プラガチャのジーン・ムーアがまさかの大活躍。</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>・プラチナガチャのジーンムーアが早くて大活躍
+・ターミンは攻守両用で万能、試練召喚が強力
+・イシスが思わぬ活躍を見せる</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>・黒バラは3回に1回600億行かず記憶再生専用
+・T260Gはわき会員でガチャが一番きついかも</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇姫レイド
+・T260Gレイド
+・ビクトール無限流し切り
+・プラガチャ活躍
+・記憶再生</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YcLlJD-Bph4</t>
+        </is>
+      </c>
+      <c r="J426" s="2" t="inlineStr">
+        <is>
+          <t>YcLlJD-Bph4</t>
+        </is>
+      </c>
+      <c r="K426" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】緊急！予想つかん！7.5周年祭リアム主人公軍団＆人気ヴィラン参戦！！公式先行情報確認【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年祭の公式先行情報を確認する緊急回。
+リアム・アーニャ・ダリアスの主人公軍団が参戦。
+トークアイ・オルレット・ラゼムの人気ヴィランも登場。</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>・好きなキャラのダリアスやラゼムが来て嬉しい
+・斧の貴重なキャラが補強できて良かった
+・主人公とヴィランの熱い参戦テキスト</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>・白火戦の残りが第3弾持ち越しで来なかった
+・土曜開催で家事と被りプレイ時間が取りにくい</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年お知らせ
+・主人公軍団
+・人気ヴィラン
+・ガチャ先行情報
+・ラゼム</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dytcMBmvoEw</t>
+        </is>
+      </c>
+      <c r="J427" s="2" t="inlineStr">
+        <is>
+          <t>dytcMBmvoEw</t>
+        </is>
+      </c>
+      <c r="K427" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】雪だるま無し！白薔薇レイド2:30で最強軍団を超強化せよ【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>雪だるま無しの白薔薇レイド2分30秒編成を紹介。
+サイヴァを育成枠に入れつつ最強軍団を超強化。
+大技散らしの流れで安定して2分32秒台を記録。</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>・雪だるま無しでもサイヴァ育成しつつ2分30秒台で回せる
+・無限流し切りで安定、大技散らしの流れが速い</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>・無限が引けないと600億に届かず下ぶれる
+・ビクトールの3ターン目が影ロかどうかで運に左右される</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇レイド
+・雪だるま無し
+・サイヴァ育成
+・ビクトール無限流し切り
+・記憶再生</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=u52GkzOvVH0</t>
+        </is>
+      </c>
+      <c r="J428" s="2" t="inlineStr">
+        <is>
+          <t>u52GkzOvVH0</t>
+        </is>
+      </c>
+      <c r="K428" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ここでも無双！今話題のあのキャラが闘者の関門まで全て破壊してしまった【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>話題のこよみが闘者の関門を全て破壊してしまった検証。
+置き物枠0でこよみ1人だけで自動再戦周回が可能。
+育成枠を4枠確保でき周回適性が抜群。</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ1人で置き物枠0でもクリアでき衝撃的
+・育成枠を4枠確保でき周回効率が高い
+・専用武器RS+100%で火力十分</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>・タイム自体は14秒で特別速くはない</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ
+・闘者の関門
+・置き物枠0
+・育成枠4枠
+・自動再戦周回</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-z6-HCAiBxw</t>
+        </is>
+      </c>
+      <c r="J429" s="2" t="inlineStr">
+        <is>
+          <t>-z6-HCAiBxw</t>
+        </is>
+      </c>
+      <c r="K429" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはり環境を変えてしまった...！こよみとサイヴァが強すぎた！！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>こよみとサイヴァが強すぎて環境を変えてしまった検証。
+セフェルマルカーをこよみ・裁判・サライで一気に蹂躙。
+サライの状態異常全解除で毒ギミックも無効化。</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>・裁判のターン開始時バフ量とエクストラフォースがえぐい
+・こよみが化け物火力で早々に乾燥する
+・サライの状態異常全解除で毒ギミックを潰し安定
+・エクストラフォースを全員無条件1.75倍にできる</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>・サライ単体は発狂できず地味な場面もある</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ
+・サイヴァ/裁判
+・サライ・グラキエス
+・セフェルマルカー
+・環境変化</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8fC-0f4Jyqw</t>
+        </is>
+      </c>
+      <c r="J430" s="2" t="inlineStr">
+        <is>
+          <t>8fC-0f4Jyqw</t>
+        </is>
+      </c>
+      <c r="K430" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】6月6日は7.5周年当日！ヤバいガチャがまだ待っている？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>6月6日7.5周年当日ガチャの内容をみんなで予想。
+新メイン4人とアビス2体の超豪華ダブルガチャと予測。
+前回予想の答え合わせでは4キャラ正解者が多数。</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>・新メインキャラは一部除き非常に強かった
+・白薔薇アビスやT260Gアビスはイラストも性能も期待</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>・シーレだけは過去主人公補正もあり今回協力的ではなかった
+・タコおじさんはシリアスな場面で実装は早すぎる</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年当日ガチャ予想
+・新メインキャラ
+・アビスキャラ
+・ダブルガチャ
+・予想発表会</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=To-hSFJojc8</t>
+        </is>
+      </c>
+      <c r="J431" s="2" t="inlineStr">
+        <is>
+          <t>To-hSFJojc8</t>
+        </is>
+      </c>
+      <c r="K431" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】衝撃のお知らせが到来！7.5周年が思った以上にヤバそうな気配...【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年の衝撃的なお知らせをチェック。
+当日はリアム編とトークアイ編のダブルガチャが来る。
+6月11日にもガチャが挟まり想像以上にヤバい配置。</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>・新速人系の追加や7.5周年記念クエストの報酬が豪華
+・白火戦からの贈り物が久々復活でテンションが上がる
+・SSS超進化がもう1個できそう</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>・6月6日に新メインキャラが来ず過去主人公だった
+・10日間に2回ガチャと頻度が多く財布が怖い</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年お知らせ
+・リアム編ガチャ
+・トークアイ編ガチャ
+・新速人系
+・ガチャ頻度</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=eTv05cg5Cm4</t>
+        </is>
+      </c>
+      <c r="J432" s="2" t="inlineStr">
+        <is>
+          <t>eTv05cg5Cm4</t>
+        </is>
+      </c>
+      <c r="K432" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年キャラは引くべき？飯綱こよみ・サイヴァガチャ性能チェック&amp;キャラランク評価【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年6キャラの性能チェックとランク評価。
+こよみは超アタッカー、裁判はパーティ全体への影響力大。
+効果量を全て『大々/台』で揃えた遊び心も話題に。</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>・こよみは斬員12ヒットの超アタッカーで火力ソース優秀
+・裁判は体力精神デバフで無人島でも使え影響力が高い
+・ストライフはヒット数多くエフェクト早くレイド向き
+・大々はバランス良くエクストラフォースも入れられる</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>・シーレはエクストラフォース支援が無くやや控えめ
+・ストライフは代償ダメージがありランスコアでは注意</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年性能チェック
+・こよみ超アタッカー
+・裁判評価
+・サライ/大々
+・ランク付け</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UQNxblOunvs</t>
+        </is>
+      </c>
+      <c r="J433" s="2" t="inlineStr">
+        <is>
+          <t>UQNxblOunvs</t>
+        </is>
+      </c>
+      <c r="K433" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】聖王厄はぶっ壊れか？聖王厄ガチャキャラランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>終了間近の聖王厄ガチャを最終ランク評価。
+聖王アビスはステデバフが暴れっぷりで星3評価。
+ロロ・バンパイアレディは条件付きで星2の評価。</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビスはあらゆる場面でステデバフを入れ暴れる
+・聖王アビスは貴重な斧枠で陰編成のリーダー級
+・インの導きバフは今後のアビスシナジーでポテンシャル高い</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>・ロロは7回避弾前提で全バフ取得が厳しく周回不向き
+・バンパイアレディは突出した強さがなく目新しさに欠ける
+・聖王アビスは技3が闇術で過去スタイルに継承不可</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビス評価
+・ステデバフ
+・星3評価
+・ロロ
+・バンパイアレディ</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_Qrh7WjK47U</t>
+        </is>
+      </c>
+      <c r="J434" s="2" t="inlineStr">
+        <is>
+          <t>_Qrh7WjK47U</t>
+        </is>
+      </c>
+      <c r="K434" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】SSS防具超進化！進化後の性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>SSS防具超進化後の性能を全8種チェック。
+セオマントの初期BP+3とハルモニアの体制が特に優秀。
+ゴールデンローブの精神上昇も状態対策で輝く可能性。</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>・セオマント初期BP+3は他で真似できない個性で周回向き
+・ハルモニアは体制優秀で行動順調整にも使える
+・ゴールデンローブ2枚なら精神30%上昇で状態対策に有効</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>・属の八巻きはアビリティが大した効果でなく微妙
+・マスタリーグラブやクイックシルバーは効果が限定的</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>・超進化防具
+・セオマント
+・ハルモニアスーツ
+・ゴールデンローブ
+・進化優先度</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IYcQykYjB5o</t>
+        </is>
+      </c>
+      <c r="J435" s="2" t="inlineStr">
+        <is>
+          <t>IYcQykYjB5o</t>
+        </is>
+      </c>
+      <c r="K435" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】追憶の幻闘場「デス」ギミック解説・攻略！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>追憶の幻闘場デスのギミック解説と攻略。
+マイターン開始時のコーションをOD5連携で解除がカギ。
+短期決戦狙いで武器対なら2ターン撃破も可能。</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>・新スタイルとOD関連を入れれば常時5連携で2ターン撃破
+・セレチケのOD満タン特化5体が回答になりきつい時に確保推奨</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>・コーション解除できないと全体LP3で全滅が待つ
+・長期戦になるとLPが削り取られ火力なしは苦戦</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場デス
+・コーション解除
+・OD5連携
+・短期決戦
+・LPダメージ</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dE7RdX46Wfo</t>
+        </is>
+      </c>
+      <c r="J436" s="2" t="inlineStr">
+        <is>
+          <t>dE7RdX46Wfo</t>
+        </is>
+      </c>
+      <c r="K436" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】SS3体確定！63連ガチャで当たり＆天井交換でのオススメスタイルは？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>SS3体確定63連ガチャの当たりと天井交換おすすめ紹介。
+交換チケット対象外の白薔薇姫などが狙える点が特徴。
+マイス・ミドつのり・メロトセロイなど候補を幅広く解説。</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>・交換チケット対象外の白薔薇姫やマイスを入手できる
+・ミドつのりは継承で性能が1段引き上がり汎用性高い
+・幻闘場特化スタイルは腐らず便利</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>・マイスは扱いが非常に難しくBP補助が必須
+・正月神など周回スタイルは既存勢は無理に取らなくてよい</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>・63連ガチャ
+・天井交換
+・白薔薇姫
+・ミドつのり
+・幻闘場特化</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I437" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qiw3Bakl7_s</t>
+        </is>
+      </c>
+      <c r="J437" s="2" t="inlineStr">
+        <is>
+          <t>qiw3Bakl7_s</t>
+        </is>
+      </c>
+      <c r="K437" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「飯綱こよみ 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>ロマンシング祭こよみ編のスタイル考察と性能チェック。
+専用武器と継承込みで最終4.75倍の斬の化け物アタッカー。
+火ダメ軽減も持つオールラウンダーで新規に特におすすめ。</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>・専用武器と継承込みで最終4.75倍の超火力
+・火ダメ軽減75%も持ち弱点がないオールラウンダー
+・覚醒のこ玉プラスは誰でも継承でき味方全体強化</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>・新色の御剣の余目上昇は12ターンしか継続しない
+・陰術持ちでナJKに戻ると属性が変わる懸念</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ編
+・専用武器
+・最終4.75倍
+・火ダメ軽減
+・継承覚醒のこ玉</t>
+        </is>
+      </c>
+      <c r="H438" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I438" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=scfNDDD1TjQ</t>
+        </is>
+      </c>
+      <c r="J438" s="2" t="inlineStr">
+        <is>
+          <t>scfNDDD1TjQ</t>
+        </is>
+      </c>
+      <c r="K438" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】幻闘場をじっくり攻略する配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場をじっくり攻略する生配信。
+各武器種でギミックを確認しながらの実戦プレイ。
+最新スタイルやウェポンシステムで快適に攻略。</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>・最新スタイルやウェポンシステムで快適に攻略できる</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
+        <is>
+          <t>・手持ち次第ではOD5連携を出せず苦戦することがある</t>
+        </is>
+      </c>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場攻略
+・生配信
+・武器種別攻略
+・ギミック確認
+・実戦プレイ</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uGNCAA-svUA</t>
+        </is>
+      </c>
+      <c r="J439" s="2" t="inlineStr">
+        <is>
+          <t>uGNCAA-svUA</t>
+        </is>
+      </c>
+      <c r="K439" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「サイヴァ 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>ロマンシング祭サイヴァ編のスタイル考察と性能チェック。
+裁判・サライ・大々の3キャラを評価しランク付け。
+裁判は全体への影響力が高くこの環境屈指の強さ。</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>・裁判はエクストラフォース無条件付与で環境屈指の強さ
+・サライは状態異常解除で無人島適性が高い
+・大々は効果量が全て大で防御も火力もバランス良い</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>・サライの状態異常解除は自身生存が前提という弱点</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>・サイヴァ編
+・裁判評価
+・サライ
+・大々
+・ランク付け</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zt5YvvG0GV8</t>
+        </is>
+      </c>
+      <c r="J440" s="2" t="inlineStr">
+        <is>
+          <t>zt5YvvG0GV8</t>
+        </is>
+      </c>
+      <c r="K440" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】制圧 レイド T260 サラ編成 満額 2分39秒【ロマンシングサガ　リユニバース】</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>制圧レイドT260をサラ編成で満額2分39秒。
+プレイタイムを示す短尺の周回記録動画。
+編成と立ち回りの参考用クリップ。</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>・サラ編成で満額を2分39秒の好タイムで撃破</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr"/>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>・制圧レイド
+・T260
+・サラ編成
+・満額
+・タイム2分39秒</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I441" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y_vxbO8pRBg</t>
+        </is>
+      </c>
+      <c r="J441" s="2" t="inlineStr">
+        <is>
+          <t>y_vxbO8pRBg</t>
+        </is>
+      </c>
+      <c r="K441" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K441"/>
+  <dimension ref="A1:K444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29632,6 +29632,197 @@
         </is>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】6月6日は7.5周年当日！全力でみんなで盛りあがろう！！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>三蔵の7.5周年お祝いライブ配信
+回線トラブルでカクカク続出も視聴者と盛り上がる
+リアム編でアーニャ・リアムを天井手前でコンプ</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>・アーニャの新イラストが神がかって良い
+・視聴者に恵まれ盛り上がった
+・110連でリアム編コンプ達成</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>・配信回線が不安定でカクカク・音切れが多発
+・視聴者が一時2000人以上離脱
+・ガチャのすり抜けが多い</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年
+・ライブ配信
+・ガチャ実況
+・リアム編
+・配信トラブル
+・アーニャ</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=upe2mps2BV0</t>
+        </is>
+      </c>
+      <c r="J442" s="2" t="inlineStr">
+        <is>
+          <t>upe2mps2BV0</t>
+        </is>
+      </c>
+      <c r="K442" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07T01:06:19Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年ガチャ更新前にガチャ引く！～ライブ配信/声あり～</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>あきんの7.5周年ガチャ更新前ライブ配信
+再来狙いも天井までかかる渋い引き
+新OD演出とサイバーの火力を絶賛</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>・新オーバードライブ演出がかっこいい
+・サイバーを入れるだけで火力が激増
+・引き得なガチャでレイドで使える
+・幻闘場は古スタイルも使える良コンテンツ</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>・天井まで引かされ渋い
+・シィレイが残念すぎて引く気にならない
+・T260Gレイドは手持ち不足で満額すら厳しい
+・幻闘場の更新スパンが長い</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>・ライブ配信
+・7.5周年ガチャ
+・再来狙い
+・天井
+・レイド攻略
+・オーバードライブ</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HaM3VBW_aRI</t>
+        </is>
+      </c>
+      <c r="J443" s="2" t="inlineStr">
+        <is>
+          <t>HaM3VBW_aRI</t>
+        </is>
+      </c>
+      <c r="K443" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07T01:06:19Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年Romancing祭トゥ・クアイ編ガチャ評価 #ロマサガRS #shorts #ガチャ</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年Romancing祭トゥ・クアイ編のガチャ評価ショート
+字幕が音楽のみで内容の書き起こしは不可
+タイトルからガチャ評価動画と判断</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr"/>
+      <c r="F444" s="2" t="inlineStr"/>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ評価
+・トゥ・クアイ編
+・ショート動画</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Kl7OcRQLsDY</t>
+        </is>
+      </c>
+      <c r="J444" s="2" t="inlineStr">
+        <is>
+          <t>Kl7OcRQLsDY</t>
+        </is>
+      </c>
+      <c r="K444" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07T01:06:19Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K444"/>
+  <dimension ref="A1:K461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29823,6 +29823,1113 @@
         </is>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「脅威」こよみ超え!?トゥ・クァイのSSSS24連打込み40ヒット&amp;まさかの無尽塔で宴会ダリアス!?の最新サポート型　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>トゥ・クァイとダリアスのサポート型性能を評価。
+トゥ・クァイは追撃ヒット数は多いがサポート爆発力不足。
+ダリアスは状態異常解除のみが取り柄で総合C評価。</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>・トゥ・クァイは技3リピートで40ヒットの猛攻
+・ダリアスは状態異常解除しつつ攻撃できる</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
+        <is>
+          <t>・トゥ・クァイのサポートは爆発しても大したことない
+・ダリアスは弱すぎて総合C・大外れ枠
+・リアムは継承ないと出番なし</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>・トゥ・クァイ
+・ダリアス
+・サポート型
+・SSSS24連打
+・性能評価</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I445" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=20hp9mh1gTw</t>
+        </is>
+      </c>
+      <c r="J445" s="2" t="inlineStr">
+        <is>
+          <t>20hp9mh1gTw</t>
+        </is>
+      </c>
+      <c r="K445" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:32:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】マイス「上位互換」ラゼムの連打力&amp;52連打リアムの底すらない火力!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>ラゼムとリアムの火力性能を評価。
+ラゼムはマイスの上位互換で火力SS総合B。
+リアムは継承込み52連打で瞬発火力が環境随一。</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>・ラゼムの連打アタッカー性能が高い
+・リアムの瞬発火力インパクトは環境随一
+・リアムは継承があるほど対応力が上がる</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>・ラゼムはマイスとほぼ同じで1体あれば十分
+・リアムは継承がないと使い勝手がない</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>・ラゼム
+・リアム
+・マイス上位互換
+・52連打
+・火力SS</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cV3e4m3-DX4</t>
+        </is>
+      </c>
+      <c r="J446" s="2" t="inlineStr">
+        <is>
+          <t>cV3e4m3-DX4</t>
+        </is>
+      </c>
+      <c r="K446" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:32:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】1位は!?「VS第2弾」第1弾と超決戦!!サイヴァ…こよみ…まさかの12体4ガチャランキング!!最新スタイル比較検討会→2026年6月8日版　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>VS第2弾4ガチャ12体の最新ランキング(6/8版)。
+再来サライが最上位、ダイ・ダイ・リアムが上位。
+C-レイ・オルレッド・ダリアス・ストライフは最下位。</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>・再来サライは攻防全て仕上がり最上位評価
+・リアムの50連打の爆発力
+・ダイ・ダイのサポートが圧倒的に強い</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャを引くこと自体は基本おすすめしない
+・C-レイ・ダリアス・オルレッド・ストライフは弱い
+・こよみは対応力がなく結構強いだけ</t>
+        </is>
+      </c>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>・VS第2弾
+・12体ランキング
+・再来サライ
+・リアム
+・引くべきか</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I447" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=e8PqD5IkJts</t>
+        </is>
+      </c>
+      <c r="J447" s="2" t="inlineStr">
+        <is>
+          <t>e8PqD5IkJts</t>
+        </is>
+      </c>
+      <c r="K447" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:32:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】第2弾ランキング&amp;「想定外」アーニャ圧倒的陽引率の実力!!今後の陽編成に必須!?&amp;デバフの波…オルレット　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>第2弾ランキングとアーニャ・オルレッド評価。
+アーニャは陽編成で圧倒的、ホーリーチェーンが強力。
+オルレッドはデバフのみ取り柄で継承頼みの貧弱性能。</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>・アーニャの陽引率とホーリーチェーンが超強力
+・オルレッドの全ステデバフはまだ腐っていない</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>・オルレッドは継承バーニングソング頼みで貧弱
+・毒性染め編成は現環境ではいまい</t>
+        </is>
+      </c>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>・アーニャ
+・オルレッド
+・陽編成
+・ホーリーチェーン
+・デバフ</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lcytxuFlSow</t>
+        </is>
+      </c>
+      <c r="J448" s="2" t="inlineStr">
+        <is>
+          <t>lcytxuFlSow</t>
+        </is>
+      </c>
+      <c r="K448" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:32:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】癖が強いのは強者の証！トゥクアイ編性能確認【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>トゥクアイ編の性能を確認、癖は強いが強者。
+エクストラフォース1.75倍を全体配布し40ヒット。
+条件次第で200億超の爆発力を出せる。</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>・条件が揃えば200億超級の爆発火力
+・残陽全体にエクストラフォース1.75倍を配れる
+・討伐戦など複数戦で強力</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>・効果は5ターン限定で6ターン以降は失速
+・長期戦は絶対NG
+・防御はディフェンスアップ30%のみ</t>
+        </is>
+      </c>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>・トゥクアイ
+・性能確認
+・1.75倍全体
+・40ヒット
+・爆発火力</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I449" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LdLjnUVYle4</t>
+        </is>
+      </c>
+      <c r="J449" s="2" t="inlineStr">
+        <is>
+          <t>LdLjnUVYle4</t>
+        </is>
+      </c>
+      <c r="K449" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:33:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】下剋上なるか！？６大ガチャランキング★引くべき優先順位考察【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年6大ガチャの引くべき優先順位を考察。
+全ガチャを使った所感でランキング化。
+リアムら新キャラは強いが復刻系は様子見。</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>・リアムは容易に30〜40ヒットで強い
+・63年ガチャは大当たりが多く優秀</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>・復刻ロマフェスは回さなくていい
+・セレチケや一部ガチャは無理に引かなくていい</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>・6大ガチャ
+・優先順位
+・ガチャランキング
+・リアム
+・63年ガチャ</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WddZbKUYX7E</t>
+        </is>
+      </c>
+      <c r="J450" s="2" t="inlineStr">
+        <is>
+          <t>WddZbKUYX7E</t>
+        </is>
+      </c>
+      <c r="K450" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:33:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こう使えば最強格！？トゥクアイ検証完了★メリットデメリット共有、普通に強い【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>トゥクアイ検証完了、使い方は難しいが普通に強い。
+集団戦でターゲットを散らすと真価を発揮。
+手動操作が複雑でコマンド管理が必要。</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>・火力がめちゃくちゃ高く普通に強い
+・集団戦でエクストラフォースを複数受けられる
+・月下必殺ザなど必殺技が強力</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>・手動操作がめんどくさく使いづらい
+・防御はディフェンスアップ30%のみ
+・5回制限技を使い切ると一択になる</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>・トゥクアイ
+・検証完了
+・集団戦
+・複雑操作
+・必殺技</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cr6SUs16HIA</t>
+        </is>
+      </c>
+      <c r="J451" s="2" t="inlineStr">
+        <is>
+          <t>cr6SUs16HIA</t>
+        </is>
+      </c>
+      <c r="K451" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:33:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】6人全コンプ済！SSS判定有！最新キャラランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>6人全コンプ済みで最新キャラランキングを作成。
+ダリアスは多才だが防御50%・火力不足でA止まり。
+バランス重視で実際の使いやすさを評価。</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>・ダリアスは多才なサポートで斧討伐に使える
+・ウィルはヒット数が多く火力も出せる</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>・ダリアスは防御50%が低く火力も出ずA止まり
+・オルレッドは以前ほどではなくイマイチ</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>・キャラランキング
+・6人全コンプ
+・ダリアスA
+・SSS判定
+・バランス評価</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lNkXzgW-1Os</t>
+        </is>
+      </c>
+      <c r="J452" s="2" t="inlineStr">
+        <is>
+          <t>lNkXzgW-1Os</t>
+        </is>
+      </c>
+      <c r="K452" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:33:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】圧倒的破壊力★危険な２人！超戦士は眠れない！！ラゼム＆リアム相性ばっちり！メリットデメリット共有【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>ラゼムとリアムの検証完了、相性は抜群。
+ラゼムはマイス上位の破壊力で普通に強い。
+リアムはOD満タ維持で40ヒットの高火力。</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>・ラゼムとリアムの相性が抜群で一緒に使える
+・ラゼムはマイスより破壊力がありそう
+・リアムはヒット数が多く普通に強い</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>・ラゼムは高速ジュエルビストンと相性が悪い
+・リアムは防御強化があまり高くない
+・ラゼムはBP・サイ点増加のデメリットあり</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>・ラゼム
+・リアム
+・相性抜群
+・マイス上位
+・40ヒット</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nLj3AIdxrx0</t>
+        </is>
+      </c>
+      <c r="J453" s="2" t="inlineStr">
+        <is>
+          <t>nLj3AIdxrx0</t>
+        </is>
+      </c>
+      <c r="K453" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:33:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】すりぬけ連発！！！かぶり連打！！160連！！りあむ＆トゥクアイ編ガチャ【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>りあむ＆トゥクアイ編ガチャを160連実施。
+すりぬけ連発・かぶり連打の渋い引き。
+マイク不調で音声なしのまま投稿。</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr"/>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>・すりぬけが連発し渋い
+・かぶり連打で効率が悪い</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ160連
+・りあむ
+・トゥクアイ
+・すりぬけ連発
+・かぶり</t>
+        </is>
+      </c>
+      <c r="H454" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vdyIX030iCw</t>
+        </is>
+      </c>
+      <c r="J454" s="2" t="inlineStr">
+        <is>
+          <t>vdyIX030iCw</t>
+        </is>
+      </c>
+      <c r="K454" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:33:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】この世界線を救いに来た！第２部主人公軍団性能確認【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>第2部主人公軍団リアム・アーニャの性能を確認。
+リアムは40ヒットだがOD後は3ヒットで威力D懸念。
+アーニャは陽編成バッファーで防御87%と硬い。</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>・アーニャは陽編成でホーリーチェーン3重で火力増
+・アーニャは防御87%と硬いバッファー
+・リアムはリキャスト技で40ヒットの高火力</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>・リアムはオーバーフロー後3ヒットで威力D
+・前回リアムの方が防御強化は高い</t>
+        </is>
+      </c>
+      <c r="G455" s="2" t="inlineStr">
+        <is>
+          <t>・第2部主人公
+・リアム
+・アーニャ
+・陽編成
+・ホーリーチェーン</t>
+        </is>
+      </c>
+      <c r="H455" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=weR9mv-1k7o</t>
+        </is>
+      </c>
+      <c r="J455" s="2" t="inlineStr">
+        <is>
+          <t>weR9mv-1k7o</t>
+        </is>
+      </c>
+      <c r="K455" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:33:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはり確保案件はあの2人！？最新版新ガチャ確保ランキング！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>最新版の新ガチャ確保優先度ランキングを発表。
+性能のみで最優先〜優先度低の4段階で評価。
+サイバー・こよみが最優先級で非常に優秀。</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>・サイバー・こよみは最優先級で超優秀
+・サライ・代々・聖王も強力で陰属性が良い</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>・復刻5スタイルは優先度低
+・ガチャが5日単位で来て悩ましい</t>
+        </is>
+      </c>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>・確保ランキング
+・優先度4段階
+・サイバー
+・こよみ
+・7.5周年</t>
+        </is>
+      </c>
+      <c r="H456" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7WrQXpvGvlA</t>
+        </is>
+      </c>
+      <c r="J456" s="2" t="inlineStr">
+        <is>
+          <t>7WrQXpvGvlA</t>
+        </is>
+      </c>
+      <c r="K456" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:35:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】かつて人権と呼ばれた男の復権！？リアム編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>リアム編ガチャの性能を詳しくチェック。
+ダリアスは斧の闇サポーターで全体強化が豊富。
+攻撃強化・OD上昇・状態異常全解除を備える。</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>・ダリアスは味方全体の攻撃・防御強化が豊富
+・ターン終了時の状態異常全解除を備える
+・ODゲージ上昇やBP回復のサポートもある</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="inlineStr">
+        <is>
+          <t>・実装直後で不明点があり評価は暫定</t>
+        </is>
+      </c>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>・リアム編
+・ダリアス
+・斧サポーター
+・全体強化
+・性能チェック</t>
+        </is>
+      </c>
+      <c r="H457" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I457" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DRSOgq7Kxzw</t>
+        </is>
+      </c>
+      <c r="J457" s="2" t="inlineStr">
+        <is>
+          <t>DRSOgq7Kxzw</t>
+        </is>
+      </c>
+      <c r="K457" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:35:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】閲覧注意！この動画を見るとリアムを欲しくなってしまうかも？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>リアムは強いが今は焦って引くなと注意喚起。
+6月11日・16日と連続でガチャが控えている。
+短期決戦で将来総点弾継承のリアムが強烈。</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>・リアムは短期決戦で将来総点弾継承が強烈
+・7.5周年で討伐の難易度が下がった</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>・連続ガチャが控えるため今は焦って引かない方が良い
+・討伐セルマルカは作業がめんどくさい</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>・リアム
+・閲覧注意
+・連続ガチャ
+・継承
+・討伐</t>
+        </is>
+      </c>
+      <c r="H458" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Xxt8EaNRa70</t>
+        </is>
+      </c>
+      <c r="J458" s="2" t="inlineStr">
+        <is>
+          <t>Xxt8EaNRa70</t>
+        </is>
+      </c>
+      <c r="K458" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:35:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】実はこっちのガチャが当たり説！？トゥ・クアイ編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>トゥ・クアイ編ガチャの性能をチェック。
+ラゼムは剣の光アタッカーで追撃が非常に多い。
+全体BP+5だが消費BPも重くなるデメリット。</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>・ラゼムは追撃が多くヒット数が豊富
+・味方全体にOD・ウィーク攻撃強化150%とBP+5</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
+        <is>
+          <t>・ラゼムがいると味方全員の消費BPが5重くなる</t>
+        </is>
+      </c>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>・トゥ・クアイ編
+・ラゼム
+・剣アタッカー
+・追撃多数
+・BPデメリット</t>
+        </is>
+      </c>
+      <c r="H459" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I459" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Z-K-TNNtR4E</t>
+        </is>
+      </c>
+      <c r="J459" s="2" t="inlineStr">
+        <is>
+          <t>Z-K-TNNtR4E</t>
+        </is>
+      </c>
+      <c r="K459" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:35:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】把握必須の情報解説！神速陣・改が周回に最強過ぎた！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>制圧戦交換所に追加された神速陣・改を解説。
+周回向けに最強級で旧版から大幅強化。
+チャンネル登録6万人達成の報告も。</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>・神速陣・改が超便利で周回に最強級
+・旧版からめちゃくちゃ強化された</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>・6月6日のライブ配信がYouTube混雑でカクカク・音飛び</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>・神速陣・改
+・制圧戦交換所
+・周回最強
+・大幅強化
+・6万人達成</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iCuRx1PGihE</t>
+        </is>
+      </c>
+      <c r="J460" s="2" t="inlineStr">
+        <is>
+          <t>iCuRx1PGihE</t>
+        </is>
+      </c>
+      <c r="K460" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:35:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】6月6日は7.5周年当日！全力でみんなで盛りあがろう！！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年当日の記念ライブ配信(本編)。
+配信ラグや残像が続くトラブルに見舞われる。
+配信中にチャンネル6万人を達成し祝う。</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>・配信中にチャンネル登録6万人を達成</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>・配信のラグ・カクカクが続くトラブル</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年
+・ライブ配信
+・配信ラグ
+・6万人達成
+・お祝い</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I461" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xm5oIQvvi-U</t>
+        </is>
+      </c>
+      <c r="J461" s="2" t="inlineStr">
+        <is>
+          <t>xm5oIQvvi-U</t>
+        </is>
+      </c>
+      <c r="K461" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08T13:35:35Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K461"/>
+  <dimension ref="A1:K468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30930,6 +30930,455 @@
         </is>
       </c>
     </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】とあるデータで確定「4体ネタバレ」7.5周年第3弾でついに八歌仙揃う!?ガチのあと1枠を誰が獲得するかガチャ予想!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年第3弾ガチャを予想する動画
+データから新規4体が確定との情報
+八歌仙完成かあと1枠の獲得を考察</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr"/>
+      <c r="F462" s="2" t="inlineStr"/>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年第3弾
+・ガチャ予想
+・八歌仙
+・新規4体確定
+・あと1枠</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4RfmqvhoZnY</t>
+        </is>
+      </c>
+      <c r="J462" s="2" t="inlineStr">
+        <is>
+          <t>4RfmqvhoZnY</t>
+        </is>
+      </c>
+      <c r="K462" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10T01:07:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今週の井戸「大ダメージ」満額オート!!こよみ無し勢にシルバードラゴン井戸ランクインの可能性は!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>今週の井戸はシルバードラゴン討伐
+ランクインには1ターン討伐が条件
+暦み・サイバ等が有力で満額オート達成</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>・暦みは弱点を突けて非常に有力
+・桁違いのダメージで1人余裕残し討伐</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>・1ターン討伐できるメンツは手持ちにいない</t>
+        </is>
+      </c>
+      <c r="G463" s="2" t="inlineStr">
+        <is>
+          <t>・井戸
+・シルバードラゴン
+・1ターン討伐
+・満額オート
+・こよみ</t>
+        </is>
+      </c>
+      <c r="H463" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_KYXJZzCjQg</t>
+        </is>
+      </c>
+      <c r="J463" s="2" t="inlineStr">
+        <is>
+          <t>_KYXJZzCjQg</t>
+        </is>
+      </c>
+      <c r="K463" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10T01:07:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　後悔先に立たず　今でも悔やむキャラランキング</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>取り逃して後悔したキャラTOP5を紹介
+1位ビクトル、2位シマなどを挙げる
+性能を見極めて確保すべきと教訓を語る</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトルは火力もバフも高く最高のキャラ
+・シマは能力上昇＋自火力で超王樹級
+・木ハはモーション速く周回で活躍
+・ウンディネは術＋霊で編成を組みやすい</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>・アタッカーだからと安易に確保を見送った
+・ウンディネはエクストラフォース無し
+・ゲは新規アタッカー増で価値が薄れ気味</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>・後悔キャラランキング
+・ビクトル
+・シマ
+・木ハ
+・確保優先度</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8dDfG2O4smw</t>
+        </is>
+      </c>
+      <c r="J464" s="2" t="inlineStr">
+        <is>
+          <t>8dDfG2O4smw</t>
+        </is>
+      </c>
+      <c r="K464" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10T01:07:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始250日目　メインミッションが想像以上に難しい</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣250日目の進捗報告
+特性上げで戦力強化、異名育成へ方針転換
+メインミッションの3拠点制圧が難関</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>・特性を上げたら途端に強くなり落ちにくい
+・新キャラ5体入手、島左近が復勝に刺さる
+・軍雄リーグは徳川優遇で勝率が良い
+・石田三成が優秀で勢力戦を維持できる</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
+        <is>
+          <t>・メインミッションの3完全制圧がきつい
+・拠点移動が月3個しか買えず厳しい
+・イベント1万位目標がいよいよ厳しい
+・釘ばかり溜まり巻物素材が枯渇する</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>・信長の野望出陣
+・250日目
+・特性上げ
+・メインミッション
+・制圧率</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I465" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=U1C9F3uw224</t>
+        </is>
+      </c>
+      <c r="J465" s="2" t="inlineStr">
+        <is>
+          <t>U1C9F3uw224</t>
+        </is>
+      </c>
+      <c r="K465" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10T01:07:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】大本命ガチャがやってくる！？！遂に全員が揃う予感...【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>6月11日の7.5周年第3弾ガチャを予想
+前回と同じヴンセント等6スタイルを本命視
+八歌仙完成を見込みパーフェクトを狙う</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>・前回予想と同じでパーフェクトを狙える自信
+・7.5周年は祭りで全力で盛り上がれる</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャラッシュで予想動画の制作が大忙し
+・予想が簡単すぎて動画作りに悩む</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>・6月11日ガチャ
+・7.5周年第3弾
+・ガチャ予想
+・八歌仙
+・アビスキャラ</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tyfzUlcVSfc</t>
+        </is>
+      </c>
+      <c r="J466" s="2" t="inlineStr">
+        <is>
+          <t>tyfzUlcVSfc</t>
+        </is>
+      </c>
+      <c r="K466" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10T01:07:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ダイ・ダイの仕掛け気づきました？ #ロマサガRS #shorts</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>ダイ・ダイのスタイルの仕掛けに気づくShorts
+各種バフが全て『大』効果になる仕組み
+HP回復やガードアップ等が全部ダイヤ対応</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>・全効果が『大』になる作り込みが凄い</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr"/>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>・ダイ・ダイ
+・仕掛け
+・全効果『大』
+・バフ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LKx12CytI3Y</t>
+        </is>
+      </c>
+      <c r="J467" s="2" t="inlineStr">
+        <is>
+          <t>LKx12CytI3Y</t>
+        </is>
+      </c>
+      <c r="K467" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10T01:07:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】2026年6月上旬ガチャ総まとめ！全12スタイル引くべきスタイルランキング！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>6月上旬実装の全12スタイルをティア評価
+暦みとサイバーが最優先の最高ランク
+ラーゼムやリアム等を用途別に解説</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>・暦みは4.75倍火力で弱点なしオールラウンダー
+・サイバーは最終ダメ1.87倍＋看門周回特攻
+・ラーゼムは使いこなせば非常に強力
+・オルレッは6月幻統上デスに刺さる性能</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>・サイバーは火ダメ軽減が低くEF被りに注意
+・シーレは火力・軽減・バフが弱く器用貧乏
+・ダリアスはサポートが中途半端で削りも低い
+・トークアイはメイン技5回制限で火力低下</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>・6月上旬ガチャ
+・ティアランク
+・暦み
+・サイバー
+・引くべきスタイル</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=p1eoKrQ5Oqk</t>
+        </is>
+      </c>
+      <c r="J468" s="2" t="inlineStr">
+        <is>
+          <t>p1eoKrQ5Oqk</t>
+        </is>
+      </c>
+      <c r="K468" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10T01:07:08Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K468"/>
+  <dimension ref="A1:K480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31379,6 +31379,786 @@
         </is>
       </c>
     </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】限定を超えろ!!「最強プラチナ」スタイルは誰!?どれも即時活用可能なステージをご紹介　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>プラチナガチャ新スタイル3体の性能を詳細評価
+フランシスは打突熱バフの置き物型として優秀
+3体目はレイドでも活躍できるアタッカー性能</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>・打突熱バフ最大1690%と置き物としてなかなかの性能
+・アタッカーとしてレイドでも活躍できる強さ
+・新規の手持ち不足を補うありがたいプラチナガチャ
+・直近のバッハ・デスを知力デバフで封殺できる</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>・シルバー自体は使い勝手がなさそうで継承頼み
+・永続追撃の起点が単体攻撃で動きが固定される構造
+・縛りあり前提の強さで運用が難しい</t>
+        </is>
+      </c>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>・プラチナガチャ
+・スタイル性能評価
+・継承技
+・レイド適性
+・置き物バフ</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I469" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IZWZ9fheM1I</t>
+        </is>
+      </c>
+      <c r="J469" s="2" t="inlineStr">
+        <is>
+          <t>IZWZ9fheM1I</t>
+        </is>
+      </c>
+      <c r="K469" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11T01:10:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「最速周回」ラストレイド聖王厄!!気絶させてくれるのを活用し2分を切れ!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>聖王厄レイドの最速周回編成を紹介
+3ターン目の割合ダメージによる気絶を活用
+うまく気絶すれば1分台後半、2分切りが可能</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>・気絶をうまく活用すれば1分台後半の高速周回が可能
+・自由枠ありでも2分前半を狙える編成</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>・自動周回で気絶を安定させるのが難しい
+・うまく倒れてくれないと2分40秒ほどかかる</t>
+        </is>
+      </c>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>・聖王厄レイド
+・最速周回
+・気絶活用
+・編成紹介</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MWlrcJMsrBA</t>
+        </is>
+      </c>
+      <c r="J470" s="2" t="inlineStr">
+        <is>
+          <t>MWlrcJMsrBA</t>
+        </is>
+      </c>
+      <c r="K470" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11T01:10:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「推しが来た」八歌仙よりソティだ!?エスパーギャルのハイ◯グが止まらないハーフアニバーサリー第3弾お知らせ!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>ハーフアニバーサリー第3弾のお知らせを確認
+ソティ登場、ロボ・白薔薇は来ず予想通りの展開
+第4弾以降の高難度に備え魂アビリティ準備を推奨</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>・ロボや白薔薇が来なかったのは良し
+・残りのキャラは性能重視で来そうで注目</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>・2度目のしょぼい報酬追加で制圧戦締めくくり
+・ガチャだけの更新で内容があっさり
+・7月の水着ガチャに備え周年で使いすぎ注意</t>
+        </is>
+      </c>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>・ハーフアニバ第3弾
+・ソティ
+・制圧戦
+・ガチャ計画
+・水着ガチャ</t>
+        </is>
+      </c>
+      <c r="H471" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=khQRtjLOE_I</t>
+        </is>
+      </c>
+      <c r="J471" s="2" t="inlineStr">
+        <is>
+          <t>khQRtjLOE_I</t>
+        </is>
+      </c>
+      <c r="K471" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11T01:10:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】八歌仙揃い踏み！6月11日更新情報まとめ【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>6月11日更新の7.5周年記念ガチャ第3弾まとめ
+クロエ編とダリオ編で八歌仙の新スタイルが勢揃い
+次回更新は6月16日と早めのペースで続く</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>・八歌仙の新イラスト勢がついに揃いガチャを回す価値あり
+・ガチャは回す予定と前向き</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>・T260Gと白薔薇のアビス版がまだ来ない
+・メモリアの追加報酬に限定装備などの目玉はなし</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年第3弾
+・八歌仙
+・ロマンシングフェス
+・更新情報まとめ</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AjhzNsF5t_U</t>
+        </is>
+      </c>
+      <c r="J472" s="2" t="inlineStr">
+        <is>
+          <t>AjhzNsF5t_U</t>
+        </is>
+      </c>
+      <c r="K472" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11T01:10:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】限定無し！6月12日ガシャ予告！ 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>6月12日ガシャ予告、限定なしの恒常2体
+インフィニットジャスティス(攻撃型)がUR登場
+ストライクノワール(支援型)も同時実装</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>・いつかUR化を期待していたインジャスがついに登場
+・限定ではなく恒常なのでいつか引ける安心感</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>・スターゲイザー本体はUR実装されず
+・ナイチンゲール100連爆死のダメージが残りダイヤ温存
+・限定なしなので今回は我慢と判断</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ガシャ予告
+・インフィニットジャスティス
+・ストライクノワール</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rqjWIPkyuV0</t>
+        </is>
+      </c>
+      <c r="J473" s="2" t="inlineStr">
+        <is>
+          <t>rqjWIPkyuV0</t>
+        </is>
+      </c>
+      <c r="K473" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11T01:10:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】限定無し！6月12日ガシャ予告！ #SDガンダムGジェネレーションエターナル ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>6月12日ガシャ予告、限定なしの恒常2体
+インフィニットジャスティス(攻撃型)がUR登場
+ストライクノワール(支援型)も同時実装</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>・いつかUR化を期待していたインジャスがついに登場
+・限定ではなく恒常なのでいつか引ける安心感</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>・スターゲイザー本体はUR実装されず
+・ナイチンゲール100連爆死のダメージが残りダイヤ温存
+・限定なしなので今回は我慢と判断</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ガシャ予告
+・インフィニットジャスティス
+・ストライクノワール</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=skuyyRKuLhQ</t>
+        </is>
+      </c>
+      <c r="J474" s="2" t="inlineStr">
+        <is>
+          <t>skuyyRKuLhQ</t>
+        </is>
+      </c>
+      <c r="K474" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11T01:10:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今しかない！聖王レイド満額1:52★代用編成検証有！環境最強キャラを育成しつくそう！！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>聖王厄レイドを複数編成で検証、満額1分52秒
+ビクトールなし等の代用編成でも2分台で周回可能
+安定編成は1分50〜59秒で自動周回向き</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトールが環境最強級で驚きの強さ
+・ビクトール枠はサラや空海でも代用可能
+・視聴者と編成を共有し合う協力体制が良い
+・あんずもんさんの検証企画が素晴らしいと絶賛</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>・全滅周回は味方が狙い通り落ちず安定させにくい
+・バフ重複など編成ミスに注意が必要</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>・聖王厄レイド
+・周回検証
+・代用編成
+・ビクトール
+・全滅周回</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I475" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gxZHLpW5SYg</t>
+        </is>
+      </c>
+      <c r="J475" s="2" t="inlineStr">
+        <is>
+          <t>gxZHLpW5SYg</t>
+        </is>
+      </c>
+      <c r="K475" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11T01:10:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS】止まるんじゃねぇぞ、、陰属性実装されすぎて独走状態【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>第3弾ガチャのクロエ編・ダリオ編を考察
+新規6スタイル中3体が闇属性でさらに闇が加速
+ヴィンセントは継承技込みで瞬間火力に期待</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>・ヴィンセントは継承技で瞬間火力がえげつなくなりそう
+・ボルカノは毎回いい線の性能で今回も期待
+・ソティはロマパス継承技が結構強い
+・クロエ編を回す予定と前向き</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>・闇属性が実装されすぎて独走状態とバランスに疑問
+・光・棍棒周りは周回環境ほど強くない
+・エクストラフォース倍率が低くダメージが出ない問題</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>・第3弾ガチャ考察
+・闇属性
+・クロエ
+・ヴィンセント
+・八歌仙</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pcwqzhfyARI</t>
+        </is>
+      </c>
+      <c r="J476" s="2" t="inlineStr">
+        <is>
+          <t>pcwqzhfyARI</t>
+        </is>
+      </c>
+      <c r="K476" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11T01:10:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>【スマグロ】イベントやるよ！</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>久々のスマグロ配信で新イベントとガチャに挑戦
+ロトガチャで10連ピックアップ4つの神引き
+30階ローグライク攻略とマルチ竜王戦も検証</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>・10連でピックアップ4つ・念願のロト盾入手の神引き
+・キラーマシンは攻撃力96でめちゃくちゃ強い
+・攻撃速度ビルドが爽快で楽しい
+・視聴者との協力マルチでギリギリクリアが楽しい</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>・ピックアップ率2%は渋く無課金で揃えるのは困難
+・超難しい竜王マルチは竜王武器なしではほぼ無理
+・ミルザバグのお詫びがジュエル110のみで少ない
+・30階攻略は長くて時間がかかりすぎる</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>・スマグロ
+・ロトシリーズガチャ
+・キラーマシン
+・竜王マルチ
+・ローグライク階層</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pgAth-1J32w</t>
+        </is>
+      </c>
+      <c r="J477" s="2" t="inlineStr">
+        <is>
+          <t>pgAth-1J32w</t>
+        </is>
+      </c>
+      <c r="K477" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11T01:10:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】これで主役が全員揃った！7.5周年ガチャ第3弾に大本命がやってきた！？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年第3弾で八歌仙ガチャが全員集合
+クロエ編とダリオ編の計6スタイルが登場
+後半は予想企画の答え合わせ、5キャラ正解者も</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>・待望の八歌仙全員集合でテンション上がる
+・クロエは江島先生の書が使われ魅力的なキャラ
+・ガチャ開催期間が長く見比べて選べる優しさ
+・予想企画は120名参加・70名が4キャラ正解と盛況</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>・6スタイル中5つが杖でバランスが悪い
+・5日に1回のガチャ実装ペースはさすがに怖い
+・イベント追加がなくあっさりしたお知らせ</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年第3弾
+・八歌仙全員集合
+・クロエ
+・予想企画
+・ガチャ告知</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=n2d6NWgvweQ</t>
+        </is>
+      </c>
+      <c r="J478" s="2" t="inlineStr">
+        <is>
+          <t>n2d6NWgvweQ</t>
+        </is>
+      </c>
+      <c r="K478" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11T01:10:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】2T全滅1分50秒〜聖王〔厄〕レイド〜（仲間のユーキルさん・軽油さん編成）</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>仲間考案の聖王厄レイド2ターン全滅周回を紹介
+デバフ魂を外し体勢を下げる防具で調整
+1分51秒、理想運用なら1分40秒も可能</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="inlineStr">
+        <is>
+          <t>・仲間考案の編成で1分40秒の高速周回も可能</t>
+        </is>
+      </c>
+      <c r="F479" s="2" t="inlineStr">
+        <is>
+          <t>・ダメージがギリギリ届かないことが多く記憶周回推奨
+・暦みに攻撃が入らないとやり直しが必要</t>
+        </is>
+      </c>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>・聖王厄レイド
+・2ターン全滅
+・周回編成
+・クァイ</t>
+        </is>
+      </c>
+      <c r="H479" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=i-8HmdLVHvo</t>
+        </is>
+      </c>
+      <c r="J479" s="2" t="inlineStr">
+        <is>
+          <t>i-8HmdLVHvo</t>
+        </is>
+      </c>
+      <c r="K479" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11T01:10:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】聖王〔厄〕レイド〜井戸キャラ：2:17</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>聖王厄レイドを井戸キャラ編成で周回
+タイムは2分17秒
+実況なしのプレイ映像のみの動画</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr"/>
+      <c r="F480" s="2" t="inlineStr"/>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>・聖王厄レイド
+・井戸キャラ
+・周回タイム</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=p5ae4WTQ2Tw</t>
+        </is>
+      </c>
+      <c r="J480" s="2" t="inlineStr">
+        <is>
+          <t>p5ae4WTQ2Tw</t>
+        </is>
+      </c>
+      <c r="K480" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11T01:10:25Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K480"/>
+  <dimension ref="A1:K507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32159,6 +32159,1764 @@
         </is>
       </c>
     </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ランク付け「八歌仙後編」!!武器種の枠を超えた便利さソティ&amp;目覚めろダリオの32連打エクストラ2.25倍!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>八歌仙後編のソティとダリオをランク付け評価
+ソティは武器種を超えたリンク配布の便利枠だが火力は控えめ
+ダリオはEX2.25倍と32連打追撃で隙のない優等生アタッカー</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
+          <t>・ソティは幅広く薄くサポートでき入れてみたら便利な使用感
+・ダリオは継承込み6コード32ヒットの追撃が強くブレがない
+・ダリオはEX合計2.25倍で防御サポートも91〜94%と鉄壁
+・今回ガチャではヴィンセントとボルカノが少し抜けて強い</t>
+        </is>
+      </c>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>・ソティはエクストラもステバフもなく火力にパンチがない
+・ソティの上ぶれは確率25%頼みでスカもあり拡張性がない
+・ダリオは爆裂火力ではなくサポートも普通で突き抜け感がない
+・悩ましいダブルガチャで残りのガチャを検討してから引くべき</t>
+        </is>
+      </c>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>・ソティ性能評価
+・ダリオ性能評価
+・八歌仙ランク付け
+・EX2.25倍
+・確保優先度</t>
+        </is>
+      </c>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I481" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DWu9HTp1LSw</t>
+        </is>
+      </c>
+      <c r="J481" s="2" t="inlineStr">
+        <is>
+          <t>DWu9HTp1LSw</t>
+        </is>
+      </c>
+      <c r="K481" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「有力」新たな陰EXと筆でしっかり殴る個人火力!!ヴィンセントガチャの価値とは!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>ヴィンセントガチャ副産物キャラの性能を評価
+自身はEX・OD合計3.75倍の個人火力を持つサブアタッカー
+陰EX1.5倍配布は有力だが拡張性不足で総合評価B</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>・自身の火力補正はEX・OD合計で3.75倍と結構強い
+・全体術680%・単体術800%の自力バフも結構強い
+・各行動パターンで自己完結できるBP周りで隙のない個人性能
+・毎ターンODゲージ55%供給は結構便利</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>・EXは1.5倍止まりで爆発力がなく縛りも結構きつい
+・火力サポートは3回上限で最近の拡張性トレンドに欠ける
+・陰卒としての編成価値は副産物レベルで総合評価B</t>
+        </is>
+      </c>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>・ヴィンセントガチャ
+・陰EX1.5倍
+・サブアタッカー
+・総合評価B
+・確保優先度</t>
+        </is>
+      </c>
+      <c r="H482" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=G-9HoTXcfZw</t>
+        </is>
+      </c>
+      <c r="J482" s="2" t="inlineStr">
+        <is>
+          <t>G-9HoTXcfZw</t>
+        </is>
+      </c>
+      <c r="K482" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「熱最強」EX2.25倍の拡張性を併せ持つ無限バフボルカノ&amp;刹那的火力サポート熱1.75倍にBP99で枯渇無し!?エスパーギャル　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D483" s="2" t="inlineStr">
+        <is>
+          <t>熱EX2.25倍まで拡張できる無限バフのボルカノを評価
+エスパーギャルは熱EX1.75倍配布とBP99減で螺旋対策向き
+両者とも熱術アタッカー不足が課題で総合評価はB</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
+          <t>・ボルカノの熱術EX2倍付与はかなり強力で継承込み2.25倍に拡張可
+・ボルカノの防御は87〜94%と環境最高クラスの強さ
+・エスパーギャルの消費BP99減少3ターンは螺旋やレイド熱編成で便利
+・エスパーはBPサポーターの割に5行動44ヒットで殴れる</t>
+        </is>
+      </c>
+      <c r="F483" s="2" t="inlineStr">
+        <is>
+          <t>・良い熱術アタッカーが不在で熱編成の展望は割と絶望的
+・エスパーの追撃は威力オールEでストライフよりかなり弱い
+・両者とも総合評価Bで狙って取るには苦しいガチャ</t>
+        </is>
+      </c>
+      <c r="G483" s="2" t="inlineStr">
+        <is>
+          <t>・ボルカノ性能評価
+・エスパーギャル
+・熱EX2.25倍
+・BP99対策
+・熱編成不足</t>
+        </is>
+      </c>
+      <c r="H483" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I483" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MBrA6Y0mOqc</t>
+        </is>
+      </c>
+      <c r="J483" s="2" t="inlineStr">
+        <is>
+          <t>MBrA6Y0mOqc</t>
+        </is>
+      </c>
+      <c r="K483" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「全員EX1.75倍」ヴィンセントが更なる境地へ…毎ターン撃てるファントムコール+モドキ!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>新ヴィンセントは毎ターン撃てるファントムコール系が武器
+呪い印で防御弱化は最大2万5500%、全体に技術EX1.75倍配布
+火力SS汎用SSの総合評価Sだが引くのは高難度出揃い後で良い</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>・全員に技&amp;術EX1.75倍を配れる環境最高峰の火力サポート
+・呪い印込みで防御弱化は最大2万5500%に到達し十分強い
+・全ステバフ最大675%ばら撒きと高防御で防御面も安心
+・配布版から純粋にパワーアップし個人火力もしっかり出る</t>
+        </is>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>・追撃は5行動9ヒットと少なくサブアタッカーとしては最後峰止まり
+・回避もダメブロもなく無人島適性は火力くらいしかない
+・まだ引く必要はなく高難易度が出揃ってからじわじわ引くべき</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>・ヴィンセント新スタイル
+・ファントムコール+
+・呪い印
+・EX1.75倍配布
+・ガチャは様子見</t>
+        </is>
+      </c>
+      <c r="H484" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I484" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=loS31UfSI2Q</t>
+        </is>
+      </c>
+      <c r="J484" s="2" t="inlineStr">
+        <is>
+          <t>loS31UfSI2Q</t>
+        </is>
+      </c>
+      <c r="K484" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　確保できて良かった　入手できて良かったキャラランキング</t>
+        </is>
+      </c>
+      <c r="D485" s="2" t="inlineStr">
+        <is>
+          <t>入手して良かったキャラベスト5を発表(現行ガチャは除外)
+5位マイス、4位加藤しのぶ、3位AJ、2位ウィル
+1位はアプデで化けた雪だるま、レイド攻略の救世主に</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="inlineStr">
+        <is>
+          <t>・雪だるまはアプデで仲間呼び中もODが使え無条件EX1.75倍が強力
+・ウィルは硬さに加え全体回避や回復などサポートが充実
+・AJは反撃5回追撃が強く制圧戦の火力の決め手になった
+・加藤しのぶのおかげで無人島がめちゃくちゃ楽しくなった
+・マイスは貴重なアンサガ製アタッカーで幻闘場でも使える</t>
+        </is>
+      </c>
+      <c r="F485" s="2" t="inlineStr">
+        <is>
+          <t>・雪だるまは以前は追撃がなく周回やレイドで使いにくい印象だった
+・ウィルはEP回復がない点だけが惜しい
+・加藤しのぶは覚えさせたい技を日々周回してもなかなか覚えない</t>
+        </is>
+      </c>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>・キャラランキング
+・雪だるま
+・ウィル
+・AJ
+・加藤しのぶ
+・マイス</t>
+        </is>
+      </c>
+      <c r="H485" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I485" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xgD8A1Awas0</t>
+        </is>
+      </c>
+      <c r="J485" s="2" t="inlineStr">
+        <is>
+          <t>xgD8A1Awas0</t>
+        </is>
+      </c>
+      <c r="K485" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SR ソードインパルスガンダム  武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSRソードインパルスガンダムを紹介
+武装攻撃アニメーションを収めたショート動画
+セリフ付きの戦闘演出を短時間でチェックできる</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr"/>
+      <c r="F486" s="2" t="inlineStr"/>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ソードインパルス
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H486" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-oFtw42xfr4</t>
+        </is>
+      </c>
+      <c r="J486" s="2" t="inlineStr">
+        <is>
+          <t>-oFtw42xfr4</t>
+        </is>
+      </c>
+      <c r="K486" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】インジャとノワールの性能が一部公開されたので確認しよう 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D487" s="2" t="inlineStr">
+        <is>
+          <t>新ユニットのインジャとストライクノワールの公開性能を確認
+インジャはクリ特化攻撃型、ノワールは2体指定マップ兵器の支援型
+今回は恒常のみで限定なし、ガチャはすり抜け待ちの我慢推奨</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="inlineStr">
+        <is>
+          <t>・インジャはクリ率上昇持ちでEX武装のクリダメアップを発動させやすい
+・ノワールのEX武装は射程1〜5でかなり使いやすい
+・ノワールは2体指定かつ移動後発動可の変わったマップ兵器持ち
+・スヴェンは支援回数2回で恒常としてシンプルに使いやすい支援キャラ</t>
+        </is>
+      </c>
+      <c r="F487" s="2" t="inlineStr">
+        <is>
+          <t>・インジャのアビリティは超一撃テンションが条件でテンション上げが必要
+・サポーターのカガリは作品縛り+エネルギー回復でここ最近で一番微妙
+・恒常ユニットのみで限定がいないため今回のガチャは我慢で見送り</t>
+        </is>
+      </c>
+      <c r="G487" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・インフィニットジャスティス
+・ストライクノワール
+・新ガチャ性能
+・サポーター評価</t>
+        </is>
+      </c>
+      <c r="H487" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I487" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=58V0FDSTo8s</t>
+        </is>
+      </c>
+      <c r="J487" s="2" t="inlineStr">
+        <is>
+          <t>58V0FDSTo8s</t>
+        </is>
+      </c>
+      <c r="K487" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SR ブラストインパルスガンダム  武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSRブラストインパルスガンダム紹介
+武装攻撃のアニメーションを収めたショート動画
+戦闘ボイスとともに各武装の演出を確認できる</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr"/>
+      <c r="F488" s="2" t="inlineStr"/>
+      <c r="G488" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ブラストインパルス
+・武装アニメ
+・ショート動画</t>
+        </is>
+      </c>
+      <c r="H488" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I488" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JMI1jiAw6bk</t>
+        </is>
+      </c>
+      <c r="J488" s="2" t="inlineStr">
+        <is>
+          <t>JMI1jiAw6bk</t>
+        </is>
+      </c>
+      <c r="K488" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】火力高めで使いやすい！URストライクノワールの性能確認 #SDガンダムGジェネレーションエターナル ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D489" s="2" t="inlineStr">
+        <is>
+          <t>6月12日実装のURストライクノワール性能を確認
+射程1〜5のEX武装や2体指定マップ兵器が特徴
+支援回数2回のダメージ特化支援キャラと評価</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>・EX武装が射程1〜5でかなり使いやすい
+・マップ兵器は2体指定で防御20%減デバフ、移動後も発動可
+・支援回数2回で恒常の支援キャラとしてかなり使いやすい
+・搭乗縛りが緩くシンプルにダメージを出しやすい</t>
+        </is>
+      </c>
+      <c r="F489" s="2" t="inlineStr"/>
+      <c r="G489" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ストライクノワール
+・UR性能確認
+・支援型ユニット
+・マップ兵器</t>
+        </is>
+      </c>
+      <c r="H489" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I489" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ahfa9nWXK3E</t>
+        </is>
+      </c>
+      <c r="J489" s="2" t="inlineStr">
+        <is>
+          <t>ahfa9nWXK3E</t>
+        </is>
+      </c>
+      <c r="K489" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SR フォースインパルスガンダム 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSRフォースインパルスガンダム紹介
+武装攻撃のアニメーションを収めたショート動画
+シン・アスカのボイスとともに武装演出を確認できる</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr"/>
+      <c r="F490" s="2" t="inlineStr"/>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・フォースインパルス
+・武装アニメ
+・ショート動画</t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I490" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ehPjcDdCLBc</t>
+        </is>
+      </c>
+      <c r="J490" s="2" t="inlineStr">
+        <is>
+          <t>ehPjcDdCLBc</t>
+        </is>
+      </c>
+      <c r="K490" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】まぁた有償ガチャで回すぞ！『7.5周年記念 Romancing祭 クロエ編＆ダリオ編』【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年Romancing祭クロエ編＆ダリオ編ガチャ実況
+序盤は爆死続きだが後半でクロエやダリオを確保
+ソティやミスティック小林も引けてジュエルは一部温存</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr">
+        <is>
+          <t>・クロエとミスティック小林を被りなく確保できた
+・ダリオやソティも引けて一安心
+・ステップ7分の有償ジュエルを温存できた</t>
+        </is>
+      </c>
+      <c r="F491" s="2" t="inlineStr">
+        <is>
+          <t>・序盤20連は演出すらなく出が悪い
+・引きが悪くテンションが下がる展開が続いた
+・ダリオ編はビンセント以外全員杖という偏りに疑問
+・被りが多く銃スタイルの更新が進まない不満</t>
+        </is>
+      </c>
+      <c r="G491" s="2" t="inlineStr">
+        <is>
+          <t>・ロマサガRS
+・7.5周年
+・Romancing祭
+・ガチャ実況
+・クロエ編
+・ダリオ編</t>
+        </is>
+      </c>
+      <c r="H491" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I491" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lZ2go4Fd86o</t>
+        </is>
+      </c>
+      <c r="J491" s="2" t="inlineStr">
+        <is>
+          <t>lZ2go4Fd86o</t>
+        </is>
+      </c>
+      <c r="K491" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】クリティカル特化！URインフィニットジャスティスの性能確認 #SDガンダムGジェネレーションエターナル ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>6月12日実装のURインフィニットジャスティスを確認
+クリティカル率上昇でダメージを伸ばす攻撃型ユニット
+アスランのEXアビリティで移動力や余ダメも強化</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>・クリティカルダメージアップを比較的発動させやすい
+・クリティカル特化でダメージを伸ばしやすい
+・オーブタグ搭乗でMP+6・余ダメージ15%上昇が優秀</t>
+        </is>
+      </c>
+      <c r="F492" s="2" t="inlineStr">
+        <is>
+          <t>・アビリティ発動にテンション超一撃が必要で準備がいる
+・マップ兵器はファトムで広範囲の殲滅は期待薄
+・恒常ユニットなのでチャンスステップ増加は持たない</t>
+        </is>
+      </c>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・インフィニットジャスティス
+・UR性能確認
+・クリティカル特化
+・アスラン</t>
+        </is>
+      </c>
+      <c r="H492" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I492" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=p11nK-a3_3w</t>
+        </is>
+      </c>
+      <c r="J492" s="2" t="inlineStr">
+        <is>
+          <t>p11nK-a3_3w</t>
+        </is>
+      </c>
+      <c r="K492" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新たな性能連発！こっちは全員鉄壁だ★ダリオ編解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D493" s="2" t="inlineStr">
+        <is>
+          <t>ダリオ編ガチャの新スタイル性能を初見解説
+ダリオ・ソティ・ボルカノ全員が75%超の防御軽減持ち
+鉄壁かつ火力も高く全体的に強いガチャと評価</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="inlineStr">
+        <is>
+          <t>・全員75%以上の防御軽減持ちで鉄壁
+・ダリオは覚醒後に軽減率91%超で火力も高い
+・ソティはマルチウェポンシステムで幅広く優秀
+・ボルカノは熱術特化で軽減90%超・バフ配布も強力
+・制約がある分強い設計は好評価</t>
+        </is>
+      </c>
+      <c r="F493" s="2" t="inlineStr">
+        <is>
+          <t>・ダリオのビビリ解除は被弾10回が必要で時間がかかる
+・ボルカノは熱属性攻撃限定の縛りがきつい
+・投稿者自身はクロエ編優先でこちらは引かない予定</t>
+        </is>
+      </c>
+      <c r="G493" s="2" t="inlineStr">
+        <is>
+          <t>・ロマサガRS
+・ダリオ編
+・性能考察
+・防御軽減
+・ボルカノ
+・ソティ</t>
+        </is>
+      </c>
+      <c r="H493" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I493" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZMTfaCMqOwM</t>
+        </is>
+      </c>
+      <c r="J493" s="2" t="inlineStr">
+        <is>
+          <t>ZMTfaCMqOwM</t>
+        </is>
+      </c>
+      <c r="K493" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新主人公たちの性能は化け物か！？クロエ編性能確認【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>クロエ編ガチャの新スタイル性能を初見確認
+クロエは全体火力、ビンセントは超短期決戦向け
+エスパーギャルは1.75倍バフ配布でレイド適性高い</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>・クロエは全体攻撃の火力が高くOD支援の継承技も優秀
+・ビンセントは超短期決戦で2.5倍級の高火力
+・エスパーギャルの全体1.75倍バフ3ターン配布が偉い
+・3人ともぼちぼち強いアタッカー性能</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
+        <is>
+          <t>・クロエの単体火力は控えめ
+・ビンセントは50ヒット以下制限など発動条件が厳しい
+・エスパーギャルのバフは今回の環境では刺さりにくいかも</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>・ロマサガRS
+・クロエ編
+・性能考察
+・新ガチャ
+・エスパーギャル
+・ビンセント</t>
+        </is>
+      </c>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I494" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nRUu2BqqoTk</t>
+        </is>
+      </c>
+      <c r="J494" s="2" t="inlineStr">
+        <is>
+          <t>nRUu2BqqoTk</t>
+        </is>
+      </c>
+      <c r="K494" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B495" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】誰でも簡単に使える方法共有！使いこなせば最強級ヴィンセントを徹底解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D495" s="2" t="inlineStr">
+        <is>
+          <t>新SSヴィンセントの強みと使い方をパワポ解説と実戦動画で徹底考察
+呪印付与で敵防御弱化と味方ステバフ、EXフォース最大2.5倍で火力大
+ヒット数超過のデバフと速すぎる行動順をODなどで調整するのがコツ</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr">
+        <is>
+          <t>・EXフォース最大2.5倍級の火力で使いこなせば最強級と評価
+・呪印中は殴るだけで敵防御弱化と味方ステバフが入り強力
+・防御系バフは最大90%超まで盛れてめちゃくちゃ強い
+・ODは行動順に割り込まれないため最後に動かす調整が可能</t>
+        </is>
+      </c>
+      <c r="F495" s="2" t="inlineStr">
+        <is>
+          <t>・ヒット数上限を使い切ると味方全体に90%の大デバフが入る点に注意
+・先行体制持ちで足が速すぎ、行動順の制御が安定しない
+・レヴナントコールはバトル中1回しか使えず使い所を選ぶ</t>
+        </is>
+      </c>
+      <c r="G495" s="2" t="inlineStr">
+        <is>
+          <t>・ヴィンセント解説
+・レヴナントコール
+・呪印とヒット数管理
+・行動順調整
+・EXフォース</t>
+        </is>
+      </c>
+      <c r="H495" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I495" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xEsyVQVBA5k</t>
+        </is>
+      </c>
+      <c r="J495" s="2" t="inlineStr">
+        <is>
+          <t>xEsyVQVBA5k</t>
+        </is>
+      </c>
+      <c r="K495" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:30:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年記念 神楽 第3弾ガチャやります😻</t>
+        </is>
+      </c>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年第3弾のクロエ編・ダリオ編ガチャをライブ配信で性能確認しつつ実施
+新スタイル性能を雑談込みでチェックし、ガチャではクロエなどを確保
+イベント消化やミルザ高速討伐談義、次回ガチャへのジュエル温存も話題に</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>・ソティはウェポンシフト系サポートが優秀で普通に強いと評価
+・今回のガチャではダリオが一番強いと評価
+・ガチャでクロエを確保、メダル交換でビクトールも入手
+・第4弾は黒薔薇姫などが来そうで激アツと予想</t>
+        </is>
+      </c>
+      <c r="F496" s="2" t="inlineStr">
+        <is>
+          <t>・今回のガチャは全体的に微妙でスルーも視野との評価
+・欲しいキャラがなかなか当たらないと嘆き
+・ダリオの技性能はアタッカーとしては物足りないとツッコミ
+・次回ガチャが5日後と早くジュエル温存が必要と注意喚起</t>
+        </is>
+      </c>
+      <c r="G496" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年第3弾ガチャ
+・新スタイル性能談義
+・ライブ配信
+・ミルザ討伐
+・ジュエル温存</t>
+        </is>
+      </c>
+      <c r="H496" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I496" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TfeqQ2HD-P8</t>
+        </is>
+      </c>
+      <c r="J496" s="2" t="inlineStr">
+        <is>
+          <t>TfeqQ2HD-P8</t>
+        </is>
+      </c>
+      <c r="K496" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:30:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C497" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】大注目の新メインキャラ2人！クロエ編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D497" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年第3弾クロエ編のクロエ・ヴィンセント・エスパーギャルを性能チェック
+ギャルは短期決戦型の熱術アタッカー、ヴィンセントは呪印ギミックが特徴
+クロエは専用連携技が強力で陰属性編成向き、3人とも粒揃いと総評</t>
+        </is>
+      </c>
+      <c r="E497" s="2" t="inlineStr">
+        <is>
+          <t>・エスパーギャルは短期決戦向きの高火力でBPサポートも優秀
+・ヴィンセントはヒット数を抑えた編成なら強力で火ダメ軽減も貼れる
+・クロエは専用連携技が超強力でOD加速など陰属性編成と好相性
+・陰属性が強い今の環境的にクロエ編3人は粒揃いと評価</t>
+        </is>
+      </c>
+      <c r="F497" s="2" t="inlineStr">
+        <is>
+          <t>・ヴィンセントは呪印を使い切ると味方に90%大デバフのデメリット
+・エスパーギャルは無理して引くほどの性能ではない
+・クロエはぶっ壊れという感じはしない
+・第1弾ガチャほどのインパクトはないと総評</t>
+        </is>
+      </c>
+      <c r="G497" s="2" t="inlineStr">
+        <is>
+          <t>・クロエ編ガチャ
+・性能チェック
+・ヴィンセント呪印
+・エスパーギャル
+・陰属性編成</t>
+        </is>
+      </c>
+      <c r="H497" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I497" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HwehweGLCJE</t>
+        </is>
+      </c>
+      <c r="J497" s="2" t="inlineStr">
+        <is>
+          <t>HwehweGLCJE</t>
+        </is>
+      </c>
+      <c r="K497" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:30:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】神回！どうしても欲しいキャラをガチャで追ったらトンデモナイ目に合いました！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年第3弾のクロエ編ガチャをクロエとヴィンセント狙いで回す動画
+エスパーギャルばかりが連発し、まさかの天井突破で約170連まで沼る
+最後にクロエとヴィンセントが2連続で登場し、なんとかコンプ達成</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>・最後にクロエとヴィンセントが並んで出てコンプ達成
+・ヴィンセントは性能面で一番欲しい注目キャラと評価
+・クロエはキャラ人気・イラスト・陰属性強化の面で確保したい存在</t>
+        </is>
+      </c>
+      <c r="F498" s="2" t="inlineStr">
+        <is>
+          <t>・天井を突破し約170連と課金がかさむ大波乱の展開
+・エスパーギャルばかり連発しメンタルをやられると悲鳴
+・ロケの都合で初日に引けず、引きの悪さを嘆く</t>
+        </is>
+      </c>
+      <c r="G498" s="2" t="inlineStr">
+        <is>
+          <t>・クロエ編ガチャ
+・天井突破
+・ヴィンセント狙い
+・エスパーギャル連発
+・ガチャ実況</t>
+        </is>
+      </c>
+      <c r="H498" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ReAnVjZa9t4</t>
+        </is>
+      </c>
+      <c r="J498" s="2" t="inlineStr">
+        <is>
+          <t>ReAnVjZa9t4</t>
+        </is>
+      </c>
+      <c r="K498" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:30:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B499" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはり本気出したら強かった？ダリオ編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D499" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年第3弾ダリオ編のダリオ・ソティ・ボルカノを性能チェック
+ボルカノは熱×術限定の超ピンポイント性能、ソティは杖中心のサポート特化
+ダリオは大器晩成型ながらスペックは相当高く当たりと評価</t>
+        </is>
+      </c>
+      <c r="E499" s="2" t="inlineStr">
+        <is>
+          <t>・ダリオは持っているスペックが相当高く当たりと評価
+・ダリオの火ダメ軽減は常時94%程で全キャラ中トップクラス
+・ソティは継承込みで悪くなく杖・体剣編成のサポートに優秀
+・ボルカノも刺さる場面で編成が組めれば強い</t>
+        </is>
+      </c>
+      <c r="F499" s="2" t="inlineStr">
+        <is>
+          <t>・ボルカノは熱×術限定でピンポイントすぎ、無理して取る性能ではない
+・ダリオはスタートダッシュが遅く今は目立った活躍がしにくい
+・既存メインキャラはあまり優遇されていない印象と指摘</t>
+        </is>
+      </c>
+      <c r="G499" s="2" t="inlineStr">
+        <is>
+          <t>・ダリオ編ガチャ
+・性能チェック
+・ダリオ評価
+・ソティ
+・ボルカノ</t>
+        </is>
+      </c>
+      <c r="H499" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I499" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=i7-nRptLg-I</t>
+        </is>
+      </c>
+      <c r="J499" s="2" t="inlineStr">
+        <is>
+          <t>i7-nRptLg-I</t>
+        </is>
+      </c>
+      <c r="K499" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:30:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】全武器種一気見せ！幻闘場デス剣〜杖の戦録クリアパーティー紹介</t>
+        </is>
+      </c>
+      <c r="D500" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場デスの剣〜杖まで全武器種の戦録クリアパーティーをライブで一気に紹介
+剣は大苦戦するも聖王アビスの加入などで以降の攻略は安定
+敵のLP攻撃やポーションを割るヒット数条件などギミック対策も解説</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビス加入で攻略が大きく安定、天井してでも取って良かった
+・セレチケで取ったストーミーが間接攻撃に強く大活躍
+・ジェラール&amp;アビスなどの編成で意外と火力が出ると好評価</t>
+        </is>
+      </c>
+      <c r="F500" s="2" t="inlineStr">
+        <is>
+          <t>・剣の戦録はギリギリの大苦戦でかなり手こずった
+・敵のLP攻撃や弱体破り持ちが厄介で事故要素あり</t>
+        </is>
+      </c>
+      <c r="G500" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場デス
+・全武器種クリア編成
+・聖王アビス
+・ヒット数ギミック
+・視聴者質問</t>
+        </is>
+      </c>
+      <c r="H500" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I500" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Nc31RzTKYJQ</t>
+        </is>
+      </c>
+      <c r="J500" s="2" t="inlineStr">
+        <is>
+          <t>Nc31RzTKYJQ</t>
+        </is>
+      </c>
+      <c r="K500" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:30:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B501" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C501" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年Romancing祭ダリオ編ガチャ評価 #ロマサガRS #shorts #ガチャ</t>
+        </is>
+      </c>
+      <c r="D501" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年Romancing祭ダリオ編ガチャの評価を扱うショート動画
+字幕は音楽表記のみで発言内容は取得できず詳細は不明
+評価の中身は動画本編を直接確認する必要あり</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr"/>
+      <c r="F501" s="2" t="inlineStr"/>
+      <c r="G501" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年Romancing祭
+・ダリオ編ガチャ
+・ガチャ評価
+・ショート動画</t>
+        </is>
+      </c>
+      <c r="H501" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I501" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=X7f0ihG5xgA</t>
+        </is>
+      </c>
+      <c r="J501" s="2" t="inlineStr">
+        <is>
+          <t>X7f0ihG5xgA</t>
+        </is>
+      </c>
+      <c r="K501" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:30:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年Romancing祭クロエ編ガチャ評価 #ロマサガRS #shorts #ガチャ</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年Romancing祭クロエ編ガチャの評価ショート動画
+字幕がBGMのみで音声解説の内容は取得できず
+タイトルからクロエ編スタイルのガチャ評価と推測</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr"/>
+      <c r="F502" s="2" t="inlineStr"/>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年祭
+・クロエ編ガチャ
+・ガチャ評価
+・ショート動画</t>
+        </is>
+      </c>
+      <c r="H502" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I502" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ejOdSWvv3VQ</t>
+        </is>
+      </c>
+      <c r="J502" s="2" t="inlineStr">
+        <is>
+          <t>ejOdSWvv3VQ</t>
+        </is>
+      </c>
+      <c r="K502" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B503" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C503" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】ヴィンセント・クインブラ能力値早見表〜最大数値が味方全体で ~軽減96%~攻撃強化23250%~フォース2.5倍~バフ1575%って ~😱</t>
+        </is>
+      </c>
+      <c r="D503" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年第3弾ガチャのヴィンセント能力値早見表を紹介
+味方全体に軽減96%・攻撃強化2万%超など破格の数値
+ヒット数調整は必要だが今回のガチャの大当たりと評価</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>・軽減96%・攻撃強化23250%など壊れ級の数値
+・エクストラフォース最大2.5倍で短期決戦向きに使える
+・行動高速化で1ターン目からほぼ最速で動ける
+・今回のガチャの大当たりと評価</t>
+        </is>
+      </c>
+      <c r="F503" s="2" t="inlineStr">
+        <is>
+          <t>・ヒット数調整を誤ると味方全体に強烈なデバフ
+・ターンごとに攻撃回数の調整が必要で運用に手間</t>
+        </is>
+      </c>
+      <c r="G503" s="2" t="inlineStr">
+        <is>
+          <t>・ヴィンセント
+・能力値早見表
+・7.5周年ガチャ
+・火力サポーター
+・ヒット数調整</t>
+        </is>
+      </c>
+      <c r="H503" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I503" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pi9WKHeKXTs</t>
+        </is>
+      </c>
+      <c r="J503" s="2" t="inlineStr">
+        <is>
+          <t>pi9WKHeKXTs</t>
+        </is>
+      </c>
+      <c r="K503" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】ミルザレイド:全滅1分36秒 ~誰でも出来る‼︎分かり易く解説 ~「魂・防具・技・立ち回り」</t>
+        </is>
+      </c>
+      <c r="D504" s="2" t="inlineStr">
+        <is>
+          <t>ミルザレイド全滅周回を魂・防具・技・立ち回りで解説
+バフ系の魂は外し属性被ダメを下げる防具を装備
+手順通りなら誰でも1分30秒台の高速周回が可能と紹介</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>・誰でも真似すれば1分30秒台が出せると太鼓判
+・火力が出る人は術を使えばさらにタイム短縮可能</t>
+        </is>
+      </c>
+      <c r="F504" s="2" t="inlineStr">
+        <is>
+          <t>・ヴィクトールはBPが足りないため輝石で補う必要あり</t>
+        </is>
+      </c>
+      <c r="G504" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザレイド
+・全滅周回
+・魂・防具構成
+・立ち回り解説</t>
+        </is>
+      </c>
+      <c r="H504" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I504" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wDdpq9Mgopk</t>
+        </is>
+      </c>
+      <c r="J504" s="2" t="inlineStr">
+        <is>
+          <t>wDdpq9Mgopk</t>
+        </is>
+      </c>
+      <c r="K504" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B505" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C505" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【大感謝】みんなが使ってるキャラは！？推しポイントランキング⑫【No.612】</t>
+        </is>
+      </c>
+      <c r="D505" s="2" t="inlineStr">
+        <is>
+          <t>視聴者129名参加の推しキャラランキング第12回を発表
+10位が同点4キャラの波乱、新顔や久々のキャラも続々
+1位は前回に続き連覇、汎用アセルスは5年半トップ10維持</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="inlineStr">
+        <is>
+          <t>・129名参加で前回より大幅に盛り上がった企画
+・汎用アセルスは5年半連続トップ10入りの愛されキャラ
+・ロックブーケやグスタフなど納得の常連が安定ランクイン
+・3位は前回76位から急上昇の大躍進
+・1位は女王以来2キャラ目の連覇を達成</t>
+        </is>
+      </c>
+      <c r="F505" s="2" t="inlineStr">
+        <is>
+          <t>・実装から日が浅いキャラは上位に入りにくい傾向</t>
+        </is>
+      </c>
+      <c r="G505" s="2" t="inlineStr">
+        <is>
+          <t>・推しキャラランキング
+・視聴者アンケート
+・トップ10発表
+・汎用アセルス
+・連覇達成</t>
+        </is>
+      </c>
+      <c r="H505" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I505" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5FzPPZkSuhQ</t>
+        </is>
+      </c>
+      <c r="J505" s="2" t="inlineStr">
+        <is>
+          <t>5FzPPZkSuhQ</t>
+        </is>
+      </c>
+      <c r="K505" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「クロエ 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年Romancing祭クロエ編の新スタイル3体を考察
+クロエB評価・ヴィンセントA評価・エスパーギャルB評価
+狙い目はヴィンセント、ガチャ出揃い後の判断も推奨</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>・ヴィンセントは条件達成で味方火力爆増のA評価で狙い目
+・クロエは全体4回16ヒットの貴重な範囲アタッカー
+・エスパーギャルの消費BP-99とODゲージ満タンは強力
+・ガチャ期間が長くじっくり検討する時間がある</t>
+        </is>
+      </c>
+      <c r="F506" s="2" t="inlineStr">
+        <is>
+          <t>・クロエは実装直後の使い道が乏しく評価はB止まり
+・ヴィンセントはヒット数超過で全能力90%低下の重い代償
+・エスパーギャルは使用1回限りで短期決戦専用のB評価
+・6スタイル中5スタイルが杖武器でバランスに不満</t>
+        </is>
+      </c>
+      <c r="G506" s="2" t="inlineStr">
+        <is>
+          <t>・クロエ編ガチャ
+・クロエ
+・ヴィンセント
+・エスパーギャル
+・スタイル評価</t>
+        </is>
+      </c>
+      <c r="H506" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I506" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fYkxXKYh9Hg</t>
+        </is>
+      </c>
+      <c r="J506" s="2" t="inlineStr">
+        <is>
+          <t>fYkxXKYh9Hg</t>
+        </is>
+      </c>
+      <c r="K506" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C507" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】制圧戦 [厄]レイド　制圧後のオススメ周回編成を[自由枠2]編成を6種紹介!!ヴィクトール無しも紹介!!【ロマンシングサガ　リユニバース】</t>
+        </is>
+      </c>
+      <c r="D507" s="2" t="inlineStr">
+        <is>
+          <t>制圧戦[厄]レイドの全制圧後オススメ周回編成を6種紹介
+自由枠2の自動再戦向けで全滅なしの安定重視構成
+記憶再戦用の2ターン全滅編成(1分32秒)も併せて解説</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="inlineStr">
+        <is>
+          <t>・自由枠2で手持ちに合わせやすい編成を6種も紹介
+・全滅なし構成で事故が少なく安定して自動周回できる
+・記憶再戦編成なら1分32秒の高速周回が可能
+・AJ等がいない場合のバフ役代用案にも言及</t>
+        </is>
+      </c>
+      <c r="F507" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザ2ターン全滅は事故が多く戦闘が長引く恐れ
+・記憶再戦用編成はかなり安定しないため記憶再戦推奨</t>
+        </is>
+      </c>
+      <c r="G507" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦レイド
+・周回編成
+・自由枠2
+・記憶再戦
+・ヴィンセント活用</t>
+        </is>
+      </c>
+      <c r="H507" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I507" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4R58z3Q6NNM</t>
+        </is>
+      </c>
+      <c r="J507" s="2" t="inlineStr">
+        <is>
+          <t>4R58z3Q6NNM</t>
+        </is>
+      </c>
+      <c r="K507" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:38Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K507"/>
+  <dimension ref="A1:K512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -33917,6 +33917,340 @@
         </is>
       </c>
     </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】次のレイドボス出現！さぁミルザいくぞ！　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>制圧戦の全制圧達成を視聴者と見届ける生配信
+7.5周年第3弾ガチャ（クロエ編・ダリオ編）を考察
+エスパーギャル連発に苦しむもクロエ・ダリオ等確保</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>・ビンセントは100回カウント維持で味方火力が伸び期待大
+・クロエは全体9回16ヒットで全体火力トップクラス
+・ダリオの防御バフ・軽減率が異常に高い
+・狙いのクロエM小林・ダリオ・ビンセントを確保できた
+・歴代一番の衝撃キャラは初期リアム（リボルブ）と回想</t>
+        </is>
+      </c>
+      <c r="F508" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャが渋くエスパーギャル4連発で天井寸前
+・エスパーギャルは使い道が分からない
+・ボルカノは熱術ウィークが術パ必須でピンポイントすぎる
+・最近のアビリティは複雑すぎて頭が痛くなると不満
+・ビクトール未所持で周回が遅く引かなかったのを後悔</t>
+        </is>
+      </c>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦全制圧
+・7.5周年第3弾ガチャ
+・クロエ
+・ダリオ
+・ビンセント
+・ミルザ不具合</t>
+        </is>
+      </c>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I508" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GOB3oT1DInc</t>
+        </is>
+      </c>
+      <c r="J508" s="2" t="inlineStr">
+        <is>
+          <t>GOB3oT1DInc</t>
+        </is>
+      </c>
+      <c r="K508" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13T01:06:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B509" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C509" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】次のレイドボス出現！さぁミルザいくぞ！　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D509" s="2" t="inlineStr">
+        <is>
+          <t>ミルザレイド後の制圧戦周回編成を模索する生配信
+ビクトール無しの編成に苦戦も視聴者案で解決
+育成枠2体で2分半周回が完成し大満足</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="inlineStr">
+        <is>
+          <t>・視聴者・吹雪さん考案の編成が天才的と絶賛
+・雪だるま無し・育成枠2体で600億周回が可能に
+・ツヴァイク三槍士が想定以上に強いと評価
+・気絶周回が楽しいと満足</t>
+        </is>
+      </c>
+      <c r="F509" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトール未所持で周回火力が微妙に足りず苦戦
+・ミルザレイドが不具合で一気に終了し驚いた
+・加藤がカウンターで周回の邪魔になると不満
+・連続ガチャ日程で課金がきついと嘆き</t>
+        </is>
+      </c>
+      <c r="G509" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦周回
+・ミルザレイド
+・周回編成
+・ビクトール
+・視聴者編成</t>
+        </is>
+      </c>
+      <c r="H509" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I509" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bpAvMYOnjWQ</t>
+        </is>
+      </c>
+      <c r="J509" s="2" t="inlineStr">
+        <is>
+          <t>bpAvMYOnjWQ</t>
+        </is>
+      </c>
+      <c r="K509" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13T01:06:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】URフルアーマーZZガンダム 武装アニメ  ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D510" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのURフルアーマーZZ紹介
+武装アニメーションをショート動画で披露
+ハイメガキャノン等の戦闘演出を収録</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="inlineStr"/>
+      <c r="F510" s="2" t="inlineStr"/>
+      <c r="G510" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・フルアーマーZZ
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H510" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I510" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MBvWKdPLjXw</t>
+        </is>
+      </c>
+      <c r="J510" s="2" t="inlineStr">
+        <is>
+          <t>MBvWKdPLjXw</t>
+        </is>
+      </c>
+      <c r="K510" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13T01:06:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B511" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C511" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年記念第３弾ガチャを考察する配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D511" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年第3弾ガチャ（クロエ編・ダリオ編）を徹底考察
+ビンセントを最高評価で激押しし1点狙いで確保成功
+エスパーギャル・ボルカノは評価を下げ気味に判定</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="inlineStr">
+        <is>
+          <t>・ビンセントは攻撃倍率がえぐく軽減も持てると激押し
+・ダリオは火ダメ軽減90%近くで長期戦の全てが詰まっている
+・クロエの全体火力はトップクラスと評価
+・ソフィーティアは幻闘場で一生使える便利枠
+・30〜40連でビンセント1点狙い成功</t>
+        </is>
+      </c>
+      <c r="F511" s="2" t="inlineStr">
+        <is>
+          <t>・エスパーギャルは3ターン短期決戦すぎて将来性が低い
+・ボルカノは熱術アタッカー必須でマニア向けすぎる
+・クロエは全体攻撃が刺さるコンテンツがなく今回最弱説
+・ソフィーティアの効果量は現代に追いついていない
+・ソフィーティア優遇など運営の推しに疑問</t>
+        </is>
+      </c>
+      <c r="G511" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年第3弾ガチャ
+・ビンセント
+・ダリオ
+・クロエ
+・エスパーギャル
+・ガチャ考察</t>
+        </is>
+      </c>
+      <c r="H511" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I511" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Jwnfi8c7sK4</t>
+        </is>
+      </c>
+      <c r="J511" s="2" t="inlineStr">
+        <is>
+          <t>Jwnfi8c7sK4</t>
+        </is>
+      </c>
+      <c r="K511" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13T01:06:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】制圧戦 レイド ミルザ[厄]　2分未満の編成をとりあえず4種紹介!!最後に代用解説もあります【ロマンシングサガ　リユニバース】</t>
+        </is>
+      </c>
+      <c r="D512" s="2" t="inlineStr">
+        <is>
+          <t>制圧戦レイド・ミルザ[厄]の2分未満周回編成4種を紹介
+2ターン全滅周回中心に継承・技設定を細かく解説
+最後に代用キャラとOD設定のコツも説明</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザはダメカ・カウンター無しの優しい仕様と評価
+・最速1分26秒の2ターン全滅周回編成を実現
+・全滅なし1分57秒の安定編成も用意
+・11日の新ガチャでレイド追い込みキャラに期待</t>
+        </is>
+      </c>
+      <c r="F512" s="2" t="inlineStr">
+        <is>
+          <t>・直接攻撃が多くカウンター持ち編成だと戦闘が長引く
+・ビクトール不在だと他キャラでは戦闘時間が大幅に伸びる</t>
+        </is>
+      </c>
+      <c r="G512" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦レイド
+・ミルザ[厄]
+・周回編成
+・継承設定
+・代用解説</t>
+        </is>
+      </c>
+      <c r="H512" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I512" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XhGUmW5OEoY</t>
+        </is>
+      </c>
+      <c r="J512" s="2" t="inlineStr">
+        <is>
+          <t>XhGUmW5OEoY</t>
+        </is>
+      </c>
+      <c r="K512" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13T01:06:40Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K512"/>
+  <dimension ref="A1:K523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -34251,6 +34251,721 @@
         </is>
       </c>
     </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B513" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C513" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】忘れてません??「元祖陰属性」この男たち!!からの謎ガチャ来たるの7.5周年後半戦スタート　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D513" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年前半戦が終わり後半戦スタート
+第4弾シングルガチャの登場キャラを予測
+サガフロ・アンサガ系の男性キャラが有力か</t>
+        </is>
+      </c>
+      <c r="E513" s="2" t="inlineStr">
+        <is>
+          <t>・元祖陰属性キャラの実装に期待
+・ミルザ・せ王は人気キャラと評価</t>
+        </is>
+      </c>
+      <c r="F513" s="2" t="inlineStr">
+        <is>
+          <t>・立ち絵なしキャラはガチャ化望み薄と分析
+・サガフロ2系は実装が薄め</t>
+        </is>
+      </c>
+      <c r="G513" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年後半戦
+・第4弾シングルガチャ予測
+・8河仙
+・サガフロ・アンサガ枠
+・実装周期考察</t>
+        </is>
+      </c>
+      <c r="H513" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I513" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=H24SYsiew6k</t>
+        </is>
+      </c>
+      <c r="J513" s="2" t="inlineStr">
+        <is>
+          <t>H24SYsiew6k</t>
+        </is>
+      </c>
+      <c r="K513" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14T01:05:39.861955+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみ無し勢の「オアシス」爆裂ダメージ出しやすいミルザでカモれ!!レイド600億満額速報!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>暦み無し勢向けミルザレイド満額600億編成
+白腹やロボより速く回れて安定
+裁判とイシスでフォローでき自動も安定</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>・暦み無しでも満額600億を早く周回
+・ビクトール上ぶれ無くリスクが低く安定
+・ミルザが爆裂ダメージを出しやすい</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr"/>
+      <c r="G514" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザレイド
+・満額600億
+・暦み無し編成
+・自動再戦
+・装備紹介</t>
+        </is>
+      </c>
+      <c r="H514" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I514" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nubUtKVnWbU</t>
+        </is>
+      </c>
+      <c r="J514" s="2" t="inlineStr">
+        <is>
+          <t>nubUtKVnWbU</t>
+        </is>
+      </c>
+      <c r="K514" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14T01:05:39.861955+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B515" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C515" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　こよみ級の逸材は第2弾ガチャ主人公３体の中にいるのか？戦いを通じてインパクト王決定戦！</t>
+        </is>
+      </c>
+      <c r="D515" s="2" t="inlineStr">
+        <is>
+          <t>新主人公3体のインパクトを実戦で比較
+幻闘・セフェルマルカ戦で性能を検証
+インパクト王1位はビンセントと評価</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="inlineStr">
+        <is>
+          <t>・ビンセントは火力の伸びが大きく1位
+・ダリオは覚醒後の火力が高い
+・クロエは火力一撃が高く瞬発力あり</t>
+        </is>
+      </c>
+      <c r="F515" s="2" t="inlineStr">
+        <is>
+          <t>・ビンセントはHPゲージ系が苦手で防御に難
+・ダリオは覚醒まで遅く味方の防御補助が必要
+・クロエは追撃回数少なめで火力貢献しきれず</t>
+        </is>
+      </c>
+      <c r="G515" s="2" t="inlineStr">
+        <is>
+          <t>・ダリオ・ビンセント・クロエ
+・インパクト比較
+・幻闘
+・セフェルマルカ戦
+・暦み</t>
+        </is>
+      </c>
+      <c r="H515" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I515" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zfEeRJAexfo</t>
+        </is>
+      </c>
+      <c r="J515" s="2" t="inlineStr">
+        <is>
+          <t>zfEeRJAexfo</t>
+        </is>
+      </c>
+      <c r="K515" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14T01:05:39.861955+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SR ヴェルデバスターガンダム 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナルの武装アニメShorts
+SRヴェルデバスターガンダムを紹介
+短い戦闘演出のショート動画</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr"/>
+      <c r="F516" s="2" t="inlineStr"/>
+      <c r="G516" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ヴェルデバスターガンダム
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H516" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I516" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qls95Iel-Ws</t>
+        </is>
+      </c>
+      <c r="J516" s="2" t="inlineStr">
+        <is>
+          <t>qls95Iel-Ws</t>
+        </is>
+      </c>
+      <c r="K516" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14T01:05:39.861955+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B517" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C517" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】群雄割拠！8大ガチャランキング！引くべき優先順位を考察【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D517" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年8大ガチャの引く優先順位を考察
+1位サイバ編、2位トルキア、3位暦み編
+ダリオ・ボルカノは将来性枠で様子見</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="inlineStr">
+        <is>
+          <t>・1位サイバ編は全コンテンツで活躍する万能
+・ビンセントは順位システムが強力な大当たり枠
+・暦みは現環境で活躍し取得推奨</t>
+        </is>
+      </c>
+      <c r="F517" s="2" t="inlineStr">
+        <is>
+          <t>・ダリオは10ヒットがネックで活躍する敵がいない
+・ボルカノは汎用性が無く熱術編成限定
+・ダリアスは火力が出ず防御も50%で物足りない</t>
+        </is>
+      </c>
+      <c r="G517" s="2" t="inlineStr">
+        <is>
+          <t>・8大ガチャランキング
+・サイバ編1位
+・ビンセント大当たり
+・暦み推奨
+・引く優先順位</t>
+        </is>
+      </c>
+      <c r="H517" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I517" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3vj9rl8C2tk</t>
+        </is>
+      </c>
+      <c r="J517" s="2" t="inlineStr">
+        <is>
+          <t>3vj9rl8C2tk</t>
+        </is>
+      </c>
+      <c r="K517" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14T01:05:39.861955+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今しかない！ミルザレイド満額1:42付近代用キャラ検証★環境最強キャラを育成すべし！！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>ミルザレイド満額の代用キャラを多数検証
+全滅周回でリアム軸が安定して強い
+雪だるま編成で最速1分42秒を達成</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>・リアムが強力で全滅周回が安定
+・雪だるま編成が最速1:42で最高記録
+・AJ・アーゼル等の代用でも満額可能</t>
+        </is>
+      </c>
+      <c r="F518" s="2" t="inlineStr">
+        <is>
+          <t>・AJや雪だるまは硬すぎて落ちず調整が難しい
+・暦みのOD不発で事故るパターンあり
+・ミルザレイドは編成が面倒で手こずる</t>
+        </is>
+      </c>
+      <c r="G518" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザレイド満額
+・代用キャラ検証
+・全滅周回
+・リアム軸
+・最速1:42</t>
+        </is>
+      </c>
+      <c r="H518" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I518" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QxpxDbSXLHw</t>
+        </is>
+      </c>
+      <c r="J518" s="2" t="inlineStr">
+        <is>
+          <t>QxpxDbSXLHw</t>
+        </is>
+      </c>
+      <c r="K518" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14T01:05:39.861955+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C519" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】まさかのSSS評価有！最強レベルの矛と盾がぶつかり合う★最新キャラランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D519" s="2" t="inlineStr">
+        <is>
+          <t>ダリオ・クロエ編の最新キャラを評価
+ビンセント・ダリオはSS評価の最強級
+ボルカノ等は刺さる時の爆発力に期待</t>
+        </is>
+      </c>
+      <c r="E519" s="2" t="inlineStr">
+        <is>
+          <t>・ビンセントとダリオはSS評価の最強級
+・ボルカノは選択と集中で刺さる時は凄まじい
+・クロエは全体/単体を選べOD配布も優秀</t>
+        </is>
+      </c>
+      <c r="F519" s="2" t="inlineStr">
+        <is>
+          <t>・ダリオは強いが活躍する敵がいない
+・ソティはインフレで評価が下がりロマパス前提
+・ボルカノ・クロエは防具系数が低くヒラが苦しい</t>
+        </is>
+      </c>
+      <c r="G519" s="2" t="inlineStr">
+        <is>
+          <t>・最新キャラランキング
+・ビンセントSS
+・ダリオSS
+・ボルカノS
+・クロエS</t>
+        </is>
+      </c>
+      <c r="H519" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I519" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bld8WzzUjJs</t>
+        </is>
+      </c>
+      <c r="J519" s="2" t="inlineStr">
+        <is>
+          <t>bld8WzzUjJs</t>
+        </is>
+      </c>
+      <c r="K519" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14T01:05:39.861955+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>【スマグロ】イベントやってます、後半眠りながらしゃべってます😻</t>
+        </is>
+      </c>
+      <c r="D520" s="2" t="inlineStr">
+        <is>
+          <t>スマグロのイベントを雑談しながらプレイ
+マルチや対戦に挑戦するも無課金は苦戦
+残り3日で鍵不足、龍討伐を急ぐ配信</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="inlineStr">
+        <is>
+          <t>・イベントのマルチを楽しく周回
+・レベルが上がれば勝てると前向き</t>
+        </is>
+      </c>
+      <c r="F520" s="2" t="inlineStr">
+        <is>
+          <t>・無課金だと対戦が厳しく勝てない
+・残り3日で鍵が足りず焦り
+・攻撃速度が遅く感じ不満</t>
+        </is>
+      </c>
+      <c r="G520" s="2" t="inlineStr">
+        <is>
+          <t>・スマグロ
+・イベント周回
+・マルチクエスト
+・無課金プレイ
+・龍討伐</t>
+        </is>
+      </c>
+      <c r="H520" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I520" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Nh1PQMfh72U</t>
+        </is>
+      </c>
+      <c r="J520" s="2" t="inlineStr">
+        <is>
+          <t>Nh1PQMfh72U</t>
+        </is>
+      </c>
+      <c r="K520" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14T01:05:39.861955+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B521" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C521" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】見届けてください。これが天井突破直後にダリオ編を回した結果です...【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D521" s="2" t="inlineStr">
+        <is>
+          <t>天井突破直後にダリオ編ガチャへ挑戦
+序盤は爆死もソティ等を確保
+後半は完凸級の大勝利で撤退</t>
+        </is>
+      </c>
+      <c r="E521" s="2" t="inlineStr">
+        <is>
+          <t>・後半ダリオ編は約90連で大勝利
+・ソティ・ダリオ・ボルカノを確保
+・2周目ステップで端末に救済された</t>
+        </is>
+      </c>
+      <c r="F521" s="2" t="inlineStr">
+        <is>
+          <t>・前半クロエ編で天井突破しジュエル大量消費
+・ステップアップですり抜け・被りが連発
+・ガチャが多すぎてジュエルがすぐ枯渇</t>
+        </is>
+      </c>
+      <c r="G521" s="2" t="inlineStr">
+        <is>
+          <t>・ダリオ編ガチャ
+・天井突破
+・ステップアップ
+・ソティ・ボルカノ
+・ガチャ実況</t>
+        </is>
+      </c>
+      <c r="H521" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I521" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WaqEHfHWs9s</t>
+        </is>
+      </c>
+      <c r="J521" s="2" t="inlineStr">
+        <is>
+          <t>WaqEHfHWs9s</t>
+        </is>
+      </c>
+      <c r="K521" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14T01:05:39.861955+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】気になる八歌仙の性能は？クロエ・ダリオガチャ性能チェック&amp;キャラランク評価【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D522" s="2" t="inlineStr">
+        <is>
+          <t>クロエ・ダリオガチャの性能をまとめて考察
+注目はヴンセント、配布より大幅強化
+他キャラは必須感薄く高難度待ちか</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>・ヴンセントは追撃4回・威力4Sで火力期待
+・ダリオは状態異常耐性バフ持ちで高難度に刺さる可能性
+・エスパーゲルは消費BP99減少が優秀</t>
+        </is>
+      </c>
+      <c r="F522" s="2" t="inlineStr">
+        <is>
+          <t>・ヴンセント以外は墓線がパッとしない
+・ダリオは10回避弾に時間かかり遅咲き
+・クロエはODゲージアップ無く味方支援必須</t>
+        </is>
+      </c>
+      <c r="G522" s="2" t="inlineStr">
+        <is>
+          <t>・クロエ・ダリオガチャ
+・ヴンセント評価
+・ダリオ覚醒
+・エスパーゲルBP支援
+・キャラランク</t>
+        </is>
+      </c>
+      <c r="H522" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I522" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8ggvgrK021o</t>
+        </is>
+      </c>
+      <c r="J522" s="2" t="inlineStr">
+        <is>
+          <t>8ggvgrK021o</t>
+        </is>
+      </c>
+      <c r="K522" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14T01:05:39.861955+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B523" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C523" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「ダリオ 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D523" s="2" t="inlineStr">
+        <is>
+          <t>ダリオ編ガチャ3体のスタイル性能を考察
+ダリオA-、ボルカノB+、ソティBと評価
+いずれも高難度向けで様子見も一案</t>
+        </is>
+      </c>
+      <c r="E523" s="2" t="inlineStr">
+        <is>
+          <t>・ダリオは覚醒後2.75倍31ヒットで強力
+・ボルカノは熱術パで余ダメ底上げ・軽減率高い
+・ソティは4武器種対応で常時OD満タンが優秀</t>
+        </is>
+      </c>
+      <c r="F523" s="2" t="inlineStr">
+        <is>
+          <t>・ダリオは10回避弾のハードルが高く遅咲き
+・ボルカノは熱術編成限定で運用条件が厳しい
+・ソティは本人火力控えめ・余ダメ支援は低め</t>
+        </is>
+      </c>
+      <c r="G523" s="2" t="inlineStr">
+        <is>
+          <t>・ダリオ編考察
+・ダリオA-
+・ボルカノB+
+・ソティB
+・ランク付け</t>
+        </is>
+      </c>
+      <c r="H523" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I523" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KWf8e3bICLU</t>
+        </is>
+      </c>
+      <c r="J523" s="2" t="inlineStr">
+        <is>
+          <t>KWf8e3bICLU</t>
+        </is>
+      </c>
+      <c r="K523" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14T01:05:39.861955+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K523"/>
+  <dimension ref="A1:K533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -34966,6 +34966,677 @@
         </is>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「ギミック無視」4ターン螺旋ジュエルビースト完全破壊!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D524" s="2" t="inlineStr">
+        <is>
+          <t>螺旋ジュエルビーストをギミック無視で4ターン撃破
+OD前提・偶数ターンは全員ODでカウンター回避
+カタリナのカウンターとサバ追撃で火力確保</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>・カタリナのカウンターがすごく強い
+・自動エクストラザが1.75倍と強い
+・サバの追撃で火力アップ</t>
+        </is>
+      </c>
+      <c r="F524" s="2" t="inlineStr">
+        <is>
+          <t>・暦読みがいても半ターンしか早くならない
+・6ターン超えだと裁判の方が強く短期向き
+・本気の発動条件が不明のまま</t>
+        </is>
+      </c>
+      <c r="G524" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋ジュエルビースト
+・4ターン撃破
+・ギミック無視
+・OD貫通
+・カタリナ
+・サバ</t>
+        </is>
+      </c>
+      <c r="H524" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I524" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6yXzRL4mVTQ</t>
+        </is>
+      </c>
+      <c r="J524" s="2" t="inlineStr">
+        <is>
+          <t>6yXzRL4mVTQ</t>
+        </is>
+      </c>
+      <c r="K524" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15T03:32:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B525" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C525" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】頂上決戦「VS第3弾」第1弾2弾と比較してわかったこと!!意外なランキングにご期待ください→18体6ガチャランキング!!最新スタイル比較検討会→2026年6月15日版　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D525" s="2" t="inlineStr">
+        <is>
+          <t>頂上決戦VS第3弾、18体6ガチャをランキング
+1位サバ・2位裁判が環境を底上げする最強格
+外れガチャは即撤退、引くべきは上位2ガチャ</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="inlineStr">
+        <is>
+          <t>・サバは全味方1.75倍底上げで環境最強の1位
+・裁判は全コンテンツ対応で確保推奨の2位
+・ビンセントは誰にでも効く1.75倍ばら撒き</t>
+        </is>
+      </c>
+      <c r="F525" s="2" t="inlineStr">
+        <is>
+          <t>・ストライフ以外の最下層は外れで即撤退推奨
+・ダリアスは火力がおまけすぎる
+・エスパーのBP99保持は焼けクソ性能
+・ボルカノ・アーニャはお仲間不足で伸び代なし
+・暦読みはスルー推奨</t>
+        </is>
+      </c>
+      <c r="G525" s="2" t="inlineStr">
+        <is>
+          <t>・18体6ガチャランキング
+・サバ1位
+・裁判2位
+・ビンセント
+・暦読みスルー
+・エクストラ拡張性</t>
+        </is>
+      </c>
+      <c r="H525" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I525" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=upZ4wGbJvlo</t>
+        </is>
+      </c>
+      <c r="J525" s="2" t="inlineStr">
+        <is>
+          <t>upZ4wGbJvlo</t>
+        </is>
+      </c>
+      <c r="K525" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15T03:32:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新主人公がまた３体登場！さぁお迎えに行くぞ！　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D526" s="2" t="inlineStr">
+        <is>
+          <t>新主人公お迎え回の周回・記憶再生ライブ配信
+アマゾネス確保、暦読み裁判の取得を推奨
+魂アビリティのひらめき難しさを雑談</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>・暦読み・裁判は取っておいた方がいい
+・アマゾネスは武器が強く必須級
+・制圧戦は定期開催してほしい</t>
+        </is>
+      </c>
+      <c r="F526" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャの頻度が早すぎて困る
+・魂アビリティが全然ひらめかない
+・明日のメンテが8時までと長い
+・属性縛り100%編成は難しい</t>
+        </is>
+      </c>
+      <c r="G526" s="2" t="inlineStr">
+        <is>
+          <t>・周回配信
+・記憶再生
+・アマゾネス
+・暦読み裁判推奨
+・魂アビリティ
+・制圧戦延長</t>
+        </is>
+      </c>
+      <c r="H526" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I526" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=djlxaG7e7o8</t>
+        </is>
+      </c>
+      <c r="J526" s="2" t="inlineStr">
+        <is>
+          <t>djlxaG7e7o8</t>
+        </is>
+      </c>
+      <c r="K526" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15T03:32:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B527" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C527" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR ストライクノワールガンダム 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D527" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSSRストライクノワール
+武装アニメ紹介のショート動画
+キャラのセリフ演出を収録</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="inlineStr"/>
+      <c r="F527" s="2" t="inlineStr"/>
+      <c r="G527" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ストライクノワール
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H527" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I527" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ktpQJAMsy5A</t>
+        </is>
+      </c>
+      <c r="J527" s="2" t="inlineStr">
+        <is>
+          <t>ktpQJAMsy5A</t>
+        </is>
+      </c>
+      <c r="K527" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15T03:32:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】もうこれでいい。ヴィンセントの超簡単使用方法【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D528" s="2" t="inlineStr">
+        <is>
+          <t>ヴィンセントの超簡単な使い方を実演解説
+自己バフ多いノエル・暦読みと組めば楽に運用
+相方タクトの先行検証も併せて紹介</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>・自己バフ持ち(ノエル等)と組めばビンセントは簡単
+・ノエルは会のトップで本当に強い
+・デメリットは今のインフレ環境では軽い問題
+・キャラランクはSS評価</t>
+        </is>
+      </c>
+      <c r="F528" s="2" t="inlineStr">
+        <is>
+          <t>・ビンセントはヒット数管理がめんどくさい
+・超過時に全能力90%低下デバフが痛い
+・収容時にステバフが消え途中出しの石攻撃が危険</t>
+        </is>
+      </c>
+      <c r="G528" s="2" t="inlineStr">
+        <is>
+          <t>・ビンセント運用
+・ノエル
+・自己バフ編成
+・ヒット数管理
+・螺旋・討伐
+・75周年箱</t>
+        </is>
+      </c>
+      <c r="H528" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I528" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ln3rjLiozDg</t>
+        </is>
+      </c>
+      <c r="J528" s="2" t="inlineStr">
+        <is>
+          <t>Ln3rjLiozDg</t>
+        </is>
+      </c>
+      <c r="K528" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15T03:32:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B529" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C529" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】イベント色々やってます</t>
+        </is>
+      </c>
+      <c r="D529" s="2" t="inlineStr">
+        <is>
+          <t>16日ガチャ前の消化イベント周回ライブ配信
+宝塚記念や競馬の雑談を交えつつ進行
+斧縛りパで火力不足に苦戦</t>
+        </is>
+      </c>
+      <c r="E529" s="2" t="inlineStr">
+        <is>
+          <t>・ボルカノの熱解放は100%エクホで強い
+・強キャラを取ればある程度簡単にクリアできる</t>
+        </is>
+      </c>
+      <c r="F529" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャが多すぎる
+・斧縛りパで火力が足りず苦戦
+・闇落ちターミンが斧でないのが惜しい</t>
+        </is>
+      </c>
+      <c r="G529" s="2" t="inlineStr">
+        <is>
+          <t>・イベント周回
+・ガチャ前消化
+・斧縛り編成
+・ボルカノ熱解放
+・宝塚記念雑談
+・16日ガチャ</t>
+        </is>
+      </c>
+      <c r="H529" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I529" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uG_wZsFJ02g</t>
+        </is>
+      </c>
+      <c r="J529" s="2" t="inlineStr">
+        <is>
+          <t>uG_wZsFJ02g</t>
+        </is>
+      </c>
+      <c r="K529" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15T03:32:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新たな最優先案件が登場！？新ガチャ確保優先度ランキング【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D530" s="2" t="inlineStr">
+        <is>
+          <t>6/14最新の新ガチャ確保優先度ランキング
+最優先はサバ・暦読みに加えビンセントが追加
+陰属性が突出してインフレ中と分析</t>
+        </is>
+      </c>
+      <c r="E530" s="2" t="inlineStr">
+        <is>
+          <t>・サバは環境を作る最優先で長く活躍
+・暦読みは属性不問の超強力サポート
+・ビンセントは陰属性を強化し最優先
+・リアムはODゲージ常時満タンで優秀
+・代々は味方強化で高難度の救世主</t>
+        </is>
+      </c>
+      <c r="F530" s="2" t="inlineStr">
+        <is>
+          <t>・ダリオは被弾10回条件が現環境で発動困難
+・ストライフは属性が悪く入る余地少
+・ボルカノは縛りが多く編成難度が高い
+・ダリアス・オレットは無理して取る要素なし
+・シーレは優先度低</t>
+        </is>
+      </c>
+      <c r="G530" s="2" t="inlineStr">
+        <is>
+          <t>・確保優先度ランキング
+・サバ最優先
+・暦読み
+・ビンセント追加
+・陰属性インフレ
+・ダリオ評価難</t>
+        </is>
+      </c>
+      <c r="H530" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I530" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Auxt9fpCxP0</t>
+        </is>
+      </c>
+      <c r="J530" s="2" t="inlineStr">
+        <is>
+          <t>Auxt9fpCxP0</t>
+        </is>
+      </c>
+      <c r="K530" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15T03:32:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B531" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C531" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年第4弾は大荒れの予感！遂にあの2人がやってくる！？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D531" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年第4弾ガチャの登場キャラ予想動画
+主役は白薔薇姫アビスとT260Gアビスと予想
+フックス・オイゲン等6スタイルを推測</t>
+        </is>
+      </c>
+      <c r="E531" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ期間が長めに取られている</t>
+        </is>
+      </c>
+      <c r="F531" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャの頻度が多すぎる</t>
+        </is>
+      </c>
+      <c r="G531" s="2" t="inlineStr">
+        <is>
+          <t>・第4弾ガチャ予想
+・白薔薇姫アビス
+・T260Gアビス
+・フックス
+・オイゲン
+・6/16実装予想</t>
+        </is>
+      </c>
+      <c r="H531" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I531" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jTpN9JISEqs</t>
+        </is>
+      </c>
+      <c r="J531" s="2" t="inlineStr">
+        <is>
+          <t>jTpN9JISEqs</t>
+        </is>
+      </c>
+      <c r="K531" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15T03:32:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第124回 ~鋼鉄兵たちの井戸 ~最適解パーティ徹底考察 ~👊ランク上位を目指そう👊 【TYAMU RADIO】</t>
+        </is>
+      </c>
+      <c r="D532" s="2" t="inlineStr">
+        <is>
+          <t>第124回鋼鉄兵たちの井戸の最適解パーティ考察
+全属性弱点・7体ステージの高難度井戸
+サライグラキエスがほぼ確定枠と予想</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>・サライグラキエスは全体16連打+1.75倍で確定枠級
+・全属性弱点でどの属性アタッカーも活躍可能
+・Sマシーンは全体47ヒットでダークホース</t>
+        </is>
+      </c>
+      <c r="F532" s="2" t="inlineStr">
+        <is>
+          <t>・鋼鉄兵の火力が高く弱体破りが厄介
+・2~3ターン決着だとデバフが守備面で効かない
+・7体ステージで予想が過去一難しい</t>
+        </is>
+      </c>
+      <c r="G532" s="2" t="inlineStr">
+        <is>
+          <t>・鋼鉄兵たちの井戸
+・高難度7体ステージ
+・全属性弱点
+・サライグラキエス
+・打熱属性
+・Sマシーン</t>
+        </is>
+      </c>
+      <c r="H532" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I532" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZtCi4InOIt0</t>
+        </is>
+      </c>
+      <c r="J532" s="2" t="inlineStr">
+        <is>
+          <t>ZtCi4InOIt0</t>
+        </is>
+      </c>
+      <c r="K532" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15T03:32:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B533" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C533" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】難解なヴィンセントの運用方法を解説！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D533" s="2" t="inlineStr">
+        <is>
+          <t>複雑なヴィンセントの運用方法を丁寧に解説
+ヒット数制限を行動順とODで回避する技術
+3人OD連携でビンセントを先に動かすのが鍵</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="inlineStr">
+        <is>
+          <t>・ビンセントはかなり強く激推しスタイル
+・エクストラフォース倍率2.5倍はAJ超え
+・火ダメ軽減80%まで重ねられて硬い
+・暦読み・裁判に続く当たりスタイル</t>
+        </is>
+      </c>
+      <c r="F533" s="2" t="inlineStr">
+        <is>
+          <t>・性能が複雑で正しく運用しないと弱い
+・ヒット数超過で全能力90%低下のペナルティ
+・技3レブナントコールは1回制限で扱いづらい
+・行動順調整が必要で1癖2癖ある</t>
+        </is>
+      </c>
+      <c r="G533" s="2" t="inlineStr">
+        <is>
+          <t>・ビンセント運用
+・ヒット数制限
+・行動順調整
+・OD連携
+・火ダメ軽減
+・螺旋560回</t>
+        </is>
+      </c>
+      <c r="H533" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I533" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fjGBhfNIrao</t>
+        </is>
+      </c>
+      <c r="J533" s="2" t="inlineStr">
+        <is>
+          <t>fjGBhfNIrao</t>
+        </is>
+      </c>
+      <c r="K533" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15T03:32:05Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K533"/>
+  <dimension ref="A1:K549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -35637,6 +35637,1021 @@
         </is>
       </c>
     </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】聖王厄「ギミック解明」出禁&amp;こよみ無しで完璧に倒せ!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D534" s="2" t="inlineStr">
+        <is>
+          <t>聖王厄のギミックを解明して攻略
+33ヒット以内で「今」発動を回避
+こよみ無し・出禁編成で完璧討伐</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr">
+        <is>
+          <t>・ギミック理解で攻撃を完封できる
+・ODで守ればパスト負けを回避可能</t>
+        </is>
+      </c>
+      <c r="F534" s="2" t="inlineStr">
+        <is>
+          <t>・敵LP攻撃が多いと4ターンで即リタイア
+・ヒット数超過で防御強化されダメージが通らない</t>
+        </is>
+      </c>
+      <c r="G534" s="2" t="inlineStr">
+        <is>
+          <t>・聖王厄
+・ギミック攻略
+・ヒット数調整
+・OD防御
+・こよみ無し編成</t>
+        </is>
+      </c>
+      <c r="H534" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I534" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QMFn-tWgzRo</t>
+        </is>
+      </c>
+      <c r="J534" s="2" t="inlineStr">
+        <is>
+          <t>QMFn-tWgzRo</t>
+        </is>
+      </c>
+      <c r="K534" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B535" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C535" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「最強の名の下に」御堂系統グスタフ!!&amp;無限∞追撃&amp;無限∞カウンター!!プルミエールの上振れ確率は!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D535" s="2" t="inlineStr">
+        <is>
+          <t>プルミエールは確率50%カウンターのロマン型
+グスタフは2度の火力底上げで無難に強い
+両者とも突き抜けない橋休め性能</t>
+        </is>
+      </c>
+      <c r="E535" s="2" t="inlineStr">
+        <is>
+          <t>・グスタフは味方全体火力の底上げが優秀
+・グスタフは追撃と防御天品が優秀</t>
+        </is>
+      </c>
+      <c r="F535" s="2" t="inlineStr">
+        <is>
+          <t>・プルミエールは確率50%発動が酷い
+・プルミエールは敵全体攻撃時以外仕事がない
+・グスタフは拡張性が無く使われなくなる</t>
+        </is>
+      </c>
+      <c r="G535" s="2" t="inlineStr">
+        <is>
+          <t>・プルミエール
+・グスタフ
+・無限カウンター
+・エクストラばら巻き
+・ガチャ評価</t>
+        </is>
+      </c>
+      <c r="H535" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I535" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=c55M_y00a0U</t>
+        </is>
+      </c>
+      <c r="J535" s="2" t="inlineStr">
+        <is>
+          <t>c55M_y00a0U</t>
+        </is>
+      </c>
+      <c r="K535" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「ランクイン可能」今週の井戸!!鋼鉄兵1ターンクッキング　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>今週の井戸はカウンター全体で1ターン殲滅
+ブーケ猛者でOFFセットし全力攻撃
+ターゲット調整でランクイン可能</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr">
+        <is>
+          <t>・カウンター全体スタイルで1ターン殲滅可能
+・デスマシーンも有効</t>
+        </is>
+      </c>
+      <c r="F536" s="2" t="inlineStr">
+        <is>
+          <t>・行動順次第で倒しきれず崩れる</t>
+        </is>
+      </c>
+      <c r="G536" s="2" t="inlineStr">
+        <is>
+          <t>・今週の井戸
+・鋼鉄兵
+・カウンター編成
+・1ターン殲滅
+・ランクイン</t>
+        </is>
+      </c>
+      <c r="H536" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I536" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uXCiWVqdVGw</t>
+        </is>
+      </c>
+      <c r="J536" s="2" t="inlineStr">
+        <is>
+          <t>uXCiWVqdVGw</t>
+        </is>
+      </c>
+      <c r="K536" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】明日のイベントお知らせチェック！　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D537" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年第4弾ブライダルガチャを事前チェック
+メロトセロイ・メリッサ等の花嫁ガチャ告知
+井戸攻略雑談と無人島・螺旋回廊の予想</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトール神眼の権技は当たり性能
+・制圧戦延長で育成しやすい
+・螺旋回廊はギミックが深く良い</t>
+        </is>
+      </c>
+      <c r="F537" s="2" t="inlineStr">
+        <is>
+          <t>・ブライダルは強キャラ出ず微妙な印象
+・ガチャの出し順が悪い(黒バラ先が良かった)
+・集回イベントが単調そうで心配</t>
+        </is>
+      </c>
+      <c r="G537" s="2" t="inlineStr">
+        <is>
+          <t>・ブライダルガチャ
+・7.5周年第4弾
+・今週の井戸
+・螺旋回廊予想
+・無人島予想</t>
+        </is>
+      </c>
+      <c r="H537" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I537" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=j6N65X38VQI</t>
+        </is>
+      </c>
+      <c r="J537" s="2" t="inlineStr">
+        <is>
+          <t>j6N65X38VQI</t>
+        </is>
+      </c>
+      <c r="K537" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　聖王厄：討伐クエスト　フルオート真似するだけ　放置しながらクリア可能に！</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>聖王厄討伐をフルオート放置で攻略
+ロロ・暦読み・裁判等で体制を固める
+朝ぼらけを2ターン目に打つのが味噌</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>・フルオート放置でクリア可能
+・暦読みのダメージが圧倒的
+・デバフを入れれば他キャラでも勝てる</t>
+        </is>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
+        <is>
+          <t>・イン攻撃と打攻撃が痛く対策必須
+・熱雷ライを食らうとダメージが通らず注意</t>
+        </is>
+      </c>
+      <c r="G538" s="2" t="inlineStr">
+        <is>
+          <t>・聖王厄討伐
+・フルオート
+・朝ぼらけ
+・デバフ対策
+・6ターンクリア</t>
+        </is>
+      </c>
+      <c r="H538" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I538" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xfBPtnOhfRE</t>
+        </is>
+      </c>
+      <c r="J538" s="2" t="inlineStr">
+        <is>
+          <t>xfBPtnOhfRE</t>
+        </is>
+      </c>
+      <c r="K538" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C539" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR スターゲイザー 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D539" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSSRスターゲイザー
+武装アニメーションを紹介
+ショート動画</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="inlineStr"/>
+      <c r="F539" s="2" t="inlineStr"/>
+      <c r="G539" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・スターゲイザー
+・SSR
+・武装アニメ</t>
+        </is>
+      </c>
+      <c r="H539" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I539" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SZWtiAtdYCE</t>
+        </is>
+      </c>
+      <c r="J539" s="2" t="inlineStr">
+        <is>
+          <t>SZWtiAtdYCE</t>
+        </is>
+      </c>
+      <c r="K539" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】メロセロは欲しい！『7.5周年記念 ロマンシングブライド Romancing祭 メロトセロイ編＆バルテルミー編』【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年ブライド ダブルガチャを実況
+メロセロ・ハーディ等を無事確保
+ピック出ず天井寸前のヒヤヒヤ展開</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>・メロセロのイラストが高クオリティ
+・ラゼムがポロっと出てファインプレイ</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>・ステップ5までピック出ないこと多すぎ
+・同キャラ別スタイルのすり抜けが最悪</t>
+        </is>
+      </c>
+      <c r="G540" s="2" t="inlineStr">
+        <is>
+          <t>・ロマンシングブライド
+・メロトセロイ
+・ガチャ実況
+・ピック確定
+・無償ジュエル</t>
+        </is>
+      </c>
+      <c r="H540" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I540" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=q8Inklge2Ig</t>
+        </is>
+      </c>
+      <c r="J540" s="2" t="inlineStr">
+        <is>
+          <t>q8Inklge2Ig</t>
+        </is>
+      </c>
+      <c r="K540" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C541" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】マイス亜種！？神速バルテルミー編解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D541" s="2" t="inlineStr">
+        <is>
+          <t>バルテルミーはマイス亜種の熱属性版
+継承込みでラゼムをさらに固くできる
+グスタフ・ハーディも控えめ評価</t>
+        </is>
+      </c>
+      <c r="E541" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミーは継承込みで優秀
+・全体マタンでオーバードライブできる</t>
+        </is>
+      </c>
+      <c r="F541" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミーは継承無いとラゼムで十分
+・ラゼム以降の流れでインパクトに欠ける
+・ハーディはカウンターで使い所が限定的</t>
+        </is>
+      </c>
+      <c r="G541" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミー
+・マイス亜種
+・グスタフ
+・ハーディ
+・継承</t>
+        </is>
+      </c>
+      <c r="H541" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I541" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9TJBFvbZXEM</t>
+        </is>
+      </c>
+      <c r="J541" s="2" t="inlineStr">
+        <is>
+          <t>9TJBFvbZXEM</t>
+        </is>
+      </c>
+      <c r="K541" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】誰が予想できるのか！神速メリッサ編性能確認【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>メリッサはOD・BP特化の優秀サポーター
+メロセロは1個前継承前提で控えめ
+プルミエールはカタリナ下位の趣味枠</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr">
+        <is>
+          <t>・メリッサは唯一性ありエクストラフォースも配れる
+・メリッサはサポーターとして優秀</t>
+        </is>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>・メロセロは火力もなく控えめすぎ
+・プルミエールは確率50%で不安定
+・プルミエールはスタートダッシュが遅い</t>
+        </is>
+      </c>
+      <c r="G542" s="2" t="inlineStr">
+        <is>
+          <t>・メリッサ
+・メロトセロイ
+・プルミエール
+・OD/BPサポート
+・カウンター</t>
+        </is>
+      </c>
+      <c r="H542" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I542" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ONRHei2d_3I</t>
+        </is>
+      </c>
+      <c r="J542" s="2" t="inlineStr">
+        <is>
+          <t>ONRHei2d_3I</t>
+        </is>
+      </c>
+      <c r="K542" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C543" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】○○○連！？引く、、そこにガチャがある限り【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D543" s="2" t="inlineStr">
+        <is>
+          <t>ブライダル第3弾を回しメリッサを確保
+奇跡の神引きでメロセロも入手
+バルテルミーは無償で追いガチャ</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="inlineStr">
+        <is>
+          <t>・メリッサとメロセロを神引きで確保
+・ドラクエコラボキャラは未だに強い</t>
+        </is>
+      </c>
+      <c r="F543" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミー1点狙いは厳しい
+・周年ガチャでガチャ画面がパンク気味</t>
+        </is>
+      </c>
+      <c r="G543" s="2" t="inlineStr">
+        <is>
+          <t>・ブライダルガチャ
+・メリッサ
+・メロトセロイ
+・FFRKコラボ
+・天井</t>
+        </is>
+      </c>
+      <c r="H543" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I543" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QjD4scXdeC0</t>
+        </is>
+      </c>
+      <c r="J543" s="2" t="inlineStr">
+        <is>
+          <t>QjD4scXdeC0</t>
+        </is>
+      </c>
+      <c r="K543" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年第4弾は花嫁ガチャ！メロトセロイ編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>メロセロ編3人の性能を詳細チェック
+メロセロはOD前提環境で当たり性能
+メリッサは時短・プルミエールは趣味枠</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>・メロセロはサポート優秀で当たり
+・メリッサはレイド時短・無人島で活躍
+・メロセロのイラストが力入っている</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>・プルミエールは安定しないロマン枠
+・メロセロは継承無いと火ダメ軽減が弱い
+・メリッサは自身火力がほぼ0</t>
+        </is>
+      </c>
+      <c r="G544" s="2" t="inlineStr">
+        <is>
+          <t>・メロトセロイ
+・メリッサ
+・プルミエール
+・チャージブラスト
+・継承前提</t>
+        </is>
+      </c>
+      <c r="H544" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I544" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OlyEqWFT36k</t>
+        </is>
+      </c>
+      <c r="J544" s="2" t="inlineStr">
+        <is>
+          <t>OlyEqWFT36k</t>
+        </is>
+      </c>
+      <c r="K544" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B545" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C545" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こっちの主役は全員男！バルテルミー編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D545" s="2" t="inlineStr">
+        <is>
+          <t>男性3人バルテルミー編の性能チェック
+グスタフが無難に1番使いやすい
+バルテルミーは熱のマイスで目新しさ薄い</t>
+        </is>
+      </c>
+      <c r="E545" s="2" t="inlineStr">
+        <is>
+          <t>・グスタフは先制火力＆味方強化で使いやすい
+・ハーディは関節多用の敵で奇跡的活躍も</t>
+        </is>
+      </c>
+      <c r="F545" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミーはただのマイスで引きが弱い
+・ハーディは現状無理して引かなくてよい
+・花嫁ガチャは神楽弾より性能が弱い</t>
+        </is>
+      </c>
+      <c r="G545" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミー
+・グスタフ
+・ハーディ
+・マイス亜種
+・残熱アタッカー</t>
+        </is>
+      </c>
+      <c r="H545" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I545" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TDY0DhK7950</t>
+        </is>
+      </c>
+      <c r="J545" s="2" t="inlineStr">
+        <is>
+          <t>TDY0DhK7950</t>
+        </is>
+      </c>
+      <c r="K545" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年Romancing祭メロトセロイ編ガチャ評価 #ロマサガRS #shorts #ガチャ</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年Romancing祭の評価ショート
+メロトセロイ編ガチャを評価
+花嫁ガチャ紹介</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="inlineStr"/>
+      <c r="F546" s="2" t="inlineStr"/>
+      <c r="G546" s="2" t="inlineStr">
+        <is>
+          <t>・メロトセロイ編
+・ガチャ評価
+・7.5周年
+・Romancing祭</t>
+        </is>
+      </c>
+      <c r="H546" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I546" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9aGBFnqEVNg</t>
+        </is>
+      </c>
+      <c r="J546" s="2" t="inlineStr">
+        <is>
+          <t>9aGBFnqEVNg</t>
+        </is>
+      </c>
+      <c r="K546" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年Romancing祭バルテルミー編ガチャ評価 #ロマサガRS #shorts #ガチャ</t>
+        </is>
+      </c>
+      <c r="D547" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年Romancing祭の評価ショート
+バルテルミー編ガチャを評価
+花嫁ガチャ紹介</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="inlineStr"/>
+      <c r="F547" s="2" t="inlineStr"/>
+      <c r="G547" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミー編
+・ガチャ評価
+・7.5周年
+・Romancing祭</t>
+        </is>
+      </c>
+      <c r="H547" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I547" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cSOsZX4IyVk</t>
+        </is>
+      </c>
+      <c r="J547" s="2" t="inlineStr">
+        <is>
+          <t>cSOsZX4IyVk</t>
+        </is>
+      </c>
+      <c r="K547" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】バルテルミー能力値早見表 ~鋼鉄兵たちの井戸での活躍度50%❓継承＋フォースOD1.75倍＋ﾄﾞﾗｲﾌﾞﾁｪｲﾝ~TOP編成を紹介👏</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>バルテルミーの能力値を早見表で解説
+火力サポートと本人火力が高水準
+鋼鉄兵の井戸でデスマシーン編成が有望</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>・エクストラフォースOD1.75倍付与が強い
+・本人火力も全体16ヒットでやばい
+・継承で追撃減らせば井戸で活躍</t>
+        </is>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>・追撃が多く井戸の移動度を食いやすい</t>
+        </is>
+      </c>
+      <c r="G548" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミー能力値
+・鋼鉄兵の井戸
+・フォースOD1.75倍
+・デスマシーン編成
+・継承</t>
+        </is>
+      </c>
+      <c r="H548" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I548" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6V9B58e-G08</t>
+        </is>
+      </c>
+      <c r="J548" s="2" t="inlineStr">
+        <is>
+          <t>6V9B58e-G08</t>
+        </is>
+      </c>
+      <c r="K548" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベント解説と注意点と周回編成の紹介 討伐 聖王[厄]のオートクリア編成の紹介【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D549" s="2" t="inlineStr">
+        <is>
+          <t>ハーディの転職イベントを解説
+制圧戦延長中で早期攻略を推奨
+討伐聖王厄のオートクリア編成を紹介</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="inlineStr">
+        <is>
+          <t>・1日記憶再戦でステップ10到達可能
+・オートクリア編成で討伐を攻略可能</t>
+        </is>
+      </c>
+      <c r="F549" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦延長で早く戻りたい運営の図計
+・新規向け難易度をもっと下げてほしかった</t>
+        </is>
+      </c>
+      <c r="G549" s="2" t="inlineStr">
+        <is>
+          <t>・ハーディの転職
+・パネルイベント
+・討伐聖王厄
+・オートクリア編成
+・制圧戦延長</t>
+        </is>
+      </c>
+      <c r="H549" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I549" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=etCq9mz9A8U</t>
+        </is>
+      </c>
+      <c r="J549" s="2" t="inlineStr">
+        <is>
+          <t>etCq9mz9A8U</t>
+        </is>
+      </c>
+      <c r="K549" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17T01:07:45Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K549"/>
+  <dimension ref="A1:K556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36652,6 +36652,471 @@
         </is>
       </c>
     </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】まさかの!?ランク付け!!「マイスを終わらせに」バルテルミーの完全上位互換性能&amp;思わぬ伏兵メリッサの唯一性…!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>バルテルミーとメリッサのガチャ性能を高難度評価。
+バルテルミーは全体追撃主体で火力SS、マイス更新。
+メリッサは壁＋支援のエクストラ1.5倍置き物。</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミー火力SSでマイス上位互換
+・属性が被らず使い勝手が出てくる
+・メリッサのダメブロ2回が無人島に刺さる
+・メリッサのエクストラ1.5倍置き物が便利</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>・上位勢を見ると回ることはなさそう
+・メリッサは戦闘力がなく火力添え物
+・ハーディ・ブルエールはキャラ愛頼みの性能
+・シングル時期で薄められた危ないガチャ</t>
+        </is>
+      </c>
+      <c r="G550" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミー性能
+・メリッサ性能
+・全体追撃
+・ダブルガチャ
+・厳選評価</t>
+        </is>
+      </c>
+      <c r="H550" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I550" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4WxfOG08MHc</t>
+        </is>
+      </c>
+      <c r="J550" s="2" t="inlineStr">
+        <is>
+          <t>4WxfOG08MHc</t>
+        </is>
+      </c>
+      <c r="K550" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T01:07:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「∞追撃」敵が倒れても止まらないハーディの聖王接待追撃!!&amp;先代をさらに確かな強さにする継承持ちメロトセロイ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>ハーディは関節避弾追撃型で火力S総合A。
+アラケスの焼き直しで根本的に強くはない。
+メロトセロイは継承エクストラ1.25倍が売り。</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="inlineStr">
+        <is>
+          <t>・ハーディは聖王の関節攻撃にアタッカーとして刺さる
+・避弾ごとの防御サポートが優秀
+・メロトセロイの継承エクストラ25%が先代に着実なプラス</t>
+        </is>
+      </c>
+      <c r="F551" s="2" t="inlineStr">
+        <is>
+          <t>・根本的に強くないスタイルの焼き直し
+・アラケスから大した変化はない
+・メロトセロイは中飛ばで火力いまいち
+・付け置き性能が続く</t>
+        </is>
+      </c>
+      <c r="G551" s="2" t="inlineStr">
+        <is>
+          <t>・ハーディ性能
+・メロトセロイ性能
+・関節避弾追撃
+・継承エクストラ
+・橋休めガチャ</t>
+        </is>
+      </c>
+      <c r="H551" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I551" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=oonpo9djzc0</t>
+        </is>
+      </c>
+      <c r="J551" s="2" t="inlineStr">
+        <is>
+          <t>oonpo9djzc0</t>
+        </is>
+      </c>
+      <c r="K551" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T01:07:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　FFRKがロマサガRSとコラボ決定！！　今ガチャ引くの待ったが正解？</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>FFRKがロマサガRSとコラボ決定（7/10～）。
+ドラクエタクトの前例から相互コラボを予想。
+今のダブルガチャは引かず待ち推奨。</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>・FFRKコラボに期待
+・ドラクエタクトコラボのキャラは結構強かった
+・暦み・サイバー3体がおすすめ</t>
+        </is>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>・相互だとコンプに18万必要できつい
+・毎週ダブルガチャ続きで負担
+・今は引かず待った方がいい
+・復刻なしだと取捨が悩ましい</t>
+        </is>
+      </c>
+      <c r="G552" s="2" t="inlineStr">
+        <is>
+          <t>・FFRKコラボ
+・7月10日開始
+・ドラクエタクト前例
+・ガチャ待ち
+・ジョエル確保</t>
+        </is>
+      </c>
+      <c r="H552" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I552" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GvGikzIRAQg</t>
+        </is>
+      </c>
+      <c r="J552" s="2" t="inlineStr">
+        <is>
+          <t>GvGikzIRAQg</t>
+        </is>
+      </c>
+      <c r="K552" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T01:07:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B553" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C553" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ガチャチェックして行こう！　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D553" s="2" t="inlineStr">
+        <is>
+          <t>生配信でガチャチェックと聖王攻略を視聴者と雑談。
+63連チケットドロップや聖王ギミックを議論。
+今回のガチャはスルー気味の評価。</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="inlineStr">
+        <is>
+          <t>・代々が超絶便利で評価急上昇
+・朝ぼらけ＆赤ネサスで聖王攻略可能
+・63連チケットが取りこぼし分も貰える
+・グスタフはバフ持ちで一応良い</t>
+        </is>
+      </c>
+      <c r="F553" s="2" t="inlineStr">
+        <is>
+          <t>・今回のガチャは刺さるキャラがおらずスルーでいい
+・聖王のダメージ減・発狂条件が分かりにくい
+・熱雷属性だとダメージが通らなくなる
+・ダブルガチャ連続で負担</t>
+        </is>
+      </c>
+      <c r="G553" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャチェック生配信
+・63連チケット
+・聖王アビス攻略
+・代々が便利
+・朝ぼらけ対策</t>
+        </is>
+      </c>
+      <c r="H553" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I553" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WVUllMewpcY</t>
+        </is>
+      </c>
+      <c r="J553" s="2" t="inlineStr">
+        <is>
+          <t>WVUllMewpcY</t>
+        </is>
+      </c>
+      <c r="K553" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T01:07:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SR ケルベロスバクゥハウンド 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSRケルベロスバクゥハウンド武装アニメ紹介。
+短い戦闘ボイス中心のShorts。
+ロマサガRS以外のゲーム動画。</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr"/>
+      <c r="F554" s="2" t="inlineStr"/>
+      <c r="G554" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ケルベロスバクゥハウンド
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H554" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I554" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=555Vip380qI</t>
+        </is>
+      </c>
+      <c r="J554" s="2" t="inlineStr">
+        <is>
+          <t>555Vip380qI</t>
+        </is>
+      </c>
+      <c r="K554" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T01:07:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B555" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C555" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】聖王[厄]Romancing攻略 ※手動 【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D555" s="2" t="inlineStr">
+        <is>
+          <t>聖王アビスRomancingを手動で攻略解説。
+サイバー暦み聖王代々女神編成で挑戦。
+朝ぼらけ無効化と生後の歌回避が要。</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="inlineStr">
+        <is>
+          <t>・女神の朝ぼらけで陰属性攻撃を全無効化できて強い
+・生後の歌で遅延の歌を回避できる
+・代々はダメージを出せて強い
+・2023以前スタイルでメダル交換しやすい</t>
+        </is>
+      </c>
+      <c r="F555" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビスは陰属性で超火力連発しきつい
+・追加効果は受けてしまうので注意
+・ダメージ無効化頼みの戦法しかできなかった</t>
+        </is>
+      </c>
+      <c r="G555" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビス攻略
+・朝ぼらけ無効化
+・生後の歌
+・手動攻略
+・女神編成</t>
+        </is>
+      </c>
+      <c r="H555" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I555" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Oj7srY5sSRI</t>
+        </is>
+      </c>
+      <c r="J555" s="2" t="inlineStr">
+        <is>
+          <t>Oj7srY5sSRI</t>
+        </is>
+      </c>
+      <c r="K555" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T01:07:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】完全網羅討伐聖王！様々編成でなぎ倒す！！！超短期決戦＆堅実＆超耐久解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>聖王アビス攻略を2T・4T・12T耐久の3編成で解説。
+育成状況で結果が大きく変わると指摘。
+最終皇帝男やサーミンが活躍。</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>・最終皇帝男は耐久で必須級のいいキャラ
+・サーミンのカウンターHKが優秀
+・ルクスオーバーエッジが壊れ性能
+・ロックブーケが避弾追撃で刺さる</t>
+        </is>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>・育成状態で送金（結果）が全然変わる
+・2ターンクリアはカウンター式できつい
+・暦みとビンセントどちら取るか悩ましい
+・裁判は防御ゲージが高くないのが難点</t>
+        </is>
+      </c>
+      <c r="G556" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビス攻略
+・2ターン編成
+・12ターン耐久
+・最終皇帝男
+・育成依存</t>
+        </is>
+      </c>
+      <c r="H556" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I556" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ED4T0KZJY5M</t>
+        </is>
+      </c>
+      <c r="J556" s="2" t="inlineStr">
+        <is>
+          <t>ED4T0KZJY5M</t>
+        </is>
+      </c>
+      <c r="K556" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T01:07:18Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K556"/>
+  <dimension ref="A1:K574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -37117,6 +37117,1177 @@
         </is>
       </c>
     </row>
+    <row r="557">
+      <c r="A557" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B557" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C557" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Memoria幼子の祈り→③〜最終⑬話　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D557" s="2" t="inlineStr">
+        <is>
+          <t>Memoria『幼子の祈り』の③話から最終⑬話を収録
+ストーリーパートを一気にプレイ
+字幕情報が乏しく内容の詳細は不明</t>
+        </is>
+      </c>
+      <c r="E557" s="2" t="inlineStr"/>
+      <c r="F557" s="2" t="inlineStr"/>
+      <c r="G557" s="2" t="inlineStr">
+        <is>
+          <t>・Memoria
+・幼子の祈り
+・ストーリー周回</t>
+        </is>
+      </c>
+      <c r="H557" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I557" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CB17Q9CiKVM</t>
+        </is>
+      </c>
+      <c r="J557" s="2" t="inlineStr">
+        <is>
+          <t>CB17Q9CiKVM</t>
+        </is>
+      </c>
+      <c r="K557" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T14:01:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】63連ガチャ「大逆転」まさかのアイツが来て手のひら返しクルー　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="inlineStr">
+        <is>
+          <t>63連ガチャに挑戦した記録動画
+途中から大逆転、まさかのキャラが登場
+結果に手のひら返しで盛り上がる</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>・まさかのキャラが当たり大逆転の引き</t>
+        </is>
+      </c>
+      <c r="F558" s="2" t="inlineStr"/>
+      <c r="G558" s="2" t="inlineStr">
+        <is>
+          <t>・63連ガチャ
+・大逆転
+・ガチャ結果</t>
+        </is>
+      </c>
+      <c r="H558" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I558" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=L0j_FrAtPdY</t>
+        </is>
+      </c>
+      <c r="J558" s="2" t="inlineStr">
+        <is>
+          <t>L0j_FrAtPdY</t>
+        </is>
+      </c>
+      <c r="K558" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T14:01:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B559" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C559" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】24体「厳選極まる」第4弾VSこよみ…サイヴァ…ヴィンセント!!→24体8ガチャランキング!!最新スタイル比較検討会→2026年6月19日版　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D559" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年ラスト5弾含む全8ガチャ24体を厳選ランキング
+暦み・ヴィンセント・ボルカノなど高難度向けを高評価
+スルー確定組も多く投稿者は暦みまで様子見の構え</t>
+        </is>
+      </c>
+      <c r="E559" s="2" t="inlineStr">
+        <is>
+          <t>・暦みは高難度のクリアターン短縮が非常に有用
+・ヴィンセントは汎用性と突出した強さ
+・ボルカノは熱アタッカーと組ませると強力
+・岩ずもは火力ベース作りに必須級</t>
+        </is>
+      </c>
+      <c r="F559" s="2" t="inlineStr">
+        <is>
+          <t>・メロトセロイは特徴なしで性能過去最低
+・ボルレットはデバフしかできない
+・ダリアス・ミニオンは出力が弱い
+・ハーディは必然性がなく殴った方が早い</t>
+        </is>
+      </c>
+      <c r="G559" s="2" t="inlineStr">
+        <is>
+          <t>・24体ランキング
+・厳選
+・暦み
+・ヴィンセント
+・継承優先度</t>
+        </is>
+      </c>
+      <c r="H559" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I559" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rybrEeMcChg</t>
+        </is>
+      </c>
+      <c r="J559" s="2" t="inlineStr">
+        <is>
+          <t>rybrEeMcChg</t>
+        </is>
+      </c>
+      <c r="K559" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T14:01:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C560" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始259日目　難敵毛利元就が勢力戦で大暴れ！城Lv上げが困難なので対策を知りたい！</t>
+        </is>
+      </c>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣プレイ259日目の進捗報告
+武将育成や拠点取りで意味値・制圧率を着実に向上
+城Lv上げと毛利元就対策に課題が残る</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>・弓の武将は希少価値が高くありがたい
+・眠っていた武将を育成し意味値がアップ
+・プレイヤーレベル92まで順調に上昇</t>
+        </is>
+      </c>
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>・城Lv上げが困難で対策を知りたい
+・毛利元就が勢力戦で大暴れし難敵
+・中国地方の拠点がなかなか取れない</t>
+        </is>
+      </c>
+      <c r="G560" s="2" t="inlineStr">
+        <is>
+          <t>・信長の野望出陣
+・259日目
+・武将育成
+・拠点取り
+・意味値</t>
+        </is>
+      </c>
+      <c r="H560" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I560" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=89aV7MSyVUQ</t>
+        </is>
+      </c>
+      <c r="J560" s="2" t="inlineStr">
+        <is>
+          <t>89aV7MSyVUQ</t>
+        </is>
+      </c>
+      <c r="K560" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T14:01:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B561" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C561" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】緊急速報！ファイナルファンタジーとロマサガRSのコラボが決定！【FFRK】【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D561" s="2" t="inlineStr">
+        <is>
+          <t>FFRKとロマサガRSのコラボ決定の緊急速報（FF側7/10～）。
+ドラクエタクトの前例からRS側開催も予想。
+FF4世代として期待大。</t>
+        </is>
+      </c>
+      <c r="E561" s="2" t="inlineStr">
+        <is>
+          <t>・コラボはゲームが盛り上がるので大歓迎
+・7月の閑散期に投入されれば盛り上がる
+・ドラクエタクトコラボはめちゃ盛り上がった
+・セシルなどFFキャラ参戦に期待</t>
+        </is>
+      </c>
+      <c r="F561" s="2" t="inlineStr">
+        <is>
+          <t>・RS側ではまだ何も発表されておらず不明
+・FF側だけ開催の可能性もある</t>
+        </is>
+      </c>
+      <c r="G561" s="2" t="inlineStr">
+        <is>
+          <t>・FFRKコラボ
+・緊急速報
+・7月10日
+・RS側開催予想
+・FFキャラ参戦</t>
+        </is>
+      </c>
+      <c r="H561" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I561" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6u-LP29DLHk</t>
+        </is>
+      </c>
+      <c r="J561" s="2" t="inlineStr">
+        <is>
+          <t>6u-LP29DLHk</t>
+        </is>
+      </c>
+      <c r="K561" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T01:07:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】まさかの展開に衝撃が！7.5周年第4弾はジューンブライドガチャ！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年第4弾はまさかのジューンブライドガチャ（約4年ぶり）。
+メロトセロイ・メリッサ花嫁、バルテルミー花婿が登場。
+聖王アビス討伐クエストも開催。</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャメンツが豪華で胸熱
+・メリッサお母ちゃん復活が嬉しい
+・バルテルミー・グスタフ・ハーディ花婿も魅力的
+・3000ジュエル＆ログボが嬉しい</t>
+        </is>
+      </c>
+      <c r="F562" s="2" t="inlineStr">
+        <is>
+          <t>・神楽系終了後で新キャラの性能が気になる
+・復刻エスパーガールは無理する必要なし
+・ダブルガチャ連続でガチャ過多</t>
+        </is>
+      </c>
+      <c r="G562" s="2" t="inlineStr">
+        <is>
+          <t>・ジューンブライドガチャ
+・メロトセロイ
+・メリッサ
+・バルテルミー
+・聖王アビス討伐</t>
+        </is>
+      </c>
+      <c r="H562" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I562" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=T7SjsmKH1IU</t>
+        </is>
+      </c>
+      <c r="J562" s="2" t="inlineStr">
+        <is>
+          <t>T7SjsmKH1IU</t>
+        </is>
+      </c>
+      <c r="K562" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T01:07:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B563" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C563" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年最強のガチャはどれ？おすすめガチャランキング中間発表！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D563" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年8ガチャを性能のみでランキング中間発表
+8位バルテルミー編、7位メロトセロイ編と新ガチャが下位
+リアム・ダリオは単体性能が高く上位候補</t>
+        </is>
+      </c>
+      <c r="E563" s="2" t="inlineStr">
+        <is>
+          <t>・リアムは当たりで継承込み短期決戦が強力
+・ダリオはカタログスペックが高い
+・メリッサは使い所次第で良性能</t>
+        </is>
+      </c>
+      <c r="F563" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミー編は直近ガチャで見劣りし8位
+・メロトセロイ編はコスプレ寄りで性能控えめ
+・アーニャ・ダリアスは優先度が低い</t>
+        </is>
+      </c>
+      <c r="G563" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年
+・ガチャランキング
+・中間発表
+・リアム
+・ダリオ</t>
+        </is>
+      </c>
+      <c r="H563" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I563" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Y0Q-QykK5HI</t>
+        </is>
+      </c>
+      <c r="J563" s="2" t="inlineStr">
+        <is>
+          <t>Y0Q-QykK5HI</t>
+        </is>
+      </c>
+      <c r="K563" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T14:01:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こんなことある？超絶展開でWガチャ史上最●コンプ！？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>4年ぶりのロマンシングブライドWガチャに挑戦
+メロトセロイ編で神引き連発、メリッサまでコンプ
+絶好調の流れでバルテルミー編にも続行</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="inlineStr">
+        <is>
+          <t>・メロトセロイのイラストが最高で乗り換えたいほど
+・序盤からムクチャ等の神引きで勝ち確
+・花嫁ガチャのシーズナル演出が良い</t>
+        </is>
+      </c>
+      <c r="F564" s="2" t="inlineStr">
+        <is>
+          <t>・バーニーは昔ほどSSが出る信頼度がない</t>
+        </is>
+      </c>
+      <c r="G564" s="2" t="inlineStr">
+        <is>
+          <t>・ロマンシングブライド
+・Wガチャ
+・メロトセロイ
+・神引き
+・ガチャ実況</t>
+        </is>
+      </c>
+      <c r="H564" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I564" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZabH-OccZ-U</t>
+        </is>
+      </c>
+      <c r="J564" s="2" t="inlineStr">
+        <is>
+          <t>ZabH-OccZ-U</t>
+        </is>
+      </c>
+      <c r="K564" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T14:01:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C565" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】このイベントは諦めちゃダメ！聖王イベントで激ウマ報酬を必ず取る方法を解説！！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
+        <is>
+          <t>情説イベント・セオアビスの期間限定報酬を解説
+ロマンシング1回クリアで報酬一括、無理なら周回でOK
+投稿者はこの救済設計を大絶賛</t>
+        </is>
+      </c>
+      <c r="E565" s="2" t="inlineStr">
+        <is>
+          <t>・ジュエル500・ソウルピース100など報酬が豪華
+・ロマンシング以外は記憶再戦で楽に集められる
+・クリア＋周回どちらでも取れる救済設計を大賛成</t>
+        </is>
+      </c>
+      <c r="F565" s="2" t="inlineStr">
+        <is>
+          <t>・報酬期間が約1週間と短い
+・ロマンシングは難易度が高く忙しい層には厳しい</t>
+        </is>
+      </c>
+      <c r="G565" s="2" t="inlineStr">
+        <is>
+          <t>・セオアビス
+・聖王[厄]
+・期間限定報酬
+・記憶再戦
+・ロマンシング</t>
+        </is>
+      </c>
+      <c r="H565" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I565" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jyuYSHvqqQM</t>
+        </is>
+      </c>
+      <c r="J565" s="2" t="inlineStr">
+        <is>
+          <t>jyuYSHvqqQM</t>
+        </is>
+      </c>
+      <c r="K565" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T14:01:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C566" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今回は〇〇推奨か？メロトセロイ・バルテルミーガチャ性能チェック&amp;キャラランク評価【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D566" s="2" t="inlineStr">
+        <is>
+          <t>メロセロイ・バルテルミー他ガチャ性能とランクを評価。
+注目はハーディの関節避弾追撃。
+全体的に性能控えめな橋休めガチャ。</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="inlineStr">
+        <is>
+          <t>・ハーディは強敵の関節攻撃に刺さり無人島でも使える
+・技マシン運用が優秀なキャラが多い
+・ダメブロ2回は無人島に刺さる
+・小スタイルは貴重な上戦力</t>
+        </is>
+      </c>
+      <c r="F566" s="2" t="inlineStr">
+        <is>
+          <t>・全体的に性能控えめな印象
+・汎用性高いキャラは見つけられず
+・マイス・ラゼムの属性違いは火力落ちそう
+・看門武器で本領発揮できないのが残念</t>
+        </is>
+      </c>
+      <c r="G566" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ性能評価
+・キャラランク
+・ハーディ注目
+・関節避弾追撃
+・橋休めガチャ</t>
+        </is>
+      </c>
+      <c r="H566" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I566" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5oGmLJVMXzo</t>
+        </is>
+      </c>
+      <c r="J566" s="2" t="inlineStr">
+        <is>
+          <t>5oGmLJVMXzo</t>
+        </is>
+      </c>
+      <c r="K566" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T01:07:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B567" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C567" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】聖王〔厄〕記憶周回：32秒…（ロマンシングクリア出来ない方用）</t>
+        </is>
+      </c>
+      <c r="D567" s="2" t="inlineStr">
+        <is>
+          <t>聖王[厄]の記憶周回を32秒で回す編成を紹介
+ロマンシングをクリアできない人向けの周回用
+字幕情報が乏しく詳細解説は不明</t>
+        </is>
+      </c>
+      <c r="E567" s="2" t="inlineStr">
+        <is>
+          <t>・32秒で周回でき報酬集めが効率的</t>
+        </is>
+      </c>
+      <c r="F567" s="2" t="inlineStr"/>
+      <c r="G567" s="2" t="inlineStr">
+        <is>
+          <t>・聖王[厄]
+・記憶周回
+・32秒編成
+・周回</t>
+        </is>
+      </c>
+      <c r="H567" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I567" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8g-s5I2OXgA</t>
+        </is>
+      </c>
+      <c r="J567" s="2" t="inlineStr">
+        <is>
+          <t>8g-s5I2OXgA</t>
+        </is>
+      </c>
+      <c r="K567" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T14:01:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C568" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第124回鋼鉄兵たちの井戸〜‼️12手攻略‼️100位以内編成＋TOP編成のヒント有りよ☺️</t>
+        </is>
+      </c>
+      <c r="D568" s="2" t="inlineStr">
+        <is>
+          <t>鋼鉄兵たちの井戸を12手で攻略、100位以内編成を紹介。
+サライ・ブラキエス・サバ・Sマシーン・リアユト編成。
+トップ編成のヒントも提示。</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="inlineStr">
+        <is>
+          <t>・この編成でも100位以内を目指せる
+・今からでもランク50以内が可能
+・ロト武器は優秀</t>
+        </is>
+      </c>
+      <c r="F568" s="2" t="inlineStr">
+        <is>
+          <t>・デスマシーンが古く持っていない人もいる</t>
+        </is>
+      </c>
+      <c r="G568" s="2" t="inlineStr">
+        <is>
+          <t>・鋼鉄兵たちの井戸
+・12手攻略
+・100位以内
+・デスマシーン
+・トップ編成予想</t>
+        </is>
+      </c>
+      <c r="H568" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MA9RdPKIja4</t>
+        </is>
+      </c>
+      <c r="J568" s="2" t="inlineStr">
+        <is>
+          <t>MA9RdPKIja4</t>
+        </is>
+      </c>
+      <c r="K568" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T01:07:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第124回 ~鋼鉄兵たちの井戸 ~‼️攻略‼️目指せ‼︎100位以内~全てお見せ致します👀</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>鋼鉄兵たちの井戸の自作オリジナル編成を紹介。
+全体アタッカー2台サライ＆デスマシーンにビクトール採用。
+14手編成で100位以内可能。</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトールは火力サポート値が高く採用価値あり
+・この編成でも100位を目指せる
+・ロト武器は突入が埋まり優秀</t>
+        </is>
+      </c>
+      <c r="F569" s="2" t="inlineStr">
+        <is>
+          <t>・2手アタッカーで手数が少なめ</t>
+        </is>
+      </c>
+      <c r="G569" s="2" t="inlineStr">
+        <is>
+          <t>・鋼鉄兵たちの井戸
+・オリジナル編成
+・全体アタッカー2台
+・ビクトール採用
+・14手</t>
+        </is>
+      </c>
+      <c r="H569" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VxDVBrB2ygs</t>
+        </is>
+      </c>
+      <c r="J569" s="2" t="inlineStr">
+        <is>
+          <t>VxDVBrB2ygs</t>
+        </is>
+      </c>
+      <c r="K569" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T01:07:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【追いガチャ動画】鉄壁ブロッカー現る！？【No.614】</t>
+        </is>
+      </c>
+      <c r="D570" s="2" t="inlineStr">
+        <is>
+          <t>クロエ編ガチャでエスパーギャルを狙う追いガチャ実況
+ヴィンセント3体やクロエ・アルベルトを引き当てる
+物欲センサーで本命は出ず天井到達</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="inlineStr">
+        <is>
+          <t>・クロエのイラストがとてもきれい
+・ヴィンセントを3体引けた好調な引き</t>
+        </is>
+      </c>
+      <c r="F570" s="2" t="inlineStr">
+        <is>
+          <t>・物欲センサーで本命エスパーギャルが出ず
+・ペット枠の連続すり抜けで天井到達</t>
+        </is>
+      </c>
+      <c r="G570" s="2" t="inlineStr">
+        <is>
+          <t>・追いガチャ
+・クロエ編
+・エスパーギャル
+・ヴィンセント
+・天井</t>
+        </is>
+      </c>
+      <c r="H570" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xs9EnAaQ87Q</t>
+        </is>
+      </c>
+      <c r="J570" s="2" t="inlineStr">
+        <is>
+          <t>xs9EnAaQ87Q</t>
+        </is>
+      </c>
+      <c r="K570" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T14:01:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B571" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C571" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】討伐クエスト「聖王[厄]」Romancingを攻略！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D571" s="2" t="inlineStr">
+        <is>
+          <t>討伐クエスト聖王アビスRomancingを攻略。
+新営の歌・エクスキューションフレーム等のギミックを解説。
+女神不採用でもギミック理解でクリア。</t>
+        </is>
+      </c>
+      <c r="E571" s="2" t="inlineStr">
+        <is>
+          <t>・ギミック理解すれば足りない手持ちでもクリア可能
+・女神の朝ぼらけがファイナルストライク対策に有効
+・役割分担がしっかりした良いパーティー
+・残属性アタッカーが有効</t>
+        </is>
+      </c>
+      <c r="F571" s="2" t="inlineStr">
+        <is>
+          <t>・かなりの強敵で特攻キャラないと激破が難しい
+・新営の歌のBP99ダウンがきつい
+・熱雷属性アタッカーは採用しづらい
+・コーション後は本気モードでダメージ通りにくい</t>
+        </is>
+      </c>
+      <c r="G571" s="2" t="inlineStr">
+        <is>
+          <t>・聖王アビス攻略
+・敵ギミック解説
+・新営の歌対策
+・朝ぼらけ有効
+・残属性アタッカー</t>
+        </is>
+      </c>
+      <c r="H571" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4rybJioSChc</t>
+        </is>
+      </c>
+      <c r="J571" s="2" t="inlineStr">
+        <is>
+          <t>4rybJioSChc</t>
+        </is>
+      </c>
+      <c r="K571" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T01:07:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「バルテルミー 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>バルテルミー編ガチャのバルテルミー等を性能考察
+術算の火炎ODは1.75倍と強力だが運用条件が多い
+マイス/ラゼム所持なら無理に引かなくてよくB+評価</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="inlineStr">
+        <is>
+          <t>・術算誓の火炎ODで最終ダメ1.75倍は強力
+・味方への75%軽減が優秀
+・メリッサと相性が良く夫婦コンビが噛み合う</t>
+        </is>
+      </c>
+      <c r="F572" s="2" t="inlineStr">
+        <is>
+          <t>・先制・BP消費22など運用ハードルが高い
+・消費BP+5の重いデメリットがある
+・ODゲージ上昇を自前で持たない
+・マイス/ラゼム所持なら無理に取る必要なし</t>
+        </is>
+      </c>
+      <c r="G572" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミー
+・グスタフ
+・性能考察
+・オーバードライブ
+・継承</t>
+        </is>
+      </c>
+      <c r="H572" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TNsnNSxkSnU</t>
+        </is>
+      </c>
+      <c r="J572" s="2" t="inlineStr">
+        <is>
+          <t>TNsnNSxkSnU</t>
+        </is>
+      </c>
+      <c r="K572" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T14:01:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「メロトセロイ 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D573" s="2" t="inlineStr">
+        <is>
+          <t>メロトセロイ編ガチャの3スタイルを性能考察
+メロトセロイ単体はC評価だが継承込みでA-に化ける
+メリッサはOD・BP・軽減の3要素が高水準で優秀</t>
+        </is>
+      </c>
+      <c r="E573" s="2" t="inlineStr">
+        <is>
+          <t>・メリッサはOD満タン5ターンとBP回復が優秀
+・メロトセロイはクリスマス継承込みで大幅強化
+・メロトセロイのOD連携付与は他と被らず利点</t>
+        </is>
+      </c>
+      <c r="F573" s="2" t="inlineStr">
+        <is>
+          <t>・メロトセロイ単体は最低のC評価
+・アタッカーもサポーターも見劣りする
+・メロトセロイの火ダメ軽減23%は低い</t>
+        </is>
+      </c>
+      <c r="G573" s="2" t="inlineStr">
+        <is>
+          <t>・メロトセロイ
+・メリッサ
+・性能考察
+・継承
+・オーバードライブ</t>
+        </is>
+      </c>
+      <c r="H573" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I573" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pcbgii6nDKQ</t>
+        </is>
+      </c>
+      <c r="J573" s="2" t="inlineStr">
+        <is>
+          <t>pcbgii6nDKQ</t>
+        </is>
+      </c>
+      <c r="K573" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T14:01:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】討伐 聖王[厄] 無理をしてロマンシング クリアする必要ない？あえてチャレンジ3以下9種の編成紹介します【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>討伐聖王[厄]のギミック解説と低難度向け編成紹介
+ロマンシングは難しいが記憶再戦の周回で報酬は取れる
+チャレンジ3以下9種の編成を提示し無理クリア不要と説く</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="inlineStr">
+        <is>
+          <t>・チャレンジ3以下は記憶再戦可で1日かからず集まる
+・無理にロマンシングをクリアしなくても報酬を取れる</t>
+        </is>
+      </c>
+      <c r="F574" s="2" t="inlineStr">
+        <is>
+          <t>・ロマンシングは偶数ターンのバフ増で難しい
+・熱来編成NGなどギミックが複雑
+・イを過ぎると攻撃が激しく耐えきれない</t>
+        </is>
+      </c>
+      <c r="G574" s="2" t="inlineStr">
+        <is>
+          <t>・聖王[厄]
+・討伐
+・記憶再戦
+・低難度編成
+・期間限定報酬</t>
+        </is>
+      </c>
+      <c r="H574" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=626Qz7Wk3Aw</t>
+        </is>
+      </c>
+      <c r="J574" s="2" t="inlineStr">
+        <is>
+          <t>626Qz7Wk3Aw</t>
+        </is>
+      </c>
+      <c r="K574" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T14:01:20Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K574"/>
+  <dimension ref="A1:K579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -38288,6 +38288,322 @@
         </is>
       </c>
     </row>
+    <row r="575">
+      <c r="A575" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B575" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C575" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ギミック解明「〇〇出禁」螺旋570階シグフレイ速報!!徹底対策でデメリットを乗り越えろ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D575" s="2" t="inlineStr">
+        <is>
+          <t>螺旋570階シグフレイのギミックを速報解説
+技を打ち込みすぎると即死、知力デバフで対策
+技・打無効ターンあり術師中心編成で攻略</t>
+        </is>
+      </c>
+      <c r="E575" s="2" t="inlineStr">
+        <is>
+          <t>・最近流行りの全体攻撃追撃が有効
+・シグフレイはHPが低く術が揃えば2ターンで撃破可</t>
+        </is>
+      </c>
+      <c r="F575" s="2" t="inlineStr">
+        <is>
+          <t>・技を打ち込みすぎると即死、知力デバフ必須
+・シグフレイに技を当てると強化されて危険
+・打を無効化する術があり挙動の見極めが必要</t>
+        </is>
+      </c>
+      <c r="G575" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋570階
+・シグフレイ
+・技出禁ギミック
+・術師編成
+・全体追撃</t>
+        </is>
+      </c>
+      <c r="H575" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I575" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6EcXHcgmJSo</t>
+        </is>
+      </c>
+      <c r="J575" s="2" t="inlineStr">
+        <is>
+          <t>6EcXHcgmJSo</t>
+        </is>
+      </c>
+      <c r="K575" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20T01:04:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　個人的に好きな技モーション武器種別N.o1を一挙公開</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>武器種別ごとに好きな技モーションを一挙紹介
+手持ちから各武器1番好きな技をピックアップ
+視聴者にも好きなモーションをコメント募集</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="inlineStr">
+        <is>
+          <t>・お気に入りの技モーションへの愛着を語る企画</t>
+        </is>
+      </c>
+      <c r="F576" s="2" t="inlineStr"/>
+      <c r="G576" s="2" t="inlineStr">
+        <is>
+          <t>・技モーション
+・武器種別
+・お気に入り技紹介</t>
+        </is>
+      </c>
+      <c r="H576" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Z1AbegIatRM</t>
+        </is>
+      </c>
+      <c r="J576" s="2" t="inlineStr">
+        <is>
+          <t>Z1AbegIatRM</t>
+        </is>
+      </c>
+      <c r="K576" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20T01:04:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B577" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C577" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】R 105スローターダガー 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D577" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのR機体の武装アニメShorts
+R 105スローターダガーの武装モーション披露
+短尺でアニメーションを紹介</t>
+        </is>
+      </c>
+      <c r="E577" s="2" t="inlineStr"/>
+      <c r="F577" s="2" t="inlineStr"/>
+      <c r="G577" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・スローターダガー
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H577" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nrAI40wSFzw</t>
+        </is>
+      </c>
+      <c r="J577" s="2" t="inlineStr">
+        <is>
+          <t>nrAI40wSFzw</t>
+        </is>
+      </c>
+      <c r="K577" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20T01:04:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】現環境最高の引き得ガチャ考察★驚愕の11大ガチャランキング天元突破！！！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>計8ガチャ11種を引き得価値でランキング考察
+1位サイバー編は環境を作るオールスターで最強
+リアム・黒エ・クア編も使い道明確で高評価</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="inlineStr">
+        <is>
+          <t>・サイバー編は環境を作る最強で裁判/代々/再来すべて大当たり
+・リアムは陽攻40ヒット級で火力も防御も高く優秀
+・2クアはビクトルの置き物性能が長期戦で必須級
+・黒エは全体16ヒットで火力が伸びる珍しい性能
+・バルテルミのグスタッフが想定より強くメカ全体強化に優秀</t>
+        </is>
+      </c>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>・メロドセロイ編は飛び抜けず全体軽減率が低く避弾するときつい
+・メリサは自身の火力が皆無で今回は刺さらず残念
+・アイナ系はロックエスト50%止まりで物足りない
+・最終後定女(63年)は前週から評価を落とした
+・ロマファレス復刻は内容ほぼ変わらず優先度低め</t>
+        </is>
+      </c>
+      <c r="G578" s="2" t="inlineStr">
+        <is>
+          <t>・11大ガチャランキング
+・引き得考察
+・サイバー編が1位
+・リアム/黒エ評価
+・7.5周年ガチャ</t>
+        </is>
+      </c>
+      <c r="H578" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FuhA5x41aI8</t>
+        </is>
+      </c>
+      <c r="J578" s="2" t="inlineStr">
+        <is>
+          <t>FuhA5x41aI8</t>
+        </is>
+      </c>
+      <c r="K578" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20T01:04:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B579" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C579" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋回廊570階「シグフレイ」を攻略！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>螺旋570階シグフレイ＋手下3体を攻略解説
+4体共通弱点は斬性、術アタッカー編成が理想
+ギミック多数だが把握すれば撃破は可能</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="inlineStr">
+        <is>
+          <t>・共通弱点が斬性で全体火力の斬スタイルが理想
+・7.5周年で有効な術アタッカーを入手可能
+・ギミックを把握すれば撃破は可能</t>
+        </is>
+      </c>
+      <c r="F579" s="2" t="inlineStr">
+        <is>
+          <t>・技攻撃100%カットで術編成必須の縛り
+・シグフレイに技を当てると強化されてしまう
+・奇数ターンに打/突無効のランダムギミックで編成制限
+・手下撃破時に能力アップ解除の反撃あり警戒が必要</t>
+        </is>
+      </c>
+      <c r="G579" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋570階
+・シグフレイ
+・斬属性弱点
+・術師編成
+・コーション対策</t>
+        </is>
+      </c>
+      <c r="H579" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WydC_juBXtg</t>
+        </is>
+      </c>
+      <c r="J579" s="2" t="inlineStr">
+        <is>
+          <t>WydC_juBXtg</t>
+        </is>
+      </c>
+      <c r="K579" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20T01:04:13Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K579"/>
+  <dimension ref="A1:K593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -38604,6 +38604,934 @@
         </is>
       </c>
     </row>
+    <row r="580">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「7.5周年VSドラクエコラボ」トップ層が激変!?6月最新Tier発表!!7.5周年からの環境変化を調査　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年とドラクエコラボでトップ層が激変。
+月刊累計ティアを6月最新版に再整理。
+環境を作れるSSS級スペックが必須に。</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="inlineStr">
+        <is>
+          <t>・西王は優秀な継承持ちで強い
+・リラは5ヒット追撃蓄積が突出
+・デスマシーンは井戸で殲滅できる強さ
+・インセントのエクストラ拡張性は随一
+・全体攻撃環境が後押しで浮上</t>
+        </is>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
+        <is>
+          <t>・単体追撃スタイルは環境から消えつつ
+・古いスタイルは優先度が下がる
+・挑発ステルスは無人島で戦いづらい
+・ミルフィはお仲間に恵まれず微妙</t>
+        </is>
+      </c>
+      <c r="G580" s="2" t="inlineStr">
+        <is>
+          <t>・最新Tier発表
+・7.5周年環境変化
+・継承の優秀さ
+・全体攻撃環境
+・無人島適性</t>
+        </is>
+      </c>
+      <c r="H580" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EXPESURrYyQ</t>
+        </is>
+      </c>
+      <c r="J580" s="2" t="inlineStr">
+        <is>
+          <t>EXPESURrYyQ</t>
+        </is>
+      </c>
+      <c r="K580" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21T01:06:46Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B581" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C581" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　聖王厄：聖王・めがみなしで勝利</t>
+        </is>
+      </c>
+      <c r="D581" s="2" t="inlineStr">
+        <is>
+          <t>アビス王(聖王厄)を聖王・女神なしで攻略。
+アドラ暦みAJサイバターミンのイン寄せ編成。
+運も絡めなんとか勝利。</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンのツイートローズヒールが重要
+・アドラの受けが大きく安定
+・リバイバ副防具で粘れる</t>
+        </is>
+      </c>
+      <c r="F581" s="2" t="inlineStr">
+        <is>
+          <t>・5ターン目が一番きつい
+・インを超えると発狂してきつい
+・運要素が大きい戦い</t>
+        </is>
+      </c>
+      <c r="G581" s="2" t="inlineStr">
+        <is>
+          <t>・聖王厄攻略
+・女神なし編成
+・イン寄せ編成
+・ターミン重要
+・5ターン目が山場</t>
+        </is>
+      </c>
+      <c r="H581" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2zBHMuwuits</t>
+        </is>
+      </c>
+      <c r="J581" s="2" t="inlineStr">
+        <is>
+          <t>2zBHMuwuits</t>
+        </is>
+      </c>
+      <c r="K581" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21T01:06:46Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　螺旋回廊570：討伐　術だけで撃破</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>螺旋570シグフレイを術だけで撃破。
+豪体で低威力技はカット、技攻撃は強化される。
+杖パで6ターン討伐。</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr">
+        <is>
+          <t>・エスパーギャルが圧倒的最高火力
+・大キグリフトでダメージが出る
+・クロエも火力貢献</t>
+        </is>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>・豪体で低威力技は通らない
+・技攻撃でシグフレが強化され危険
+・コーション発動でダメージ量増加
+・緑以外の手下はHPが高い</t>
+        </is>
+      </c>
+      <c r="G582" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋570攻略
+・シグフレイ
+・豪体ギミック
+・術編成
+・デバフ重要</t>
+        </is>
+      </c>
+      <c r="H582" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Y87WVQZcDus</t>
+        </is>
+      </c>
+      <c r="J582" s="2" t="inlineStr">
+        <is>
+          <t>Y87WVQZcDus</t>
+        </is>
+      </c>
+      <c r="K582" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21T01:06:46Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋回廊 570階シグフレイ 手動攻略【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D583" s="2" t="inlineStr">
+        <is>
+          <t>螺旋570シグフレイを手動攻略。
+技がダメカされ術アタッカー主体で挑む。
+暦みの術継承で4ターン撃破。</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="inlineStr">
+        <is>
+          <t>・暦みの術継承が有効
+・ターミンの全体カウンター狙い
+・代々はアビリティが優秀</t>
+        </is>
+      </c>
+      <c r="F583" s="2" t="inlineStr">
+        <is>
+          <t>・技攻撃しすぎでシグフレ強化→大ダメージ
+・裁判は火力出せず空気気味
+・代々のダメージが定期的に通らない</t>
+        </is>
+      </c>
+      <c r="G583" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋570攻略
+・シグフレイ
+・手動攻略
+・術アタッカー
+・技攻撃注意</t>
+        </is>
+      </c>
+      <c r="H583" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B7cImKnmRM0</t>
+        </is>
+      </c>
+      <c r="J583" s="2" t="inlineStr">
+        <is>
+          <t>B7cImKnmRM0</t>
+        </is>
+      </c>
+      <c r="K583" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21T01:06:46Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SRエールストライクガンダム 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSRエールストライクガンダム。
+武装アニメを紹介するShorts動画。</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="inlineStr"/>
+      <c r="F584" s="2" t="inlineStr"/>
+      <c r="G584" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・エールストライク
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H584" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I584" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RLE7AhmujpU</t>
+        </is>
+      </c>
+      <c r="J584" s="2" t="inlineStr">
+        <is>
+          <t>RLE7AhmujpU</t>
+        </is>
+      </c>
+      <c r="K584" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21T01:06:46Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SRソードストライクガンダム 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D585" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSRソードストライクガンダム。
+武装アニメを紹介するShorts動画。</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="inlineStr"/>
+      <c r="F585" s="2" t="inlineStr"/>
+      <c r="G585" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ソードストライク
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H585" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I585" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Z9ekKeIykt8</t>
+        </is>
+      </c>
+      <c r="J585" s="2" t="inlineStr">
+        <is>
+          <t>Z9ekKeIykt8</t>
+        </is>
+      </c>
+      <c r="K585" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21T01:06:46Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B586" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】あのキャラが無双！！螺旋570階3ターンfinish★ギミック解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D586" s="2" t="inlineStr">
+        <is>
+          <t>螺旋570シグフレイを3ターン撃破しギミック解説。
+豪体で低威力技カット、技攻撃でシグフレ強化。
+マナツ術編成でバルテルミが超特攻。</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミが全集中OD5倍で超火力
+・ボルカノのバフで火力が跳ねる
+・ターミンは唯一無二で抜けない
+・自己バフ高く乾燥するキャラは豪体に強い</t>
+        </is>
+      </c>
+      <c r="F586" s="2" t="inlineStr">
+        <is>
+          <t>・AJが使いづらくなってきた
+・威力40ヒット系は豪体で通らない
+・技攻撃でシグフレにワンパンされる</t>
+        </is>
+      </c>
+      <c r="G586" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋570攻略
+・シグフレイ
+・豪体解説
+・バルテルミ特攻
+・3ターン撃破</t>
+        </is>
+      </c>
+      <c r="H586" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I586" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Qd5QmkFiigs</t>
+        </is>
+      </c>
+      <c r="J586" s="2" t="inlineStr">
+        <is>
+          <t>Qd5QmkFiigs</t>
+        </is>
+      </c>
+      <c r="K586" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21T01:06:46Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B587" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】環境支配級変動あり！遂に。最新キャラランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D587" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年ブライダル16人実装で最新キャラランキング。
+AJをトリプルSから引退させる環境変化。
+バルテルミSS、メリッサ/グスタフS判定。</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="inlineStr">
+        <is>
+          <t>・メリッサはサポート特化Sで初心者向き
+・グスタフは全体バフ多くバランス良い
+・メロトセロイ継承で2倍は強烈
+・バルテルミは集団戦で強い</t>
+        </is>
+      </c>
+      <c r="F587" s="2" t="inlineStr">
+        <is>
+          <t>・AJは環境支配ではなくなった
+・プレミエルは確率追撃で運用不安定
+・ハーディは汎用性高くなくA
+・メロトセロイ本体は東京軽減率低い</t>
+        </is>
+      </c>
+      <c r="G587" s="2" t="inlineStr">
+        <is>
+          <t>・最新キャラランキング
+・ブライダル
+・AJ卒業
+・豪体影響
+・全体攻撃環境</t>
+        </is>
+      </c>
+      <c r="H587" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I587" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TWBVZD7z_W0</t>
+        </is>
+      </c>
+      <c r="J587" s="2" t="inlineStr">
+        <is>
+          <t>TWBVZD7z_W0</t>
+        </is>
+      </c>
+      <c r="K587" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21T01:06:46Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B588" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋570攻略中+α😻</t>
+        </is>
+      </c>
+      <c r="D588" s="2" t="inlineStr">
+        <is>
+          <t>生配信で制圧戦の魂アビリティ周回と螺旋570に挑戦。
+シグフレは技も術もカットされ非常に硬い。
+ガチャや雑談を交えた配信回。</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="inlineStr">
+        <is>
+          <t>・黒エの火力はさすがに強い
+・ノエルが強い
+・ターミンのカウンターが効く
+・制圧戦の育成プラスで一気にレベル上げ便利</t>
+        </is>
+      </c>
+      <c r="F588" s="2" t="inlineStr">
+        <is>
+          <t>・シグフレは技も術もカットで卑怯なほど硬い
+・ビーナス未育成で力不足
+・弱体破りされきつい</t>
+        </is>
+      </c>
+      <c r="G588" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋570
+・シグフレイ
+・制圧戦周回
+・魂アビリティ
+・生配信雑談</t>
+        </is>
+      </c>
+      <c r="H588" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I588" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EOc5xRrtaWg</t>
+        </is>
+      </c>
+      <c r="J588" s="2" t="inlineStr">
+        <is>
+          <t>EOc5xRrtaWg</t>
+        </is>
+      </c>
+      <c r="K588" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21T01:06:46Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B589" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C589" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】周回パラダイスはここだ！期間延長で激ウマ周回延長中の制圧戦を解説【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D589" s="2" t="inlineStr">
+        <is>
+          <t>期間延長中の制圧戦周回パラダイスを解説。
+ミルザアビスが2ターン全滅周回で最適。
+育成枠あり/なし4パターンの編成を紹介。</t>
+        </is>
+      </c>
+      <c r="E589" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザアビスは2ターン全滅で美味しい
+・ビクトールはレイドで大活躍
+・魂アビリティが無限にひらめく
+・育成枠2でも記憶/自動再戦両対応で効率的</t>
+        </is>
+      </c>
+      <c r="F589" s="2" t="inlineStr">
+        <is>
+          <t>・ソウルピースが高価でレベルは詰まる
+・育成枠なし最速はリタマラが面倒
+・ビクトールなしだとタイム犠牲</t>
+        </is>
+      </c>
+      <c r="G589" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦周回
+・周回パラダイス
+・ミルザアビス
+・育成枠編成
+・ビクトール</t>
+        </is>
+      </c>
+      <c r="H589" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DUwMAOCdfWM</t>
+        </is>
+      </c>
+      <c r="J589" s="2" t="inlineStr">
+        <is>
+          <t>DUwMAOCdfWM</t>
+        </is>
+      </c>
+      <c r="K589" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21T01:06:46Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B590" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C590" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはり新キャラに大活躍キャラ有り！螺旋回廊570階に挑戦！！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D590" s="2" t="inlineStr">
+        <is>
+          <t>螺旋570シグフレイ初日に挑戦。
+シグフレと盾持ち手下は技攻撃が一切通らず術必須。
+西王アビスの軽減ゲーで5ターン撃破。</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="inlineStr">
+        <is>
+          <t>・エスパーギャルが大活躍で最高火力
+・黒エ編ガチャは当たりで強い
+・ターミンは3ヶ月前でも未だ強い
+・サイバーはサポート能力高くポテンシャル◎
+・西王アビスがいれば被弾0の塗りゲー</t>
+        </is>
+      </c>
+      <c r="F590" s="2" t="inlineStr">
+        <is>
+          <t>・技オンリー編成では100%勝てない
+・ボスへの技攻撃は強化されるので厳禁
+・音を倒しすぎると弱体破りを使われる疑い
+・黒エは打属性無効化されると0ダメージ</t>
+        </is>
+      </c>
+      <c r="G590" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋570攻略
+・シグフレイ
+・術編成必須
+・西王アビス軽減
+・インパ</t>
+        </is>
+      </c>
+      <c r="H590" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Lf92ivNh55Q</t>
+        </is>
+      </c>
+      <c r="J590" s="2" t="inlineStr">
+        <is>
+          <t>Lf92ivNh55Q</t>
+        </is>
+      </c>
+      <c r="K590" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21T01:07:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B591" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C591" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】結局誰を取るべき？7.5周年セレチケ当たりキャラ完全解説！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D591" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年セレチケのおすすめ交換候補を独断で解説。
+無人島で活躍するキャラ中心、2025年実装を推奨。
+本人はバレンタインメロトセロイ予定。</t>
+        </is>
+      </c>
+      <c r="E591" s="2" t="inlineStr">
+        <is>
+          <t>・バレンタインメロトセロイは全体状態異常回復で無人島◎
+・ファティマはサポート能力が高い
+・女神アカネサスは火力デバフ強力
+・キハチは周回性能が高い
+・メカは消費BP減少で今も使える</t>
+        </is>
+      </c>
+      <c r="F591" s="2" t="inlineStr">
+        <is>
+          <t>・2024年以前は恒常交換所で入手可で優先度低
+・リラは置物用途減り優先度低
+・旧ビューネは最新に適正で見劣り</t>
+        </is>
+      </c>
+      <c r="G591" s="2" t="inlineStr">
+        <is>
+          <t>・セレチケ交換
+・おすすめ候補
+・無人島適性
+・継承用キャラ
+・2025年キャラ推奨</t>
+        </is>
+      </c>
+      <c r="H591" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I591" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wgaTU6pkbfM</t>
+        </is>
+      </c>
+      <c r="J591" s="2" t="inlineStr">
+        <is>
+          <t>wgaTU6pkbfM</t>
+        </is>
+      </c>
+      <c r="K591" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21T01:06:46Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B592" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】⭐️初実装⭐️ ~第125回 カン＝ケルゥの井 ~キャラ徹底考察 ~✨強敵井戸を堪能しよう✨</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="inlineStr">
+        <is>
+          <t>第125回カン=ケルゥの井戸を実装前に徹底考察。
+突属性と雷弱点、術強化が挑戦の置き手。
+毒対策に回避キャラが必須。</t>
+        </is>
+      </c>
+      <c r="E592" s="2" t="inlineStr">
+        <is>
+          <t>・サライグラキエスは弱点取れ4Sウィーク1.75倍
+・ビクトールは単体人権アタッカー
+・リアムは雷弱点41連打で刺さる
+・雪だるまはフォース2.5倍サポート</t>
+        </is>
+      </c>
+      <c r="F592" s="2" t="inlineStr">
+        <is>
+          <t>・ダメブロでは毒をカットできない
+・アレツは時代が終わりつつある
+・木ハは手数少なくサブ止まり
+・毒3人で発狂6連が脅威</t>
+        </is>
+      </c>
+      <c r="G592" s="2" t="inlineStr">
+        <is>
+          <t>・カンケルゥの井戸
+・突属性置き手
+・雷弱点
+・毒対策
+・ベスト編成予想</t>
+        </is>
+      </c>
+      <c r="H592" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I592" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=V8yG1AQzwa4</t>
+        </is>
+      </c>
+      <c r="J592" s="2" t="inlineStr">
+        <is>
+          <t>V8yG1AQzwa4</t>
+        </is>
+      </c>
+      <c r="K592" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21T01:06:46Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B593" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C593" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年記念ロマンシングブライドを考察する配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D593" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年ブライダルガチャ6体を生配信考察。
+メロトセロイ本体はC評価だが継承は価値あり。
+全体的に控えめなガチャ評価。</t>
+        </is>
+      </c>
+      <c r="E593" s="2" t="inlineStr">
+        <is>
+          <t>・メリッサはOD/BP/火ダメ軽減の3役で硬い
+・グスタフは全体バフ高くバランス型
+・暦みは絶対引くべき便利キャラ
+・ハーディは関節で追撃ストック刺されば強い</t>
+        </is>
+      </c>
+      <c r="F593" s="2" t="inlineStr">
+        <is>
+          <t>・メロトセロイ本体は爆裂弱く継承前提
+・プレミエルは確率多すぎ下ぶれ弱い
+・バルテルミはドライブチェインなく致命的
+・今回ガチャは全体的に控えめ</t>
+        </is>
+      </c>
+      <c r="G593" s="2" t="inlineStr">
+        <is>
+          <t>・ブライダルガチャ考察
+・メロトセロイC評価
+・バルテルミ
+・プレミエル
+・継承価値</t>
+        </is>
+      </c>
+      <c r="H593" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I593" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UHakNSS46pY</t>
+        </is>
+      </c>
+      <c r="J593" s="2" t="inlineStr">
+        <is>
+          <t>UHakNSS46pY</t>
+        </is>
+      </c>
+      <c r="K593" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21T01:06:46Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K593"/>
+  <dimension ref="A1:K600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39532,6 +39532,473 @@
         </is>
       </c>
     </row>
+    <row r="594">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B594" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年「ラストガチャ」シルエットクイズ!?あのシリーズのキャラたちが追加される理由とは　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年ラストガチャの内容をシルエットから予想
+インサガキャラ追加とアデルの父親登場を考察
+父の日シングルガチャの可能性に言及</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="inlineStr"/>
+      <c r="F594" s="2" t="inlineStr">
+        <is>
+          <t>・インサガ発売日記念が告知なく地味に終了</t>
+        </is>
+      </c>
+      <c r="G594" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年ラストガチャ
+・インサガ追加
+・シルエットクイズ
+・父の日
+・シングルガチャ予想</t>
+        </is>
+      </c>
+      <c r="H594" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lf8zvZYgQBk</t>
+        </is>
+      </c>
+      <c r="J594" s="2" t="inlineStr">
+        <is>
+          <t>lf8zvZYgQBk</t>
+        </is>
+      </c>
+      <c r="K594" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22T14:17:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B595" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C595" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】制圧戦雑談周回　HP仮天井まで上げていこう　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D595" s="2" t="inlineStr">
+        <is>
+          <t>制圧戦を周回しながら雑談配信
+7.5周年ガチャのおすすめランキングを作成
+各スタイルの強さや使い所を視聴者と議論</t>
+        </is>
+      </c>
+      <c r="E595" s="2" t="inlineStr">
+        <is>
+          <t>・サイバーは確保しておきたい高性能
+・ダリオが扱いやすく良かった
+・ターミンは今でも強い
+・グスタフは井戸でスコア99万の大活躍
+・ハーディも刺されば面白い性能</t>
+        </is>
+      </c>
+      <c r="F595" s="2" t="inlineStr">
+        <is>
+          <t>・プルミエルのタンク性能は不要との声
+・メロセロイは火力が出ない
+・バルテルミは編成難易度が高め</t>
+        </is>
+      </c>
+      <c r="G595" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦周回
+・ガチャランキング
+・スタイル評価
+・雑談配信
+・継承</t>
+        </is>
+      </c>
+      <c r="H595" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I595" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=43rwEh_H8ZE</t>
+        </is>
+      </c>
+      <c r="J595" s="2" t="inlineStr">
+        <is>
+          <t>43rwEh_H8ZE</t>
+        </is>
+      </c>
+      <c r="K595" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22T14:17:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】63連ガチャ最終結論交換優先度ここに決着【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D596" s="2" t="inlineStr">
+        <is>
+          <t>63連ガチャの天井交換優先度を最終結論
+トリプルS級は最終皇帝とミド君が筆頭
+7.5周年最後まで待ってから交換すべき</t>
+        </is>
+      </c>
+      <c r="E596" s="2" t="inlineStr">
+        <is>
+          <t>・最終皇帝は6連オーバーエンチャントで非常に強い
+・ミド君はタクト継承で技10回超え強力
+・メロセロイは継承込みでダパ最強クラス
+・エミリアは検証で威力が高くおすすめ
+・リアムは40連撃以上が続き優秀</t>
+        </is>
+      </c>
+      <c r="F596" s="2" t="inlineStr">
+        <is>
+          <t>・トリプルS以外は無理に交換しなくていい
+・防御系キャラが飽和し交換価値が悩ましい
+・今すぐ交換せず最後まで待つべき</t>
+        </is>
+      </c>
+      <c r="G596" s="2" t="inlineStr">
+        <is>
+          <t>・天井交換優先度
+・最終皇帝
+・ミド君
+・メロセロイ継承
+・SS評価</t>
+        </is>
+      </c>
+      <c r="H596" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I596" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8a6JwQD4wd8</t>
+        </is>
+      </c>
+      <c r="J596" s="2" t="inlineStr">
+        <is>
+          <t>8a6JwQD4wd8</t>
+        </is>
+      </c>
+      <c r="K596" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22T14:17:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B597" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C597" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ここに来て最優先に追加発生！新ガチャ確保優先度ランキング【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D597" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年29スタイルから確保優先度ランキング
+最優先はサイバー暦みヴィンセントに代々が追加
+優先度高はトゥクアイ・リアム・サライ等</t>
+        </is>
+      </c>
+      <c r="E597" s="2" t="inlineStr">
+        <is>
+          <t>・サイバーは環境を作る高スペックで最優先
+・暦みはどこでも強く螺旋でも活躍
+・代々は火ダメ軽減トップで最優先に昇格
+・サライは火力が高くレイドでも使える
+・リアムは継承込みでトップレベル火力</t>
+        </is>
+      </c>
+      <c r="F597" s="2" t="inlineStr">
+        <is>
+          <t>・トゥクアイはビクトールセット前提で単体火力は控えめ
+・ラゼムはバルテルミ登場で優先度中に降格</t>
+        </is>
+      </c>
+      <c r="G597" s="2" t="inlineStr">
+        <is>
+          <t>・確保優先度ランキング
+・サイバー最優先
+・代々の評価上昇
+・ロマンシングブライド
+・継承</t>
+        </is>
+      </c>
+      <c r="H597" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I597" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=178AEI3NTig</t>
+        </is>
+      </c>
+      <c r="J597" s="2" t="inlineStr">
+        <is>
+          <t>178AEI3NTig</t>
+        </is>
+      </c>
+      <c r="K597" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22T14:17:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B598" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C598" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】知らないと後悔します！7.5周年期間中にでやるべきこと徹底解説【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D598" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年期間中の期限付きタスクを注意喚起
+タクト討伐や各ミッションで計1万超のジュエル
+超進化忘れやパネル交換所の見落としに注意</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="inlineStr">
+        <is>
+          <t>・ストーリー応援で3000ジュエル等報酬が豪華
+・記念クエスト+パネル交換で4000ジュエル以上
+・ジュエルセールはかなりお得な価格</t>
+        </is>
+      </c>
+      <c r="F598" s="2" t="inlineStr">
+        <is>
+          <t>・超進化ミッションは忘れやすく5000ジュエル取り逃し注意
+・パネル交換所は場所が分かりにくく見落としやすい
+・ジュエルセール両方買うと12万で高い</t>
+        </is>
+      </c>
+      <c r="G598" s="2" t="inlineStr">
+        <is>
+          <t>・期限切れ注意
+・ジュエル回収
+・ミッション
+・パネル交換所
+・ジュエルセール</t>
+        </is>
+      </c>
+      <c r="H598" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZHTR2tiMUR8</t>
+        </is>
+      </c>
+      <c r="J598" s="2" t="inlineStr">
+        <is>
+          <t>ZHTR2tiMUR8</t>
+        </is>
+      </c>
+      <c r="K598" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22T14:17:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B599" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C599" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】鋼鉄兵たちの井戸 ~オープンチャット仲間の知恵が集結‼️‼️ ~魅惑の10手編成を紹介 ~（1位の立ち回り動画もあります☺️）</t>
+        </is>
+      </c>
+      <c r="D599" s="2" t="inlineStr">
+        <is>
+          <t>鋼鉄兵たちの井戸のクリア編成を紹介
+オプチャ仲間の知恵を集めた10手編成
+ロックブーケやバルテルミ継承の工夫が光る</t>
+        </is>
+      </c>
+      <c r="E599" s="2" t="inlineStr">
+        <is>
+          <t>・ロックブーケのデバフ継承で手数を3手に削減
+・聖王のマント超進化でBP問題を解消
+・オプチャ仲間の知恵が詰まった良編成</t>
+        </is>
+      </c>
+      <c r="F599" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミは元BPが7不足する欠点</t>
+        </is>
+      </c>
+      <c r="G599" s="2" t="inlineStr">
+        <is>
+          <t>・鋼鉄兵たちの井戸
+・10手編成
+・継承テクニック
+・聖王のマント超進化
+・BP問題解決</t>
+        </is>
+      </c>
+      <c r="H599" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I599" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jMikdW4tFHk</t>
+        </is>
+      </c>
+      <c r="J599" s="2" t="inlineStr">
+        <is>
+          <t>jMikdW4tFHk</t>
+        </is>
+      </c>
+      <c r="K599" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22T14:17:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】2026年6月中旬ガチャ総まとめ！全24スタイル引くべきスタイルランキング！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D600" s="2" t="inlineStr">
+        <is>
+          <t>6月中旬実装ガチャ全24スタイルをティアランク
+Sにヴィンセント追加、代々をAへ格上げ
+ダリオやクロエ等のダークホースも評価</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="inlineStr">
+        <is>
+          <t>・ヴィンセントは味方ダメージ最大2.5倍の強サポーター
+・代々は環境に刺さり火ダメ87%軽減で高難度向き
+・ダリオは倍率2.75倍で高難易度に強い
+・クロエは高火力の全体アタッカー
+・グスタフはバランス型で熱アタッカーとして有望</t>
+        </is>
+      </c>
+      <c r="F600" s="2" t="inlineStr">
+        <is>
+          <t>・ヴィンセントは扱いが難しく新規向けではない
+・ダリオは現状活躍機会が乏しい
+・バルテルミは扱いづらく火問武器が持てない
+・メロセロイはキャラパワーが低くアタッカー性能不足</t>
+        </is>
+      </c>
+      <c r="G600" s="2" t="inlineStr">
+        <is>
+          <t>・6月中旬ティアランク
+・ヴィンセントS評価
+・代々A格上げ
+・ダークホース
+・継承評価</t>
+        </is>
+      </c>
+      <c r="H600" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=naTkJB-VM0s</t>
+        </is>
+      </c>
+      <c r="J600" s="2" t="inlineStr">
+        <is>
+          <t>naTkJB-VM0s</t>
+        </is>
+      </c>
+      <c r="K600" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22T14:17:35Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K600"/>
+  <dimension ref="A1:K606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39999,6 +39999,396 @@
         </is>
       </c>
     </row>
+    <row r="601">
+      <c r="A601" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B601" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C601" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　トゥ・クアイVSこよみ　光と厄の頂上決戦　まさかの結果...最強対決</t>
+        </is>
+      </c>
+      <c r="D601" s="2" t="inlineStr">
+        <is>
+          <t>ツクアイとこよみの火力を同条件で比較検証。
+こよみ(暦み)が圧倒的火力で軍配。
+ツクアイは技3ならメインアタッカー級。</t>
+        </is>
+      </c>
+      <c r="E601" s="2" t="inlineStr">
+        <is>
+          <t>・こよみは一撃が重く圧倒的火力
+・ツクアイ技3はメインアタッカーで4億超え
+・ツクアイのサポート(残つ用補助)は優秀</t>
+        </is>
+      </c>
+      <c r="F601" s="2" t="inlineStr">
+        <is>
+          <t>・ツクアイ技2は火力微妙でサブアタッカー級
+・ツクアイは立ち上がりが弱い
+・妖属性を揃えないと火力が厳しい</t>
+        </is>
+      </c>
+      <c r="G601" s="2" t="inlineStr">
+        <is>
+          <t>・ツクアイ検証
+・こよみ比較
+・火力対決
+・妖属性
+・技3運用</t>
+        </is>
+      </c>
+      <c r="H601" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I601" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OWpmHg5jgGg</t>
+        </is>
+      </c>
+      <c r="J601" s="2" t="inlineStr">
+        <is>
+          <t>OWpmHg5jgGg</t>
+        </is>
+      </c>
+      <c r="K601" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T01:06:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ここに来て完全新キャラ降臨の予感！？7.5周年第5弾の内容を予想した結果がやば過ぎた...【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D602" s="2" t="inlineStr">
+        <is>
+          <t>6/24実装の7.5周年第5弾ガチャを予想。
+梅雨にちなみ「バ有前線」シングルガチャと予想。
+リズ・テス・レインの3体を本命に挙げる。</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="inlineStr">
+        <is>
+          <t>・リズは久しく来ておらず実装に期待</t>
+        </is>
+      </c>
+      <c r="F602" s="2" t="inlineStr">
+        <is>
+          <t>・第4弾ロマンシングブライドはストーリーが薄味</t>
+        </is>
+      </c>
+      <c r="G602" s="2" t="inlineStr">
+        <is>
+          <t>・第5弾予想
+・6/24ガチャ
+・梅雨ガチャ
+・リズ/テス予想
+・レイン予想</t>
+        </is>
+      </c>
+      <c r="H602" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0ZJU1L2u2Us</t>
+        </is>
+      </c>
+      <c r="J602" s="2" t="inlineStr">
+        <is>
+          <t>0ZJU1L2u2Us</t>
+        </is>
+      </c>
+      <c r="K602" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T01:06:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B603" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第125回~カン＝ケルゥの井戸🌟攻略🌟~これを見れば貴方も💡100位以内💡 ~全てお見せ致します</t>
+        </is>
+      </c>
+      <c r="D603" s="2" t="inlineStr">
+        <is>
+          <t>カン＝ケルゥの井戸の100位以内向け攻略。
+サイバ軸の自作31手編成を紹介。
+2ターン目にODぶっぱする戦法。</t>
+        </is>
+      </c>
+      <c r="E603" s="2" t="inlineStr">
+        <is>
+          <t>・31手で50〜100位に入れる</t>
+        </is>
+      </c>
+      <c r="F603" s="2" t="inlineStr">
+        <is>
+          <t>・23手より上は思い浮かばない難しい編成</t>
+        </is>
+      </c>
+      <c r="G603" s="2" t="inlineStr">
+        <is>
+          <t>・カン＝ケルゥの井戸
+・31手編成
+・ランキング100位
+・OD2ターン目ぶっぱ
+・サイバ軸</t>
+        </is>
+      </c>
+      <c r="H603" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I603" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DBzGz8j1M8s</t>
+        </is>
+      </c>
+      <c r="J603" s="2" t="inlineStr">
+        <is>
+          <t>DBzGz8j1M8s</t>
+        </is>
+      </c>
+      <c r="K603" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T01:06:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B604" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第123回シルバードラゴンの井戸〜‼️攻略‼️目指せ！！100位</t>
+        </is>
+      </c>
+      <c r="D604" s="2" t="inlineStr">
+        <is>
+          <t>シルバードラゴンの井戸の100位狙い攻略。
+マイス先制バフで手軽に火力を出す編成。
+仲間の助言で19手→16手に短縮。</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="inlineStr">
+        <is>
+          <t>・マイス先制バフで手軽に火力が出る
+・攻略を話せる仲間コミュが有意義</t>
+        </is>
+      </c>
+      <c r="F604" s="2" t="inlineStr">
+        <is>
+          <t>・トップとはかなり点差がある</t>
+        </is>
+      </c>
+      <c r="G604" s="2" t="inlineStr">
+        <is>
+          <t>・シルバードラゴンの井戸
+・マイス先制バフ
+・16手
+・100位以内
+・攻略コミュ</t>
+        </is>
+      </c>
+      <c r="H604" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I604" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yWnVKQ0fbFI</t>
+        </is>
+      </c>
+      <c r="J604" s="2" t="inlineStr">
+        <is>
+          <t>yWnVKQ0fbFI</t>
+        </is>
+      </c>
+      <c r="K604" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T01:06:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B605" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C605" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【ガチャ動画】GB来たので俺は行きます【No.613】</t>
+        </is>
+      </c>
+      <c r="D605" s="2" t="inlineStr">
+        <is>
+          <t>黒エ/ダリオ編をエスパーギャル狙いでガチャ実況。
+天井でロモク確保など近況を雑談報告。
+後半クロエや小林姉さんを引き当てる。</t>
+        </is>
+      </c>
+      <c r="E605" s="2" t="inlineStr">
+        <is>
+          <t>・エスパーギャルはイラストが綺麗
+・クロエが来てくれて嬉しい</t>
+        </is>
+      </c>
+      <c r="F605" s="2" t="inlineStr">
+        <is>
+          <t>・最近ガチャの頻度が早く多い</t>
+        </is>
+      </c>
+      <c r="G605" s="2" t="inlineStr">
+        <is>
+          <t>・GBガチャ実況
+・エスパーギャル狙い
+・黒エ/ダリオ編
+・天井
+・雑談</t>
+        </is>
+      </c>
+      <c r="H605" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I605" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=O-3nmdoKfn0</t>
+        </is>
+      </c>
+      <c r="J605" s="2" t="inlineStr">
+        <is>
+          <t>O-3nmdoKfn0</t>
+        </is>
+      </c>
+      <c r="K605" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T01:06:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B606" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C606" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「トゥ・クアイ 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D606" s="2" t="inlineStr">
+        <is>
+          <t>ツクアイ編ガチャのスタイル性能を考察。
+ツクアイB+、オルレッドB、ラゼムを評価。
+残つ用サポートやOD周りの強みを分析。</t>
+        </is>
+      </c>
+      <c r="E606" s="2" t="inlineStr">
+        <is>
+          <t>・ツクアイ技3は40ヒットの強力アタッカー
+・ツクアイの残つ用1.75倍サポートが凶悪
+・オルレッドのODゲージ上昇が強くデバッファー優秀
+・ラゼムのODエクストラフォース付与が強力</t>
+        </is>
+      </c>
+      <c r="F606" s="2" t="inlineStr">
+        <is>
+          <t>・ツクアイは使用5回制限と余ダメ低下が難点
+・ツクアイの火ダメ30%軽減は頼りない
+・オルレッドは打/熱縛りで軽減率も低い
+・ラゼムは消費BP重く全体BP+5のデメリット</t>
+        </is>
+      </c>
+      <c r="G606" s="2" t="inlineStr">
+        <is>
+          <t>・ツクアイ考察
+・オルレッド考察
+・ラゼム考察
+・残つ用サポート
+・ランク付け</t>
+        </is>
+      </c>
+      <c r="H606" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I606" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5Zjkt8jKz7A</t>
+        </is>
+      </c>
+      <c r="J606" s="2" t="inlineStr">
+        <is>
+          <t>5Zjkt8jKz7A</t>
+        </is>
+      </c>
+      <c r="K606" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23T01:06:32Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K606"/>
+  <dimension ref="A1:K611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40389,6 +40389,326 @@
         </is>
       </c>
     </row>
+    <row r="607">
+      <c r="A607" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B607" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C607" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】水着前倒しからの「FFコラボ」の気配…!!その理由は!?眼福水着に見とれてる場合じゃないぞ!!おしらせ読んでいこう　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D607" s="2" t="inlineStr">
+        <is>
+          <t>ハーフアニバ後に単発水着ガチャが異例の前倒し登場。
+来週の生放送でFFコラボ告知の気配と予想。
+ラグナの水鉄砲・運の無人島など今後の予定を整理。</t>
+        </is>
+      </c>
+      <c r="E607" s="2" t="inlineStr">
+        <is>
+          <t>・例年にない水着前倒しでFFコラボへの期待が高まる
+・水着スタイルは眼福で楽しみ</t>
+        </is>
+      </c>
+      <c r="F607" s="2" t="inlineStr">
+        <is>
+          <t>・単発イベントは報酬がほぼなし
+・人間女の連達性能はいまいちそう
+・無人島の塔破壊回数は人により差が出そう</t>
+        </is>
+      </c>
+      <c r="G607" s="2" t="inlineStr">
+        <is>
+          <t>・水着前倒し
+・FFコラボ予感
+・ラグナの水鉄砲
+・運の無人島
+・生放送告知</t>
+        </is>
+      </c>
+      <c r="H607" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I607" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DB5RFVZd34Y</t>
+        </is>
+      </c>
+      <c r="J607" s="2" t="inlineStr">
+        <is>
+          <t>DB5RFVZd34Y</t>
+        </is>
+      </c>
+      <c r="K607" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T01:03:42.863786+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B608" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C608" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】う～ん、でかい。 6月24日更新情報まとめ 【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D608" s="2" t="inlineStr">
+        <is>
+          <t>6/24開始のロマンシングバカンス2026の更新情報まとめ。
+人間女・ネメシス・カの新Sスタイルがシングルガチャで登場。
+ラグナの水鉄砲・運の無人島第5回・星に願いログボを紹介。</t>
+        </is>
+      </c>
+      <c r="E608" s="2" t="inlineStr">
+        <is>
+          <t>・人間女のイラストが個人的に刺さり追っかけたい
+・HP成長目安が5240に上がり育成に良い
+・無人島チャレンジで最大1500ジュエル等もらえる</t>
+        </is>
+      </c>
+      <c r="F608" s="2" t="inlineStr">
+        <is>
+          <t>・星に願いログボの仕組みが分かりにくい
+・結局どっちもジュエル一択になりそう</t>
+        </is>
+      </c>
+      <c r="G608" s="2" t="inlineStr">
+        <is>
+          <t>・バカンス2026
+・シングルガチャ
+・人間女
+・運の無人島
+・星に願いログボ
+・HP5240</t>
+        </is>
+      </c>
+      <c r="H608" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I608" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5yCqaF_i2UM</t>
+        </is>
+      </c>
+      <c r="J608" s="2" t="inlineStr">
+        <is>
+          <t>5yCqaF_i2UM</t>
+        </is>
+      </c>
+      <c r="K608" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T01:03:42.863786+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B609" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C609" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】Rバスターガンダム 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D609" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのRバスターガンダム武装アニメShort。
+セリフ付きで武装演出を短く紹介する動画。
+ロマサガRS以外のゲーム関連ショート投稿。</t>
+        </is>
+      </c>
+      <c r="E609" s="2" t="inlineStr"/>
+      <c r="F609" s="2" t="inlineStr"/>
+      <c r="G609" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・Rバスターガンダム
+・武装アニメ
+・Short</t>
+        </is>
+      </c>
+      <c r="H609" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I609" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A-OAfW_gZIM</t>
+        </is>
+      </c>
+      <c r="J609" s="2" t="inlineStr">
+        <is>
+          <t>A-OAfW_gZIM</t>
+        </is>
+      </c>
+      <c r="K609" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T01:03:42.863786+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B610" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C610" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】衝撃の情報がやってきた！6月最後はまさかのフライング水着ガチャ【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D610" s="2" t="inlineStr">
+        <is>
+          <t>6月最後に異例のフライング水着ガチャが告知され衝撃。
+人間女・ネメシス・カのGBキャラ水着Sスタイルが登場。
+ネメシス新スタイルは無人島特攻の可能性を予想。</t>
+        </is>
+      </c>
+      <c r="E610" s="2" t="inlineStr">
+        <is>
+          <t>・水着ガチャは毎年の夏の楽しみで嬉しい
+・GB（ゲームボーイ）サガのキャラは人気で訴求力大
+・ネメシス新スタイルが無人島特攻なら面白い</t>
+        </is>
+      </c>
+      <c r="F610" s="2" t="inlineStr">
+        <is>
+          <t>・水着ならダブルで来てほしかったがシングルで残念
+・予想動画は0正解で大惨敗
+・次ガチャが7/2の4時締切で寝落ち注意</t>
+        </is>
+      </c>
+      <c r="G610" s="2" t="inlineStr">
+        <is>
+          <t>・フライング水着ガチャ
+・人間女
+・ネメシス
+・運の無人島
+・7.5周年表記消滅
+・予想動画</t>
+        </is>
+      </c>
+      <c r="H610" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I610" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XmbTFgF13Yk</t>
+        </is>
+      </c>
+      <c r="J610" s="2" t="inlineStr">
+        <is>
+          <t>XmbTFgF13Yk</t>
+        </is>
+      </c>
+      <c r="K610" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T01:03:42.863786+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B611" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C611" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【ガチャ動画】花嫁(花婿)お迎えしたく・・・！！【No.616】</t>
+        </is>
+      </c>
+      <c r="D611" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年記念ロマンシングブライドのガチャ動画。
+2人で10連ずつメロディ・ハーディ狙いに挑戦。
+こ太君が10連でハーディを引き当て好結果。</t>
+        </is>
+      </c>
+      <c r="E611" s="2" t="inlineStr">
+        <is>
+          <t>・こ太君が10回でハーディを引けて良い引き
+・欲しいキャラがいる時は引いておく方針に納得</t>
+        </is>
+      </c>
+      <c r="F611" s="2" t="inlineStr">
+        <is>
+          <t>・ジュエルに余裕がなく天井まで回せない
+・ターコはメロディ狙いが出ず残念</t>
+        </is>
+      </c>
+      <c r="G611" s="2" t="inlineStr">
+        <is>
+          <t>・ロマンシングブライド
+・花嫁花婿ガチャ
+・10連
+・ハーディ
+・7.5周年</t>
+        </is>
+      </c>
+      <c r="H611" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I611" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ugnz8ZbzbRU</t>
+        </is>
+      </c>
+      <c r="J611" s="2" t="inlineStr">
+        <is>
+          <t>Ugnz8ZbzbRU</t>
+        </is>
+      </c>
+      <c r="K611" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T01:03:42.863786+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K611"/>
+  <dimension ref="A1:K623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40709,6 +40709,810 @@
         </is>
       </c>
     </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「リラをアプデ」EX4.5倍にんげんおんな!!サポートこなしながら無尽塔にも対応する回避とは!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D612" s="2" t="inlineStr">
+        <is>
+          <t>人間女はEX4.5倍のリラ型アタッカー兼サポ
+高難度S総合A、火力伸ばしたリラだが半端
+無人島で回避1回を付与しつつ戦える</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="inlineStr">
+        <is>
+          <t>・火力が高くEX最大4.5倍まで伸びる
+・継承が自己完結できるバランス
+・マイターン回避1回で粘れる
+・無人島適正を持たせられる</t>
+        </is>
+      </c>
+      <c r="F612" s="2" t="inlineStr">
+        <is>
+          <t>・ジェラールやリラの劣化版で半端
+・味方サポートが400%のみで控えめ
+・似た技が多くレポン(売り)がない
+・既存リラ持ちには必要性が薄い</t>
+        </is>
+      </c>
+      <c r="G612" s="2" t="inlineStr">
+        <is>
+          <t>・人間女
+・リラ型
+・EX4.5倍
+・無人島回避
+・高難度S</t>
+        </is>
+      </c>
+      <c r="H612" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I612" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D09fxa65dts</t>
+        </is>
+      </c>
+      <c r="J612" s="2" t="inlineStr">
+        <is>
+          <t>D09fxa65dts</t>
+        </is>
+      </c>
+      <c r="K612" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T01:08:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B613" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C613" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】晩成「最強置物」34連打しつつの最大火力サポートのカイ!!防防御が100%に迫る!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D613" s="2" t="inlineStr">
+        <is>
+          <t>カイは晩成型の最強置物サポーター
+全ステバフ770%・防御96%を継続できる
+高難度SS総合SS、無人島向けの良スタイル</t>
+        </is>
+      </c>
+      <c r="E613" s="2" t="inlineStr">
+        <is>
+          <t>・全ステバフ770%を継続してばら撒ける
+・防御96%まで上がり守りが堅い
+・HP/BP自動回復で自己完結
+・アタッカー兼用で本人火力も高い</t>
+        </is>
+      </c>
+      <c r="F613" s="2" t="inlineStr">
+        <is>
+          <t>・スロースタートで5ターンまで弱い
+・ダメブロやウェポンが少ない
+・強さが長期戦・無人島に限定的
+・無人島をやらないなら不要</t>
+        </is>
+      </c>
+      <c r="G613" s="2" t="inlineStr">
+        <is>
+          <t>・カイ
+・置物サポ
+・防御96%
+・全ステバフ770%
+・無人島</t>
+        </is>
+      </c>
+      <c r="H613" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WCecacbN6Fo</t>
+        </is>
+      </c>
+      <c r="J613" s="2" t="inlineStr">
+        <is>
+          <t>WCecacbN6Fo</t>
+        </is>
+      </c>
+      <c r="K613" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T01:08:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B614" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C614" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】3体ランク付!!「超強化」ネメシスの先代互換性は!?超詳細に使い勝手を考えつつほか2体も並べて評価!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D614" s="2" t="inlineStr">
+        <is>
+          <t>ネメシスは追撃28ヒットの無人島アタッカー
+EXがなく立ち上がりは絶望的に弱い
+高難度特攻SS総合B、仙台継承が確実</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="inlineStr">
+        <is>
+          <t>・ジャッジメントシャドウ継承で火力抜群
+・追撃28ヒットで討伐ターンを短縮
+・無人島の状況が確実に好転する
+・仙台に技継承して純粋強化もできる</t>
+        </is>
+      </c>
+      <c r="F614" s="2" t="inlineStr">
+        <is>
+          <t>・EXがなく立ち上がりが絶望的に弱い
+・仙台の1ターン回避を失った
+・長期戦の無人島以外で出番がない
+・螺旋や討伐ではまず使わない</t>
+        </is>
+      </c>
+      <c r="G614" s="2" t="inlineStr">
+        <is>
+          <t>・ネメシス
+・追撃28ヒット
+・ジャッジメントシャドウ
+・無人島
+・総合B</t>
+        </is>
+      </c>
+      <c r="H614" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bvpDLNqRBz4</t>
+        </is>
+      </c>
+      <c r="J614" s="2" t="inlineStr">
+        <is>
+          <t>bvpDLNqRBz4</t>
+        </is>
+      </c>
+      <c r="K614" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T01:08:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B615" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C615" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】F91ステージ参戦！ロードマップ生配信まとめ 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D615" s="2" t="inlineStr">
+        <is>
+          <t>F91ステージが6月末追加、同時ガチャも開催
+新イベント・新作品多数とダイヤ配布
+エターナルパス2やDMM版配信も発表</t>
+        </is>
+      </c>
+      <c r="E615" s="2" t="inlineStr">
+        <is>
+          <t>・1000ダイヤや900万DL記念パックを配布
+・F91・ガンダムW等の新ステージ多数追加
+・イフストーリーで展開の幅が無限
+・エターナルパス2でコミック読み放題</t>
+        </is>
+      </c>
+      <c r="F615" s="2" t="inlineStr">
+        <is>
+          <t>・各イベント期間が連続せず間が空く
+・マップボイスに不具合が発生中
+・F91耐久型のバランス調整(下方修正)
+・エターナルパス2はアニメが見られない</t>
+        </is>
+      </c>
+      <c r="G615" s="2" t="inlineStr">
+        <is>
+          <t>・F91ステージ
+・ロードマップ
+・ガチャ
+・ダイヤ配布
+・エターナルパス2</t>
+        </is>
+      </c>
+      <c r="H615" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I615" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0emnSaW5R0U</t>
+        </is>
+      </c>
+      <c r="J615" s="2" t="inlineStr">
+        <is>
+          <t>0emnSaW5R0U</t>
+        </is>
+      </c>
+      <c r="K615" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T01:08:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B616" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C616" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】う～ん､でかい。にんげんおんなが欲しい！『夏を先取り！ロマンシングバカンス2026 Romancing祭 にんげんおんな編』【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D616" s="2" t="inlineStr">
+        <is>
+          <t>人間女狙いのシングルガチャを50連
+人間女とバーニー(斧)を引けて満足
+FFコラボの可能性は半々と予想</t>
+        </is>
+      </c>
+      <c r="E616" s="2" t="inlineStr">
+        <is>
+          <t>・人間女のイラストが最高で満足
+・お目当ての人間女を引けた
+・貴重な斧のバーニーも当たって嬉しい
+・ダリアスら斧勢が揃って嬉しい</t>
+        </is>
+      </c>
+      <c r="F616" s="2" t="inlineStr">
+        <is>
+          <t>・もう1体欲しいと思うと出ない
+・ステップ7の1/3保証はきつそう</t>
+        </is>
+      </c>
+      <c r="G616" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ
+・人間女
+・バーニー(斧)
+・50連
+・FFコラボ予想</t>
+        </is>
+      </c>
+      <c r="H616" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xUXHixjnsTE</t>
+        </is>
+      </c>
+      <c r="J616" s="2" t="inlineStr">
+        <is>
+          <t>xUXHixjnsTE</t>
+        </is>
+      </c>
+      <c r="K616" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T01:08:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B617" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C617" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】話題のカイ検証！弱点つかなくてもとんでもない結果に・・【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D617" s="2" t="inlineStr">
+        <is>
+          <t>カイを弱点つかずに検証、3ターン目から強い
+ダメージが完体メロセロを超える結果に
+防御90%超で硬く長ラウンドで活躍</t>
+        </is>
+      </c>
+      <c r="E617" s="2" t="inlineStr">
+        <is>
+          <t>・ダメージが完体メロセロを超えるほど強い
+・3ターン目から本気を出せる
+・追撃技が強く回想率も高い
+・防御90%超で非常に硬い</t>
+        </is>
+      </c>
+      <c r="F617" s="2" t="inlineStr">
+        <is>
+          <t>・1〜2ターン目は微妙で弱い
+・弱点をつかないと本領発揮しない
+・現状の螺旋170では出番が少ない
+・刺さる場面が長期戦に限られる</t>
+        </is>
+      </c>
+      <c r="G617" s="2" t="inlineStr">
+        <is>
+          <t>・カイ検証
+・ライ編成
+・追撃
+・防御90%
+・メロセロ比較</t>
+        </is>
+      </c>
+      <c r="H617" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I617" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6Cri240QTQc</t>
+        </is>
+      </c>
+      <c r="J617" s="2" t="inlineStr">
+        <is>
+          <t>6Cri240QTQc</t>
+        </is>
+      </c>
+      <c r="K617" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T01:08:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B618" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C618" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】神速性能確認！にんげんおんな編3人チェック！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D618" s="2" t="inlineStr">
+        <is>
+          <t>人間女・ネメシス・カイを神速で性能確認
+人間女は継承なしだと火力が頭打ち
+カイは硬いが遅く、ネメシスは継承運用前提</t>
+        </is>
+      </c>
+      <c r="E618" s="2" t="inlineStr">
+        <is>
+          <t>・カイは防御90%超で非常に硬い
+・ネメシスはジャッジ継承で火力+ダメブロ
+・人間女は交代相手でもダメージを与えやすい</t>
+        </is>
+      </c>
+      <c r="F618" s="2" t="inlineStr">
+        <is>
+          <t>・人間女は継承なしで火力が頭打ち
+・人間女の味方バフ1.25倍は弱く被る
+・ネメシス本体は無人島で使えずダメブロなし
+・カイは遅く5ターン想定でないと活きない</t>
+        </is>
+      </c>
+      <c r="G618" s="2" t="inlineStr">
+        <is>
+          <t>・人間女
+・ネメシス
+・カイ
+・無人島
+・継承運用</t>
+        </is>
+      </c>
+      <c r="H618" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I618" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DmGxP8CJDgo</t>
+        </is>
+      </c>
+      <c r="J618" s="2" t="inlineStr">
+        <is>
+          <t>DmGxP8CJDgo</t>
+        </is>
+      </c>
+      <c r="K618" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T01:08:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B619" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C619" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ロマンシングバカンス2026ガチャ😻</t>
+        </is>
+      </c>
+      <c r="D619" s="2" t="inlineStr">
+        <is>
+          <t>人間女・カイ・ネメシスをガチャしつつ評価
+カイは5ターン目以降に化ける長期戦特化
+ネメシスは無人島必須も継承運用が前提</t>
+        </is>
+      </c>
+      <c r="E619" s="2" t="inlineStr">
+        <is>
+          <t>・人間女は火力が高く追撃も多い
+・カイは長期戦なら最強クラスで防御も高い
+・ネメシスは無人島必須で貴重な斧枠</t>
+        </is>
+      </c>
+      <c r="F619" s="2" t="inlineStr">
+        <is>
+          <t>・人間女は継承技がなく頭打ちで普通
+・カイは遅くスタンバイ5が長くストレス
+・ネメシス本体はEXなしで回避も失い微妙</t>
+        </is>
+      </c>
+      <c r="G619" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ
+・人間女
+・カイ
+・ネメシス
+・長期戦</t>
+        </is>
+      </c>
+      <c r="H619" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I619" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4xBhG4lsaRY</t>
+        </is>
+      </c>
+      <c r="J619" s="2" t="inlineStr">
+        <is>
+          <t>4xBhG4lsaRY</t>
+        </is>
+      </c>
+      <c r="K619" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T01:08:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B620" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C620" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】最強の高難易度サポーター爆誕！？にんげんおんな編性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D620" s="2" t="inlineStr">
+        <is>
+          <t>人間女・ネメシス・カイ3人を初見性能チェック
+カイは5ターン目以降に最強クラスのサポ
+軽減96%超で全キャラトップの待機慢性型</t>
+        </is>
+      </c>
+      <c r="E620" s="2" t="inlineStr">
+        <is>
+          <t>・カイは軽減96%超で全キャラトップ
+・カイは火力バフもBP配布も化け物級
+・ネメシスは技マシンが優秀で無人島向き
+・人間女は技マシンとしての価値が高い</t>
+        </is>
+      </c>
+      <c r="F620" s="2" t="inlineStr">
+        <is>
+          <t>・カイは開幕1〜2ターンがしょぼい
+・ネメシスはEXが一切なく大きな弱点
+・人間女は置き物性能を失い必須感がない
+・いずれも5ターン目以降や長期戦が前提</t>
+        </is>
+      </c>
+      <c r="G620" s="2" t="inlineStr">
+        <is>
+          <t>・カイ
+・ネメシス
+・人間女
+・軽減96%
+・待機型サポ</t>
+        </is>
+      </c>
+      <c r="H620" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CmsbV6NhSBE</t>
+        </is>
+      </c>
+      <c r="J620" s="2" t="inlineStr">
+        <is>
+          <t>CmsbV6NhSBE</t>
+        </is>
+      </c>
+      <c r="K620" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T01:08:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B621" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C621" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】要注意事項あり！新要素多数のイベントの内容をチェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D621" s="2" t="inlineStr">
+        <is>
+          <t>ラグーナの水鉄砲イベントと星に願いを解説
+交換所が分かりづらく星に願いは要投票
+初見殺しボスは冷属性60ヒットで撃破</t>
+        </is>
+      </c>
+      <c r="E621" s="2" t="inlineStr">
+        <is>
+          <t>・星に願いの報酬は期待値同じで損しない
+・最速11秒周回が可能で効率的
+・初見殺しボスも冷属性60ヒットで簡単撃破</t>
+        </is>
+      </c>
+      <c r="F621" s="2" t="inlineStr">
+        <is>
+          <t>・交換所と星に願いが分かりづらい
+・星に願いは自分用を交換しないと貰えない
+・ボスは初見殺し率100%
+・交換後のイベント周回は意味が薄い</t>
+        </is>
+      </c>
+      <c r="G621" s="2" t="inlineStr">
+        <is>
+          <t>・水鉄砲イベント
+・星に願い
+・周回効率
+・初見殺しボス
+・集圧戦</t>
+        </is>
+      </c>
+      <c r="H621" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=i2fuh-bkG4k</t>
+        </is>
+      </c>
+      <c r="J621" s="2" t="inlineStr">
+        <is>
+          <t>i2fuh-bkG4k</t>
+        </is>
+      </c>
+      <c r="K621" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T01:08:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B622" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C622" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】カイ能力値早見表 ~5ターン目から本領発揮‼️ ~軽減96%回復小BP4フォースweak1.75倍バフ1000以上火力3930</t>
+        </is>
+      </c>
+      <c r="D622" s="2" t="inlineStr">
+        <is>
+          <t>カイの能力値をターン別にまとめた早見表
+5ターン目から軽減96%・火力3930%で本領
+6行動34ヒットでアタッカーとしても優秀</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="inlineStr">
+        <is>
+          <t>・5ターン目以降の軽減96%が脅威的
+・攻撃強化3930%とバフ量が破格
+・毎ターン小回復とBP4も配れる
+・6行動34ヒットでアタッカーも優秀</t>
+        </is>
+      </c>
+      <c r="F622" s="2" t="inlineStr">
+        <is>
+          <t>・前半2ターンは弱い
+・自分の好きな属性には刺さらない</t>
+        </is>
+      </c>
+      <c r="G622" s="2" t="inlineStr">
+        <is>
+          <t>・カイ能力値
+・ターン別性能
+・軽減96%
+・火力3930%
+・高難度</t>
+        </is>
+      </c>
+      <c r="H622" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5cc8QIZDNc8</t>
+        </is>
+      </c>
+      <c r="J622" s="2" t="inlineStr">
+        <is>
+          <t>5cc8QIZDNc8</t>
+        </is>
+      </c>
+      <c r="K622" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T01:08:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B623" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C623" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭にんげんおんな編ガチャ評価 #ロマサガRS #shorts #ガチャ</t>
+        </is>
+      </c>
+      <c r="D623" s="2" t="inlineStr">
+        <is>
+          <t>にんげんおんな編ガチャ評価のショート動画
+字幕が取得できず内容の詳細は不明
+タイトルよりガチャ評価系と推定</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="inlineStr"/>
+      <c r="F623" s="2" t="inlineStr"/>
+      <c r="G623" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ評価
+・にんげんおんな編
+・ショート</t>
+        </is>
+      </c>
+      <c r="H623" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I623" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0er2tHxLCA4</t>
+        </is>
+      </c>
+      <c r="J623" s="2" t="inlineStr">
+        <is>
+          <t>0er2tHxLCA4</t>
+        </is>
+      </c>
+      <c r="K623" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25T01:08:22Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K599"/>
+  <dimension ref="A1:K606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39909,6 +39909,479 @@
         </is>
       </c>
     </row>
+    <row r="600">
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】無尽塔30層「必勝」長期戦!!メタルアルカイザー!!背水無しで精度の高いダメブロ戦立ち回りを構築せよ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D600" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔30層メタルアルカイザーを攻略
+序盤フラワーサンクチュアリでダメブロ安定化
+ビクトル軸＋ネメシス追撃で長期戦を完遂</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="inlineStr">
+        <is>
+          <t>・背水なしでも精度の高いダメブロ立ち回りで安定
+・終盤は敵攻撃がぬるくなり全力オートでOK
+・携帯タイマーで張り付き不要、ゆっくり攻略可能</t>
+        </is>
+      </c>
+      <c r="F600" s="2" t="inlineStr">
+        <is>
+          <t>・全体範囲攻撃が多いターンは横1列のもらい事故に注意
+・序盤2ターンは敵の全体攻撃が多く不安定</t>
+        </is>
+      </c>
+      <c r="G600" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔30層
+・メタルアルカイザー
+・ダメブロ構成
+・フラワーサンクチュアリ
+・ビクトル
+・全力オート</t>
+        </is>
+      </c>
+      <c r="H600" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Pj-VU_c5GDU</t>
+        </is>
+      </c>
+      <c r="J600" s="2" t="inlineStr">
+        <is>
+          <t>Pj-VU_c5GDU</t>
+        </is>
+      </c>
+      <c r="K600" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T01:05:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B601" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C601" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始268日目記録　脅威　果たして２将星は取るべきか？</t>
+        </is>
+      </c>
+      <c r="D601" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣プレイ268日目の進捗報告
+新キャラ10体入手、竜造寺系が大量に集結
+勢力戦・共闘の反省と今後の目標を整理</t>
+        </is>
+      </c>
+      <c r="E601" s="2" t="inlineStr">
+        <is>
+          <t>・別枠イベントがあるのは育成に有効でありがたい
+・長宗我部盛親を1覚醒でき成長を実感
+・立花宗茂は軽減率が高く補填20秒も大きい</t>
+        </is>
+      </c>
+      <c r="F601" s="2" t="inlineStr">
+        <is>
+          <t>・共闘は対応キャラ不足で10位以内が取れない
+・勢力戦は強敵武将の城は取り返され戦力差が無意味
+・オートタイプ不足で小早川を取っても活かしづらい</t>
+        </is>
+      </c>
+      <c r="G601" s="2" t="inlineStr">
+        <is>
+          <t>・信長の野望出陣
+・キャラ入手状況
+・勢力戦
+・共闘
+・開発・神社
+・立花宗茂</t>
+        </is>
+      </c>
+      <c r="H601" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I601" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mSnCkoOApCE</t>
+        </is>
+      </c>
+      <c r="J601" s="2" t="inlineStr">
+        <is>
+          <t>mSnCkoOApCE</t>
+        </is>
+      </c>
+      <c r="K601" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T01:05:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】総決算7.5周年最強キャラランキング★Tier表更新【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D602" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年総決算の最強キャラTier表を更新
+5月実装キャラを卒業させ環境を再整理
+無人島・交代・西王アビリティの環境変化を解説</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="inlineStr">
+        <is>
+          <t>・西王のアビリティが無人島で刺さり環境支配級
+・ビクトルはEX継承で超級・無人島まで万能で残留
+・検証技なしスタイルを従来以上に高評価</t>
+        </is>
+      </c>
+      <c r="F602" s="2" t="inlineStr">
+        <is>
+          <t>・5月実装のAランク勢は威力不足で軒並み卒業
+・ターミンはパワー不足で環境支配級から陥落
+・無人島は交代でバフ消され火力が出にくい</t>
+        </is>
+      </c>
+      <c r="G602" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年Tier表
+・卒業式
+・無人島
+・交代(レアス)
+・西王アビス
+・ビクトル</t>
+        </is>
+      </c>
+      <c r="H602" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5kILob7Vz5E</t>
+        </is>
+      </c>
+      <c r="J602" s="2" t="inlineStr">
+        <is>
+          <t>5kILob7Vz5E</t>
+        </is>
+      </c>
+      <c r="K602" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T01:05:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B603" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】超性能の怪物現る！最新キャラランキング★7.5周年final【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D603" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年final最新キャラランキングを発表
+5月実装キャラ卒業＋意外なキャラも整理
+螺旋・討伐・集会・無人島を同列に評価</t>
+        </is>
+      </c>
+      <c r="E603" s="2" t="inlineStr">
+        <is>
+          <t>・検証技なしスタイルは従来以上に評価アップ
+・ビクトルは見切り回避で無人島でも使え残留
+・西王アビリティが環境支配級で刺さる</t>
+        </is>
+      </c>
+      <c r="F603" s="2" t="inlineStr">
+        <is>
+          <t>・無人島が強いだけでは最強とはしない評価基準
+・ターミンはメスのパワー不足で卒業
+・Aランク勢は威力不足で多数卒業</t>
+        </is>
+      </c>
+      <c r="G603" s="2" t="inlineStr">
+        <is>
+          <t>・最新キャラランキング
+・7.5周年final
+・卒業ルール
+・無人島評価
+・ビクトル
+・ターミン</t>
+        </is>
+      </c>
+      <c r="H603" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I603" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=t0aLk4diRYk</t>
+        </is>
+      </c>
+      <c r="J603" s="2" t="inlineStr">
+        <is>
+          <t>t0aLk4diRYk</t>
+        </is>
+      </c>
+      <c r="K603" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T01:05:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B604" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】本当に申し訳ありませんでした！水着ガチャ対決＃3浦田優編【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D604" s="2" t="inlineStr">
+        <is>
+          <t>男3人による水着ガチャ対決の最終戦
+浦田の録画ミスで罰ゲーム(青汁)を実施
+新グループ名「ガムシャラ3」を提案</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="inlineStr">
+        <is>
+          <t>・70連でコンプした引きを「だいぶ強い」と称賛
+・3人グループ始動で反響が大きく好評</t>
+        </is>
+      </c>
+      <c r="F604" s="2" t="inlineStr">
+        <is>
+          <t>・浦田の画面録画ミスで対決映像が出せず謝罪
+・名前候補は大人の事情で使えないものがある</t>
+        </is>
+      </c>
+      <c r="G604" s="2" t="inlineStr">
+        <is>
+          <t>・水着ガチャ対決
+・ガチャ天井
+・罰ゲーム
+・グループ名
+・ガムシャラ3</t>
+        </is>
+      </c>
+      <c r="H604" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I604" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ijll8ZM1kWg</t>
+        </is>
+      </c>
+      <c r="J604" s="2" t="inlineStr">
+        <is>
+          <t>ijll8ZM1kWg</t>
+        </is>
+      </c>
+      <c r="K604" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T01:05:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B605" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C605" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年使い込んだ結論。結局1番の当たりはあのキャラでした【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D605" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年実装キャラを使い込んだ最終評価
+裁判・暦み・サライが全コンテンツで活躍
+当たり1位は万能の裁判という結論</t>
+        </is>
+      </c>
+      <c r="E605" s="2" t="inlineStr">
+        <is>
+          <t>・裁判は全コンテンツで活躍する文句なし最高評価
+・暦みは弱点無視の圧倒的火力で周回短縮
+・サライはウィークEXと状態異常解除が優秀
+・ストライフは代償ダメでレイド気絶周回に好相性
+・黒エは意外と火力が出てゴリ押し編成に重宝</t>
+        </is>
+      </c>
+      <c r="F605" s="2" t="inlineStr">
+        <is>
+          <t>・代々はレイド・集会では瞬間火力不足で出番なし
+・黒エは火ダメ軽減率が低く防御面に工夫が必要</t>
+        </is>
+      </c>
+      <c r="G605" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年キャラ評価
+・裁判
+・暦み
+・サライ
+・ストライフ
+・トップ3</t>
+        </is>
+      </c>
+      <c r="H605" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I605" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jnMdv-T2OBY</t>
+        </is>
+      </c>
+      <c r="J605" s="2" t="inlineStr">
+        <is>
+          <t>jnMdv-T2OBY</t>
+        </is>
+      </c>
+      <c r="K605" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T01:05:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B606" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C606" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】高難易度苦手でも29層目指せる「第5回！雲の上の無尽塔」【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D606" s="2" t="inlineStr">
+        <is>
+          <t>無人島(無尽塔)29層までの攻略ワンポイント解説
+7層ペンギン・15層守護者・20層バウムが関門
+30層メタルアルカイザーは別格で対象外</t>
+        </is>
+      </c>
+      <c r="E606" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年キャラがあれば26層まで全力オート可能
+・各階突破でジュエルが貰えてお得
+・ポルカ・オタマはセレチケ交換でダメブロ要員に</t>
+        </is>
+      </c>
+      <c r="F606" s="2" t="inlineStr">
+        <is>
+          <t>・30層メタルアルカイザーは意味不明な難易度で対象外
+・無人島は大味すぎて別の味変コンテンツが欲しい
+・15層守護者・20層バウムはギミック知らないと苦戦</t>
+        </is>
+      </c>
+      <c r="G606" s="2" t="inlineStr">
+        <is>
+          <t>・雲の上の無人島
+・29層攻略
+・皇帝ペンギン
+・守護者ギミック
+・ゴールデンバウム
+・ダメブロ</t>
+        </is>
+      </c>
+      <c r="H606" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I606" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=h9ZuPjaeq5s</t>
+        </is>
+      </c>
+      <c r="J606" s="2" t="inlineStr">
+        <is>
+          <t>h9ZuPjaeq5s</t>
+        </is>
+      </c>
+      <c r="K606" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28T01:05:39Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K606"/>
+  <dimension ref="A1:K614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40382,6 +40382,532 @@
         </is>
       </c>
     </row>
+    <row r="607">
+      <c r="A607" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B607" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C607" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「7周年は弱かった」月刊ワースト&amp;MVPランキング!!2025年12月振り返り→7.5周年と比較して参考にしてみよう　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D607" s="2" t="inlineStr">
+        <is>
+          <t>7周年12月分の月刊ワースト&amp;MVPを振り返り
+上位1桁スタイルのみ実用、他は撤退案件
+7.5周年も同様で冷静な厳選が必要</t>
+        </is>
+      </c>
+      <c r="E607" s="2" t="inlineStr">
+        <is>
+          <t>・メロトセロイは未来から来た超高完成度SS
+・シェリ像・シャムマベルは万能型で長く生き残る
+・リアム・ハイフリアムは継承で中期火力が強烈
+・イリアは半年先性能でとてつもなく強い</t>
+        </is>
+      </c>
+      <c r="F607" s="2" t="inlineStr">
+        <is>
+          <t>・周年の主人公系は活躍の記憶がなく外し
+・継承含め使えず勢いで引くと損する典型
+・上位1桁以外は全て撤退案件の副産物</t>
+        </is>
+      </c>
+      <c r="G607" s="2" t="inlineStr">
+        <is>
+          <t>・7周年振り返り
+・ワースト&amp;MVP
+・上位1桁のみ実用
+・厳選優先
+・継承評価</t>
+        </is>
+      </c>
+      <c r="H607" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I607" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1adSLfkfXcc</t>
+        </is>
+      </c>
+      <c r="J607" s="2" t="inlineStr">
+        <is>
+          <t>1adSLfkfXcc</t>
+        </is>
+      </c>
+      <c r="K607" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T02:25:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B608" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C608" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ネタバレ読めた「七の脅威」FF!?いや正解はコレ!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D608" s="2" t="inlineStr">
+        <is>
+          <t>水着がシングルガチャで異例の前倒し実装
+七夕イベント・結果発表生放送が重なる特別週
+御神獣5人や英雄絡みの実装を予想</t>
+        </is>
+      </c>
+      <c r="E608" s="2" t="inlineStr">
+        <is>
+          <t>・水着前倒し+七夕+結果発表でメリハリある7月初日に期待</t>
+        </is>
+      </c>
+      <c r="F608" s="2" t="inlineStr">
+        <is>
+          <t>・直近は日程が詰まりすぎコラボはなさそう</t>
+        </is>
+      </c>
+      <c r="G608" s="2" t="inlineStr">
+        <is>
+          <t>・七の脅威予想
+・水着前倒し
+・七夕イベント
+・御神獣実装予想
+・直近コラボなし</t>
+        </is>
+      </c>
+      <c r="H608" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I608" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=72qNuZ4oMTU</t>
+        </is>
+      </c>
+      <c r="J608" s="2" t="inlineStr">
+        <is>
+          <t>72qNuZ4oMTU</t>
+        </is>
+      </c>
+      <c r="K608" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T02:25:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B609" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C609" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　無尽塔35階　3ターン討伐　モイなしでOK</t>
+        </is>
+      </c>
+      <c r="D609" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔35階を3ターンで討伐する編成を紹介
+リラ・暦読み・サバ・お玉でモイ不要
+石化はサバで解除しリラの攻撃回数で殲滅</t>
+        </is>
+      </c>
+      <c r="E609" s="2" t="inlineStr">
+        <is>
+          <t>・リラは攻撃回数が多く久々に使えて強い
+・お玉の防御でモイなしでも安定攻略できる
+・サバがいると石化を解除できて大きい
+・ディッパー食らってもHP0にならず安全</t>
+        </is>
+      </c>
+      <c r="F609" s="2" t="inlineStr">
+        <is>
+          <t>・30階は7時間47分かかり非常にきつかった</t>
+        </is>
+      </c>
+      <c r="G609" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔35階
+・3ターン討伐
+・リラ
+・石化解除
+・ダメブロ</t>
+        </is>
+      </c>
+      <c r="H609" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I609" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TEfQG9RKJIA</t>
+        </is>
+      </c>
+      <c r="J609" s="2" t="inlineStr">
+        <is>
+          <t>TEfQG9RKJIA</t>
+        </is>
+      </c>
+      <c r="K609" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T02:25:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B610" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C610" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】限定F91のタイプは？6月30日ガシャ予告！＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D610" s="2" t="inlineStr">
+        <is>
+          <t>6/30ガシャでF91ツインベスパーは攻撃型
+F90 ADS金剛合装備は通常ユニットの支援型
+カロ像も限定でサポスキ次第では要確保</t>
+        </is>
+      </c>
+      <c r="E610" s="2" t="inlineStr">
+        <is>
+          <t>・F91は予想通り攻撃型で限定らしい性能</t>
+        </is>
+      </c>
+      <c r="F610" s="2" t="inlineStr">
+        <is>
+          <t>・カロも限定でサポスキ次第では追う必要があり負担</t>
+        </is>
+      </c>
+      <c r="G610" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・6/30ガシャ予告
+・F91攻撃型
+・F90支援型
+・カロ限定</t>
+        </is>
+      </c>
+      <c r="H610" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I610" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wFwrfHJddFM</t>
+        </is>
+      </c>
+      <c r="J610" s="2" t="inlineStr">
+        <is>
+          <t>wFwrfHJddFM</t>
+        </is>
+      </c>
+      <c r="K610" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T02:25:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B611" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C611" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】限定F91のタイプは？6月30日ガシャ予告！ 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D611" s="2" t="inlineStr">
+        <is>
+          <t>6/30ガシャでF91ツインベスパーは攻撃型
+F90 ADS金剛合装備は通常ユニットの支援型
+カロ像も限定でサポスキ次第では要確保</t>
+        </is>
+      </c>
+      <c r="E611" s="2" t="inlineStr">
+        <is>
+          <t>・F91は予想通り攻撃型で限定らしい性能</t>
+        </is>
+      </c>
+      <c r="F611" s="2" t="inlineStr">
+        <is>
+          <t>・カロも限定でサポスキ次第では追う必要があり負担</t>
+        </is>
+      </c>
+      <c r="G611" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・6/30ガシャ予告
+・F91攻撃型
+・F90支援型
+・カロ限定</t>
+        </is>
+      </c>
+      <c r="H611" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I611" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zYsgrSmSG1A</t>
+        </is>
+      </c>
+      <c r="J611" s="2" t="inlineStr">
+        <is>
+          <t>zYsgrSmSG1A</t>
+        </is>
+      </c>
+      <c r="K611" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T02:25:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】問い合わせ多数！今ならセレチケどれと交換？最新情報アップデート【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D612" s="2" t="inlineStr">
+        <is>
+          <t>セレチケ交換優先度の最新アップデート版を解説
+継承込みで各スタイルの評価を再調整
+女神やボクオーンなど複数がランク変動</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="inlineStr">
+        <is>
+          <t>・G女神+アカネサスは行動回数で全バフが乗り超強烈でS
+・レッド+ライジングアルフニックスで硬く回復も最高
+・賢者系はフリーシルト継承で防御81%超の高水準
+・ボクオーン系は全体防御強化で未だにS評価</t>
+        </is>
+      </c>
+      <c r="F612" s="2" t="inlineStr">
+        <is>
+          <t>・ドローレスはデスメタルコード継承必須で条件が重い
+・最近使わないスタイルは複数リムーブ・降格
+・バートランドは暦み実装で優先度が低下</t>
+        </is>
+      </c>
+      <c r="G612" s="2" t="inlineStr">
+        <is>
+          <t>・セレチケ交換
+・継承優先度
+・評価アップデート
+・S/A評価
+・ガチャ</t>
+        </is>
+      </c>
+      <c r="H612" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I612" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NTcD_vXml2g</t>
+        </is>
+      </c>
+      <c r="J612" s="2" t="inlineStr">
+        <is>
+          <t>NTcD_vXml2g</t>
+        </is>
+      </c>
+      <c r="K612" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T02:25:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B613" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C613" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第126回イフリートたちの井戸 ~最適解パーティ考察~‼️大切なお知らせがあります‼️〜👊ランク上位を目指そう👊</t>
+        </is>
+      </c>
+      <c r="D613" s="2" t="inlineStr">
+        <is>
+          <t>6/29実装イフリートたちの井戸を事前考察
+初の2ラウンド制で2R目のHPが桁違いに高い
+要属性中心+突熱/打熱弱点を狙う編成が有力</t>
+        </is>
+      </c>
+      <c r="E613" s="2" t="inlineStr">
+        <is>
+          <t>・マイターンODゲージ満タンで編成の幅が広がる
+・要属性・打属性アタッカーが全体的に刺さる</t>
+        </is>
+      </c>
+      <c r="F613" s="2" t="inlineStr">
+        <is>
+          <t>・2ラウンド目のHPが約3.5億と桁違いで厄介
+・敵が弱体破り・強化破りを持ちデバフ・バフが通用しない
+・2〜3ターン決着で1戦が長くプレイ負担が大きい</t>
+        </is>
+      </c>
+      <c r="G613" s="2" t="inlineStr">
+        <is>
+          <t>・イフリートの井戸
+・第126回
+・2ラウンド制
+・要属性アタッカー
+・弱体/強化破り
+・シャビさん休止</t>
+        </is>
+      </c>
+      <c r="H613" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-kKtgLf6Lz0</t>
+        </is>
+      </c>
+      <c r="J613" s="2" t="inlineStr">
+        <is>
+          <t>-kKtgLf6Lz0</t>
+        </is>
+      </c>
+      <c r="K613" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T02:25:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B614" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C614" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】2026年6月下旬ガチャ総まとめ！全27スタイル引くべきスタイルランキング！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D614" s="2" t="inlineStr">
+        <is>
+          <t>6月下旬実装ガチャ全27スタイルをティアランク
+7.5周年最終決定版、新規3体と評価変動を解説
+暦み・サイバー・ビンセントがS評価</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="inlineStr">
+        <is>
+          <t>・暦みはオールラウンダーで火ダメ軽減も完備、初心者必入手
+・サイバーは味方攻撃倍率を高く上げるサポートが優秀
+・ビンセントは癖強だがポテンシャルは軍を抜く
+・大々は硬く強敵戦のダメージ抑制に貢献しA評価</t>
+        </is>
+      </c>
+      <c r="F614" s="2" t="inlineStr">
+        <is>
+          <t>・アーニャは現環境で洋態が少なくCへ降格
+・人間女シスカはバフ量控えめでサポート力不足
+・Bランク総取りはジュエルが足りず厳選が重要</t>
+        </is>
+      </c>
+      <c r="G614" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年ガチャ
+・ティアランキング
+・全27スタイル
+・S評価3体
+・セレチケ厳選</t>
+        </is>
+      </c>
+      <c r="H614" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=l070xfIwdMA</t>
+        </is>
+      </c>
+      <c r="J614" s="2" t="inlineStr">
+        <is>
+          <t>l070xfIwdMA</t>
+        </is>
+      </c>
+      <c r="K614" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29T02:25:47Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K614"/>
+  <dimension ref="A1:K622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40908,6 +40908,534 @@
         </is>
       </c>
     </row>
+    <row r="615">
+      <c r="A615" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B615" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C615" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】危険「その編成ダメ」クリアパは嘘!?自分なりの編成と立ち回りを極めてギリギリの戦いを制すんだ!!無尽塔36層シャムマベル討伐　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D615" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔36層シャムマベル討伐の攻略解説
+出回りクリアパは時間制限が厳しく非推奨
+天秘アスラと西王デバフでギリギリ制覇</t>
+        </is>
+      </c>
+      <c r="E615" s="2" t="inlineStr">
+        <is>
+          <t>・天秘アスラなら敵の増加攻撃に耐えられる
+・絶望の歌で追撃ストックし実質マイターン攻撃
+・ランスダンスの回避上振れは長期戦で有効</t>
+        </is>
+      </c>
+      <c r="F615" s="2" t="inlineStr">
+        <is>
+          <t>・出回り編成は時間制限が厳しく非推奨
+・西王は200ターン途中で必ず力尽きる
+・ネメシスの回避運ゲーと単体お祈りゲー</t>
+        </is>
+      </c>
+      <c r="G615" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔36層
+・シャムマベル討伐
+・編成・立ち回り
+・西王デバフ
+・ネメシス火力</t>
+        </is>
+      </c>
+      <c r="H615" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I615" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=p0pz4AeXD6I</t>
+        </is>
+      </c>
+      <c r="J615" s="2" t="inlineStr">
+        <is>
+          <t>p0pz4AeXD6I</t>
+        </is>
+      </c>
+      <c r="K615" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T01:04:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B616" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C616" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】脱出機能付き! F90(A.D.S.混合装着時)の性能確認＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D616" s="2" t="inlineStr">
+        <is>
+          <t>6/30実装F90(ADS金剛装備)の性能確認
+射程1-5の使いやすい防御25%減デバフ役
+デフスタリオンと組めば一気に使いやすい</t>
+        </is>
+      </c>
+      <c r="E616" s="2" t="inlineStr">
+        <is>
+          <t>・射程1-5で防御25%減と使いやすいデバフ
+・脱出機能でやられても一応安心
+・デフスタリオンが自前でテンション条件を満たせる
+・支援が攻撃力上昇タイプで火力が出る</t>
+        </is>
+      </c>
+      <c r="F616" s="2" t="inlineStr">
+        <is>
+          <t>・デバフがかぶりやすい
+・支援型単体だとテンション条件を発動させづらい
+・脱出後は武装と地形適性が変わる</t>
+        </is>
+      </c>
+      <c r="G616" s="2" t="inlineStr">
+        <is>
+          <t>・F90 ADS
+・支援型
+・防御25%減デバフ
+・デフスタリオン
+・脱出機能</t>
+        </is>
+      </c>
+      <c r="H616" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1Yq6G-dWUxM</t>
+        </is>
+      </c>
+      <c r="J616" s="2" t="inlineStr">
+        <is>
+          <t>1Yq6G-dWUxM</t>
+        </is>
+      </c>
+      <c r="K616" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T01:04:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B617" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C617" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】ダメージ無効！？F91(ツイン・ヴェスバー装備)の性能確認 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D617" s="2" t="inlineStr">
+        <is>
+          <t>6/30実装F91(ツインヴェスバー)の性能確認
+初撃ダメージ無効が強烈な攻撃型限定
+HPキープ前提で設定再現度の高い性能</t>
+        </is>
+      </c>
+      <c r="E617" s="2" t="inlineStr">
+        <is>
+          <t>・初撃ダメージ無効がインパクト大
+・HP75%以上で攻撃15%上昇・移動+1が便利
+・Cブックがチャンスステップ2回で使いやすい
+・F91の設定再現度が高く良い</t>
+        </is>
+      </c>
+      <c r="F617" s="2" t="inlineStr">
+        <is>
+          <t>・射程1-4と短め
+・初撃ダメージ無効は支援攻撃で消費されると無意味</t>
+        </is>
+      </c>
+      <c r="G617" s="2" t="inlineStr">
+        <is>
+          <t>・F91ツインヴェスバー
+・攻撃型限定
+・初撃ダメージ無効
+・HPキープ
+・Cブック</t>
+        </is>
+      </c>
+      <c r="H617" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I617" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NDD3d7KnfoE</t>
+        </is>
+      </c>
+      <c r="J617" s="2" t="inlineStr">
+        <is>
+          <t>NDD3d7KnfoE</t>
+        </is>
+      </c>
+      <c r="K617" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T01:04:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B618" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C618" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】限定F91達の性能が一部公開されたので確認しよう 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D618" s="2" t="inlineStr">
+        <is>
+          <t>6/30ガチャ実装ユニットの性能を一通り確認
+F91は初撃無効、F90は使いやすいデバフ役
+投稿者はF91狙いで100連を予定</t>
+        </is>
+      </c>
+      <c r="E618" s="2" t="inlineStr">
+        <is>
+          <t>・F91の初撃ダメージ無効が強力
+・F90はデフスタリオンと組むと使いやすい
+・F91の設定再現度が高い</t>
+        </is>
+      </c>
+      <c r="F618" s="2" t="inlineStr">
+        <is>
+          <t>・F91の射程が短め
+・F90のデバフがかぶりやすい
+・サポーターは既存試作機タグ強化で無理に追う程でない
+・サポートのHP回復量は控えめ</t>
+        </is>
+      </c>
+      <c r="G618" s="2" t="inlineStr">
+        <is>
+          <t>・限定F91
+・F90 ADS
+・初撃ダメージ無効
+・サポーター カロ像
+・試作機タグ</t>
+        </is>
+      </c>
+      <c r="H618" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I618" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zmv92t3qk6M</t>
+        </is>
+      </c>
+      <c r="J618" s="2" t="inlineStr">
+        <is>
+          <t>Zmv92t3qk6M</t>
+        </is>
+      </c>
+      <c r="K618" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T01:04:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B619" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C619" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】FFコラボくるならこの６人でしょ！！！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D619" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS×FFコラボが来るなら誰かを予想
+FFレコードキーパー側のコラボから期待
+クラウド風ギュスタブなど6組を妄想</t>
+        </is>
+      </c>
+      <c r="E619" s="2" t="inlineStr">
+        <is>
+          <t>・前回ドラクエタクトコラボが盛り上がった
+・クラウドの格好をしたギュスタブが見たい
+・ブルー×ウォリアーオブライトが熱い</t>
+        </is>
+      </c>
+      <c r="F619" s="2" t="inlineStr">
+        <is>
+          <t>・第3弾予想は結局来なかった
+・現時点でFFコラボ告知がなく来ないかも</t>
+        </is>
+      </c>
+      <c r="G619" s="2" t="inlineStr">
+        <is>
+          <t>・FFコラボ予想
+・FFレコードキーパー
+・ギュスタブ
+・セフィロス
+・バルフレア</t>
+        </is>
+      </c>
+      <c r="H619" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I619" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-dU5y1U6jak</t>
+        </is>
+      </c>
+      <c r="J619" s="2" t="inlineStr">
+        <is>
+          <t>-dU5y1U6jak</t>
+        </is>
+      </c>
+      <c r="K619" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T01:04:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B620" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C620" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】無尽塔30からLet's go😻</t>
+        </is>
+      </c>
+      <c r="D620" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔30〜36層の周回攻略を生配信
+全力オートで6〜12時間かかる長期戦
+ガチャで人間女狙うも出ず貝で妥協</t>
+        </is>
+      </c>
+      <c r="E620" s="2" t="inlineStr">
+        <is>
+          <t>・新しい女神編成なら無尽塔をクリアできる
+・ネメシスに排水を付けると強い
+・排水を覚えれば周回が楽になる</t>
+        </is>
+      </c>
+      <c r="F620" s="2" t="inlineStr">
+        <is>
+          <t>・30層全力オート6時間・36層11時間半と長すぎる
+・古い女神はBP不足で積む
+・ガチャで人間女が出ず実質爆死
+・ゲームがたまに落ちて目が離せない</t>
+        </is>
+      </c>
+      <c r="G620" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔30-36層
+・全力オート長時間
+・女神編成
+・ネメシス排水
+・ガチャ(人間女/貝)</t>
+        </is>
+      </c>
+      <c r="H620" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-jieAi9YUOE</t>
+        </is>
+      </c>
+      <c r="J620" s="2" t="inlineStr">
+        <is>
+          <t>-jieAi9YUOE</t>
+        </is>
+      </c>
+      <c r="K620" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T01:04:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B621" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C621" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】白薔薇とT260Gはこの日のためだった！？7月1日のガチャはこれだ！！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D621" s="2" t="inlineStr">
+        <is>
+          <t>7/1のガチャをサガフロ発売記念と予想
+主役は白薔薇アビスとT260Gアビス
+FFレコードキーパーコラボは7/10頃に期待</t>
+        </is>
+      </c>
+      <c r="E621" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦で目立った白薔薇・T260アビスが満を持して来そう
+・FFコラボが来たら盛り上がる
+・ドラクエタクトコラボが盛り上がった実績</t>
+        </is>
+      </c>
+      <c r="F621" s="2" t="inlineStr">
+        <is>
+          <t>・公式生放送の予告がなくFFコラボは今回見送りか</t>
+        </is>
+      </c>
+      <c r="G621" s="2" t="inlineStr">
+        <is>
+          <t>・7/1ガチャ予想
+・サガフロ発売記念
+・白薔薇アビス
+・T260アビス
+・FFコラボ</t>
+        </is>
+      </c>
+      <c r="H621" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lPDt9spl8g4</t>
+        </is>
+      </c>
+      <c r="J621" s="2" t="inlineStr">
+        <is>
+          <t>lPDt9spl8g4</t>
+        </is>
+      </c>
+      <c r="K621" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T01:04:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B622" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C622" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ヴィンセント狙いで起きた奇跡 #ロマサガRS #shorts</t>
+        </is>
+      </c>
+      <c r="D622" s="2" t="inlineStr">
+        <is>
+          <t>ヴィンセント狙いのガチャを実演
+単発5回の1発目でまさかの大当たり
+一撃で終了する奇跡を披露</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="inlineStr">
+        <is>
+          <t>・1発目で目当てが出る奇跡
+・嬉しいSSスタイル獲得</t>
+        </is>
+      </c>
+      <c r="F622" s="2" t="inlineStr"/>
+      <c r="G622" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ実演
+・ヴィンセント狙い
+・単発5回
+・1発目大当たり</t>
+        </is>
+      </c>
+      <c r="H622" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DRRfGW5YGrc</t>
+        </is>
+      </c>
+      <c r="J622" s="2" t="inlineStr">
+        <is>
+          <t>DRRfGW5YGrc</t>
+        </is>
+      </c>
+      <c r="K622" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T01:04:45Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K622"/>
+  <dimension ref="A1:K633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -41436,6 +41436,719 @@
         </is>
       </c>
     </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B623" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C623" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「FFコラボ」いずこ!?からの夏本番無尽塔本番で本気のガチャが来る!!お知らせ読んでこー　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D623" s="2" t="inlineStr">
+        <is>
+          <t>水着イベントとダブルガチャのお知らせを確認
+FFコラボは赤月さん休暇時に放置と予想
+4倍速目的でアビリティ武器は購入予定</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="inlineStr">
+        <is>
+          <t>・無人島を遊ばせる意図があるのは良い
+・4倍速が魅力なのでアビ武器は買う</t>
+        </is>
+      </c>
+      <c r="F623" s="2" t="inlineStr">
+        <is>
+          <t>・夏の福袋はお得ではないのでスルー推奨
+・復刻はルーティンでタイミングは特にない
+・オーラムはゲーム内効果で大したものなし
+・中身が半分差し替えかもで物足りない</t>
+        </is>
+      </c>
+      <c r="G623" s="2" t="inlineStr">
+        <is>
+          <t>・水着イベント
+・FFコラボ予想
+・無人島復刻
+・ガチャ更新
+・七夕イベント</t>
+        </is>
+      </c>
+      <c r="H623" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I623" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=K8VeGQlCNhg</t>
+        </is>
+      </c>
+      <c r="J623" s="2" t="inlineStr">
+        <is>
+          <t>K8VeGQlCNhg</t>
+        </is>
+      </c>
+      <c r="K623" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T01:05:49Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B624" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C624" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】無尽塔　36６階から挑戦！　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D624" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔36階に挑戦するライブ配信
+HPが高すぎて単調と不満が続出
+新ネメシスの性能向上は好評</t>
+        </is>
+      </c>
+      <c r="E624" s="2" t="inlineStr">
+        <is>
+          <t>・新スタイルのネメシスが強く使いやすくなった
+・絶望の歌が役立つ場面あり</t>
+        </is>
+      </c>
+      <c r="F624" s="2" t="inlineStr">
+        <is>
+          <t>・HPが高すぎて調整ミス級
+・今回の無人島は単調でつまらない
+・30階クリアに8時間かかるほど長い
+・過去の無人島より盛り上がりに欠ける</t>
+        </is>
+      </c>
+      <c r="G624" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔36階
+・無人島
+・ネメシス
+・排水
+・フルオート</t>
+        </is>
+      </c>
+      <c r="H624" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I624" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WFQdoEHZrcQ</t>
+        </is>
+      </c>
+      <c r="J624" s="2" t="inlineStr">
+        <is>
+          <t>WFQdoEHZrcQ</t>
+        </is>
+      </c>
+      <c r="K624" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T01:05:49Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B625" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C625" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】無尽塔　30階から挑戦！　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D625" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔30階に挑戦する長時間ライブ配信
+白必須・団光必須のギミックで大苦戦
+排水編成でないと突破困難と判明</t>
+        </is>
+      </c>
+      <c r="E625" s="2" t="inlineStr">
+        <is>
+          <t>・新ネメシスの排水運用が有効
+・まさかり継承でダメージが伸びる</t>
+        </is>
+      </c>
+      <c r="F625" s="2" t="inlineStr">
+        <is>
+          <t>・HPが高く1600万回復で全然減らない
+・コーションで防御強化され長期戦になる
+・白なしだと突破が困難
+・地獄と評するほどの難易度</t>
+        </is>
+      </c>
+      <c r="G625" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔30階
+・シャムマベル
+・コーション
+・団光
+・排水編成</t>
+        </is>
+      </c>
+      <c r="H625" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pmDNBLaBrFg</t>
+        </is>
+      </c>
+      <c r="J625" s="2" t="inlineStr">
+        <is>
+          <t>pmDNBLaBrFg</t>
+        </is>
+      </c>
+      <c r="K625" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T01:05:49Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B626" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C626" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】URガンダムF91(ツイン・ヴェスバー装備) 武装アニメ  ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D626" s="2" t="inlineStr">
+        <is>
+          <t>URガンダムF91ツインヴェスバーの武装アニメShorts
+戦闘ボイス中心の短尺動画
+「強力すぎる」と性能を高評価</t>
+        </is>
+      </c>
+      <c r="E626" s="2" t="inlineStr">
+        <is>
+          <t>・F91ツインヴェスバーが強力すぎる性能</t>
+        </is>
+      </c>
+      <c r="F626" s="2" t="inlineStr"/>
+      <c r="G626" s="2" t="inlineStr">
+        <is>
+          <t>・GジェネエターナルF91
+・ツインヴェスバー
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H626" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I626" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=67qXarqAAwY</t>
+        </is>
+      </c>
+      <c r="J626" s="2" t="inlineStr">
+        <is>
+          <t>67qXarqAAwY</t>
+        </is>
+      </c>
+      <c r="K626" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T01:05:49Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B627" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C627" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】F91(ツインヴェスバー)とりま100連！ 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D627" s="2" t="inlineStr">
+        <is>
+          <t>F91ツインヴェスバー狙いで100連ガチャ
+目当てのツインヴェスバーを無事確保
+F90は出ず限定サポーターは自引き成功</t>
+        </is>
+      </c>
+      <c r="E627" s="2" t="inlineStr">
+        <is>
+          <t>・ツインヴェスバー確保で前回の爆死を払拭
+・限定サポーターのカロッズを自引きできた
+・UR確定演出が多く盛り上がった</t>
+        </is>
+      </c>
+      <c r="F627" s="2" t="inlineStr">
+        <is>
+          <t>・目当てのF90が出なかった
+・前回のナイチンゲール・フェネクスは追いガチャで爆死</t>
+        </is>
+      </c>
+      <c r="G627" s="2" t="inlineStr">
+        <is>
+          <t>・GジェネF91
+・100連ガチャ
+・ツインヴェスバー
+・F90
+・カロッズ</t>
+        </is>
+      </c>
+      <c r="H627" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I627" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=eK5kBJkaEys</t>
+        </is>
+      </c>
+      <c r="J627" s="2" t="inlineStr">
+        <is>
+          <t>eK5kBJkaEys</t>
+        </is>
+      </c>
+      <c r="K627" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T01:05:49Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B628" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C628" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】水着ラッシュ！7月1日更新情報まとめ 【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D628" s="2" t="inlineStr">
+        <is>
+          <t>7月1日更新の水着キャンペーン情報まとめ
+イリス編は推し2人で優先的に回す方針
+副防具は性能を確認して選ぶ必要あり</t>
+        </is>
+      </c>
+      <c r="E628" s="2" t="inlineStr">
+        <is>
+          <t>・イリス編はディーバNo.5とウルピナで重要度高い
+・ログボ・ミッションで各3000ジュエル貰える
+・福袋チケットで最低1体はピック確保できる</t>
+        </is>
+      </c>
+      <c r="F628" s="2" t="inlineStr">
+        <is>
+          <t>・副防具は1つしか選べず間違えると取り返せない</t>
+        </is>
+      </c>
+      <c r="G628" s="2" t="inlineStr">
+        <is>
+          <t>・水着キャンペーン
+・イリス編
+・木ハ編
+・福袋チケット
+・ロマンシングパス</t>
+        </is>
+      </c>
+      <c r="H628" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I628" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=w1BWAqcXf2A</t>
+        </is>
+      </c>
+      <c r="J628" s="2" t="inlineStr">
+        <is>
+          <t>w1BWAqcXf2A</t>
+        </is>
+      </c>
+      <c r="K628" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T01:05:49Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B629" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C629" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】強キャラオーラが半端ない6人【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D629" s="2" t="inlineStr">
+        <is>
+          <t>水着ガチャ6キャラの性能とオーラを考察
+イリス編の人気キャラ勢に特に注目
+復刻ミドはインフレで採用に悩むと本音</t>
+        </is>
+      </c>
+      <c r="E629" s="2" t="inlineStr">
+        <is>
+          <t>・イリス・ディーバNo.5・ウルピナと人気キャラ揃い
+・お玉のダメブロ剣・怪獣持ちに期待
+・ミーティアは好きな人が多い枠</t>
+        </is>
+      </c>
+      <c r="F629" s="2" t="inlineStr">
+        <is>
+          <t>・このタイミングで6人は課金的にきつい
+・夏福袋は1万円で高くて買えない
+・復刻ミド・マイスはインフレで今更削るか悩む</t>
+        </is>
+      </c>
+      <c r="G629" s="2" t="inlineStr">
+        <is>
+          <t>・水着ガチャ6人
+・木ハ
+・お玉
+・イリス編
+・復刻ミド</t>
+        </is>
+      </c>
+      <c r="H629" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I629" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sTC9FTCswo8</t>
+        </is>
+      </c>
+      <c r="J629" s="2" t="inlineStr">
+        <is>
+          <t>sTC9FTCswo8</t>
+        </is>
+      </c>
+      <c r="K629" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T01:05:49Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B630" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C630" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】悲報！7.5周年終了直前にどう考えてもヤバいガチャが来てしまう...【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D630" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年直前に水着ダブルガチャが連続到来
+無人島開催中のお玉投入を警戒
+次は7月7日でFFコラボの可能性も示唆</t>
+        </is>
+      </c>
+      <c r="E630" s="2" t="inlineStr">
+        <is>
+          <t>・木ハのイラストが抜群に良い
+・イリス・ディーバ・ウルピナが魅力的
+・復刻ミドは技マシン継承で価値あり</t>
+        </is>
+      </c>
+      <c r="F630" s="2" t="inlineStr">
+        <is>
+          <t>・水着連続でジュエルが枯渇しそう
+・副防具は間違えると個別対応なしで自己責任
+・お玉が無人島人権化しそうで恐ろしい
+・復刻ミド以外は今更取る価値が薄い</t>
+        </is>
+      </c>
+      <c r="G630" s="2" t="inlineStr">
+        <is>
+          <t>・水着ダブルガチャ
+・木ハ
+・お玉
+・イリス編
+・復刻ミド</t>
+        </is>
+      </c>
+      <c r="H630" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I630" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=d73_gvFjROE</t>
+        </is>
+      </c>
+      <c r="J630" s="2" t="inlineStr">
+        <is>
+          <t>d73_gvFjROE</t>
+        </is>
+      </c>
+      <c r="K630" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T01:05:49Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B631" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C631" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第126回イフリートたちの井戸 ~‼️攻略‼️ランキング100位を目指して ~全てお見せします</t>
+        </is>
+      </c>
+      <c r="D631" s="2" t="inlineStr">
+        <is>
+          <t>イフリートたちの井戸をランキング100位向けに攻略
+テルミ等5名で2ターン23手クリア編成を紹介
+魂を積めばさらに上位を狙えると解説</t>
+        </is>
+      </c>
+      <c r="E631" s="2" t="inlineStr">
+        <is>
+          <t>・魂を積めば十分に上位を狙える編成
+・テルミの継承で足りない部分を対策可能</t>
+        </is>
+      </c>
+      <c r="F631" s="2" t="inlineStr">
+        <is>
+          <t>・抽選や下ブレでやり直しが多い運要素あり</t>
+        </is>
+      </c>
+      <c r="G631" s="2" t="inlineStr">
+        <is>
+          <t>・イフリートたちの井戸
+・ランキング100位
+・2ターン23手
+・継承技
+・魂</t>
+        </is>
+      </c>
+      <c r="H631" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I631" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0nwvVez9bjA</t>
+        </is>
+      </c>
+      <c r="J631" s="2" t="inlineStr">
+        <is>
+          <t>0nwvVez9bjA</t>
+        </is>
+      </c>
+      <c r="K631" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T01:05:49Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B632" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C632" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【ガチャ動画】ジュエル２万弱でコンプできますか？【No.618】</t>
+        </is>
+      </c>
+      <c r="D632" s="2" t="inlineStr">
+        <is>
+          <t>ジュエル約1.9万で水着3キャラのコンプに挑戦
+60連＋天井狙いで人間女など確保を目指す
+コンプできず天井まで貯めて再挑戦へ</t>
+        </is>
+      </c>
+      <c r="E632" s="2" t="inlineStr">
+        <is>
+          <t>・女性3人が水着で登場と喜ぶ
+・序盤にすり抜けでSSを引けた場面あり</t>
+        </is>
+      </c>
+      <c r="F632" s="2" t="inlineStr">
+        <is>
+          <t>・ジュエル2万弱ではコンプできなかった
+・引きが渋く天井まで届かなかった</t>
+        </is>
+      </c>
+      <c r="G632" s="2" t="inlineStr">
+        <is>
+          <t>・水着ガチャ
+・人間女
+・ネメシス
+・ギュスターヴ
+・60連天井</t>
+        </is>
+      </c>
+      <c r="H632" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I632" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=36qajPsPs8k</t>
+        </is>
+      </c>
+      <c r="J632" s="2" t="inlineStr">
+        <is>
+          <t>36qajPsPs8k</t>
+        </is>
+      </c>
+      <c r="K632" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T01:05:49Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B633" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C633" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】かなり注意喚起!!めずらしくお知らせチェック!!【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D633" s="2" t="inlineStr">
+        <is>
+          <t>先取り水着に続き7月1日から水着イベント到来
+副防具は1つ選択制でミスは個別対応なし
+次イベントは7月7日の七夕予定</t>
+        </is>
+      </c>
+      <c r="E633" s="2" t="inlineStr"/>
+      <c r="F633" s="2" t="inlineStr">
+        <is>
+          <t>・副防具は性能確認しないとミスしても個別対応なし</t>
+        </is>
+      </c>
+      <c r="G633" s="2" t="inlineStr">
+        <is>
+          <t>・水着イベント
+・副防具選択
+・看問
+・七夕イベント
+・アンケート</t>
+        </is>
+      </c>
+      <c r="H633" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I633" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pfbLqyDnAGQ</t>
+        </is>
+      </c>
+      <c r="J633" s="2" t="inlineStr">
+        <is>
+          <t>pfbLqyDnAGQ</t>
+        </is>
+      </c>
+      <c r="K633" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01T01:05:49Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K633"/>
+  <dimension ref="A1:K653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42149,6 +42149,1290 @@
         </is>
       </c>
     </row>
+    <row r="634">
+      <c r="A634" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B634" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C634" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】引くべし!!「SSSS24連打」で真っ当進化した鬼八&amp;ノエルよりヒット数増加したウルピナの継承含めた強さ!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D634" s="2" t="inlineStr">
+        <is>
+          <t>水着鬼八とウルピナの厳選比較。
+鬼八は環境上位へきっちり更新、大満足。
+ウルピナはノエル劣化気味で評価B止まり。</t>
+        </is>
+      </c>
+      <c r="E634" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八は出力・持続力とも満足の環境上位更新
+・ウルピナSSSS24連打で火力SS評価
+・鬼八のエクストラ6倍と持続性が優秀</t>
+        </is>
+      </c>
+      <c r="F634" s="2" t="inlineStr">
+        <is>
+          <t>・ウルピナは総合評価Bでノエルの劣化版
+・ウルピナの挑発アビリティは時代遅れ注意
+・2ターン交互運用がむしろ弱いと感じる</t>
+        </is>
+      </c>
+      <c r="G634" s="2" t="inlineStr">
+        <is>
+          <t>・水着鬼八
+・ウルピナ
+・SSSS24連打
+・ノエル型
+・厳選比較</t>
+        </is>
+      </c>
+      <c r="H634" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I634" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-n321VBbdTE</t>
+        </is>
+      </c>
+      <c r="J634" s="2" t="inlineStr">
+        <is>
+          <t>-n321VBbdTE</t>
+        </is>
+      </c>
+      <c r="K634" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B635" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C635" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】関門スービエ「鬼八無し」自由枠2体!!世界記録に迫れるのはあいつしかいない!?闘者の関門2026年7月　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D635" s="2" t="inlineStr">
+        <is>
+          <t>関門スービエをビクトール中心に攻略。
+自由枠2体・鬼八無しで10秒圏内。
+制圧戦や副防具の注意喚起も添える。</t>
+        </is>
+      </c>
+      <c r="E635" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトールだけで自由枠2体10秒と満足
+・配布アレツも実用的でOD無しで安定</t>
+        </is>
+      </c>
+      <c r="F635" s="2" t="inlineStr">
+        <is>
+          <t>・リバイバほどの強さはないと指摘
+・副防具選択イベントは触らず注意</t>
+        </is>
+      </c>
+      <c r="G635" s="2" t="inlineStr">
+        <is>
+          <t>・関門スービエ
+・ビクトール
+・自由枠2体
+・周回編成
+・副防具注意</t>
+        </is>
+      </c>
+      <c r="H635" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I635" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Uh0j0O6zynI</t>
+        </is>
+      </c>
+      <c r="J635" s="2" t="inlineStr">
+        <is>
+          <t>Uh0j0O6zynI</t>
+        </is>
+      </c>
+      <c r="K635" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B636" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C636" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年VS水着鬼八!!最強は誰!?「真」比較検討会7.5周年ファイナル!!最強ガチャを順に引くだけの簡単な作業!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D636" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年ガチャ全体の最終比較検討会。
+サイバ編が全項目高水準で最強格。
+無人島ネメシスや鬼八の汎用性も高評価。</t>
+        </is>
+      </c>
+      <c r="E636" s="2" t="inlineStr">
+        <is>
+          <t>・サイバ編は全項目高水準で平均値が最強
+・無人島更新のネメシスは価値が高い
+・ウルピナはどこ系で分かりやすく火力高い
+・鬼八・リアムは属性使い分けの汎用性</t>
+        </is>
+      </c>
+      <c r="F636" s="2" t="inlineStr">
+        <is>
+          <t>・ボルカノは使い所がなさそう
+・イリスは立ち上がりが悪く回避活かせず
+・副産物スタイルがいない鬼畜ガチャ仕様</t>
+        </is>
+      </c>
+      <c r="G636" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年
+・比較検討会
+・サイバ編
+・ネメシス
+・確保優先度</t>
+        </is>
+      </c>
+      <c r="H636" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I636" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fOkwYgqp8fs</t>
+        </is>
+      </c>
+      <c r="J636" s="2" t="inlineStr">
+        <is>
+          <t>fOkwYgqp8fs</t>
+        </is>
+      </c>
+      <c r="K636" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B637" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C637" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「即買い!!」エレノア全体42連打で途切れない攻撃!!熱術をリードする待望の最強アタッカーがロマンシングパス配布で→2026年7月　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D637" s="2" t="inlineStr">
+        <is>
+          <t>ロマパス配布のエレノアを性能解説。
+5ターン目に全体42連打のぶっ壊れ。
+熱術アタッカー不足を補う即買い評価。</t>
+        </is>
+      </c>
+      <c r="E637" s="2" t="inlineStr">
+        <is>
+          <t>・5ターン目全体42ヒットのぶっ壊れ火力
+・即買い推奨、熱術アタッカー不足を補填
+・ボルカノの熱術パートナーとしてベスト
+・パス機能の4倍速は攻略上かなり重要</t>
+        </is>
+      </c>
+      <c r="F637" s="2" t="inlineStr">
+        <is>
+          <t>・5ターン目到達まで立ち上がりそこそこ
+・BPが途中不足で2ターン目から補填必要
+・広告スキップ機能は不便でサービス不十分</t>
+        </is>
+      </c>
+      <c r="G637" s="2" t="inlineStr">
+        <is>
+          <t>・ロマパス
+・エレノア
+・全体42連打
+・熱術アタッカー
+・ボルカノ相棒</t>
+        </is>
+      </c>
+      <c r="H637" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I637" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hgAcgLYSsN4</t>
+        </is>
+      </c>
+      <c r="J637" s="2" t="inlineStr">
+        <is>
+          <t>hgAcgLYSsN4</t>
+        </is>
+      </c>
+      <c r="K637" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B638" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C638" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】URガンダムF90(A.D.S.混合装着時) 武装アニメ  ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D638" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのURガンダムF90。
+A.D.S.混合装着時の武装アニメ紹介。
+セリフ入りの短尺ショート動画。</t>
+        </is>
+      </c>
+      <c r="E638" s="2" t="inlineStr"/>
+      <c r="F638" s="2" t="inlineStr"/>
+      <c r="G638" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ガンダムF90
+・武装アニメ
+・ショート</t>
+        </is>
+      </c>
+      <c r="H638" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I638" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=eT_VoFJJeP8</t>
+        </is>
+      </c>
+      <c r="J638" s="2" t="inlineStr">
+        <is>
+          <t>eT_VoFJJeP8</t>
+        </is>
+      </c>
+      <c r="K638" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B639" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C639" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ウルピナ､Diva欲しい！水着ガチャぶん回すぞ！！【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D639" s="2" t="inlineStr">
+        <is>
+          <t>水着ガチャをディバ・ウルピナ狙いで実況。
+イリス編は大きく沼って下ぶれ連発。
+鬼八編の大逆転で最終的に全員確保。</t>
+        </is>
+      </c>
+      <c r="E639" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八編が大逆転で狙いを一気に確保
+・無償ジュエル温存と確定チケット活用</t>
+        </is>
+      </c>
+      <c r="F639" s="2" t="inlineStr">
+        <is>
+          <t>・イリス編がひどく下ぶれ演出も最低
+・すり抜け・重なり連発でつらい引き</t>
+        </is>
+      </c>
+      <c r="G639" s="2" t="inlineStr">
+        <is>
+          <t>・水着ガチャ
+・ディバ狙い
+・ウルピナ
+・確定チケット
+・神引き</t>
+        </is>
+      </c>
+      <c r="H639" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I639" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vPngc04L7EA</t>
+        </is>
+      </c>
+      <c r="J639" s="2" t="inlineStr">
+        <is>
+          <t>vPngc04L7EA</t>
+        </is>
+      </c>
+      <c r="K639" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B640" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C640" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】超超超注意喚起有！＆7人全員性能確認※ロマパスエレノア込み【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D640" s="2" t="inlineStr">
+        <is>
+          <t>副防具選択の注意喚起とロマパス解説。
+水着7人＋エレノアの性能を一気確認。
+鬼八は超火力、ディバは様子見判断。</t>
+        </is>
+      </c>
+      <c r="E640" s="2" t="inlineStr">
+        <is>
+          <t>・エレノアは2.5倍4S連打でぶっ壊れ強い
+・鬼八は1人6億×24ヒットのアホ火力
+・お玉は逆転の指令でエクストラをばらまく
+・ミーティアも良い性能でイシス的に使える</t>
+        </is>
+      </c>
+      <c r="F640" s="2" t="inlineStr">
+        <is>
+          <t>・副防具選択は間違えると取り返し不可の注意
+・イリスは突用でアーニャと役割が被る
+・来週FFコラボの可能性ありディバは様子見</t>
+        </is>
+      </c>
+      <c r="G640" s="2" t="inlineStr">
+        <is>
+          <t>・副防具注意
+・ロマパスエレノア
+・鬼八
+・お玉逆転の教え
+・ディバ</t>
+        </is>
+      </c>
+      <c r="H640" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I640" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1MY3QtBdyUg</t>
+        </is>
+      </c>
+      <c r="J640" s="2" t="inlineStr">
+        <is>
+          <t>1MY3QtBdyUg</t>
+        </is>
+      </c>
+      <c r="K640" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B641" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C641" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】見せてやる、、、神引きとはこう言うことだ！！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D641" s="2" t="inlineStr">
+        <is>
+          <t>鬼八・お玉狙いで水着ガチャを実況。
+無償スタートから速攻キャッチの神引き。
+配布ドロレスの前倒しにも感謝。</t>
+        </is>
+      </c>
+      <c r="E641" s="2" t="inlineStr">
+        <is>
+          <t>・無償席スタートで鬼八・お玉を速攻確保
+・7.5周年締切前の配布ドロレスがありがたい</t>
+        </is>
+      </c>
+      <c r="F641" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャは闇、優勝席は被りが多い</t>
+        </is>
+      </c>
+      <c r="G641" s="2" t="inlineStr">
+        <is>
+          <t>・神引き
+・鬼八
+・お玉
+・無償ガチャ
+・配布ドロレス</t>
+        </is>
+      </c>
+      <c r="H641" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I641" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PBz9RBfOleo</t>
+        </is>
+      </c>
+      <c r="J641" s="2" t="inlineStr">
+        <is>
+          <t>PBz9RBfOleo</t>
+        </is>
+      </c>
+      <c r="K641" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B642" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C642" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7.5周年終了直前！驚愕の大台突破14大ガチャランキング！引き忘れ絶対ない様に最後の注意喚起⚠️【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D642" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年14大ガチャを終了直前ランキング。
+サイバー編が断トツでビンセントも必取。
+引き忘れ防止の最終注意喚起。</t>
+        </is>
+      </c>
+      <c r="E642" s="2" t="inlineStr">
+        <is>
+          <t>・サイバー編は全員大当たりで断トツ1位
+・ビンセントは抜けており取るべき
+・リアム・2クアイ・暦読みも高評価
+・締切前6000ジュエル配布は運営の優しさ</t>
+        </is>
+      </c>
+      <c r="F642" s="2" t="inlineStr">
+        <is>
+          <t>・多くのスタイルは使い所が狭い
+・人間卑弥呼は威力低くヒットも伸びない
+・時間切れ間近で取り直し不可の注意</t>
+        </is>
+      </c>
+      <c r="G642" s="2" t="inlineStr">
+        <is>
+          <t>・14大ガチャ
+・ランキング
+・サイバー編
+・ビンセント
+・暦読み</t>
+        </is>
+      </c>
+      <c r="H642" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I642" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XD-g7jlIZv8</t>
+        </is>
+      </c>
+      <c r="J642" s="2" t="inlineStr">
+        <is>
+          <t>XD-g7jlIZv8</t>
+        </is>
+      </c>
+      <c r="K642" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B643" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C643" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】超重要！絶対に全員急いで確認してください！おすすめ装備も大紹介【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D643" s="2" t="inlineStr">
+        <is>
+          <t>副防具の選択イベントを徹底解説。
+麦わ・パレオ・サンダルの3択を比較。
+投稿者はダメブロのサンダルを選択。</t>
+        </is>
+      </c>
+      <c r="E643" s="2" t="inlineStr">
+        <is>
+          <t>・サンダルの1ターン目まるまるダメブロが強い
+・瀕死連マで開幕火力が大幅アップ
+・周回系で持つ人との優位性が出る</t>
+        </is>
+      </c>
+      <c r="F643" s="2" t="inlineStr">
+        <is>
+          <t>・パレオは腐りやすく選ばない方がいい
+・麦わ帽子は5ターン目以降のみで被り注意
+・今後インフレで麦わのフォースが潰れる懸念
+・選択間違いは自己責任で取り返し不可</t>
+        </is>
+      </c>
+      <c r="G643" s="2" t="inlineStr">
+        <is>
+          <t>・副防具選択
+・麦わ帽子
+・日輪のサンダル
+・瀕死連マ
+・注意喚起</t>
+        </is>
+      </c>
+      <c r="H643" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2bMzo1HKE28</t>
+        </is>
+      </c>
+      <c r="J643" s="2" t="inlineStr">
+        <is>
+          <t>2bMzo1HKE28</t>
+        </is>
+      </c>
+      <c r="K643" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B644" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C644" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今回の水着ガチャはイラストだけじゃない？イリス編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D644" s="2" t="inlineStr">
+        <is>
+          <t>イリス編3体の性能を実装直後チェック。
+ウルピナは2ターンごと44ヒットの純アタ。
+ディバは残冷雷編成を強化するサポーター。</t>
+        </is>
+      </c>
+      <c r="E644" s="2" t="inlineStr">
+        <is>
+          <t>・ウルピナは2ターンごと7コ44ヒットで強力
+・ディバは残冷雷編成をエクストラで超強化
+・イリスはヘブンズインペール継承で完全体
+・イリスの水着イラストがトップクラス</t>
+        </is>
+      </c>
+      <c r="F644" s="2" t="inlineStr">
+        <is>
+          <t>・ウルピナは開幕弱く2ターンに1回が本気
+・ディバは残雷編成でしか使わなそう
+・イリスは要属性編成前提で汎用性低め</t>
+        </is>
+      </c>
+      <c r="G644" s="2" t="inlineStr">
+        <is>
+          <t>・イリス編
+・ウルピナ
+・ディバNo5
+・ヘブンズインペール
+・属性編成</t>
+        </is>
+      </c>
+      <c r="H644" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=asGXcXtcdCQ</t>
+        </is>
+      </c>
+      <c r="J644" s="2" t="inlineStr">
+        <is>
+          <t>asGXcXtcdCQ</t>
+        </is>
+      </c>
+      <c r="K644" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B645" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C645" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】この水着ガチャ全員大当たり説！？鬼八編ガチャ性能チェック！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D645" s="2" t="inlineStr">
+        <is>
+          <t>鬼八編3体を全員大当たり説で性能確認。
+鬼八は5倍エクストラでレイド人権級火力。
+お玉はチョコ継承器が最新化で当たり。</t>
+        </is>
+      </c>
+      <c r="E645" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八は5倍エクストラで火力ぶっ飛びレイド人権
+・お玉はチョコ贈り物の最新継承器で無人島当たり
+・ミーティアは残属性版イシスで置き物性能高い
+・3体とも大当たりで腐らない性能</t>
+        </is>
+      </c>
+      <c r="F645" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八は弱点つけないと貧弱で追撃なし3ターンセット
+・お玉のエクストラ付与は抽選運次第
+・ミーティアのスイカ割はランダム敵でリタマラ懸念</t>
+        </is>
+      </c>
+      <c r="G645" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八編
+・鬼八
+・お玉
+・チョコレートの贈り物
+・ミーティア</t>
+        </is>
+      </c>
+      <c r="H645" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xvplZOjy6ls</t>
+        </is>
+      </c>
+      <c r="J645" s="2" t="inlineStr">
+        <is>
+          <t>xvplZOjy6ls</t>
+        </is>
+      </c>
+      <c r="K645" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B646" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C646" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭イリス編ガチャ評価 #ロマサガRS #shorts #ガチャ</t>
+        </is>
+      </c>
+      <c r="D646" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭イリス編のガチャ評価ショート。
+音声字幕がなく内容は映像中心。
+イリス編ガチャの短尺紹介。</t>
+        </is>
+      </c>
+      <c r="E646" s="2" t="inlineStr"/>
+      <c r="F646" s="2" t="inlineStr"/>
+      <c r="G646" s="2" t="inlineStr">
+        <is>
+          <t>・Romancing祭
+・イリス編
+・ガチャ評価
+・ショート</t>
+        </is>
+      </c>
+      <c r="H646" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VLrNyLpE_QI</t>
+        </is>
+      </c>
+      <c r="J646" s="2" t="inlineStr">
+        <is>
+          <t>VLrNyLpE_QI</t>
+        </is>
+      </c>
+      <c r="K646" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B647" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C647" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭鬼八編ガチャ評価 #ロマサガRS #shorts #ガチャ</t>
+        </is>
+      </c>
+      <c r="D647" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭鬼八編のガチャ評価ショート。
+音声字幕がなく内容は映像中心。
+鬼八編ガチャの短尺紹介。</t>
+        </is>
+      </c>
+      <c r="E647" s="2" t="inlineStr"/>
+      <c r="F647" s="2" t="inlineStr"/>
+      <c r="G647" s="2" t="inlineStr">
+        <is>
+          <t>・Romancing祭
+・鬼八編
+・ガチャ評価
+・ショート</t>
+        </is>
+      </c>
+      <c r="H647" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I647" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XnG9rRUXoHc</t>
+        </is>
+      </c>
+      <c r="J647" s="2" t="inlineStr">
+        <is>
+          <t>XnG9rRUXoHc</t>
+        </is>
+      </c>
+      <c r="K647" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B648" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C648" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】鬼八・ミーティア・おたま能力値早見表 ~この3姫の性能 ~めちゃ良いよ💞〜新 ~能力値早見表  ~完成⭐️</t>
+        </is>
+      </c>
+      <c r="D648" s="2" t="inlineStr">
+        <is>
+          <t>鬼八・ミーティア・お玉の能力値早見表を解説。
+鬼八がダントツの目玉で絶対に欲しい。
+お玉はカウンター55ヒットの高火力。</t>
+        </is>
+      </c>
+      <c r="E648" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八は今回の目玉で大当たり絶対欲しい
+・ミーティアは残サポーターで本人火力も良い
+・お玉はカウンター55ヒットとフォース付与が強い</t>
+        </is>
+      </c>
+      <c r="F648" s="2" t="inlineStr">
+        <is>
+          <t>・お玉は直接攻撃を受けるステージ限定で運用注意</t>
+        </is>
+      </c>
+      <c r="G648" s="2" t="inlineStr">
+        <is>
+          <t>・能力値早見表
+・鬼八編
+・ミーティア
+・お玉カウンター
+・フォース</t>
+        </is>
+      </c>
+      <c r="H648" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I648" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C7oa0j_lgHs</t>
+        </is>
+      </c>
+      <c r="J648" s="2" t="inlineStr">
+        <is>
+          <t>C7oa0j_lgHs</t>
+        </is>
+      </c>
+      <c r="K648" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B649" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C649" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】イリス・Diva No5・ウルピナ能力値早見表 ~陽パのサポーター・斬冷雷EXF   1.5倍・斬突44ヒット</t>
+        </is>
+      </c>
+      <c r="D649" s="2" t="inlineStr">
+        <is>
+          <t>イリス・ディバNo5・ウルピナの早見表解説。
+ウルピナは2ターンごとの火力がやばい。
+ディバは体力精神デバフ持ちの優秀サポ。</t>
+        </is>
+      </c>
+      <c r="E649" s="2" t="inlineStr">
+        <is>
+          <t>・ウルピナは2ターンごとの火力が許されるレベル
+・ディバNo5は体力精神デバフ持ちで火力サポ優秀
+・イリスは講師の白度継承で強いサポーター</t>
+        </is>
+      </c>
+      <c r="F649" s="2" t="inlineStr">
+        <is>
+          <t>・ウルピナは仲間サポートがない
+・イリスは早見表だと何か足りず継承必須
+・ディバはジュエル無い人は様子見でOK</t>
+        </is>
+      </c>
+      <c r="G649" s="2" t="inlineStr">
+        <is>
+          <t>・能力値早見表
+・ウルピナ
+・ディバNo5
+・体力精神デバフ
+・イリス</t>
+        </is>
+      </c>
+      <c r="H649" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I649" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HUU60FjtO30</t>
+        </is>
+      </c>
+      <c r="J649" s="2" t="inlineStr">
+        <is>
+          <t>HUU60FjtO30</t>
+        </is>
+      </c>
+      <c r="K649" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B650" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C650" s="2" t="inlineStr">
+        <is>
+          <t>ちゃむのYouTubeガチャ配信~久しぶりの配信やな…ワクワク☺️…「私を10連で取って」</t>
+        </is>
+      </c>
+      <c r="D650" s="2" t="inlineStr">
+        <is>
+          <t>久々のガチャ配信で鬼八を狙う。
+Wi-Fiトラブルと課金忘れで大混乱。
+SS大量も鬼八出ず天井コンプ確定。</t>
+        </is>
+      </c>
+      <c r="E650" s="2" t="inlineStr">
+        <is>
+          <t>・SSがめちゃくちゃ出た
+・鬼八はぶっ壊れ性能で強い
+・お玉は2.5倍フォースで移動でも使えそう</t>
+        </is>
+      </c>
+      <c r="F650" s="2" t="inlineStr">
+        <is>
+          <t>・Wi-Fiトラブルと課金忘れで配信が大混乱
+・爆発だけで肝心の鬼八が出ず天井コンプ
+・今年のガチャ運が悪くジュエルがピンチ</t>
+        </is>
+      </c>
+      <c r="G650" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ配信
+・鬼八狙い
+・天井コンプ
+・Wi-Fiトラブル
+・お玉</t>
+        </is>
+      </c>
+      <c r="H650" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I650" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lCzVE06xw1k</t>
+        </is>
+      </c>
+      <c r="J650" s="2" t="inlineStr">
+        <is>
+          <t>lCzVE06xw1k</t>
+        </is>
+      </c>
+      <c r="K650" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B651" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C651" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】交換期限迫る！7.5周年記念SSスタイル交換チケットオススメ交換候補最終版【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D651" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年SS交換チケのおすすめ最終版。
+継承候補技を持つスタイルを中心に紹介。
+遠征特化や無人島用の実用枠も解説。</t>
+        </is>
+      </c>
+      <c r="E651" s="2" t="inlineStr">
+        <is>
+          <t>・各種継承技で手持ちスタイルを強化できる
+・遠征特化スタイルは幻闘上で高ポテンシャル
+・バレンタインお玉のチョコ贈り物は無人島で価値上昇</t>
+        </is>
+      </c>
+      <c r="F651" s="2" t="inlineStr">
+        <is>
+          <t>・4月復刻の白姫など5体が交換対象外で残念
+・過去と現行の性能差が大きく即戦力は限定的
+・無料63連を回してから交換すべきで悩ましい</t>
+        </is>
+      </c>
+      <c r="G651" s="2" t="inlineStr">
+        <is>
+          <t>・SS交換チケット
+・継承候補
+・遠征特化
+・無人島
+・最終決定版</t>
+        </is>
+      </c>
+      <c r="H651" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I651" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=e1ei_fLInT4</t>
+        </is>
+      </c>
+      <c r="J651" s="2" t="inlineStr">
+        <is>
+          <t>e1ei_fLInT4</t>
+        </is>
+      </c>
+      <c r="K651" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B652" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C652" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】闘者の関門-スービエ- 周回編成7種紹介!!最速は自由枠1で6秒!!【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D652" s="2" t="inlineStr">
+        <is>
+          <t>関門スービエの周回編成7種を紹介。
+最速は自由枠1で6秒の高速周回。
+鬼八・ビクトール・配布アレツが活躍。</t>
+        </is>
+      </c>
+      <c r="E652" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八は実装ごとに毎回周回で出番がある
+・ビクトールはさすがに早い
+・配布アレツも20連攻撃で高性能</t>
+        </is>
+      </c>
+      <c r="F652" s="2" t="inlineStr">
+        <is>
+          <t>・関門は戦闘時間が短すぎて動画尺を稼げない</t>
+        </is>
+      </c>
+      <c r="G652" s="2" t="inlineStr">
+        <is>
+          <t>・関門スービエ
+・周回編成7種
+・6秒周回
+・鬼八
+・配布アレツ</t>
+        </is>
+      </c>
+      <c r="H652" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I652" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZLAsFUJioAw</t>
+        </is>
+      </c>
+      <c r="J652" s="2" t="inlineStr">
+        <is>
+          <t>ZLAsFUJioAw</t>
+        </is>
+      </c>
+      <c r="K652" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B653" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C653" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】残り数時間！制圧戦の追い込みだ!!【ロマンシング サガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D653" s="2" t="inlineStr">
+        <is>
+          <t>制圧戦の残り数時間を追い込みで周回。
+字幕はほぼ効果音のみの短尺動画。
+締切前の集回を促す内容。</t>
+        </is>
+      </c>
+      <c r="E653" s="2" t="inlineStr"/>
+      <c r="F653" s="2" t="inlineStr"/>
+      <c r="G653" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦
+・追い込み
+・周回
+・短尺</t>
+        </is>
+      </c>
+      <c r="H653" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I653" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=t6belsxTHOs</t>
+        </is>
+      </c>
+      <c r="J653" s="2" t="inlineStr">
+        <is>
+          <t>t6belsxTHOs</t>
+        </is>
+      </c>
+      <c r="K653" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T01:11:12Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K653"/>
+  <dimension ref="A1:K666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -43433,6 +43433,840 @@
         </is>
       </c>
     </row>
+    <row r="654">
+      <c r="A654" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B654" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C654" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「高火力」エクストラ斬冷雷1.5倍が自在に繰り出せるDiva No.5&amp;汎用性を究めたミーティアのサポート力!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D654" s="2" t="inlineStr">
+        <is>
+          <t>ディーバNo.5とミーティアの新スタイル性能考察
+ディーバは斬冷雷の属性引率で全体火力底上げが強力
+ミーティアは開幕特化の無難な汎用サポート</t>
+        </is>
+      </c>
+      <c r="E654" s="2" t="inlineStr">
+        <is>
+          <t>・波紋攻撃の置き物ステバフは環境最高峰の強さ
+・ディーバは短期決戦の火力ソースとして非常に強力
+・ミーティアは開幕エクストラ+DP増加が周回で便利</t>
+        </is>
+      </c>
+      <c r="F654" s="2" t="inlineStr">
+        <is>
+          <t>・ミーティアはイシスよりステバフが弱く微妙
+・ディーバは防御15%のみで通常高難度には不足
+・エクストラ1.25〜1.5倍ばら撒きは物足りない</t>
+        </is>
+      </c>
+      <c r="G654" s="2" t="inlineStr">
+        <is>
+          <t>・ディーバNo.5
+・ミーティア
+・エクストラ
+・属性引率
+・高難度評価</t>
+        </is>
+      </c>
+      <c r="H654" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I654" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OBS_jlDhvVc</t>
+        </is>
+      </c>
+      <c r="J654" s="2" t="inlineStr">
+        <is>
+          <t>OBS_jlDhvVc</t>
+        </is>
+      </c>
+      <c r="K654" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T07:42:53Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B655" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C655" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「将来性の塊」セレチケラスト!!ガチャ厳選勢最後に何取った!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D655" s="2" t="inlineStr">
+        <is>
+          <t>セレチケラストでガチャ厳選勢が何を取ったか紹介
+「将来性の塊」となる選択がテーマ
+字幕がほぼ空のため詳細は動画参照</t>
+        </is>
+      </c>
+      <c r="E655" s="2" t="inlineStr"/>
+      <c r="F655" s="2" t="inlineStr"/>
+      <c r="G655" s="2" t="inlineStr">
+        <is>
+          <t>・セレチケ
+・ガチャ厳選</t>
+        </is>
+      </c>
+      <c r="H655" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I655" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dG9Mx_hQl-o</t>
+        </is>
+      </c>
+      <c r="J655" s="2" t="inlineStr">
+        <is>
+          <t>dG9Mx_hQl-o</t>
+        </is>
+      </c>
+      <c r="K655" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T07:42:53Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B656" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C656" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　おたま入りで実戦　被弾する度に強くなる　聖王厄で実力判明！</t>
+        </is>
+      </c>
+      <c r="D656" s="2" t="inlineStr">
+        <is>
+          <t>おたま入り編成で聖王厄に実戦挑戦
+被弾でエクストラフォースをばら撒くおたまが活躍
+ダメブロと火力調整を決めて容易に撃破</t>
+        </is>
+      </c>
+      <c r="E656" s="2" t="inlineStr">
+        <is>
+          <t>・おたまの被弾時エクストラフォースばら撒きが強力
+・味方全体付与で破壊力が大きく上がる
+・暦読みとサイヴァの火力が高くほぼ締める</t>
+        </is>
+      </c>
+      <c r="F656" s="2" t="inlineStr">
+        <is>
+          <t>・火力が出すぎてHP調整が難しいおかしな仕様
+・確率付与のため受け切れるかは運次第</t>
+        </is>
+      </c>
+      <c r="G656" s="2" t="inlineStr">
+        <is>
+          <t>・おたま
+・エクストラフォース
+・聖王厄
+・ダメブロ調整</t>
+        </is>
+      </c>
+      <c r="H656" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I656" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0fGo0kz9AZw</t>
+        </is>
+      </c>
+      <c r="J656" s="2" t="inlineStr">
+        <is>
+          <t>0fGo0kz9AZw</t>
+        </is>
+      </c>
+      <c r="K656" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T07:42:53Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B657" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C657" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】F91(ツインヴェスバー)とりま100連！Shorts版#3 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D657" s="2" t="inlineStr">
+        <is>
+          <t>100連終盤でUR確定から狙いが全部揃う
+前回の悪い引きを払拭する会心の結果
+最後はグレートジオング狙いも届かず</t>
+        </is>
+      </c>
+      <c r="E657" s="2" t="inlineStr">
+        <is>
+          <t>・狙いのユニットが全部揃う会心の引き
+・前回の引きを払拭できて満足</t>
+        </is>
+      </c>
+      <c r="F657" s="2" t="inlineStr">
+        <is>
+          <t>・グレートジオングやフローレンスは出ず</t>
+        </is>
+      </c>
+      <c r="G657" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・100連ガチャ
+・UR確定
+・コンプ</t>
+        </is>
+      </c>
+      <c r="H657" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I657" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ElIbxQUZz0k</t>
+        </is>
+      </c>
+      <c r="J657" s="2" t="inlineStr">
+        <is>
+          <t>ElIbxQUZz0k</t>
+        </is>
+      </c>
+      <c r="K657" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T07:42:53Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B658" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C658" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】F91(ツインヴェスバー)とりま100連！Shorts版#2 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D658" s="2" t="inlineStr">
+        <is>
+          <t>100連中盤は演出なしの静かな展開が続く
+折り返し以降もピックSSRや昇格が出ず
+最後に限定サポーターを自引きして一矢報いる</t>
+        </is>
+      </c>
+      <c r="E658" s="2" t="inlineStr">
+        <is>
+          <t>・限定サポーター自引きはラクス以来の収穫
+・試作機のサポーター獲得は地味に嬉しい</t>
+        </is>
+      </c>
+      <c r="F658" s="2" t="inlineStr">
+        <is>
+          <t>・中盤は演出も昇格もなく寂しい区間
+・F90はピック期間を逃すと出づらい</t>
+        </is>
+      </c>
+      <c r="G658" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・100連ガチャ
+・限定サポーター
+・F90</t>
+        </is>
+      </c>
+      <c r="H658" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I658" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Nr41RWQJrc4</t>
+        </is>
+      </c>
+      <c r="J658" s="2" t="inlineStr">
+        <is>
+          <t>Nr41RWQJrc4</t>
+        </is>
+      </c>
+      <c r="K658" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T07:42:53Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B659" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C659" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】F91(ツインヴェスバー)とりま100連！Shorts版#1 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D659" s="2" t="inlineStr">
+        <is>
+          <t>F91ツインヴェスバー狙いの100連ガチャ前半
+序盤にUR確定演出からツインヴェスバー入手
+新規SSRも順調に出て幸先の良い滑り出し</t>
+        </is>
+      </c>
+      <c r="E659" s="2" t="inlineStr">
+        <is>
+          <t>・目玉のツインヴェスバーを早期に入手
+・今回は演出が多くキャラ付きSSRも豊富</t>
+        </is>
+      </c>
+      <c r="F659" s="2" t="inlineStr">
+        <is>
+          <t>・前回ナイチンゲール100連は出ず悲惨だった</t>
+        </is>
+      </c>
+      <c r="G659" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・100連ガチャ
+・F91
+・ツインヴェスバー</t>
+        </is>
+      </c>
+      <c r="H659" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I659" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=d1Sb-DiF24w</t>
+        </is>
+      </c>
+      <c r="J659" s="2" t="inlineStr">
+        <is>
+          <t>d1Sb-DiF24w</t>
+        </is>
+      </c>
+      <c r="K659" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T07:42:53Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B660" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C660" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】チート過ぎる！最強の矛鬼八＆盾おたま！超鬼門無人島シャムマベルを３ターンでゴリ押ししてしまう【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D660" s="2" t="inlineStr">
+        <is>
+          <t>新キャラ鬼八とおたまで超鬼門無人島シャムマベルへ
+装備・継承を工夫して3ターンでゴリ押しクリア
+おたまの被弾エクストラフォースばら撒きが攻略の鍵</t>
+        </is>
+      </c>
+      <c r="E660" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八は矛役として最強クラスの火力でチート過ぎる
+・おたまの被弾エクストラばら撒きが盾役として優秀
+・ターン開始バフ解除やクリーミードレスの工夫が刺さる</t>
+        </is>
+      </c>
+      <c r="F660" s="2" t="inlineStr">
+        <is>
+          <t>・1ターン目をチョコ無しで凌ぐ調整が非常に難しい
+・行動順が運次第でやり直し前提になる</t>
+        </is>
+      </c>
+      <c r="G660" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八
+・おたま
+・無人島シャムマベル
+・エクストラフォース
+・装備・継承</t>
+        </is>
+      </c>
+      <c r="H660" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I660" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=thkB2CFMaYM</t>
+        </is>
+      </c>
+      <c r="J660" s="2" t="inlineStr">
+        <is>
+          <t>thkB2CFMaYM</t>
+        </is>
+      </c>
+      <c r="K660" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T07:42:53Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B661" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C661" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】最強の鬼八がここに爆誕！闘者の関門周回で実力をさっそく発揮！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D661" s="2" t="inlineStr">
+        <is>
+          <t>新実装の鬼八で闘者の関門スービエを周回検証
+八奇来命で最速5秒、育成枠込みでも6〜7秒
+瀕死装備で火力が跳ね上がり1枠周回も可能に</t>
+        </is>
+      </c>
+      <c r="E661" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八は周回性能ぶっ壊れで1〜2年後も使われ得る
+・育成枠2〜3枠入れても余裕で周回可能
+・日輪装のサンダル瀕死編成で火力が跳ね上がる
+・波乗りスービエの演出が面白い</t>
+        </is>
+      </c>
+      <c r="F661" s="2" t="inlineStr">
+        <is>
+          <t>・新ガチャは虎の子ゼロで狙いを引けず
+・報酬はどれを選んでも大差なし</t>
+        </is>
+      </c>
+      <c r="G661" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八
+・闘者の関門
+・スービエ
+・周回
+・瀕死装備</t>
+        </is>
+      </c>
+      <c r="H661" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I661" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0a1AH12kpj8</t>
+        </is>
+      </c>
+      <c r="J661" s="2" t="inlineStr">
+        <is>
+          <t>0a1AH12kpj8</t>
+        </is>
+      </c>
+      <c r="K661" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T07:42:53Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B662" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C662" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】水着エレノアの性能が予想以上！？今月のロマンシングパス特典の内容をチェック！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D662" s="2" t="inlineStr">
+        <is>
+          <t>今月のロマンシングパス水着エレノアを性能チェック
+ターン経過で追撃とエクストラが強化され最大42ヒット
+パスキャラとしては破格の性能と高評価</t>
+        </is>
+      </c>
+      <c r="E662" s="2" t="inlineStr">
+        <is>
+          <t>・5ターン完成後の火力はパスキャラとして破格
+・3000ジュエルで確実に入手できてお得
+・無償ジュエルやおまけ特典も豪華</t>
+        </is>
+      </c>
+      <c r="F662" s="2" t="inlineStr">
+        <is>
+          <t>・立ち上がりが遅く短期決戦環境では活躍場所が少ない
+・味方を強化する要素を一切持たない
+・武器の精神デバフは現環境ではほぼ死に要素</t>
+        </is>
+      </c>
+      <c r="G662" s="2" t="inlineStr">
+        <is>
+          <t>・水着エレノア
+・ロマンシングパス
+・イグニッション
+・エクストラフォース</t>
+        </is>
+      </c>
+      <c r="H662" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I662" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LP-sPujDu2Q</t>
+        </is>
+      </c>
+      <c r="J662" s="2" t="inlineStr">
+        <is>
+          <t>LP-sPujDu2Q</t>
+        </is>
+      </c>
+      <c r="K662" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T07:42:53Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B663" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C663" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7月のロマンシングパスは買うべき？ロマパスキャラ・武器性能確認&amp;買うべきか【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D663" s="2" t="inlineStr">
+        <is>
+          <t>7月ロマンシングパスの上級・通常の中身を確認
+上級エレノアは完成後火力が高く「買って良い寄り」
+通常パス武器は必須感が薄くスルー判断</t>
+        </is>
+      </c>
+      <c r="E663" s="2" t="inlineStr">
+        <is>
+          <t>・エレノアは貴重な熱全体アタッカーで完成後火力が高い
+・最大アビバフ6100%以上・ステバフ3700%以上の火力
+・優勝分ジュエルが無償で返ってくるのも嬉しい</t>
+        </is>
+      </c>
+      <c r="F663" s="2" t="inlineStr">
+        <is>
+          <t>・完成まで5ターンかかり短期戦に不向き
+・置き物性能はゼロ
+・通常武器の精神デバフはソウルアビで代用可能で唯一性が低い</t>
+        </is>
+      </c>
+      <c r="G663" s="2" t="inlineStr">
+        <is>
+          <t>・ロマンシングパス
+・エレノア
+・パス武器
+・買うべきか</t>
+        </is>
+      </c>
+      <c r="H663" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I663" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UC3tVt1CduQ</t>
+        </is>
+      </c>
+      <c r="J663" s="2" t="inlineStr">
+        <is>
+          <t>UC3tVt1CduQ</t>
+        </is>
+      </c>
+      <c r="K663" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T07:42:53Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B664" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C664" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】関門スービエ ~火力足りない方向け ~7秒 ~鬼八の2パターン活用法</t>
+        </is>
+      </c>
+      <c r="D664" s="2" t="inlineStr">
+        <is>
+          <t>関門スービエ周回を火力帯別に3パターン解説
+鬼八＋継承キラメキで最短5秒が基本形
+火力不足なら来命OD使用か名心十六戦ODなしで7秒</t>
+        </is>
+      </c>
+      <c r="E664" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八入りが現最強で最短5秒周回が可能
+・火力不足でも7秒で回れる代替2パターンを用意</t>
+        </is>
+      </c>
+      <c r="F664" s="2" t="inlineStr">
+        <is>
+          <t>・火力が足りないと基本形の5秒は再現できない</t>
+        </is>
+      </c>
+      <c r="G664" s="2" t="inlineStr">
+        <is>
+          <t>・関門スービエ
+・鬼八
+・周回
+・キラメキ</t>
+        </is>
+      </c>
+      <c r="H664" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I664" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gESItaYq0KI</t>
+        </is>
+      </c>
+      <c r="J664" s="2" t="inlineStr">
+        <is>
+          <t>gESItaYq0KI</t>
+        </is>
+      </c>
+      <c r="K664" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T07:42:53Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B665" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C665" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【追いガチャ動画】貯めては回し 貯めては回し・・・【No.619】</t>
+        </is>
+      </c>
+      <c r="D665" s="2" t="inlineStr">
+        <is>
+          <t>水着ガチャに討伐で貯めたジュエルで追いガチャ40連
+60連まで渋かったが80〜90連で一気に排出
+天井前の90連で被りなしのまさかのコンプ達成</t>
+        </is>
+      </c>
+      <c r="E665" s="2" t="inlineStr">
+        <is>
+          <t>・90連被りなしコンプの会心の引き
+・討伐周回で貯めたジュエルが実った</t>
+        </is>
+      </c>
+      <c r="F665" s="2" t="inlineStr">
+        <is>
+          <t>・前回60連はネメシスのみと渋い結果だった</t>
+        </is>
+      </c>
+      <c r="G665" s="2" t="inlineStr">
+        <is>
+          <t>・追いガチャ
+・水着ガチャ
+・コンプ
+・天井</t>
+        </is>
+      </c>
+      <c r="H665" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I665" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pDU73ofbooA</t>
+        </is>
+      </c>
+      <c r="J665" s="2" t="inlineStr">
+        <is>
+          <t>pDU73ofbooA</t>
+        </is>
+      </c>
+      <c r="K665" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T07:42:53Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B666" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C666" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「鬼八 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D666" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭「鬼八編」3体のスタイル考察と格付け
+鬼八B+・ミーティアB・おたまA-の評価
+周回・置き物・無人島特攻と役割がきれいに分担</t>
+        </is>
+      </c>
+      <c r="E666" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八はウィーク時6倍の攻撃倍率がえげつない
+・おたまは1〜2ターン被ダメ92%軽減が脅威的
+・ミーティアは斬ウィーク2倍の置き物として優秀
+・チョコレートの贈り物継承なら無人島で活躍期待</t>
+        </is>
+      </c>
+      <c r="F666" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八はサポート皆無で高難度では弾かれる恐れ
+・鬼八は19ターン以降急激に息切れ
+・おたまのエクストラ付与は運ゲーで爆死要素あり
+・ミーティアは2ターン目に効果半減し継続性がない</t>
+        </is>
+      </c>
+      <c r="G666" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八
+・ミーティア
+・おたま
+・ロマンシング祭
+・格付け</t>
+        </is>
+      </c>
+      <c r="H666" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I666" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LkXEPFW1vLQ</t>
+        </is>
+      </c>
+      <c r="J666" s="2" t="inlineStr">
+        <is>
+          <t>LkXEPFW1vLQ</t>
+        </is>
+      </c>
+      <c r="K666" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03T07:42:53Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K666"/>
+  <dimension ref="A1:K676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -44267,6 +44267,686 @@
         </is>
       </c>
     </row>
+    <row r="667">
+      <c r="A667" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B667" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C667" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】副防具選択「痛恨のミス」3択を見誤るな!!アサガオのパレオ 日輪草のサンダル ハイビスカスの麦わら帽…それぞれの良さを徹底的に考える　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D667" s="2" t="inlineStr">
+        <is>
+          <t>今週イベントの副防具3択を徹底考察
+麦わら帽を1位に選ぶも判断に迷い
+サンダルのダメブロ自由付与が唯一無二と後悔気味</t>
+        </is>
+      </c>
+      <c r="E667" s="2" t="inlineStr">
+        <is>
+          <t>・サンダルのダメブロ1ターン自由付与は戦術幅が大きい
+・パレオの最大BP+5永続は必要時に確実に打破できる
+・麦わら帽は5ター目以降EXクリ1.5倍永続で長期戦向き</t>
+        </is>
+      </c>
+      <c r="F667" s="2" t="inlineStr">
+        <is>
+          <t>・パレオは使う機会が少なく永続効果も既存で足りがち
+・サンダルの攻防上げ数値は誤差でメリット薄い
+・麦わら帽は無人島専用で5ター目到達自体が稀
+・間違えて選んでも個別対応は不可の仕様</t>
+        </is>
+      </c>
+      <c r="G667" s="2" t="inlineStr">
+        <is>
+          <t>・副防具3択
+・朝顔のパレオ
+・日輪草のサンダル
+・麦わら帽
+・ランク付け</t>
+        </is>
+      </c>
+      <c r="H667" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I667" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-xXEvQ4Mg0o</t>
+        </is>
+      </c>
+      <c r="J667" s="2" t="inlineStr">
+        <is>
+          <t>-xXEvQ4Mg0o</t>
+        </is>
+      </c>
+      <c r="K667" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T01:06:51Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B668" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C668" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】水着ランク付け「EX全強化」超進化したおたまのぶっ壊れ性能をまとめ!!&amp;A.J.を継承しさらなる単体強化!!イリス　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D668" s="2" t="inlineStr">
+        <is>
+          <t>EX全強化おたまがぶっ壊れ性能に進化
+追撃火力とエクストラばら撒きが唯一無二
+イリスは高難度Sで防御と火力サポート両立</t>
+        </is>
+      </c>
+      <c r="E668" s="2" t="inlineStr">
+        <is>
+          <t>・おたまの追撃火力が最大6170%に到達し格段に向上
+・おたまのエクストラばら撒きはぶっ壊れで唯一無二
+・おたまはディフェンス77%も付きダメブロ2ターン継承で活躍
+・イリスは90%台防御と火力サポートを両立でき螺旋で活躍</t>
+        </is>
+      </c>
+      <c r="F668" s="2" t="inlineStr">
+        <is>
+          <t>・おたまの防御はバレンタインの天品のままが良かった
+・エクストラ全属性発動は7.5%と運ゲ要素
+・イリスは根本的に強いスタイルを混ぜると出力不足になる
+・イリスは飛び抜けた点がなく火力サポートも普通止まり</t>
+        </is>
+      </c>
+      <c r="G668" s="2" t="inlineStr">
+        <is>
+          <t>・水着ランク付け
+・おたまEX強化
+・エクストラばら撒き
+・イリス継承
+・特攻性能</t>
+        </is>
+      </c>
+      <c r="H668" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I668" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=b1iZjRF5Kpc</t>
+        </is>
+      </c>
+      <c r="J668" s="2" t="inlineStr">
+        <is>
+          <t>b1iZjRF5Kpc</t>
+        </is>
+      </c>
+      <c r="K668" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T01:06:51Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B669" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C669" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始274日目記録　絆愛　立花家を支える者</t>
+        </is>
+      </c>
+      <c r="D669" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣274日目のプレイ記録
+総合力・制圧率・開発が着実に前進
+大友家キャラ不足でイベント編成に苦戦</t>
+        </is>
+      </c>
+      <c r="E669" s="2" t="inlineStr">
+        <is>
+          <t>・育成30化で戦力が上げやすくなった
+・工場戦は戦術を練り113位まで上昇
+・島根を制圧しレベル93まで到達</t>
+        </is>
+      </c>
+      <c r="F669" s="2" t="inlineStr">
+        <is>
+          <t>・大友家キャラが全然おらずレスデンイベントがきつい
+・レスデンで火力不足でオート友軍がすぐ落ちる
+・森・政宗が強すぎて回転率が早く隣を避けるしかない
+・記録913位の壁が厳しい</t>
+        </is>
+      </c>
+      <c r="G669" s="2" t="inlineStr">
+        <is>
+          <t>・出陣274日目
+・制圧率44%
+・レスデンイベント
+・工場戦
+・開発・内政</t>
+        </is>
+      </c>
+      <c r="H669" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I669" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GwQv06frl5E</t>
+        </is>
+      </c>
+      <c r="J669" s="2" t="inlineStr">
+        <is>
+          <t>GwQv06frl5E</t>
+        </is>
+      </c>
+      <c r="K669" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T01:06:51Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B670" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C670" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　選択　限定防具どれにする？　ひとつ交換して実践！</t>
+        </is>
+      </c>
+      <c r="D670" s="2" t="inlineStr">
+        <is>
+          <t>無人島35回シャムーバベルを実践攻略
+新サンダルで木ハを一旦生存させて突破
+瀕死化＋魂アビ禁止で火力を確保し4ターン勝利</t>
+        </is>
+      </c>
+      <c r="E670" s="2" t="inlineStr">
+        <is>
+          <t>・木ハの火力が今回かなり良かった
+・サンダル装備で被弾しても一旦生存できる
+・瀕死化して魂アビを禁止したのが火力の決め手
+・ビンセントのダメブロ所持が勝因の一つ</t>
+        </is>
+      </c>
+      <c r="F670" s="2" t="inlineStr">
+        <is>
+          <t>・3ターンでは抜けられず条件の厳しい4ターン編成に
+・お玉は攻撃させると火力が下がるため攻撃不可
+・状態異常が入ると崩れるギリギリの戦い</t>
+        </is>
+      </c>
+      <c r="G670" s="2" t="inlineStr">
+        <is>
+          <t>・無人島35回
+・シャムーバベル
+・サンダル装備
+・瀕死活用
+・4ターン編成</t>
+        </is>
+      </c>
+      <c r="H670" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I670" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JlzgVdhfORU</t>
+        </is>
+      </c>
+      <c r="J670" s="2" t="inlineStr">
+        <is>
+          <t>JlzgVdhfORU</t>
+        </is>
+      </c>
+      <c r="K670" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T01:06:51Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B671" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C671" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　比較　関門：スービエvs鬼八　育成枠1体or4体で周回編成</t>
+        </is>
+      </c>
+      <c r="D671" s="2" t="inlineStr">
+        <is>
+          <t>関門スービエvs鬼八を周回タイム比較
+育成枠1体なら6秒の高速周回
+育成枠4体でも24秒で育成しつつ回せる</t>
+        </is>
+      </c>
+      <c r="E671" s="2" t="inlineStr">
+        <is>
+          <t>・育成枠1体なら6秒で瞬殺周回できる
+・育成枠4体でも24秒と十分速く育成も進む
+・瀕死時サンダルで短期戦の被弾を軽減</t>
+        </is>
+      </c>
+      <c r="F671" s="2" t="inlineStr">
+        <is>
+          <t>・育成枠4体は1体より周回タイムが遅くなる
+・短期戦だとHP満タ運用でも被弾が気になる</t>
+        </is>
+      </c>
+      <c r="G671" s="2" t="inlineStr">
+        <is>
+          <t>・関門周回
+・スービエ
+・鬼八
+・育成枠比較
+・周回タイム</t>
+        </is>
+      </c>
+      <c r="H671" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I671" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zV3RdDXcB-A</t>
+        </is>
+      </c>
+      <c r="J671" s="2" t="inlineStr">
+        <is>
+          <t>zV3RdDXcB-A</t>
+        </is>
+      </c>
+      <c r="K671" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T01:06:51Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B672" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C672" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみと比較でわかりやすい新ウルピナの真実！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D672" s="2" t="inlineStr">
+        <is>
+          <t>新ウルピナを暦みと直接比較検証
+暦みのダメージと汎用性が圧倒的
+ウルピナはボードゲージ不足が弱点</t>
+        </is>
+      </c>
+      <c r="E672" s="2" t="inlineStr">
+        <is>
+          <t>・暦みのダメージがえげつなく30億超を記録
+・暦みはどこでも継承を持ち込める汎用性が強み
+・暦みはボードゲージ75%クラスで覚醒も活きる</t>
+        </is>
+      </c>
+      <c r="F672" s="2" t="inlineStr">
+        <is>
+          <t>・ウルピナはボードゲージが低いのが致命的弱点
+・ウルピナはダメージが伸びず暦みの25億止まり
+・ウルピナは自己バフ不足で継承しない方がマシ
+・ノエルと違い事故回避が厳しく回しづらい</t>
+        </is>
+      </c>
+      <c r="G672" s="2" t="inlineStr">
+        <is>
+          <t>・新ウルピナ
+・暦みと比較
+・ボードゲージ
+・継承
+・ダメージ検証</t>
+        </is>
+      </c>
+      <c r="H672" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I672" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CiPrpc5fjjg</t>
+        </is>
+      </c>
+      <c r="J672" s="2" t="inlineStr">
+        <is>
+          <t>CiPrpc5fjjg</t>
+        </is>
+      </c>
+      <c r="K672" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T01:06:51Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B673" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C673" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】あなたのジュエル増やします...【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D673" s="2" t="inlineStr">
+        <is>
+          <t>今もらい逃しやすいジュエル獲得情報を紹介
+リポストキャンペーンとアンケートで2500獲得
+週末限定クエストの育成報酬も忘れず回収を</t>
+        </is>
+      </c>
+      <c r="E673" s="2" t="inlineStr">
+        <is>
+          <t>・公式ジュエルチャレンジ企画が面白く6150配布された
+・アンケート回答だけで1000ジュエルもらえてお得
+・週末クエストは育成成長反映100回付きで有用</t>
+        </is>
+      </c>
+      <c r="F673" s="2" t="inlineStr">
+        <is>
+          <t>・リポストキャンペーンがゲーム内未告知で知らない人が多い
+・4000リポスト達成が途中で止まっている
+・アンケート・キャンペーンは期限が近く見落としやすい</t>
+        </is>
+      </c>
+      <c r="G673" s="2" t="inlineStr">
+        <is>
+          <t>・ジュエル獲得
+・リポストキャンペーン
+・プレイヤーアンケート
+・週末限定クエスト
+・公式企画</t>
+        </is>
+      </c>
+      <c r="H673" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I673" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8Fe0-I9yZuY</t>
+        </is>
+      </c>
+      <c r="J673" s="2" t="inlineStr">
+        <is>
+          <t>8Fe0-I9yZuY</t>
+        </is>
+      </c>
+      <c r="K673" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T01:06:51Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B674" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C674" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】最強クラスが複数！？最新版ガチャ確保優先度ランキング【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D674" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年後・最新版ガチャ確保優先度を解説
+気ハが速度性能で純アタッカーながら最優先
+お玉は無人島必須級で第2位に</t>
+        </is>
+      </c>
+      <c r="E674" s="2" t="inlineStr">
+        <is>
+          <t>・気ハはエフェクトが速く周回人権級で最優先
+・気ハは追撃なしEX倍率型でレイド・関門で長く使える
+・お玉は無人島でエクストラばら撒きが必須級に強い
+・お玉は無人島以外でも普通に使える汎用性</t>
+        </is>
+      </c>
+      <c r="F674" s="2" t="inlineStr">
+        <is>
+          <t>・アタッカーは1ヶ月でインフレし価値が落ちやすい
+・ノエルのように最強でもすぐ抜かれる
+・周回速度でソウルアビ差が付く仕様は危険な面もある</t>
+        </is>
+      </c>
+      <c r="G674" s="2" t="inlineStr">
+        <is>
+          <t>・確保優先度ランキング
+・気ハ最優先
+・お玉
+・水着ガチャ
+・周回速度</t>
+        </is>
+      </c>
+      <c r="H674" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I674" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8GFsuXPqe6Y</t>
+        </is>
+      </c>
+      <c r="J674" s="2" t="inlineStr">
+        <is>
+          <t>8GFsuXPqe6Y</t>
+        </is>
+      </c>
+      <c r="K674" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T01:06:51Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B675" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C675" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「イリス 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D675" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭イリス編3スタイルを考察
+イリスはB、ディーバはB＋、ウルピナは火力特化
+条件・デメリットの見極めが評価の分かれ目</t>
+        </is>
+      </c>
+      <c r="E675" s="2" t="inlineStr">
+        <is>
+          <t>・イリスは被ダメ78%軽減で幻闘場・羅刹でエース級
+・イリスの技3が強力で将来の継承候補にもなる
+・ディーバは全能力600%上昇と3属性対応で汎用性が高い
+・ウルピナは44ヒットの凸アタッカーでトップティア火力</t>
+        </is>
+      </c>
+      <c r="F675" s="2" t="inlineStr">
+        <is>
+          <t>・イリスは陽属性・ウィーク・単体の3条件が厳しい
+・ディーバはOD上昇要素がなくサポートが別途必要
+・ウルピナは真夏の失礼剣で挑発が付くデメリット
+・ウルピナは脳筋系で味方の被ダメ軽減サポートが必須</t>
+        </is>
+      </c>
+      <c r="G675" s="2" t="inlineStr">
+        <is>
+          <t>・イリス編考察
+・イリス評価B
+・ディーバB＋
+・ウルピナ火力特化
+・継承候補</t>
+        </is>
+      </c>
+      <c r="H675" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I675" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=97NnFFHPXOo</t>
+        </is>
+      </c>
+      <c r="J675" s="2" t="inlineStr">
+        <is>
+          <t>97NnFFHPXOo</t>
+        </is>
+      </c>
+      <c r="K675" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T01:06:51Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B676" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C676" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベント解説 要注意点有り!!周回編成の紹介 選択クエストの解説 選んだ副防具の理由と使用感【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D676" s="2" t="inlineStr">
+        <is>
+          <t>新イベント・キャンベルマリンリゾートを解説
+選択クエストの副防具3択と選定理由を詳説
+周回のためサンダルを選択し使用感も検証</t>
+        </is>
+      </c>
+      <c r="E676" s="2" t="inlineStr">
+        <is>
+          <t>・サンダルは瀕死時で最大連待ち2800%を狙え自由枠を作れる
+・サンダルは制圧戦レイドの2ターン全滅で代用困難な貴重品
+・麦わら帽は長期戦ほど待値が高くなる
+・3障害2の凸熱弱点は通常攻撃で11秒周回可能</t>
+        </is>
+      </c>
+      <c r="F676" s="2" t="inlineStr">
+        <is>
+          <t>・選択クエストは1つしか選べず7/8まで要熟考
+・サンダルは代償ダメージで井戸では使えない
+・サンダルはエクストラフォース無しでドレスに劣る場面あり
+・麦わら帽は5ターン以上の高難度でしか使えない</t>
+        </is>
+      </c>
+      <c r="G676" s="2" t="inlineStr">
+        <is>
+          <t>・新イベント解説
+・選択クエスト
+・副防具3択
+・サンダル選択
+・周回編成</t>
+        </is>
+      </c>
+      <c r="H676" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I676" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nag1Xuf7Dwc</t>
+        </is>
+      </c>
+      <c r="J676" s="2" t="inlineStr">
+        <is>
+          <t>nag1Xuf7Dwc</t>
+        </is>
+      </c>
+      <c r="K676" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04T01:06:51Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K676"/>
+  <dimension ref="A1:K686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -44947,6 +44947,656 @@
         </is>
       </c>
     </row>
+    <row r="677">
+      <c r="A677" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B677" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C677" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「厳選勢最後のガチャ」ハーフアニバ7.5周年総決算!!ガチャ厳選勢誰を引く!?こよみ 鬼八 ボルカノ リアム ヴィンセントにおたま!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D677" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年ガチャを掛け合い形式で実況引き
+水着ガチャからすり抜け・爆死を連発
+最後は第3希望止まりでほぼ終了</t>
+        </is>
+      </c>
+      <c r="E677" s="2" t="inlineStr"/>
+      <c r="F677" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャがすり抜け続きで渋い引き
+・第3希望止まりで爆死気味</t>
+        </is>
+      </c>
+      <c r="G677" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年ガチャ
+・水着ガチャ
+・ガチャ実況
+・すり抜け
+・爆死</t>
+        </is>
+      </c>
+      <c r="H677" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I677" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2HnoF4YTiFk</t>
+        </is>
+      </c>
+      <c r="J677" s="2" t="inlineStr">
+        <is>
+          <t>2HnoF4YTiFk</t>
+        </is>
+      </c>
+      <c r="K677" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05T01:52:52Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B678" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C678" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】確定ガチャバレ「七」のつく日と言えば!?まだまだ続く夏真っ盛りに向けて行われるシーズナルイベントとは　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D678" s="2" t="inlineStr">
+        <is>
+          <t>「七」のつく日の確定ガチャ告知動画
+夏のシーズナルイベント開催を予告
+字幕は音楽主体で内容はほぼ取得できず</t>
+        </is>
+      </c>
+      <c r="E678" s="2" t="inlineStr"/>
+      <c r="F678" s="2" t="inlineStr"/>
+      <c r="G678" s="2" t="inlineStr">
+        <is>
+          <t>・確定ガチャ
+・七のつく日
+・シーズナルイベント
+・夏イベント</t>
+        </is>
+      </c>
+      <c r="H678" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I678" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=eqMb4U798LI</t>
+        </is>
+      </c>
+      <c r="J678" s="2" t="inlineStr">
+        <is>
+          <t>eqMb4U798LI</t>
+        </is>
+      </c>
+      <c r="K678" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05T01:52:52Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B679" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C679" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】結局使うならどっち？　エクストラフォース陽単体と陰単体比較実践対決</t>
+        </is>
+      </c>
+      <c r="D679" s="2" t="inlineStr">
+        <is>
+          <t>セフィロト戦で光(陽)PTと闇(陰)PTを比較
+陰PTは火力型で決着が早い
+防御型の陽PTでもイリスの火力が突出</t>
+        </is>
+      </c>
+      <c r="E679" s="2" t="inlineStr">
+        <is>
+          <t>・イリスがサポーターなのに火力トップで優秀
+・陰PTは火力が高く決着が早い
+・リラの火力が終盤しっかり伸びる
+・白バラがBP撒き・毒解除で活躍
+・ODのエクストラフォース陽が強力</t>
+        </is>
+      </c>
+      <c r="F679" s="2" t="inlineStr">
+        <is>
+          <t>・陽PT(防御型)はLP攻撃がきつく長期戦
+・白バラ採用でEPが後半枯渇しがち
+・ダリオは覚醒まで9ターンかかり火力が遅い</t>
+        </is>
+      </c>
+      <c r="G679" s="2" t="inlineStr">
+        <is>
+          <t>・セフィロト戦
+・陽単体vs陰単体
+・エクストラフォース
+・光PT/闇PT
+・イリス</t>
+        </is>
+      </c>
+      <c r="H679" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I679" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lgZzTfufSv8</t>
+        </is>
+      </c>
+      <c r="J679" s="2" t="inlineStr">
+        <is>
+          <t>lgZzTfufSv8</t>
+        </is>
+      </c>
+      <c r="K679" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05T01:52:52Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B680" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C680" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSRガンダムF90ⅡI タイプ 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D680" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSSRガンダムF90IIを紹介
+武装のアニメーションを見せるショート動画
+台詞のみで解説はなし</t>
+        </is>
+      </c>
+      <c r="E680" s="2" t="inlineStr"/>
+      <c r="F680" s="2" t="inlineStr"/>
+      <c r="G680" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ガンダムF90II
+・SSR
+・武装アニメ
+・ショート</t>
+        </is>
+      </c>
+      <c r="H680" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I680" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mdcDdJ4pI5g</t>
+        </is>
+      </c>
+      <c r="J680" s="2" t="inlineStr">
+        <is>
+          <t>mdcDdJ4pI5g</t>
+        </is>
+      </c>
+      <c r="K680" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05T01:52:52Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B681" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C681" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】最新版魂アビリティランキング！環境に合わせて評価あがった物多数紹介【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D681" s="2" t="inlineStr">
+        <is>
+          <t>環境変化を踏まえ魂アビリティを再ランキング
+1位は吸収系、敵弱体化・デバフ系が高評価
+ダメブロや行動速度系の価値が上昇</t>
+        </is>
+      </c>
+      <c r="E681" s="2" t="inlineStr">
+        <is>
+          <t>・吸収4は敵を弱らせ自分を強化する究極のチート
+・能力弱体・全能力アップ解除が高難度で刺さる
+・ダメージブロック系は価値が上がった
+・ラウンド開始の行動速度上下系が行動調整に有用</t>
+        </is>
+      </c>
+      <c r="F681" s="2" t="inlineStr">
+        <is>
+          <t>・全体力アップ系は他アビ増加で優先度が低下
+・排水の意思は入手困難で汎用性は高くない</t>
+        </is>
+      </c>
+      <c r="G681" s="2" t="inlineStr">
+        <is>
+          <t>・魂アビリティ
+・ランキング
+・吸収系
+・能力弱体解除
+・ダメージブロック
+・無人島</t>
+        </is>
+      </c>
+      <c r="H681" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I681" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JBTDVzVAJ6M</t>
+        </is>
+      </c>
+      <c r="J681" s="2" t="inlineStr">
+        <is>
+          <t>JBTDVzVAJ6M</t>
+        </is>
+      </c>
+      <c r="K681" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05T01:52:52Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B682" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C682" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】周年明けに化け物が！！5大ガチャランキング＆究極の選択3種の副防具解説、私はこれにした【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D682" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年の5大ガチャを使用感込みで再評価
+1位は気発(SSS8ヒット)で環境破壊級
+副防具は3種解説、私はダメブロのサンダル</t>
+        </is>
+      </c>
+      <c r="E682" s="2" t="inlineStr">
+        <is>
+          <t>・気発はSSS8ヒットで6億火力の化け物
+・お玉はチョコ継承で2ターン無敵が破格
+・サンダルのダメブロ→リレイズ生存戦法が強烈
+・イリスは属性ヒットリーダーで幻統でも活躍
+・麦わら帽子は5ターン以降の火力底上げが強力</t>
+        </is>
+      </c>
+      <c r="F682" s="2" t="inlineStr">
+        <is>
+          <t>・人間女は能力Eで火力が伸びにくい
+・フェルディナントは剣姫線の威力が低く罠
+・大当たりバックは序盤が弱く西洋アビスに刺さらない</t>
+        </is>
+      </c>
+      <c r="G682" s="2" t="inlineStr">
+        <is>
+          <t>・5大ガチャランキング
+・気発
+・お玉
+・副防具選択
+・無人島
+・7.5周年</t>
+        </is>
+      </c>
+      <c r="H682" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I682" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pt57iTFfUho</t>
+        </is>
+      </c>
+      <c r="J682" s="2" t="inlineStr">
+        <is>
+          <t>pt57iTFfUho</t>
+        </is>
+      </c>
+      <c r="K682" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05T01:52:52Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B683" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C683" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】SSS判定有★今年もあいつが破壊する！最新キャラランキング★【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D683" s="2" t="inlineStr">
+        <is>
+          <t>日曜恒例の最新キャラランキングを調整
+気発・お玉はトリプルSの特級戦力枠
+単体エクホ持ち増加でマイス枠は評価下げ</t>
+        </is>
+      </c>
+      <c r="E683" s="2" t="inlineStr">
+        <is>
+          <t>・気発は1回行動で6億の唯一無二の火力
+・お玉は挑発+ストック追撃で最強の盾
+・お玉のチョコ継承2ターン無敵は破格
+・イリスは双剣・属性ヒットリーダーでS評価</t>
+        </is>
+      </c>
+      <c r="F683" s="2" t="inlineStr">
+        <is>
+          <t>・ディーバ5は防御軽減75%が標準的でSS届かず
+・ウルピナは自己バフが薄く火力が伸びにくい
+・マイス枠(ラゼム/バルテルミ)は評価下げ</t>
+        </is>
+      </c>
+      <c r="G683" s="2" t="inlineStr">
+        <is>
+          <t>・最新キャラランキング
+・気発
+・お玉
+・イリス
+・特級戦力
+・無人島</t>
+        </is>
+      </c>
+      <c r="H683" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I683" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sbPsoxxwxp8</t>
+        </is>
+      </c>
+      <c r="J683" s="2" t="inlineStr">
+        <is>
+          <t>sbPsoxxwxp8</t>
+        </is>
+      </c>
+      <c r="K683" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05T01:52:52Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B684" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C684" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】真のおすすめスタイルはこれだ！7.5周年セレクトチケットおすすめスタイル最終版！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D684" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年セレクトチケットのおすすめ最終版
+交換期限7/9、7/7ガチャの技マシンに注意
+最新持ちなら技マシン優先、お玉ネメシス等</t>
+        </is>
+      </c>
+      <c r="E684" s="2" t="inlineStr">
+        <is>
+          <t>・お玉のチョコ継承は価値が跳ね上がった
+・ネメシスのジャッジメントシャドウは無人島必須
+・貝のアクアフォールは水着貝と相性抜群
+・イリスのヘブンズインペールは要編成で優秀
+・女神(赤ネサス)は今でも十分強い</t>
+        </is>
+      </c>
+      <c r="F684" s="2" t="inlineStr">
+        <is>
+          <t>・対応する最新スタイル未所持なら無理に交換不要
+・気発の発期ラメは価値が下がった
+・雷パは組む機会が少なく技マシンが使いにくい</t>
+        </is>
+      </c>
+      <c r="G684" s="2" t="inlineStr">
+        <is>
+          <t>・セレクトチケット
+・技マシン
+・7.5周年
+・お玉/ネメシス
+・交換期限
+・ケルビン枠</t>
+        </is>
+      </c>
+      <c r="H684" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I684" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=py-7_FQmS4Y</t>
+        </is>
+      </c>
+      <c r="J684" s="2" t="inlineStr">
+        <is>
+          <t>py-7_FQmS4Y</t>
+        </is>
+      </c>
+      <c r="K684" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05T01:52:52Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B685" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C685" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】猛者ひしめく水着キャラは引くべきか？にんげんおんなガチャ最終評価ランキング&amp;イベント防具選んでみた【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D685" s="2" t="inlineStr">
+        <is>
+          <t>終了間近の水着ガチャキャラを最終評価
+ネメシス・人間女は星1、貝は星2評価
+イベント防具は瀕死付きサンダルを選択</t>
+        </is>
+      </c>
+      <c r="E685" s="2" t="inlineStr">
+        <is>
+          <t>・貝は3ターン目以降の火ダメ軽減90%超で高難度向き
+・ネメシスは過去継承で無人島適性あり(星2)
+・貝は攻防バフが強力で高難度適性が高い</t>
+        </is>
+      </c>
+      <c r="F685" s="2" t="inlineStr">
+        <is>
+          <t>・ネメシスはエクホ自前無しで火力が出にくい(星1)
+・人間女はOD1.25倍が低く優先度低め(星1)
+・貝は5ターンかかり序盤のパワー不足が気になる</t>
+        </is>
+      </c>
+      <c r="G685" s="2" t="inlineStr">
+        <is>
+          <t>・水着キャラ最終評価
+・ネメシス
+・人間女
+・貝
+・イベント防具
+・無人島</t>
+        </is>
+      </c>
+      <c r="H685" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I685" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cyEtLQkYl9w</t>
+        </is>
+      </c>
+      <c r="J685" s="2" t="inlineStr">
+        <is>
+          <t>cyEtLQkYl9w</t>
+        </is>
+      </c>
+      <c r="K685" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05T01:52:52Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B686" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C686" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】解説付き！限定SS副防具どれを選べばいい？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D686" s="2" t="inlineStr">
+        <is>
+          <t>キャンベルマリンリゾートの限定SS副防具3種解説
+基本は火力底上げのハイビスカス麦わら帽子推奨
+第2候補は瀕死・無敵を作る日輪層のサンダル</t>
+        </is>
+      </c>
+      <c r="E686" s="2" t="inlineStr">
+        <is>
+          <t>・麦わら帽子は5ターン以降ダメージ1.5倍で高難度に重宝
+・サンダルは1ターン無敵と能動的瀕死化で唯一性あり
+・パレオの消費BP-5は周回で便利</t>
+        </is>
+      </c>
+      <c r="F686" s="2" t="inlineStr">
+        <is>
+          <t>・麦わら帽子は1~4ターン戦・レイドでは意味がない
+・パレオは使い所が想像しにくく優先度低め
+・麦わら帽子は将来エクホクリ重複で無意味化の恐れ</t>
+        </is>
+      </c>
+      <c r="G686" s="2" t="inlineStr">
+        <is>
+          <t>・限定SS副防具
+・麦わら帽子
+・日輪層のサンダル
+・朝顔のパレオ
+・キャンベルマリンリゾート</t>
+        </is>
+      </c>
+      <c r="H686" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I686" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RHD-_nR0Ss0</t>
+        </is>
+      </c>
+      <c r="J686" s="2" t="inlineStr">
+        <is>
+          <t>RHD-_nR0Ss0</t>
+        </is>
+      </c>
+      <c r="K686" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05T01:52:52Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K686"/>
+  <dimension ref="A1:K698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -45597,6 +45597,778 @@
         </is>
       </c>
     </row>
+    <row r="687">
+      <c r="A687" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B687" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C687" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今籠るべきはココ!?「魂アビリティロス」制圧戦終了で都市伝説的な閃きに賭けろ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D687" s="2" t="inlineStr">
+        <is>
+          <t>魂アビリティロス制圧戦が終了。
+次に籠るべき閃きスポットを提案。
+都市伝説的な閃き狙いに賭ける。</t>
+        </is>
+      </c>
+      <c r="E687" s="2" t="inlineStr"/>
+      <c r="F687" s="2" t="inlineStr"/>
+      <c r="G687" s="2" t="inlineStr">
+        <is>
+          <t>・魂アビリティ
+・制圧戦終了
+・閃き道場
+・周回スポット</t>
+        </is>
+      </c>
+      <c r="H687" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I687" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Q_Aq4I6M0Rc</t>
+        </is>
+      </c>
+      <c r="J687" s="2" t="inlineStr">
+        <is>
+          <t>Q_Aq4I6M0Rc</t>
+        </is>
+      </c>
+      <c r="K687" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T01:09:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B688" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C688" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】無尽塔37階から　どこまで行けるのか？　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D688" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔37階から先を生配信で挑戦。
+水着キャラの性能を実戦比較。
+イリスとビクトールの強さを再確認。</t>
+        </is>
+      </c>
+      <c r="E688" s="2" t="inlineStr">
+        <is>
+          <t>・イリスはサポーターなのに自己バフ込みで火力がえぐい
+・ビクトールのバフが火力を大きく底上げする
+・代々（ダイダイ）は安定して高火力
+・ディーバは回復量が大きく能力促進も優秀</t>
+        </is>
+      </c>
+      <c r="F688" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトールがいないと火力が全然出ず苦労する
+・ウルピナは豪体前提でやや扱いづらい
+・気ハ系は弱点が取れず全体だけでは抜けない</t>
+        </is>
+      </c>
+      <c r="G688" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔37階
+・水着キャラ考察
+・イリス
+・ビクトール
+・ディーバ</t>
+        </is>
+      </c>
+      <c r="H688" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I688" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8kozF32iAOQ</t>
+        </is>
+      </c>
+      <c r="J688" s="2" t="inlineStr">
+        <is>
+          <t>8kozF32iAOQ</t>
+        </is>
+      </c>
+      <c r="K688" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T01:09:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B689" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C689" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベ　水着　お知らせチェックして行こう！　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D689" s="2" t="inlineStr">
+        <is>
+          <t>水着イベのお知らせ確認と無人島攻略配信。
+37〜40階を各キャラで検証。
+ダンスオブポイズンは配置順で発動と判明。</t>
+        </is>
+      </c>
+      <c r="E689" s="2" t="inlineStr">
+        <is>
+          <t>・おたまが便利すぎて無人島が楽になる
+・イリスが実戦で良い働き
+・ミーティアの火力も好印象
+・キアチは火力が高い</t>
+        </is>
+      </c>
+      <c r="F689" s="2" t="inlineStr">
+        <is>
+          <t>・無人島はHPが多く道中が単調すぎる
+・ビンセントやグレーは単体専用で使いにくい
+・状態異常やBP管理が厄介な階が多い</t>
+        </is>
+      </c>
+      <c r="G689" s="2" t="inlineStr">
+        <is>
+          <t>・水着イベント
+・無人島36-40階
+・おたま
+・イリス
+・配置順の仕様</t>
+        </is>
+      </c>
+      <c r="H689" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I689" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cLjBB3X8nag</t>
+        </is>
+      </c>
+      <c r="J689" s="2" t="inlineStr">
+        <is>
+          <t>cLjBB3X8nag</t>
+        </is>
+      </c>
+      <c r="K689" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T01:09:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B690" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C690" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベ　水着　お知らせチェックして行こう！　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D690" s="2" t="inlineStr">
+        <is>
+          <t>水着ガチャのお知らせと引くキャラを検討。
+アクセはサンダルか排水かで悩む。
+6体の当たり外れを視聴者と議論。</t>
+        </is>
+      </c>
+      <c r="E690" s="2" t="inlineStr">
+        <is>
+          <t>・おたまは当たり確実で入手優先
+・キアチは火力が高く継承で秒殺周回可能
+・ミーティアの評価が高い</t>
+        </is>
+      </c>
+      <c r="F690" s="2" t="inlineStr">
+        <is>
+          <t>・リーバは6体中で一番微妙との声
+・気ハ8は弱点取れないと汎用性が低く高難度向きでない
+・クリエゴ（排水系）は上限まで火力が上がらない
+・無人島のHPが多すぎる</t>
+        </is>
+      </c>
+      <c r="G690" s="2" t="inlineStr">
+        <is>
+          <t>・水着ガチャ
+・アクセ選択
+・おたま
+・気ハ8
+・キャラ評価</t>
+        </is>
+      </c>
+      <c r="H690" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I690" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=z6OWyfRhxEc</t>
+        </is>
+      </c>
+      <c r="J690" s="2" t="inlineStr">
+        <is>
+          <t>z6OWyfRhxEc</t>
+        </is>
+      </c>
+      <c r="K690" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T01:09:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B691" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C691" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SRガンダムF90Ⅱ 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D691" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのショートＰＶ。
+SRガンダムF90IIの武装アニメを紹介。
+戦闘ボイス中心の短尺動画。</t>
+        </is>
+      </c>
+      <c r="E691" s="2" t="inlineStr"/>
+      <c r="F691" s="2" t="inlineStr"/>
+      <c r="G691" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ガンダムF90II
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H691" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I691" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2l7OlQtqJzc</t>
+        </is>
+      </c>
+      <c r="J691" s="2" t="inlineStr">
+        <is>
+          <t>2l7OlQtqJzc</t>
+        </is>
+      </c>
+      <c r="K691" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T01:09:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B692" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C692" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】迷ったけど追いガシャします！F91(ツインヴェスバー)追加100連！ 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D692" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルでF91追加100連ガチャ。
+ツインヴェスバー凸狙いで追いガシャ。
+UR率上ぶれでF91を2凸達成。</t>
+        </is>
+      </c>
+      <c r="E692" s="2" t="inlineStr">
+        <is>
+          <t>・UR率が上ぶれて引きが好調
+・F91ツインヴェスバーを2凸できた
+・待機戦突入で当たりが多かった</t>
+        </is>
+      </c>
+      <c r="F692" s="2" t="inlineStr">
+        <is>
+          <t>・F91確定枠にサポーターやカロが混ざる仕様が紛らわしい
+・演出が弱めで盛り上がりに欠ける場面あり</t>
+        </is>
+      </c>
+      <c r="G692" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・F91ツインヴェスバー
+・100連ガチャ
+・追いガシャ</t>
+        </is>
+      </c>
+      <c r="H692" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I692" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KOYoguHCJUM</t>
+        </is>
+      </c>
+      <c r="J692" s="2" t="inlineStr">
+        <is>
+          <t>KOYoguHCJUM</t>
+        </is>
+      </c>
+      <c r="K692" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T01:09:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B693" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C693" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ガチャと無尽塔36から</t>
+        </is>
+      </c>
+      <c r="D693" s="2" t="inlineStr">
+        <is>
+          <t>ガチャと無尽塔36階を生配信で攻略。
+おたまガチャは天井2連続の渋い結果。
+鬼8戦はデバフ不足で勝てず。</t>
+        </is>
+      </c>
+      <c r="E693" s="2" t="inlineStr">
+        <is>
+          <t>・おたまはくそ強く体勢が変わっても使える
+・フリクエのスペシャルマスは判定2倍でお得
+・おたまは今後も長く使える主力</t>
+        </is>
+      </c>
+      <c r="F693" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ運が悪く2連続で天井（ミーティアすり抜け）
+・ビンセントがいないと無尽塔36階4ターンは無理
+・鬼8戦はデバフキャラが揃わず勝てない
+・4秒なのに3秒表示になるバグが気になる</t>
+        </is>
+      </c>
+      <c r="G693" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔36階
+・おたまガチャ
+・フリクエ周回
+・鬼8戦
+・デバフ</t>
+        </is>
+      </c>
+      <c r="H693" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I693" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=T7psC8xtWo4</t>
+        </is>
+      </c>
+      <c r="J693" s="2" t="inlineStr">
+        <is>
+          <t>T7psC8xtWo4</t>
+        </is>
+      </c>
+      <c r="K693" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T01:09:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B694" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C694" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】次のガチャは●●濃厚？7月7日のガチャを徹底予想【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D694" s="2" t="inlineStr">
+        <is>
+          <t>7月7日のガチャ内容を徹底予想。
+七夕ログボ確定から七夕ガチャ濃厚と読む。
+エミリア編とラファエル編を大胆予想。</t>
+        </is>
+      </c>
+      <c r="E694" s="2" t="inlineStr">
+        <is>
+          <t>・七夕ログボが確定で7/7七夕ガチャは濃厚と予想
+・エミリア×レンの織姫彦星コンビに期待</t>
+        </is>
+      </c>
+      <c r="F694" s="2" t="inlineStr">
+        <is>
+          <t>・FFレコードキーパーコラボは今回は無さそう（公式が言及を避けている）</t>
+        </is>
+      </c>
+      <c r="G694" s="2" t="inlineStr">
+        <is>
+          <t>・7月7日ガチャ予想
+・七夕ガチャ
+・FFコラボ
+・エミリア編
+・ラファエル編</t>
+        </is>
+      </c>
+      <c r="H694" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I694" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=id4sB1rl5ak</t>
+        </is>
+      </c>
+      <c r="J694" s="2" t="inlineStr">
+        <is>
+          <t>id4sB1rl5ak</t>
+        </is>
+      </c>
+      <c r="K694" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T01:09:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B695" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C695" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】盗賊ギルド ~幻のイフリート 12手編成 ~</t>
+        </is>
+      </c>
+      <c r="D695" s="2" t="inlineStr">
+        <is>
+          <t>盗賊ギルド発の幻の12手編成を披露。
+ビクトール等で月下必水算を2回使用。
+仲間の知恵が生んだ特別編成を紹介。</t>
+        </is>
+      </c>
+      <c r="E695" s="2" t="inlineStr">
+        <is>
+          <t>・オリジナリティ溢れる魅惑の12手編成
+・BP補填を駆使したチート的な立ち回り</t>
+        </is>
+      </c>
+      <c r="F695" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトールの機嫌次第で13手止まりになることもある</t>
+        </is>
+      </c>
+      <c r="G695" s="2" t="inlineStr">
+        <is>
+          <t>・井戸
+・12手編成
+・盗賊ギルド
+・ビクトール</t>
+        </is>
+      </c>
+      <c r="H695" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I695" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UGeM5n_cCZs</t>
+        </is>
+      </c>
+      <c r="J695" s="2" t="inlineStr">
+        <is>
+          <t>UGeM5n_cCZs</t>
+        </is>
+      </c>
+      <c r="K695" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T01:09:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B696" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C696" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第127回シュウザーたちの井戸〜最適解パーティ考察〜👊ランク上位を目指そう👊</t>
+        </is>
+      </c>
+      <c r="D696" s="2" t="inlineStr">
+        <is>
+          <t>第127回シュウザーたちの井戸を事前考察。
+弱点は残属性でアタッカーの幅が広い。
+2ターンクリアの最適解パーティを予想。</t>
+        </is>
+      </c>
+      <c r="E696" s="2" t="inlineStr">
+        <is>
+          <t>・キアチは残塁フォース6倍からのS連打で活躍
+・ミーティアは残力補助とEP補助が優秀
+・リーバはサブアタッカー兼火力サポで優秀</t>
+        </is>
+      </c>
+      <c r="F696" s="2" t="inlineStr">
+        <is>
+          <t>・リーバの唯一の弱点は行動回数の少なさ</t>
+        </is>
+      </c>
+      <c r="G696" s="2" t="inlineStr">
+        <is>
+          <t>・シュウザー井戸
+・残属性
+・最適解パーティ
+・2ターンクリア
+・ガチャキャラ</t>
+        </is>
+      </c>
+      <c r="H696" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I696" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aDXS8pfbiC8</t>
+        </is>
+      </c>
+      <c r="J696" s="2" t="inlineStr">
+        <is>
+          <t>aDXS8pfbiC8</t>
+        </is>
+      </c>
+      <c r="K696" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T01:09:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B697" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C697" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ロマンシングバカンス2026第二弾を考察する配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D697" s="2" t="inlineStr">
+        <is>
+          <t>ロマンシングバカンス2026第二弾を考察配信。
+水着ガチャ2連続で引くキャラを吟味。
+考察フォーマットを強み弱み重視に刷新。</t>
+        </is>
+      </c>
+      <c r="E697" s="2" t="inlineStr">
+        <is>
+          <t>・復刻のツナライザー等マップ持ちが狙い目
+・鬼系はため技6ループで18〜19ターン戦えレイドでも強い
+・水着スタイルは5倍アビリティ適用で優秀
+・考察を強み弱み明確化して新規にも分かりやすく改善</t>
+        </is>
+      </c>
+      <c r="F697" s="2" t="inlineStr">
+        <is>
+          <t>・同一キャラ別スタイルの能力アップ3倍が技術3倍になるバグ
+・排水（ソウルアビリティ）が無人島の設計を壊すガンで禁止を望む
+・新メロセロは壁役として不要だった感
+・無人島はHPが多く運営も手抜きと言うほど単調</t>
+        </is>
+      </c>
+      <c r="G697" s="2" t="inlineStr">
+        <is>
+          <t>・バカンス2026第二弾
+・水着ガチャ
+・スタイル考察
+・排水問題
+・無人島</t>
+        </is>
+      </c>
+      <c r="H697" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I697" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TVb-Afi0jzY</t>
+        </is>
+      </c>
+      <c r="J697" s="2" t="inlineStr">
+        <is>
+          <t>TVb-Afi0jzY</t>
+        </is>
+      </c>
+      <c r="K697" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T01:09:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B698" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C698" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】暇になったら記憶再戦はココ!!魂アビリティ閃き道場!?成長判定回数1日最高10,800回!!【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D698" s="2" t="inlineStr">
+        <is>
+          <t>魂アビリティ閃き道場の周回効率を検証。
+フリクエのスペシャル/チャレンジは判定2倍。
+弱点別のおすすめ周回場所も紹介。</t>
+        </is>
+      </c>
+      <c r="E698" s="2" t="inlineStr">
+        <is>
+          <t>・スペシャルとチャレンジは成長判定2倍で魂上げが効率的
+・神より明らかに魂アビリティが閃きやすい
+・魂関連上げでフリクエの周回優先度が上がった</t>
+        </is>
+      </c>
+      <c r="F698" s="2" t="inlineStr">
+        <is>
+          <t>・神マスは判定1回で非効率
+・連磨素材が足りるなら第2候補止まりの周回</t>
+        </is>
+      </c>
+      <c r="G698" s="2" t="inlineStr">
+        <is>
+          <t>・魂アビリティ
+・成長判定回数
+・フリクエ周回
+・スペシャル/チャレンジ
+・おすすめ場所</t>
+        </is>
+      </c>
+      <c r="H698" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I698" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NyKnKSlZmIc</t>
+        </is>
+      </c>
+      <c r="J698" s="2" t="inlineStr">
+        <is>
+          <t>NyKnKSlZmIc</t>
+        </is>
+      </c>
+      <c r="K698" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06T01:09:24Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K698"/>
+  <dimension ref="A1:K710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -46369,6 +46369,776 @@
         </is>
       </c>
     </row>
+    <row r="699">
+      <c r="A699" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B699" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C699" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「セミファイナル」7.5周年VS水着→27体9ガチャランキング!!最新スタイル比較検討会→2026年6月25日版　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D699" s="2" t="inlineStr">
+        <is>
+          <t>7.5周年VS水着の27体9ガチャランキング
+バルテルミーがマイス型最優秀と高評価
+ネメシスは新型だが現環境では火力弱め</t>
+        </is>
+      </c>
+      <c r="E699" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミーはエクストラ1.5倍付与+全体連打で最優秀
+・サイバ・ビンセントはエクストラ付与環境で外しづらい強さ</t>
+        </is>
+      </c>
+      <c r="F699" s="2" t="inlineStr">
+        <is>
+          <t>・ネメシスは現環境のアタッカーでは弱め、回避も消失
+・暦読み編のガチャは引きたくないほど渋い</t>
+        </is>
+      </c>
+      <c r="G699" s="2" t="inlineStr">
+        <is>
+          <t>・9ガチャランキング
+・バルテルミー
+・ネメシス
+・サイバ
+・ビンセント
+・確保優先度</t>
+        </is>
+      </c>
+      <c r="H699" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I699" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0_buUaYjd2I</t>
+        </is>
+      </c>
+      <c r="J699" s="2" t="inlineStr">
+        <is>
+          <t>0_buUaYjd2I</t>
+        </is>
+      </c>
+      <c r="K699" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07T02:03:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B700" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C700" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「末代まで後悔!?」ハイビスカスの麦わら帽を取った男の末路　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D700" s="2" t="inlineStr">
+        <is>
+          <t>報酬でハイビスカスの麦わら帽を選んだ男
+本来欲しかった物を取り逃す痛恨のミス
+交換ミスは末代まで後悔、選択は慎重に</t>
+        </is>
+      </c>
+      <c r="E700" s="2" t="inlineStr"/>
+      <c r="F700" s="2" t="inlineStr">
+        <is>
+          <t>・報酬アイテムの取り間違えは後悔が大きい</t>
+        </is>
+      </c>
+      <c r="G700" s="2" t="inlineStr">
+        <is>
+          <t>・交換所
+・麦わら帽
+・取り間違え
+・水着イベント</t>
+        </is>
+      </c>
+      <c r="H700" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I700" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UZ8fEe3Eo0A</t>
+        </is>
+      </c>
+      <c r="J700" s="2" t="inlineStr">
+        <is>
+          <t>UZ8fEe3Eo0A</t>
+        </is>
+      </c>
+      <c r="K700" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07T02:03:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B701" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C701" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ローズ!?「過去最大」水着推しキャラ到来で我々のジュエルは枯渇!!いつまで続く水着によるジュエル搾取　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D701" s="2" t="inlineStr">
+        <is>
+          <t>水着推しキャラ到来でジュエルが枯渇
+棚夕は来るがコスプレなしでシンディ登場
+花火玉集めやログボ・ミッションを忘れず</t>
+        </is>
+      </c>
+      <c r="E701" s="2" t="inlineStr">
+        <is>
+          <t>・花火玉を集めて交換するログボがお得
+・シンディキャンベルが尖った性能で強そう</t>
+        </is>
+      </c>
+      <c r="F701" s="2" t="inlineStr">
+        <is>
+          <t>・水着ラッシュでジュエルが搾取され続ける
+・前回の副防具サンダル取り違えのような事故に注意</t>
+        </is>
+      </c>
+      <c r="G701" s="2" t="inlineStr">
+        <is>
+          <t>・水着ガチャ
+・ジュエル枯渇
+・花火玉ログボ
+・シンディ
+・サガフロ記念</t>
+        </is>
+      </c>
+      <c r="H701" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I701" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yErAUTrNKd8</t>
+        </is>
+      </c>
+      <c r="J701" s="2" t="inlineStr">
+        <is>
+          <t>yErAUTrNKd8</t>
+        </is>
+      </c>
+      <c r="K701" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07T02:03:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B702" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C702" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今回の無尽塔30層　本音　所感や最適編成について</t>
+        </is>
+      </c>
+      <c r="D702" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔30層メタルアルカイザー戦を解説
+排水の意思持ちビクトールが最適解
+HP1200億の超長期戦で運要素も大きい</t>
+        </is>
+      </c>
+      <c r="E702" s="2" t="inlineStr">
+        <is>
+          <t>・排水の意思持ちビクトールが最適でオート運用可
+・挑発+カウンター編成で単体攻撃を捌ける</t>
+        </is>
+      </c>
+      <c r="F702" s="2" t="inlineStr">
+        <is>
+          <t>・HP1200億で超長期戦になりきつい
+・女神編成はダメブロ確率頼みで運ゲ
+・ユリアン手動編成では7時間47分かかった</t>
+        </is>
+      </c>
+      <c r="G702" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔30層
+・メタルアルカイザー
+・排水の意思
+・ビクトール
+・挑発・カウンター
+・ユリアン編成</t>
+        </is>
+      </c>
+      <c r="H702" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I702" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4SZh-FMnQu4</t>
+        </is>
+      </c>
+      <c r="J702" s="2" t="inlineStr">
+        <is>
+          <t>4SZh-FMnQu4</t>
+        </is>
+      </c>
+      <c r="K702" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07T02:03:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B703" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C703" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】みんな大好き水着　本番　気になるキャラ見よう！　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D703" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔30回超えに挑む参加型ロング配信
+排水のビクトール推奨で他は超長期戦
+HP1200億の単調ギミックは長すぎと不満</t>
+        </is>
+      </c>
+      <c r="E703" s="2" t="inlineStr">
+        <is>
+          <t>・排水ビクトールなら3〜4時間で比較的早くクリア可
+・苦戦しつつも30回を無事クリアできた</t>
+        </is>
+      </c>
+      <c r="F703" s="2" t="inlineStr">
+        <is>
+          <t>・HP1200億でターン数かけすぎ、単調で長すぎる
+・12時間ルールでアプリが落ちる仕様がきつい
+・このままだと無人島を回さなくなりそうと苦言</t>
+        </is>
+      </c>
+      <c r="G703" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔30回
+・メタルアルカイザー
+・排水ビクトール
+・12時間ルール
+・ユリアン編成
+・運営への要望</t>
+        </is>
+      </c>
+      <c r="H703" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I703" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MJIPfQDT0fE</t>
+        </is>
+      </c>
+      <c r="J703" s="2" t="inlineStr">
+        <is>
+          <t>MJIPfQDT0fE</t>
+        </is>
+      </c>
+      <c r="K703" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07T02:03:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B704" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C704" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】まだまだ水着は続く  7月7日更新情報まとめ 【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D704" s="2" t="inlineStr">
+        <is>
+          <t>7月7日サガフロ発売日記念更新情報まとめ
+メイレン編・エミリア編で10キャラ大量登場
+花火大会ログボは最大1.5万ジュエル</t>
+        </is>
+      </c>
+      <c r="E704" s="2" t="inlineStr">
+        <is>
+          <t>・今回のヒューズはコ棒でなくSSで登場
+・新スタイル10キャラが一気に強化されそう
+・真夏の大花火ログボは最大1.5万ジュエルとお得</t>
+        </is>
+      </c>
+      <c r="F704" s="2" t="inlineStr">
+        <is>
+          <t>・ホームBGMが10日更新表記で切替が早すぎ気味</t>
+        </is>
+      </c>
+      <c r="G704" s="2" t="inlineStr">
+        <is>
+          <t>・サガフロ発売日記念
+・メイレン編
+・エミリア編
+・ヒューズSS
+・真夏の花火ログボ
+・星に願い</t>
+        </is>
+      </c>
+      <c r="H704" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I704" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QRI4bVB3dRg</t>
+        </is>
+      </c>
+      <c r="J704" s="2" t="inlineStr">
+        <is>
+          <t>QRI4bVB3dRg</t>
+        </is>
+      </c>
+      <c r="K704" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07T02:03:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B705" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C705" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSRガンダムF90(火星独立ジオン軍仕様) 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D705" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSSRガンダムF90
+火星独立ジオン軍仕様の武装アニメ紹介
+タイプC相手に圧倒する演出のShort動画</t>
+        </is>
+      </c>
+      <c r="E705" s="2" t="inlineStr"/>
+      <c r="F705" s="2" t="inlineStr"/>
+      <c r="G705" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ガンダムF90
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H705" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I705" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WehhBfrHeZM</t>
+        </is>
+      </c>
+      <c r="J705" s="2" t="inlineStr">
+        <is>
+          <t>WehhBfrHeZM</t>
+        </is>
+      </c>
+      <c r="K705" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07T02:03:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B706" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C706" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】常夏のサガフロ！アセルスが来ない・・怪しいぞ。神速の公式最新情報確認【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D706" s="2" t="inlineStr">
+        <is>
+          <t>7月更新の公式最新情報を確認する配信
+ヒューズ・エミリア・タコおじさんが登場
+水着露出多くYouTube検索に弾かれる問題</t>
+        </is>
+      </c>
+      <c r="E706" s="2" t="inlineStr">
+        <is>
+          <t>・待望の銃タイプSSが来て嬉しい
+・タコおじさん(T260)の再登場が嬉しい
+・エミリアは毎回強く今回も期待</t>
+        </is>
+      </c>
+      <c r="F706" s="2" t="inlineStr">
+        <is>
+          <t>・水着の露出が多くYouTube検索に引っかからず画像を出せない
+・アセルスが来ないのが怪しい</t>
+        </is>
+      </c>
+      <c r="G706" s="2" t="inlineStr">
+        <is>
+          <t>・サガフロ発売日記念
+・ヒューズ
+・タコおじさん(T260)
+・銃スタイル
+・エミリア
+・水着</t>
+        </is>
+      </c>
+      <c r="H706" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I706" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=c9ZDfTcAU5o</t>
+        </is>
+      </c>
+      <c r="J706" s="2" t="inlineStr">
+        <is>
+          <t>c9ZDfTcAU5o</t>
+        </is>
+      </c>
+      <c r="K706" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07T02:03:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B707" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C707" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】無尽塔30からLet's go😻</t>
+        </is>
+      </c>
+      <c r="D707" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔30から挑む長時間の参加型配信
+魂アビ全獲得しビクトールの回避性能を絶賛
+排水習得と暦読み・裁判の専用武器確保</t>
+        </is>
+      </c>
+      <c r="E707" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトールの魂アビ(自己挑発+ブロッキング+天身)で回避が優秀
+・排水は汎用性が高くレイド周回も短縮できる
+・暦読み・裁判の専用武器は強力で確保優先</t>
+        </is>
+      </c>
+      <c r="F707" s="2" t="inlineStr">
+        <is>
+          <t>・鬼ハの今回の性能にはがっかり
+・女性側の水着キャラを引けていない
+・ビクトールの魅力が285回でも覚えず渋い</t>
+        </is>
+      </c>
+      <c r="G707" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔30
+・魂アビリティ
+・ビクトール
+・排水の意思
+・暦読み・裁判の専用武器
+・水着ガチャ</t>
+        </is>
+      </c>
+      <c r="H707" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I707" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6KxQZxeKBy0</t>
+        </is>
+      </c>
+      <c r="J707" s="2" t="inlineStr">
+        <is>
+          <t>6KxQZxeKBy0</t>
+        </is>
+      </c>
+      <c r="K707" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07T02:03:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B708" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C708" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】何かが起こる！？今回のお知らせに隠された秘密にみんな気付いた？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D708" s="2" t="inlineStr">
+        <is>
+          <t>7月7日の新お知らせに隠れた秘密を考察
+メイレン・ドール・タコおじさん実装で歓喜
+花火1.5万ジュエルとBGM異例更新に注目</t>
+        </is>
+      </c>
+      <c r="E708" s="2" t="inlineStr">
+        <is>
+          <t>・メイレン・ドール・タコおじさん実装でテンション上昇
+・星に願いの2000ジュエル固定は素晴らしい選択
+・水着第3弾で今夏を満喫できる</t>
+        </is>
+      </c>
+      <c r="F708" s="2" t="inlineStr">
+        <is>
+          <t>・大型でもないのに1.5万ジュエル配布は裏があると勘繰る
+・ホームBGMが3日で切替わる異例で真意が読めない</t>
+        </is>
+      </c>
+      <c r="G708" s="2" t="inlineStr">
+        <is>
+          <t>・お知らせ考察
+・メイレン編
+・タコおじさん初実装
+・真夏の花火1.5万
+・ホームBGM異例
+・星に願い2000</t>
+        </is>
+      </c>
+      <c r="H708" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I708" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Qqoh5tWGe3w</t>
+        </is>
+      </c>
+      <c r="J708" s="2" t="inlineStr">
+        <is>
+          <t>Qqoh5tWGe3w</t>
+        </is>
+      </c>
+      <c r="K708" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07T02:03:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B709" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C709" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベント解説 要注意点有り!! 周回編成も紹介【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D709" s="2" t="inlineStr">
+        <is>
+          <t>ラグナの水鉄砲イベントの解説と注意点
+最終防衛システムは冷続60ヒットで撃破
+星に願いの選択は連磨席セット推奨</t>
+        </is>
+      </c>
+      <c r="E709" s="2" t="inlineStr">
+        <is>
+          <t>・周回難易度は低めで11秒編成で流せる
+・最終防衛システムは冷続ヒット60回で確実に突破可</t>
+        </is>
+      </c>
+      <c r="F709" s="2" t="inlineStr">
+        <is>
+          <t>・配布武器の進化素材は約2780周必要できつい
+・制圧戦と重なり交換の優先順位付けが必要
+・交換所の期限が1週間と短い</t>
+        </is>
+      </c>
+      <c r="G709" s="2" t="inlineStr">
+        <is>
+          <t>・ラグナの水鉄砲
+・周回編成
+・最終防衛システム
+・冷続性
+・星に願い
+・制圧戦</t>
+        </is>
+      </c>
+      <c r="H709" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I709" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Srdc_3gSndI</t>
+        </is>
+      </c>
+      <c r="J709" s="2" t="inlineStr">
+        <is>
+          <t>Srdc_3gSndI</t>
+        </is>
+      </c>
+      <c r="K709" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07T02:03:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B710" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C710" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】魂アビリティ閃き道場!?閃き抽選回数1日最大10,800回!!結果を流し見【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D710" s="2" t="inlineStr">
+        <is>
+          <t>魂アビリティの閃き道場を回した記録
+閃き抽選は1日最大10,800回まで可能
+大量抽選の結果をBGMと共に流し見</t>
+        </is>
+      </c>
+      <c r="E710" s="2" t="inlineStr">
+        <is>
+          <t>・閃き抽選が1日最大10,800回と大量に回せる</t>
+        </is>
+      </c>
+      <c r="F710" s="2" t="inlineStr"/>
+      <c r="G710" s="2" t="inlineStr">
+        <is>
+          <t>・魂アビリティ
+・閃き道場
+・閃き抽選
+・流し見</t>
+        </is>
+      </c>
+      <c r="H710" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I710" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=m4el4dTyZ1E</t>
+        </is>
+      </c>
+      <c r="J710" s="2" t="inlineStr">
+        <is>
+          <t>m4el4dTyZ1E</t>
+        </is>
+      </c>
+      <c r="K710" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07T02:03:55Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K710"/>
+  <dimension ref="A1:K725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -47139,6 +47139,984 @@
         </is>
       </c>
     </row>
+    <row r="711">
+      <c r="A711" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B711" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C711" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「打無限」増幅バフ…最後の刺客！？メイレン&amp;ただのマスコットに収まらない32連打エクストラ冷1.5倍のタコおじさん!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D711" s="2" t="inlineStr">
+        <is>
+          <t>打属性無限増幅型メイレンの性能を辛口評価
+拡張性1.25倍止まりで中途半端と指摘
+タコおじは霊編成ファンプレイ向けと結論</t>
+        </is>
+      </c>
+      <c r="E711" s="2" t="inlineStr">
+        <is>
+          <t>・全体バフはいつも通り強い
+・タコおじのエクストラ永続付与は良い
+・タコおじの防御75%はなかなか良い</t>
+        </is>
+      </c>
+      <c r="F711" s="2" t="inlineStr">
+        <is>
+          <t>・メイレンは拡張性1.25倍で強く感じない
+・属性縛りがただの縛りで弱い
+・メイレンは防御50%に下げられ不遇
+・タコおじは立ち上がり遅く使い所がない</t>
+        </is>
+      </c>
+      <c r="G711" s="2" t="inlineStr">
+        <is>
+          <t>・メイレン性能
+・タコおじ性能
+・無限増幅バフ
+・属性縛り編成
+・高難度評価</t>
+        </is>
+      </c>
+      <c r="H711" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I711" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YGlgYV_Adig</t>
+        </is>
+      </c>
+      <c r="J711" s="2" t="inlineStr">
+        <is>
+          <t>YGlgYV_Adig</t>
+        </is>
+      </c>
+      <c r="K711" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T13:54:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B712" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C712" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】サライを凌ぐ「全体SS20連打」デバフに弱化とサポートもOKヒューズ&amp;打熱陽エクストラ組み合わせで常時1.5倍置物に継承で1.75倍エミリアの継承汎用性!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D712" s="2" t="inlineStr">
+        <is>
+          <t>ヒューズは全体SS20連打で特攻性が高い
+エミリアはエクストラ拡張が救いの無難サポ
+2体ならヒューズ推奨と結論づける</t>
+        </is>
+      </c>
+      <c r="E712" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズの2ターン全体41ヒットが強力
+・ヒューズは安定感がある
+・エミリアのエクストラ武器は強い
+・エミリアはデバフ/BP対策で対応力あり</t>
+        </is>
+      </c>
+      <c r="F712" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズはエクストラ拡張がなく連続性に難
+・エミリアは個人火力含め全体が無難すぎる
+・エミリアは根本的にそんなに強くない</t>
+        </is>
+      </c>
+      <c r="G712" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズ性能
+・エミリア性能
+・全体SS20連打
+・エクストラ付与
+・継承汎用性</t>
+        </is>
+      </c>
+      <c r="H712" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I712" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uReGYE0hB6E</t>
+        </is>
+      </c>
+      <c r="J712" s="2" t="inlineStr">
+        <is>
+          <t>uReGYE0hB6E</t>
+        </is>
+      </c>
+      <c r="K712" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T13:54:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B713" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C713" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】集いし願いを　結果にある違和感が　疑問に思う事とは</t>
+        </is>
+      </c>
+      <c r="D713" s="2" t="inlineStr">
+        <is>
+          <t>星2「集いし願い」イベントの結果を報告
+連魔防具素材が多く選ばれた点に疑問
+月1の短期連魔特化イベントを運営へ提案</t>
+        </is>
+      </c>
+      <c r="E713" s="2" t="inlineStr">
+        <is>
+          <t>・イベントが結構楽しかった
+・良い結果が出て嬉しい
+・ソウルピースやジュエルが出た</t>
+        </is>
+      </c>
+      <c r="F713" s="2" t="inlineStr">
+        <is>
+          <t>・連魔周回がきついという声が多い
+・連魔素材がなぜ多いのか疑問</t>
+        </is>
+      </c>
+      <c r="G713" s="2" t="inlineStr">
+        <is>
+          <t>・集いし願い結果
+・連魔防具素材
+・ロマパス
+・周回負担
+・運営への提案</t>
+        </is>
+      </c>
+      <c r="H713" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I713" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZjVEqGhtrwk</t>
+        </is>
+      </c>
+      <c r="J713" s="2" t="inlineStr">
+        <is>
+          <t>ZjVEqGhtrwk</t>
+        </is>
+      </c>
+      <c r="K713" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T13:54:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B714" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C714" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】無償ジュエル110連分は犠牲になりました『サガ フロンティア発売日記念 Romancing祭 メイレン編＆エミリア編』【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D714" s="2" t="inlineStr">
+        <is>
+          <t>エミリア編を無償110連から回すも爆死
+すり抜け連発で課金しても3体止まり
+メイレンとエミリアは最低限確保で終了</t>
+        </is>
+      </c>
+      <c r="E714" s="2" t="inlineStr">
+        <is>
+          <t>・メイレンとエミリアを確保できた
+・シンディを引けた</t>
+        </is>
+      </c>
+      <c r="F714" s="2" t="inlineStr">
+        <is>
+          <t>・110連やって何も出ず爆死
+・演出が弱く全く出ない
+・すり抜けが連発する
+・課金した途端すり抜け</t>
+        </is>
+      </c>
+      <c r="G714" s="2" t="inlineStr">
+        <is>
+          <t>・エミリア編ガチャ
+・メイレン編ガチャ
+・無償110連
+・すり抜け
+・爆死</t>
+        </is>
+      </c>
+      <c r="H714" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I714" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mTiBvJWBVfA</t>
+        </is>
+      </c>
+      <c r="J714" s="2" t="inlineStr">
+        <is>
+          <t>mTiBvJWBVfA</t>
+        </is>
+      </c>
+      <c r="K714" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T13:54:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B715" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C715" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】神速6人性能確認！注意喚起ありエミリア＆メイレン編【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D715" s="2" t="inlineStr">
+        <is>
+          <t>真夏の花火は適当交換NGと注意喚起
+メイレン編・エミリア編の新6体を性能確認
+ヒューズは使えるが全体的に抑えめと評価</t>
+        </is>
+      </c>
+      <c r="E715" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズは3対1回超物資で使いやすい
+・エミリアはぼちぼち強い
+・シンディは影パなら強いかも
+・ドールは全員10で価値がある</t>
+        </is>
+      </c>
+      <c r="F715" s="2" t="inlineStr">
+        <is>
+          <t>・メイレンの打の導きは使う機会が少ない
+・ドールはアルティメットミド君に劣る
+・今回のガチャは全体的に抑えめ
+・新キャラは必須感がなく刺さる場面限定</t>
+        </is>
+      </c>
+      <c r="G715" s="2" t="inlineStr">
+        <is>
+          <t>・花火交換注意
+・メイレン編性能
+・エミリア編性能
+・ヒューズ評価
+・導きシリーズ</t>
+        </is>
+      </c>
+      <c r="H715" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I715" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=E5fnTBJ7Qz4</t>
+        </is>
+      </c>
+      <c r="J715" s="2" t="inlineStr">
+        <is>
+          <t>E5fnTBJ7Qz4</t>
+        </is>
+      </c>
+      <c r="K715" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T13:54:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B716" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C716" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】15000ジュエルだと！人の夢、人の望み、人の業！！！花火イベント詳しく解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D716" s="2" t="inlineStr">
+        <is>
+          <t>夏の大花火大会の交換券50枚を解説
+堅実分配で最低3500ジュエル確保を推奨
+1点賭けの超ギャンブルと危険例に注意喚起</t>
+        </is>
+      </c>
+      <c r="E716" s="2" t="inlineStr">
+        <is>
+          <t>・堅実分配なら確実にジュエルがもらえる
+・最大1万5000ジュエルの夢がある</t>
+        </is>
+      </c>
+      <c r="F716" s="2" t="inlineStr">
+        <is>
+          <t>・1箇所43枚は最悪51ジュエルの危険例
+・適当に交換するのはダメ</t>
+        </is>
+      </c>
+      <c r="G716" s="2" t="inlineStr">
+        <is>
+          <t>・花火イベント
+・交換券50枚
+・堅実分配
+・1点ギャンブル
+・注意喚起</t>
+        </is>
+      </c>
+      <c r="H716" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I716" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fhJLBkb_DIE</t>
+        </is>
+      </c>
+      <c r="J716" s="2" t="inlineStr">
+        <is>
+          <t>fhJLBkb_DIE</t>
+        </is>
+      </c>
+      <c r="K716" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T13:54:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B717" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C717" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】無尽塔36クリア（後半部分）　2026サガ フロンティア発売日記念ガチャ</t>
+        </is>
+      </c>
+      <c r="D717" s="2" t="inlineStr">
+        <is>
+          <t>サガフロ記念ダブルガチャを引き性能を評価
+ヒューズとオタマを確保、他は微妙と結論
+無尽塔36シャムマベル戦は攻略しきれず苦戦</t>
+        </is>
+      </c>
+      <c r="E717" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズが強く引けて大きい
+・オタマ(氷の剣素材)確保でライオン等クリア
+・均等ベットで最低3500確保</t>
+        </is>
+      </c>
+      <c r="F717" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズも無尽塔36では火力が足りず微妙
+・ガチャ全体は環境を変えるほどでない
+・ダブルガチャ連発しすぎ
+・無尽塔36をクリアできず</t>
+        </is>
+      </c>
+      <c r="G717" s="2" t="inlineStr">
+        <is>
+          <t>・サガフロ記念ガチャ
+・ヒューズ確保
+・タコおじ
+・無尽塔36攻略
+・花火番号ベット</t>
+        </is>
+      </c>
+      <c r="H717" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I717" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rDbjbuyeeQQ</t>
+        </is>
+      </c>
+      <c r="J717" s="2" t="inlineStr">
+        <is>
+          <t>rDbjbuyeeQQ</t>
+        </is>
+      </c>
+      <c r="K717" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T13:54:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B718" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C718" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】待望の新キャラの性能が実は...！エミリア編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D718" s="2" t="inlineStr">
+        <is>
+          <t>エミリア編3体の性能を詳しくチェック
+シンディは陰属性レイドで輝く優秀な置物
+タコおじは冷続趣味枠、エミリアは打熱陽サポ</t>
+        </is>
+      </c>
+      <c r="E718" s="2" t="inlineStr">
+        <is>
+          <t>・シンディはレイドで輝く優秀な置物
+・エミリアは打熱陽で意外と火力が出る
+・タコおじは冷続編成の強化に良い
+・エミリアのイラストは100点</t>
+        </is>
+      </c>
+      <c r="F718" s="2" t="inlineStr">
+        <is>
+          <t>・タコおじはデメリット持ちで刺さる場面少ない
+・エミリアは汎用性が限りなく低い
+・全体的に趣味ガチャでジュエル溜め込み期間</t>
+        </is>
+      </c>
+      <c r="G718" s="2" t="inlineStr">
+        <is>
+          <t>・タコおじ性能
+・シンディ性能
+・エミリア性能
+・陰属性レイド
+・趣味ガチャ</t>
+        </is>
+      </c>
+      <c r="H718" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I718" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gTm0_KUFsT0</t>
+        </is>
+      </c>
+      <c r="J718" s="2" t="inlineStr">
+        <is>
+          <t>gTm0_KUFsT0</t>
+        </is>
+      </c>
+      <c r="K718" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T13:54:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B719" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C719" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今回1番の当たりはこの3人の中に？メイレン編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D719" s="2" t="inlineStr">
+        <is>
+          <t>メイレン編3体の性能をチェック
+ヒューズは全体SS20と邪魔性能で今回1番
+ドールとメイレンは一昔前スペックでデフレ気味</t>
+        </is>
+      </c>
+      <c r="E719" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズは開幕/3の倍数で全体SS20と高火力
+・ヒューズは敵の防御/ステータスを下げる優秀な邪魔
+・全員10なので始めたてには強化になる</t>
+        </is>
+      </c>
+      <c r="F719" s="2" t="inlineStr">
+        <is>
+          <t>・ドールは継承なしミド君で今更感
+・メイレンは一昔前の誓い系で縛りきつい
+・3人ともデフレ気味の趣味ガチャ</t>
+        </is>
+      </c>
+      <c r="G719" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズ性能
+・ドール性能
+・メイレン性能
+・全体SS20ヒット
+・デバフ邪魔</t>
+        </is>
+      </c>
+      <c r="H719" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I719" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pTHzJ1pD-n0</t>
+        </is>
+      </c>
+      <c r="J719" s="2" t="inlineStr">
+        <is>
+          <t>pTHzJ1pD-n0</t>
+        </is>
+      </c>
+      <c r="K719" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T13:54:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B720" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C720" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】オイシイ報酬を絶対に取り逃がすな！このイベントマジで要注意！！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D720" s="2" t="inlineStr">
+        <is>
+          <t>潜入キャンベルマリンリゾートの複雑仕様を紹介
+パスキーで部屋解放、周回場所の切替に注意
+花火大会は全賭け1.5万か均等3500かと解説</t>
+        </is>
+      </c>
+      <c r="E720" s="2" t="inlineStr">
+        <is>
+          <t>・イベントに変化をつける姿勢が嬉しい
+・ボスは残弱で簡単に勝てる
+・均等振りで最低3500保障</t>
+        </is>
+      </c>
+      <c r="F720" s="2" t="inlineStr">
+        <is>
+          <t>・同じ場所を周回すると何も得られず後悔
+・ジュエルのドロップ率が薄そうで注意
+・全賭けは0の可能性が高く怖い</t>
+        </is>
+      </c>
+      <c r="G720" s="2" t="inlineStr">
+        <is>
+          <t>・マリンリゾート解説
+・パスキー周回
+・スパイダー001防具
+・花火大会
+・ボス戦</t>
+        </is>
+      </c>
+      <c r="H720" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I720" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tpnVsue1c_U</t>
+        </is>
+      </c>
+      <c r="J720" s="2" t="inlineStr">
+        <is>
+          <t>tpnVsue1c_U</t>
+        </is>
+      </c>
+      <c r="K720" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T13:54:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B721" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C721" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭エミリア編ガチャ評価 #ロマサガRS #shorts #ガチャ</t>
+        </is>
+      </c>
+      <c r="D721" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭エミリア編のガチャ評価ショート
+字幕が音楽のみで内容は取得できず
+タイトルからガチャ性能評価と推測</t>
+        </is>
+      </c>
+      <c r="E721" s="2" t="inlineStr"/>
+      <c r="F721" s="2" t="inlineStr"/>
+      <c r="G721" s="2" t="inlineStr">
+        <is>
+          <t>・エミリア編ガチャ
+・ガチャ評価
+・shorts</t>
+        </is>
+      </c>
+      <c r="H721" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I721" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5mDjbtSjrOc</t>
+        </is>
+      </c>
+      <c r="J721" s="2" t="inlineStr">
+        <is>
+          <t>5mDjbtSjrOc</t>
+        </is>
+      </c>
+      <c r="K721" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T13:54:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B722" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C722" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭メイレン編ガチャ評価 #ロマサガRS #shorts #ガチャ</t>
+        </is>
+      </c>
+      <c r="D722" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭メイレン編のガチャ評価ショート
+字幕が音楽のみで内容は取得できず
+タイトルからガチャ性能評価と推測</t>
+        </is>
+      </c>
+      <c r="E722" s="2" t="inlineStr"/>
+      <c r="F722" s="2" t="inlineStr"/>
+      <c r="G722" s="2" t="inlineStr">
+        <is>
+          <t>・メイレン編ガチャ
+・ガチャ評価
+・shorts</t>
+        </is>
+      </c>
+      <c r="H722" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I722" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=crWH_S_ySRo</t>
+        </is>
+      </c>
+      <c r="J722" s="2" t="inlineStr">
+        <is>
+          <t>crWH_S_ySRo</t>
+        </is>
+      </c>
+      <c r="K722" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T13:54:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B723" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C723" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】エミリア・シンディ・キャンベル・タコおじさん能力値早見表 ~火力サポーターがずらーりー〜エミリア編ガチャ</t>
+        </is>
+      </c>
+      <c r="D723" s="2" t="inlineStr">
+        <is>
+          <t>サガフロ記念ガチャ3体の能力値を考察
+タコおじはマスコット、エミリアは火力サポ
+シンディは敵多数で輝くテクニカルサポ</t>
+        </is>
+      </c>
+      <c r="E723" s="2" t="inlineStr">
+        <is>
+          <t>・エミリアは火力サポーターとして強い
+・シンディは敵が多いほど火力が上がり強力
+・シンディは主軸になるポテンシャルあり</t>
+        </is>
+      </c>
+      <c r="F723" s="2" t="inlineStr">
+        <is>
+          <t>・タコおじは雪だるまの劣化版で汎用性厳しい
+・タコおじは初動が遅い
+・エミリアは突き抜け感が足りない
+・シンディはすぐ引かず様子見が良い</t>
+        </is>
+      </c>
+      <c r="G723" s="2" t="inlineStr">
+        <is>
+          <t>・タコおじ考察
+・エミリア考察
+・シンディ考察
+・火力サポーター
+・能力値早見表</t>
+        </is>
+      </c>
+      <c r="H723" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I723" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hERDn-5riJ8</t>
+        </is>
+      </c>
+      <c r="J723" s="2" t="inlineStr">
+        <is>
+          <t>hERDn-5riJ8</t>
+        </is>
+      </c>
+      <c r="K723" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T13:54:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B724" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C724" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第127回シュウザーたちの井戸‼️攻略‼️〜ランキング100位を目指して〜全てお見せします♪</t>
+        </is>
+      </c>
+      <c r="D724" s="2" t="inlineStr">
+        <is>
+          <t>シュウザーたちの井戸を8手クリア編成で攻略
+100位前後を狙える暦みダメージ戦法を紹介
+上位6手編成は未解明で今週も白熱と語る</t>
+        </is>
+      </c>
+      <c r="E724" s="2" t="inlineStr">
+        <is>
+          <t>・8手運用で100位前後を狙える
+・今週の井戸も楽しくなってきた</t>
+        </is>
+      </c>
+      <c r="F724" s="2" t="inlineStr">
+        <is>
+          <t>・6手の上位編成がまだ分からない</t>
+        </is>
+      </c>
+      <c r="G724" s="2" t="inlineStr">
+        <is>
+          <t>・シュウザーの井戸
+・8手クリア編成
+・ランキング100位
+・暦みダメージ
+・グスタフ継承</t>
+        </is>
+      </c>
+      <c r="H724" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I724" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iF9iPWxxe7Y</t>
+        </is>
+      </c>
+      <c r="J724" s="2" t="inlineStr">
+        <is>
+          <t>iF9iPWxxe7Y</t>
+        </is>
+      </c>
+      <c r="K724" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T13:54:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B725" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C725" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】理解していないと後悔案件 新イベントの進め方やキャンペーンを徹底解説します!!【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D725" s="2" t="inlineStr">
+        <is>
+          <t>潜入キャンベルマリンリゾートの進め方を解説
+パスキーで部屋解放、周回場所の切替が必須
+花火大会は全突1.5万か均等3500かと説明</t>
+        </is>
+      </c>
+      <c r="E725" s="2" t="inlineStr">
+        <is>
+          <t>・全突なら1万5000ジュエルの夢
+・均等振りで最低3500ジュエル保障</t>
+        </is>
+      </c>
+      <c r="F725" s="2" t="inlineStr">
+        <is>
+          <t>・最初に記憶再戦を固定化してはダメ
+・同じ場所を周回すると損
+・パスキー5個以上は無駄になる
+・イベントが複雑で注意点が多い</t>
+        </is>
+      </c>
+      <c r="G725" s="2" t="inlineStr">
+        <is>
+          <t>・マリンリゾートイベント
+・パスキー
+・周回注意点
+・花火大会
+・ジュエル交換</t>
+        </is>
+      </c>
+      <c r="H725" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I725" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SF83kHWzXpo</t>
+        </is>
+      </c>
+      <c r="J725" s="2" t="inlineStr">
+        <is>
+          <t>SF83kHWzXpo</t>
+        </is>
+      </c>
+      <c r="K725" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T13:54:13Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K725"/>
+  <dimension ref="A1:K740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48117,6 +48117,980 @@
         </is>
       </c>
     </row>
+    <row r="726">
+      <c r="A726" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B726" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C726" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋でも何でも「新テンプレ」鬼八&amp;おたまで無尽塔40層ヴァッハ神を破壊し今回の無尽塔をゴールする　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D726" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔40層ヴァッハ神を鬼八＆おたま新テンプレで攻略
+ターミンの治力デバフやODを駆使しギリギリ削り切る
+ガチャ当日に即クリア、排水なしゴール更新</t>
+        </is>
+      </c>
+      <c r="E726" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八＆おたまの新テンプレ編成が強力
+・ガチャ当日に即クリアできた
+・排水なしゴール更新できた</t>
+        </is>
+      </c>
+      <c r="F726" s="2" t="inlineStr">
+        <is>
+          <t>・バッハのランダムヒットBP削りが運ゲーで厄介
+・サ魂デバフがないと1ターン目が厳しい</t>
+        </is>
+      </c>
+      <c r="G726" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔40層
+・ヴァッハ神
+・鬼八
+・おたま
+・新テンプレ</t>
+        </is>
+      </c>
+      <c r="H726" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I726" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=K35V4rPUpQ4</t>
+        </is>
+      </c>
+      <c r="J726" s="2" t="inlineStr">
+        <is>
+          <t>K35V4rPUpQ4</t>
+        </is>
+      </c>
+      <c r="K726" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:48:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B727" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C727" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】FFRKコラボ「こうてい」にウボァーと言わせろ!!最新編成2種&amp;全力オート&amp;ギミック解説!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D727" s="2" t="inlineStr">
+        <is>
+          <t>FFRKコラボ皇帝戦の最新編成2種と全力オートを紹介
+リアム等でOD満タン維持すれば全力オートで安定
+回避と防御低下が厄介だが殴り切れる内容</t>
+        </is>
+      </c>
+      <c r="E727" s="2" t="inlineStr">
+        <is>
+          <t>・リアム等でOD満タン維持でき全力オートで安定
+・1ゲージ目はカウンターが有効
+・ギミック少なく駆け抜けられる</t>
+        </is>
+      </c>
+      <c r="F727" s="2" t="inlineStr">
+        <is>
+          <t>・回避によるディフレクトで防御低下が致命的
+・回避の時間稼ぎがしんどい
+・しっかり目の防御が必要</t>
+        </is>
+      </c>
+      <c r="G727" s="2" t="inlineStr">
+        <is>
+          <t>・FFRKコラボ
+・皇帝戦
+・全力オート
+・編成2種
+・OD満タン</t>
+        </is>
+      </c>
+      <c r="H727" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I727" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=g0m8PPUF0eI</t>
+        </is>
+      </c>
+      <c r="J727" s="2" t="inlineStr">
+        <is>
+          <t>g0m8PPUF0eI</t>
+        </is>
+      </c>
+      <c r="K727" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:48:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B728" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C728" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】IFストーリーを体験！新イベント開催予告！ 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D728" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネ新イベントEシミュレーターUC0079を予告
+IFストーリーで史実と異なる歴史を体験、7/16開催
+報酬にSP化チップ、キャラ2人とも使いやすそう</t>
+        </is>
+      </c>
+      <c r="E728" s="2" t="inlineStr">
+        <is>
+          <t>・SP化・SSP化チップがもらえてありがたい
+・セイラ・ララァ2人とも使いやすそう
+・作品数だけ無限にイベントできそう
+・キャラ条件がタグ制で別作品に乗せやすい</t>
+        </is>
+      </c>
+      <c r="F728" s="2" t="inlineStr">
+        <is>
+          <t>・部隊1の出撃制限が厳しめ</t>
+        </is>
+      </c>
+      <c r="G728" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・IFストーリー
+・UC0079
+・フルアーマーガンダム
+・出撃制限</t>
+        </is>
+      </c>
+      <c r="H728" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I728" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7-nVINBG4lQ</t>
+        </is>
+      </c>
+      <c r="J728" s="2" t="inlineStr">
+        <is>
+          <t>7-nVINBG4lQ</t>
+        </is>
+      </c>
+      <c r="K728" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:48:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B729" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C729" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】IFストーリーを体験！新イベント開催予告！ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D729" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネ新イベントEシミュレーターUC79を予告(Shorts)
+IFストーリーで史実と異なる歴史を観測、7/16開催
+SP化チップ報酬、部隊1は出撃制限あり</t>
+        </is>
+      </c>
+      <c r="E729" s="2" t="inlineStr">
+        <is>
+          <t>・報酬にチップがもらえてありがたい
+・キャラ2人とも使いやすそう
+・タグ制で別作品ユニットにも乗せやすい</t>
+        </is>
+      </c>
+      <c r="F729" s="2" t="inlineStr">
+        <is>
+          <t>・部隊1の出撃制限が厳しめ</t>
+        </is>
+      </c>
+      <c r="G729" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・IFストーリー
+・UC79
+・出撃制限
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H729" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I729" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HdW7rUDZ_Ow</t>
+        </is>
+      </c>
+      <c r="J729" s="2" t="inlineStr">
+        <is>
+          <t>HdW7rUDZ_Ow</t>
+        </is>
+      </c>
+      <c r="K729" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:48:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B730" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C730" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ガチャは無いよ FFRKコラボ 7月10日更新情報まとめ 【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D730" s="2" t="inlineStr">
+        <is>
+          <t>FFRKコラボ記念の7/10更新情報を確認、ガチャはなし
+討伐クエスト皇帝戦でエクスカリバー等を交換所で入手
+ログボ＋ミッションで計8000ジュエル配布</t>
+        </is>
+      </c>
+      <c r="E730" s="2" t="inlineStr">
+        <is>
+          <t>・計8000ジュエルをしっかり配ってくれてありがたい
+・エクスカリバーFF2など限定品が交換できる</t>
+        </is>
+      </c>
+      <c r="F730" s="2" t="inlineStr">
+        <is>
+          <t>・エクスカリバーはロマショップに追加されない限定品で取り逃し注意</t>
+        </is>
+      </c>
+      <c r="G730" s="2" t="inlineStr">
+        <is>
+          <t>・FFRKコラボ
+・ガチャなし
+・討伐クエスト
+・エクスカリバー
+・ジュエル配布</t>
+        </is>
+      </c>
+      <c r="H730" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I730" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=K3fEgNELVGY</t>
+        </is>
+      </c>
+      <c r="J730" s="2" t="inlineStr">
+        <is>
+          <t>K3fEgNELVGY</t>
+        </is>
+      </c>
+      <c r="K730" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:48:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B731" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C731" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こんなのおかしいですよ！メイレンさん！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D731" s="2" t="inlineStr">
+        <is>
+          <t>FF討伐クエストをメイレン中心の編成で攻略
+火力が出て簡単に倒しやすかった
+ガチャ部分は実況せずダイジェスト気味</t>
+        </is>
+      </c>
+      <c r="E731" s="2" t="inlineStr">
+        <is>
+          <t>・メイレンで火力が出て簡単に倒せた</t>
+        </is>
+      </c>
+      <c r="F731" s="2" t="inlineStr"/>
+      <c r="G731" s="2" t="inlineStr">
+        <is>
+          <t>・FF討伐クエスト
+・メイレン
+・皇帝戦
+・ガチャ</t>
+        </is>
+      </c>
+      <c r="H731" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I731" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6fvFo9TR0rg</t>
+        </is>
+      </c>
+      <c r="J731" s="2" t="inlineStr">
+        <is>
+          <t>6fvFo9TR0rg</t>
+        </is>
+      </c>
+      <c r="K731" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:48:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B732" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C732" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ファイナルイグニッションかっこいい・・ロマパスエレノアの火力がやばする【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D732" s="2" t="inlineStr">
+        <is>
+          <t>ロマパスのエレノアの火力をブラスト相性で検証
+ファイナルイグニッションの演出がかっこよく火力がえぐい
+手加減しても敵が溶けるほどエレノアがぶっ飛んだ性能</t>
+        </is>
+      </c>
+      <c r="E732" s="2" t="inlineStr">
+        <is>
+          <t>・エレノアの火力がぶっ飛び一人だけ飛び抜けている
+・ファイナルイグニッションの演出がかっこいい
+・5ターン戦なら火力として活躍でき満足</t>
+        </is>
+      </c>
+      <c r="F732" s="2" t="inlineStr">
+        <is>
+          <t>・軽減がなく耐久性能はない(5ターン以降向け)
+・火力が高すぎて手加減が必要なほど</t>
+        </is>
+      </c>
+      <c r="G732" s="2" t="inlineStr">
+        <is>
+          <t>・ロマパスエレノア
+・ファイナルイグニッション
+・火力検証
+・ブラスト相性</t>
+        </is>
+      </c>
+      <c r="H732" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I732" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XPxIc30OKN4</t>
+        </is>
+      </c>
+      <c r="J732" s="2" t="inlineStr">
+        <is>
+          <t>XPxIc30OKN4</t>
+        </is>
+      </c>
+      <c r="K732" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:48:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B733" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C733" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】残り時間僅か有！4大ガチャランキング引くべき優先順位考察【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D733" s="2" t="inlineStr">
+        <is>
+          <t>4大ガチャの引くべき優先順位を1〜4位でランキング考察
+1位は気ハ＆オタマ、24ヒットの環境破壊性能で超おすすめ
+残り2日、迷っているなら引いて良いと結論</t>
+        </is>
+      </c>
+      <c r="E733" s="2" t="inlineStr">
+        <is>
+          <t>・気ハは24ヒットの環境破壊級アタッカーで超おすすめ
+・オタマは9種フォース＆無人島ほぼ必須で強力
+・イリスは高相性で環境を選べる優秀なサポーター
+・ヒューズは全体SS20ヒット＋デバフ両立で強力</t>
+        </is>
+      </c>
+      <c r="F733" s="2" t="inlineStr">
+        <is>
+          <t>・エミリアは必須級ではなく属性内の便利枠止まり
+・メイレンの1.25倍付与率は低く控えめ
+・タコ寺・シンディはニッチで優先度控えめ</t>
+        </is>
+      </c>
+      <c r="G733" s="2" t="inlineStr">
+        <is>
+          <t>・4大ガチャ
+・引くべき優先順位
+・気ハ
+・オタマ
+・イリス
+・ヒューズ</t>
+        </is>
+      </c>
+      <c r="H733" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I733" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YK2Ulzm05os</t>
+        </is>
+      </c>
+      <c r="J733" s="2" t="inlineStr">
+        <is>
+          <t>YK2Ulzm05os</t>
+        </is>
+      </c>
+      <c r="K733" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:48:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B734" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C734" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】無尽塔37から</t>
+        </is>
+      </c>
+      <c r="D734" s="2" t="inlineStr">
+        <is>
+          <t>無尽塔37層からの攻略を生配信、エレノアも軽く育成
+ピンクタイガーや雪だるま編成で試行錯誤するも苦戦
+排水を覚えないと突破は厳しいと締めくくり</t>
+        </is>
+      </c>
+      <c r="E734" s="2" t="inlineStr">
+        <is>
+          <t>・エレノアなど新スタイルを配信外で入手できた</t>
+        </is>
+      </c>
+      <c r="F734" s="2" t="inlineStr">
+        <is>
+          <t>・雑魚が強すぎて火力・BPが足りず苦戦
+・排水を覚えないと突破は無理そう</t>
+        </is>
+      </c>
+      <c r="G734" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔37層
+・生配信
+・エレノア
+・編成試行錯誤
+・収益化雑談</t>
+        </is>
+      </c>
+      <c r="H734" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I734" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sj8fGEp2TxQ</t>
+        </is>
+      </c>
+      <c r="J734" s="2" t="inlineStr">
+        <is>
+          <t>sj8fGEp2TxQ</t>
+        </is>
+      </c>
+      <c r="K734" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:48:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B735" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C735" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】緊急事態発生！遂にロマサガRSとファイナルファンタジーレコードキーパーとのコラボが開幕した！【FFRK】</t>
+        </is>
+      </c>
+      <c r="D735" s="2" t="inlineStr">
+        <is>
+          <t>FFRKコラボ開幕を緊急動画で大興奮リポート
+FF2半乱軍のテーマがホームBGMになり感動
+ガチャなしでジュエル配布、最高のコラボと絶賛</t>
+        </is>
+      </c>
+      <c r="E735" s="2" t="inlineStr">
+        <is>
+          <t>・FF2の名曲がRSで流れるBGM変更に大感動
+・ガチャなしでジュエル大量配布はただただラッキー
+・楽しませるためだけの最高のコラボ</t>
+        </is>
+      </c>
+      <c r="F735" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャが1〜2キャラでもあれば嬉しかった</t>
+        </is>
+      </c>
+      <c r="G735" s="2" t="inlineStr">
+        <is>
+          <t>・FFRKコラボ
+・FF2半乱軍のテーマ
+・ホームBGM
+・ジュエル配布
+・サガラジオ</t>
+        </is>
+      </c>
+      <c r="H735" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I735" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UcCWR7KAmnA</t>
+        </is>
+      </c>
+      <c r="J735" s="2" t="inlineStr">
+        <is>
+          <t>UcCWR7KAmnA</t>
+        </is>
+      </c>
+      <c r="K735" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:48:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B736" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C736" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】こうていとの戦い ~9ターン撃破 ~</t>
+        </is>
+      </c>
+      <c r="D736" s="2" t="inlineStr">
+        <is>
+          <t>FFRKコラボ皇帝戦ロマンシングを9ターンで撃破
+編成はブーケ・暦み・サイバ・ターミン・最終皇帝女の5名
+各継承を紹介しつつ攻略</t>
+        </is>
+      </c>
+      <c r="E736" s="2" t="inlineStr">
+        <is>
+          <t>・手持ち編成で9ターン撃破できた</t>
+        </is>
+      </c>
+      <c r="F736" s="2" t="inlineStr"/>
+      <c r="G736" s="2" t="inlineStr">
+        <is>
+          <t>・皇帝戦
+・ロマンシング
+・9ターン撃破
+・編成紹介
+・継承</t>
+        </is>
+      </c>
+      <c r="H736" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I736" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Kmm-ItZagig</t>
+        </is>
+      </c>
+      <c r="J736" s="2" t="inlineStr">
+        <is>
+          <t>Kmm-ItZagig</t>
+        </is>
+      </c>
+      <c r="K736" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:48:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B737" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C737" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【ガチャ動画】おたまほしい【No.620】</t>
+        </is>
+      </c>
+      <c r="D737" s="2" t="inlineStr">
+        <is>
+          <t>水着第2弾ガチャでおたま狙いのガチャ配信
+コウタ君が60連ほどで水着おたま等4体を引き当てる
+引けたら握手会開催と盛り上がる雑談ガチャ回</t>
+        </is>
+      </c>
+      <c r="E737" s="2" t="inlineStr">
+        <is>
+          <t>・少ない連数で水着おたま等4体を引き当てた
+・前回も90連でコンプできGBキャラ運が好調</t>
+        </is>
+      </c>
+      <c r="F737" s="2" t="inlineStr">
+        <is>
+          <t>・ターコは1万ジュエル溶かしても何も出ずパニック買いを反省</t>
+        </is>
+      </c>
+      <c r="G737" s="2" t="inlineStr">
+        <is>
+          <t>・水着ガチャ
+・おたま
+・イリス
+・ガチャ配信
+・パニック買い</t>
+        </is>
+      </c>
+      <c r="H737" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I737" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=T4fLtThfvfU</t>
+        </is>
+      </c>
+      <c r="J737" s="2" t="inlineStr">
+        <is>
+          <t>T4fLtThfvfU</t>
+        </is>
+      </c>
+      <c r="K737" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:48:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B738" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C738" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こうていとの戦い配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D738" s="2" t="inlineStr">
+        <is>
+          <t>FFRKコラボ皇帝戦を生配信で初見攻略
+FF2のBGMを絶賛、ガチャは来ないとラジオで明言
+弱点なし＆エリクサー回復で火力押し切りが必要と検証</t>
+        </is>
+      </c>
+      <c r="E738" s="2" t="inlineStr">
+        <is>
+          <t>・FF2のBGMがかっこよくコラボを楽しめた
+・ミニコラボはジュエル配布もあり助かる</t>
+        </is>
+      </c>
+      <c r="F738" s="2" t="inlineStr">
+        <is>
+          <t>・弱点がなくサやビンセント等ウィーク要員が使いづらい
+・エリクサーや連撃でHP回復され火力押し切りが必要
+・ガチャは来ないと明言され少し残念</t>
+        </is>
+      </c>
+      <c r="G738" s="2" t="inlineStr">
+        <is>
+          <t>・皇帝戦
+・生配信
+・FF2 BGM
+・弱点なし
+・エリクサー回復</t>
+        </is>
+      </c>
+      <c r="H738" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I738" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VvgifjGaF8E</t>
+        </is>
+      </c>
+      <c r="J738" s="2" t="inlineStr">
+        <is>
+          <t>VvgifjGaF8E</t>
+        </is>
+      </c>
+      <c r="K738" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:48:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B739" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C739" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】討伐クエスト「こうてい」Romancingを攻略！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D739" s="2" t="inlineStr">
+        <is>
+          <t>FFRKコラボ皇帝戦ロマンシングの攻略を解説
+弱点なし・回避・エリクサー回復のギミックと対策を紹介
+難易度低めでSSS武器エクスカリバーを入手可能</t>
+        </is>
+      </c>
+      <c r="E739" s="2" t="inlineStr">
+        <is>
+          <t>・難易度はかなり低めで挑戦しやすい
+・SSS武器エクスカリバーを入手できてお得
+・ODゲージ上昇スタイルで回避を貫ける</t>
+        </is>
+      </c>
+      <c r="F739" s="2" t="inlineStr">
+        <is>
+          <t>・弱点がなくエクストラフォースや余ダメ上昇が使えない
+・エリクサーや7連撃でHP回復されるので火力が必要</t>
+        </is>
+      </c>
+      <c r="G739" s="2" t="inlineStr">
+        <is>
+          <t>・皇帝戦
+・ロマンシング攻略
+・ブリンク回避
+・エリクサー回復
+・エクスカリバー</t>
+        </is>
+      </c>
+      <c r="H739" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I739" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=b6uc1BSgE5U</t>
+        </is>
+      </c>
+      <c r="J739" s="2" t="inlineStr">
+        <is>
+          <t>b6uc1BSgE5U</t>
+        </is>
+      </c>
+      <c r="K739" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:48:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B740" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C740" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】2026年7月上旬ガチャ総まとめ！全12スタイル引くべきスタイルランキング！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D740" s="2" t="inlineStr">
+        <is>
+          <t>7月上旬実装ガチャ全12スタイルをティアランク付け
+Sなし、Aは気ハとヒューズで火力重視の高評価
+オタマは継承前提で強力な特別枠として紹介</t>
+        </is>
+      </c>
+      <c r="E740" s="2" t="inlineStr">
+        <is>
+          <t>・気ハは残雷の超高火力で短期戦・レイドで活躍
+・ヒューズは全体火力とデバフを両立でき魅力
+・オタマは継承前提なら無人島等で非常に強力
+・Dナンバー5はザレ3属性で汎用性が高い</t>
+        </is>
+      </c>
+      <c r="F740" s="2" t="inlineStr">
+        <is>
+          <t>・Sランク該当なしで必須級はいない
+・気ハ・ヒューズはサポート要素が薄く高難易度で採用されにくい
+・シンディやメイレンは扱いづらく優先度低め
+・タコおじさんは敵の冷続火力も上げるデメリット持ち</t>
+        </is>
+      </c>
+      <c r="G740" s="2" t="inlineStr">
+        <is>
+          <t>・7月上旬ガチャ
+・ティアランク
+・気ハ
+・ヒューズ
+・オタマ
+・全12スタイル</t>
+        </is>
+      </c>
+      <c r="H740" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I740" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sfa6i2-xkxs</t>
+        </is>
+      </c>
+      <c r="J740" s="2" t="inlineStr">
+        <is>
+          <t>sfa6i2-xkxs</t>
+        </is>
+      </c>
+      <c r="K740" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T02:48:26Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K740"/>
+  <dimension ref="A1:K746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -49091,6 +49091,396 @@
         </is>
       </c>
     </row>
+    <row r="741">
+      <c r="A741" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B741" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C741" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　閲覧注意！！　性能度外視！惚れ込んだ女性キャラTOP5</t>
+        </is>
+      </c>
+      <c r="D741" s="2" t="inlineStr">
+        <is>
+          <t>性能度外視、投稿者が惚れ込んだ女性キャラTOP5。
+5位エレノア4位アールブ3位アーニャ2位オルレット。
+1位は最新イリス、絵欲しさに天井まで確保。</t>
+        </is>
+      </c>
+      <c r="E741" s="2" t="inlineStr">
+        <is>
+          <t>・イリスは絵が欲しくて天井まで確保した最推し
+・オルレットは卓越した腹筋と足入れが魅力
+・アールブは上下半身のギャップと見た目が良い
+・エレノアはふくらはぎと膝裏のバランスが良い
+・アーニャは旅立ちの幕開けが素晴らしい</t>
+        </is>
+      </c>
+      <c r="F741" s="2" t="inlineStr"/>
+      <c r="G741" s="2" t="inlineStr">
+        <is>
+          <t>・女性キャラTOP5
+・性能度外視
+・イリス1位
+・キャラ絵の魅力
+・リクエスト企画</t>
+        </is>
+      </c>
+      <c r="H741" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I741" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hrj0l69bMMU</t>
+        </is>
+      </c>
+      <c r="J741" s="2" t="inlineStr">
+        <is>
+          <t>hrj0l69bMMU</t>
+        </is>
+      </c>
+      <c r="K741" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T12:24:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B742" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C742" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】FFRKコラボこうていRomancing攻略 #ロマサガRS #shorts</t>
+        </is>
+      </c>
+      <c r="D742" s="2" t="inlineStr">
+        <is>
+          <t>FFRKコラボの皇帝Romancing難度に挑戦するshorts。
+敵が体力全回復やエリクサーで長期戦化。
+押し切れず最後はやられて終了。</t>
+        </is>
+      </c>
+      <c r="E742" s="2" t="inlineStr"/>
+      <c r="F742" s="2" t="inlineStr">
+        <is>
+          <t>・敵が体力を全回復してきて面倒
+・エリクサー使用で長期戦がだるい
+・このターンで倒せず押し切れなかった</t>
+        </is>
+      </c>
+      <c r="G742" s="2" t="inlineStr">
+        <is>
+          <t>・FFRKコラボ
+・皇帝Romancing
+・高難度攻略
+・shorts</t>
+        </is>
+      </c>
+      <c r="H742" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I742" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Sc35oYfX6xQ</t>
+        </is>
+      </c>
+      <c r="J742" s="2" t="inlineStr">
+        <is>
+          <t>Sc35oYfX6xQ</t>
+        </is>
+      </c>
+      <c r="K742" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T12:24:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B743" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C743" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】使ってわかったあのキャラ強し！鬼八&amp;イリスガチャ最終評価ランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D743" s="2" t="inlineStr">
+        <is>
+          <t>鬼八&amp;イリスガチャ終了間近の最終評価ランキング。
+鬼八とお玉を特期戦力、DAとミーティアを星2に。
+ウルピナ・イリスは星1、確保推奨は鬼八とお玉。</t>
+        </is>
+      </c>
+      <c r="E743" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八は爆火力で周回コンテンツ引っ張りだこの特期戦力
+・お玉は唯一性満載で高難度・螺旋で活躍間違いなし
+・DAナンバー5は霊雷編成で攻防バランス良く現環境マッチ
+・ミーティアは置き物火力バフとBPサポートが優秀
+・鬼八とお玉は確保して損なしと評価</t>
+        </is>
+      </c>
+      <c r="F743" s="2" t="inlineStr">
+        <is>
+          <t>・ウルピナは同型アタッカー多く唯一性が薄い星1
+・イリスは火力バフが単体かつ陽条件で場所を選ぶ星1
+・ミーティアはバフ量がイシスに劣り1ターンのみ
+・DAは編成難度が高く手持ち揃った人向け</t>
+        </is>
+      </c>
+      <c r="G743" s="2" t="inlineStr">
+        <is>
+          <t>・鬼八&amp;イリスガチャ
+・最終評価ランキング
+・鬼八特期戦力
+・お玉高難度
+・星3〜星1評価</t>
+        </is>
+      </c>
+      <c r="H743" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I743" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mDF9RLSr5TY</t>
+        </is>
+      </c>
+      <c r="J743" s="2" t="inlineStr">
+        <is>
+          <t>mDF9RLSr5TY</t>
+        </is>
+      </c>
+      <c r="K743" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T12:24:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B744" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C744" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】カモキングたちの井戸 ~100位台を狙え‼︎~ヒューズ無し編成 ~</t>
+        </is>
+      </c>
+      <c r="D744" s="2" t="inlineStr">
+        <is>
+          <t>カモキングたちの井戸、100位台狙いの攻略動画。
+ヒューズ無しの暦み・Sターミン等11手編成を紹介。
+結果は11手で172位クリア。</t>
+        </is>
+      </c>
+      <c r="E744" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズ未所持でも100位台を狙える編成を用意</t>
+        </is>
+      </c>
+      <c r="F744" s="2" t="inlineStr">
+        <is>
+          <t>・上位を狙うにはヒューズが必要になる</t>
+        </is>
+      </c>
+      <c r="G744" s="2" t="inlineStr">
+        <is>
+          <t>・カモキング井戸
+・100位台狙い
+・ヒューズ無し編成
+・11手クリア
+・ランキング</t>
+        </is>
+      </c>
+      <c r="H744" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I744" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5aP56s_h9Cs</t>
+        </is>
+      </c>
+      <c r="J744" s="2" t="inlineStr">
+        <is>
+          <t>5aP56s_h9Cs</t>
+        </is>
+      </c>
+      <c r="K744" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T12:24:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B745" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C745" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】シュウザーたちの井戸 ~先週の振り返り ~「7手攻略とTOP編成の解説」</t>
+        </is>
+      </c>
+      <c r="D745" s="2" t="inlineStr">
+        <is>
+          <t>シュウザーたちの井戸トップクリア編成の解説。
+7手クリア編成と1位6手編成を比較紹介。
+範囲アタッカーが活躍した週。</t>
+        </is>
+      </c>
+      <c r="E745" s="2" t="inlineStr">
+        <is>
+          <t>・範囲アタッカーが活躍した井戸環境
+・魂強化が進んだアレツはグスタフ超えで6手可能</t>
+        </is>
+      </c>
+      <c r="F745" s="2" t="inlineStr">
+        <is>
+          <t>・自分は魂が足りず6手クリアには届かなかった</t>
+        </is>
+      </c>
+      <c r="G745" s="2" t="inlineStr">
+        <is>
+          <t>・シュウザー井戸
+・7手クリア
+・TOP編成解説
+・グスタフ
+・アレツ</t>
+        </is>
+      </c>
+      <c r="H745" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I745" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_ha_LEsmnoY</t>
+        </is>
+      </c>
+      <c r="J745" s="2" t="inlineStr">
+        <is>
+          <t>_ha_LEsmnoY</t>
+        </is>
+      </c>
+      <c r="K745" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T12:24:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B746" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C746" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】誰がトップ!?「環境最強属性とは」最新陰陽Tier!!属性分布図を把握して今来ているガチャを厳選しやすくする!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D746" s="2" t="inlineStr">
+        <is>
+          <t>最新の陰陽属性Tierと分布図でガチャ厳選を解説。
+上位は陰の万能スタイル、ビンセント裁判ターミンが最強格。
+属性を固める有用性は低下、手持ち少ないほど非推奨。</t>
+        </is>
+      </c>
+      <c r="E746" s="2" t="inlineStr">
+        <is>
+          <t>・陰属性はウィーク無視でも強いスタイルが揃い最強格
+・ビンセントは弱点無しでも最大火力を出せる最上位アタッカー
+・ターミンは攻守デバフとBP回避を備え万能で入れ得
+・バルテルミーは全体連打可能で汎用性から浮上の可能性
+・女神はダメブロ蓄積と全体ODで無人島問わず活躍</t>
+        </is>
+      </c>
+      <c r="F746" s="2" t="inlineStr">
+        <is>
+          <t>・属性を固める有用性は低く手持ち少ないほど非推奨
+・暦みは1ターンしか強くほぼ規制前提の割り切り性能
+・メイレンやアーニャは個人火力が低くバトル参加条件が厳しい
+・上位層を超えないスタイルはノールックでスルー可</t>
+        </is>
+      </c>
+      <c r="G746" s="2" t="inlineStr">
+        <is>
+          <t>・陰陽属性Tier
+・属性分布図
+・ガチャ厳選
+・陰属性最強
+・上位層の指標</t>
+        </is>
+      </c>
+      <c r="H746" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I746" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Krxz6Ms0GZQ</t>
+        </is>
+      </c>
+      <c r="J746" s="2" t="inlineStr">
+        <is>
+          <t>Krxz6Ms0GZQ</t>
+        </is>
+      </c>
+      <c r="K746" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T12:25:56Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K746"/>
+  <dimension ref="A1:K750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -49481,6 +49481,261 @@
         </is>
       </c>
     </row>
+    <row r="747">
+      <c r="A747" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B747" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C747" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】素顔が知りたい…「水着ジ・エンド」からの謎ガチャ週間突入のガチャ予想!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D747" s="2" t="inlineStr">
+        <is>
+          <t>字幕が音楽・雑音のみで本編内容を取得できず。
+タイトルから水着ジ・エンド後の謎ガチャ週間の予想動画と推測。
+具体的な評価は本編を要確認。</t>
+        </is>
+      </c>
+      <c r="E747" s="2" t="inlineStr"/>
+      <c r="F747" s="2" t="inlineStr"/>
+      <c r="G747" s="2" t="inlineStr">
+        <is>
+          <t>・水着ジ・エンド
+・謎ガチャ週間
+・ガチャ予想</t>
+        </is>
+      </c>
+      <c r="H747" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I747" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WdEKoUfWbS4</t>
+        </is>
+      </c>
+      <c r="J747" s="2" t="inlineStr">
+        <is>
+          <t>WdEKoUfWbS4</t>
+        </is>
+      </c>
+      <c r="K747" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14T01:34:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B748" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C748" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　こうてい　全力フルオート攻略　サイヴァ、こよみなしで挑戦</t>
+        </is>
+      </c>
+      <c r="D748" s="2" t="inlineStr">
+        <is>
+          <t>あんずもんが皇帝を暦なし・推しエレノアで完全フルオート攻略。
+エレノアは5ターン以降に火力が急上昇し圧倒的な破壊力。
+聖王のデバフと回のサポートで11ターンクリア。</t>
+        </is>
+      </c>
+      <c r="E748" s="2" t="inlineStr">
+        <is>
+          <t>・エレノアは5ターン目以降ぶっ切りの火力で最強クラス
+・聖王を入れると精神低下でダメージが通りやすく非常に楽
+・回(カ)は攻撃回数が多くBP切れも防ぐ優秀なサポート
+・ソティが連続攻撃でデバフを稼ぎエレノアと好相性</t>
+        </is>
+      </c>
+      <c r="F748" s="2" t="inlineStr">
+        <is>
+          <t>・エレノアは避弾がきつく防御を上げないと事故リスクあり
+・回はウィークが取れずエレノアより火力面で見劣り</t>
+        </is>
+      </c>
+      <c r="G748" s="2" t="inlineStr">
+        <is>
+          <t>・皇帝フルオート
+・エレノア
+・暦なし編成
+・聖王デバフ
+・長期戦向き</t>
+        </is>
+      </c>
+      <c r="H748" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I748" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AdjI1OBgr60</t>
+        </is>
+      </c>
+      <c r="J748" s="2" t="inlineStr">
+        <is>
+          <t>AdjI1OBgr60</t>
+        </is>
+      </c>
+      <c r="K748" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14T01:34:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B749" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C749" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】思わぬ伏兵現る！使ってわかるこの強さ★新キャラランキング★鬼八＆おたまガチャ終了直前【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D749" s="2" t="inlineStr">
+        <is>
+          <t>つむつむが鬼八＆おたまガチャ終了直前の新キャラをランク付け。
+ヒューズがSS、エミリアとエレノアがS評価。
+シンディ・メイレン・ドール・タコおじさんはA止まり。</t>
+        </is>
+      </c>
+      <c r="E749" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズはSS20ヒット全体で御両師会に優秀な超火力
+・エレノアは5ターン目以降SS級でボルカンとの相性がやばい
+・エミリアは3属性サポーターで上の苦戦を緩和できる</t>
+        </is>
+      </c>
+      <c r="F749" s="2" t="inlineStr">
+        <is>
+          <t>・シンディキャンベルはバフがニッチで防具も低くA止まり
+・メイレンはEF1.25倍と低く西王比較で厳しい
+・ドールは2ターン目以降は自分だけで実装回数の少なさも不安
+・タコおじさんは3回冷光が攻撃条件で使い勝手に難</t>
+        </is>
+      </c>
+      <c r="G749" s="2" t="inlineStr">
+        <is>
+          <t>・新キャラランキング
+・ヒューズSS
+・エレノアS
+・エミリアS
+・過称評価</t>
+        </is>
+      </c>
+      <c r="H749" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I749" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SQHF8KTnYug</t>
+        </is>
+      </c>
+      <c r="J749" s="2" t="inlineStr">
+        <is>
+          <t>SQHF8KTnYug</t>
+        </is>
+      </c>
+      <c r="K749" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14T01:34:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B750" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C750" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今1番ぶっ壊れな技って多分これだよね？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D750" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーが「チョコレートの贈り物」をぶっ壊れ技と紹介。
+2ターン味方全員が回数無制限のダメージブロックで無敵化。
+FFRKコラボ皇帝戦をおたま軸で7ターン攻略。</t>
+        </is>
+      </c>
+      <c r="E750" s="2" t="inlineStr">
+        <is>
+          <t>・チョコレートの贈り物は2ターン全攻撃を0にする壊れ性能
+・おたまは火力貢献・EFばらまき・火力バフで万能
+・ガードアップ超極大で開幕2ターンの防御も高い
+・ジェラールは7.5周年前だが今も十分強い</t>
+        </is>
+      </c>
+      <c r="F750" s="2" t="inlineStr">
+        <is>
+          <t>・超長期戦ではダメージブロックの恩恵が薄れる場面もある
+・おたまのEFは自前持ちと被りやすく弱点なし相手では無駄になりがち</t>
+        </is>
+      </c>
+      <c r="G750" s="2" t="inlineStr">
+        <is>
+          <t>・チョコレートの贈り物
+・おたま
+・ダメージブロック
+・皇帝戦
+・火力貢献</t>
+        </is>
+      </c>
+      <c r="H750" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I750" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xIipCP2WkTM</t>
+        </is>
+      </c>
+      <c r="J750" s="2" t="inlineStr">
+        <is>
+          <t>xIipCP2WkTM</t>
+        </is>
+      </c>
+      <c r="K750" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14T01:34:25Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K750"/>
+  <dimension ref="A1:K756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -49736,6 +49736,411 @@
         </is>
       </c>
     </row>
+    <row r="751">
+      <c r="A751" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B751" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C751" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】まさかの水星ガシャ！？7月16日ガシャ予告 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D751" s="2" t="inlineStr">
+        <is>
+          <t>7/16ガシャ予告を解説。ダリルバルデとミカエリスが登場。
+2体ともシーズン2仕様で、まさかの水星の魔女から2枠追加。
+水星URは6体に。ファースト記念ガシャは別開催、性能は明日判明。</t>
+        </is>
+      </c>
+      <c r="E751" s="2" t="inlineStr">
+        <is>
+          <t>・水星から2枠追加でURが一気に6体に増えた
+・他作品もURをもっと出せると分かって良かった</t>
+        </is>
+      </c>
+      <c r="F751" s="2" t="inlineStr">
+        <is>
+          <t>・性能未公開でまだ評価できない
+・ファースト記念ガシャと同時開催だが内容は無関係</t>
+        </is>
+      </c>
+      <c r="G751" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・7/16ガシャ予告
+・ダリルバルデ
+・ミカエリス
+・水星の魔女
+・900万DL記念ガシャ</t>
+        </is>
+      </c>
+      <c r="H751" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I751" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JCmDNCHI0Rg</t>
+        </is>
+      </c>
+      <c r="J751" s="2" t="inlineStr">
+        <is>
+          <t>JCmDNCHI0Rg</t>
+        </is>
+      </c>
+      <c r="K751" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15T01:07:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B752" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C752" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】まさかの水星ガシャ！？7月16日ガシャ予告 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D752" s="2" t="inlineStr">
+        <is>
+          <t>7/16ガシャ予告を解説するShorts版。ダリルバルデとミカエリス。
+2体ともシーズン2仕様で、まさかの水星の魔女から2枠追加。
+水星URは6体に。ファースト記念は別開催、性能は明日判明。</t>
+        </is>
+      </c>
+      <c r="E752" s="2" t="inlineStr">
+        <is>
+          <t>・水星から2枠追加でURが一気に6体に増えた
+・他作品もURをもっと出せると分かって良かった</t>
+        </is>
+      </c>
+      <c r="F752" s="2" t="inlineStr">
+        <is>
+          <t>・性能未公開でまだ評価できない
+・ファースト記念ガシャと同時開催だが内容は無関係</t>
+        </is>
+      </c>
+      <c r="G752" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・7/16ガシャ予告
+・ダリルバルデ
+・ミカエリス
+・水星の魔女
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H752" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I752" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=O8MhHbUBjMY</t>
+        </is>
+      </c>
+      <c r="J752" s="2" t="inlineStr">
+        <is>
+          <t>O8MhHbUBjMY</t>
+        </is>
+      </c>
+      <c r="K752" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15T01:07:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B753" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C753" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】無尽塔41の倒し方を探る</t>
+        </is>
+      </c>
+      <c r="D753" s="2" t="inlineStr">
+        <is>
+          <t>排水なしで無尽塔41層クリアを模索する検証配信。
+気ハチ・ノエル・AJ・ビクトール等を試すもHPがほぼ減らず。
+ボスが強すぎ結局クリアならず。排水必須との結論に。</t>
+        </is>
+      </c>
+      <c r="E753" s="2" t="inlineStr">
+        <is>
+          <t>・AJを入れると火力がガツンと上がる
+・6ブーケが強く回避・解除に便利
+・ノエルは火力こそ正義で頼れる
+・無償ジュエルが貯まり7/16ガチャは60〜70連引けそう</t>
+        </is>
+      </c>
+      <c r="F753" s="2" t="inlineStr">
+        <is>
+          <t>・41層ボスが強すぎHPがミリしか減らない
+・回復と防御上昇がえぐく実質クリア不能
+・LP削り攻撃の回避が運ゲーで理不尽
+・12時間で強制終了・セーブ不可の仕様に不満
+・FFRKコラボはガチャなしで残念</t>
+        </is>
+      </c>
+      <c r="G753" s="2" t="inlineStr">
+        <is>
+          <t>・無尽塔41層
+・排水なし攻略
+・メルティパッション
+・ノエル/AJ/気ハチ
+・LP削り対策
+・7/16ガチャ</t>
+        </is>
+      </c>
+      <c r="H753" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I753" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1Epsh8wPpHE</t>
+        </is>
+      </c>
+      <c r="J753" s="2" t="inlineStr">
+        <is>
+          <t>1Epsh8wPpHE</t>
+        </is>
+      </c>
+      <c r="K753" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15T01:07:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B754" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C754" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】あの2キャラが遂に来てしまう！？7月16日のガチャを徹底予想！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D754" s="2" t="inlineStr">
+        <is>
+          <t>7/16実装ガチャを徹底予想する恒例動画。
+メインストーリーは8月頭、今回は夏祭り・浴衣ガチャと予想。
+兄ニー編とコッペリア編のダブルガチャを大胆予想。</t>
+        </is>
+      </c>
+      <c r="E754" s="2" t="inlineStr">
+        <is>
+          <t>・兄ニー・オルロージュ・コッペリアは浴衣が似合いそう
+・バイメニャの若い頃が実装されたら大当たり</t>
+        </is>
+      </c>
+      <c r="F754" s="2" t="inlineStr">
+        <is>
+          <t>・FFRKコラボガチャは用意できないとPが明言済み
+・マニアックな編成予想で「誰が引くのか」と自嘲</t>
+        </is>
+      </c>
+      <c r="G754" s="2" t="inlineStr">
+        <is>
+          <t>・7/16ガチャ予想
+・夏祭り・浴衣ガチャ
+・兄ニー編
+・コッペリア編
+・バイメニャ若い頃
+・公式生放送は8月頭予想</t>
+        </is>
+      </c>
+      <c r="H754" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I754" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=luDHtJNRJi4</t>
+        </is>
+      </c>
+      <c r="J754" s="2" t="inlineStr">
+        <is>
+          <t>luDHtJNRJi4</t>
+        </is>
+      </c>
+      <c r="K754" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15T01:07:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B755" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C755" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第128回カモキングたちの井戸〜8つのクリアパーティ徹底考察〜厳選16体によるクリア考察</t>
+        </is>
+      </c>
+      <c r="D755" s="2" t="inlineStr">
+        <is>
+          <t>第128回カモキングたちの井戸の攻略考察動画。
+敵3体ランダムで単体アタッカーも活躍、弱点は突・雷。
+活躍キャラ16体とクリア編成8パターンを徹底解説。</t>
+        </is>
+      </c>
+      <c r="E755" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズは全体WS20ヒットと雷弱点が刺さり最有力
+・暦み・ビクトールは弱点なしでもスタメン級の実績
+・リアムの雷単体41ヒットが強力
+・アイスは味方へのバフ量がやばい</t>
+        </is>
+      </c>
+      <c r="F755" s="2" t="inlineStr">
+        <is>
+          <t>・サライは手数が多いのがネガティブ要素
+・アイスも8ヒットで手数多めが難点
+・カモフックの元動画は弱すぎて試し打ち未遂</t>
+        </is>
+      </c>
+      <c r="G755" s="2" t="inlineStr">
+        <is>
+          <t>・カモキングたちの井戸
+・第128回
+・弱点は突・雷
+・活躍キャラ16体
+・クリア編成8パターン
+・ヒューズ筆頭</t>
+        </is>
+      </c>
+      <c r="H755" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I755" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=h7lcDsFvXpM</t>
+        </is>
+      </c>
+      <c r="J755" s="2" t="inlineStr">
+        <is>
+          <t>h7lcDsFvXpM</t>
+        </is>
+      </c>
+      <c r="K755" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15T01:07:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B756" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C756" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】🌟ちゃむのガチャ配信🌟〜ヒューズ1点狙い〜カモキングたちの井戸に挑んで〜TOPを狙え‼️</t>
+        </is>
+      </c>
+      <c r="D756" s="2" t="inlineStr">
+        <is>
+          <t>ヒューズ1点狙いのガチャ配信。無償ジュエルで天井へ。
+すり抜けでミドやドールが来つつ、新スタイルを無事確保。
+取得キャラで無尽塔に挑むも不具合と育成不足で撤退。</t>
+        </is>
+      </c>
+      <c r="E756" s="2" t="inlineStr">
+        <is>
+          <t>・すり抜けが緩和されている
+・すり抜けでもミド級に強く取れて良かった</t>
+        </is>
+      </c>
+      <c r="F756" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズが天井近くまで出ず渋い
+・不具合でゲーム音が消えるトラブル
+・育成不足で無尽塔をまだ攻略できず</t>
+        </is>
+      </c>
+      <c r="G756" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ配信
+・ヒューズ1点狙い
+・メイレン編ガチャ
+・すり抜け緩和
+・無尽塔挑戦
+・無償ジュエル天井</t>
+        </is>
+      </c>
+      <c r="H756" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I756" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=n8A8raGcel4</t>
+        </is>
+      </c>
+      <c r="J756" s="2" t="inlineStr">
+        <is>
+          <t>n8A8raGcel4</t>
+        </is>
+      </c>
+      <c r="K756" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15T01:07:55Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K756"/>
+  <dimension ref="A1:K763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -50141,6 +50141,459 @@
         </is>
       </c>
     </row>
+    <row r="757">
+      <c r="A757" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B757" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C757" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「予告デーヴィド!?」FFコラボ終結からのアセルス来た!!!サガスカ緋色勢も慌てるな!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D757" s="2" t="inlineStr">
+        <is>
+          <t>アセルス定期便がストーリーに詰め込まれシングルガチャで実装。
+連達第1弾はマカとデス、今回のアセルスは強くない見立て。
+FFコラボは完全終結、螺旋ガチャも更新でひ雪・ネバン登場。</t>
+        </is>
+      </c>
+      <c r="E757" s="2" t="inlineStr">
+        <is>
+          <t>・ゴールデンローブ超進化で精神を補填する戦い方が良さそう
+・来週のデイビドやネバン限定に期待</t>
+        </is>
+      </c>
+      <c r="F757" s="2" t="inlineStr">
+        <is>
+          <t>・このタイミングのアセルスはおそらくあまり強くない
+・復刻はメリット薄く、よほどでない限り引く必要なし
+・シングルは最終工程など大物を突っ込む傾向で注意</t>
+        </is>
+      </c>
+      <c r="G757" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスガチャ
+・FFコラボ終結
+・連達マカ/デス
+・副防具超進化
+・螺旋ガチャ更新</t>
+        </is>
+      </c>
+      <c r="H757" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I757" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UmrZUkPzrgg</t>
+        </is>
+      </c>
+      <c r="J757" s="2" t="inlineStr">
+        <is>
+          <t>UmrZUkPzrgg</t>
+        </is>
+      </c>
+      <c r="K757" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B758" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C758" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】ダリルバルデとミカエリスの性能が一部公開されたので確認しよう 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D758" s="2" t="inlineStr">
+        <is>
+          <t>明日実装のダリルバルデとミカエリス等の性能を先行確認。
+ダリルバルデは低HPキープ型でピーキー、グエルと噛み合う。
+ミカエリスは覚醒武装射程減少で局所的、全て恒常。</t>
+        </is>
+      </c>
+      <c r="E758" s="2" t="inlineStr">
+        <is>
+          <t>・グエルのHP0でも5%回復とダリルバルデの低HPキープが噛み合う
+・シャディの支援防御2回は攻キャラとしてありがたい
+・ミカエリスの射程減少は刺さる所では便利</t>
+        </is>
+      </c>
+      <c r="F758" s="2" t="inlineStr">
+        <is>
+          <t>・ダリルバルデはかなりピーキーで扱いが難しそう
+・ラウダはサポートスキルがエネルギー回復で使いづらい
+・全部恒常なので好きでなければスルーが無難</t>
+        </is>
+      </c>
+      <c r="G758" s="2" t="inlineStr">
+        <is>
+          <t>・ダリルバルデ
+・ミカエリス
+・グエル/シャディ
+・射程減少デバフ
+・恒常ユニット</t>
+        </is>
+      </c>
+      <c r="H758" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I758" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-NarUTiVo-M</t>
+        </is>
+      </c>
+      <c r="J758" s="2" t="inlineStr">
+        <is>
+          <t>-NarUTiVo-M</t>
+        </is>
+      </c>
+      <c r="K758" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B759" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C759" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】低HP型 ダリルバルデ(Season2仕様)の性能確認 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D759" s="2" t="inlineStr">
+        <is>
+          <t>低HP型ダリルバルデ(Season2仕様)の性能を確認するShorts。
+HP25%以下でスウェー付与、キープできれば強いがピーキー。
+搭乗キャラのグエルがHP0でも踏ん張れて噛み合う。</t>
+        </is>
+      </c>
+      <c r="E759" s="2" t="inlineStr">
+        <is>
+          <t>・HPを減らしキープできれば結構強い
+・グエルの踏ん張り効果と低HPキープが噛み合う</t>
+        </is>
+      </c>
+      <c r="F759" s="2" t="inlineStr">
+        <is>
+          <t>・EX武装が必中など癖が強く、かなりピーキーで扱いが難しそう</t>
+        </is>
+      </c>
+      <c r="G759" s="2" t="inlineStr">
+        <is>
+          <t>・ダリルバルデ
+・低HP型
+・スウェー付与
+・グエル
+・攻撃型</t>
+        </is>
+      </c>
+      <c r="H759" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I759" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UFxlWcr2RUI</t>
+        </is>
+      </c>
+      <c r="J759" s="2" t="inlineStr">
+        <is>
+          <t>UFxlWcr2RUI</t>
+        </is>
+      </c>
+      <c r="K759" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B760" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C760" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ストーリー更新！7月16日更新情報まとめ 【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D760" s="2" t="inlineStr">
+        <is>
+          <t>7/16更新の暦み編第6話全編、アセルス編の情報まとめ。
+ボックスとログボで3000ジュエル、超進化防具も追加。
+今回のコラボは大規模でなくイベントボスのみの模様。</t>
+        </is>
+      </c>
+      <c r="E760" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスは欲しい・取っておきたい
+・イベントボックスとログボで結構ジュエルが貰える
+・超進化防具に現時のコテ・エルメスの靴が追加</t>
+        </is>
+      </c>
+      <c r="F760" s="2" t="inlineStr">
+        <is>
+          <t>・今回のコラボはドラクエタクト時のような大規模ではなくイベントボスだけっぽい
+・マカは努力目標ぐらい</t>
+        </is>
+      </c>
+      <c r="G760" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス編
+・暦み編第6話
+・連達 王地連/ナイトメア
+・超進化防具
+・螺旋更新</t>
+        </is>
+      </c>
+      <c r="H760" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I760" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zff6Gz7erKI</t>
+        </is>
+      </c>
+      <c r="J760" s="2" t="inlineStr">
+        <is>
+          <t>Zff6Gz7erKI</t>
+        </is>
+      </c>
+      <c r="K760" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B761" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C761" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】覚醒武装の射程減少 ミカエリス(Season2仕様)の性能確認 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D761" s="2" t="inlineStr">
+        <is>
+          <t>ミカエリス(Season2仕様)の性能を確認するShorts。
+覚醒武装の射程減少デバフ持ちで特殊武装相手に強い。
+キャラのシャディは支援防御2回持ちで無難に優秀。</t>
+        </is>
+      </c>
+      <c r="E761" s="2" t="inlineStr">
+        <is>
+          <t>・射程減少は刺さる所では刺さる便利な効果
+・シャディの支援防御2回はありがたい
+・シャディはHP回復持ちで耐久型として十分いい</t>
+        </is>
+      </c>
+      <c r="F761" s="2" t="inlineStr"/>
+      <c r="G761" s="2" t="inlineStr">
+        <is>
+          <t>・ミカエリス
+・覚醒武装射程減少
+・耐久型
+・シャディ
+・支援防御2回</t>
+        </is>
+      </c>
+      <c r="H761" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I761" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lPCe6Nw0j9c</t>
+        </is>
+      </c>
+      <c r="J761" s="2" t="inlineStr">
+        <is>
+          <t>lPCe6Nw0j9c</t>
+        </is>
+      </c>
+      <c r="K761" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B762" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C762" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】遂にアセルス現る！公式最新情報【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D762" s="2" t="inlineStr">
+        <is>
+          <t>暦読み編第6話前編記念でアセルス・マカ・デスのシングルガチャ。
+復刻ジュエルビースト勢は今も使え、超進化防具も追加。
+アセルスは人気だが環境を引っ張るスタイルではない見立て。</t>
+        </is>
+      </c>
+      <c r="E762" s="2" t="inlineStr">
+        <is>
+          <t>・リバイバルの神など全員未だに使える
+・防具超進化系（現時のコテ・エルメスの靴）が好きで嬉しい
+・マカは4刀→5刀流で強そう</t>
+        </is>
+      </c>
+      <c r="F762" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスは直近すごく使うタイミングはなく環境を引っ張るスタイルではない</t>
+        </is>
+      </c>
+      <c r="G762" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス編
+・マカ/デス
+・防具超進化
+・復刻ジュエルビースト
+・螺旋チケット</t>
+        </is>
+      </c>
+      <c r="H762" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I762" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7OyDgjT_t2Y</t>
+        </is>
+      </c>
+      <c r="J762" s="2" t="inlineStr">
+        <is>
+          <t>7OyDgjT_t2Y</t>
+        </is>
+      </c>
+      <c r="K762" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B763" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C763" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】要チェック要素アリ！アセルス登場の最新情報をさっそく確認していく！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D763" s="2" t="inlineStr">
+        <is>
+          <t>7/16から暦読み編第6話全編、シングルのアセルス編が開催。
+シングルは強キャラが盛られる傾向で性能に警戒が必要。
+超進化防具に現時のコテ・エルメスの靴が追加、要チェック。</t>
+        </is>
+      </c>
+      <c r="E763" s="2" t="inlineStr">
+        <is>
+          <t>・超進化防具（現時のコテ・エルメスの靴）追加は要チェックで期待
+・イベントとログボで3000ジュエルずつ貰えてありがたい</t>
+        </is>
+      </c>
+      <c r="F763" s="2" t="inlineStr">
+        <is>
+          <t>・シングルガチャは強キャラが盛られる傾向で「やべえのかな」と警戒</t>
+        </is>
+      </c>
+      <c r="G763" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス編
+・暦読み編第6話
+・超進化防具追加
+・スケジュール予想
+・ジュエル配布</t>
+        </is>
+      </c>
+      <c r="H763" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I763" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=THZPf_Pv7LI</t>
+        </is>
+      </c>
+      <c r="J763" s="2" t="inlineStr">
+        <is>
+          <t>THZPf_Pv7LI</t>
+        </is>
+      </c>
+      <c r="K763" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K763"/>
+  <dimension ref="A1:K779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -50594,6 +50594,1067 @@
         </is>
       </c>
     </row>
+    <row r="764">
+      <c r="A764" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B764" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C764" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ランク付「その超進化待って」副防具2種追加!!エルメスのくつとげんじのこての使い方を詳細解説しつつ過去8種防具を組み合わせたシナジーランキング!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D764" s="2" t="inlineStr">
+        <is>
+          <t>超進化副防具エルメスの靴と現事のコテが追加
+シナジー重視で必要になるまで進化は温存推奨
+能力プラス100に釣られず素材管理が重要</t>
+        </is>
+      </c>
+      <c r="E764" s="2" t="inlineStr">
+        <is>
+          <t>・エルメスの靴は行動補正上昇永続で行動順調整に有用
+・現事のコテはヒドラレザー等と重ねて火ダメ軽減が伸びる
+・西洋マント・ハルモニア等は継続して有用</t>
+        </is>
+      </c>
+      <c r="F764" s="2" t="inlineStr">
+        <is>
+          <t>・能力プラス100はステバフ環境でほぼ無意味
+・先走った超進化は使い所がなく無駄になる
+・残・火のみ体制で単品では効果薄</t>
+        </is>
+      </c>
+      <c r="G764" s="2" t="inlineStr">
+        <is>
+          <t>・超進化副防具
+・エルメスの靴
+・現事のコテ
+・シナジー
+・素材管理</t>
+        </is>
+      </c>
+      <c r="H764" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I764" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B6BuJuik-oY</t>
+        </is>
+      </c>
+      <c r="J764" s="2" t="inlineStr">
+        <is>
+          <t>B6BuJuik-oY</t>
+        </is>
+      </c>
+      <c r="K764" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B765" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C765" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】3体ランキング!!「サイヴァ超え」長兄デスのEX2.5倍付与に戦慄する&amp;最終皇帝女の残像!?エクストラ付与しつつの尻上がり編成マカ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D765" s="2" t="inlineStr">
+        <is>
+          <t>デス・マカ・アセルスの3体をランキング考察
+デスのEX直接関節2.5倍付与に戦慄する性能
+マカは属性縛りきつく不遇スタイルの評価</t>
+        </is>
+      </c>
+      <c r="E765" s="2" t="inlineStr">
+        <is>
+          <t>・デスはEX直接関節2.5倍で全アタッカー永続強化
+・デスは副産物的に持っておきたい性能
+・アセルスは60ヒットで長期戦・電池切れなし</t>
+        </is>
+      </c>
+      <c r="F765" s="2" t="inlineStr">
+        <is>
+          <t>・デスは1体しか超強化できないのがデメリット
+・マカは属性縛りの割にリターン少ない不遇スタイル
+・マカは昔の皇帝女より弱い個人性能</t>
+        </is>
+      </c>
+      <c r="G765" s="2" t="inlineStr">
+        <is>
+          <t>・デス
+・マカ
+・アセルス
+・エクストラフォース
+・3体ランキング</t>
+        </is>
+      </c>
+      <c r="H765" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I765" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=O1H-TBswqAY</t>
+        </is>
+      </c>
+      <c r="J765" s="2" t="inlineStr">
+        <is>
+          <t>O1H-TBswqAY</t>
+        </is>
+      </c>
+      <c r="K765" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B766" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C766" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】全てを薙ぎ倒す「陰60連打」アセルスで全てのアタッカーが過去のものに!?鬼八、こよみと徹底比較し継承の最優先を確定する!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D766" s="2" t="inlineStr">
+        <is>
+          <t>陰60連打アセルスを鬼八・こよみと徹底比較
+技2で腕力3000%到達のぶっ壊れ瞬発力
+継承はエクストラとBP+2を最優先と確定</t>
+        </is>
+      </c>
+      <c r="E766" s="2" t="inlineStr">
+        <is>
+          <t>・技2で60ヒット腕力3000%到達のぶっ壊れ
+・短期戦から長期戦までカバー可能
+・暦読み未所持なら最有力で欲しい</t>
+        </is>
+      </c>
+      <c r="F766" s="2" t="inlineStr">
+        <is>
+          <t>・BPが基本4不足で使いづらい構造
+・3ターンフィニッシュには爆発力不足
+・2ターンごとで火力が膨らむ感じはない</t>
+        </is>
+      </c>
+      <c r="G766" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス
+・陰60連打
+・暦読み比較
+・継承優先度
+・リキャスト2</t>
+        </is>
+      </c>
+      <c r="H766" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I766" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=d1j-WgrejUI</t>
+        </is>
+      </c>
+      <c r="J766" s="2" t="inlineStr">
+        <is>
+          <t>d1j-WgrejUI</t>
+        </is>
+      </c>
+      <c r="K766" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B767" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C767" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】前夜　お知らせ読んでいこう！　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D767" s="2" t="inlineStr">
+        <is>
+          <t>前夜のお知らせ読み＆雑談の縦型配信
+アセルス編ガチャよりヒューズを高評価
+投稿者は今回のガチャは引かない方針</t>
+        </is>
+      </c>
+      <c r="E767" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズがめちゃくちゃ強くデバフも入る
+・ヒューズは継承技も良くガサ入れで使える</t>
+        </is>
+      </c>
+      <c r="F767" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス編は1ターン井戸で萎える
+・ウィーク条件がネックで興味が薄い
+・イベントがないのがきつい</t>
+        </is>
+      </c>
+      <c r="G767" s="2" t="inlineStr">
+        <is>
+          <t>・雑談配信
+・アセルス編ガチャ
+・ヒューズ
+・縦型配信</t>
+        </is>
+      </c>
+      <c r="H767" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I767" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uAYzrpvX7ws</t>
+        </is>
+      </c>
+      <c r="J767" s="2" t="inlineStr">
+        <is>
+          <t>uAYzrpvX7ws</t>
+        </is>
+      </c>
+      <c r="K767" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B768" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C768" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】まただよ、、『こよみ編 第6話 前編 公開記念 Romancing祭 アセルス編』【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D768" s="2" t="inlineStr">
+        <is>
+          <t>アセルス編ガチャを80連回すも1体のみ
+引き渋り続きでモチベーションが低下
+結局優勝ガチャの天井でアセルス確保</t>
+        </is>
+      </c>
+      <c r="E768" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスを最終的に確保できた
+・今回のアセルスのイラストがかっこいい</t>
+        </is>
+      </c>
+      <c r="F768" s="2" t="inlineStr">
+        <is>
+          <t>・3体ピックアップなのに全然出ない
+・2枚抜きの外れ続きでモチベが下がる
+・結局天井まで行ってしまった</t>
+        </is>
+      </c>
+      <c r="G768" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス編ガチャ
+・ガチャ実況
+・天井
+・引き渋り</t>
+        </is>
+      </c>
+      <c r="H768" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I768" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Pq3myWEPYNA</t>
+        </is>
+      </c>
+      <c r="J768" s="2" t="inlineStr">
+        <is>
+          <t>Pq3myWEPYNA</t>
+        </is>
+      </c>
+      <c r="K768" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B769" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C769" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】特定行動超火力！アセルス編神速解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D769" s="2" t="inlineStr">
+        <is>
+          <t>アセルス編3キャラを車内から神速解説
+アセルスSS60ヒット2ターンに1回の火力
+デスは1人2.5倍・マカは24ヒットアタッカー</t>
+        </is>
+      </c>
+      <c r="E769" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスはSS60ヒットで火力が強い
+・デスは1人を2.5倍に高められ悪さできそう
+・マカはアタッカー性能を持ってきて偉い</t>
+        </is>
+      </c>
+      <c r="F769" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスは攻撃回数が多くもっさりする
+・アセルスは1ターン目は弱くBP足りない
+・マカのエクストラウィークは他と被る</t>
+        </is>
+      </c>
+      <c r="G769" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス
+・デス
+・マカ
+・SS60ヒット
+・車内配信</t>
+        </is>
+      </c>
+      <c r="H769" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I769" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0ERmQpqLn-o</t>
+        </is>
+      </c>
+      <c r="J769" s="2" t="inlineStr">
+        <is>
+          <t>0ERmQpqLn-o</t>
+        </is>
+      </c>
+      <c r="K769" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B770" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C770" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】アセルスの使い方！デメリット克服！聖王厄遂に2ターンfinish【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D770" s="2" t="inlineStr">
+        <is>
+          <t>アセルスのBP不足を竜人会継承で克服
+青ベルトで最後に動かし行動順を調整
+聖王厄を60ヒット前に2ターンで撃破</t>
+        </is>
+      </c>
+      <c r="E770" s="2" t="inlineStr">
+        <is>
+          <t>・竜人会でBP回復し技2技3ループが可能に
+・アセルス1人で300億超の火力
+・聖王厄を2ターンフィニッシュ達成
+・暦読みの中間火力も優秀</t>
+        </is>
+      </c>
+      <c r="F770" s="2" t="inlineStr">
+        <is>
+          <t>・継承技は追撃が出ずBP不足になるデメリット
+・一枠を調整に使わないといけない</t>
+        </is>
+      </c>
+      <c r="G770" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス
+・竜人会
+・BP克服
+・聖王厄2ターン
+・行動順調整</t>
+        </is>
+      </c>
+      <c r="H770" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I770" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XLFaBTzzX0w</t>
+        </is>
+      </c>
+      <c r="J770" s="2" t="inlineStr">
+        <is>
+          <t>XLFaBTzzX0w</t>
+        </is>
+      </c>
+      <c r="K770" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B771" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C771" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】火力最大到達点1人で400億越1ターン★アセルス×デスがやばすぎる【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D771" s="2" t="inlineStr">
+        <is>
+          <t>アセルス×デスで1人400億超の最大火力
+キハも240億の高火力を記録
+デスの直接関節エクストラが被らず優秀</t>
+        </is>
+      </c>
+      <c r="E771" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス×デスで1人400億超の火力
+・キハも約240億の高火力
+・デスの直接関節エクストラは被りにくく偉い</t>
+        </is>
+      </c>
+      <c r="F771" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスはBP消費が多く回しづらい
+・残人で弱点をつく必要がある縛り</t>
+        </is>
+      </c>
+      <c r="G771" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス
+・デス
+・キハ
+・最大火力400億
+・エクストラフォース</t>
+        </is>
+      </c>
+      <c r="H771" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I771" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZprRxGNpWQo</t>
+        </is>
+      </c>
+      <c r="J771" s="2" t="inlineStr">
+        <is>
+          <t>ZprRxGNpWQo</t>
+        </is>
+      </c>
+      <c r="K771" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B772" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C772" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみ編 第6話 前編 公開記念ガチャ😻</t>
+        </is>
+      </c>
+      <c r="D772" s="2" t="inlineStr">
+        <is>
+          <t>こよみ編第6話ガチャを実況＆雑談配信
+アセルスとデスをセットで確保
+キハとアセルスの火力を比較検証</t>
+        </is>
+      </c>
+      <c r="E772" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスはエクストラを乗せるほど強い
+・アセルスは防御面のケアもできる
+・デスの死の力・オバドラ満タンが強い
+・キハの火力がえぐい</t>
+        </is>
+      </c>
+      <c r="F772" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスは強くも弱くもない印象
+・アセルスは技にコストを要求される
+・デスは今回は取らない判断</t>
+        </is>
+      </c>
+      <c r="G772" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス
+・デス
+・ガチャ実況
+・キハ火力比較</t>
+        </is>
+      </c>
+      <c r="H772" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I772" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7suI39FD7G4</t>
+        </is>
+      </c>
+      <c r="J772" s="2" t="inlineStr">
+        <is>
+          <t>7suI39FD7G4</t>
+        </is>
+      </c>
+      <c r="K772" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B773" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C773" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】みんな気付いてる？実はこのイベント大チャンスなんです！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D773" s="2" t="inlineStr">
+        <is>
+          <t>暦読み編ボックスガチャイベントを解説
+Box11のライクス調査許可証が重要
+21以降はプラチナチケット狙いで価値上昇</t>
+        </is>
+      </c>
+      <c r="E773" s="2" t="inlineStr">
+        <is>
+          <t>・Box11のライクス調査許可証は必ず取るべき
+・プラチナチケットはプラガチャ限定用で価値上昇
+・配布ビンセントで最速周回できる</t>
+        </is>
+      </c>
+      <c r="F773" s="2" t="inlineStr">
+        <is>
+          <t>・連静が5枠ずつで面倒・一気にやらせてほしい
+・11以降の目玉報酬は従来しょぼい</t>
+        </is>
+      </c>
+      <c r="G773" s="2" t="inlineStr">
+        <is>
+          <t>・ボックスガチャ
+・ライクス調査許可証
+・プラチナチケット
+・11秒周回</t>
+        </is>
+      </c>
+      <c r="H773" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I773" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AH_Y1Kv09rI</t>
+        </is>
+      </c>
+      <c r="J773" s="2" t="inlineStr">
+        <is>
+          <t>AH_Y1Kv09rI</t>
+        </is>
+      </c>
+      <c r="K773" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B774" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C774" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】脅威の60ヒットアタッカー爆誕！？アセルス編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D774" s="2" t="inlineStr">
+        <is>
+          <t>アセルス編3キャラの性能を実装直後チェック
+マカはデューン系で後方ほど強化される
+アセルスはSS60ヒットの脅威のアタッカー</t>
+        </is>
+      </c>
+      <c r="E774" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスはSS60ヒットで強力
+・マカは後方キャラほど強化され防御も硬くなる
+・マカのエクストラフォースも後方ほど倍率上昇</t>
+        </is>
+      </c>
+      <c r="F774" s="2" t="inlineStr">
+        <is>
+          <t>・マカのバフはカンストしやすく3人目以降は無駄気味
+・エクストラウィークは重複せず被りやすい</t>
+        </is>
+      </c>
+      <c r="G774" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス
+・マカ
+・デス
+・SS60ヒット
+・デューン系</t>
+        </is>
+      </c>
+      <c r="H774" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I774" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=W6nJ6nhYEyc</t>
+        </is>
+      </c>
+      <c r="J774" s="2" t="inlineStr">
+        <is>
+          <t>W6nJ6nhYEyc</t>
+        </is>
+      </c>
+      <c r="K774" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B775" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C775" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】圧倒的1位はこれだ！最新版超進化おすすめ防具ランキング【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D775" s="2" t="inlineStr">
+        <is>
+          <t>最新版の超進化防具おすすめランキング
+1位西王マント2位ハルモニア3位エルメスの靴
+新規の現事のコテはダメブロ付与が貴重</t>
+        </is>
+      </c>
+      <c r="E775" s="2" t="inlineStr">
+        <is>
+          <t>・西王マントはBP補給で毎日使う最優秀装備
+・ハルモニアは火ダメ軽減20%で優秀
+・現事のコテはダメブロ1回付与が貴重で神
+・エルメスの靴は行動順上昇で当たり</t>
+        </is>
+      </c>
+      <c r="F775" s="2" t="inlineStr">
+        <is>
+          <t>・現事のコテは残体制のみで若干使いにくい
+・エルメスの靴は突体制のみ・火ダメ15%止まり</t>
+        </is>
+      </c>
+      <c r="G775" s="2" t="inlineStr">
+        <is>
+          <t>・超進化防具ランキング
+・西王マント
+・ハルモニア
+・エルメスの靴
+・現事のコテ</t>
+        </is>
+      </c>
+      <c r="H775" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I775" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=w7Ng71ZLOkc</t>
+        </is>
+      </c>
+      <c r="J775" s="2" t="inlineStr">
+        <is>
+          <t>w7Ng71ZLOkc</t>
+        </is>
+      </c>
+      <c r="K775" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B776" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C776" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】過去最高の性能持ちが⁉︎アセルスガチャ性能チェック・キャラランク付け【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D776" s="2" t="inlineStr">
+        <is>
+          <t>ガチャ3キャラの性能をテキスト中心にまとめ
+アセルス60ヒットは全キャラトップクラス
+マカは必須感なく来週見てからでも良い</t>
+        </is>
+      </c>
+      <c r="E776" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスのSS60ヒットは全キャラトップクラス
+・デスのEX2.5倍は優秀でシナジー高い
+・マカは最後に動くキャラのバフ量がとんでもない</t>
+        </is>
+      </c>
+      <c r="F776" s="2" t="inlineStr">
+        <is>
+          <t>・マカはすぐ上限到達で窮屈・必須感がない
+・デス・アセルスはウィーク条件依存で相手を選ぶ
+・マカは残縛りで扱いづらい</t>
+        </is>
+      </c>
+      <c r="G776" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス
+・デス
+・マカ
+・キャラランク付け
+・エクストラフォース</t>
+        </is>
+      </c>
+      <c r="H776" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I776" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8x-HnWRHoio</t>
+        </is>
+      </c>
+      <c r="J776" s="2" t="inlineStr">
+        <is>
+          <t>8x-HnWRHoio</t>
+        </is>
+      </c>
+      <c r="K776" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B777" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C777" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】アセルス編ガチャ能力値早見表 ~斬陰属性強化ガチャ‼️SS60連は…エグい…【アセルス・デス・マカ考察】</t>
+        </is>
+      </c>
+      <c r="D777" s="2" t="inlineStr">
+        <is>
+          <t>アセルス編ガチャの能力値早見表を紹介
+アセルスが飛び抜けてやばく獲得必須
+マカ・デスは確保するか悩ましい性能</t>
+        </is>
+      </c>
+      <c r="E777" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスは60連打・火力バフ3745%で獲得必須
+・デスは斬一体強化で活躍・フォース被りづらい
+・久々に良いアタッカーアセルスが来て良かった</t>
+        </is>
+      </c>
+      <c r="F777" s="2" t="inlineStr">
+        <is>
+          <t>・マカはサポート値がインフレせず活躍枠が微妙
+・デスもサポート値がインフレせず確保か悩む</t>
+        </is>
+      </c>
+      <c r="G777" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス
+・デス
+・マカ
+・能力値早見表
+・斬陰強化ガチャ</t>
+        </is>
+      </c>
+      <c r="H777" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I777" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LD9CmB2n56g</t>
+        </is>
+      </c>
+      <c r="J777" s="2" t="inlineStr">
+        <is>
+          <t>LD9CmB2n56g</t>
+        </is>
+      </c>
+      <c r="K777" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B778" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C778" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「アセルス 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D778" s="2" t="inlineStr">
+        <is>
+          <t>アセルス・マカ・デスをスタイル考察しランク付け
+3体ともに総合評価Bと判定
+いずれもウィーク条件依存で相手を選ぶ</t>
+        </is>
+      </c>
+      <c r="E778" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスはSS60ヒットで体持ちにも強い
+・デスは単体2.5倍でフォース被りにくく強力
+・マカは上ではライクスで活躍でき便利枠かも</t>
+        </is>
+      </c>
+      <c r="F778" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスはザン・イン弱点必須で相手を選ぶ
+・マカは残かつウィーク条件がきつく扱いづらい
+・デスはLP-5デメリットが重く敵依存</t>
+        </is>
+      </c>
+      <c r="G778" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス
+・マカ
+・デス
+・スタイル考察
+・ランク付けB</t>
+        </is>
+      </c>
+      <c r="H778" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I778" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=njbaBzZttdI</t>
+        </is>
+      </c>
+      <c r="J778" s="2" t="inlineStr">
+        <is>
+          <t>njbaBzZttdI</t>
+        </is>
+      </c>
+      <c r="K778" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B779" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C779" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベント解説 注意点 11秒周回編成3種紹介【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D779" s="2" t="inlineStr">
+        <is>
+          <t>暦読み編イベントの解説と注意点を紹介
+11秒周回編成を3種類紹介
+ボックスガチャの効率的な回し方を解説</t>
+        </is>
+      </c>
+      <c r="E779" s="2" t="inlineStr">
+        <is>
+          <t>・11秒周回編成を3種紹介
+・6踏み出した先が集回おすすめ</t>
+        </is>
+      </c>
+      <c r="F779" s="2" t="inlineStr">
+        <is>
+          <t>・周回メリットはレリック連静ぐらいで薄い
+・目ぼしいもの回収後は他クエへ移行推奨
+・レリックアクセの同一3つ狙いは沼にはまる</t>
+        </is>
+      </c>
+      <c r="G779" s="2" t="inlineStr">
+        <is>
+          <t>・暦読み編イベント
+・ボックスガチャ
+・11秒周回編成
+・レリック連静</t>
+        </is>
+      </c>
+      <c r="H779" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I779" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6LIVb8tA7is</t>
+        </is>
+      </c>
+      <c r="J779" s="2" t="inlineStr">
+        <is>
+          <t>6LIVb8tA7is</t>
+        </is>
+      </c>
+      <c r="K779" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:52:17Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K779"/>
+  <dimension ref="A1:K789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -51655,6 +51655,669 @@
         </is>
       </c>
     </row>
+    <row r="780">
+      <c r="A780" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B780" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C780" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「周年明けにぶっ壊れ」月刊ワースト&amp;MVPランキング!!2026年1月振り返り→強さの指標は未来から来たマイス!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D780" s="2" t="inlineStr">
+        <is>
+          <t>2026年1月ガチャの月刊ワースト＆MVP振り返り
+正月ネタガチャや縛り系スタイルは総じて不遇
+MVPはマイス、火力サポートの好指標に</t>
+        </is>
+      </c>
+      <c r="E780" s="2" t="inlineStr">
+        <is>
+          <t>・マイスはエクストラ突出で火力サポートの好指標
+・ミドはサブアタッカーとして今も使える
+・デスマシーンは全体連打を先取りしたぶっ壊れ
+・ファイアブリンガーは回避・個人火力が高水準</t>
+        </is>
+      </c>
+      <c r="F780" s="2" t="inlineStr">
+        <is>
+          <t>・正月ネタガチャは高難度で使い道ほぼなし
+・ラウンド縛りスタイルは縛らない方が強く不遇
+・アセルス・気ハは継承目的のみで外れ気味
+・モンスター娘ガチャも大枠外れで急ぐ必要なし</t>
+        </is>
+      </c>
+      <c r="G780" s="2" t="inlineStr">
+        <is>
+          <t>・月刊ランキング
+・正月ガチャ
+・マイス評価
+・縛りスタイル
+・MVP選定</t>
+        </is>
+      </c>
+      <c r="H780" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I780" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=frWwvqarPTE</t>
+        </is>
+      </c>
+      <c r="J780" s="2" t="inlineStr">
+        <is>
+          <t>frWwvqarPTE</t>
+        </is>
+      </c>
+      <c r="K780" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19T01:07:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B781" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C781" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「アセルス」のランクは!?→9体3ガチャランキング!!最新スタイルの最強を決める比較検討会→2026年7月18日版　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D781" s="2" t="inlineStr">
+        <is>
+          <t>アセルス等9体を3ガチャで比較検討
+最下シンディ、縛りきついメイレン・マカは評価控えめ
+デス・アセルスは尖った強さで出番多い</t>
+        </is>
+      </c>
+      <c r="E781" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスはノエル型を尖らせSS60連打で強力
+・デスはエクストラ3倍重ねがけで突破役に強い
+・マカは仕上げれば火力サポートがちょいぶっ壊れ
+・エミリアは継承豊富で対応力高く使いやすい</t>
+        </is>
+      </c>
+      <c r="F781" s="2" t="inlineStr">
+        <is>
+          <t>・シンディは火力もサポートも弱く最下評価
+・タコおじは立ち上がり4ターンでチグハグ
+・メイレンは縛りきつくエクストラ1.25倍と低い
+・マカは2体目まで弱く編成の手間が重い</t>
+        </is>
+      </c>
+      <c r="G781" s="2" t="inlineStr">
+        <is>
+          <t>・9体比較
+・アセルス評価
+・縛り性能
+・マカ再評価
+・デス性能</t>
+        </is>
+      </c>
+      <c r="H781" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I781" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kIqs3L7ubVA</t>
+        </is>
+      </c>
+      <c r="J781" s="2" t="inlineStr">
+        <is>
+          <t>kIqs3L7ubVA</t>
+        </is>
+      </c>
+      <c r="K781" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19T01:07:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B782" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C782" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　神継承　持っていた事に感謝　あって良かった継承技80選</t>
+        </is>
+      </c>
+      <c r="D782" s="2" t="inlineStr">
+        <is>
+          <t>あって良かった継承技80選を武器別に紹介
+パリーや標平演舞、真食の御剣など実用技を解説
+今も現役で使える継承技を多数ピックアップ</t>
+        </is>
+      </c>
+      <c r="E782" s="2" t="inlineStr">
+        <is>
+          <t>・暦みの真食の御剣は防具弱体で今も重宝
+・最終皇帝女ルクスオーバーは火力爆上げで優秀
+・グスタフのエンジン連行は井戸で強力
+・バートランドの標平演舞は状態異常対策に有効
+・最終皇帝男レディアントセイバーはカウンターが強い</t>
+        </is>
+      </c>
+      <c r="F782" s="2" t="inlineStr"/>
+      <c r="G782" s="2" t="inlineStr">
+        <is>
+          <t>・継承技80選
+・武器別紹介
+・井戸活躍
+・状態異常対策
+・現役技</t>
+        </is>
+      </c>
+      <c r="H782" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I782" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=E6myz9wZ5gk</t>
+        </is>
+      </c>
+      <c r="J782" s="2" t="inlineStr">
+        <is>
+          <t>E6myz9wZ5gk</t>
+        </is>
+      </c>
+      <c r="K782" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19T01:07:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B783" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C783" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】　新規の方オススメ　序盤育成優先順位　TOP5</t>
+        </is>
+      </c>
+      <c r="D783" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣の序盤育成優先順位TOP5
+上杉謙信・北条氏政ら序盤強武将を紹介
+育成はSR武将優先、覚醒しやすさが鍵</t>
+        </is>
+      </c>
+      <c r="E783" s="2" t="inlineStr">
+        <is>
+          <t>・上杉謙信は武攻撃特攻で430%まで火力上昇
+・北条氏政は攻撃・会心上昇で火力が伸びる
+・SR武将は経験値少なく覚醒しやすく優秀
+・長宗我部元親は序盤の火力が高く強い</t>
+        </is>
+      </c>
+      <c r="F783" s="2" t="inlineStr">
+        <is>
+          <t>・長宗我部は強行解除でいずれ他キャラに劣る</t>
+        </is>
+      </c>
+      <c r="G783" s="2" t="inlineStr">
+        <is>
+          <t>・序盤育成
+・優先順位TOP5
+・上杉謙信
+・SR武将育成
+・覚醒効率</t>
+        </is>
+      </c>
+      <c r="H783" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I783" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IpXFu6o3KbY</t>
+        </is>
+      </c>
+      <c r="J783" s="2" t="inlineStr">
+        <is>
+          <t>IpXFu6o3KbY</t>
+        </is>
+      </c>
+      <c r="K783" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19T01:07:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B784" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C784" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】使い込んでSSS評価有！最新キャラランキング★要注意事項あり【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D784" s="2" t="inlineStr">
+        <is>
+          <t>日曜恒例の最新キャラランキング
+アセルスはトリプルS、使い込んで最高評価
+デスはザ・インのみでS止まり</t>
+        </is>
+      </c>
+      <c r="E784" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスは焦るハと双璧で300〜400億の火力
+・アセルスは使い込んだ結果トリプルS最高評価
+・デスは2.5倍配布が唯一無二で偉い</t>
+        </is>
+      </c>
+      <c r="F784" s="2" t="inlineStr">
+        <is>
+          <t>・デスはザ・インのトリガー依存で日陰、S止まり
+・デスは行動回数1でレイト運用向け</t>
+        </is>
+      </c>
+      <c r="G784" s="2" t="inlineStr">
+        <is>
+          <t>・最新ランキング
+・アセルスSSS
+・デス評価
+・螺旋基準
+・継承重視</t>
+        </is>
+      </c>
+      <c r="H784" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I784" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1S-f2uUYKX0</t>
+        </is>
+      </c>
+      <c r="J784" s="2" t="inlineStr">
+        <is>
+          <t>1S-f2uUYKX0</t>
+        </is>
+      </c>
+      <c r="K784" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19T01:07:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B785" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C785" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ジュエルビースト2ターンfinishに挑戦！それ行けゴリ押しの新星アセルス★【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D785" s="2" t="inlineStr">
+        <is>
+          <t>螺旋ジュエルビーストの2ターンゴリ押しに挑戦
+ミルザ投入で足りないHPを削り切る編成
+アセルスが1人60発340億で主軸に</t>
+        </is>
+      </c>
+      <c r="E785" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスは1人60発で340億超と圧巻
+・ミルザはマウンティフィストのカウンターが刺さる
+・マリスロードのファスト1.75倍が被らず強力</t>
+        </is>
+      </c>
+      <c r="F785" s="2" t="inlineStr">
+        <is>
+          <t>・ジュエルビーストは発狂・術無効でトップクラスに厄介
+・マスロケットスタート次第でクリアが不安定</t>
+        </is>
+      </c>
+      <c r="G785" s="2" t="inlineStr">
+        <is>
+          <t>・ジュエルビースト
+・2ターン攻略
+・ミルザ採用
+・アセルス火力
+・カウンター運用</t>
+        </is>
+      </c>
+      <c r="H785" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I785" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7Luw58wueNk</t>
+        </is>
+      </c>
+      <c r="J785" s="2" t="inlineStr">
+        <is>
+          <t>7Luw58wueNk</t>
+        </is>
+      </c>
+      <c r="K785" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19T01:07:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B786" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C786" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】火力限界突破★4大ガチャランキング！引くべき優先順位考察【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D786" s="2" t="inlineStr">
+        <is>
+          <t>開催中4ガチャの引くべき優先順位を考察
+当たりはヒューズ、火力こそ正義の全体20ヒット
+復刻ジュエルビーストは最下でスルー推奨</t>
+        </is>
+      </c>
+      <c r="E786" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズは全体20ヒットに強力追撃で最強格
+・エミリアは幻統・術技で汎用性高く現役
+・シンディキャンベルはレイドで活躍</t>
+        </is>
+      </c>
+      <c r="F786" s="2" t="inlineStr">
+        <is>
+          <t>・復刻ジュエルビーストは今更で出番増えずスルー
+・打特化メイレンはエクストラ不要量少なく進化待ち
+・アシュラ系は火力低く使いどころに注意</t>
+        </is>
+      </c>
+      <c r="G786" s="2" t="inlineStr">
+        <is>
+          <t>・4ガチャ比較
+・ヒューズ当たり
+・メイレン評価
+・エミリア現状
+・復刻スルー</t>
+        </is>
+      </c>
+      <c r="H786" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I786" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dsWIOZmQ_WU</t>
+        </is>
+      </c>
+      <c r="J786" s="2" t="inlineStr">
+        <is>
+          <t>dsWIOZmQ_WU</t>
+        </is>
+      </c>
+      <c r="K786" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19T01:07:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B787" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C787" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】最強クラスのガチャ登場に驚愕！？最新版確保優先度ランキング【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D787" s="2" t="inlineStr">
+        <is>
+          <t>7月18日最新版の確保優先度ランキング
+4ガチャ15スタイルを性能のみで優先度分け
+木ハオタ確保推奨、ミーティア・ヒューズも優先</t>
+        </is>
+      </c>
+      <c r="E787" s="2" t="inlineStr">
+        <is>
+          <t>・木ハオタは最優先で非常に強いガチャ評価
+・ミーティア・ヒューズを優先度高に据える</t>
+        </is>
+      </c>
+      <c r="F787" s="2" t="inlineStr">
+        <is>
+          <t>・メイレン編は7月20日終了で判断を急ぐ必要</t>
+        </is>
+      </c>
+      <c r="G787" s="2" t="inlineStr">
+        <is>
+          <t>・確保優先度
+・15スタイル
+・性能評価
+・アセルス編
+・終了間近</t>
+        </is>
+      </c>
+      <c r="H787" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I787" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bWtG7_0ujG8</t>
+        </is>
+      </c>
+      <c r="J787" s="2" t="inlineStr">
+        <is>
+          <t>bWtG7_0ujG8</t>
+        </is>
+      </c>
+      <c r="K787" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19T01:07:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B788" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C788" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】銃で当たりはあのキャラ！メイレン&amp;エミリアガチャ最終評価ランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D788" s="2" t="inlineStr">
+        <is>
+          <t>終了間近のメイレン＆エミリアガチャ最終評価
+星1〜星3＋特級戦力の4段階でランク付け
+ドールは星1、タコ・シンディ・エミリアは星2</t>
+        </is>
+      </c>
+      <c r="E788" s="2" t="inlineStr">
+        <is>
+          <t>・タコおじさんは霊32ヒットでレイド・周回向き
+・エミリアは打熱サポート複数持ちで器用
+・シンディはウィークインのアタッカー支援に好相性</t>
+        </is>
+      </c>
+      <c r="F788" s="2" t="inlineStr">
+        <is>
+          <t>・ドールは目立った性能なく星1評価
+・エミリアはエクストラがウィーク条件で残念
+・タコおじは敵の霊攻撃時にデメリットあり注意</t>
+        </is>
+      </c>
+      <c r="G788" s="2" t="inlineStr">
+        <is>
+          <t>・最終評価
+・星ランク
+・ドール星1
+・タコおじ星2
+・エミリア星2</t>
+        </is>
+      </c>
+      <c r="H788" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I788" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PoLN7SY7M1o</t>
+        </is>
+      </c>
+      <c r="J788" s="2" t="inlineStr">
+        <is>
+          <t>PoLN7SY7M1o</t>
+        </is>
+      </c>
+      <c r="K788" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19T01:07:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B789" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C789" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第129回サウノックたちの井戸〜6つのクリア編成考察【厳選20体によるクリア考察】</t>
+        </is>
+      </c>
+      <c r="D789" s="2" t="inlineStr">
+        <is>
+          <t>7月20日開始の第129回サウノック井戸を考察
+弱点は打熱要、斬に体制ありで編成に工夫
+1ターン撃破想定で活躍キャラ20体を厳選</t>
+        </is>
+      </c>
+      <c r="E789" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズは全体10連打＋デバフで大活躍中
+・ビクトールは単体40連打のスーパーアタッカー
+・バルテルミーは熱全体＋フォース400%で採用価値</t>
+        </is>
+      </c>
+      <c r="F789" s="2" t="inlineStr">
+        <is>
+          <t>・暦みは斬に体制ありで今回は火力が厳しい
+・井戸のHP・剛体配分が据え置きで1ターン化が進む</t>
+        </is>
+      </c>
+      <c r="G789" s="2" t="inlineStr">
+        <is>
+          <t>・サウノック井戸
+・1ターン撃破
+・打熱要弱点
+・ヒューズ活躍
+・火力サポーター</t>
+        </is>
+      </c>
+      <c r="H789" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I789" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ts1-Cqqm9ZM</t>
+        </is>
+      </c>
+      <c r="J789" s="2" t="inlineStr">
+        <is>
+          <t>Ts1-Cqqm9ZM</t>
+        </is>
+      </c>
+      <c r="K789" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19T01:07:15Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K789"/>
+  <dimension ref="A1:K795"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -52318,6 +52318,429 @@
         </is>
       </c>
     </row>
+    <row r="790">
+      <c r="A790" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B790" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C790" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋580階「最終皇帝出禁」ギミック解明速報!!編成2パターンでサクッとお給料アップ&amp;ジュエル確保!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D790" s="2" t="inlineStr">
+        <is>
+          <t>螺旋580階「最終皇帝」のギミックを速報解説。
+対象武器以外はダメージが通らず攻撃弱化が鍵。
+編成2パターンを提示し安定攻略を実演。</t>
+        </is>
+      </c>
+      <c r="E790" s="2" t="inlineStr">
+        <is>
+          <t>・対象武器が攻撃弱化を入れ防御を実質無効化できる
+・精神バフを盛れば常にカウンター状態で有利
+・ブーケが回避しながらうまく立ち回ってくれる
+・サイバ＋ターミンの編成は安定感がある
+・貝は弱点でなくともトレズトンで十分強い</t>
+        </is>
+      </c>
+      <c r="F790" s="2" t="inlineStr">
+        <is>
+          <t>・対象武器以外ではダメージが通らず編成が縛られる
+・カオンの回数が足りないと気絶コンボでやられる
+・ODなしの直接攻撃は気絶コンボで落とされる</t>
+        </is>
+      </c>
+      <c r="G790" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋回廊580階
+・最終皇帝
+・武器種制限
+・気絶コンボ
+・OD活用
+・編成2パターン</t>
+        </is>
+      </c>
+      <c r="H790" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I790" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=niWySQG3MXk</t>
+        </is>
+      </c>
+      <c r="J790" s="2" t="inlineStr">
+        <is>
+          <t>niWySQG3MXk</t>
+        </is>
+      </c>
+      <c r="K790" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T01:45:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B791" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C791" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始287日目記録　加速　成長したが課題も,,,</t>
+        </is>
+      </c>
+      <c r="D791" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣プレイ287日目の進捗記録。
+新キャラ5体入手、威名77万台・ランク95に到達。
+共闘は全滅しなくなったが功城戦は毛利に苦戦中。</t>
+        </is>
+      </c>
+      <c r="E791" s="2" t="inlineStr">
+        <is>
+          <t>・高橋紹運を100連で入手でき立花が大きく強化される
+・威名が前回から約1.8万上がり成長を実感
+・共闘で全滅しなくなり戦力的にかなり良くなった
+・長宗我部国親はバフ性能が高く交換して良かった
+・成田甲斐をガチャで入手でき今後に期待
+・野々村胸のりは能力は低いが特性が素晴らしい
+・視聴者コメントの助言で意識を転換し勝てるようになった</t>
+        </is>
+      </c>
+      <c r="F791" s="2" t="inlineStr">
+        <is>
+          <t>・毛利元就が強すぎて戦力差3万でも全然勝てない
+・功城戦551で目標700に届かず遅れている
+・軍雄リーグは編成ミスで35位止まり
+・吉川秋田を枠不足で編成に入れられなかった
+・長宗我部国親の交換1万2000は結構高かった
+・マイレージ20万は残り2か月でかなりきつい
+・制圧率が上がらず神社を強化できない</t>
+        </is>
+      </c>
+      <c r="G791" s="2" t="inlineStr">
+        <is>
+          <t>・信長の野望出陣
+・287日目記録
+・新キャラ入手
+・共闘
+・功城戦
+・マイレージ20万目標</t>
+        </is>
+      </c>
+      <c r="H791" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I791" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NxldL_pLAjQ</t>
+        </is>
+      </c>
+      <c r="J791" s="2" t="inlineStr">
+        <is>
+          <t>NxldL_pLAjQ</t>
+        </is>
+      </c>
+      <c r="K791" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T01:45:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B792" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C792" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSRパーフェクトジオング 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D792" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSSRパーフェクトジオング紹介。
+武装アニメーションをShortsで収録。
+シロッコのボイス付き演出を短尺で披露。</t>
+        </is>
+      </c>
+      <c r="E792" s="2" t="inlineStr">
+        <is>
+          <t>・「一気に殲滅する」など迫力ある殲滅演出</t>
+        </is>
+      </c>
+      <c r="F792" s="2" t="inlineStr"/>
+      <c r="G792" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・SSRパーフェクトジオング
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H792" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I792" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Nd0-Lz3xSxk</t>
+        </is>
+      </c>
+      <c r="J792" s="2" t="inlineStr">
+        <is>
+          <t>Nd0-Lz3xSxk</t>
+        </is>
+      </c>
+      <c r="K792" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T01:45:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B793" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C793" s="2" t="inlineStr">
+        <is>
+          <t>【サイコロ観光の旅】知り合いにドッキリを仕掛けて広島SaGa観光を突然する～前編【サガどうでしょう】</t>
+        </is>
+      </c>
+      <c r="D793" s="2" t="inlineStr">
+        <is>
+          <t>広島出身VTuber天王寺立にドッキリ企画を敢行。
+24面ダイスで広島23地域を巡りサガ要素を探す旅。
+1投目は廿日市＝宮島、2投目で155km先の芸北へ。</t>
+        </is>
+      </c>
+      <c r="E793" s="2" t="inlineStr">
+        <is>
+          <t>・1発目に宮島を引けて観光として最高のスタート
+・宮島の牡蠣カレーパンが熱々で美味しい
+・ネギタコの揚げもみじが甘みとしょっぱさで地味にうまい
+・鹿を「インパラ」、厳島神社を「レイ姫」としてサガ認定できた
+・景観に配慮した和風スタバなど街並みが綺麗
+・車移動のおかげで海岸の真下まで行けて恵まれた</t>
+        </is>
+      </c>
+      <c r="F793" s="2" t="inlineStr">
+        <is>
+          <t>・予定を2日間まるごと嘘で埋められた本人は災難
+・2投目で155km先の芸北を引き6か所制覇に暗雲
+・宮島だけで4時間近くかかりスケジュールが厳しい
+・大崎上島などフェリー必須の地域は当日中に行けない
+・揚げもみじは甘いものが苦手だとつらい</t>
+        </is>
+      </c>
+      <c r="G793" s="2" t="inlineStr">
+        <is>
+          <t>・サガどうでしょう
+・サイコロ観光の旅
+・広島県
+・ドッキリ企画
+・宮島
+・サガスポット探し</t>
+        </is>
+      </c>
+      <c r="H793" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I793" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CXh9AB_ghjA</t>
+        </is>
+      </c>
+      <c r="J793" s="2" t="inlineStr">
+        <is>
+          <t>CXh9AB_ghjA</t>
+        </is>
+      </c>
+      <c r="K793" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T01:45:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B794" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C794" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋回廊580階「最終皇帝」を攻略！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D794" s="2" t="inlineStr">
+        <is>
+          <t>螺旋回廊580階・最終皇帝の攻略解説動画。
+武器種縛りとデッドリーカウンターの対処法を紹介。
+アセルス未所持でも手持ち編成でクリア可能と実証。</t>
+        </is>
+      </c>
+      <c r="E794" s="2" t="inlineStr">
+        <is>
+          <t>・武器種制限を含めても敵はかなり弱く難易度は良い落としどころ
+・ソティ＋トークアイでOD常時満タンにしカウンターを無効化できる
+・アセルス・デスマカを引いていれば恐ろしく楽になる
+・装飾品や防具はこだわり不要で火力重視でよい
+・手持ちのアタッカーが弱くても総合力でカバーできた</t>
+        </is>
+      </c>
+      <c r="F794" s="2" t="inlineStr">
+        <is>
+          <t>・剣・槍・弓・杖・術以外は99%カットでほぼ無効
+・直近ガチャ（斬・陰特化）接待の露骨なステージ構成
+・デッドリーカウンターで直接攻撃に反撃される
+・40ヒット必要なマイターンコーションが手数を要求
+・武器種縛りがあるぶん編成がめんどくさい</t>
+        </is>
+      </c>
+      <c r="G794" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋回廊580階
+・最終皇帝
+・武器種縛り
+・デッドリーカウンター
+・マイターンコーション
+・クラウドシフト</t>
+        </is>
+      </c>
+      <c r="H794" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I794" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=f2Q6SM0fI8A</t>
+        </is>
+      </c>
+      <c r="J794" s="2" t="inlineStr">
+        <is>
+          <t>f2Q6SM0fI8A</t>
+        </is>
+      </c>
+      <c r="K794" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T01:45:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B795" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C795" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7月23日までのオススメの周回方法の紹介!今週のやり残しチェック!オマケに井戸もやります!【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D795" s="2" t="inlineStr">
+        <is>
+          <t>7月23日までのやり残しと周回方法をまとめた回。
+週末限定クエスト・FFコラボ・皇帝との戦いを整理。
+20日12時開始の鍛錬道場と今週の井戸編成も紹介。</t>
+        </is>
+      </c>
+      <c r="E795" s="2" t="inlineStr">
+        <is>
+          <t>・週末限定クエストは短時間で終わり豪華アイテムと交換できる
+・FFコラボミッションは合計5000ジュエルもらえてお得
+・ヒューズの全体火力は今のところ頭1つ抜けている
+・ロマパス上級のデイリー自動再戦チケットが6000回になり優秀
+・鍛錬道場は技のランク上げがなくても魂強化に使える
+・皇帝との戦いはロマンシング1回クリアで全交換できる</t>
+        </is>
+      </c>
+      <c r="F795" s="2" t="inlineStr">
+        <is>
+          <t>・井戸の報酬は挑戦の証とフレンドメダル程度でやらなくてもよい
+・現行イベントは必要分を回収したら周回する意味がほぼない
+・FFコラボは特務遠征ではミッション達成にならないので注意
+・共通錬磨素材は足りなくなりやすい
+・鍛錬道場はステータス育成の上限が低め
+・井戸は魂レベルや技の発動順で7手に届かずリトライが必要</t>
+        </is>
+      </c>
+      <c r="G795" s="2" t="inlineStr">
+        <is>
+          <t>・やり残しチェック
+・週末限定クエスト
+・FFコラボミッション
+・鍛錬道場
+・井戸
+・自動再戦</t>
+        </is>
+      </c>
+      <c r="H795" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I795" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=79bwPyXOFmA</t>
+        </is>
+      </c>
+      <c r="J795" s="2" t="inlineStr">
+        <is>
+          <t>79bwPyXOFmA</t>
+        </is>
+      </c>
+      <c r="K795" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20T01:45:23Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K795"/>
+  <dimension ref="A1:K805"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -52741,6 +52741,650 @@
         </is>
       </c>
     </row>
+    <row r="796">
+      <c r="A796" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B796" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C796" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「待望」プレイアブル化がようやく現実に!?水着!!浴衣!!ハロウィン!!!!推しキャラが万全の状態で到来し天井不可避のガチャ予想　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D796" s="2" t="inlineStr">
+        <is>
+          <t>探すか発売日記念ガチャの実装6体を予想する動画。
+GB・アンサガ枠に人気キャラ・新キャラを加えた構成を読む。
+水着後編を経て次は浴衣が控えると予測する。</t>
+        </is>
+      </c>
+      <c r="E796" s="2" t="inlineStr"/>
+      <c r="F796" s="2" t="inlineStr"/>
+      <c r="G796" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ予想
+・探すか発売記念
+・アンサガ/GB枠
+・水着・浴衣
+・新キャラ枠</t>
+        </is>
+      </c>
+      <c r="H796" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I796" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-p1Xl9UANGc</t>
+        </is>
+      </c>
+      <c r="J796" s="2" t="inlineStr">
+        <is>
+          <t>-p1Xl9UANGc</t>
+        </is>
+      </c>
+      <c r="K796" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21T01:27:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B797" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C797" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　技上げ道場　雑談しながら技Lv UP　Popular games in Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D797" s="2" t="inlineStr">
+        <is>
+          <t>技上げ道場をやりながらの雑談配信。
+ロマサガRSの人口減少やサブコンテンツの弱さを語る。
+今回のアセルスは特攻の割に微妙で技象用と評価。</t>
+        </is>
+      </c>
+      <c r="E797" s="2" t="inlineStr">
+        <is>
+          <t>・井戸や制圧戦はやり応えがあって良い
+・エレノアが強くて螺旋580もいける</t>
+        </is>
+      </c>
+      <c r="F797" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスは特攻でも4ターンで微妙・欲しくない
+・高難易度の所要時間が7〜8時間と長すぎる
+・サブコンテンツが弱くモチベが下がる
+・不具合(バグ)が増えている</t>
+        </is>
+      </c>
+      <c r="G797" s="2" t="inlineStr">
+        <is>
+          <t>・技上げ道場
+・雑談配信
+・プレイ人口減少
+・サブコンテンツ
+・アセルス評価</t>
+        </is>
+      </c>
+      <c r="H797" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I797" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Lo-MeMsGX2M</t>
+        </is>
+      </c>
+      <c r="J797" s="2" t="inlineStr">
+        <is>
+          <t>Lo-MeMsGX2M</t>
+        </is>
+      </c>
+      <c r="K797" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21T01:27:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B798" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C798" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　螺旋回廊580階　最終皇帝　攻略詳細を大公開</t>
+        </is>
+      </c>
+      <c r="D798" s="2" t="inlineStr">
+        <is>
+          <t>螺旋580階最終皇帝の攻略アフタートーク。
+弱点はザイン、剣槍弓杖術で攻撃弱化、体術系はダメカ。
+術編成8ターン安定と火力編成4ターンを紹介。</t>
+        </is>
+      </c>
+      <c r="E798" s="2" t="inlineStr">
+        <is>
+          <t>・術編成(エレノア等)は全員生存で安定して倒せる
+・火力編成は4ターンで倒せて楽
+・エレノアの火力が弱点でないのに高くて驚き</t>
+        </is>
+      </c>
+      <c r="F798" s="2" t="inlineStr">
+        <is>
+          <t>・デッドリーカウンターの気絶が厄介で注意が必要
+・体術/斧/コンボ/証券はダメカで避けるべき</t>
+        </is>
+      </c>
+      <c r="G798" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋580階
+・最終皇帝ギミック
+・術編成
+・火力編成
+・デッドリーカウンター</t>
+        </is>
+      </c>
+      <c r="H798" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I798" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=v2VYREwXcpI</t>
+        </is>
+      </c>
+      <c r="J798" s="2" t="inlineStr">
+        <is>
+          <t>v2VYREwXcpI</t>
+        </is>
+      </c>
+      <c r="K798" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21T01:27:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B799" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C799" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】超簡単全力オート5編成！螺旋580階最終皇帝【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D799" s="2" t="inlineStr">
+        <is>
+          <t>螺旋580階を全力オートで倒す4編成を紹介。
+アセルス+キハ軸、デス編成、剣4人組など。
+弱点さえ突けばヒット数だけで装備適当でも勝てる。</t>
+        </is>
+      </c>
+      <c r="E799" s="2" t="inlineStr">
+        <is>
+          <t>・アルベドの消費3減少がアタッカー性能でずるいほど強い
+・ルビーが運命の輪や弱体化で優秀
+・アセルス/キハはできん化せず活躍する</t>
+        </is>
+      </c>
+      <c r="F799" s="2" t="inlineStr">
+        <is>
+          <t>・体術/コンボ/証券は99%カットでダメージが通らない</t>
+        </is>
+      </c>
+      <c r="G799" s="2" t="inlineStr">
+        <is>
+          <t>・全力オート
+・螺旋580階
+・アセルス編成
+・デス編成
+・ヒット数稼ぎ</t>
+        </is>
+      </c>
+      <c r="H799" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I799" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ScGVc_EmNVE</t>
+        </is>
+      </c>
+      <c r="J799" s="2" t="inlineStr">
+        <is>
+          <t>ScGVc_EmNVE</t>
+        </is>
+      </c>
+      <c r="K799" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21T01:27:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B800" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C800" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋ガチャと螺旋580攻略中</t>
+        </is>
+      </c>
+      <c r="D800" s="2" t="inlineStr">
+        <is>
+          <t>螺旋ガチャを引きつつ螺旋580を攻略する配信。
+ギミックを手探りで解きながらアセルス火力で挑戦。
+10ターン以降の強化とBP不足に苦戦する。</t>
+        </is>
+      </c>
+      <c r="E800" s="2" t="inlineStr">
+        <is>
+          <t>・ネバンは運ゲ次第で衝撃火力がかなり高い
+・アセルスは火力が出て強い
+・ターミンが偉いダメージを出して強い</t>
+        </is>
+      </c>
+      <c r="F800" s="2" t="inlineStr">
+        <is>
+          <t>・新螺旋ガチャのキャラは大半が微妙
+・アセルスはBP不足で扱いづらい
+・10ターン以降の敵強化が硬すぎる</t>
+        </is>
+      </c>
+      <c r="G800" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋ガチャ
+・螺旋580階
+・アセルス火力
+・BP不足
+・ネバン評価</t>
+        </is>
+      </c>
+      <c r="H800" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I800" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Oj2oZ7dytKY</t>
+        </is>
+      </c>
+      <c r="J800" s="2" t="inlineStr">
+        <is>
+          <t>Oj2oZ7dytKY</t>
+        </is>
+      </c>
+      <c r="K800" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21T01:27:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B801" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C801" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】この性能が螺旋ガチャでいいの？新キャラの性能確認とさっそくガチャを引く！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D801" s="2" t="inlineStr">
+        <is>
+          <t>螺旋回廊ガチャ更新でネバン・フィリップ・弘雪の性能を確認。
+ネバンは全て運ゲだが99%自傷などレイド向けが強力。
+初期コンプを狙いガチャを引き達成する。</t>
+        </is>
+      </c>
+      <c r="E801" s="2" t="inlineStr">
+        <is>
+          <t>・ネバンは99%自傷やダメージブロックがレイドで強力
+・ネバンは配布級の螺旋ガチャで取れて優秀
+・フィリップのサポート性能は悪くない</t>
+        </is>
+      </c>
+      <c r="F801" s="2" t="inlineStr">
+        <is>
+          <t>・ネバンは確率頼みで運ゲ要素が強い
+・フィリップは性能は並で趣味枠
+・弘雪は趣味性能でアンサガ枠止まり</t>
+        </is>
+      </c>
+      <c r="G801" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋回廊ガチャ
+・ネバン性能
+・フィリップ性能
+・弘雪性能
+・初期コンプ</t>
+        </is>
+      </c>
+      <c r="H801" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I801" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MpJTsV6JgbU</t>
+        </is>
+      </c>
+      <c r="J801" s="2" t="inlineStr">
+        <is>
+          <t>MpJTsV6JgbU</t>
+        </is>
+      </c>
+      <c r="K801" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21T01:27:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B802" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C802" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはりアセルスが大活躍！？新しくやってきた螺旋回廊580を初回攻略【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D802" s="2" t="inlineStr">
+        <is>
+          <t>螺旋580階最終皇帝をアセルス軸で初回攻略。
+剣槍弓杖術以外はダメカ、直接攻撃はカウンター注意。
+斬弱点かつアセルスは間接攻撃で相性抜群と判明。</t>
+        </is>
+      </c>
+      <c r="E802" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスは斬弱点かつ間接攻撃で相性抜群
+・キハもできん化せず高火力を出す
+・ターミン&amp;シャールなど主人公勢がまだ最前線で強い</t>
+        </is>
+      </c>
+      <c r="F802" s="2" t="inlineStr">
+        <is>
+          <t>・デッドリーカウンターの気絶で全滅リスク
+・体術系アタッカーはできん化で火力が通らない
+・コーション解除に大量のヒット数を稼ぐ必要</t>
+        </is>
+      </c>
+      <c r="G802" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋580階
+・最終皇帝ギミック
+・アセルス接待
+・コーション解除
+・ヒット数稼ぎ</t>
+        </is>
+      </c>
+      <c r="H802" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I802" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aZvl7Qe2Y-g</t>
+        </is>
+      </c>
+      <c r="J802" s="2" t="inlineStr">
+        <is>
+          <t>aZvl7Qe2Y-g</t>
+        </is>
+      </c>
+      <c r="K802" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21T01:27:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B803" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C803" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第129回サウノックたちの井戸〜8手編成で〜100位以内を狙え！！</t>
+        </is>
+      </c>
+      <c r="D803" s="2" t="inlineStr">
+        <is>
+          <t>サウノックたちの井戸のランキング100位向け攻略。
+ビクトール・AJ・サイバ等の8手編成を紹介。
+現在1位は6手、キャラ入替で6手も狙えると案内。</t>
+        </is>
+      </c>
+      <c r="E803" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンに資源召喚を継承し1手でダメージを稼げる</t>
+        </is>
+      </c>
+      <c r="F803" s="2" t="inlineStr"/>
+      <c r="G803" s="2" t="inlineStr">
+        <is>
+          <t>・サウノックたちの井戸
+・8手編成
+・ランキング100位
+・ターミン運用</t>
+        </is>
+      </c>
+      <c r="H803" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I803" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CR7SdfYiTTM</t>
+        </is>
+      </c>
+      <c r="J803" s="2" t="inlineStr">
+        <is>
+          <t>CR7SdfYiTTM</t>
+        </is>
+      </c>
+      <c r="K803" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21T01:27:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B804" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C804" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみ編第6話ガチャを考察する配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D804" s="2" t="inlineStr">
+        <is>
+          <t>アセルス・マカ・デスの3体ガチャを考察する生配信。
+暦読み等が既におり取得優先度は高くないと評価。
+マカは条件が厳しく使いづらい、デスはアセルス補完向き。</t>
+        </is>
+      </c>
+      <c r="E804" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスは2ターンに1度SS60ヒットの超火力
+・デスはアセルス補完で悪さできそう
+・マカは条件がハマれば火力がえぐい</t>
+        </is>
+      </c>
+      <c r="F804" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスは暦読みがいて取得優先度は低め
+・マカは残統一・ウィーク前提で使いづらい
+・マカは自己エクホがなく火力が出にくい</t>
+        </is>
+      </c>
+      <c r="G804" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ編第6話ガチャ
+・アセルス考察
+・マカ考察
+・デス考察
+・螺旋残弱点予想</t>
+        </is>
+      </c>
+      <c r="H804" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I804" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=g1PIjmoBhNQ</t>
+        </is>
+      </c>
+      <c r="J804" s="2" t="inlineStr">
+        <is>
+          <t>g1PIjmoBhNQ</t>
+        </is>
+      </c>
+      <c r="K804" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21T01:27:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B805" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C805" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋回廊580階 解説 3ターンクリアの編成の詳細を紹介!!【ロマンシング サガ リ ユニバース】</t>
+        </is>
+      </c>
+      <c r="D805" s="2" t="inlineStr">
+        <is>
+          <t>螺旋580階最終皇帝のギミックを丁寧に解説。
+コーション解除は指定技40回、直接攻撃はOD必須。
+3ターンクリア編成の詳細を紹介する。</t>
+        </is>
+      </c>
+      <c r="E805" s="2" t="inlineStr">
+        <is>
+          <t>・全技で火力デバフが入り火力重視で組める
+・3ターンで安定してクリアできる</t>
+        </is>
+      </c>
+      <c r="F805" s="2" t="inlineStr">
+        <is>
+          <t>・体術/斧/コンボ/証券技は99%カットされる
+・直接攻撃のカウンターで確実に気絶させられる</t>
+        </is>
+      </c>
+      <c r="G805" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋580階
+・ギミック解説
+・コーション解除40回
+・3ターン編成
+・11ターン時間切れ</t>
+        </is>
+      </c>
+      <c r="H805" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I805" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8pm2be04auA</t>
+        </is>
+      </c>
+      <c r="J805" s="2" t="inlineStr">
+        <is>
+          <t>8pm2be04auA</t>
+        </is>
+      </c>
+      <c r="K805" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21T01:27:15Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K805"/>
+  <dimension ref="A1:K813"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -53385,6 +53385,524 @@
         </is>
       </c>
     </row>
+    <row r="806">
+      <c r="A806" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B806" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C806" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「神話」予想通りの新キャラ祭!!ウコム!!エリス(シルベン?)ストーリー後編ダブルガチャお知らせ読んでこー　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D806" s="2" t="inlineStr">
+        <is>
+          <t>エリス・ウコムのガチャ予想が的中と自称
+後編はつなぎイベント扱いで内容は薄め
+イベント無い期間なので普段の消化を推奨</t>
+        </is>
+      </c>
+      <c r="E806" s="2" t="inlineStr">
+        <is>
+          <t>・ウコムの槍性能に注目
+・イスカンダールが無人島対応しそうで期待</t>
+        </is>
+      </c>
+      <c r="F806" s="2" t="inlineStr">
+        <is>
+          <t>・後編はつなぎイベント扱いで内容が薄い
+・目立ったイベントが特にない</t>
+        </is>
+      </c>
+      <c r="G806" s="2" t="inlineStr">
+        <is>
+          <t>・ウコムガチャ
+・エリス
+・ストーリー後編
+・ダブルガチャ
+・イスカンダール</t>
+        </is>
+      </c>
+      <c r="H806" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I806" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TQWwaxeicCI</t>
+        </is>
+      </c>
+      <c r="J806" s="2" t="inlineStr">
+        <is>
+          <t>TQWwaxeicCI</t>
+        </is>
+      </c>
+      <c r="K806" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23T01:06:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B807" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C807" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　「ヒマ」を「チャンス」に　神時間　隙間時間にやるべき事4選</t>
+        </is>
+      </c>
+      <c r="D807" s="2" t="inlineStr">
+        <is>
+          <t>イベント空白期にやるべき育成4選を紹介
+技上げ・魂レベル・関門武器上げが柱
+螺旋回廊討伐や記憶再生も忘れず推奨</t>
+        </is>
+      </c>
+      <c r="E807" s="2" t="inlineStr">
+        <is>
+          <t>・技99で威力+10%と効率的
+・短連道場の自動周回が手軽で便利
+・記憶再生は5分程度で済むので必須</t>
+        </is>
+      </c>
+      <c r="F807" s="2" t="inlineStr">
+        <is>
+          <t>・ガードアップ等カタカナ技は技上げ効果なし</t>
+        </is>
+      </c>
+      <c r="G807" s="2" t="inlineStr">
+        <is>
+          <t>・技上げ
+・魂レベル上げ
+・関門武器
+・螺旋回廊
+・記憶再生</t>
+        </is>
+      </c>
+      <c r="H807" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I807" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GXp6XFt73GA</t>
+        </is>
+      </c>
+      <c r="J807" s="2" t="inlineStr">
+        <is>
+          <t>GXp6XFt73GA</t>
+        </is>
+      </c>
+      <c r="K807" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23T01:06:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B808" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C808" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】R RFグフ 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D808" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのRFグフ武装アニメ紹介
+武装ボイスを披露するショート動画
+短尺で演出を見せる内容</t>
+        </is>
+      </c>
+      <c r="E808" s="2" t="inlineStr"/>
+      <c r="F808" s="2" t="inlineStr"/>
+      <c r="G808" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・RFグフ
+・武装アニメ
+・ショート</t>
+        </is>
+      </c>
+      <c r="H808" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I808" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4DnsN5TJMOQ</t>
+        </is>
+      </c>
+      <c r="J808" s="2" t="inlineStr">
+        <is>
+          <t>4DnsN5TJMOQ</t>
+        </is>
+      </c>
+      <c r="K808" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23T01:06:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B809" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C809" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】本日リリース！DMM版触ってみた感想 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D809" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルDMM版がリリースされPC選択肢増加
+画質・動作はDMM版が快適と評価
+難点はBGMパックが未販売な点</t>
+        </is>
+      </c>
+      <c r="E809" s="2" t="inlineStr">
+        <is>
+          <t>・DMM版は画質がくっきり見やすい
+・戦闘アニメが綺麗に描画される
+・Google Play版より動作が快適</t>
+        </is>
+      </c>
+      <c r="F809" s="2" t="inlineStr">
+        <is>
+          <t>・Google Play PC版はフリーズやローディングが長い
+・DMM版はBGMパックが購入不可
+・BGM購入済の人は反映されず損をする</t>
+        </is>
+      </c>
+      <c r="G809" s="2" t="inlineStr">
+        <is>
+          <t>・DMM版
+・Google Play版比較
+・画質
+・戦闘アニメ
+・BGMパック</t>
+        </is>
+      </c>
+      <c r="H809" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I809" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FN-WOGQt2s0</t>
+        </is>
+      </c>
+      <c r="J809" s="2" t="inlineStr">
+        <is>
+          <t>FN-WOGQt2s0</t>
+        </is>
+      </c>
+      <c r="K809" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23T01:06:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B810" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C810" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ウコムとエリス実装 7月23日更新情報まとめ 【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D810" s="2" t="inlineStr">
+        <is>
+          <t>7/23更新でウコム・エリス実装のダブルガチャ
+HP育成上限が5270へ上昇
+投稿者はエリス編優先で様子見の構え</t>
+        </is>
+      </c>
+      <c r="E810" s="2" t="inlineStr">
+        <is>
+          <t>・HP育成上限が5270に上昇
+・トリプルS槍ウコムの槍が交換所で入手可
+・ログインボーナスで3000ジュエル</t>
+        </is>
+      </c>
+      <c r="F810" s="2" t="inlineStr">
+        <is>
+          <t>・エリスはシルベン名義で初登場ではない
+・最近ガチャの引きが悪くモチベ低下
+・ダブルガチャで石消費が激しい</t>
+        </is>
+      </c>
+      <c r="G810" s="2" t="inlineStr">
+        <is>
+          <t>・ウコム編
+・エリス編
+・暦読み第6話
+・HP5270
+・水発連携</t>
+        </is>
+      </c>
+      <c r="H810" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I810" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZufhD4wFLfU</t>
+        </is>
+      </c>
+      <c r="J810" s="2" t="inlineStr">
+        <is>
+          <t>ZufhD4wFLfU</t>
+        </is>
+      </c>
+      <c r="K810" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23T01:06:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B811" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C811" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】強者がいる気配！神速公式情報確認【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D811" s="2" t="inlineStr">
+        <is>
+          <t>暦読み第6話ダブルガチャの内容を確認
+ウコム編とエリス編の新スタイルを解説
+投稿者はルージュ推しで実装に期待</t>
+        </is>
+      </c>
+      <c r="E811" s="2" t="inlineStr">
+        <is>
+          <t>・イスカンダールは毎回そこそこ強い
+・弓槍・人術系が揃いインパ強化に期待
+・推しのルージュ実装に期待</t>
+        </is>
+      </c>
+      <c r="F811" s="2" t="inlineStr">
+        <is>
+          <t>・コーデリアは性能がニッチで弱め傾向が続く
+・ダブルガチャで石消費が激しい
+・最近のガチャの引きに不安</t>
+        </is>
+      </c>
+      <c r="G811" s="2" t="inlineStr">
+        <is>
+          <t>・ウコム編
+・エリス編
+・ルージュ
+・コーデリア
+・イスカンダール</t>
+        </is>
+      </c>
+      <c r="H811" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I811" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lJmn-hSF3I8</t>
+        </is>
+      </c>
+      <c r="J811" s="2" t="inlineStr">
+        <is>
+          <t>lJmn-hSF3I8</t>
+        </is>
+      </c>
+      <c r="K811" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23T01:06:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B812" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C812" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】エリス神が遂に降臨！最新のガチャがヤバすぎた！！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D812" s="2" t="inlineStr">
+        <is>
+          <t>7/23実装のウコム・エリスガチャに大興奮
+ミンサガの神々が続々降臨する展開
+次ガチャは7/31と予想し警戒</t>
+        </is>
+      </c>
+      <c r="E812" s="2" t="inlineStr">
+        <is>
+          <t>・ウコム・エリスのプレイアブル実装に歓喜
+・エリスをシルベン名義で実装する愛を評価
+・サイバの例からウコムも強い可能性</t>
+        </is>
+      </c>
+      <c r="F812" s="2" t="inlineStr">
+        <is>
+          <t>・夏の花火玉交換は今回がラストで要注意
+・復刻ガチャは無し
+・予想大会でウコム・エリス正解者は0名</t>
+        </is>
+      </c>
+      <c r="G812" s="2" t="inlineStr">
+        <is>
+          <t>・エリス実装
+・ウコム編
+・エリス編
+・花火玉交換ラスト
+・ガチャ予想大会</t>
+        </is>
+      </c>
+      <c r="H812" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I812" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xlhsXiDuT6o</t>
+        </is>
+      </c>
+      <c r="J812" s="2" t="inlineStr">
+        <is>
+          <t>xlhsXiDuT6o</t>
+        </is>
+      </c>
+      <c r="K812" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23T01:06:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B813" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C813" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】ちゃむのガチャ配信〜アセルスとマカが欲しい✨【神引きするまで終われません…】</t>
+        </is>
+      </c>
+      <c r="D813" s="2" t="inlineStr">
+        <is>
+          <t>アセルス・マカ狙いのガチャ配信
+60連でアセルスを確保
+マカ・デスは次ガチャを見て様子見で終了</t>
+        </is>
+      </c>
+      <c r="E813" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスはWS5行動60ヒット腕力3700%バフでぶっ壊れ
+・マカはサポーター武力から高アタッカー性能
+・デスは斬アタッカーの火力サポーターで優秀</t>
+        </is>
+      </c>
+      <c r="F813" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス確保に60連を要し引きが渋かった
+・マカ・デスは次ガチャ性能を見て保留</t>
+        </is>
+      </c>
+      <c r="G813" s="2" t="inlineStr">
+        <is>
+          <t>・アセルス
+・マカ
+・デス
+・ガチャ配信
+・センジュエル</t>
+        </is>
+      </c>
+      <c r="H813" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I813" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4S-R4sx16-Q</t>
+        </is>
+      </c>
+      <c r="J813" s="2" t="inlineStr">
+        <is>
+          <t>4S-R4sx16-Q</t>
+        </is>
+      </c>
+      <c r="K813" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23T01:06:09Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K813"/>
+  <dimension ref="A1:K834"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -53903,6 +53903,1366 @@
         </is>
       </c>
     </row>
+    <row r="814">
+      <c r="A814" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B814" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C814" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「100ヒット可能」!?超上振れ&amp;ダメブロでとにかく堅い無尽塔でも汎用イスカンダール&amp;マイス型ハイブリッドでサブアタッカー最高峰ルージュ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D814" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローがルージュとイスカンダールを性能考察。
+ルージュは長期戦のマイターンOD満タが強み。
+イスカンダールは無人島向けの上振れ型カウンター。</t>
+        </is>
+      </c>
+      <c r="E814" s="2" t="inlineStr">
+        <is>
+          <t>・ルージュは長期戦でマイターンOD満タが強力
+・イスカンダールは初手瞬発力とダメブロ、無限追撃
+・味方全体への火力・防御サポートもできる</t>
+        </is>
+      </c>
+      <c r="F814" s="2" t="inlineStr">
+        <is>
+          <t>・ルージュは突き抜けず無難、代わりがいる
+・イスカンダールは個人火力が中途半端
+・エクストラも自己バフも弱く1人では倒しきれない</t>
+        </is>
+      </c>
+      <c r="G814" s="2" t="inlineStr">
+        <is>
+          <t>・ルージュ
+・イスカンダール
+・マイス型
+・無人島
+・カウンター</t>
+        </is>
+      </c>
+      <c r="H814" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I814" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WRr3h2oZVU4</t>
+        </is>
+      </c>
+      <c r="J814" s="2" t="inlineStr">
+        <is>
+          <t>WRr3h2oZVU4</t>
+        </is>
+      </c>
+      <c r="K814" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B815" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C815" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「超有能置物」全体37ヒットの最強神様エリス&amp;アセルスと陰をサポートするサブアタッカー零姫　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D815" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローがエリスと零姫を性能考察。
+エリスは全体37ヒットの置き物特化で総合A。
+零姫は超短期戦専用で出力弱く総合B。</t>
+        </is>
+      </c>
+      <c r="E815" s="2" t="inlineStr">
+        <is>
+          <t>・エリスは全体37ヒットの猛攻、置き物として優秀
+・エリスはエクストラ拡張性が高い</t>
+        </is>
+      </c>
+      <c r="F815" s="2" t="inlineStr">
+        <is>
+          <t>・エリスは絡むと即離脱がネック、スロースタート
+・零姫は術算3回のみで出力弱く中途半端
+・零姫は目立った特徴が全くない</t>
+        </is>
+      </c>
+      <c r="G815" s="2" t="inlineStr">
+        <is>
+          <t>・エリス
+・零姫
+・全体攻撃
+・置き物
+・エクストラ拡張</t>
+        </is>
+      </c>
+      <c r="H815" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I815" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XgxrvjSf-MA</t>
+        </is>
+      </c>
+      <c r="J815" s="2" t="inlineStr">
+        <is>
+          <t>XgxrvjSf-MA</t>
+        </is>
+      </c>
+      <c r="K815" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B816" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C816" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】6体ランキング「〇〇が最強に」ウコムの冷雷サポートがとあるキャラを強力サポート&amp;いつものコーデリアがマイス型踏襲で激変!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D816" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローが6体ランキングでコーデリア等を考察。
+ウコムはエクストラ置き物として強力。
+コーデリアは縛りきつく刺さらない性能。</t>
+        </is>
+      </c>
+      <c r="E816" s="2" t="inlineStr">
+        <is>
+          <t>・ウコムはエクストラ置き物として強力
+・ウコムは貝と相性最高
+・エリスは確定1.75倍で運用価値十分</t>
+        </is>
+      </c>
+      <c r="F816" s="2" t="inlineStr">
+        <is>
+          <t>・コーデリアは縛りがきつい割に刺さらない
+・コーデリアはいつも通り特徴がない
+・ウコムは片持ち属性だと弱く貝以外出番薄い</t>
+        </is>
+      </c>
+      <c r="G816" s="2" t="inlineStr">
+        <is>
+          <t>・6体ランキング
+・ウコム
+・コーデリア
+・貝サポート
+・エクストラ</t>
+        </is>
+      </c>
+      <c r="H816" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I816" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=v4uO8tM7nAw</t>
+        </is>
+      </c>
+      <c r="J816" s="2" t="inlineStr">
+        <is>
+          <t>v4uO8tM7nAw</t>
+        </is>
+      </c>
+      <c r="K816" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B817" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C817" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】雑談周回　井戸とかもやろう　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D817" s="2" t="inlineStr">
+        <is>
+          <t>あんずもんの雑談周回配信。井戸や制圧戦を周回。
+アセルス実装や明日のガチャを雑談。
+セフェルマルカーの火力インフレを実感。</t>
+        </is>
+      </c>
+      <c r="E817" s="2" t="inlineStr">
+        <is>
+          <t>・セフェルマルカーの火力インフレで周回が楽に
+・井戸1位編成が予想外に強かった</t>
+        </is>
+      </c>
+      <c r="F817" s="2" t="inlineStr">
+        <is>
+          <t>・イベントの波が激しく更新が早すぎる
+・無人島30がきつすぎてやることがない
+・ストーリーイベントが薄い</t>
+        </is>
+      </c>
+      <c r="G817" s="2" t="inlineStr">
+        <is>
+          <t>・雑談周回
+・井戸
+・アセルスガチャ
+・制圧戦
+・猛暑</t>
+        </is>
+      </c>
+      <c r="H817" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I817" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4e8cpZkDKcY</t>
+        </is>
+      </c>
+      <c r="J817" s="2" t="inlineStr">
+        <is>
+          <t>4e8cpZkDKcY</t>
+        </is>
+      </c>
+      <c r="K817" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B818" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C818" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始294日目記録　加速　進捗状況に変化が</t>
+        </is>
+      </c>
+      <c r="D818" s="2" t="inlineStr">
+        <is>
+          <t>あんずもんの信長の野望出陣プレイ294日目記録。
+新武将4体入手やプレイヤーランク96到達を報告。
+武田信虎など新規武将の性能に注目。</t>
+        </is>
+      </c>
+      <c r="E818" s="2" t="inlineStr">
+        <is>
+          <t>・武田信虎が竹特攻で強くなりそう
+・すごろく6のキャラは意外と強い武将が多い
+・滝川一益系や小田過が取れて嬉しい</t>
+        </is>
+      </c>
+      <c r="F818" s="2" t="inlineStr">
+        <is>
+          <t>・足軽秋は統率が低く引かない予定
+・覚醒5段階必要でコバンが厳しい
+・共闘の全報酬は課金しないと厳しい</t>
+        </is>
+      </c>
+      <c r="G818" s="2" t="inlineStr">
+        <is>
+          <t>・信長の野望出陣
+・294日目
+・新武将
+・制圧率
+・すごろく6</t>
+        </is>
+      </c>
+      <c r="H818" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I818" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5o2gu3WYmmU</t>
+        </is>
+      </c>
+      <c r="J818" s="2" t="inlineStr">
+        <is>
+          <t>5o2gu3WYmmU</t>
+        </is>
+      </c>
+      <c r="K818" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B819" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C819" s="2" t="inlineStr">
+        <is>
+          <t>新作ガンダムシリーズ発表！！『機動戦士ガンダムRG XARX ZERO』</t>
+        </is>
+      </c>
+      <c r="D819" s="2" t="inlineStr">
+        <is>
+          <t>新作ガンダム『RG XARX ZERO』の発表情報を紹介。
+ゲームと世界観を共有するメディアミックス展開。
+主人公機ガンダムゼロはシンプルな見た目。</t>
+        </is>
+      </c>
+      <c r="E819" s="2" t="inlineStr">
+        <is>
+          <t>・ガンダムゼロがシンプルな見た目で良い
+・メディアミックス前提の展開に期待
+・地球侵食など挑戦的な設定が面白い</t>
+        </is>
+      </c>
+      <c r="F819" s="2" t="inlineStr">
+        <is>
+          <t>・今回の話だけでは完結せず続きはゲーム
+・公開キャラが主人公しかまだない</t>
+        </is>
+      </c>
+      <c r="G819" s="2" t="inlineStr">
+        <is>
+          <t>・新作ガンダム
+・RGシリーズ
+・アポカリプス
+・メディアミックス
+・2027年</t>
+        </is>
+      </c>
+      <c r="H819" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I819" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fJ63xd4SSYs</t>
+        </is>
+      </c>
+      <c r="J819" s="2" t="inlineStr">
+        <is>
+          <t>fJ63xd4SSYs</t>
+        </is>
+      </c>
+      <c r="K819" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B820" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C820" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】とりまエリス編だけ、、『こよみ編 第6話 後編 公開記念 Romancing祭 エリス編』【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D820" s="2" t="inlineStr">
+        <is>
+          <t>明星chがエリス編ガチャを70連実況。
+ルージュ・コーデリア・エリスを50連で全て確保。
+すり抜けでタリアも来て引きが良かった。</t>
+        </is>
+      </c>
+      <c r="E820" s="2" t="inlineStr">
+        <is>
+          <t>・50連でピックが全て揃い引きが良かった
+・オートでOD使えて使いやすくなった</t>
+        </is>
+      </c>
+      <c r="F820" s="2" t="inlineStr">
+        <is>
+          <t>・最近のガチャの引きが良くなくモチベ低下
+・コーデリアは消費BP増加付与が重い</t>
+        </is>
+      </c>
+      <c r="G820" s="2" t="inlineStr">
+        <is>
+          <t>・エリス編ガチャ
+・50連で確定
+・コーデリア
+・引き
+・OD</t>
+        </is>
+      </c>
+      <c r="H820" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I820" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pbwgx3m_B_s</t>
+        </is>
+      </c>
+      <c r="J820" s="2" t="inlineStr">
+        <is>
+          <t>pbwgx3m_B_s</t>
+        </is>
+      </c>
+      <c r="K820" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B821" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C821" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】あの編成でイスカンダール化けてしまう件【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D821" s="2" t="inlineStr">
+        <is>
+          <t>つむつむがイスカンダール×マカの組み合わせを検証。
+マカのバフで威力E低火力のイスカンが化ける。
+螺旋の最終皇帝相手にカウンターで大ダメージ。</t>
+        </is>
+      </c>
+      <c r="E821" s="2" t="inlineStr">
+        <is>
+          <t>・イスカンダール×マカで火力が化ける
+・マカのバフでカウンターが強烈に伸びる
+・残弱の相手ではさらにやばい火力に</t>
+        </is>
+      </c>
+      <c r="F821" s="2" t="inlineStr">
+        <is>
+          <t>・イスカンダール単体は威力Eで火力が出ない
+・DP系のバフは今回ほぼ機能せず微妙</t>
+        </is>
+      </c>
+      <c r="G821" s="2" t="inlineStr">
+        <is>
+          <t>・イスカンダール
+・マカ
+・カウンター
+・螺旋回廊
+・残弱</t>
+        </is>
+      </c>
+      <c r="H821" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I821" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0HQdlFDLn74</t>
+        </is>
+      </c>
+      <c r="J821" s="2" t="inlineStr">
+        <is>
+          <t>0HQdlFDLn74</t>
+        </is>
+      </c>
+      <c r="K821" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B822" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C822" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】神々が降臨！！セコム＆エリス編6人全員性能確認「【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D822" s="2" t="inlineStr">
+        <is>
+          <t>つむつむがウコム&amp;エリス編6人全員の性能を確認。
+ウコムとエリスは当たり枠で取りたい評価。
+コーデリアは消費BP増加が今の流行りに逆行。</t>
+        </is>
+      </c>
+      <c r="E822" s="2" t="inlineStr">
+        <is>
+          <t>・ウコム・エリスは当たり枠で取りたい
+・イスカンダールは面白いことができそう
+・ウコムはエクストラばらまきが強力</t>
+        </is>
+      </c>
+      <c r="F822" s="2" t="inlineStr">
+        <is>
+          <t>・コーデリアは消費BP増加が今の編成に合わない
+・ルージュ・レイ姫は威力Dで火力が低い
+・レイ姫は超短期戦専用で出力が弱い</t>
+        </is>
+      </c>
+      <c r="G822" s="2" t="inlineStr">
+        <is>
+          <t>・6人性能確認
+・ウコム
+・エリス
+・イスカンダール
+・コーデリア</t>
+        </is>
+      </c>
+      <c r="H822" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I822" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ps5V2x6X3NM</t>
+        </is>
+      </c>
+      <c r="J822" s="2" t="inlineStr">
+        <is>
+          <t>Ps5V2x6X3NM</t>
+        </is>
+      </c>
+      <c r="K822" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B823" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C823" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみ編 第6話 後編 公開記念Wガチャ😻</t>
+        </is>
+      </c>
+      <c r="D823" s="2" t="inlineStr">
+        <is>
+          <t>もんでるのWガチャ配信。マカ×カウンターのバグ話題。
+イスカンダールは面白い当たり、レイ姫は超微妙評価。
+後半は猛暑や置き配盗難の雑談。</t>
+        </is>
+      </c>
+      <c r="E823" s="2" t="inlineStr">
+        <is>
+          <t>・イスカンダールは面白い当たり
+・エリスはバフ枚数がやばく強い
+・ターン開始で敵全体能力ダウンが強い</t>
+        </is>
+      </c>
+      <c r="F823" s="2" t="inlineStr">
+        <is>
+          <t>・レイ姫は超絶微妙で弱め、能力が適当
+・マカ×カウンターはオーバーフローでバグる</t>
+        </is>
+      </c>
+      <c r="G823" s="2" t="inlineStr">
+        <is>
+          <t>・Wガチャ
+・イスカンダール
+・マカバグ
+・レイ姫
+・猛暑</t>
+        </is>
+      </c>
+      <c r="H823" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I823" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CDZ2Yon2ZGE</t>
+        </is>
+      </c>
+      <c r="J823" s="2" t="inlineStr">
+        <is>
+          <t>CDZ2Yon2ZGE</t>
+        </is>
+      </c>
+      <c r="K823" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B824" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C824" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】衝撃的な内容にびっくり！新イベントの内容と周回を解説【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D824" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーが新イベント（後編ストーリー）を解説。
+内容は薄くつなぎ、周回は4番の1箇所のみ。
+近日の公式生放送53に期待。</t>
+        </is>
+      </c>
+      <c r="E824" s="2" t="inlineStr">
+        <is>
+          <t>・ストーリーが面白く続きが気になる
+・神様編成で12秒周回ができる</t>
+        </is>
+      </c>
+      <c r="F824" s="2" t="inlineStr">
+        <is>
+          <t>・イベント内容が薄くつなぎになっている
+・周回スポットが1箇所しかない
+・ストーリーは賛否両論</t>
+        </is>
+      </c>
+      <c r="G824" s="2" t="inlineStr">
+        <is>
+          <t>・新イベント
+・周回スポット
+・ストーリー
+・公式生放送
+・連マの遺跡</t>
+        </is>
+      </c>
+      <c r="H824" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I824" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BkW6EWnhAHU</t>
+        </is>
+      </c>
+      <c r="J824" s="2" t="inlineStr">
+        <is>
+          <t>BkW6EWnhAHU</t>
+        </is>
+      </c>
+      <c r="K824" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B825" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C825" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ロマサガRS界のギャルが遂に実装か！？ストーリー後編ガチャを徹底予想【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D825" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーが後編ガチャの内容を徹底予想。
+千き・すみれ・教授の3スタイルを予想。
+シグナス・ワグナス・サウザも陰属性から予想。</t>
+        </is>
+      </c>
+      <c r="E825" s="2" t="inlineStr"/>
+      <c r="F825" s="2" t="inlineStr"/>
+      <c r="G825" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ予想
+・ちあき
+・教授
+・シグナス
+・陰属性</t>
+        </is>
+      </c>
+      <c r="H825" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I825" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DuHTP-GFTTk</t>
+        </is>
+      </c>
+      <c r="J825" s="2" t="inlineStr">
+        <is>
+          <t>DuHTP-GFTTk</t>
+        </is>
+      </c>
+      <c r="K825" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B826" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C826" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】結局神は強い説が浮上？ウコム編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D826" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーがウコム編3体の性能をチェック。
+イスカンダールは強力なカウンターディフェンダー。
+ウコムは普通に強キャラ、エリスが一番の当たり。</t>
+        </is>
+      </c>
+      <c r="E826" s="2" t="inlineStr">
+        <is>
+          <t>・イスカンダールは面白くカウンター好きは取る価値
+・ウコムはエクストラをばらまけて偉い
+・総合ではエリスが一番の当たり</t>
+        </is>
+      </c>
+      <c r="F826" s="2" t="inlineStr">
+        <is>
+          <t>・イスカンダールは属性ザンのみでエクストラなし
+・レイ姫は技3が3回限定で4ター目以降息切れ
+・陰属性は過剰供給気味で今はジュエル温存ターン</t>
+        </is>
+      </c>
+      <c r="G826" s="2" t="inlineStr">
+        <is>
+          <t>・ウコム編
+・イスカンダール
+・レイ姫
+・ウコム
+・カウンター</t>
+        </is>
+      </c>
+      <c r="H826" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I826" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KfGpNEKwvUI</t>
+        </is>
+      </c>
+      <c r="J826" s="2" t="inlineStr">
+        <is>
+          <t>KfGpNEKwvUI</t>
+        </is>
+      </c>
+      <c r="K826" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B827" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C827" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはり噂通りの強キャラ！？エリス編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D827" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーがエリス編3体の性能をチェック。
+エリスは今回の当たりで洋属性パ必須級。
+ルージュは待機型、コーデリアはマイス型で難度高。</t>
+        </is>
+      </c>
+      <c r="E827" s="2" t="inlineStr">
+        <is>
+          <t>・エリスが今回の当たりで洋属性パ必須級
+・エリスはイラストも素晴らしい
+・ルージュは高スペックで味方サポートも豊富</t>
+        </is>
+      </c>
+      <c r="F827" s="2" t="inlineStr">
+        <is>
+          <t>・ルージュは5ター目から本気の待機型で使い道が見えにくい
+・コーデリアはマイス型で無理する性能でない
+・コーデリアは弱点必須で編成難易度が高い</t>
+        </is>
+      </c>
+      <c r="G827" s="2" t="inlineStr">
+        <is>
+          <t>・エリス編
+・エリス
+・ルージュ
+・コーデリア
+・洋属性</t>
+        </is>
+      </c>
+      <c r="H827" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I827" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OKAqEyo2GPw</t>
+        </is>
+      </c>
+      <c r="J827" s="2" t="inlineStr">
+        <is>
+          <t>OKAqEyo2GPw</t>
+        </is>
+      </c>
+      <c r="K827" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B828" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C828" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】神々はやはり引くべき？ウコム&amp;エリスガチャ性能チェック・キャラランク付け【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D828" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんが6体の性能をまとめランク付け。
+エリスは置き物性能とバフの多さで注目。
+神2体は性能が盛られている印象。</t>
+        </is>
+      </c>
+      <c r="E828" s="2" t="inlineStr">
+        <is>
+          <t>・エリスは置き物性能が高くバフも多い、攻防バランス良好
+・神(ウコム・エリス)は性能が盛られている
+・コーデリアの技3は技マシン候補として優秀</t>
+        </is>
+      </c>
+      <c r="F828" s="2" t="inlineStr">
+        <is>
+          <t>・レイ姫は術3を使い切ると火力ダウン、威力も低い
+・ウコムは1点狙いになるのが厳しい
+・コーデリアはOD運用前提で自己OD満タできない</t>
+        </is>
+      </c>
+      <c r="G828" s="2" t="inlineStr">
+        <is>
+          <t>・性能まとめ
+・キャラランク
+・エリス
+・ウコム
+・OD特化</t>
+        </is>
+      </c>
+      <c r="H828" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I828" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Uu799mWnqSw</t>
+        </is>
+      </c>
+      <c r="J828" s="2" t="inlineStr">
+        <is>
+          <t>Uu799mWnqSw</t>
+        </is>
+      </c>
+      <c r="K828" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B829" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C829" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】エリス編ガチャ能力値早見表〜火力サポーターガチャ〜特に…陽属性か…りょく…ヤバいわ😨【エリス・コーデリア・ルージュ】</t>
+        </is>
+      </c>
+      <c r="D829" s="2" t="inlineStr">
+        <is>
+          <t>tyamuがエリス編の能力値早見表を解説。
+エリスは洋の火力サポーター兼全体アタッカー。
+初登場エクストラフォースで全体2.25倍が強力。</t>
+        </is>
+      </c>
+      <c r="E829" s="2" t="inlineStr">
+        <is>
+          <t>・エリスは洋の火力サポーターとして一級品
+・エリスは属性全体アタッカーも兼ね一石二鳥
+・ルージュは中長期戦でかなり強い</t>
+        </is>
+      </c>
+      <c r="F829" s="2" t="inlineStr">
+        <is>
+          <t>・ルージュは汎用性低くスカウト機会が気がかり
+・コーデリアは各数値がそこまで高くない
+・どこで使うか問題がありそう</t>
+        </is>
+      </c>
+      <c r="G829" s="2" t="inlineStr">
+        <is>
+          <t>・エリス編早見表
+・エリス
+・陽属性
+・エクストラフォース
+・コーデリア</t>
+        </is>
+      </c>
+      <c r="H829" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I829" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=toyPWjPeEPk</t>
+        </is>
+      </c>
+      <c r="J829" s="2" t="inlineStr">
+        <is>
+          <t>toyPWjPeEPk</t>
+        </is>
+      </c>
+      <c r="K829" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B830" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C830" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】ウコム編ガチャ能力値早見表〜氷雷爆撃機 ~参上‼️超絶反撃追撃 ~連撃‼️【ウコム・零姫・イスカンダール】</t>
+        </is>
+      </c>
+      <c r="D830" s="2" t="inlineStr">
+        <is>
+          <t>tyamuがウコム編の能力値早見表を解説。
+計算するとウコムとイスカンダールが強力と判明。
+ウコムは爆撃機並みの全体34連打火力。</t>
+        </is>
+      </c>
+      <c r="E830" s="2" t="inlineStr">
+        <is>
+          <t>・イスカンダールは残直接攻撃5回受けでぶっ壊れ性能
+・ウコムは爆撃機並みの全体火力34連打
+・ウコムは霊属性のキャラを強化できる</t>
+        </is>
+      </c>
+      <c r="F830" s="2" t="inlineStr">
+        <is>
+          <t>・レイ姫は標準アタッカー止まりで変わりがいる</t>
+        </is>
+      </c>
+      <c r="G830" s="2" t="inlineStr">
+        <is>
+          <t>・ウコム編早見表
+・ウコム
+・イスカンダール
+・反撃追撃
+・霊属性</t>
+        </is>
+      </c>
+      <c r="H830" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I830" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uhJbRtTfaec</t>
+        </is>
+      </c>
+      <c r="J830" s="2" t="inlineStr">
+        <is>
+          <t>uhJbRtTfaec</t>
+        </is>
+      </c>
+      <c r="K830" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B831" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C831" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【大感謝】１番閃いてるのは誰！？魂アビリティ所持数グランプリ【No.623】</t>
+        </is>
+      </c>
+      <c r="D831" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねるの魂アビリティ所持数グランプリ。
+視聴者107名の集計で上位キャラを発表。
+1位はAJ、2位はリラとこよみ。</t>
+        </is>
+      </c>
+      <c r="E831" s="2" t="inlineStr"/>
+      <c r="F831" s="2" t="inlineStr"/>
+      <c r="G831" s="2" t="inlineStr">
+        <is>
+          <t>・魂アビリティ
+・所持数ランキング
+・視聴者企画
+・AJ
+・こよみ</t>
+        </is>
+      </c>
+      <c r="H831" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I831" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=24-UI8AENsU</t>
+        </is>
+      </c>
+      <c r="J831" s="2" t="inlineStr">
+        <is>
+          <t>24-UI8AENsU</t>
+        </is>
+      </c>
+      <c r="K831" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B832" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C832" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみ編第6話ガチャを考察する配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D832" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのこよみ編ガチャ考察生配信。
+ウコムは上振れ強いが下振れ弱い村っ気スタイル。
+レイ姫はBP優秀だが火力役として中途半端で低評価。</t>
+        </is>
+      </c>
+      <c r="E832" s="2" t="inlineStr">
+        <is>
+          <t>・ウコムは上振れが強く2ター目から強い、防御も高い
+・イスカンダールは残相手にカウンターで強い</t>
+        </is>
+      </c>
+      <c r="F832" s="2" t="inlineStr">
+        <is>
+          <t>・ウコムは村っ気があり計算が複雑で下振れ弱い
+・レイ姫はBP役兼火力が中途半端で低評価
+・イスカンダールはエクストラフォースが2ターンのみで残念</t>
+        </is>
+      </c>
+      <c r="G832" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ編ガチャ
+・ウコム
+・レイ姫
+・イスカンダール
+・エクストラフォース</t>
+        </is>
+      </c>
+      <c r="H832" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I832" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6zc2B3rqv70</t>
+        </is>
+      </c>
+      <c r="J832" s="2" t="inlineStr">
+        <is>
+          <t>6zc2B3rqv70</t>
+        </is>
+      </c>
+      <c r="K832" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B833" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C833" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「ウコム 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D833" s="2" t="inlineStr">
+        <is>
+          <t>ジュラがウコム編3体を考察しランク付け。
+ウコムはB＋、レイ姫はB、イスカンダールはB＋。
+どれもワンポイント採用で無理に取らなくてよい。</t>
+        </is>
+      </c>
+      <c r="E833" s="2" t="inlineStr">
+        <is>
+          <t>・ウコムは技算起点の全体34ヒットがぶっ飛んだ性能
+・ウコムは冷続性の槍として速攻で活躍しそう
+・イスカンダールは残相手に強力で味方サポートもできる</t>
+        </is>
+      </c>
+      <c r="F833" s="2" t="inlineStr">
+        <is>
+          <t>・ウコムは村っ気があり技算に使用回数制限
+・レイ姫は火力が3ターン限定で高難度性能不足
+・イスカンダールは万能でなく特定相手特攻、エクストラ2ターンのみ</t>
+        </is>
+      </c>
+      <c r="G833" s="2" t="inlineStr">
+        <is>
+          <t>・ウコム編考察
+・ランク付け
+・ウコム
+・レイ姫
+・イスカンダール</t>
+        </is>
+      </c>
+      <c r="H833" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I833" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zPtev6CPmD0</t>
+        </is>
+      </c>
+      <c r="J833" s="2" t="inlineStr">
+        <is>
+          <t>zPtev6CPmD0</t>
+        </is>
+      </c>
+      <c r="K833" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B834" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C834" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベント解説 注意点 11秒周回の編成3種紹介【ロマンシング サガ リ ユニバース】</t>
+        </is>
+      </c>
+      <c r="D834" s="2" t="inlineStr">
+        <is>
+          <t>RS周回チャンネルが新イベントを解説。
+周回の注意点を紹介。
+11秒周回の編成3種を紹介。</t>
+        </is>
+      </c>
+      <c r="E834" s="2" t="inlineStr"/>
+      <c r="F834" s="2" t="inlineStr"/>
+      <c r="G834" s="2" t="inlineStr">
+        <is>
+          <t>・新イベント解説
+・11秒周回
+・編成3種
+・周回
+・注意点</t>
+        </is>
+      </c>
+      <c r="H834" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I834" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QqbnCDaLjGA</t>
+        </is>
+      </c>
+      <c r="J834" s="2" t="inlineStr">
+        <is>
+          <t>QqbnCDaLjGA</t>
+        </is>
+      </c>
+      <c r="K834" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24T15:25:55Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K834"/>
+  <dimension ref="A1:K838"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -55263,6 +55263,250 @@
         </is>
       </c>
     </row>
+    <row r="835">
+      <c r="A835" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B835" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C835" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「ベット黄金比」15000ジュエル必勝法!?花火玉ベットにはそれぞれの勝ち方がある→パターン3種をご提案　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D835" s="2" t="inlineStr">
+        <is>
+          <t>花火玉ベット(期限31日朝4時)の賭け方指南
+全ベット/分散/中央値の3パターンを提案
+おすすめは最低保証を残しつつ上ぶれ狙い</t>
+        </is>
+      </c>
+      <c r="E835" s="2" t="inlineStr">
+        <is>
+          <t>・32番号ベットで2等5850/3等2950も狙える
+・中央値狙いは安定して20連分を確保しやすい</t>
+        </is>
+      </c>
+      <c r="F835" s="2" t="inlineStr">
+        <is>
+          <t>・0ベットは最低保証のみで意味が薄い
+・全ベットは捨て花火玉が発生してしまう</t>
+        </is>
+      </c>
+      <c r="G835" s="2" t="inlineStr">
+        <is>
+          <t>・花火玉ベット
+・ジュエル
+・交換期限
+・賭け方3種</t>
+        </is>
+      </c>
+      <c r="H835" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I835" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1OIM313APYY</t>
+        </is>
+      </c>
+      <c r="J835" s="2" t="inlineStr">
+        <is>
+          <t>1OIM313APYY</t>
+        </is>
+      </c>
+      <c r="K835" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T02:04:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B836" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C836" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】N RFザク 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D836" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのN RFザク武装アニメ
+武装演出を見せるショート動画
+セリフのみで解説ナレーションは無し</t>
+        </is>
+      </c>
+      <c r="E836" s="2" t="inlineStr"/>
+      <c r="F836" s="2" t="inlineStr"/>
+      <c r="G836" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・RFザク
+・武装アニメ
+・ショート</t>
+        </is>
+      </c>
+      <c r="H836" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I836" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=48kg8ahI0yg</t>
+        </is>
+      </c>
+      <c r="J836" s="2" t="inlineStr">
+        <is>
+          <t>48kg8ahI0yg</t>
+        </is>
+      </c>
+      <c r="K836" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T02:04:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B837" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C837" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR ダギ・イルス(地球連邦軍仕様)  武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D837" s="2" t="inlineStr">
+        <is>
+          <t>GジェネSSRダギ・イルス(連邦仕様)武装アニメ
+武装演出を見せるショート動画
+セリフのみで解説ナレーションは無し</t>
+        </is>
+      </c>
+      <c r="E837" s="2" t="inlineStr"/>
+      <c r="F837" s="2" t="inlineStr"/>
+      <c r="G837" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ダギ・イルス
+・武装アニメ
+・ショート</t>
+        </is>
+      </c>
+      <c r="H837" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I837" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=izEOOk_BtXI</t>
+        </is>
+      </c>
+      <c r="J837" s="2" t="inlineStr">
+        <is>
+          <t>izEOOk_BtXI</t>
+        </is>
+      </c>
+      <c r="K837" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T02:04:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B838" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C838" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】3大ガチャランキング！引くべき優先度考察★使ってみた所感解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D838" s="2" t="inlineStr">
+        <is>
+          <t>新3大ガチャを使ってみた所感で優先度付け
+3位デリス(エリス弓)/2位グコム/1位アセルス編
+アセルスの爆発力とマカの環境性能が光る</t>
+        </is>
+      </c>
+      <c r="E838" s="2" t="inlineStr">
+        <is>
+          <t>・エリス:大望の弓の強キャラ、置き物性能が優秀
+・グコム:霊全体攻撃、最大2.25倍で強力
+・アセルス:弱点攻撃で300〜400億出る爆発力
+・デス:単体EXフォース2.5倍の最高級サポート
+・マカ:残弱点でバフ量がえげつなく環境級</t>
+        </is>
+      </c>
+      <c r="F838" s="2" t="inlineStr">
+        <is>
+          <t>・エリス:追撃が6ターン目で遠く長期戦向け
+・グコム:50%抽選頼みで運要素が大きい
+・レイ姫:火力低く覚醒に課題、優先度控えめ
+・コードリア/ルージュ:火力伸びず飛び抜けない
+・マカ×カウンター2枚でエラー発生の不具合あり</t>
+        </is>
+      </c>
+      <c r="G838" s="2" t="inlineStr">
+        <is>
+          <t>・3大ガチャ
+・エリス弓
+・グコム
+・アセルス
+・デス
+・マカ</t>
+        </is>
+      </c>
+      <c r="H838" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I838" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3ijfPLtwyls</t>
+        </is>
+      </c>
+      <c r="J838" s="2" t="inlineStr">
+        <is>
+          <t>3ijfPLtwyls</t>
+        </is>
+      </c>
+      <c r="K838" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25T02:04:45Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K838"/>
+  <dimension ref="A1:K850"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -55507,6 +55507,804 @@
         </is>
       </c>
     </row>
+    <row r="839">
+      <c r="A839" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B839" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C839" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「不純な動機」神々とアセルスを天秤にかけ選んだスタイルは…!?ガチャ厳選勢ガチャを引く!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D839" s="2" t="inlineStr">
+        <is>
+          <t>ガチャ厳選勢がアセルス狙いでガチャを実演
+アセルスは便利だがそこまで欲しくない微妙枠
+マカは被りやすく活躍機会が少ないと評価</t>
+        </is>
+      </c>
+      <c r="E839" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスは便利で取れればラッキー枠</t>
+        </is>
+      </c>
+      <c r="F839" s="2" t="inlineStr">
+        <is>
+          <t>・マカはザンウィークでしか作れず被りやすい
+・マカは活躍機会がほぼ出ない
+・アセルスはそこまで欲しくない微妙な性能</t>
+        </is>
+      </c>
+      <c r="G839" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ実演
+・アセルス
+・マカ
+・エクストラウィーク
+・厳選</t>
+        </is>
+      </c>
+      <c r="H839" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I839" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Dk_a46WXN9I</t>
+        </is>
+      </c>
+      <c r="J839" s="2" t="inlineStr">
+        <is>
+          <t>Dk_a46WXN9I</t>
+        </is>
+      </c>
+      <c r="K839" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26T01:09:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B840" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C840" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「最強神々」エリスVSアセルス→9体3ガチャランキング!!最新スタイルの最強を決める比較検討会→2026年7月26日版　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D840" s="2" t="inlineStr">
+        <is>
+          <t>エリス編9スタイルを最強比較でランク付け
+エリスは全体攻撃連打で環境屈指の強さ
+霊姫・マカ・ウコムは条件付きで伸び悩む</t>
+        </is>
+      </c>
+      <c r="E840" s="2" t="inlineStr">
+        <is>
+          <t>・エリスは全体攻撃連打が環境屈指で無人島無双
+・ルージュは1人でOD満タンを配れて優秀
+・デスは数値が高く便利で確保推奨
+・コーデリアは技3継承が刺さる場合あり</t>
+        </is>
+      </c>
+      <c r="F840" s="2" t="inlineStr">
+        <is>
+          <t>・霊姫は前スタイルと差がなく圧倒的最下位
+・マカは拡張性を活かせる機会がほぼない
+・ウコムは50%抽選頼みで安定感がない
+・イスカンダールは個人火力に爆発力がない</t>
+        </is>
+      </c>
+      <c r="G840" s="2" t="inlineStr">
+        <is>
+          <t>・エリス編
+・最強ランキング
+・エリス
+・ウコム
+・マカ
+・継承</t>
+        </is>
+      </c>
+      <c r="H840" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I840" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mELM8Zce61c</t>
+        </is>
+      </c>
+      <c r="J840" s="2" t="inlineStr">
+        <is>
+          <t>mELM8Zce61c</t>
+        </is>
+      </c>
+      <c r="K840" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26T01:09:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B841" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C841" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　個性ありそうなキャラが登場　最新お知らせ見て行こう　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D841" s="2" t="inlineStr">
+        <is>
+          <t>技上げ雑談配信で最新お知らせや周回を紹介
+絆の記憶スペシャルはソウル抽選2回でお得
+井戸1ターン化やランキング運ゲー化に不満も</t>
+        </is>
+      </c>
+      <c r="E841" s="2" t="inlineStr">
+        <is>
+          <t>・絆の記憶スペシャルはソウル抽選2回でお得
+・周回速度とスタミナ改善はメリット大
+・昔の手動集回は個性があって面白かった</t>
+        </is>
+      </c>
+      <c r="F841" s="2" t="inlineStr">
+        <is>
+          <t>・井戸の1ターン化は10回で飽きてやる気が出ない
+・ランキングが手数のみの運ゲーになりつつある
+・周回に作業感が強くなってきた</t>
+        </is>
+      </c>
+      <c r="G841" s="2" t="inlineStr">
+        <is>
+          <t>・雑談配信
+・フリークエスト周回
+・ソウルアビリティ
+・井戸
+・ランキング</t>
+        </is>
+      </c>
+      <c r="H841" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I841" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=06IzuLk-AVU</t>
+        </is>
+      </c>
+      <c r="J841" s="2" t="inlineStr">
+        <is>
+          <t>06IzuLk-AVU</t>
+        </is>
+      </c>
+      <c r="K841" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26T01:09:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B842" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C842" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　歓喜　FFRKコラボイベント・討伐攻略徹底解説</t>
+        </is>
+      </c>
+      <c r="D842" s="2" t="inlineStr">
+        <is>
+          <t>FFRKコラボ皇帝討伐を徹底攻略解説
+第2形態は能力解除や回復が厄介で短期決戦推奨
+お玉入り陰編成でOD維持し8ターン撃破</t>
+        </is>
+      </c>
+      <c r="E842" s="2" t="inlineStr">
+        <is>
+          <t>・暦読みの火力が高く代々は攻防兼備で便利
+・状態異常がないのは戦いやすい良点
+・ジュエル大量入手できるありがたいイベント</t>
+        </is>
+      </c>
+      <c r="F842" s="2" t="inlineStr">
+        <is>
+          <t>・第2形態はBP増加や能力解除で長期戦は厳しい
+・フレア16が高火力で防御低いキャラは沈む
+・弱点が狭くウィークを取りづらい</t>
+        </is>
+      </c>
+      <c r="G842" s="2" t="inlineStr">
+        <is>
+          <t>・FFRKコラボ
+・皇帝討伐
+・第2形態
+・オーバードライブ
+・短期決戦</t>
+        </is>
+      </c>
+      <c r="H842" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I842" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UseiizGu_sM</t>
+        </is>
+      </c>
+      <c r="J842" s="2" t="inlineStr">
+        <is>
+          <t>UseiizGu_sM</t>
+        </is>
+      </c>
+      <c r="K842" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26T01:09:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B843" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C843" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】騎士ガンダム祭り！8月の更新情報まとめ 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D843" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネ8月更新情報とガチャ予告をまとめ
+限定アルトロン等とSDガンダム外伝祭りが目玉
+月末は控えめだが8月はSDガンダムに全振り</t>
+        </is>
+      </c>
+      <c r="E843" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ内容を事前告知してくれるのはありがたい
+・SDガンダム外伝のレトロRPGマップが良い
+・アルガス騎士団など期待できるイベント</t>
+        </is>
+      </c>
+      <c r="F843" s="2" t="inlineStr">
+        <is>
+          <t>・月末イベントのボリュームは控えめな印象</t>
+        </is>
+      </c>
+      <c r="G843" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・8月更新
+・アルトロンガンダム
+・SDガンダム外伝
+・ガチャ予告</t>
+        </is>
+      </c>
+      <c r="H843" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I843" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JH6T-uEes_g</t>
+        </is>
+      </c>
+      <c r="J843" s="2" t="inlineStr">
+        <is>
+          <t>JH6T-uEes_g</t>
+        </is>
+      </c>
+      <c r="K843" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26T01:09:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B844" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C844" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】きたぞきたぞ！やはり強い神々大暴れ！新キャラランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D844" s="2" t="inlineStr">
+        <is>
+          <t>週次新キャラランキングでエリス編神々を評価
+エリスとウコムがSSで置き物兼火力に高評価
+マカは残弱点かつカウンター条件で化ける</t>
+        </is>
+      </c>
+      <c r="E844" s="2" t="inlineStr">
+        <is>
+          <t>・エリスは弓の希少な強キャラで置き物性能が高い
+・ウコムは霊全体アタッカーで長期戦の安定感抜群
+・マカは残弱点+カウンターでSS+級の火力
+・ルージュはOD促進と回復が使いやすい</t>
+        </is>
+      </c>
+      <c r="F844" s="2" t="inlineStr">
+        <is>
+          <t>・レイ姫は素早さが低く運用に課題
+・コーデリアはデバフ化で自身の火力が出にくい
+・マカは残弱点でない相手にはまず使わない
+・SSは減り環境支配は裁判ら一部のみ</t>
+        </is>
+      </c>
+      <c r="G844" s="2" t="inlineStr">
+        <is>
+          <t>・新キャラランキング
+・エリス
+・ウコム
+・マカ
+・イスカンダール</t>
+        </is>
+      </c>
+      <c r="H844" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I844" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9VIkhFIQLME</t>
+        </is>
+      </c>
+      <c r="J844" s="2" t="inlineStr">
+        <is>
+          <t>9VIkhFIQLME</t>
+        </is>
+      </c>
+      <c r="K844" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26T01:09:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B845" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C845" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】FFRKコラボ記念やります</t>
+        </is>
+      </c>
+      <c r="D845" s="2" t="inlineStr">
+        <is>
+          <t>FFRKコラボ記念ライブでFF2皇帝ボスに挑戦
+キャラ実装はなくボスのみで16日ガチャに期待
+FF2世代の思い出やBGMを語る雑談配信</t>
+        </is>
+      </c>
+      <c r="E845" s="2" t="inlineStr">
+        <is>
+          <t>・FF2の懐かしいBGMや演出が思い出を蘇らせる</t>
+        </is>
+      </c>
+      <c r="F845" s="2" t="inlineStr">
+        <is>
+          <t>・コラボはボスのみでキャラ実装がないのが残念</t>
+        </is>
+      </c>
+      <c r="G845" s="2" t="inlineStr">
+        <is>
+          <t>・FFRKコラボ
+・FF2皇帝
+・ボス戦
+・ガチャ予想
+・雑談配信</t>
+        </is>
+      </c>
+      <c r="H845" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I845" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=n-Hx8YoaJ0k</t>
+        </is>
+      </c>
+      <c r="J845" s="2" t="inlineStr">
+        <is>
+          <t>n-Hx8YoaJ0k</t>
+        </is>
+      </c>
+      <c r="K845" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26T01:09:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B846" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C846" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】現状ガチャの最強は意外なキャラ？最新版確保優先度ランキング【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D846" s="2" t="inlineStr">
+        <is>
+          <t>現行ガチャの確保優先度をランキング解説
+最優先なしでマカ・アセルス・エリスが優先高
+陰属性過多でルージュ・レイ姫は優先度低め</t>
+        </is>
+      </c>
+      <c r="E846" s="2" t="inlineStr">
+        <is>
+          <t>・マカは火ダメ軽減が強力で優先1位
+・アセルスは斬×陰の強属性で60ヒット短期戦向き
+・エリスはエクストラフォース配布で置き物優秀</t>
+        </is>
+      </c>
+      <c r="F846" s="2" t="inlineStr">
+        <is>
+          <t>・今回は最優先級がおらず凪の時期
+・陰属性は飽和で杖のレイ姫・ルージュは不要気味
+・マカのカウンター蓄積は不具合気味で影響は限定的</t>
+        </is>
+      </c>
+      <c r="G846" s="2" t="inlineStr">
+        <is>
+          <t>・確保優先度
+・マカ
+・アセルス
+・エリス
+・陰属性</t>
+        </is>
+      </c>
+      <c r="H846" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I846" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_nKyPo4rt5A</t>
+        </is>
+      </c>
+      <c r="J846" s="2" t="inlineStr">
+        <is>
+          <t>_nKyPo4rt5A</t>
+        </is>
+      </c>
+      <c r="K846" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26T01:09:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B847" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C847" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】隠された重要要素！これを知っているかどうかで大きく差がつく？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D847" s="2" t="inlineStr">
+        <is>
+          <t>交換所後の周回先にフリークエストを推奨
+スペシャルはソウル抽選2回で3秒周回とお得
+ただし育成上限が低く能力値は伸びない点に注意</t>
+        </is>
+      </c>
+      <c r="E847" s="2" t="inlineStr">
+        <is>
+          <t>・スペシャルはソウル抽選2回で1万週分の効率
+・汚された庭園後は1体3秒周回で高効率
+・連マの遺跡は素材集めにおすすめ</t>
+        </is>
+      </c>
+      <c r="F847" s="2" t="inlineStr">
+        <is>
+          <t>・フリークエストは育成上限が低く能力値は上がらない
+・スペシャルの場所が分かりにくく探すのが面倒</t>
+        </is>
+      </c>
+      <c r="G847" s="2" t="inlineStr">
+        <is>
+          <t>・フリークエスト
+・スペシャル周回
+・ソウルアビリティ
+・絆の記憶
+・育成</t>
+        </is>
+      </c>
+      <c r="H847" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I847" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nLxP0KErCMY</t>
+        </is>
+      </c>
+      <c r="J847" s="2" t="inlineStr">
+        <is>
+          <t>nLxP0KErCMY</t>
+        </is>
+      </c>
+      <c r="K847" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26T01:09:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B848" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C848" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはり7.5周年キャラが強過ぎた！コラボクエストの「こうてい」もオート撃破！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D848" s="2" t="inlineStr">
+        <is>
+          <t>FFRKコラボ皇帝を陰属性オート編成で撃破
+7.5周年の暦読み・サイバ・ヴィンセントが強力
+FFファンファーレに感動もガチャ無しは残念</t>
+        </is>
+      </c>
+      <c r="E848" s="2" t="inlineStr">
+        <is>
+          <t>・7.5周年の暦読み・サイバ・ヴィンセントが図抜けて強い
+・ヴィンセントが味方を固くし火ダメが怖くない
+・FFのBGMとファンファーレが素晴らしい</t>
+        </is>
+      </c>
+      <c r="F848" s="2" t="inlineStr">
+        <is>
+          <t>・第2形態は防御上昇でダメージが出づらい
+・コラボはキャラ実装ガチャがなく残念</t>
+        </is>
+      </c>
+      <c r="G848" s="2" t="inlineStr">
+        <is>
+          <t>・FFRKコラボ
+・皇帝討伐
+・陰属性編成
+・7.5周年キャラ
+・オート撃破</t>
+        </is>
+      </c>
+      <c r="H848" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I848" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yiKUBXSMKiE</t>
+        </is>
+      </c>
+      <c r="J848" s="2" t="inlineStr">
+        <is>
+          <t>yiKUBXSMKiE</t>
+        </is>
+      </c>
+      <c r="K848" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26T01:09:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B849" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C849" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第130回 ~魚人たちの井戸 ~2ターン井戸を想定したい（1ターン編成も😅）厳選❗️8パーティを紹介‼️</t>
+        </is>
+      </c>
+      <c r="D849" s="2" t="inlineStr">
+        <is>
+          <t>7/27実装の魚人たちの井戸を実装前考察
+弱点冷で打・全体アタッカーが活躍と予想
+簡単に編成が読め物足りなさを懸念し8編成紹介</t>
+        </is>
+      </c>
+      <c r="E849" s="2" t="inlineStr">
+        <is>
+          <t>・冷属性の全体アタッカーが最も輝く
+・ウコム単体編成など多彩なクリア編成が可能</t>
+        </is>
+      </c>
+      <c r="F849" s="2" t="inlineStr">
+        <is>
+          <t>・1ターン編成がすぐ分かりやりごたえがない
+・敵火力が乏しく軽減対策不要で単調になりそう
+・久々復活だが予想外の強さがないと厳しい</t>
+        </is>
+      </c>
+      <c r="G849" s="2" t="inlineStr">
+        <is>
+          <t>・魚人たちの井戸
+・井戸考察
+・冷属性
+・全体アタッカー
+・ウコム編成</t>
+        </is>
+      </c>
+      <c r="H849" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I849" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TBCffhiBCdI</t>
+        </is>
+      </c>
+      <c r="J849" s="2" t="inlineStr">
+        <is>
+          <t>TBCffhiBCdI</t>
+        </is>
+      </c>
+      <c r="K849" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26T01:09:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B850" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C850" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「エリス 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D850" s="2" t="inlineStr">
+        <is>
+          <t>ロマンシング祭エリス編3スタイルを性能考察
+エリスは置き物兼アタッカーの2役でA-評価
+コーデリアはBP消費デメリット、ルージュは晩成型</t>
+        </is>
+      </c>
+      <c r="E850" s="2" t="inlineStr">
+        <is>
+          <t>・エリスは置き物とアタッカーの2役をこなす良性能
+・エリスの軽減率は6ターン目88%で優秀
+・ルージュは宿命の共演継承で軽減役として有用</t>
+        </is>
+      </c>
+      <c r="F850" s="2" t="inlineStr">
+        <is>
+          <t>・コーデリアはBP+5消費のデメリットが重い
+・コーデリアは既存マイス型の属性違いで登場が遅い
+・ルージュは本気が5ターン目以降と遅い</t>
+        </is>
+      </c>
+      <c r="G850" s="2" t="inlineStr">
+        <is>
+          <t>・エリス編
+・スタイル考察
+・エリス
+・コーデリア
+・ルージュ</t>
+        </is>
+      </c>
+      <c r="H850" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I850" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8xrIwNblesA</t>
+        </is>
+      </c>
+      <c r="J850" s="2" t="inlineStr">
+        <is>
+          <t>8xrIwNblesA</t>
+        </is>
+      </c>
+      <c r="K850" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26T01:09:08Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K850"/>
+  <dimension ref="A1:K854"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -56305,6 +56305,283 @@
         </is>
       </c>
     </row>
+    <row r="851">
+      <c r="A851" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B851" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C851" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始280日目記録　奇跡　まっまさかの！</t>
+        </is>
+      </c>
+      <c r="D851" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣プレイ280日目の進捗記録
+立花・小生5体入手で戦力が大きく前進
+軍リーグや共闘の課題も残り改善を目指す</t>
+        </is>
+      </c>
+      <c r="E851" s="2" t="inlineStr">
+        <is>
+          <t>・立花は火力が高く大範囲攻撃で優秀
+・小生5体入手で編成を整えられる
+・貴重な弓キャラで回心率特化が強力
+・レイド8323位と火力で好順位</t>
+        </is>
+      </c>
+      <c r="F851" s="2" t="inlineStr">
+        <is>
+          <t>・軍リーグは勝率5割で成績不振
+・共闘は素人には難しく苦戦
+・オート向けキャラが少なく編成が難しい
+・火力バフは発動まで時間がかかる</t>
+        </is>
+      </c>
+      <c r="G851" s="2" t="inlineStr">
+        <is>
+          <t>・武将獲得202体
+・立花銀・小生5体
+・全国制圧率4.1%
+・軍リーグ4部
+・共闘イベント
+・工上戦700位目標</t>
+        </is>
+      </c>
+      <c r="H851" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I851" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UIgIskv0FE4</t>
+        </is>
+      </c>
+      <c r="J851" s="2" t="inlineStr">
+        <is>
+          <t>UIgIskv0FE4</t>
+        </is>
+      </c>
+      <c r="K851" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27T01:28:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B852" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C852" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】〇〇バトルで当たり級に！アセルスガチャ最終評価ランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D852" s="2" t="inlineStr">
+        <is>
+          <t>終了間近ガチャのキャラ最終評価動画
+デス・マカ・アセルスをいずれも星2評価
+個人的には息の長いデスがおすすめ</t>
+        </is>
+      </c>
+      <c r="E852" s="2" t="inlineStr">
+        <is>
+          <t>・デスは味方に火力バフ盛りでEF2.5倍が強力
+・デスは斬員強化で息が長くレイド向き
+・アセルスは最大60ヒットの高火力
+・マカは不具合級の大量バフを付与</t>
+        </is>
+      </c>
+      <c r="F852" s="2" t="inlineStr">
+        <is>
+          <t>・アセルスはウィークでないと火力が出ない
+・アセルスはBP不足で味方サポート必須
+・マカは序盤キャラのバフ量が少ない
+・デスは攻撃控えめでLP-5のデメリット</t>
+        </is>
+      </c>
+      <c r="G852" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ最終評価
+・デス星2
+・マカ星2
+・アセルス星2
+・エクストラフォース
+・斬陰ウィーク</t>
+        </is>
+      </c>
+      <c r="H852" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I852" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=P61QhCpqzDA</t>
+        </is>
+      </c>
+      <c r="J852" s="2" t="inlineStr">
+        <is>
+          <t>P61QhCpqzDA</t>
+        </is>
+      </c>
+      <c r="K852" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27T01:28:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B853" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C853" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】2026年7月下旬ガチャ総まとめ！全12スタイル引くべきスタイルランキング！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D853" s="2" t="inlineStr">
+        <is>
+          <t>7月下旬実装ガチャ全12スタイルのティア評価
+最優先枠は該当なし、エリスを有料級に
+アセルス・デス等をダークフォース候補に</t>
+        </is>
+      </c>
+      <c r="E853" s="2" t="inlineStr">
+        <is>
+          <t>・エリスは高水準の弓アタッカーで長く活躍
+・ウコムは全体34ヒットのぶっ飛んだ火力
+・デスははまれば最終ダメ2.5倍と強力
+・アセルスはSS60ヒットで強耐性にも強い</t>
+        </is>
+      </c>
+      <c r="F853" s="2" t="inlineStr">
+        <is>
+          <t>・最優先で取るべきスタイルは今回不在
+・アセルスは斬陰ウィーク前提で相手を選ぶ
+・ルージュは本気が5ター目以降と遅い
+・コーデリアは類似性能持ちなら優先度低め</t>
+        </is>
+      </c>
+      <c r="G853" s="2" t="inlineStr">
+        <is>
+          <t>・ティアランク
+・エリス有料級
+・アセルス/デス
+・ウコム/コーデリア
+・ルージュ
+・霊姫</t>
+        </is>
+      </c>
+      <c r="H853" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I853" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tc6wqkOE4bE</t>
+        </is>
+      </c>
+      <c r="J853" s="2" t="inlineStr">
+        <is>
+          <t>tc6wqkOE4bE</t>
+        </is>
+      </c>
+      <c r="K853" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27T01:28:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B854" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C854" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】7月31日までのオススメの周回方法、今週のやり残しチェック、オマケに井戸もやります【ロマンシング サガ リ ユニバース】</t>
+        </is>
+      </c>
+      <c r="D854" s="2" t="inlineStr">
+        <is>
+          <t>7月31日までのやり残しと周回方法の解説
+週末クエストやアンケ再回答など期限に注意
+記憶再戦の優先順位と当社の看問周回を紹介</t>
+        </is>
+      </c>
+      <c r="E854" s="2" t="inlineStr">
+        <is>
+          <t>・週末限定クエストは簡単で報酬が豪華
+・アンケ再回答で1000ジュエルもらえる
+・当社の看問は1日6000回で回り続けられる</t>
+        </is>
+      </c>
+      <c r="F854" s="2" t="inlineStr">
+        <is>
+          <t>・ラウンドで進化の奇跡集めは非効率
+・連磨素材は課金しても足りない</t>
+        </is>
+      </c>
+      <c r="G854" s="2" t="inlineStr">
+        <is>
+          <t>・やり残しチェック
+・週末限定クエスト
+・アンケ再回答1000ジュエル
+・螺旋回廊チケット期限
+・記憶再戦優先順位
+・当社の看問周回</t>
+        </is>
+      </c>
+      <c r="H854" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I854" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4te03whRX-4</t>
+        </is>
+      </c>
+      <c r="J854" s="2" t="inlineStr">
+        <is>
+          <t>4te03whRX-4</t>
+        </is>
+      </c>
+      <c r="K854" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27T01:28:08Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K854"/>
+  <dimension ref="A1:K861"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -56582,6 +56582,471 @@
         </is>
       </c>
     </row>
+    <row r="855">
+      <c r="A855" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B855" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C855" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「伏兵」ヒューズ&amp;エミリアVS水着鬼八&amp;おたま→12体4ガチャランキング!!最新スタイル比較検討会→2026年7月9日版　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D855" s="2" t="inlineStr">
+        <is>
+          <t>4ガチャ12スタイルを厳選比較しランク付け
+お玉・気発・ヒューズが確保優先の上位
+シンディやメイレンは出番少なく評価低め</t>
+        </is>
+      </c>
+      <c r="E855" s="2" t="inlineStr">
+        <is>
+          <t>・お玉は高防御カウンターで超強力、無人島必須
+・気発は全体攻撃連打で唯一無二の突破力
+・ヒューズはエクストラ3倍維持で全体連打が強い
+・ウルピナは剣姫文字で火力サポートも可能</t>
+        </is>
+      </c>
+      <c r="F855" s="2" t="inlineStr">
+        <is>
+          <t>・シンディは火力不足で使いどころが難しい
+・エミリアはディーバに出力・取り回しで劣る
+・ドールは緑が刺さらず劣化ミド型
+・メイレンは荒れた環境でも出番がない</t>
+        </is>
+      </c>
+      <c r="G855" s="2" t="inlineStr">
+        <is>
+          <t>・4ガチャ12体ランキング
+・お玉の防御カウンター
+・ヒューズ全体連打
+・無人島適性
+・確保優先度</t>
+        </is>
+      </c>
+      <c r="H855" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I855" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JT3nNh0tWdA</t>
+        </is>
+      </c>
+      <c r="J855" s="2" t="inlineStr">
+        <is>
+          <t>JT3nNh0tWdA</t>
+        </is>
+      </c>
+      <c r="K855" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:13:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B856" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C856" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはりあの2人は最強クラス！？最新版確保優先度ランキング【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D856" s="2" t="inlineStr">
+        <is>
+          <t>4ガチャ12体の確保優先度を発表
+最優先は気発とお玉、次点ミーティア・ヒューズ
+他は優先度中、復刻なしで低評価は無し</t>
+        </is>
+      </c>
+      <c r="E856" s="2" t="inlineStr">
+        <is>
+          <t>・気発は息が長くレイドでも長期活躍が確定的
+・お玉はチョコ継承でスペックがえぐい
+・ミーティアは属性優秀でエクストラ配布が強い
+・ヒューズは今回一番使いやすい全体アタッカー</t>
+        </is>
+      </c>
+      <c r="F856" s="2" t="inlineStr">
+        <is>
+          <t>・イリスは妖精パ限定で使い所が狭い
+・エミリアはリキャスト4で術強制が地味に不便
+・ウルピナは追撃過多で使われにくい
+・ドール・メイレンは3〜4ヶ月前の性能感</t>
+        </is>
+      </c>
+      <c r="G856" s="2" t="inlineStr">
+        <is>
+          <t>・確保優先度ランキング
+・気発・お玉が最優先
+・ミーティア・ヒューズ
+・10スタイルの銃価値
+・水着3弾ガチャ</t>
+        </is>
+      </c>
+      <c r="H856" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I856" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MwUWdWZ6xbA</t>
+        </is>
+      </c>
+      <c r="J856" s="2" t="inlineStr">
+        <is>
+          <t>MwUWdWZ6xbA</t>
+        </is>
+      </c>
+      <c r="K856" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:13:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B857" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C857" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】これ全員今すぐ確認してください！超重要な注意喚起とサンゾーの決断！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D857" s="2" t="inlineStr">
+        <is>
+          <t>真夏の大花火大会くじの交換を忘れず注意喚起
+公式生放送53回で当選番号を発表
+賭け方は自由で期待値は約3571ジュエルと同じ</t>
+        </is>
+      </c>
+      <c r="E857" s="2" t="inlineStr">
+        <is>
+          <t>・最大1万5000ジュエルが狙える熱いイベント
+・均等賭けなら最低でも10連分は確保できる</t>
+        </is>
+      </c>
+      <c r="F857" s="2" t="inlineStr">
+        <is>
+          <t>・交換を忘れると過去最大級に後悔する
+・1点賭けは半数以上が0ジュエルの高リスク</t>
+        </is>
+      </c>
+      <c r="G857" s="2" t="inlineStr">
+        <is>
+          <t>・花火くじ交換の注意喚起
+・公式生放送53回
+・くじの期待値
+・1点賭けvs均等
+・サンゾーは6番賭け</t>
+        </is>
+      </c>
+      <c r="H857" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I857" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Rvb0UzSaVvw</t>
+        </is>
+      </c>
+      <c r="J857" s="2" t="inlineStr">
+        <is>
+          <t>Rvb0UzSaVvw</t>
+        </is>
+      </c>
+      <c r="K857" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:13:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B858" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C858" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】メイレン・ヒューズ・ドール能力値早見表 ~メイレンガチャ考察〜火力激アツガチャ‼️</t>
+        </is>
+      </c>
+      <c r="D858" s="2" t="inlineStr">
+        <is>
+          <t>メイレン編ガチャの3体を能力値早見表で考察
+ヒューズは全体スーパーアタッカーで最高評価
+ドール・メイレンは井戸以外の高難度で活躍</t>
+        </is>
+      </c>
+      <c r="E858" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズはWS20ヒット追撃とフォース3倍で刺さる
+・ドールはバトル開始時2100%バフと連打が優秀
+・メイレンは打属性長期戦で当分スタメン
+・火力激アツの引きどくな当たりガチャ</t>
+        </is>
+      </c>
+      <c r="F858" s="2" t="inlineStr">
+        <is>
+          <t>・ドールとメイレンは井戸では使いづらい</t>
+        </is>
+      </c>
+      <c r="G858" s="2" t="inlineStr">
+        <is>
+          <t>・メイレン編ガチャ考察
+・能力値早見表
+・ヒューズ全体アタッカー
+・ドールのバフ性能
+・打属性長期戦</t>
+        </is>
+      </c>
+      <c r="H858" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I858" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8nuUn6kZePI</t>
+        </is>
+      </c>
+      <c r="J858" s="2" t="inlineStr">
+        <is>
+          <t>8nuUn6kZePI</t>
+        </is>
+      </c>
+      <c r="K858" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:13:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B859" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C859" s="2" t="inlineStr">
+        <is>
+          <t>ちゃむのYouTubeガチャ生配信〜何のキャラを狙う？〜取ったキャラで井戸上位を狙う👊</t>
+        </is>
+      </c>
+      <c r="D859" s="2" t="inlineStr">
+        <is>
+          <t>生配信でエリス狙いのガチャ、途中確保に成功
+マカは取れずデスをすり抜けで確保
+魚人の井戸で変化球8手編成がまさかのベスト</t>
+        </is>
+      </c>
+      <c r="E859" s="2" t="inlineStr">
+        <is>
+          <t>・エリスは来週の要弱点井戸で輝くと期待
+・オーバードライブなしの変化球8手編成でベスト達成</t>
+        </is>
+      </c>
+      <c r="F859" s="2" t="inlineStr">
+        <is>
+          <t>・狙いのマカは取れずすり抜けが多発
+・井戸が今は弱く運営に強化を要望</t>
+        </is>
+      </c>
+      <c r="G859" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ生配信
+・エリス確保
+・魚人たちの井戸
+・オーバードなし8手編成
+・すり抜け多発</t>
+        </is>
+      </c>
+      <c r="H859" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I859" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Kug30hnh3hU</t>
+        </is>
+      </c>
+      <c r="J859" s="2" t="inlineStr">
+        <is>
+          <t>Kug30hnh3hU</t>
+        </is>
+      </c>
+      <c r="K859" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:13:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B860" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C860" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第130回魚人たちの井戸〜100位以内を狙え‼️特殊な8手編成を紹介〜⭐️井戸生配信切り取りバージョン⭐️</t>
+        </is>
+      </c>
+      <c r="D860" s="2" t="inlineStr">
+        <is>
+          <t>第130回魚人たちの井戸の特殊8手編成を紹介
+オーバードライブなしでサをトップに配置
+生配信中にまさかのベスト8手を達成</t>
+        </is>
+      </c>
+      <c r="E860" s="2" t="inlineStr">
+        <is>
+          <t>・オーバードライブなしでも8手を狙える変化球編成
+・生配信で偶然ベスト8手(11位)を達成</t>
+        </is>
+      </c>
+      <c r="F860" s="2" t="inlineStr">
+        <is>
+          <t>・サとヒューズの追撃発動が遅いと14ターンに落ちる</t>
+        </is>
+      </c>
+      <c r="G860" s="2" t="inlineStr">
+        <is>
+          <t>・魚人たちの井戸130回
+・特殊8手編成
+・オーバードなし編成
+・100位以内狙い
+・ベスト達成</t>
+        </is>
+      </c>
+      <c r="H860" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I860" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Mn-87GB6-yI</t>
+        </is>
+      </c>
+      <c r="J860" s="2" t="inlineStr">
+        <is>
+          <t>Mn-87GB6-yI</t>
+        </is>
+      </c>
+      <c r="K860" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:13:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B861" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C861" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「エミリア 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D861" s="2" t="inlineStr">
+        <is>
+          <t>エミリア編ガチャ3体を考察しランク付け
+エミリアは熱属性で来月活躍見込みB+評価
+シンディは扱いづらくタコは冷続強化でB評価</t>
+        </is>
+      </c>
+      <c r="E861" s="2" t="inlineStr">
+        <is>
+          <t>・エミリアは技術両用で8月有効の熱属性が強み
+・シンディの陰属性強化効果は非常に強力で暦みと好相性
+・タコは冷続強化として貴重で32ヒットも優秀</t>
+        </is>
+      </c>
+      <c r="F861" s="2" t="inlineStr">
+        <is>
+          <t>・エミリアは性能控えめでリキャスト4の2ターン制限が残念
+・シンディは付与条件の癖が強くクロート向け
+・タコは敵の冷火力も上げ序盤打たれ弱い</t>
+        </is>
+      </c>
+      <c r="G861" s="2" t="inlineStr">
+        <is>
+          <t>・エミリア編考察
+・ランク付け
+・熱属性8月有効
+・シンディの陰強化
+・タコの冷続強化</t>
+        </is>
+      </c>
+      <c r="H861" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I861" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0jje8WMD_7w</t>
+        </is>
+      </c>
+      <c r="J861" s="2" t="inlineStr">
+        <is>
+          <t>0jje8WMD_7w</t>
+        </is>
+      </c>
+      <c r="K861" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:13:45Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K861"/>
+  <dimension ref="A1:K869"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -57047,6 +57047,524 @@
         </is>
       </c>
     </row>
+    <row r="862">
+      <c r="A862" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B862" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C862" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】夏祭りガチャ!!「確定」で来ない12体とサガスカ緋色の野望発売日記念に定期便を絡めたネタバレ!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D862" s="2" t="inlineStr">
+        <is>
+          <t>夏祭り浴衣ガチャの排出キャラを予想する回。
+過去2年の浴衣勢は再登場せず確定不可と分析。
+緋色の野望発売記念でダブルガチャも予想。</t>
+        </is>
+      </c>
+      <c r="E862" s="2" t="inlineStr">
+        <is>
+          <t>・花火大会まで1.5万ジュエル貰えるのは楽しみ
+・10連1/7の確率は当たったようなもの</t>
+        </is>
+      </c>
+      <c r="F862" s="2" t="inlineStr">
+        <is>
+          <t>・最低保証は使い道なく微妙
+・絶望的な浴衣ガチャが想像できる</t>
+        </is>
+      </c>
+      <c r="G862" s="2" t="inlineStr">
+        <is>
+          <t>・夏祭り浴衣ガチャ
+・確定枠予想
+・緋色の野望記念
+・フリー枠キャラ
+・定期便勢</t>
+        </is>
+      </c>
+      <c r="H862" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I862" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=w8Dr18_FMXI</t>
+        </is>
+      </c>
+      <c r="J862" s="2" t="inlineStr">
+        <is>
+          <t>w8Dr18_FMXI</t>
+        </is>
+      </c>
+      <c r="K862" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29T01:05:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B863" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C863" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　技上げ雑談配信　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D863" s="2" t="inlineStr">
+        <is>
+          <t>井戸更新のついでに技上げをする雑談配信。
+迷惑役の影の主役談義からレイモン再評価に発展。
+後半はチーカワやキャバクラ話で盛り上がる。</t>
+        </is>
+      </c>
+      <c r="E863" s="2" t="inlineStr">
+        <is>
+          <t>・レイモンは580でメテオダートのOD永続が有能
+・防御強化＆レジスト持ちで無人島も狙えそう
+・リアムは覚えれば火力もありおすすめ</t>
+        </is>
+      </c>
+      <c r="F863" s="2" t="inlineStr">
+        <is>
+          <t>・技がびっくりするほど覚えない
+・井戸は今回調子が良くない</t>
+        </is>
+      </c>
+      <c r="G863" s="2" t="inlineStr">
+        <is>
+          <t>・技上げ雑談
+・迷惑役議論
+・レイモン再評価
+・螺旋580
+・井戸周回</t>
+        </is>
+      </c>
+      <c r="H863" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I863" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4GUWPuP-HJY</t>
+        </is>
+      </c>
+      <c r="J863" s="2" t="inlineStr">
+        <is>
+          <t>4GUWPuP-HJY</t>
+        </is>
+      </c>
+      <c r="K863" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29T01:05:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B864" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C864" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR トールギスⅡ 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D864" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSSRトールギスⅡ紹介。
+武装アニメーションをShortsで披露する動画。
+セリフ付きの短い演出ムービー中心。</t>
+        </is>
+      </c>
+      <c r="E864" s="2" t="inlineStr"/>
+      <c r="F864" s="2" t="inlineStr"/>
+      <c r="G864" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・SSRトールギスⅡ
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H864" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I864" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jztnblCAets</t>
+        </is>
+      </c>
+      <c r="J864" s="2" t="inlineStr">
+        <is>
+          <t>jztnblCAets</t>
+        </is>
+      </c>
+      <c r="K864" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29T01:05:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B865" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C865" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今日は何かします😻</t>
+        </is>
+      </c>
+      <c r="D865" s="2" t="inlineStr">
+        <is>
+          <t>熊本地震に触れつつ実施した雑談メインの配信。
+雲上・無人島攻略やコーデリアの使い方を検証。
+パチスロ収支や株の話題も交えて進行。</t>
+        </is>
+      </c>
+      <c r="E865" s="2" t="inlineStr">
+        <is>
+          <t>・コーデリアでギリギリ突破でき手応え
+・サイバーがいればマイターンODが可能</t>
+        </is>
+      </c>
+      <c r="F865" s="2" t="inlineStr">
+        <is>
+          <t>・コーデリアはデバフ量少なく使い方が難しい
+・雲上はポルカがいないと厳しい
+・今回の無人島は長期戦ばかりで疲れた</t>
+        </is>
+      </c>
+      <c r="G865" s="2" t="inlineStr">
+        <is>
+          <t>・雲上更新
+・無人島攻略
+・コーデリア検証
+・マイス系運用
+・次回ガチャ予告</t>
+        </is>
+      </c>
+      <c r="H865" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I865" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pQSD5H-8O8U</t>
+        </is>
+      </c>
+      <c r="J865" s="2" t="inlineStr">
+        <is>
+          <t>pQSD5H-8O8U</t>
+        </is>
+      </c>
+      <c r="K865" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29T01:05:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B866" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C866" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】緊急動画！これはかなりヤバい予感がします...【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D866" s="2" t="inlineStr">
+        <is>
+          <t>セレチケ等の交換所終了を最後の注意喚起。
+7/10メンテは意味深でFFRKコラボの予感と考察。
+メンテ後に何か始まると三蔵妄想を展開。</t>
+        </is>
+      </c>
+      <c r="E866" s="2" t="inlineStr">
+        <is>
+          <t>・FFコラボへのワクワク感が幸せと語る
+・メンテ告知文からイベント開催をほぼ確信</t>
+        </is>
+      </c>
+      <c r="F866" s="2" t="inlineStr">
+        <is>
+          <t>・セレチケを毎回忘れる人が多いと注意
+・ローディング据置でガチャは来なさそう</t>
+        </is>
+      </c>
+      <c r="G866" s="2" t="inlineStr">
+        <is>
+          <t>・交換所終了注意
+・セレクトチケット
+・7/10メンテ
+・FFRKコラボ
+・サガラジオ</t>
+        </is>
+      </c>
+      <c r="H866" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I866" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JVC-LgyqVyM</t>
+        </is>
+      </c>
+      <c r="J866" s="2" t="inlineStr">
+        <is>
+          <t>JVC-LgyqVyM</t>
+        </is>
+      </c>
+      <c r="K866" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29T01:05:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B867" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C867" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】これ流石に強すぎるでしょ！俺は遂に配布界最強のキャラを見つけてしまったかもしれない...【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D867" s="2" t="inlineStr">
+        <is>
+          <t>配布のレイモンが配布界最強かもと熱弁する回。
+メテオダートでOD満タン付与＆75%軽減が優秀。
+螺旋回廊580の最終工程で実戦検証を披露。</t>
+        </is>
+      </c>
+      <c r="E867" s="2" t="inlineStr">
+        <is>
+          <t>・メテオダートは制限なくOD満タン付与でぶっ壊れ
+・スターアビの75%軽減が優秀
+・天秤持ちで装備を整えれば硬い
+・サイバーやキアッチもぶっ壊れ性能</t>
+        </is>
+      </c>
+      <c r="F867" s="2" t="inlineStr">
+        <is>
+          <t>・レイモン自身はアタッカーでなく火力は低い</t>
+        </is>
+      </c>
+      <c r="G867" s="2" t="inlineStr">
+        <is>
+          <t>・レイモン配布最強
+・メテオダート
+・OD満タン付与
+・75%軽減
+・螺旋回廊580</t>
+        </is>
+      </c>
+      <c r="H867" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I867" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nNaTigA176E</t>
+        </is>
+      </c>
+      <c r="J867" s="2" t="inlineStr">
+        <is>
+          <t>nNaTigA176E</t>
+        </is>
+      </c>
+      <c r="K867" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29T01:05:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B868" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C868" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】6体の中で当たりは？メイレン&amp;エミリアガチャ性能チェック・キャラランク付け【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D868" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭ガチャ6体の性能を個別に評価。
+一番のおすすめは自身も味方も火力を出すヒューズ。
+6体中5体がSSと偏ったラインナップと解説。</t>
+        </is>
+      </c>
+      <c r="E868" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズは自身火力＋全体火力で環境にマッチ
+・体制デバフ持ちが現環境に噛み合う
+・SS偏りで戦力手薄なら引く価値あり
+・打属性は汎用性が高く使われやすい</t>
+        </is>
+      </c>
+      <c r="F868" s="2" t="inlineStr">
+        <is>
+          <t>・ドールは2ターン目以降バフが減り弱体化
+・キャラによっては敵にもEF付与され注意</t>
+        </is>
+      </c>
+      <c r="G868" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ性能チェック
+・ヒューズ評価
+・キャラランク付け
+・打属性サポーター
+・体制デバフ</t>
+        </is>
+      </c>
+      <c r="H868" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I868" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Fv9SWl8hpvY</t>
+        </is>
+      </c>
+      <c r="J868" s="2" t="inlineStr">
+        <is>
+          <t>Fv9SWl8hpvY</t>
+        </is>
+      </c>
+      <c r="K868" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29T01:05:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B869" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C869" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「メイレン 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D869" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭メイレン編3体を考察しランク付け。
+メイレン・ドール・ヒューズいずれもB評価に。
+次の幻闘は熱霊有効で罠ガチャの予感と警戒。</t>
+        </is>
+      </c>
+      <c r="E869" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズはSS20ヒット追撃と常時OD満タンが強力
+・ヒューズは火力とジャマーを両立できる
+・3体ともSSなので引いておく価値あり
+・打属性は汎用性が高く編成しやすい</t>
+        </is>
+      </c>
+      <c r="F869" s="2" t="inlineStr">
+        <is>
+          <t>・メイレンは軽減50%と低くパワー不足でB評価
+・ドールは長期戦や強化破り相手に不向き
+・3体とも軽減率50%止まりが残念
+・次幻闘は熱霊有効で3体とも罠の予感</t>
+        </is>
+      </c>
+      <c r="G869" s="2" t="inlineStr">
+        <is>
+          <t>・メイレン考察
+・ドール性能
+・ヒューズ評価
+・打属性サポーター
+・罠ガチャ懸念</t>
+        </is>
+      </c>
+      <c r="H869" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I869" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qF-eJuPNeTc</t>
+        </is>
+      </c>
+      <c r="J869" s="2" t="inlineStr">
+        <is>
+          <t>qF-eJuPNeTc</t>
+        </is>
+      </c>
+      <c r="K869" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29T01:05:29Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K869"/>
+  <dimension ref="A1:K875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -57565,6 +57565,406 @@
         </is>
       </c>
     </row>
+    <row r="870">
+      <c r="A870" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B870" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C870" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】6体ランキング「御堂型」ドールと御堂の違い!?数値が物を言う&amp;トゥクァイが2体に!?シンディ・キャンベルの陰weak性能　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D870" s="2" t="inlineStr">
+        <is>
+          <t>移動型6体ランキング。ドールは汎用Sだが御堂の劣化版
+シンディ・キャンベルは総合C、属性縛りと発動条件が難点
+水着ガチャは序盤強め、老費は禁でお玉だけ回そう</t>
+        </is>
+      </c>
+      <c r="E870" s="2" t="inlineStr">
+        <is>
+          <t>・ドールは汎用Sで無差別の攻防上げが可能
+・上位3体は玄関鏡でもしっかり強い作り
+・ヒューズは全体攻撃連打で複数殲滅に強力
+・序盤の水着ガチャは強いので回す価値あり</t>
+        </is>
+      </c>
+      <c r="F870" s="2" t="inlineStr">
+        <is>
+          <t>・シンディ・キャンベルは総合C、属性縛りと発動条件が面倒
+・ドールはエクストラなしで拡張性がなく現環境では致命的
+・エイレンは無限バフ型で流行る要素がない
+・タコおじは冗談で使える程度の配布スペック</t>
+        </is>
+      </c>
+      <c r="G870" s="2" t="inlineStr">
+        <is>
+          <t>・6体ランキング
+・ドール性能
+・シンディ・キャンベル
+・御堂型
+・水着ガチャ</t>
+        </is>
+      </c>
+      <c r="H870" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I870" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dUrvh0oKbJY</t>
+        </is>
+      </c>
+      <c r="J870" s="2" t="inlineStr">
+        <is>
+          <t>dUrvh0oKbJY</t>
+        </is>
+      </c>
+      <c r="K870" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30T01:36:03.681809+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B871" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C871" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】魂アビ部屋へ…「緊急」防具取り逃しあるぞ!?キャンベルマリンリゾートのイベント立ち回りを考える　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D871" s="2" t="inlineStr">
+        <is>
+          <t>キャンベルマリンリゾートのイベント立ち回りを解説
+防具連魔素材の部屋はスルー、最奥の部屋にこもるのが効率的
+ジュエル等のレアドロ運と立ち回りで周回効率が変わる</t>
+        </is>
+      </c>
+      <c r="E871" s="2" t="inlineStr">
+        <is>
+          <t>・パスキーを早く入手し最奥に籠る効率周回を提案</t>
+        </is>
+      </c>
+      <c r="F871" s="2" t="inlineStr">
+        <is>
+          <t>・防具連魔素材の部屋は恩恵少なめでスルー推奨
+・ジュエル等のレアドロがなかなか落ちない</t>
+        </is>
+      </c>
+      <c r="G871" s="2" t="inlineStr">
+        <is>
+          <t>・イベント立ち回り
+・防具素材
+・パスキー
+・最奥部屋
+・レアドロ</t>
+        </is>
+      </c>
+      <c r="H871" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I871" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sa-8h9QWW_s</t>
+        </is>
+      </c>
+      <c r="J871" s="2" t="inlineStr">
+        <is>
+          <t>sa-8h9QWW_s</t>
+        </is>
+      </c>
+      <c r="K871" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30T01:36:03.681809+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B872" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C872" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】エリス取説「最強お供八選」未来におりゅ?される可能性大!!根本的なハイスペックを活かせるお仲間とは!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D872" s="2" t="inlineStr">
+        <is>
+          <t>エリスの性能解説と相性の良いお供8選を紹介
+全体37ヒット連打の高スペックだがスロースタートが難点
+ラゼムやリアム等と高シナジー、持っておくのを推奨</t>
+        </is>
+      </c>
+      <c r="E872" s="2" t="inlineStr">
+        <is>
+          <t>・エリスは全体37ヒット連打で現環境最高スペック
+・開幕エクストラ用ウィーク2.25倍で置き物として文句なし
+・ラゼム・リアム・イシス等とエクストラが被らず高シナジー
+・技マシンのコーデア・ルージュもいて回しやすいガチャ</t>
+        </is>
+      </c>
+      <c r="F872" s="2" t="inlineStr">
+        <is>
+          <t>・6ターン目から本領発揮のスロースタートで出番が限られる
+・仲間がいないと活用されず現状流行っていない
+・すぐには使えず即戦力にはならない</t>
+        </is>
+      </c>
+      <c r="G872" s="2" t="inlineStr">
+        <is>
+          <t>・エリス性能
+・お供8選
+・スロースタート
+・ラゼム/リアム
+・打属性シナジー</t>
+        </is>
+      </c>
+      <c r="H872" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I872" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zcA6rKk4Yt4</t>
+        </is>
+      </c>
+      <c r="J872" s="2" t="inlineStr">
+        <is>
+          <t>zcA6rKk4Yt4</t>
+        </is>
+      </c>
+      <c r="K872" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30T01:36:03.681809+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B873" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C873" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　優れた逸材がいるかも・・・　影の主役　実は優れている44選</t>
+        </is>
+      </c>
+      <c r="D873" s="2" t="inlineStr">
+        <is>
+          <t>アンズモンが選ぶ「影の主役」優秀サポート44選
+武器種別に壁役・攻防バフ・BPサポート型を紹介
+ビクトールやコーテオン等が高評価、コメントで意見募集</t>
+        </is>
+      </c>
+      <c r="E873" s="2" t="inlineStr">
+        <is>
+          <t>・レッドは壁役兼防御評価に貢献できる
+・最終コーテオンは攻防サポート継承技も優秀
+・ビクトール自身も火力高く味方に火力バフを撒く
+・アスラナメイクは味方の被弾を100%カットできる
+・これら影の主役は継承技豊富でパーティにマッチしやすい</t>
+        </is>
+      </c>
+      <c r="F873" s="2" t="inlineStr"/>
+      <c r="G873" s="2" t="inlineStr">
+        <is>
+          <t>・影の主役44選
+・サポートキャラ
+・攻防バフ
+・壁役
+・武器種別紹介</t>
+        </is>
+      </c>
+      <c r="H873" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I873" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3cgXOPwKlgs</t>
+        </is>
+      </c>
+      <c r="J873" s="2" t="inlineStr">
+        <is>
+          <t>3cgXOPwKlgs</t>
+        </is>
+      </c>
+      <c r="K873" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30T01:36:03.681809+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B874" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C874" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】この組み合わせはチートすぎる・・・【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D874" s="2" t="inlineStr">
+        <is>
+          <t>西王アビス攻略の変わった編成を紹介・実演
+イスカンダル＋最終コーテオ＋暦みでチェイン大量蓄積が刺さる
+アーニャの避弾時バフ消しと暦みのばらまきが強力</t>
+        </is>
+      </c>
+      <c r="E874" s="2" t="inlineStr">
+        <is>
+          <t>・この組み合わせはチートすぎるほど強い編成
+・暦みはHP/BPをばらまく『バフの王』で超優秀
+・イスカンダルのドライブオーダー高速中まくりが強力
+・アーニャの避弾時バフ消しが西王に刺さる
+・最終コーテオのルクスオーバーエンチャントが強力</t>
+        </is>
+      </c>
+      <c r="F874" s="2" t="inlineStr">
+        <is>
+          <t>・西王アビスは難しくクリアできない人が多い
+・全略オートしづらく手動操作が必要な場面がある
+・この編成はサイバー(安定感)が低め</t>
+        </is>
+      </c>
+      <c r="G874" s="2" t="inlineStr">
+        <is>
+          <t>・西王アビス攻略
+・イスカンダル編成
+・暦み(覚醒の骨玉)
+・チェインアーツ
+・アーニャ バフ消し</t>
+        </is>
+      </c>
+      <c r="H874" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I874" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lu9wCR9y2So</t>
+        </is>
+      </c>
+      <c r="J874" s="2" t="inlineStr">
+        <is>
+          <t>lu9wCR9y2So</t>
+        </is>
+      </c>
+      <c r="K874" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30T01:36:03.681809+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B875" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C875" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】公式生放送が祭りの予感！現状の把握と内容を徹底予想【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D875" s="2" t="inlineStr">
+        <is>
+          <t>7/31公式生放送ナンバー53の内容を予想
+夏祭り・浴衣ダブルガチャが濃厚と予想
+つき・アントニウス・テレーズ等6キャラを願望込みで予想</t>
+        </is>
+      </c>
+      <c r="E875" s="2" t="inlineStr">
+        <is>
+          <t>・夏祭り・浴衣ガチャで盛り上がりそう
+・シリアス続きの後の息抜きとして歓迎
+・テレーズやミカエルの浴衣実装に期待
+・なかなか良いガチャになりそうとの予想</t>
+        </is>
+      </c>
+      <c r="F875" s="2" t="inlineStr">
+        <is>
+          <t>・誰が来るかの予想は難しい
+・直近2〜4ヶ月で実装済みのキャラは除外せざるを得ない</t>
+        </is>
+      </c>
+      <c r="G875" s="2" t="inlineStr">
+        <is>
+          <t>・公式生放送予想
+・夏祭り浴衣ガチャ
+・ダブルガチャ
+・サガスカ発売日記念
+・6キャラ予想</t>
+        </is>
+      </c>
+      <c r="H875" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I875" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ff8ZOrgCQnQ</t>
+        </is>
+      </c>
+      <c r="J875" s="2" t="inlineStr">
+        <is>
+          <t>ff8ZOrgCQnQ</t>
+        </is>
+      </c>
+      <c r="K875" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30T01:36:03.681809+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K875"/>
+  <dimension ref="A1:K880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -57965,6 +57965,337 @@
         </is>
       </c>
     </row>
+    <row r="876">
+      <c r="A876" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B876" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C876" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始301日目記録　待望　新規イベントに期待</t>
+        </is>
+      </c>
+      <c r="D876" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣プレイ301日目の進捗と記録を報告
+武田信虎など新武将入手、最大名威は78万に上昇
+上杉列伝イベント開始、上杉系の新武将性能に期待</t>
+        </is>
+      </c>
+      <c r="E876" s="2" t="inlineStr">
+        <is>
+          <t>・武田信虎は特攻で火力が上がり十分強かった
+・新武将の長尾為景は弓編成で火力が上がり良さそう
+・長尾影綱は謙信合わせで係数が大きく回復もあり強力
+・タップが3万台に到達し記録が改善</t>
+        </is>
+      </c>
+      <c r="F876" s="2" t="inlineStr">
+        <is>
+          <t>・攻撃低下の間隔が長く上では攻撃前にやられる
+・名島イベントはポイント取り切れず苦戦（発数不足）
+・スゴ6はレベル18止まりで20に届かず育成不足
+・拠点が取れずレベル96のまま上げられなかった</t>
+        </is>
+      </c>
+      <c r="G876" s="2" t="inlineStr">
+        <is>
+          <t>・信長の野望出陣
+・進捗報告
+・新武将評価
+・制圧率
+・列伝イベント
+・上杉系</t>
+        </is>
+      </c>
+      <c r="H876" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I876" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5ZrxwV3QLdQ</t>
+        </is>
+      </c>
+      <c r="J876" s="2" t="inlineStr">
+        <is>
+          <t>5ZrxwV3QLdQ</t>
+        </is>
+      </c>
+      <c r="K876" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31T10:49:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B877" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C877" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】EN管理が大事！ガンダムヘビーアームズ改性能確認 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D877" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナル新実装ヘビーアームズ改の性能確認
+EN管理が重要な攻撃型、初動火力は高いが燃費悪化
+トロアのEN回復でカバー、EN回復サポーター推奨</t>
+        </is>
+      </c>
+      <c r="E877" s="2" t="inlineStr">
+        <is>
+          <t>・初動の火力は非常に高そう
+・トロアのEN回復とアタックバーストでダメージを出せる</t>
+        </is>
+      </c>
+      <c r="F877" s="2" t="inlineStr">
+        <is>
+          <t>・EN75%以上で消費40%増、燃費が悪く火力が徐々に低下
+・マップ兵器は移動後使用不可の通常タイプ</t>
+        </is>
+      </c>
+      <c r="G877" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ヘビーアームズ改
+・EN管理
+・攻撃型ユニット
+・トロア</t>
+        </is>
+      </c>
+      <c r="H877" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I877" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=R5j13T98ZbA</t>
+        </is>
+      </c>
+      <c r="J877" s="2" t="inlineStr">
+        <is>
+          <t>R5j13T98ZbA</t>
+        </is>
+      </c>
+      <c r="K877" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31T10:49:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B878" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C878" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】移動後MAP兵器＆物理射程延長！アルトロンガンダム性能確認 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D878" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナル新実装アルトロンガンダムの性能確認
+支援型で移動後MAP兵器と物理射程延長が使いやすい
+ウーフェイと組み支援攻撃の火力が高いタイプ</t>
+        </is>
+      </c>
+      <c r="E878" s="2" t="inlineStr">
+        <is>
+          <t>・移動後もMAP兵器発動可でデバフを安全に入れられ強そう
+・支援攻撃時の物理射程延長が便利
+・ウーフェイと組むと支援火力が高くエジ2に近い雰囲気</t>
+        </is>
+      </c>
+      <c r="F878" s="2" t="inlineStr">
+        <is>
+          <t>・EX武装ドラゴンハングは射程1〜4と自力攻撃だと短め</t>
+        </is>
+      </c>
+      <c r="G878" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・アルトロンガンダム
+・支援型
+・移動後MAP兵器
+・ウーフェイ</t>
+        </is>
+      </c>
+      <c r="H878" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I878" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zc6P-43rAt8</t>
+        </is>
+      </c>
+      <c r="J878" s="2" t="inlineStr">
+        <is>
+          <t>Zc6P-43rAt8</t>
+        </is>
+      </c>
+      <c r="K878" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31T10:49:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B879" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C879" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】アルトロンとヘビーアームズ改の性能が一部公開されたので確認しよう 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D879" s="2" t="inlineStr">
+        <is>
+          <t>明日実装のアルトロンとヘビーアームズ改の性能をまとめ確認
+アルトロンは移動後MAP兵器と支援火力で好印象
+ヘビーアームズ改はEN管理次第、1.5周年前で悩む</t>
+        </is>
+      </c>
+      <c r="E879" s="2" t="inlineStr">
+        <is>
+          <t>・アルトロンは移動後MAP兵器と支援火力で個人的に良さげ
+・ウーフェイの支援ダメージ上昇で火力が高い
+・ミリアルドはエンドレスワルツ編成で30%上昇</t>
+        </is>
+      </c>
+      <c r="F879" s="2" t="inlineStr">
+        <is>
+          <t>・ヘビーアームズ改はEN消費40%増で息切れしやすい
+・1.5周年が近くガチャを回すか迷う</t>
+        </is>
+      </c>
+      <c r="G879" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・アルトロン
+・ヘビーアームズ改
+・ミリアルド
+・1.5周年</t>
+        </is>
+      </c>
+      <c r="H879" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I879" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hRkPePSJx_c</t>
+        </is>
+      </c>
+      <c r="J879" s="2" t="inlineStr">
+        <is>
+          <t>hRkPePSJx_c</t>
+        </is>
+      </c>
+      <c r="K879" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31T10:49:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B880" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C880" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【ガチャ動画】遂に我らも…！？歴史的瞬間が今ここに！？【No.624】</t>
+        </is>
+      </c>
+      <c r="D880" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRSガチャ、こ太がマカ・ターコがエリス狙い
+こ太の10連で安転しピックアップ複数体を引き当てる
+チャンネル7年半で初の神引きに2人で歓喜</t>
+        </is>
+      </c>
+      <c r="E880" s="2" t="inlineStr">
+        <is>
+          <t>・こ太が10連でピックアップ複数体を引く歴史的な神引き
+・エリス（シルベン更新）やマカが魅力的なキャラ</t>
+        </is>
+      </c>
+      <c r="F880" s="2" t="inlineStr">
+        <is>
+          <t>・ターコは10連で何も出ず引きが悪い</t>
+        </is>
+      </c>
+      <c r="G880" s="2" t="inlineStr">
+        <is>
+          <t>・ロマサガRS
+・ガチャ動画
+・マカ
+・エリス
+・安転
+・神引き</t>
+        </is>
+      </c>
+      <c r="H880" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I880" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lM-ypNgSgAU</t>
+        </is>
+      </c>
+      <c r="J880" s="2" t="inlineStr">
+        <is>
+          <t>lM-ypNgSgAU</t>
+        </is>
+      </c>
+      <c r="K880" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31T10:49:32Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K880"/>
+  <dimension ref="A1:K900"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -58296,6 +58296,1305 @@
         </is>
       </c>
     </row>
+    <row r="881">
+      <c r="A881" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B881" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C881" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「未来永劫使える」継承シウグナス!!エクストラ2.5倍に全体サポートSS20連打のやり放題スタイル!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D881" s="2" t="inlineStr">
+        <is>
+          <t>継承シウグナスの高難度性能を評価。
+エクストラ2.5倍とSS20連打が強力。
+爆発力はないが総合サポートで無難に強い。</t>
+        </is>
+      </c>
+      <c r="E881" s="2" t="inlineStr">
+        <is>
+          <t>・エクストラ2.5倍とSS20連打技2が強力
+・防御・回復・BP・デバフを総合的にこなす
+・回避継承は未来永劫使えるので確保価値あり</t>
+        </is>
+      </c>
+      <c r="F881" s="2" t="inlineStr">
+        <is>
+          <t>・味方への火力補正がエクストラなしで絶望的
+・立ち回りが融通効かず爆発力がない
+・特化した良さがなく器用貧乏</t>
+        </is>
+      </c>
+      <c r="G881" s="2" t="inlineStr">
+        <is>
+          <t>・シウグナス
+・エクストラ2.5倍
+・SS20連打
+・継承性能
+・高難度評価A</t>
+        </is>
+      </c>
+      <c r="H881" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I881" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=97RglnqEB6c</t>
+        </is>
+      </c>
+      <c r="J881" s="2" t="inlineStr">
+        <is>
+          <t>97RglnqEB6c</t>
+        </is>
+      </c>
+      <c r="K881" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:09:31Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B882" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C882" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ギミック解明速報「熱冷CAUTION解除」ウンボルをゴリ押しなぎ倒せ!?ウンディーネ&amp;ボルカノそれぞれの対処法を剣と大剣で解説　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D882" s="2" t="inlineStr">
+        <is>
+          <t>ウンボル幻闘場を剣・大剣で攻略する速報。
+CAUTION解除か3ターン目ゴリ押しの2択。
+高火力なら属性無視で瞬殺可能。</t>
+        </is>
+      </c>
+      <c r="E882" s="2" t="inlineStr">
+        <is>
+          <t>・高火力武器は属性無視でビクトールなど瞬殺で楽勝</t>
+        </is>
+      </c>
+      <c r="F882" s="2" t="inlineStr">
+        <is>
+          <t>・火力なき武器はギミック破壊必須で難しい
+・再来のレイでウンディネの火力が上がるので注意
+・LPダメで長期戦が不可</t>
+        </is>
+      </c>
+      <c r="G882" s="2" t="inlineStr">
+        <is>
+          <t>・ウンボル攻略
+・CAUTION解除
+・ゴリ押し
+・21ヒット
+・ビクトール瞬殺</t>
+        </is>
+      </c>
+      <c r="H882" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I882" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Idh4X1ZdTC4</t>
+        </is>
+      </c>
+      <c r="J882" s="2" t="inlineStr">
+        <is>
+          <t>Idh4X1ZdTC4</t>
+        </is>
+      </c>
+      <c r="K882" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:09:31Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B883" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C883" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】エレノア3-4秒「色を属性と合わせて」花火玉周回!! #ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D883" s="2" t="inlineStr">
+        <is>
+          <t>エレノアで花火玉イベントを周回する動画。
+敵の色を属性に合わせるのがコツ。
+1戦3〜4秒の高速周回編成。</t>
+        </is>
+      </c>
+      <c r="E883" s="2" t="inlineStr">
+        <is>
+          <t>・エレノア周回が3〜4秒と高速でお手軽</t>
+        </is>
+      </c>
+      <c r="F883" s="2" t="inlineStr"/>
+      <c r="G883" s="2" t="inlineStr">
+        <is>
+          <t>・花火玉周回
+・エレノア編成
+・色と属性合わせ
+・高速周回</t>
+        </is>
+      </c>
+      <c r="H883" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I883" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gcK8aaqTz4c</t>
+        </is>
+      </c>
+      <c r="J883" s="2" t="inlineStr">
+        <is>
+          <t>gcK8aaqTz4c</t>
+        </is>
+      </c>
+      <c r="K883" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:09:31Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B884" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C884" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「新型ダメブロ」エクストラにOD満タンと便利かつ強いジニー!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D884" s="2" t="inlineStr">
+        <is>
+          <t>新キャラ・ジニーの高難度性能を評価。
+エクストラ2倍と高防御・ダメブロが売り。
+総合評価Aだがポンコツ気味で器用貧乏。</t>
+        </is>
+      </c>
+      <c r="E884" s="2" t="inlineStr">
+        <is>
+          <t>・エクストラ拡張性2倍が強い
+・防御が優秀（棒立ち75%、技で81%）
+・水風船シールドとダメブロで特攻性あり</t>
+        </is>
+      </c>
+      <c r="F884" s="2" t="inlineStr">
+        <is>
+          <t>・自身の火力補正がなくポンコツ気味
+・ディフェンシブ寄りでガンガン起用はしにくい
+・総合的に微妙な器用貧乏</t>
+        </is>
+      </c>
+      <c r="G884" s="2" t="inlineStr">
+        <is>
+          <t>・ジニー性能
+・ダメブロ
+・エクストラ2倍
+・高防御
+・高難度評価A</t>
+        </is>
+      </c>
+      <c r="H884" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I884" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kF_tUIm06eE</t>
+        </is>
+      </c>
+      <c r="J884" s="2" t="inlineStr">
+        <is>
+          <t>kF_tUIm06eE</t>
+        </is>
+      </c>
+      <c r="K884" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:09:31Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B885" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C885" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「世界記録」関門シュウザー速報!!自由枠を目指し一択アタッカーの編成を究めろ!!闘者の関門2026年8月　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D885" s="2" t="inlineStr">
+        <is>
+          <t>闘者の関門シュウザーの速報攻略。
+置き物バフ重視で世界記録は10〜15秒。
+自由枠1つを想定した編成を紹介。</t>
+        </is>
+      </c>
+      <c r="E885" s="2" t="inlineStr">
+        <is>
+          <t>・置き物バフ重視でダメージ増加、世界記録10秒台</t>
+        </is>
+      </c>
+      <c r="F885" s="2" t="inlineStr"/>
+      <c r="G885" s="2" t="inlineStr">
+        <is>
+          <t>・闘者の関門
+・シュウザー
+・置き物バフ
+・世界記録編成
+・自由枠</t>
+        </is>
+      </c>
+      <c r="H885" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I885" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nUSw77Yky64</t>
+        </is>
+      </c>
+      <c r="J885" s="2" t="inlineStr">
+        <is>
+          <t>nUSw77Yky64</t>
+        </is>
+      </c>
+      <c r="K885" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:09:31Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B886" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C886" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】SSS評価組は生き残れるか？新キャラランキング！幻闘場難易度激変【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D886" s="2" t="inlineStr">
+        <is>
+          <t>日曜恒例の新キャラランキング配信。
+幻闘場が激変し難易度が急上昇。
+幻闘場特攻キャラの評価を大幅見直し。</t>
+        </is>
+      </c>
+      <c r="E886" s="2" t="inlineStr">
+        <is>
+          <t>・リアルクイーンは幻闘場特攻でS評価
+・コーデリアが冷属性全体で幻闘場に刺さり評価UP
+・暦みや裁判が環境で圧倒的に強い
+・イリス・ミーティア・ネメシスが幻闘場で活躍</t>
+        </is>
+      </c>
+      <c r="F886" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場がぬるくなると動画需要が減ると嘆く
+・リアルクイーンは体術に裁判がいると優先度低め
+・弓・銃・斧・杖など火力不足の武器種は難しい</t>
+        </is>
+      </c>
+      <c r="G886" s="2" t="inlineStr">
+        <is>
+          <t>・新キャラランキング
+・幻闘場難易度激変
+・リアルクイーンS
+・コーデリア評価UP
+・ウンボル特攻</t>
+        </is>
+      </c>
+      <c r="H886" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I886" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B8KHaKLsIok</t>
+        </is>
+      </c>
+      <c r="J886" s="2" t="inlineStr">
+        <is>
+          <t>B8KHaKLsIok</t>
+        </is>
+      </c>
+      <c r="K886" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:10:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B887" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C887" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新たなインフレか！夏祭り6人の性能確認【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D887" s="2" t="inlineStr">
+        <is>
+          <t>夏祭りガチャ6人の性能を確認する配信。
+シウグナスやリアルクイーンなど新スタイルを評価。
+新たなインフレを感じる強キャラ揃い。</t>
+        </is>
+      </c>
+      <c r="E887" s="2" t="inlineStr">
+        <is>
+          <t>・シウグナスは天使人連携2.5倍でSS20連打の当たり
+・リアルクイーンは敵弱体と自己火力が優秀
+・アデルは順当に強化されバフ配りが優秀</t>
+        </is>
+      </c>
+      <c r="F887" s="2" t="inlineStr">
+        <is>
+          <t>・ジニーの水風船シールドがリキャスト4で1回のみは残念
+・シウグナスのエクストラフォースは自分だけで全体に配れない</t>
+        </is>
+      </c>
+      <c r="G887" s="2" t="inlineStr">
+        <is>
+          <t>・夏祭りガチャ
+・6人性能確認
+・シウグナス当たり
+・ジニーOD満タン
+・リアルクイーン</t>
+        </is>
+      </c>
+      <c r="H887" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I887" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OdKJold7wL4</t>
+        </is>
+      </c>
+      <c r="J887" s="2" t="inlineStr">
+        <is>
+          <t>OdKJold7wL4</t>
+        </is>
+      </c>
+      <c r="K887" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:10:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B888" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C888" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】強すぎて草！鬼門幻闘場ウンディーネ＆ボルカノ6種剣/大剣/体術/小剣/銃/棍棒【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D888" s="2" t="inlineStr">
+        <is>
+          <t>鬼門の幻闘場ウンボルを複数武器種で攻略。
+20ヒットで属性CAUTION解除がカギ。
+斧など火力不足の武器種はかなり難しい。</t>
+        </is>
+      </c>
+      <c r="E888" s="2" t="inlineStr">
+        <is>
+          <t>・剣・体術は火力が高くゴリ押しで攻略しやすい
+・リアルクイーンやお玉・雪だるまが特攻で刺さる
+・久々に考える編成で楽しい高難度</t>
+        </is>
+      </c>
+      <c r="F888" s="2" t="inlineStr">
+        <is>
+          <t>・斧やコンボは火力不足でかなり難しい
+・直接/間接攻撃の使い分けが必須で複雑
+・最近の中で一番難しい難易度</t>
+        </is>
+      </c>
+      <c r="G888" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場ウンボル
+・武器種別攻略
+・CAUTION解除
+・直接間接使い分け
+・体術特攻</t>
+        </is>
+      </c>
+      <c r="H888" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I888" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VWmJTZFiEck</t>
+        </is>
+      </c>
+      <c r="J888" s="2" t="inlineStr">
+        <is>
+          <t>VWmJTZFiEck</t>
+        </is>
+      </c>
+      <c r="K888" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:10:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B889" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C889" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】幻闘場高難易度化で評価UPあり★4大ガチャランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D889" s="2" t="inlineStr">
+        <is>
+          <t>高難易度化を受けた最新ガチャランキング配信。
+幻闘場特攻キャラの引き得度を評価。
+ピンクパンチやコーデリアなど注目株を解説。</t>
+        </is>
+      </c>
+      <c r="E889" s="2" t="inlineStr">
+        <is>
+          <t>・ジニーはボルカノ特攻で全体防御80%超と優秀
+・コーデリアがウンボルに刺さり取って良かった
+・ピンクパンチは行動回数で火力が跳ね上がる</t>
+        </is>
+      </c>
+      <c r="F889" s="2" t="inlineStr">
+        <is>
+          <t>・リアルクイーンは防御60%が物足りず必須ではない
+・ピンクパンチは自分にバフを貼れず落ちると微妙
+・霊姫は技力が低く運用に課題</t>
+        </is>
+      </c>
+      <c r="G889" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャランキング
+・幻闘場高難易度化
+・引き得評価
+・ピンクパンチ
+・コーデリア評価UP</t>
+        </is>
+      </c>
+      <c r="H889" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I889" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bwX37bq8eYY</t>
+        </is>
+      </c>
+      <c r="J889" s="2" t="inlineStr">
+        <is>
+          <t>bwX37bq8eYY</t>
+        </is>
+      </c>
+      <c r="K889" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:10:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B890" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C890" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】結局今回1番のあたりは誰なの？リアルクィーン編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D890" s="2" t="inlineStr">
+        <is>
+          <t>リアルクイーン編ガチャ3人の性能チェック。
+つきは術特攻の強力アタッカーだが敵を選ぶ。
+アデルはサポート寄りで装備を要調整。</t>
+        </is>
+      </c>
+      <c r="E890" s="2" t="inlineStr">
+        <is>
+          <t>・つきは敵が術中心なら30ヒット追撃で大火力
+・つきはエクストラフォース2倍で高威力
+・アデルはレジスト防御で耐久も確保</t>
+        </is>
+      </c>
+      <c r="F890" s="2" t="inlineStr">
+        <is>
+          <t>・つきは技を2連続で受けると信念が切れ貧弱化
+・つきは敵を選び必須タイミングが少ない
+・同等火力のキャラが他にもいて無理して取る必要は薄い</t>
+        </is>
+      </c>
+      <c r="G890" s="2" t="inlineStr">
+        <is>
+          <t>・リアルクイーン編
+・つき性能
+・アデル性能
+・術特攻
+・ガチャ性能チェック</t>
+        </is>
+      </c>
+      <c r="H890" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I890" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AFK0GQYjRKo</t>
+        </is>
+      </c>
+      <c r="J890" s="2" t="inlineStr">
+        <is>
+          <t>AFK0GQYjRKo</t>
+        </is>
+      </c>
+      <c r="K890" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:11:49Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B891" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C891" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】みんなが持ってるキャラたちが無双イベント！？新イベントの注意点と解説【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D891" s="2" t="inlineStr">
+        <is>
+          <t>新イベント「巨大な尺玉」の注意点とボス解説。
+開催期間が非常に短いのが最大の注意点。
+ボスは弱点属性を規定回数当てるギミック。</t>
+        </is>
+      </c>
+      <c r="E891" s="2" t="inlineStr">
+        <is>
+          <t>・配布キャラだけでボスギミックを攻略できる
+・配布モニカが属性追撃で非常に便利
+・ジュエルなど報酬が多くお得</t>
+        </is>
+      </c>
+      <c r="F891" s="2" t="inlineStr">
+        <is>
+          <t>・開催期間が実質5〜6日と非常に短く要注意
+・ギミックを理解しないとボスは倒せない仕様</t>
+        </is>
+      </c>
+      <c r="G891" s="2" t="inlineStr">
+        <is>
+          <t>・尺玉イベント
+・短い開催期間
+・色別周回
+・ボスギミック
+・配布編成攻略</t>
+        </is>
+      </c>
+      <c r="H891" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I891" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dFSf5IVqaGY</t>
+        </is>
+      </c>
+      <c r="J891" s="2" t="inlineStr">
+        <is>
+          <t>dFSf5IVqaGY</t>
+        </is>
+      </c>
+      <c r="K891" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:11:49Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B892" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C892" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】気付いた？これ1人破格な性能いるよね！ジニー編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D892" s="2" t="inlineStr">
+        <is>
+          <t>ジニー編ガチャ3人の性能チェック。
+シウグナスが1番の当たりで破格の性能。
+ピンクパンチは性別縛りが厳しいサポーター。</t>
+        </is>
+      </c>
+      <c r="E892" s="2" t="inlineStr">
+        <is>
+          <t>・シウグナスは技3の戦士鉄人連携が破格で継承価値大
+・シウグナスは暦みサイバー編成にハマり汎用性が高い
+・ピンクパンチはエクストラ1.75倍の置き物性能が高い
+・ジニーはOD環境で冷編成の重要な役割</t>
+        </is>
+      </c>
+      <c r="F892" s="2" t="inlineStr">
+        <is>
+          <t>・ピンクパンチは性別不明・男性縛りで編成が狭い
+・シウグナスはLP消費でマイターン連打はできない
+・ジニーは冷編成を組む人以外には刺さりにくい</t>
+        </is>
+      </c>
+      <c r="G892" s="2" t="inlineStr">
+        <is>
+          <t>・ジニー編
+・シウグナス当たり
+・ピンクパンチ
+・ジニー冷編成
+・ブラッドサマータイム</t>
+        </is>
+      </c>
+      <c r="H892" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I892" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fVqJ3QFqnu0</t>
+        </is>
+      </c>
+      <c r="J892" s="2" t="inlineStr">
+        <is>
+          <t>fVqJ3QFqnu0</t>
+        </is>
+      </c>
+      <c r="K892" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:13:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B893" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C893" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはり祭りがやってきた！熱かったくじ結果と公式生放送の内容まとめ【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D893" s="2" t="inlineStr">
+        <is>
+          <t>公式生放送直後の内容まとめと感想配信。
+夏祭りダブルガチャやイベント情報を解説。
+くじ結果や闘者の関門などの新情報も紹介。</t>
+        </is>
+      </c>
+      <c r="E893" s="2" t="inlineStr">
+        <is>
+          <t>・くじで3等が当選しラッキーだった
+・闘者の関門の武器威力が97に上昇しやりがいあり
+・協力ミッションで最大3000ジュエルもらえてお得</t>
+        </is>
+      </c>
+      <c r="F893" s="2" t="inlineStr">
+        <is>
+          <t>・夏祭りガチャの開催期間が実質5〜6日と短くタイト
+・くじは均等がけの方が得だったかもと複雑な心境</t>
+        </is>
+      </c>
+      <c r="G893" s="2" t="inlineStr">
+        <is>
+          <t>・公式生放送まとめ
+・夏祭り2026
+・ダブルガチャ
+・くじ結果
+・闘者の関門97</t>
+        </is>
+      </c>
+      <c r="H893" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I893" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nautnOBi0r4</t>
+        </is>
+      </c>
+      <c r="J893" s="2" t="inlineStr">
+        <is>
+          <t>nautnOBi0r4</t>
+        </is>
+      </c>
+      <c r="K893" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:11:49Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B894" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C894" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新キャラ性能確認とガチャ引く！～ライブ配信/声あり～</t>
+        </is>
+      </c>
+      <c r="D894" s="2" t="inlineStr">
+        <is>
+          <t>ガチャ更新キャラの性能確認ライブ配信。
+リアルクイーン編とジニー編を評価。
+火力は出るがBP不足に注意が必要。</t>
+        </is>
+      </c>
+      <c r="E894" s="2" t="inlineStr">
+        <is>
+          <t>・リアルクイーンは開幕の置き物火力バフが多め
+・シグナスはバランスが取れて相性が良い
+・ピンクパンチは性別不明で1.75倍と強い</t>
+        </is>
+      </c>
+      <c r="F894" s="2" t="inlineStr">
+        <is>
+          <t>・リアルクイーンはBP不足で技を連発できない
+・アデルは中長期戦でBP不足になりがち
+・つきは技を2連続で受けると弱体化</t>
+        </is>
+      </c>
+      <c r="G894" s="2" t="inlineStr">
+        <is>
+          <t>・新キャラ性能確認
+・リアルクイーン編
+・ジニー編
+・打熱編成
+・BP周り注意</t>
+        </is>
+      </c>
+      <c r="H894" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I894" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Lc6JHHF00lM</t>
+        </is>
+      </c>
+      <c r="J894" s="2" t="inlineStr">
+        <is>
+          <t>Lc6JHHF00lM</t>
+        </is>
+      </c>
+      <c r="K894" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:12:46Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B895" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C895" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】攻略のカギは熱冷〇〇！幻闘場ウンディーネ&amp;ボルカノ大剣の戦録ギミック紹介&amp;クリアパーティー紹介【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D895" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場ウンディーネ&amp;ボルカノを大剣で攻略。
+熱20重でCAUTION解除、火力優先が有効。
+気絶やLPダメで難易度は高め。</t>
+        </is>
+      </c>
+      <c r="E895" s="2" t="inlineStr">
+        <is>
+          <t>・威力アップ連撃中心の大剣編成が有効</t>
+        </is>
+      </c>
+      <c r="F895" s="2" t="inlineStr">
+        <is>
+          <t>・気絶攻撃やLPダメで従来より難易度が高め
+・大剣はイン以外レジストで火力確保が課題</t>
+        </is>
+      </c>
+      <c r="G895" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場ウンボル
+・大剣攻略
+・熱冷ギミック
+・CAUTION解除</t>
+        </is>
+      </c>
+      <c r="H895" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I895" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VvWFT72arlw</t>
+        </is>
+      </c>
+      <c r="J895" s="2" t="inlineStr">
+        <is>
+          <t>VvWFT72arlw</t>
+        </is>
+      </c>
+      <c r="K895" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:09:31Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B896" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C896" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】8月の幻闘場をガンガンクリアしていく配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D896" s="2" t="inlineStr">
+        <is>
+          <t>8月の幻闘場ウンボルに挑む生配信。
+マイターン20ヒットの条件が非常に厳しい。
+配信中は体術と杖しかクリアできず苦戦。</t>
+        </is>
+      </c>
+      <c r="E896" s="2" t="inlineStr">
+        <is>
+          <t>・火力でゴリ押しできる武器種は攻略が楽
+・今まで微妙だった弓キャラが活躍して面白い
+・連携技が増えて強化された</t>
+        </is>
+      </c>
+      <c r="F896" s="2" t="inlineStr">
+        <is>
+          <t>・マイターン20ヒットの条件が厳しすぎる
+・体術は冷属性持ちがなくスタンもされ不利
+・小剣・弓・斧は火力不足でかなり難しい
+・配信中は体術と杖しかクリアできず悔しい</t>
+        </is>
+      </c>
+      <c r="G896" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場ウンボル
+・20ヒット条件
+・武器種別攻略
+・火力ゴリ押し
+・高難度</t>
+        </is>
+      </c>
+      <c r="H896" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I896" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4ne6MtP7gak</t>
+        </is>
+      </c>
+      <c r="J896" s="2" t="inlineStr">
+        <is>
+          <t>4ne6MtP7gak</t>
+        </is>
+      </c>
+      <c r="K896" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:12:46Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B897" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C897" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】追憶の幻闘場「ボルカノ＆ウンディーネ」ギミック解説・攻略！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D897" s="2" t="inlineStr">
+        <is>
+          <t>追憶の幻闘場ボルカノ&amp;ウンディーネのギミック解説。
+熱冷属性を軸にした攻略ポイントを紹介。
+字幕が自動生成のため詳細は不鮮明。</t>
+        </is>
+      </c>
+      <c r="E897" s="2" t="inlineStr"/>
+      <c r="F897" s="2" t="inlineStr"/>
+      <c r="G897" s="2" t="inlineStr">
+        <is>
+          <t>・追憶の幻闘場
+・ボルカノ&amp;ウンディーネ
+・ギミック解説
+・熱冷攻略</t>
+        </is>
+      </c>
+      <c r="H897" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I897" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UviXO52-lbU</t>
+        </is>
+      </c>
+      <c r="J897" s="2" t="inlineStr">
+        <is>
+          <t>UviXO52-lbU</t>
+        </is>
+      </c>
+      <c r="K897" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:09:31Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B898" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C898" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】公式生放送終わりのガチャ考察最速配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D898" s="2" t="inlineStr">
+        <is>
+          <t>公式生放送直後のガチャ性能考察・最速配信。
+リアルクイーンやピンクパンチを計算しながら評価。
+4ターンに1度の大火力など性能を分析。</t>
+        </is>
+      </c>
+      <c r="E898" s="2" t="inlineStr">
+        <is>
+          <t>・リアルクイーンは4ターンに1度2.5倍36ヒットで普通に強い
+・打熱の置き物として1ターン目1480とそこそこ使える
+・ピンクパンチは性別不明で1.75倍と強い</t>
+        </is>
+      </c>
+      <c r="F898" s="2" t="inlineStr">
+        <is>
+          <t>・リアルクイーンは防御62%が微妙で発動が遅い
+・最近は発揮開始が遅くデメリット持ちスタイルが多すぎる
+・視聴メダルの切り替えが早すぎて前回分を取り切れない</t>
+        </is>
+      </c>
+      <c r="G898" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ考察
+・リアルクイーン
+・ピンクパンチ
+・打熱編成
+・最速配信</t>
+        </is>
+      </c>
+      <c r="H898" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I898" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ma6-dmgNowk</t>
+        </is>
+      </c>
+      <c r="J898" s="2" t="inlineStr">
+        <is>
+          <t>ma6-dmgNowk</t>
+        </is>
+      </c>
+      <c r="K898" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:12:46Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B899" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C899" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベントの解説 今回も注意点有り!!周回編成の紹介 ボスバトルの解説【ロマンシング サガ リ ユニバース】</t>
+        </is>
+      </c>
+      <c r="D899" s="2" t="inlineStr">
+        <is>
+          <t>新イベント「巨大な尺玉」の周回とボス解説。
+赤木青の尺玉を協力ミッションで集める。
+ボスは弱点3〜5回ヒットのギミック必須。</t>
+        </is>
+      </c>
+      <c r="E899" s="2" t="inlineStr">
+        <is>
+          <t>・協力ミッション達成でセンジュエルがもらえてお得
+・配布のハのお面が入手できる</t>
+        </is>
+      </c>
+      <c r="F899" s="2" t="inlineStr">
+        <is>
+          <t>・協力ミッションで半強制的に周回させられるのは好ましくない
+・花火玉のHPが約3500万と高い</t>
+        </is>
+      </c>
+      <c r="G899" s="2" t="inlineStr">
+        <is>
+          <t>・花火玉イベント
+・尺玉赤木青
+・協力ミッション
+・ボスギミック
+・センジュエル</t>
+        </is>
+      </c>
+      <c r="H899" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I899" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gB1NpvxuJlM</t>
+        </is>
+      </c>
+      <c r="J899" s="2" t="inlineStr">
+        <is>
+          <t>gB1NpvxuJlM</t>
+        </is>
+      </c>
+      <c r="K899" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:09:31Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B900" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C900" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】闘者の関門-シュウザー- 周回編成を9種紹介!!追撃順の固定化!?最速は11秒【ロマンシング サガ リ ユニバース】</t>
+        </is>
+      </c>
+      <c r="D900" s="2" t="inlineStr">
+        <is>
+          <t>闘者の関門シュウザーの周回編成9種を紹介。
+追撃順固定化テクで最速11秒周回。
+武器威力は97に上昇、星25まで約3000周。</t>
+        </is>
+      </c>
+      <c r="E900" s="2" t="inlineStr">
+        <is>
+          <t>・追撃順固定化で最速11秒の安定周回が可能
+・武器威力が97に上昇（過去最高）</t>
+        </is>
+      </c>
+      <c r="F900" s="2" t="inlineStr">
+        <is>
+          <t>・星25まで約3000周が必要で周回負荷が大きい</t>
+        </is>
+      </c>
+      <c r="G900" s="2" t="inlineStr">
+        <is>
+          <t>・シュウザー周回
+・編成9種
+・最速11秒
+・追撃順固定化
+・武器威力97</t>
+        </is>
+      </c>
+      <c r="H900" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I900" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zWN8ynP8o7M</t>
+        </is>
+      </c>
+      <c r="J900" s="2" t="inlineStr">
+        <is>
+          <t>zWN8ynP8o7M</t>
+        </is>
+      </c>
+      <c r="K900" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T01:09:31Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K900"/>
+  <dimension ref="A1:K902"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -59595,6 +59595,148 @@
         </is>
       </c>
     </row>
+    <row r="901">
+      <c r="A901" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B901" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C901" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「リアルクィーン 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D901" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭リアルクイーン編のガチャ3体を考察。
+リアルクイーンは打熱アタッカーで8月幻闘場ボルカに有効。
+つき・アデルは活躍場面が限定的でB評価。</t>
+        </is>
+      </c>
+      <c r="E901" s="2" t="inlineStr">
+        <is>
+          <t>・リアルクイーン:4ターンに1度36ヒット＋支援・デバフ
+・リアルクイーン:熱属性で8月幻闘場ボルカに有効
+・つき:術攻撃特攻で40〜50ヒットの恐ろしい手数
+・つき:8月ボルカノ&amp;ウンディネで力を発揮できる
+・アデル:要属性連携で火ダメ軽減役として優秀</t>
+        </is>
+      </c>
+      <c r="F901" s="2" t="inlineStr">
+        <is>
+          <t>・リアルクイーン:火力重視だと味方へ代償ダメージ
+・つき:術以外の敵には自己バフが機能せず活躍限定
+・つき:ボルカノ以外で刺さる場面が少ない
+・アデル:参千を継承できないと火ダメ軽減役止まり
+・アデル:本体火力・攻撃回数が物足りない</t>
+        </is>
+      </c>
+      <c r="G901" s="2" t="inlineStr">
+        <is>
+          <t>・リアルクイーン編考察
+・リアルクイーン性能
+・つき性能
+・アデル性能
+・8月幻闘場ボルカノ</t>
+        </is>
+      </c>
+      <c r="H901" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I901" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8PFOTwk1WGk</t>
+        </is>
+      </c>
+      <c r="J901" s="2" t="inlineStr">
+        <is>
+          <t>8PFOTwk1WGk</t>
+        </is>
+      </c>
+      <c r="K901" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T01:20:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B902" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C902" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「ジニー 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D902" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭ジニー編のガチャ3体を性能考察。
+看板ジニーが頭一つ優秀でOD支援と火ダメ軽減が強力。
+シグナス・ピンクパンチは環境次第でB評価。</t>
+        </is>
+      </c>
+      <c r="E902" s="2" t="inlineStr">
+        <is>
+          <t>・ジニー:冷×OD×ウィーク時に最終ダメ2倍と強力
+・ジニー:火ダメ軽減80%台で高難度向き
+・ジニー:実質3回攻撃ならODゲージ常時満タン可能
+・シグナス:最大火力2.5倍×5回36ヒットと高火力
+・ピンクパンチ:男性/不明への1.75倍支援が優秀</t>
+        </is>
+      </c>
+      <c r="F902" s="2" t="inlineStr">
+        <is>
+          <t>・ジニー:現環境は引属性が強く冷属性の出番が不安
+・ジニー:最終ダメ2倍は3条件達成が難しい
+・シグナス:LP消費と確率回復で連続使用が不安定
+・ピンクパンチ:自身が女性で支援を受けられない
+・ピンクパンチ:女性優遇環境で採用が微妙</t>
+        </is>
+      </c>
+      <c r="G902" s="2" t="inlineStr">
+        <is>
+          <t>・ジニー編ガチャ考察
+・ジニー性能
+・シグナス性能
+・ピンクパンチ性能
+・冷属性サポート</t>
+        </is>
+      </c>
+      <c r="H902" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I902" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=urpPB7d1K58</t>
+        </is>
+      </c>
+      <c r="J902" s="2" t="inlineStr">
+        <is>
+          <t>urpPB7d1K58</t>
+        </is>
+      </c>
+      <c r="K902" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T01:20:11Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K902"/>
+  <dimension ref="A1:K923"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -59737,6 +59737,1306 @@
         </is>
       </c>
     </row>
+    <row r="903">
+      <c r="A903" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B903" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C903" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】幻闘「落とし穴」盤石の槍&amp;杖!!これでも「低難度」ギミック立ち回り→追憶の幻闘場ウンディーネ&amp;ボルカノ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D903" s="2" t="inlineStr">
+        <is>
+          <t>追憶の幻闘場ウンディーネ&amp;ボルカノを槍・杖で攻略
+槍はBP枯渇と代償ダメで立ち回りがシビア
+杖は属性揃いで最小人数の編成が組みやすい</t>
+        </is>
+      </c>
+      <c r="E903" s="2" t="inlineStr">
+        <is>
+          <t>・杖は属性が揃うため最小人数で21ヒット狙える
+・斧はゴリ押しでレベル4まで到達</t>
+        </is>
+      </c>
+      <c r="F903" s="2" t="inlineStr">
+        <is>
+          <t>・弓はレベル3までしか届かない
+・槍はBP枯渇・代償ダメで打ち直し不可などシビア
+・コーデリアは火力サポート不在でコーション破壊要員止まり</t>
+        </is>
+      </c>
+      <c r="G903" s="2" t="inlineStr">
+        <is>
+          <t>・追憶の幻闘場
+・ウンディーネ
+・ボルカノ
+・槍攻略
+・杖攻略</t>
+        </is>
+      </c>
+      <c r="H903" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I903" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6q1y5qN5EDM</t>
+        </is>
+      </c>
+      <c r="J903" s="2" t="inlineStr">
+        <is>
+          <t>6q1y5qN5EDM</t>
+        </is>
+      </c>
+      <c r="K903" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B904" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C904" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ネタバレ「夏の最終回」サガ〇〇来る来る!!出禁キャラを差し引けば楽勝よのガチャ予想　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D904" s="2" t="inlineStr">
+        <is>
+          <t>「夏の最終回」の次ガチャを予想する動画
+出禁キャラを差し引いた予想を展開
+※字幕がBGM主体で詳細不明</t>
+        </is>
+      </c>
+      <c r="E904" s="2" t="inlineStr"/>
+      <c r="F904" s="2" t="inlineStr"/>
+      <c r="G904" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ予想
+・夏の最終回
+・出禁キャラ</t>
+        </is>
+      </c>
+      <c r="H904" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I904" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8JJmZsMtyvw</t>
+        </is>
+      </c>
+      <c r="J904" s="2" t="inlineStr">
+        <is>
+          <t>8JJmZsMtyvw</t>
+        </is>
+      </c>
+      <c r="K904" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B905" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C905" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】アデル引くべし!?「週間ランキング」エリス&amp;ウコムと現ガチャ比較検討会ラストチャンス!!リアルクィーン&amp;斬陽最強アタッカーアデル性能詳細　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D905" s="2" t="inlineStr">
+        <is>
+          <t>エリス&amp;ウコムと現ガチャの週間ランキング比較
+リアルクイーンは本年ワースト級のC評価
+アデルは実質アタッカーだが環境上位のB評価</t>
+        </is>
+      </c>
+      <c r="E905" s="2" t="inlineStr">
+        <is>
+          <t>・アデルは継承前提で残陽3.25倍と強い
+・ブレない立ち回りと高いEFで環境上位・火力SS</t>
+        </is>
+      </c>
+      <c r="F905" s="2" t="inlineStr">
+        <is>
+          <t>・リアルクイーンはリキャスト4ターンで2ターンしか働かず本年ワースト1位
+・リアルクイーンは継承技3も忘れて構わないほど無効果
+・アデルもサポート性能はおまけ以下</t>
+        </is>
+      </c>
+      <c r="G905" s="2" t="inlineStr">
+        <is>
+          <t>・週間ランキング
+・リアルクイーン評価
+・アデル評価
+・継承起点
+・総合評価</t>
+        </is>
+      </c>
+      <c r="H905" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I905" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=I4Rx7n5uB8Q</t>
+        </is>
+      </c>
+      <c r="J905" s="2" t="inlineStr">
+        <is>
+          <t>I4Rx7n5uB8Q</t>
+        </is>
+      </c>
+      <c r="K905" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B906" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C906" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】神引きからの「逃亡」タマゴローが滑り込んだガチャはどれ!?エリス編ウコム編ツバキにジニーに…　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D906" s="2" t="inlineStr">
+        <is>
+          <t>エリス・ウコム等のガチャを実戦する動画
+神引きから滑り込みガチャを紹介
+※字幕がBGM主体で詳細不明</t>
+        </is>
+      </c>
+      <c r="E906" s="2" t="inlineStr"/>
+      <c r="F906" s="2" t="inlineStr"/>
+      <c r="G906" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ実戦
+・エリス
+・ウコム
+・ツバキ
+・ジニー</t>
+        </is>
+      </c>
+      <c r="H906" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I906" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hAacOZhS75c</t>
+        </is>
+      </c>
+      <c r="J906" s="2" t="inlineStr">
+        <is>
+          <t>hAacOZhS75c</t>
+        </is>
+      </c>
+      <c r="K906" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B907" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C907" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】URアルトロンガンダム(EW版) 武装アニメ  ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D907" s="2" t="inlineStr">
+        <is>
+          <t>URアルトロンガンダム(EW版)の武装アニメ紹介
+ドラゴンハング等の戦闘ボイスを収録
+※セリフ主体で評価コメントなし</t>
+        </is>
+      </c>
+      <c r="E907" s="2" t="inlineStr"/>
+      <c r="F907" s="2" t="inlineStr"/>
+      <c r="G907" s="2" t="inlineStr">
+        <is>
+          <t>・アルトロンガンダム
+・武装アニメ
+・EW版
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H907" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I907" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7mI_w92Zx6M</t>
+        </is>
+      </c>
+      <c r="J907" s="2" t="inlineStr">
+        <is>
+          <t>7mI_w92Zx6M</t>
+        </is>
+      </c>
+      <c r="K907" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B908" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C908" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】アルトロン100連追いガシャするぞ！ 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D908" s="2" t="inlineStr">
+        <is>
+          <t>前回外したアルトロンを追い100連
+天井込みで2凸まで到達し満足
+表示バグに悩まされつつ自引き成功</t>
+        </is>
+      </c>
+      <c r="E908" s="2" t="inlineStr">
+        <is>
+          <t>・自引きでき天井込み2凸まで行けて良かった
+・支援型でも攻撃力1万超えるのが良い
+・ドラゴンハングの伸びる演出が面白い</t>
+        </is>
+      </c>
+      <c r="F908" s="2" t="inlineStr">
+        <is>
+          <t>・演出がなく失速気味
+・SSRは沢山出るのにピック枠エピオンが全然出ない
+・謎の表示バグが多発</t>
+        </is>
+      </c>
+      <c r="G908" s="2" t="inlineStr">
+        <is>
+          <t>・アルトロン
+・100連追いガシャ
+・天井交換
+・2凸
+・ヘビーアームズ</t>
+        </is>
+      </c>
+      <c r="H908" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I908" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9SYMb0QRgEo</t>
+        </is>
+      </c>
+      <c r="J908" s="2" t="inlineStr">
+        <is>
+          <t>9SYMb0QRgEo</t>
+        </is>
+      </c>
+      <c r="K908" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B909" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C909" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR ムシャゴースト 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D909" s="2" t="inlineStr">
+        <is>
+          <t>SSRムシャゴーストの武装アニメ紹介
+戦闘ボイスを短尺で収録
+※セリフ主体で評価コメントなし</t>
+        </is>
+      </c>
+      <c r="E909" s="2" t="inlineStr"/>
+      <c r="F909" s="2" t="inlineStr"/>
+      <c r="G909" s="2" t="inlineStr">
+        <is>
+          <t>・ムシャゴースト
+・武装アニメ
+・SSR
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H909" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I909" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UgSom-20Bk8</t>
+        </is>
+      </c>
+      <c r="J909" s="2" t="inlineStr">
+        <is>
+          <t>UgSom-20Bk8</t>
+        </is>
+      </c>
+      <c r="K909" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B910" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C910" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】迷ったけどアルトロン 100連回すぞ！Shorts版#3 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D910" s="2" t="inlineStr">
+        <is>
+          <t>100連ラスト、限定確定枠も専用機止まり(Shorts#3)
+セーラ等の狙いキャラも来ず
+追いガシャ確定の展開</t>
+        </is>
+      </c>
+      <c r="E910" s="2" t="inlineStr">
+        <is>
+          <t>・専用機のHP回復ならまだマシと前向き</t>
+        </is>
+      </c>
+      <c r="F910" s="2" t="inlineStr">
+        <is>
+          <t>・100連確定枠でも限定が出ず追いガシャ確定
+・狙いのセーラ等が来ない</t>
+        </is>
+      </c>
+      <c r="G910" s="2" t="inlineStr">
+        <is>
+          <t>・アルトロン
+・100連
+・Shorts
+・天井確定枠
+・追いガシャ</t>
+        </is>
+      </c>
+      <c r="H910" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I910" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_2IfIUlzXQ8</t>
+        </is>
+      </c>
+      <c r="J910" s="2" t="inlineStr">
+        <is>
+          <t>_2IfIUlzXQ8</t>
+        </is>
+      </c>
+      <c r="K910" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B911" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C911" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】迷ったけどアルトロン 100連回すぞ！Shorts版#2 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D911" s="2" t="inlineStr">
+        <is>
+          <t>100連中盤、URは出るが限定は出ず(Shorts#2)
+ピック被りで攻撃型を凸れたのは良い
+分かりやすく限定が出ないパターン</t>
+        </is>
+      </c>
+      <c r="E911" s="2" t="inlineStr">
+        <is>
+          <t>・攻撃型を凸れて火力が上がるのは良い</t>
+        </is>
+      </c>
+      <c r="F911" s="2" t="inlineStr">
+        <is>
+          <t>・限定アルトロンが出ないパターン
+・ピック被りが続く</t>
+        </is>
+      </c>
+      <c r="G911" s="2" t="inlineStr">
+        <is>
+          <t>・アルトロン
+・100連
+・Shorts
+・攻撃型凸
+・UR被り</t>
+        </is>
+      </c>
+      <c r="H911" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I911" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=f9kSRIzaGDk</t>
+        </is>
+      </c>
+      <c r="J911" s="2" t="inlineStr">
+        <is>
+          <t>f9kSRIzaGDk</t>
+        </is>
+      </c>
+      <c r="K911" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B912" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C912" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】迷ったけどアルトロン 100連回すぞ！Shorts版#1 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D912" s="2" t="inlineStr">
+        <is>
+          <t>アルトロン限定狙いで100連開始(Shorts#1)
+序盤アムロで何も出ず流れが悪い
+コンテナカットインも入らず厳しい展開</t>
+        </is>
+      </c>
+      <c r="E912" s="2" t="inlineStr">
+        <is>
+          <t>・支援型の強いURがいると攻略が色々楽になる</t>
+        </is>
+      </c>
+      <c r="F912" s="2" t="inlineStr">
+        <is>
+          <t>・序盤から演出なしで限定が出ず厳しい</t>
+        </is>
+      </c>
+      <c r="G912" s="2" t="inlineStr">
+        <is>
+          <t>・アルトロン
+・100連
+・Shorts
+・エピオン
+・支援型</t>
+        </is>
+      </c>
+      <c r="H912" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I912" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nWvDAvk-4Ig</t>
+        </is>
+      </c>
+      <c r="J912" s="2" t="inlineStr">
+        <is>
+          <t>nWvDAvk-4Ig</t>
+        </is>
+      </c>
+      <c r="K912" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B913" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C913" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SR メリクリウス 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D913" s="2" t="inlineStr">
+        <is>
+          <t>SRメリクリウスの武装アニメ紹介
+「覚悟なさい」等の戦闘ボイスを収録
+※セリフ主体で評価コメントなし</t>
+        </is>
+      </c>
+      <c r="E913" s="2" t="inlineStr"/>
+      <c r="F913" s="2" t="inlineStr"/>
+      <c r="G913" s="2" t="inlineStr">
+        <is>
+          <t>・メリクリウス
+・武装アニメ
+・SR
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H913" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I913" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=oWJPb5BMvA0</t>
+        </is>
+      </c>
+      <c r="J913" s="2" t="inlineStr">
+        <is>
+          <t>oWJPb5BMvA0</t>
+        </is>
+      </c>
+      <c r="K913" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B914" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C914" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】闘者の関門シュウザーでまさかのキャラが大活躍！？周回方法を解説【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D914" s="2" t="inlineStr">
+        <is>
+          <t>闘者の関門シューザーの周回方法を解説
+レイ姫が全体攻撃アタッカーとして大活躍
+武器力97更新で周回はしっかりやりたい</t>
+        </is>
+      </c>
+      <c r="E914" s="2" t="inlineStr">
+        <is>
+          <t>・レイ姫が短期決戦で大活躍「このためにあったのか」
+・技2の全体6回→単体15回の発動順が便利</t>
+        </is>
+      </c>
+      <c r="F914" s="2" t="inlineStr">
+        <is>
+          <t>・シューザーは敵が多く単体攻撃だと対応が難しい</t>
+        </is>
+      </c>
+      <c r="G914" s="2" t="inlineStr">
+        <is>
+          <t>・闘者の関門
+・シューザー周回
+・レイ姫
+・武器力97
+・置き物編成</t>
+        </is>
+      </c>
+      <c r="H914" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I914" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=27UIuqYnp6g</t>
+        </is>
+      </c>
+      <c r="J914" s="2" t="inlineStr">
+        <is>
+          <t>27UIuqYnp6g</t>
+        </is>
+      </c>
+      <c r="K914" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B915" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C915" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】不可能を可能にする裏技？視聴者からの情報が凄すぎたので紹介します！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D915" s="2" t="inlineStr">
+        <is>
+          <t>視聴者提供の裏技をチャンネルで共有
+行動順補正低下を100以上入れると追撃順が固定化
+シューザー周回で1発目に冷を固定できる</t>
+        </is>
+      </c>
+      <c r="E915" s="2" t="inlineStr">
+        <is>
+          <t>・行動順固定の裏技は知っておくべき有用テク
+・固欠人会・ファイターシフトで能動的に固定可能
+・視聴者のやり込みと情報提供に感謝</t>
+        </is>
+      </c>
+      <c r="F915" s="2" t="inlineStr">
+        <is>
+          <t>・人系素材のハードルが高くミーティア龍級が必要</t>
+        </is>
+      </c>
+      <c r="G915" s="2" t="inlineStr">
+        <is>
+          <t>・行動順補正低下
+・追撃順固定
+・シューザー周回
+・固欠人会
+・視聴者情報</t>
+        </is>
+      </c>
+      <c r="H915" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I915" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5hFrRqtWzDw</t>
+        </is>
+      </c>
+      <c r="J915" s="2" t="inlineStr">
+        <is>
+          <t>5hFrRqtWzDw</t>
+        </is>
+      </c>
+      <c r="K915" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B916" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C916" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】この時期には化け物ガチャがやってくる！？運命の8月6日がやってくる【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D916" s="2" t="inlineStr">
+        <is>
+          <t>恒例の次ガチャ予想動画
+8月6日は夏祭りの次に肝試しガチャと予想
+昨年外した肝試しに今年こそと再挑戦</t>
+        </is>
+      </c>
+      <c r="E916" s="2" t="inlineStr">
+        <is>
+          <t>・毎週のようにガチャが来る勢いが凄い</t>
+        </is>
+      </c>
+      <c r="F916" s="2" t="inlineStr">
+        <is>
+          <t>・2025年は肝試しが来ず悔しかった
+・運営もガチャネタ切れでは(推測)</t>
+        </is>
+      </c>
+      <c r="G916" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ予想
+・肝試しガチャ
+・夏祭りガチャ
+・8月6日</t>
+        </is>
+      </c>
+      <c r="H916" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I916" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GThJWrLnqR4</t>
+        </is>
+      </c>
+      <c r="J916" s="2" t="inlineStr">
+        <is>
+          <t>GThJWrLnqR4</t>
+        </is>
+      </c>
+      <c r="K916" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B917" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C917" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今月のパスは買う？スルー？パメラの性能を詳しく確認【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D917" s="2" t="inlineStr">
+        <is>
+          <t>今月のロマパス パメラの性能を確認
+弓・闇アタッカーでインサガキャラ
+連魔石やソウルピース目当てでも価値あり</t>
+        </is>
+      </c>
+      <c r="E917" s="2" t="inlineStr">
+        <is>
+          <t>・イラストが良い
+・インサガ(エサガ)キャラという点で価値がある
+・パス特典の連魔石10万超・ソウルピース5000がお得
+・広告非表示や倍速も嬉しい</t>
+        </is>
+      </c>
+      <c r="F917" s="2" t="inlineStr">
+        <is>
+          <t>・ウンディーネ/ボルカノには属性が噛み合わずバリバリは刺さらない</t>
+        </is>
+      </c>
+      <c r="G917" s="2" t="inlineStr">
+        <is>
+          <t>・ロマンシングパス
+・パメラ
+・弓アタッカー
+・連魔石
+・ソウルピース</t>
+        </is>
+      </c>
+      <c r="H917" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I917" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qOD2XQ-NoCo</t>
+        </is>
+      </c>
+      <c r="J917" s="2" t="inlineStr">
+        <is>
+          <t>qOD2XQ-NoCo</t>
+        </is>
+      </c>
+      <c r="K917" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B918" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C918" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】8月のロマンシングパスは買うべきか？8月ロマパスキャラ・武器性能確認&amp;評価【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D918" s="2" t="inlineStr">
+        <is>
+          <t>8月ロマンシングパスの性能を評価
+上級パメラも通常武器もスルー寄り
+ボルカノ対策の弓補強なら検討の余地</t>
+        </is>
+      </c>
+      <c r="E918" s="2" t="inlineStr">
+        <is>
+          <t>・通常武器は味方全体バフ・闇術持ちで陰キャラに使える
+・使ったジュエルは無償分で回収できるのが嬉しい</t>
+        </is>
+      </c>
+      <c r="F918" s="2" t="inlineStr">
+        <is>
+          <t>・パメラの50ヒットアビは編成全体への恩恵が少なくスルー寄り
+・通常武器もありきたりでスルー
+・ステバフは魂アビで代替可能</t>
+        </is>
+      </c>
+      <c r="G918" s="2" t="inlineStr">
+        <is>
+          <t>・ロマンシングパス
+・パメラ評価
+・通常パス武器
+・ボルカノ</t>
+        </is>
+      </c>
+      <c r="H918" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I918" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TNW-tlGNjSY</t>
+        </is>
+      </c>
+      <c r="J918" s="2" t="inlineStr">
+        <is>
+          <t>TNW-tlGNjSY</t>
+        </is>
+      </c>
+      <c r="K918" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B919" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C919" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】なぜウコムガチャ引いたのか？終了間近ウコムガチャ引いてみた【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D919" s="2" t="inlineStr">
+        <is>
+          <t>終了間近のウコムガチャを実戦
+すり抜け祭りで結局天井交換に
+霊雷全体アタッカーとして幻闘場補強狙い</t>
+        </is>
+      </c>
+      <c r="E919" s="2" t="inlineStr">
+        <is>
+          <t>・ウコムの3ターン後レライEF1.5倍は無人島でも刺さりそう
+・イスカンダールが幻闘場で活躍で嬉しい
+・高難度が来てガチャを引く理由が増えて良い</t>
+        </is>
+      </c>
+      <c r="F919" s="2" t="inlineStr">
+        <is>
+          <t>・すり抜け続きでピックアップが出ない
+・幻闘場は難易度が高い割に報酬が見合わない</t>
+        </is>
+      </c>
+      <c r="G919" s="2" t="inlineStr">
+        <is>
+          <t>・ウコムガチャ
+・すり抜け
+・天井交換
+・霊雷アタッカー
+・幻闘場</t>
+        </is>
+      </c>
+      <c r="H919" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I919" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XksHfmROrgc</t>
+        </is>
+      </c>
+      <c r="J919" s="2" t="inlineStr">
+        <is>
+          <t>XksHfmROrgc</t>
+        </is>
+      </c>
+      <c r="K919" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B920" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C920" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】「2人」のシウグナス能力値早見表〜アタッカー重視❗️サポート重視❗️の数値を算出✨</t>
+        </is>
+      </c>
+      <c r="D920" s="2" t="inlineStr">
+        <is>
+          <t>シグナスの能力値早見表を2パターン算出
+アタッカー運用は技2連打で火力がやばい
+サポート運用は軽減92%と優秀</t>
+        </is>
+      </c>
+      <c r="E920" s="2" t="inlineStr">
+        <is>
+          <t>・アタッカー運用の火力が凄い(EF2.5倍〜8130%)
+・サポート運用は軽減92%・攻撃強化2350%と優秀
+・LP自動回復で技2連打も狙える</t>
+        </is>
+      </c>
+      <c r="F920" s="2" t="inlineStr">
+        <is>
+          <t>・サポート運用は地震以外の仲間に代償30%
+・全体/範囲攻撃前提のシチュが少なくメイン狙いには非推奨</t>
+        </is>
+      </c>
+      <c r="G920" s="2" t="inlineStr">
+        <is>
+          <t>・シグナス
+・能力値早見表
+・アタッカー運用
+・サポート運用
+・技2連打</t>
+        </is>
+      </c>
+      <c r="H920" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I920" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1dQg1mSprOQ</t>
+        </is>
+      </c>
+      <c r="J920" s="2" t="inlineStr">
+        <is>
+          <t>1dQg1mSprOQ</t>
+        </is>
+      </c>
+      <c r="K920" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B921" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C921" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第131回アサシンボスの井戸 ~10手編成で ~ランキング100位以内を取ろう👊👊</t>
+        </is>
+      </c>
+      <c r="D921" s="2" t="inlineStr">
+        <is>
+          <t>第131回アサシンボスの井戸に挑戦
+10手編成でランキング100位以内を狙う
+※字幕が不鮮明で詳細不明</t>
+        </is>
+      </c>
+      <c r="E921" s="2" t="inlineStr"/>
+      <c r="F921" s="2" t="inlineStr"/>
+      <c r="G921" s="2" t="inlineStr">
+        <is>
+          <t>・アサシンボスの井戸
+・10手編成
+・ランキング100位以内</t>
+        </is>
+      </c>
+      <c r="H921" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I921" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1kapw2ww-F8</t>
+        </is>
+      </c>
+      <c r="J921" s="2" t="inlineStr">
+        <is>
+          <t>1kapw2ww-F8</t>
+        </is>
+      </c>
+      <c r="K921" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B922" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C922" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】〜バフ屋ランキングツール公開〜ロマサガRSプレーヤー必見‼️これは…神ツールだ‼️置き物バフキャラ検索ツール【制作者：シャビさん】</t>
+        </is>
+      </c>
+      <c r="D922" s="2" t="inlineStr">
+        <is>
+          <t>シャビさん制作「バフ屋ランキング」を紹介
+置き物・行動・ミックスで最適バフキャラ検索
+無償公開の神ツールと絶賛</t>
+        </is>
+      </c>
+      <c r="E922" s="2" t="inlineStr">
+        <is>
+          <t>・見やすさ・デザインが匠の技で神ツール
+・お金を取れるレベルなのに無償公開で感謝しかない
+・体力精神/属性/攻撃回数まで細かく検索でき高難度に有用
+・リセットの忍者演出が最高</t>
+        </is>
+      </c>
+      <c r="F922" s="2" t="inlineStr">
+        <is>
+          <t>・毎回新キャラ解析を入力する管理が大変でシャビさんのリアルが心配</t>
+        </is>
+      </c>
+      <c r="G922" s="2" t="inlineStr">
+        <is>
+          <t>・バフ屋ランキング
+・検索ツール
+・シャビさん
+・置き物バフ
+・データ解析</t>
+        </is>
+      </c>
+      <c r="H922" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I922" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=t1TNmbqz6_Y</t>
+        </is>
+      </c>
+      <c r="J922" s="2" t="inlineStr">
+        <is>
+          <t>t1TNmbqz6_Y</t>
+        </is>
+      </c>
+      <c r="K922" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B923" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C923" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】続！8月の幻闘場をガンガンクリアしていく配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D923" s="2" t="inlineStr">
+        <is>
+          <t>8月の幻闘場を生配信でクリア進行
+弓は良い構築、斧が最難関
+イスカンダールは弱評価で明日のガチャを警戒</t>
+        </is>
+      </c>
+      <c r="E923" s="2" t="inlineStr">
+        <is>
+          <t>・弓は運んでいけそうな良い構築ができた
+・古いクローディア・リズの変則パーティが機能</t>
+        </is>
+      </c>
+      <c r="F923" s="2" t="inlineStr">
+        <is>
+          <t>・斧が最難関で救済キャラが来ないのがロマサガRS
+・イスカンダールはエクストラが1回しか使えず弱い
+・高難度で配信中クリアが進まない</t>
+        </is>
+      </c>
+      <c r="G923" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場
+・生配信
+・弓構築
+・斧攻略
+・イスカンダール評価</t>
+        </is>
+      </c>
+      <c r="H923" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I923" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uiVjNyrmZ5Q</t>
+        </is>
+      </c>
+      <c r="J923" s="2" t="inlineStr">
+        <is>
+          <t>uiVjNyrmZ5Q</t>
+        </is>
+      </c>
+      <c r="K923" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:54Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K923"/>
+  <dimension ref="A1:K943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -61037,6 +61037,1298 @@
         </is>
       </c>
     </row>
+    <row r="924">
+      <c r="A924" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B924" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C924" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「引くべき」最強のダメブロ副産物コッペパン&amp;全体範囲の鬼と化したアレツ→ターミン編ガチャ完結編!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D924" s="2" t="inlineStr">
+        <is>
+          <t>ターミン編ガチャの副産物コッペパンとアレツを性能解説
+コッペパンはダメブロ・代償80%ばらまきの最強級で総合A
+アレツは火力型だが総合C、仙台ありなら確保推奨</t>
+        </is>
+      </c>
+      <c r="E924" s="2" t="inlineStr">
+        <is>
+          <t>・コッペパンはダメブロ更新+代償80%で最強級の副産物
+・コッペパン高難度評価は特攻SS・総合A
+・コッペパンはガナディフェンス50%で汎用性高い
+・アレツは範囲全体連打と単体ぶち抜きが優秀</t>
+        </is>
+      </c>
+      <c r="F924" s="2" t="inlineStr">
+        <is>
+          <t>・アレツのサポートはウィークヒート200%のみで薄い
+・アレツの火力数値は1500%程度でいまいち
+・コッペパンは自己回復スタイルと相性が悪い</t>
+        </is>
+      </c>
+      <c r="G924" s="2" t="inlineStr">
+        <is>
+          <t>・ターミン編ガチャ
+・コッペパン性能
+・アレツ性能
+・ダメブロ
+・副産物</t>
+        </is>
+      </c>
+      <c r="H924" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I924" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4YdO95vpBYY</t>
+        </is>
+      </c>
+      <c r="J924" s="2" t="inlineStr">
+        <is>
+          <t>4YdO95vpBYY</t>
+        </is>
+      </c>
+      <c r="K924" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B925" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C925" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「超進化が鍵」レイド速報→シムメシュ2分台!!こよハラ継続!?いや装備を駆使して800億満額目指せ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D925" s="2" t="inlineStr">
+        <is>
+          <t>シムメシュレイドの速報攻略、2分台で800億満額を狙う
+ビクトルありで2分台前半が世界記録級、なしでも2分30秒台
+佐賀県Tシャツ超進化でBP+3のぶっ壊れ装備に</t>
+        </is>
+      </c>
+      <c r="E925" s="2" t="inlineStr">
+        <is>
+          <t>・シムメシュは3分あれば色んな編成で800億満額取れる
+・佐賀県Tシャツ超進化はBP+3のぶっ壊れ装備
+・全滅編成も開発できそうで簡単</t>
+        </is>
+      </c>
+      <c r="F925" s="2" t="inlineStr"/>
+      <c r="G925" s="2" t="inlineStr">
+        <is>
+          <t>・シムメシュレイド
+・800億満額
+・タイム短縮
+・佐賀県Tシャツ超進化</t>
+        </is>
+      </c>
+      <c r="H925" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I925" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hehMTvZXPPg</t>
+        </is>
+      </c>
+      <c r="J925" s="2" t="inlineStr">
+        <is>
+          <t>hehMTvZXPPg</t>
+        </is>
+      </c>
+      <c r="K925" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B926" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C926" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】引くべし「最強継承」を持つ新ターミン・ネシハマルカー!!先代との違いと運用立ち回りを徹底解剖&amp;解説　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D926" s="2" t="inlineStr">
+        <is>
+          <t>新ターミン・ネシハマルカーの性能を先代と比較し徹底解説
+継承術と確率追撃で汎用性が高く総合評価S、引くべき
+カウンター・回復・デバフは失い純粋強化型に変化</t>
+        </is>
+      </c>
+      <c r="E926" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンは継承持ちで汎用SS・総合S
+・冷編成で最大95%軽減と超強力な防御
+・リキャスト回しで高い瞬発火力を出せる
+・確率向上で平均値でも十分通用する</t>
+        </is>
+      </c>
+      <c r="F926" s="2" t="inlineStr">
+        <is>
+          <t>・火力数値900%とバフ系統は高くない
+・カウンター・回復・デバフを失った
+・個人火力はぶれる</t>
+        </is>
+      </c>
+      <c r="G926" s="2" t="inlineStr">
+        <is>
+          <t>・新ターミン性能
+・継承術
+・確率追撃
+・冷編成軽減95%
+・総合評価S</t>
+        </is>
+      </c>
+      <c r="H926" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I926" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yZgtGmJOjQQ</t>
+        </is>
+      </c>
+      <c r="J926" s="2" t="inlineStr">
+        <is>
+          <t>yZgtGmJOjQQ</t>
+        </is>
+      </c>
+      <c r="K926" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B927" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C927" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始309日目記録　一歩　日々を重ねていく</t>
+        </is>
+      </c>
+      <c r="D927" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣プレイ309日目の進捗を記録・報告
+上杉家の新武将2体を確保、大将不足を課題に強化中
+島左近など新武将評価と今後の目標を語る</t>
+        </is>
+      </c>
+      <c r="E927" s="2" t="inlineStr">
+        <is>
+          <t>・上杉家の新武将2体を両方確保できて強化が進んだ
+・島左近は攻城戦向きで攻撃低下持ちが優秀
+・レベル上げで歩数が増えモチベが上がった</t>
+        </is>
+      </c>
+      <c r="F927" s="2" t="inlineStr">
+        <is>
+          <t>・上杉家はメイン大将が剣心しかおらず苦しい
+・軍団リーグは編成が悪く不甲斐ない結果
+・金銭不足で武将育成が滞りがち</t>
+        </is>
+      </c>
+      <c r="G927" s="2" t="inlineStr">
+        <is>
+          <t>・信長の野望出陣
+・309日目記録
+・上杉家強化
+・島左近評価
+・今後の目標</t>
+        </is>
+      </c>
+      <c r="H927" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I927" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=I9E9kjN2BuM</t>
+        </is>
+      </c>
+      <c r="J927" s="2" t="inlineStr">
+        <is>
+          <t>I9E9kjN2BuM</t>
+        </is>
+      </c>
+      <c r="K927" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B928" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C928" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　制圧戦序盤戦！超絶！シムメシュ攻略　満額800億に挑む！ヴィクトールなし編成</t>
+        </is>
+      </c>
+      <c r="D928" s="2" t="inlineStr">
+        <is>
+          <t>ヴィクトールなし編成でシムメシュ800億満額に挑戦
+AJ・コッペパン・雪だるま編成で2分37秒で満額達成
+熱属性無効と剛体70が攻略の注意点</t>
+        </is>
+      </c>
+      <c r="E928" s="2" t="inlineStr">
+        <is>
+          <t>・ヴィクトールなしでも800億満額を達成できた
+・コッペパンの技3がかなり有効
+・育成すれば4連携でさらに安定しそう</t>
+        </is>
+      </c>
+      <c r="F928" s="2" t="inlineStr">
+        <is>
+          <t>・熱属性は完全ダメージ無効で通らない
+・剛体70で威力が低いときつい
+・雪だるまのOD暴発でタイムが遅延する</t>
+        </is>
+      </c>
+      <c r="G928" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦シムメシュ
+・800億満額
+・ヴィクトールなし編成
+・熱属性無効
+・剛体70</t>
+        </is>
+      </c>
+      <c r="H928" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I928" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LAoYg6644OU</t>
+        </is>
+      </c>
+      <c r="J928" s="2" t="inlineStr">
+        <is>
+          <t>LAoYg6644OU</t>
+        </is>
+      </c>
+      <c r="K928" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B929" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C929" s="2" t="inlineStr">
+        <is>
+          <t>【戦国無双4DX】　人生初めての無双ゲーム　やって行こう！【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D929" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS佐賀県コラボの制圧戦とWガチャを生配信(※タイトルは戦国無双だが内容はRS)
+ノアは天品・排水持ちで確保確定、コッペパンで気絶レイド短縮を狙う
+ターミン・コッペパン狙いでガチャ、制圧戦レイドを周回</t>
+        </is>
+      </c>
+      <c r="E929" s="2" t="inlineStr">
+        <is>
+          <t>・ノアは天品・排水持ちでやっと水が使える良キャラ
+・コッペパンは気絶でレイドを早く終わらせられる
+・クリムゾンサンフレアが連達で威力大幅アップ
+・制圧戦がお盆に来てありがたい</t>
+        </is>
+      </c>
+      <c r="F929" s="2" t="inlineStr">
+        <is>
+          <t>・シムメシュは前スタイルがないと防具超進化できず微妙
+・アレツ500億はダメージ供給が難しめ</t>
+        </is>
+      </c>
+      <c r="G929" s="2" t="inlineStr">
+        <is>
+          <t>・佐賀県コラボ
+・制圧戦
+・Wガチャ
+・ノア確保
+・コッペパン気絶戦法</t>
+        </is>
+      </c>
+      <c r="H929" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I929" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=b7oPfvi_noE</t>
+        </is>
+      </c>
+      <c r="J929" s="2" t="inlineStr">
+        <is>
+          <t>b7oPfvi_noE</t>
+        </is>
+      </c>
+      <c r="K929" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B930" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C930" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】ガシャも来る！？SDガンダム外伝Ⅱの正式な予告が来たから確認しよう 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D930" s="2" t="inlineStr">
+        <is>
+          <t>SDガンダム外伝2イベント「伝説の巨人」の正式予告を確認
+8/13開催でSSR3体、ネモがSSR格でいい扱い
+ガチャは13日実装、パスで外伝アニメも視聴可</t>
+        </is>
+      </c>
+      <c r="E930" s="2" t="inlineStr">
+        <is>
+          <t>・フルアーマーナイトガンダムは支援回数が増えるいいタイプ
+・ネモがSSRでいい扱いを受けている
+・パスでSDガンダム外伝アニメが見られてありがたい</t>
+        </is>
+      </c>
+      <c r="F930" s="2" t="inlineStr">
+        <is>
+          <t>・サイコゴーレム・武踏はチャンスステップが増えず残念
+・巨人・武踏は武装少なめで射程も短そう
+・サポーターは倍率低くあまり使わない</t>
+        </is>
+      </c>
+      <c r="G930" s="2" t="inlineStr">
+        <is>
+          <t>・SDガンダム外伝2
+・イベント予告
+・SSR3体
+・ピックアップガチャ
+・外伝アニメ</t>
+        </is>
+      </c>
+      <c r="H930" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I930" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FN8hQ4QCfZc</t>
+        </is>
+      </c>
+      <c r="J930" s="2" t="inlineStr">
+        <is>
+          <t>FN8hQ4QCfZc</t>
+        </is>
+      </c>
+      <c r="K930" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B931" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C931" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】天国から地獄に落ちたガチャ『Romancing祭 ターミン・ネシハマルカー編＆シムメシュ編』【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D931" s="2" t="inlineStr">
+        <is>
+          <t>ロマンシングフェスのターミン編とシムメシュ編ガチャを実況
+ターミンは1発目で当てたがシムメシュ編は大爆死
+SS排出率も下振れしコンプ不可能な引きに</t>
+        </is>
+      </c>
+      <c r="E931" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンをピック確定1発目で早々に確保できた
+・ピック確定システムはありがたい</t>
+        </is>
+      </c>
+      <c r="F931" s="2" t="inlineStr">
+        <is>
+          <t>・シムメシュ編はSS割合が下振れしてひどい引き
+・天井まで回してもコンプできない可能性
+・追い課金する気になれないほどの爆死</t>
+        </is>
+      </c>
+      <c r="G931" s="2" t="inlineStr">
+        <is>
+          <t>・ロマンシングフェス
+・ターミン編ガチャ
+・シムメシュ編ガチャ
+・佐賀県コラボ
+・大爆死</t>
+        </is>
+      </c>
+      <c r="H931" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I931" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MAAUsm8_bHw</t>
+        </is>
+      </c>
+      <c r="J931" s="2" t="inlineStr">
+        <is>
+          <t>MAAUsm8_bHw</t>
+        </is>
+      </c>
+      <c r="K931" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B932" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C932" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR 騎士ガンダム(ケンタウロス形態) 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D932" s="2" t="inlineStr">
+        <is>
+          <t>SSR騎士ガンダム(ケンタウロス形態)の武装アニメ紹介Shorts
+字幕情報が乏しく詳細な解説はなし</t>
+        </is>
+      </c>
+      <c r="E932" s="2" t="inlineStr"/>
+      <c r="F932" s="2" t="inlineStr"/>
+      <c r="G932" s="2" t="inlineStr">
+        <is>
+          <t>・騎士ガンダム
+・ケンタウロス形態
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H932" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I932" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pFdcg7hKju4</t>
+        </is>
+      </c>
+      <c r="J932" s="2" t="inlineStr">
+        <is>
+          <t>pFdcg7hKju4</t>
+        </is>
+      </c>
+      <c r="K932" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B933" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C933" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】唐突！佐賀コラボ四元像★平和を楽しむ６人の性能確認【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D933" s="2" t="inlineStr">
+        <is>
+          <t>佐賀コラボの資源像とターミン編6キャラの性能を確認
+シムメシュは熱アタッカー無人島向き、シャムマベルは完璧サポーター
+ノアは120億出せる好性能、ターミンは試練召喚継承推奨</t>
+        </is>
+      </c>
+      <c r="E933" s="2" t="inlineStr">
+        <is>
+          <t>・シムメシュは熱直接アタッカーで無人島向き
+・シャムマベルは軽減81%まで届く完璧なサポーター
+・ノアは単騎120億出せる高火力
+・アレツは単体52ヒットで威力も良い</t>
+        </is>
+      </c>
+      <c r="F933" s="2" t="inlineStr">
+        <is>
+          <t>・シムメシュはディフェンスアップが少なく要注意
+・シャムマベルは火力が出ない
+・ターミンの猫パンチは威力低くダメージが通りにくい
+・ターミンは試練召喚継承の方が強かった</t>
+        </is>
+      </c>
+      <c r="G933" s="2" t="inlineStr">
+        <is>
+          <t>・佐賀コラボ
+・四元像性能
+・シムメシュ
+・シャムマベル
+・ノア
+・ターミン</t>
+        </is>
+      </c>
+      <c r="H933" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I933" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dXIR-SkUoCo</t>
+        </is>
+      </c>
+      <c r="J933" s="2" t="inlineStr">
+        <is>
+          <t>dXIR-SkUoCo</t>
+        </is>
+      </c>
+      <c r="K933" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B934" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C934" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】雲上のRomancing佐賀Wガチャ😻</t>
+        </is>
+      </c>
+      <c r="D934" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県コラボWガチャを雑談しながら実況・性能確認
+コッペパンが当たり、シムメシュもそこそこ良い
+制圧戦のジュエル・報酬をチェックしつつ周回</t>
+        </is>
+      </c>
+      <c r="E934" s="2" t="inlineStr">
+        <is>
+          <t>・コッペパンが当たりで火力もだいぶ上がる
+・制圧戦は5000ジュエルなど報酬が多い
+・シムメシュはそこそこ良い
+・防具進化は良さそう</t>
+        </is>
+      </c>
+      <c r="F934" s="2" t="inlineStr">
+        <is>
+          <t>・シムメシュは最強という感じはしない
+・メンテ明けでスタイル並びが変わりUIに戸惑い</t>
+        </is>
+      </c>
+      <c r="G934" s="2" t="inlineStr">
+        <is>
+          <t>・佐賀コラボWガチャ
+・制圧戦
+・コッペパン当たり
+・シムメシュ性能
+・生配信</t>
+        </is>
+      </c>
+      <c r="H934" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I934" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XoALN6hbb-Y</t>
+        </is>
+      </c>
+      <c r="J934" s="2" t="inlineStr">
+        <is>
+          <t>XoALN6hbb-Y</t>
+        </is>
+      </c>
+      <c r="K934" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B935" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C935" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】緊急速報！メンテが明けたら佐賀県コラボがやってきた！！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D935" s="2" t="inlineStr">
+        <is>
+          <t>メンテ明けに2年ぶりの佐賀県コラボが突如実装され速報解説
+制圧戦とシムメシュ編・ターミン編のWガチャが登場
+佐賀県Tシャツ等の超進化やログボ等の特典も紹介</t>
+        </is>
+      </c>
+      <c r="E935" s="2" t="inlineStr">
+        <is>
+          <t>・2年ぶりの佐賀県コラボ復活が嬉しい
+・制圧戦はジュエルが大量にもらえてお得
+・ターミンは今でも最前線クラスで強い
+・お盆の好タイミングで来た</t>
+        </is>
+      </c>
+      <c r="F935" s="2" t="inlineStr">
+        <is>
+          <t>・佐賀県コラボが第1弾のみで完結してしまう可能性
+・ガチャ更新ペースが早すぎて感覚が麻痺している</t>
+        </is>
+      </c>
+      <c r="G935" s="2" t="inlineStr">
+        <is>
+          <t>・佐賀県コラボ
+・2年ぶり開催
+・制圧戦
+・Wガチャ
+・佐賀県Tシャツ超進化</t>
+        </is>
+      </c>
+      <c r="H935" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I935" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Dv_7jgF7IM8</t>
+        </is>
+      </c>
+      <c r="J935" s="2" t="inlineStr">
+        <is>
+          <t>Dv_7jgF7IM8</t>
+        </is>
+      </c>
+      <c r="K935" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B936" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C936" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】佐賀県コラボガチャはやはり強いのか！？シムメシュ編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D936" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県コラボ シムメシュ編ガチャのノアの性能をチェック
+ノアは水直接アタッカーで2ターン全体火力に真価を発揮
+極意人雷系で味方全体にエクストラフォースを付与し強力</t>
+        </is>
+      </c>
+      <c r="E936" s="2" t="inlineStr">
+        <is>
+          <t>・ノアは天品持ちで軽も高く優秀なアタッカー
+・極意人雷系で味方全体に等倍フォースを配れる
+・2ターン火力編成なら圧倒的な活躍が期待できる
+・継承で3コ追撃を増やせて更に強力</t>
+        </is>
+      </c>
+      <c r="F936" s="2" t="inlineStr">
+        <is>
+          <t>・エクストラフォース怒涛が1回限りなのが惜しい
+・1ターンの置き物としてはそこまでではない</t>
+        </is>
+      </c>
+      <c r="G936" s="2" t="inlineStr">
+        <is>
+          <t>・シムメシュ編ガチャ
+・ノア性能
+・水アタッカー
+・天品持ち
+・2ターン火力</t>
+        </is>
+      </c>
+      <c r="H936" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I936" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RDlXqQCfn1E</t>
+        </is>
+      </c>
+      <c r="J936" s="2" t="inlineStr">
+        <is>
+          <t>RDlXqQCfn1E</t>
+        </is>
+      </c>
+      <c r="K936" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B937" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C937" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】あの配布スタイルも大活躍？制圧戦の内容把握と難しいと噂のアレツを周回！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D937" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県コラボ制圧戦の内容とアレツレイド周回を解説
+アレツは術オンリー必須で周回ハードルが高い外れ枠
+配布ビンセント活躍、資源像装備の進化素材復刻に注意喚起</t>
+        </is>
+      </c>
+      <c r="E937" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦はジュエル大量で報酬もおいしい
+・配布ビンセントが継承で大活躍する
+・資源像装備をトリプルS進化させると強力</t>
+        </is>
+      </c>
+      <c r="F937" s="2" t="inlineStr">
+        <is>
+          <t>・アレツは術オンリー必須で周回ハードルが高い
+・アレツは編成・装備・育成すべて高難度の外れ枠
+・ボックス報酬はコス限定以外あまり良くない</t>
+        </is>
+      </c>
+      <c r="G937" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦
+・アレツレイド周回
+・術オンリー編成
+・配布ビンセント
+・資源像装備進化</t>
+        </is>
+      </c>
+      <c r="H937" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I937" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=m7UEcGpax-U</t>
+        </is>
+      </c>
+      <c r="J937" s="2" t="inlineStr">
+        <is>
+          <t>m7UEcGpax-U</t>
+        </is>
+      </c>
+      <c r="K937" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B938" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C938" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】隠れた大当たりキャラも存在？ターミン・ネシハマルカー編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D938" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県コラボ ターミン編ガチャのコッペパン等の性能をチェック
+コッペパンは瀕死置き物+ダメブロ要因で隠れた大当たり
+無人島やり込み勢には必須級のサポート性能</t>
+        </is>
+      </c>
+      <c r="E938" s="2" t="inlineStr">
+        <is>
+          <t>・コッペパンは瀕死特大フォースで超優秀な置き物
+・ダメブロ+回避25%を全体にばらまけて強力
+・無人島攻略には必須級で今回一番の当たりまである
+・弱点強撃で敵を継続的に弱体化できる</t>
+        </is>
+      </c>
+      <c r="F938" s="2" t="inlineStr">
+        <is>
+          <t>・ダメブロの代償でHP80%削られ瀕死になる</t>
+        </is>
+      </c>
+      <c r="G938" s="2" t="inlineStr">
+        <is>
+          <t>・ターミン編ガチャ
+・コッペパン性能
+・瀕死置き物
+・ダメブロ要因
+・無人島必須</t>
+        </is>
+      </c>
+      <c r="H938" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I938" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nbL8R0ulzAU</t>
+        </is>
+      </c>
+      <c r="J938" s="2" t="inlineStr">
+        <is>
+          <t>nbL8R0ulzAU</t>
+        </is>
+      </c>
+      <c r="K938" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B939" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C939" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】〜2:26〜レイド：シムメシュ800億ダメージ</t>
+        </is>
+      </c>
+      <c r="D939" s="2" t="inlineStr">
+        <is>
+          <t>シムメシュレイドで800億ダメージを出す周回動画(2分26秒)
+実況なしのプレイ映像中心</t>
+        </is>
+      </c>
+      <c r="E939" s="2" t="inlineStr">
+        <is>
+          <t>・2分26秒でシムメシュ800億を達成できる</t>
+        </is>
+      </c>
+      <c r="F939" s="2" t="inlineStr"/>
+      <c r="G939" s="2" t="inlineStr">
+        <is>
+          <t>・シムメシュレイド
+・800億ダメージ
+・周回タイム
+・プレイ映像</t>
+        </is>
+      </c>
+      <c r="H939" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I939" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zc--f4PJ8Ao</t>
+        </is>
+      </c>
+      <c r="J939" s="2" t="inlineStr">
+        <is>
+          <t>Zc--f4PJ8Ao</t>
+        </is>
+      </c>
+      <c r="K939" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B940" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C940" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】〜3:47秒〜レイド：シムメシュ【800億ダメージ】</t>
+        </is>
+      </c>
+      <c r="D940" s="2" t="inlineStr">
+        <is>
+          <t>シムメシュレイドで800億ダメージを出す周回動画(3分47秒)
+実況なしのプレイ映像中心</t>
+        </is>
+      </c>
+      <c r="E940" s="2" t="inlineStr">
+        <is>
+          <t>・3分47秒でシムメシュ800億を達成できる</t>
+        </is>
+      </c>
+      <c r="F940" s="2" t="inlineStr"/>
+      <c r="G940" s="2" t="inlineStr">
+        <is>
+          <t>・シムメシュレイド
+・800億ダメージ
+・周回タイム
+・プレイ映像</t>
+        </is>
+      </c>
+      <c r="H940" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I940" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dlTXKFp0GK8</t>
+        </is>
+      </c>
+      <c r="J940" s="2" t="inlineStr">
+        <is>
+          <t>dlTXKFp0GK8</t>
+        </is>
+      </c>
+      <c r="K940" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B941" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C941" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】ターミン・ネシハマルカー能力値早見表〜全方位スーパーサポーター兼アタッカー</t>
+        </is>
+      </c>
+      <c r="D941" s="2" t="inlineStr">
+        <is>
+          <t>ターミン・ネシハマルカーの能力値早見表を作成し紹介
+試練召喚継承前提で立ち回りと数値をまとめた
+4属性の永続冷を5人揃えると軽減95%と強力</t>
+        </is>
+      </c>
+      <c r="E941" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンは全方位スーパーサポーター兼アタッカー
+・永続冷を5人揃えると軽減95%とやばい性能
+・火力・軽減・サポートを巻きまくる</t>
+        </is>
+      </c>
+      <c r="F941" s="2" t="inlineStr"/>
+      <c r="G941" s="2" t="inlineStr">
+        <is>
+          <t>・ターミン能力値早見表
+・試練召喚継承
+・確率追撃
+・4属性軽減95%</t>
+        </is>
+      </c>
+      <c r="H941" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I941" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qiDiCO8Epr0</t>
+        </is>
+      </c>
+      <c r="J941" s="2" t="inlineStr">
+        <is>
+          <t>qiDiCO8Epr0</t>
+        </is>
+      </c>
+      <c r="K941" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B942" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C942" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【ガチャ動画】違う。あなたではない。【No.627】</t>
+        </is>
+      </c>
+      <c r="D942" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねるの夏祭りガチャ実況、ピンクパンチとクイーン狙い
+相方はアデル狙いで天井覚悟、2人でわいわい実況
+目当てが出ず「違う、あなたではない」を連発する引き</t>
+        </is>
+      </c>
+      <c r="E942" s="2" t="inlineStr">
+        <is>
+          <t>・新スタイル実装をお祝いするムード</t>
+        </is>
+      </c>
+      <c r="F942" s="2" t="inlineStr">
+        <is>
+          <t>・目当てのピンクパンチやアデルがなかなか出ない</t>
+        </is>
+      </c>
+      <c r="G942" s="2" t="inlineStr">
+        <is>
+          <t>・夏祭りガチャ
+・ピンクパンチ
+・クイーン
+・アデル狙い
+・ガチャ実況</t>
+        </is>
+      </c>
+      <c r="H942" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I942" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dNw6zVBhMIE</t>
+        </is>
+      </c>
+      <c r="J942" s="2" t="inlineStr">
+        <is>
+          <t>dNw6zVBhMIE</t>
+        </is>
+      </c>
+      <c r="K942" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B943" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C943" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】佐賀県ガチャを考察する配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D943" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県コラボガチャを生配信でじっくり考察
+ターミンは万能で強い、コッペパンは無人島勢には引き案件
+コンテンツとキャラの不一致やUIの見づらさに苦言</t>
+        </is>
+      </c>
+      <c r="E943" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンは万能感がありアタッカー・軽減・サポート持ちで強い
+・コッペパンは配信の消壁ダメブロで無人島に引き案件
+・ターミンは多属性パで採用できる汎用性</t>
+        </is>
+      </c>
+      <c r="F943" s="2" t="inlineStr">
+        <is>
+          <t>・コンテンツ(弓要求)とキャラが噛み合っておらず激おこ
+・スタイル説明のUIが小さすぎて見づらい
+・ターミンは確率追撃でレイル下振れの可能性
+・カウンター・HP回復が削られた</t>
+        </is>
+      </c>
+      <c r="G943" s="2" t="inlineStr">
+        <is>
+          <t>・佐賀県ガチャ考察
+・ターミン性能
+・コッペパン
+・無人島
+・UI不満</t>
+        </is>
+      </c>
+      <c r="H943" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I943" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_ej2D5KAx7Q</t>
+        </is>
+      </c>
+      <c r="J943" s="2" t="inlineStr">
+        <is>
+          <t>_ej2D5KAx7Q</t>
+        </is>
+      </c>
+      <c r="K943" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:08:59Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K943"/>
+  <dimension ref="A1:K957"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -62329,6 +62329,906 @@
         </is>
       </c>
     </row>
+    <row r="944">
+      <c r="A944" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B944" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C944" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】最強「カンスト超え!?」50連打40連打突陽アタッカーツバキ&amp;唯一無二のエクストラフォースが自動付与ピンクパンチ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D944" s="2" t="inlineStr">
+        <is>
+          <t>ツバキは術体相手に50/40ヒットをカンスト連発する最強アタッカー
+和体の敵や技3連打には弱く、行動パターン依存で下ぶれ注意
+ピンクパンチは縛れば強いがサポート薄く必須シーンは無し</t>
+        </is>
+      </c>
+      <c r="E944" s="2" t="inlineStr">
+        <is>
+          <t>・ツバキは条件次第で50/40ヒットカンストの最強アタッカー
+・ピンクパンチはエクストラ付与で確実にプラス2の価値</t>
+        </is>
+      </c>
+      <c r="F944" s="2" t="inlineStr">
+        <is>
+          <t>・ツバキは和体の敵では全く使えず下ぶれると激弱
+・ピンクパンチは絶対縛って使うべきシーンが思いつかない
+・ピンクパンチは火力以外のウェポンがない</t>
+        </is>
+      </c>
+      <c r="G944" s="2" t="inlineStr">
+        <is>
+          <t>・ツバキ性能
+・ピンクパンチ
+・カンスト火力
+・術体特攻
+・縛り編成</t>
+        </is>
+      </c>
+      <c r="H944" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I944" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=15dJUHzW-f4</t>
+        </is>
+      </c>
+      <c r="J944" s="2" t="inlineStr">
+        <is>
+          <t>15dJUHzW-f4</t>
+        </is>
+      </c>
+      <c r="K944" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T01:15:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B945" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C945" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】四元像まとめ「転生」着実にパワーアップした超万能サポートシャムマベル&amp;攻防隙がない完璧な武人ノーア&amp;手薄な熱補充!!全体攻撃熱引率シムメシュ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D945" s="2" t="inlineStr">
+        <is>
+          <t>四元像転生3体を考察、シャムマベルは回復以外万能でS評価
+ノーアは無難に強いA、シムメシュは熱全体連打のB評価
+3体とも便利だが尖った強さがなくスルー可能との結論</t>
+        </is>
+      </c>
+      <c r="E945" s="2" t="inlineStr">
+        <is>
+          <t>・シャムマベルは回復以外を万能サポートしエクストラも被りづらい
+・ノーアは優等生型で無難に強い
+・シムメシュは熱全体連打が安定し熱属性では強め</t>
+        </is>
+      </c>
+      <c r="F945" s="2" t="inlineStr">
+        <is>
+          <t>・3体とも便利さから抜け出す強さがなく代わりが多い
+・シムメシュは全体を引き上げる力がなく自ら殴るのみ
+・ノーアは完成が遅い割に最大値が高くない</t>
+        </is>
+      </c>
+      <c r="G945" s="2" t="inlineStr">
+        <is>
+          <t>・四元像転生
+・シャムマベル
+・ノーア
+・シムメシュ
+・総合評価</t>
+        </is>
+      </c>
+      <c r="H945" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I945" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=t8uJ5gX5wEU</t>
+        </is>
+      </c>
+      <c r="J945" s="2" t="inlineStr">
+        <is>
+          <t>t8uJ5gX5wEU</t>
+        </is>
+      </c>
+      <c r="K945" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T01:15:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B946" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C946" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　本日リセマラ開始　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D946" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープを初見リセマラ配信でプレイ
+人が動物化する等の独特なストーリー演出に驚きの反応
+リセマラは簡単、バフキャラと属性5編成が鍵と考察</t>
+        </is>
+      </c>
+      <c r="E946" s="2" t="inlineStr">
+        <is>
+          <t>・リセマラが簡単だった
+・ストーリーや演出が面白く初見でも楽しめた</t>
+        </is>
+      </c>
+      <c r="F946" s="2" t="inlineStr">
+        <is>
+          <t>・世界観がいきなり動物化するなど意味が分かりにくい</t>
+        </is>
+      </c>
+      <c r="G946" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝
+・スターリープ
+・リセマラ
+・初見プレイ
+・属性編成</t>
+        </is>
+      </c>
+      <c r="H946" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I946" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=P6W_q-MvwPA</t>
+        </is>
+      </c>
+      <c r="J946" s="2" t="inlineStr">
+        <is>
+          <t>P6W_q-MvwPA</t>
+        </is>
+      </c>
+      <c r="K946" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T01:15:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B947" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C947" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　制圧戦第二弾　アレツ　満額500億に挑戦！</t>
+        </is>
+      </c>
+      <c r="D947" s="2" t="inlineStr">
+        <is>
+          <t>制圧戦第二弾アレツ満額500億に2編成で挑戦
+アレツは術で防御弱化するため術主体の構成が必須
+無料配布ビンセント採用の2編成目で3分16秒に短縮</t>
+        </is>
+      </c>
+      <c r="E947" s="2" t="inlineStr">
+        <is>
+          <t>・無料配布ビンセントでもしっかり火力が出て活躍
+・サラやエスパーギャルが圧倒的に火力を稼いだ</t>
+        </is>
+      </c>
+      <c r="F947" s="2" t="inlineStr">
+        <is>
+          <t>・アレツは技で防御が上がるギミックが厄介で厳しい戦い
+・攻撃回数が長く戦闘が長引く</t>
+        </is>
+      </c>
+      <c r="G947" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦アレツ
+・満額500億
+・術主体編成
+・無料配布ビンセント
+・タイム短縮</t>
+        </is>
+      </c>
+      <c r="H947" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I947" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qV7AB-KKvfI</t>
+        </is>
+      </c>
+      <c r="J947" s="2" t="inlineStr">
+        <is>
+          <t>qV7AB-KKvfI</t>
+        </is>
+      </c>
+      <c r="K947" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T01:15:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B948" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C948" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】URモンスターブラックドラゴン 武装アニメ  ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D948" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルURブラックドラゴンの武装アニメ紹介
+セリフ入りの短い武装演出ショート動画
+性能考察ではなく演出を見せるコンテンツ</t>
+        </is>
+      </c>
+      <c r="E948" s="2" t="inlineStr"/>
+      <c r="F948" s="2" t="inlineStr"/>
+      <c r="G948" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ブラックドラゴン
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H948" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I948" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8z8N1PamqEU</t>
+        </is>
+      </c>
+      <c r="J948" s="2" t="inlineStr">
+        <is>
+          <t>8z8N1PamqEU</t>
+        </is>
+      </c>
+      <c r="K948" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T01:15:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B949" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C949" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】UR劉備ユニコーンガンダム 武装アニメ  ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D949" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルUR劉備ユニコーンガンダムの武装アニメ紹介
+セリフ入りの短い武装演出ショート動画
+性能考察ではなく演出を見せるコンテンツ</t>
+        </is>
+      </c>
+      <c r="E949" s="2" t="inlineStr"/>
+      <c r="F949" s="2" t="inlineStr"/>
+      <c r="G949" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・劉備ユニコーン
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H949" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I949" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C1uHd06HJWM</t>
+        </is>
+      </c>
+      <c r="J949" s="2" t="inlineStr">
+        <is>
+          <t>C1uHd06HJWM</t>
+        </is>
+      </c>
+      <c r="K949" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T01:15:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B950" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C950" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】わりぃやっぱ強ぇわ・・４大ガチャランキング引くべき優先順位考察【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D950" s="2" t="inlineStr">
+        <is>
+          <t>佐賀コラボ4大ガチャの引くべき優先順位を考察
+1位はターミン、冷属性編成で軽減95%超の環境最強クラス
+シャムマベル・ノーア・ツバキも実戦で強力と評価</t>
+        </is>
+      </c>
+      <c r="E950" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンは冷属性編成で軽減95%超の環境最強クラス
+・シャムマベルは超高級技マシンで器用万能
+・ツバキは想像より火力が出て強い
+・ノーアは超火力にコンバートし強力</t>
+        </is>
+      </c>
+      <c r="F950" s="2" t="inlineStr">
+        <is>
+          <t>・ボーデルは今すぐ活躍する性能ではない
+・ピンクパンチは自己完結せず使い方が浮かばない
+・ツバキは汎用性がそこまで高くなく刺さる所限定</t>
+        </is>
+      </c>
+      <c r="G950" s="2" t="inlineStr">
+        <is>
+          <t>・佐賀コラボ
+・ガチャ優先度
+・ターミン
+・冷属性軽減
+・キャラ考察</t>
+        </is>
+      </c>
+      <c r="H950" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I950" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DU1xkfWKUag</t>
+        </is>
+      </c>
+      <c r="J950" s="2" t="inlineStr">
+        <is>
+          <t>DU1xkfWKUag</t>
+        </is>
+      </c>
+      <c r="K950" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T01:15:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B951" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C951" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ガチャ即斬（引く！！）約140連！守りたい四元像の笑顔【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D951" s="2" t="inlineStr">
+        <is>
+          <t>佐賀コラボガチャを約140連引くガチャ配信
+6人中4人を確保、天井前まで到達し好結果
+無償石が潤沢でコッペパンやターミンを狙う</t>
+        </is>
+      </c>
+      <c r="E951" s="2" t="inlineStr">
+        <is>
+          <t>・福引1等が当たり無償石が潤沢で助かった
+・6人中4人を確保でき天井前まで到達
+・コッペパンが使える気がすると好感触</t>
+        </is>
+      </c>
+      <c r="F951" s="2" t="inlineStr">
+        <is>
+          <t>・クロス(すり抜け)が最近全く出ず呪われている状態
+・天井前が遠く引き切るのがきつい</t>
+        </is>
+      </c>
+      <c r="G951" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ配信
+・140連
+・佐賀コラボ
+・無償石
+・キャラ確保</t>
+        </is>
+      </c>
+      <c r="H951" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I951" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SmWri3UxwYU</t>
+        </is>
+      </c>
+      <c r="J951" s="2" t="inlineStr">
+        <is>
+          <t>SmWri3UxwYU</t>
+        </is>
+      </c>
+      <c r="K951" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T01:15:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B952" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C952" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】文句なしのSSS判定有！最新キャラランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D952" s="2" t="inlineStr">
+        <is>
+          <t>最新キャラランキングでコッペパンとターミンがトリプルS
+コッペパンは無人島特攻で唯一性が高く環境支配級
+ノア・アレツ・シムメシュ・シャムマベルはS評価</t>
+        </is>
+      </c>
+      <c r="E952" s="2" t="inlineStr">
+        <is>
+          <t>・コッペパンは無人島特攻で唯一性が高く環境支配ポテンシャル
+・ターミンは冷編成で強力かつ便利で使われ続ける
+・シャムマベルは器用万能で超優秀な継承技持ち
+・ツバキは想像以上に火力が伸びた</t>
+        </is>
+      </c>
+      <c r="F952" s="2" t="inlineStr">
+        <is>
+          <t>・ノアは軽減率が0で防御性能はない
+・シムメシュはエクストラフォース全体不要がないのが惜しい
+・アレツは瞬間火力が焦るほどではない</t>
+        </is>
+      </c>
+      <c r="G952" s="2" t="inlineStr">
+        <is>
+          <t>・キャラランキング
+・コッペパン
+・ターミン
+・無人島特攻
+・SSS評価</t>
+        </is>
+      </c>
+      <c r="H952" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I952" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bF0S4TxPddI</t>
+        </is>
+      </c>
+      <c r="J952" s="2" t="inlineStr">
+        <is>
+          <t>bF0S4TxPddI</t>
+        </is>
+      </c>
+      <c r="K952" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T01:15:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B953" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C953" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】高評価の神々たちは引くべき！？ウコム&amp;エリスガチャ最終評価ランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D953" s="2" t="inlineStr">
+        <is>
+          <t>ウコム&amp;エリスガチャの終了間近キャラを最終評価
+エリスは要属性の土台になる★3で1番のおすすめ
+ウコム・コーデリアは幻想上ネボルカ攻略に有効</t>
+        </is>
+      </c>
+      <c r="E953" s="2" t="inlineStr">
+        <is>
+          <t>・エリスは要属性を土台から強化でき汎用性が高い★3
+・ウコムは霊雷の全体アタッカーで幻統上に刺さる
+・コーデリアは現環境にマッチしたデバフ性能★2</t>
+        </is>
+      </c>
+      <c r="F953" s="2" t="inlineStr">
+        <is>
+          <t>・霊姫は必須感が薄く術さ3回制限で持久戦は息切れ★1
+・イスカンダールはカウンター系で活躍機会が限られる★1
+・ルージュは引裂編成以外では出番がなさそう</t>
+        </is>
+      </c>
+      <c r="G953" s="2" t="inlineStr">
+        <is>
+          <t>・ウコム
+・エリス
+・最終評価
+・星ランク
+・幻統上攻略</t>
+        </is>
+      </c>
+      <c r="H953" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I953" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4O6wOlUlF8U</t>
+        </is>
+      </c>
+      <c r="J953" s="2" t="inlineStr">
+        <is>
+          <t>4O6wOlUlF8U</t>
+        </is>
+      </c>
+      <c r="K953" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T01:15:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B954" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C954" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】佐賀県コラボガチャは引き得！？シムメシュ&amp;ターミンガチャ性能チェック・キャラランク付け【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D954" s="2" t="inlineStr">
+        <is>
+          <t>佐賀コラボのシムメシュ&amp;ターミンガチャ性能を詳細解説
+ターミンは回復以外何でもこなす万能弓で高評価
+コッペパンは瀕死特化で無人島役として個人的に一番注目</t>
+        </is>
+      </c>
+      <c r="E954" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンはHP回復以外何でもできる万能な弓キャラ
+・シャムマベルは霊編成で軽減95%とカチカチにできる
+・コッペパンは無人島でエースクラスの働きが見込める</t>
+        </is>
+      </c>
+      <c r="F954" s="2" t="inlineStr">
+        <is>
+          <t>・シムメシュはデバフがなく豪体持ちにダメージが通りにくい
+・コッペパンは代償ダメージ80%で通常の高難度は扱いづらい</t>
+        </is>
+      </c>
+      <c r="G954" s="2" t="inlineStr">
+        <is>
+          <t>・佐賀コラボガチャ
+・ターミン
+・シムメシュ
+・コッペパン
+・キャラランク</t>
+        </is>
+      </c>
+      <c r="H954" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I954" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Z5wVHmfO37M</t>
+        </is>
+      </c>
+      <c r="J954" s="2" t="inlineStr">
+        <is>
+          <t>Z5wVHmfO37M</t>
+        </is>
+      </c>
+      <c r="K954" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T01:15:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B955" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C955" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】ターミン・ネシハマルカー継承比較【四元召喚佐賀 🆚 四元召喚】</t>
+        </is>
+      </c>
+      <c r="D955" s="2" t="inlineStr">
+        <is>
+          <t>ターミンの資源召喚差を斧ターミンに継承した性能を比較
+今回版は地震火力が高く全体7ヒットで使い勝手が向上
+移戸勢はもう少しダメージが欲しい時に狙う価値あり</t>
+        </is>
+      </c>
+      <c r="E955" s="2" t="inlineStr">
+        <is>
+          <t>・今回の資源召喚差は地震火力が高くエクストラも上乗せ
+・全体7ヒット攻撃が打てて敵多数の場面で便利
+・移戸勢はダメージが欲しい時に取った方が良さげ</t>
+        </is>
+      </c>
+      <c r="F955" s="2" t="inlineStr">
+        <is>
+          <t>・味方全体への火力サポート量はわずかしか上回らない</t>
+        </is>
+      </c>
+      <c r="G955" s="2" t="inlineStr">
+        <is>
+          <t>・ターミン継承
+・資源召喚差
+・斧ターミン
+・移戸
+・継承比較</t>
+        </is>
+      </c>
+      <c r="H955" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I955" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dSnP1zZfpbI</t>
+        </is>
+      </c>
+      <c r="J955" s="2" t="inlineStr">
+        <is>
+          <t>dSnP1zZfpbI</t>
+        </is>
+      </c>
+      <c r="K955" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T01:15:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B956" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C956" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「ターミン 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D956" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭ターミン編のスタイル3体を考察&amp;ランク付け
+ターミンは属性別サポートのオールラウンダーでA評価
+アレツは丁寧に弱く設定されC評価、コッペパンは無人島で注目</t>
+        </is>
+      </c>
+      <c r="E956" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンは高確率追撃と属性別サポートで弱点が少ないA評価
+・コッペパンは無人島で今後活躍する唯一性のある性能</t>
+        </is>
+      </c>
+      <c r="F956" s="2" t="inlineStr">
+        <is>
+          <t>・アレツは周回も長期戦も使いにくく丁寧に弱く設定されC評価
+・コッペパンは代償80%で通常の高難度では扱いづらい</t>
+        </is>
+      </c>
+      <c r="G956" s="2" t="inlineStr">
+        <is>
+          <t>・Romancing祭
+・ターミン
+・コッペパン
+・アレツ
+・ランク付け</t>
+        </is>
+      </c>
+      <c r="H956" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I956" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hv_Aqb6snOg</t>
+        </is>
+      </c>
+      <c r="J956" s="2" t="inlineStr">
+        <is>
+          <t>hv_Aqb6snOg</t>
+        </is>
+      </c>
+      <c r="K956" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T01:15:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B957" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C957" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】佐賀県コラボ 制圧戦 -シャムマベル- とりあえずの最速2:21編＆完全自由枠1で3:04周回編成の紹介【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D957" s="2" t="inlineStr">
+        <is>
+          <t>佐賀コラボ制圧戦シャムマベルの攻略編成を解説
+技で攻撃するほどダメージが上がるギミックが特徴
+最速2分21秒編成と完全自由枠1の3分04秒編成を紹介</t>
+        </is>
+      </c>
+      <c r="E957" s="2" t="inlineStr">
+        <is>
+          <t>・技で攻撃するほど技術両方のダメージが上がる仕様
+・満額700億は成長判定ボーナスがあり目指す価値あり</t>
+        </is>
+      </c>
+      <c r="F957" s="2" t="inlineStr">
+        <is>
+          <t>・術で攻撃するとダメージが減り全体防御70も厄介
+・和力が低いとバフを盛らない限りダメージを盛れない</t>
+        </is>
+      </c>
+      <c r="G957" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦シャムマベル
+・佐賀コラボ
+・最速編成
+・満額700億
+・攻略解説</t>
+        </is>
+      </c>
+      <c r="H957" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I957" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8Ckpnh2SqAs</t>
+        </is>
+      </c>
+      <c r="J957" s="2" t="inlineStr">
+        <is>
+          <t>8Ckpnh2SqAs</t>
+        </is>
+      </c>
+      <c r="K957" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T01:15:26Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K957"/>
+  <dimension ref="A1:K969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -63229,6 +63229,760 @@
         </is>
       </c>
     </row>
+    <row r="958">
+      <c r="A958" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B958" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C958" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　本日リセマラ開始　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D958" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープのリセマラ開始配信
+視聴者と雑談しつつロマサガRSノーア育成も話題
+ノーア戦は直接攻撃・バフ要因の編成議論が中心</t>
+        </is>
+      </c>
+      <c r="E958" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトールがいればノーア無人島で700億到達可能
+・リアルクイーン(SS)を引けて盛り上がる</t>
+        </is>
+      </c>
+      <c r="F958" s="2" t="inlineStr">
+        <is>
+          <t>・ノーア戦は関節攻撃キャラ(サイバ等)は火力が出ず不向き
+・ビクトール不在の編成は火力がきつい</t>
+        </is>
+      </c>
+      <c r="G958" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープ
+・リセマラ
+・ロマサガRSノーア
+・編成議論
+・ライブ配信</t>
+        </is>
+      </c>
+      <c r="H958" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I958" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fI8aBZWz1Go</t>
+        </is>
+      </c>
+      <c r="J958" s="2" t="inlineStr">
+        <is>
+          <t>fI8aBZWz1Go</t>
+        </is>
+      </c>
+      <c r="K958" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10T01:07:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B959" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C959" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　初心者挑戦　ミッション制覇に向けてSSRヒスイGET　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D959" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープ2日目の初心者挑戦配信
+ストーリー進行とレベル上げ中心、SSRヒスイ入手
+ゲーム性はオクトラ寄りと評価</t>
+        </is>
+      </c>
+      <c r="E959" s="2" t="inlineStr">
+        <is>
+          <t>・ゲーム性はオクトラ寄りで面白い(神ゲー評)
+・SSRヒスイを入手できた</t>
+        </is>
+      </c>
+      <c r="F959" s="2" t="inlineStr">
+        <is>
+          <t>・討伐ミッションがクリアできずレベル上げが必要
+・SRキャラは育成しない方がいいとの声</t>
+        </is>
+      </c>
+      <c r="G959" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープ
+・初心者ミッション
+・SSRヒスイ
+・レベル上げ
+・ゲーム性</t>
+        </is>
+      </c>
+      <c r="H959" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I959" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nqZSOJr77vU</t>
+        </is>
+      </c>
+      <c r="J959" s="2" t="inlineStr">
+        <is>
+          <t>nqZSOJr77vU</t>
+        </is>
+      </c>
+      <c r="K959" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10T01:07:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B960" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C960" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR コマンドガンダム 武装アニメ  ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D960" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナルのコマンドガンダム武装アニメ紹介Short
+必殺技「卒撃拳」などの演出を収録
+セリフ主体の短尺演出動画</t>
+        </is>
+      </c>
+      <c r="E960" s="2" t="inlineStr"/>
+      <c r="F960" s="2" t="inlineStr"/>
+      <c r="G960" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・コマンドガンダム
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H960" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I960" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HZMP5VQ_JOs</t>
+        </is>
+      </c>
+      <c r="J960" s="2" t="inlineStr">
+        <is>
+          <t>HZMP5VQ_JOs</t>
+        </is>
+      </c>
+      <c r="K960" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10T01:07:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B961" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C961" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR ガンダムエピオン(EW版) 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D961" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナルのガンダムエピオン(EW版)武装アニメ紹介Short
+戦闘ボイスと演出を収録
+セリフ主体の短尺演出動画</t>
+        </is>
+      </c>
+      <c r="E961" s="2" t="inlineStr"/>
+      <c r="F961" s="2" t="inlineStr"/>
+      <c r="G961" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ガンダムエピオン
+・EW版
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H961" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I961" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KeTQW7f-MB0</t>
+        </is>
+      </c>
+      <c r="J961" s="2" t="inlineStr">
+        <is>
+          <t>KeTQW7f-MB0</t>
+        </is>
+      </c>
+      <c r="K961" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10T01:07:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B962" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C962" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】コッペパンレイド2:50満額実況プレイ【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D962" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRSコッペパンレイドを瀕死編成で満額700億実況
+ビンセント外し等で2:50前後を検証
+別編成も試すが不発、記憶再戦で調整予定</t>
+        </is>
+      </c>
+      <c r="E962" s="2" t="inlineStr">
+        <is>
+          <t>・瀕死系の威力アップ編成で700億満額を達成
+・ビンセントの3回行動が火力に有効</t>
+        </is>
+      </c>
+      <c r="F962" s="2" t="inlineStr">
+        <is>
+          <t>・電子/金軸編成は火力不足で不発
+・2分前半でないとタイム的に物足りない</t>
+        </is>
+      </c>
+      <c r="G962" s="2" t="inlineStr">
+        <is>
+          <t>・コッペパンレイド
+・満額700億
+・瀕死編成
+・ビンセント
+・タイム短縮</t>
+        </is>
+      </c>
+      <c r="H962" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I962" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D-wFqn8ZY68</t>
+        </is>
+      </c>
+      <c r="J962" s="2" t="inlineStr">
+        <is>
+          <t>D-wFqn8ZY68</t>
+        </is>
+      </c>
+      <c r="K962" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10T01:07:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B963" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C963" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新世代レイドキャラベスト５！タイム爆速【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D963" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRSレイドで活躍する新世代キャラ ベスト5を解説
+コッペパン・雪だるま・イシス・マカ等の性能を紹介
+「お前を呪ってみろ」継承レグナントコールが最速トレンド</t>
+        </is>
+      </c>
+      <c r="E963" s="2" t="inlineStr">
+        <is>
+          <t>・コッペパンはエクストラフォース禁止特大でレイド特攻、確保優先度が高い
+・雪だるまはオーバードライブオートで評価が急上昇
+・イシスは1ター目1.5倍を撒けて弱点発生前の隙を補える
+・ビンセントは「お前を呪ってみろ」継承が最速トレンド</t>
+        </is>
+      </c>
+      <c r="F963" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンは評価は高いがベイル/無人島キャラの方が使い勝手が上
+・無限の連打頼みでタイムがブレやすい</t>
+        </is>
+      </c>
+      <c r="G963" s="2" t="inlineStr">
+        <is>
+          <t>・新世代ベスト5
+・コッペパン特攻
+・雪だるま
+・イシス
+・レグナントコール継承</t>
+        </is>
+      </c>
+      <c r="H963" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I963" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pj9nZjkdqhc</t>
+        </is>
+      </c>
+      <c r="J963" s="2" t="inlineStr">
+        <is>
+          <t>pj9nZjkdqhc</t>
+        </is>
+      </c>
+      <c r="K963" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10T01:07:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B964" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C964" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみ軸満額2:38コッペパンレイド実況【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D964" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRSコッペパンレイドをこよみ軸で2:38満額実況
+こよみのターン開始HP回復で禁止状態を維持する仕組みを解説
+フローズンキャンディ継承が必須と紹介</t>
+        </is>
+      </c>
+      <c r="E964" s="2" t="inlineStr">
+        <is>
+          <t>・こよみのHP回復順を活かし代償ダメージで2:38満額を達成
+・フローズンキャンディ継承で700億に届く</t>
+        </is>
+      </c>
+      <c r="F964" s="2" t="inlineStr">
+        <is>
+          <t>・こよみをコッペパンより後ろに置くと成立しない配置制約
+・無限が引けないとタイムが落ちる運要素</t>
+        </is>
+      </c>
+      <c r="G964" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ軸
+・2:38満額
+・禁止状態維持
+・フローズンキャンディ継承
+・無限</t>
+        </is>
+      </c>
+      <c r="H964" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I964" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rn783LvQtjI</t>
+        </is>
+      </c>
+      <c r="J964" s="2" t="inlineStr">
+        <is>
+          <t>rn783LvQtjI</t>
+        </is>
+      </c>
+      <c r="K964" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10T01:07:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B965" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C965" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】確率極大は●●％です！気になっていたターミンの追撃確率が判明しました！！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D965" s="2" t="inlineStr">
+        <is>
+          <t>ターミンネシハマルカの「確率極大」を250周検証
+追撃発動率は約77.4%で75%前後と判明
+平均3種前後が追撃する強力な性能と評価</t>
+        </is>
+      </c>
+      <c r="E965" s="2" t="inlineStr">
+        <is>
+          <t>・確率極大は約75%と高く平均3〜4種が追撃する強力構成
+・資源召喚との組合せで高頻度に多段追撃が可能</t>
+        </is>
+      </c>
+      <c r="F965" s="2" t="inlineStr"/>
+      <c r="G965" s="2" t="inlineStr">
+        <is>
+          <t>・ターミン追撃
+・確率極大
+・250周検証
+・発動率77%
+・資源召喚</t>
+        </is>
+      </c>
+      <c r="H965" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I965" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UzKDUy-Yeso</t>
+        </is>
+      </c>
+      <c r="J965" s="2" t="inlineStr">
+        <is>
+          <t>UzKDUy-Yeso</t>
+        </is>
+      </c>
+      <c r="K965" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10T01:07:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B966" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C966" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第132回 ~教授のペットの井戸 ~バフ屋ランキングツール活用 ~最適キャラ16体❗️厳選パーティ6編成紹介‼️</t>
+        </is>
+      </c>
+      <c r="D966" s="2" t="inlineStr">
+        <is>
+          <t>8/10開始「教授のペットの井戸」の攻略考察動画
+バフ屋ランキングツールで置き物・火力サポートを選定
+活躍16体と厳選6編成を紹介、ターミン・ウコムに注目</t>
+        </is>
+      </c>
+      <c r="E966" s="2" t="inlineStr">
+        <is>
+          <t>・バフ屋ランキングツールは信頼性が高く選定に有用
+・斧ターミン+資源召喚継承の横1列15ヒットが有望</t>
+        </is>
+      </c>
+      <c r="F966" s="2" t="inlineStr">
+        <is>
+          <t>・最新ターミンしはまるかの追撃編成はまず無理筋</t>
+        </is>
+      </c>
+      <c r="G966" s="2" t="inlineStr">
+        <is>
+          <t>・教授のペットの井戸
+・バフ屋ランキングツール
+・ダ属性弱点
+・厳選6編成
+・ターミン継承</t>
+        </is>
+      </c>
+      <c r="H966" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I966" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7DsrlhFaNCs</t>
+        </is>
+      </c>
+      <c r="J966" s="2" t="inlineStr">
+        <is>
+          <t>7DsrlhFaNCs</t>
+        </is>
+      </c>
+      <c r="K966" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10T01:07:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B967" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C967" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【追いガチャ動画】それは突然やってきた・・・！！【No.628】</t>
+        </is>
+      </c>
+      <c r="D967" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県コラボ夏祭りガチャを天井まで追い引きするコラボ配信
+リアルクイーン2体・つき3体など神引き連発
+最終的にアデルを天井交換、ピンクパンチ狙いは継続</t>
+        </is>
+      </c>
+      <c r="E967" s="2" t="inlineStr">
+        <is>
+          <t>・リアルクイーンやつきを複数確保する神引き
+・天井でお目当てのアデルを確保</t>
+        </is>
+      </c>
+      <c r="F967" s="2" t="inlineStr">
+        <is>
+          <t>・ターコはジュエルが尽きお目当てのタコ(ピンクパンチ)は未確保
+・天井まで回して出費がかさむ</t>
+        </is>
+      </c>
+      <c r="G967" s="2" t="inlineStr">
+        <is>
+          <t>・追いガチャ
+・夏祭りガチャ
+・天井
+・リアルクイーン
+・神引き</t>
+        </is>
+      </c>
+      <c r="H967" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I967" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_PkSGXMGTbY</t>
+        </is>
+      </c>
+      <c r="J967" s="2" t="inlineStr">
+        <is>
+          <t>_PkSGXMGTbY</t>
+        </is>
+      </c>
+      <c r="K967" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10T01:07:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B968" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C968" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「シムメシュ 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D968" s="2" t="inlineStr">
+        <is>
+          <t>ロマンシング祭「シムメシュ編」3スタイルの性能考察とランク付け
+シムメシュB、シャムマベルA-、ノーアBと評価
+シャムマベルはデバフ+サポートで汎用性が高いと高評価</t>
+        </is>
+      </c>
+      <c r="E968" s="2" t="inlineStr">
+        <is>
+          <t>・シャムマベルはヒット数分のデバフ/バフと火ダメ軽減81%で汎用性が高くA-
+・シムメシュは打熱属性の全体範囲アタッカーとして採用価値あり</t>
+        </is>
+      </c>
+      <c r="F968" s="2" t="inlineStr">
+        <is>
+          <t>・シムメシュは火ダメ軽減30%と低くサポート要素が乏しくB
+・ノーアはサポート性能が物足りず高難易度向けでなくB</t>
+        </is>
+      </c>
+      <c r="G968" s="2" t="inlineStr">
+        <is>
+          <t>・シムメシュ編
+・スタイル考察
+・シャムマベルA-
+・ノーアB
+・デバフ支援</t>
+        </is>
+      </c>
+      <c r="H968" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I968" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=H3_9-jZAo_4</t>
+        </is>
+      </c>
+      <c r="J968" s="2" t="inlineStr">
+        <is>
+          <t>H3_9-jZAo_4</t>
+        </is>
+      </c>
+      <c r="K968" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10T01:07:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B969" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C969" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】佐賀県コラボ 制圧戦-コッペパン- 満額高速周回編成＆満額自由枠1編成 最速は2:30【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D969" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県コラボ制圧戦コッペパンの満額高速周回編成を解説
+最速2:30の高速編成と満額自由枠1編成を紹介
+コーション/禁止状態の維持や瀕死装備の要点を解説</t>
+        </is>
+      </c>
+      <c r="E969" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンは1個前の方が置き物バフ量が高く採用に好適
+・暦読みを戦闘配置し禁止状態を維持する高速周回が有効</t>
+        </is>
+      </c>
+      <c r="F969" s="2" t="inlineStr">
+        <is>
+          <t>・暦読みをコッペパンより後ろに置くと禁止状態を維持できず不可</t>
+        </is>
+      </c>
+      <c r="G969" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦コッペパン
+・満額700億
+・最速2:30
+・暦読み配置
+・瀕死装備</t>
+        </is>
+      </c>
+      <c r="H969" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I969" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_mqNB_3GSgo</t>
+        </is>
+      </c>
+      <c r="J969" s="2" t="inlineStr">
+        <is>
+          <t>_mqNB_3GSgo</t>
+        </is>
+      </c>
+      <c r="K969" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10T01:07:25Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K969"/>
+  <dimension ref="A1:K981"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -63983,6 +63983,807 @@
         </is>
       </c>
     </row>
+    <row r="970">
+      <c r="A970" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B970" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C970" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「EX2倍超え」雷窟&amp;幻闘で強力な助っ人!!ロマパス→パメラの取扱説明書!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D970" s="2" t="inlineStr">
+        <is>
+          <t>今月のロマパスはパメラ。性能を解説。
+サブアタッカー/サポで高難度B総合C。
+初心者は買い育成、ベテランはスルー推奨。</t>
+        </is>
+      </c>
+      <c r="E970" s="2" t="inlineStr">
+        <is>
+          <t>・エクストラッチが高くバフ次第で意外とダメージが出る
+・ロマパスは優勝ジュエル無償化でライトな課金要素
+・収入が多く損はない
+・初心者には育成・練成素材として有用</t>
+        </is>
+      </c>
+      <c r="F970" s="2" t="inlineStr">
+        <is>
+          <t>・火力補正が低く個人では火力が伸びない構造
+・過去技もしょぼい火力技しかない
+・メインの出番は薄く見所なし
+・総合評価Cで配布性能に戻された
+・ベテランはスルー推奨</t>
+        </is>
+      </c>
+      <c r="G970" s="2" t="inlineStr">
+        <is>
+          <t>・パメラ性能
+・ロマンシングパス
+・サブアタッカー
+・高難度評価C
+・課金判断</t>
+        </is>
+      </c>
+      <c r="H970" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I970" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6n_Jd7ECaEw</t>
+        </is>
+      </c>
+      <c r="J970" s="2" t="inlineStr">
+        <is>
+          <t>6n_Jd7ECaEw</t>
+        </is>
+      </c>
+      <c r="K970" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T01:08:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B971" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C971" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ターミンレイド「こよみテンプレ1分台」VSこよみ無しを救済せよ!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D971" s="2" t="inlineStr">
+        <is>
+          <t>ターミンレイドをこよみ無しで攻略救済。
+暦無しは寝かせつつ火力勝負で3分半。
+ブレは少ないが暦ありとの差は大きい。</t>
+        </is>
+      </c>
+      <c r="E971" s="2" t="inlineStr">
+        <is>
+          <t>・暦無し編成でも3分半で安定しブレが少ない
+・ターミンの追撃確率75%で安定する
+・自動でも満額で安定</t>
+        </is>
+      </c>
+      <c r="F971" s="2" t="inlineStr">
+        <is>
+          <t>・暦読みがないと火力が届きにくい
+・寝かさないとターミンの攻撃が長く4分ほどかかる
+・暦ありとの性能差が大きい</t>
+        </is>
+      </c>
+      <c r="G971" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンレイド
+・こよみ無し救済
+・寝かせ編成
+・火力勝負
+・追撃確率75%</t>
+        </is>
+      </c>
+      <c r="H971" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I971" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A-5fQnYNRpM</t>
+        </is>
+      </c>
+      <c r="J971" s="2" t="inlineStr">
+        <is>
+          <t>A-5fQnYNRpM</t>
+        </is>
+      </c>
+      <c r="K971" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T01:08:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B972" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C972" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「殿堂入り」ターミン編VS夏祭り→12体4ガチャランキング!!最新スタイルの最強を決める比較検討会→2026年8月10日版　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D972" s="2" t="inlineStr">
+        <is>
+          <t>夏祭り〜ターミンの最新12スタイル比較。
+4ガチャランキングで最強を検討。
+撤退ラインはつばキ&amp;アデルまで。</t>
+        </is>
+      </c>
+      <c r="E972" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンは接待級の強さで高確率上ぶれアタッカー
+・アデルはエクストラ3倍超で取り回し良く周回最適
+・つばキは術避け続けば最高峰の突アタッカー
+・ノアはエリス級の安定した高ダメージ
+・サムマベルは回復以外のサポートを完璧に習得</t>
+        </is>
+      </c>
+      <c r="F972" s="2" t="inlineStr">
+        <is>
+          <t>・リアルクイーンは数値が低くネタキャラ寄り
+・シムメシュは全サポが弱く火力サポいまいち
+・シグナスは確率50%の壁で採用しづらい
+・ジニーは刺さらないと活躍しづらい
+・ピンクパンチは代わりが効く</t>
+        </is>
+      </c>
+      <c r="G972" s="2" t="inlineStr">
+        <is>
+          <t>・4ガチャランキング
+・比較検討会
+・ターミン
+・ガチャ厳選
+・撤退ライン</t>
+        </is>
+      </c>
+      <c r="H972" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I972" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BWT6qrNOJ-w</t>
+        </is>
+      </c>
+      <c r="J972" s="2" t="inlineStr">
+        <is>
+          <t>BWT6qrNOJ-w</t>
+        </is>
+      </c>
+      <c r="K972" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T01:08:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B973" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C973" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「買う?買わない??」今月のロマンシングパスはパメラ!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D973" s="2" t="inlineStr">
+        <is>
+          <t>今月のロマンシングパスはパメラの告知。
+買うか買わないかを問うショート。
+(字幕は音楽のみで詳細な音声なし)</t>
+        </is>
+      </c>
+      <c r="E973" s="2" t="inlineStr"/>
+      <c r="F973" s="2" t="inlineStr"/>
+      <c r="G973" s="2" t="inlineStr">
+        <is>
+          <t>・ロマンシングパス
+・パメラ
+・購入判断
+・ショート</t>
+        </is>
+      </c>
+      <c r="H973" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I973" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WkcYSM61fKs</t>
+        </is>
+      </c>
+      <c r="J973" s="2" t="inlineStr">
+        <is>
+          <t>WkcYSM61fKs</t>
+        </is>
+      </c>
+      <c r="K973" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T01:08:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B974" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C974" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　SSR（配布キャラ以外）禁止縛りでストーリーどこまで行けるのか挑戦！（ボスのみ）　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D974" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープをSSR禁止縛りで挑戦。
+配布・SRのみでボス戦を攻略する配信。
+ボスが強くレベル上げで突破。</t>
+        </is>
+      </c>
+      <c r="E974" s="2" t="inlineStr">
+        <is>
+          <t>・配布・SR・108星縛りが楽しい
+・ストーリーがよくできていて面白い
+・キャラがいい味を出している
+・経験値即回復アイテムで育成が楽になる</t>
+        </is>
+      </c>
+      <c r="F974" s="2" t="inlineStr">
+        <is>
+          <t>・ボスが強すぎて何度も敗北した
+・ボスの全開回復がだるい
+・SSR使用不可はきつい</t>
+        </is>
+      </c>
+      <c r="G974" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープ
+・SSR禁止縛り
+・ボス攻略
+・ストーリー
+・経験値回復アイテム</t>
+        </is>
+      </c>
+      <c r="H974" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I974" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=I_w0IwCT1LE</t>
+        </is>
+      </c>
+      <c r="J974" s="2" t="inlineStr">
+        <is>
+          <t>I_w0IwCT1LE</t>
+        </is>
+      </c>
+      <c r="K974" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T01:08:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B975" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C975" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　SSR（配布以外）使用禁止縛りに挑戦　ストーリーどこまでいけるかチャレンジ　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D975" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープをSSR禁止で進行。
+序盤〜中盤をSR・R中心で攻略する配信。
+システムはオクトラ風、ボスは強め。</t>
+        </is>
+      </c>
+      <c r="E975" s="2" t="inlineStr">
+        <is>
+          <t>・ストーリーが明るく良質でギャグもある
+・オクトラに似た良いシステム
+・昔ながらのロープレ感で面白い
+・移動が基本オートで操作が楽</t>
+        </is>
+      </c>
+      <c r="F975" s="2" t="inlineStr">
+        <is>
+          <t>・ボスが強すぎSRとRだけでは無理
+・限定SSRは5連しか引けず渋い
+・横画面はやりづらい</t>
+        </is>
+      </c>
+      <c r="G975" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープ
+・SSR禁止縛り
+・ストーリー進行
+・オクトラ風システム
+・限定ガチャ5連</t>
+        </is>
+      </c>
+      <c r="H975" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I975" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Lz3uhIUEIZA</t>
+        </is>
+      </c>
+      <c r="J975" s="2" t="inlineStr">
+        <is>
+          <t>Lz3uhIUEIZA</t>
+        </is>
+      </c>
+      <c r="K975" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T01:08:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B976" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C976" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】限定連チャン！？8月13日ガシャ予告 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D976" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナル8月13日ガシャ予告紹介。
+ナイトガンダム(限定)と大将軍(恒常)登場。
+投稿者は今回は様子見。</t>
+        </is>
+      </c>
+      <c r="E976" s="2" t="inlineStr">
+        <is>
+          <t>・主役ナイトガンダムがやっと限定実装
+・戦国伝から初のガシャ登場で目玉
+・モンブランが初復刻</t>
+        </is>
+      </c>
+      <c r="F976" s="2" t="inlineStr">
+        <is>
+          <t>・アルトロン200連の直後で回す余裕がなく様子見</t>
+        </is>
+      </c>
+      <c r="G976" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・8月13日ガシャ予告
+・ナイトガンダム
+・限定ユニット
+・SDガンダム</t>
+        </is>
+      </c>
+      <c r="H976" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I976" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VYZ_PGe8BmI</t>
+        </is>
+      </c>
+      <c r="J976" s="2" t="inlineStr">
+        <is>
+          <t>VYZ_PGe8BmI</t>
+        </is>
+      </c>
+      <c r="K976" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T01:08:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B977" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C977" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】限定連チャン！？8月13日ガシャ予告 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D977" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナル8月13日ガシャ予告紹介。
+ナイトガンダム(限定)と大将軍(恒常)登場。
+投稿者は今回は様子見(Short版)。</t>
+        </is>
+      </c>
+      <c r="E977" s="2" t="inlineStr">
+        <is>
+          <t>・主役ナイトガンダムがやっと限定実装
+・戦国伝から初のガシャ登場で目玉
+・モンブランが初復刻</t>
+        </is>
+      </c>
+      <c r="F977" s="2" t="inlineStr">
+        <is>
+          <t>・アルトロン200連の直後で回す余裕がなく様子見</t>
+        </is>
+      </c>
+      <c r="G977" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・8月13日ガシャ予告
+・ナイトガンダム
+・限定ユニット
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H977" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I977" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=drxioviwfqI</t>
+        </is>
+      </c>
+      <c r="J977" s="2" t="inlineStr">
+        <is>
+          <t>drxioviwfqI</t>
+        </is>
+      </c>
+      <c r="K977" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T01:08:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B978" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C978" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】大注目最新版レイドTier表！評価キャラ全34人所持★使用感含め解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D978" s="2" t="inlineStr">
+        <is>
+          <t>レイドで活躍するキャラのTier表を解説。
+魂アビリティ狙いでレイド周回が重要と主張。
+ビクトール・暦読みが殿堂入り。</t>
+        </is>
+      </c>
+      <c r="E978" s="2" t="inlineStr">
+        <is>
+          <t>・魂アビリティは無課金要素で価値が高い良システム
+・トウキ吸収アビリティが最強で推しを強化できる
+・ビクトール・暦読みが頭一つ抜けた殿堂入り
+・雪だるまはODオート解禁で今優秀
+・レイド増加で毎日楽しい</t>
+        </is>
+      </c>
+      <c r="F978" s="2" t="inlineStr">
+        <is>
+          <t>・エクストラフォースは重複せず1.25倍止まり
+・AJは行動回数が多いと足を引っ張る</t>
+        </is>
+      </c>
+      <c r="G978" s="2" t="inlineStr">
+        <is>
+          <t>・レイドTier表
+・魂アビリティ
+・殿堂入り
+・ビクトール
+・最速タイム</t>
+        </is>
+      </c>
+      <c r="H978" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I978" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EmVOZyp65Es</t>
+        </is>
+      </c>
+      <c r="J978" s="2" t="inlineStr">
+        <is>
+          <t>EmVOZyp65Es</t>
+        </is>
+      </c>
+      <c r="K978" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T01:08:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B979" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C979" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】制圧戦激ウマ周回速報！今はここがおすすめだ！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D979" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県コラボ制圧戦の全制圧後周回速報。
+空島ターミン戦が眠り+ExFで激ウマ。
+ビクトール+Sレイ姫+暦読み編成で最速。</t>
+        </is>
+      </c>
+      <c r="E979" s="2" t="inlineStr">
+        <is>
+          <t>・空島ターミン戦は眠りが入りエクストラフォースで超美味しい
+・全制圧でジュエルが一気に増える
+・制圧戦マップの作り込みが素晴らしい
+・ビクトールの価値が非常に高い</t>
+        </is>
+      </c>
+      <c r="F979" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトール未所持だと『ビクハ』で辛い
+・ダメージには門武器・連マ・育成など多くの要素が要求される
+・ビクトールの行動次第で事故ることがある</t>
+        </is>
+      </c>
+      <c r="G979" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦周回
+・全制圧後
+・ターミンでシャマルカ
+・眠り周回
+・ビクトール編成</t>
+        </is>
+      </c>
+      <c r="H979" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I979" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3DRX2YCXl-Y</t>
+        </is>
+      </c>
+      <c r="J979" s="2" t="inlineStr">
+        <is>
+          <t>3DRX2YCXl-Y</t>
+        </is>
+      </c>
+      <c r="K979" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T01:08:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B980" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C980" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】佐賀県コラボに周年級キャラが存在！？最新版確保優先度ランキング【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D980" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県コラボ4ガチャ12スタイルの確保優先度。
+最優先はコっぺパンとターミンでシャマルカ。
+最優先2人が同ガチャで周年級の強さ。</t>
+        </is>
+      </c>
+      <c r="E980" s="2" t="inlineStr">
+        <is>
+          <t>・コっぺパンは唯一性が高く無人島で数年使える最優先
+・ターミンでシャマルカはワクワクする世界と技マシン価値で最優先
+・シグナスはサポート性能が高くカタログスペック最強級
+・シャムマベルは資源像で最も使いやすく冷属性が優秀
+・このガチャは最優先2人が同時で周年級の強さ</t>
+        </is>
+      </c>
+      <c r="F980" s="2" t="inlineStr">
+        <is>
+          <t>・つきはバグと敵を選ぶ点で優先度中に降格
+・アレツは息切れが早く残パなら他に強キャラ多数
+・リアルクイーン/新メシは属性編成専用で優先度低め</t>
+        </is>
+      </c>
+      <c r="G980" s="2" t="inlineStr">
+        <is>
+          <t>・確保優先度ランキング
+・佐賀県コラボ
+・コっぺパン
+・ターミンでシャマルカ
+・唯一性</t>
+        </is>
+      </c>
+      <c r="H980" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I980" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=f9IG0u4BEPI</t>
+        </is>
+      </c>
+      <c r="J980" s="2" t="inlineStr">
+        <is>
+          <t>f9IG0u4BEPI</t>
+        </is>
+      </c>
+      <c r="K980" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T01:08:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B981" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C981" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】佐賀県コラボ 制圧戦 全制圧後オススメの周回場所 完全自由枠5の全滅周回の解説!!【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D981" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県コラボ制圧戦の全制圧後おすすめ周回。
+完全自由枠1のシムメシュ編成4種を紹介。
+全滅周回は成長判定重視で好きなキャラ育成向き。</t>
+        </is>
+      </c>
+      <c r="E981" s="2" t="inlineStr">
+        <is>
+          <t>・魂アビリティ狙いなら自由枠なしで最速周回が最効率
+・完全自由枠1のシムメシュ編成は組みやすい
+・全滅周回は好きなキャラだけ編成できるのがメリット
+・成長判定回数は雑魚マスやフリクエより優秀</t>
+        </is>
+      </c>
+      <c r="F981" s="2" t="inlineStr">
+        <is>
+          <t>・最速はターミンでシムメシュより自由枠1は遅い
+・シムメシュはザ・インで組まないとダメージが通りにくい
+・今は雑魚マスやフリークエストを回る意味は全くない</t>
+        </is>
+      </c>
+      <c r="G981" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦周回
+・全制圧後
+・完全自由枠1
+・シムメシュ編成
+・全滅周回</t>
+        </is>
+      </c>
+      <c r="H981" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I981" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=t04QRKcLexA</t>
+        </is>
+      </c>
+      <c r="J981" s="2" t="inlineStr">
+        <is>
+          <t>t04QRKcLexA</t>
+        </is>
+      </c>
+      <c r="K981" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T01:08:25Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K981"/>
+  <dimension ref="A1:K995"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -64784,6 +64784,902 @@
         </is>
       </c>
     </row>
+    <row r="982">
+      <c r="A982" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B982" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C982" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「最強レイドスタイル」とは!?アタッカー&amp;サポート部門別ランキングと総合MVP発表!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D982" s="2" t="inlineStr">
+        <is>
+          <t>制圧戦一段落で勢力図が変わりレイドスタイルを再評価。
+部門別アタッカー・火力サポートをランク付けしMVP発表。
+上ブレ前提のビクトールが調整込みで頭一つ抜けると総括。</t>
+        </is>
+      </c>
+      <c r="E982" s="2" t="inlineStr">
+        <is>
+          <t>・継承ビクトールは弱点無視でもバフと挙動で出番あり優秀
+・バルテルミーは火力サポートしつつ全体を熱で殴れて強い
+・イシスは立ち上がりエクストラと加速力が唯一無二
+・継承ビンセントは動作を軽くし有効に作用</t>
+        </is>
+      </c>
+      <c r="F982" s="2" t="inlineStr">
+        <is>
+          <t>・ウルピナは実は強いが出番は主に凸のみで限定的
+・熱エレノアはロマンシングパス調整で出番なし
+・旧ネシハマルカーは杖コ追撃なしで意外な使い勝手
+・ミニオン等余分なアタッカーは副産物でも狙わず即撤退</t>
+        </is>
+      </c>
+      <c r="G982" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦
+・レイドスタイルランク
+・アタッカーティア
+・火力サポート
+・MVP発表</t>
+        </is>
+      </c>
+      <c r="H982" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I982" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=i7nTwIs44x4</t>
+        </is>
+      </c>
+      <c r="J982" s="2" t="inlineStr">
+        <is>
+          <t>i7nTwIs44x4</t>
+        </is>
+      </c>
+      <c r="K982" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:09:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B983" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C983" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】佐賀終了!!新キャラ「闇の皇帝」新たな皇帝ダブルガチャを震えて待て!!のガチャ予想　&amp;今月の日程確定　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D983" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県コラボが終了し次のガチャ内容を予想。
+新キャラ「闇の皇帝」の皇帝ダブルガチャを警戒せよと呼びかけ。
+今月の日程確定も合わせて紹介。</t>
+        </is>
+      </c>
+      <c r="E983" s="2" t="inlineStr"/>
+      <c r="F983" s="2" t="inlineStr"/>
+      <c r="G983" s="2" t="inlineStr">
+        <is>
+          <t>・佐賀コラボ終了
+・闇の皇帝
+・皇帝ダブルガチャ
+・今月の日程</t>
+        </is>
+      </c>
+      <c r="H983" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I983" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sTNTzLBTudE</t>
+        </is>
+      </c>
+      <c r="J983" s="2" t="inlineStr">
+        <is>
+          <t>sTNTzLBTudE</t>
+        </is>
+      </c>
+      <c r="K983" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:09:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B984" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C984" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　SSR（配布キャラ以外）禁止縛りでストーリーどこまで行けるのか挑戦！（ボスのみ）　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D984" s="2" t="inlineStr">
+        <is>
+          <t>制圧戦をシム飯シュ育成枠入りで周回しつつ雑談配信。
+ジニー編ガチャを引きコッペパンやノーアを確保。
+記憶再戦を絶賛、無人島の長さには不満も。</t>
+        </is>
+      </c>
+      <c r="E984" s="2" t="inlineStr">
+        <is>
+          <t>・記憶再戦(魂レベル・アビリティ)が周回を楽にして良い
+・ノーアを取ったおかげで無人島をクリアできた
+・コッペパンが最短編成の中心で強い
+・今月は幻想水滸伝が一番面白かった</t>
+        </is>
+      </c>
+      <c r="F984" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトールがいないと周回が遅く羨ましい
+・無人島は7時間かかり長すぎる
+・通常周回が単調で作業になっている
+・ノーアは火力が遅く育成が厄介</t>
+        </is>
+      </c>
+      <c r="G984" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦周回
+・シム飯シュ育成
+・ジニー編ガチャ
+・記憶再戦
+・無人島</t>
+        </is>
+      </c>
+      <c r="H984" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I984" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9rrqlVUX--k</t>
+        </is>
+      </c>
+      <c r="J984" s="2" t="inlineStr">
+        <is>
+          <t>9rrqlVUX--k</t>
+        </is>
+      </c>
+      <c r="K984" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:09:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B985" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C985" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】バーサル騎士は初のパリィ持ち！8月13日のガシャユニット達の性能確認 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D985" s="2" t="inlineStr">
+        <is>
+          <t>8月13日ガシャ実装ユニットの性能を確認。
+限定バーサル騎士は初のパリィ持ちで評価は性能次第。
+三代目大将軍はSDガンダム系強化役として期待。</t>
+        </is>
+      </c>
+      <c r="E985" s="2" t="inlineStr">
+        <is>
+          <t>・バーサル騎士のパリィは発動すれば支援防御消費なく回避で強い
+・大将軍はSDガンダム系を固めると攻防アップで無難に強化
+・バーサル騎士はハイスピードLv2で移動力上がりEX武装発動しやすい</t>
+        </is>
+      </c>
+      <c r="F985" s="2" t="inlineStr">
+        <is>
+          <t>・バーサル騎士はMP消費2で燃費が悪い
+・大将軍はEX武装が射程5なくもったいない
+・サポーターのナイトアムロはエネルギー回復でHPでなく微妙
+・パリィは確率頼みで現時点は評価が難しい</t>
+        </is>
+      </c>
+      <c r="G985" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・バーサル騎士
+・パリィ
+・三代目大将軍
+・ガシャ性能</t>
+        </is>
+      </c>
+      <c r="H985" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I985" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dVIYHo29cOk</t>
+        </is>
+      </c>
+      <c r="J985" s="2" t="inlineStr">
+        <is>
+          <t>dVIYHo29cOk</t>
+        </is>
+      </c>
+      <c r="K985" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:09:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B986" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C986" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SDガンダム系強化！「三代目頑駄無大将軍」の性能確認 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D986" s="2" t="inlineStr">
+        <is>
+          <t>ガシャ実装の三代目ガンダム大将軍の性能を確認。
+SDガンダム系を固めると攻防アップで強化役に。
+射程5がない点は惜しいが今後に期待。</t>
+        </is>
+      </c>
+      <c r="E986" s="2" t="inlineStr">
+        <is>
+          <t>・SDガンダム系で固めると同部隊を攻防アップで強化
+・テンション条件で特殊武装の射程が1伸びる
+・工場ユニットで無難に使える</t>
+        </is>
+      </c>
+      <c r="F986" s="2" t="inlineStr">
+        <is>
+          <t>・EX武装が射程5なくもったいない
+・SDガンダム系がまだ少なく現状は価値が低い</t>
+        </is>
+      </c>
+      <c r="G986" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・三代目大将軍
+・SDガンダム強化
+・支援型ユニット</t>
+        </is>
+      </c>
+      <c r="H986" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I986" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=f6H12gfzPYM</t>
+        </is>
+      </c>
+      <c r="J986" s="2" t="inlineStr">
+        <is>
+          <t>f6H12gfzPYM</t>
+        </is>
+      </c>
+      <c r="K986" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:09:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B987" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C987" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】パリィ！？限定ユニット「バーサル騎士ガンダム」の性能確認 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D987" s="2" t="inlineStr">
+        <is>
+          <t>ガシャ実装の限定バーサル騎士ガンダムを確認。
+初のパリィ持ちで発動すれば支援防御なく回避可能。
+性能次第だが現時点の評価は難しい。</t>
+        </is>
+      </c>
+      <c r="E987" s="2" t="inlineStr">
+        <is>
+          <t>・パリィ発動で支援防御消費なく回避でき強い
+・ハイスピードLv2で移動力上がりEX武装発動しやすい
+・MP上昇でEX武装の燃費をリカバリー</t>
+        </is>
+      </c>
+      <c r="F987" s="2" t="inlineStr">
+        <is>
+          <t>・EX武装MP消費2で燃費が悪い
+・パリィは確率頼みで評価が難しい
+・チャンスステップが1回のみ</t>
+        </is>
+      </c>
+      <c r="G987" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・バーサル騎士
+・パリィ
+・限定ユニット</t>
+        </is>
+      </c>
+      <c r="H987" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I987" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=t1oe6_QfdZU</t>
+        </is>
+      </c>
+      <c r="J987" s="2" t="inlineStr">
+        <is>
+          <t>t1oe6_QfdZU</t>
+        </is>
+      </c>
+      <c r="K987" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:09:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B988" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C988" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】楽園はここだ！ターミンレイド最速1:53秒3編成紹介【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D988" s="2" t="inlineStr">
+        <is>
+          <t>最後のネシハマルカーで眠り即撃破の裏技を紹介。
+コッペパンやアセルス等で1分53秒の最速編成を実演。
+ビクトールの無限次第でタイムが安定すると解説。</t>
+        </is>
+      </c>
+      <c r="E988" s="2" t="inlineStr">
+        <is>
+          <t>・眠りを入れると1回も攻撃されず終わる裏技が強力
+・コッペパン編成で1分53秒の最速を達成
+・アセルスは火力マックスで2分20秒台安定</t>
+        </is>
+      </c>
+      <c r="F988" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトールの無限が入らないと800億に届かず不安定
+・アセルスは立ち上がりが遅くスタートが遅い
+・端末がカクついてタイムがぶれる</t>
+        </is>
+      </c>
+      <c r="G988" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンレイド
+・眠り編成
+・コッペパン
+・アセルス
+・最速タイム</t>
+        </is>
+      </c>
+      <c r="H988" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I988" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ooG6DwDeNyY</t>
+        </is>
+      </c>
+      <c r="J988" s="2" t="inlineStr">
+        <is>
+          <t>ooG6DwDeNyY</t>
+        </is>
+      </c>
+      <c r="K988" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:09:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B989" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C989" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】制圧効率PT教えて！😻</t>
+        </is>
+      </c>
+      <c r="D989" s="2" t="inlineStr">
+        <is>
+          <t>久々の配信で制圧戦の効率PTを視聴者に教わりながら構築。
+眠り＋防御弱体でネシハマルカー800億を狙う編成を試行。
+コッペパンのおかげで復刻無人島もオート放置が可能に。</t>
+        </is>
+      </c>
+      <c r="E989" s="2" t="inlineStr">
+        <is>
+          <t>・コッペパンのおかげで無人島の道が開け45層まで到達
+・コッペパンでダメブロ編成がオート放置できて楽
+・ファスト武器装備でコッペパンが安定して先制ダムド</t>
+        </is>
+      </c>
+      <c r="F989" s="2" t="inlineStr">
+        <is>
+          <t>・排水がどうしても覚えられず苦戦
+・手動8時間周回が辛かった
+・ターミンはレイドでしか使わず微妙
+・女帝より白バラ回復との兼ね合いが難しい</t>
+        </is>
+      </c>
+      <c r="G989" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦効率PT
+・眠り編成
+・コッペパン
+・復刻無人島
+・オート放置</t>
+        </is>
+      </c>
+      <c r="H989" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I989" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dpDaSr9PUX0</t>
+        </is>
+      </c>
+      <c r="J989" s="2" t="inlineStr">
+        <is>
+          <t>dpDaSr9PUX0</t>
+        </is>
+      </c>
+      <c r="K989" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:09:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B990" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C990" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】大本命ガチャが来ます！次はあの大人気女性キャラが濃厚！？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D990" s="2" t="inlineStr">
+        <is>
+          <t>8月14日の次ガチャ内容を恒例の予想動画で考察。
+民サガプロジェクト上位の最終皇帝(女)・エレン・ジョー説を推す。
+3連続ダブルの後なので次はシングルガチャと予想。</t>
+        </is>
+      </c>
+      <c r="E990" s="2" t="inlineStr">
+        <is>
+          <t>・マンホール投票済みの人気キャラで実装は大いにありそう
+・サガのオリジナルキャラは魅力的で思い入れがある</t>
+        </is>
+      </c>
+      <c r="F990" s="2" t="inlineStr">
+        <is>
+          <t>・前回の肝試し予想は佐賀コラボ急遽で外れて残念
+・スケジュール急遽で実装が間に合うか不安</t>
+        </is>
+      </c>
+      <c r="G990" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ予想
+・民サガプロジェクト
+・最終皇帝女
+・シングル予想
+・答え合わせ</t>
+        </is>
+      </c>
+      <c r="H990" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I990" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1DcOl-xUmN8</t>
+        </is>
+      </c>
+      <c r="J990" s="2" t="inlineStr">
+        <is>
+          <t>1DcOl-xUmN8</t>
+        </is>
+      </c>
+      <c r="K990" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:09:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B991" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C991" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】瀕死と眠りで2分10秒台周回へ！制圧戦ターミンネシハマルカー800億オート編成紹介！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D991" s="2" t="inlineStr">
+        <is>
+          <t>瀕死と眠りを組み合わせ2分10秒台の周回を目指す。
+制圧戦ターミン・ネシハマルカー800億オート編成を紹介。
+状態異常軸で時短する立ち回りを解説。</t>
+        </is>
+      </c>
+      <c r="E991" s="2" t="inlineStr">
+        <is>
+          <t>・瀕死と眠りの組み合わせで2分10秒台まで時短
+・800億をオートで周回可能</t>
+        </is>
+      </c>
+      <c r="F991" s="2" t="inlineStr"/>
+      <c r="G991" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦ターミン
+・瀕死と眠り
+・2分10秒台周回
+・800億オート編成</t>
+        </is>
+      </c>
+      <c r="H991" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I991" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0KoR1Ufgk4g</t>
+        </is>
+      </c>
+      <c r="J991" s="2" t="inlineStr">
+        <is>
+          <t>0KoR1Ufgk4g</t>
+        </is>
+      </c>
+      <c r="K991" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:09:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B992" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C992" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】weak無しでもあの状態異常が効く！制圧戦ターミン・ネシハマルカー800億オート編成紹介！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D992" s="2" t="inlineStr">
+        <is>
+          <t>weak無しでも効く状態異常を使う制圧戦ターミン編成を紹介。
+ネシハマルカー800億をオートで攻略する構成を解説。
+弱点を突けなくても状態異常軸で火力を通す。</t>
+        </is>
+      </c>
+      <c r="E992" s="2" t="inlineStr">
+        <is>
+          <t>・weak無しでも状態異常が効き弱点なしでも通用
+・800億をオートで周回できる編成</t>
+        </is>
+      </c>
+      <c r="F992" s="2" t="inlineStr"/>
+      <c r="G992" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦ターミン
+・weak無し状態異常
+・800億オート編成
+・ネシハマルカー</t>
+        </is>
+      </c>
+      <c r="H992" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I992" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bx0_Y4UxO7I</t>
+        </is>
+      </c>
+      <c r="J992" s="2" t="inlineStr">
+        <is>
+          <t>bx0_Y4UxO7I</t>
+        </is>
+      </c>
+      <c r="K992" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:09:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B993" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C993" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】アレツ・コッペパン・ターミンガチャ能力値早見表 ~コッペパン…EXF瀕死だけじゃないのね…強すぎる‼️…アレツ…継承したらかなりヤバいやないの ~‼️</t>
+        </is>
+      </c>
+      <c r="D993" s="2" t="inlineStr">
+        <is>
+          <t>運ロマンシングサガガチャのアレツとコッペパンの能力を考察。
+アレツは過去技継承で6行動43ヒットと化けて強い。
+コッペパンは瀕死時2.2倍と防御弱体カンストで強力。</t>
+        </is>
+      </c>
+      <c r="E993" s="2" t="inlineStr">
+        <is>
+          <t>・アレツは天地継承で3ターンごと6行動43ヒットと激強
+・アレツは過去1のポテンシャルで欲しい一体
+・コッペパンは瀕死EXフォース2.2倍で防御弱体カンスト
+・ターミンはサポートしつつ火力も出せて優秀</t>
+        </is>
+      </c>
+      <c r="F993" s="2" t="inlineStr">
+        <is>
+          <t>・コッペパンはEX瀕死条件で最初は考察対象から外していた
+・アレツは残弱2ターン移動が来るか次第</t>
+        </is>
+      </c>
+      <c r="G993" s="2" t="inlineStr">
+        <is>
+          <t>・能力値早見表
+・アレツ
+・コッペパン
+・技継承
+・瀕死性能</t>
+        </is>
+      </c>
+      <c r="H993" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I993" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ThVyUeAwLsQ</t>
+        </is>
+      </c>
+      <c r="J993" s="2" t="inlineStr">
+        <is>
+          <t>ThVyUeAwLsQ</t>
+        </is>
+      </c>
+      <c r="K993" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:09:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B994" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C994" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第132回 ~教授のペットの井戸 ~ランキング100位編成‼️</t>
+        </is>
+      </c>
+      <c r="D994" s="2" t="inlineStr">
+        <is>
+          <t>教授のペットの井戸ランキング100位を狙う編成を紹介。
+第132回として井戸攻略の構成を解説。
+ランキング上位入りの立ち回りを実演。</t>
+        </is>
+      </c>
+      <c r="E994" s="2" t="inlineStr"/>
+      <c r="F994" s="2" t="inlineStr"/>
+      <c r="G994" s="2" t="inlineStr">
+        <is>
+          <t>・教授のペットの井戸
+・ランキング100位
+・井戸編成</t>
+        </is>
+      </c>
+      <c r="H994" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I994" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nQgKzGMcAMI</t>
+        </is>
+      </c>
+      <c r="J994" s="2" t="inlineStr">
+        <is>
+          <t>nQgKzGMcAMI</t>
+        </is>
+      </c>
+      <c r="K994" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:09:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B995" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C995" s="2" t="inlineStr">
+        <is>
+          <t>ちゃむのYouTubeガチャ生配信~ブッ壊れガチャ回した後に~井戸雑談&amp;配信あるかも~？</t>
+        </is>
+      </c>
+      <c r="D995" s="2" t="inlineStr">
+        <is>
+          <t>2週間ぶりのガチャ生配信でコッペパン・アレツ・ターミンを狙う。
+天井コンプで3体確保、アレツの継承性能を高評価。
+教授のペットの井戸トップ考察でヒューズ2手が鍵と解説。</t>
+        </is>
+      </c>
+      <c r="E995" s="2" t="inlineStr">
+        <is>
+          <t>・アレツは天地継承で中長期戦も戦える思った以上に強い
+・コッペパンは瀕死でもレイドで最短時間に貢献し強い
+・井戸ではヒューズが2手で必須の鍵キャラ</t>
+        </is>
+      </c>
+      <c r="F995" s="2" t="inlineStr">
+        <is>
+          <t>・すり抜けが多く3体目まで天井近くまで回す羽目に
+・井戸は4手の微調整でダメージが上がらず難しい
+・シム飯シュは井戸に刺さらず引かない</t>
+        </is>
+      </c>
+      <c r="G995" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ生配信
+・天井コンプ
+・アレツ継承
+・コッペパン
+・井戸トップ考察</t>
+        </is>
+      </c>
+      <c r="H995" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I995" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rZCY4kOL-X8</t>
+        </is>
+      </c>
+      <c r="J995" s="2" t="inlineStr">
+        <is>
+          <t>rZCY4kOL-X8</t>
+        </is>
+      </c>
+      <c r="K995" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:09:15Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K995"/>
+  <dimension ref="A1:K1003"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -65680,6 +65680,551 @@
         </is>
       </c>
     </row>
+    <row r="996">
+      <c r="A996" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B996" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C996" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新ターミン取説「最強お供四選」使いこなすと最強の強さ!!ネシハマルカーの永続アビを活かせるお仲間&amp;おすすめ編成とは!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D996" s="2" t="inlineStr">
+        <is>
+          <t>新ターミンは属性別の永続バフを味方に付与
+陰/雷/冷/熱の属性染めで効果が変化する
+最適なお供4選とテンプレ編成を紹介</t>
+        </is>
+      </c>
+      <c r="E996" s="2" t="inlineStr">
+        <is>
+          <t>・ターミン自身がアタッカーとして高火力
+・防御30%ばら撒きで実質95%防御に到達
+・BPやODゲージを潤沢に補填できる
+・属性染めで戦術的な編成の幅が出る
+・メロトセロイやアセルスなど既存も現役</t>
+        </is>
+      </c>
+      <c r="F996" s="2" t="inlineStr">
+        <is>
+          <t>・追撃が確率で火力にブレがある
+・無人島より螺旋・討伐向けで用途が限定的</t>
+        </is>
+      </c>
+      <c r="G996" s="2" t="inlineStr">
+        <is>
+          <t>・新ターミン性能
+・属性染め編成
+・お供スタイル選定
+・螺旋・討伐向け
+・BP/ODゲージ補填</t>
+        </is>
+      </c>
+      <c r="H996" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I996" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ec7MhZabFxY</t>
+        </is>
+      </c>
+      <c r="J996" s="2" t="inlineStr">
+        <is>
+          <t>Ec7MhZabFxY</t>
+        </is>
+      </c>
+      <c r="K996" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T01:23:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B997" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C997" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「こよみ終了」!?本物サルーインが来て空前絶後のインフレが起きる…かもしれない　ストーリー前編お知らせみんなで読んでいこう　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D997" s="2" t="inlineStr">
+        <is>
+          <t>暦読み編ストーリー前編とサルーイン登場を予想
+復刻の旧ネシハマルカーは引いておくべき
+連道場で技ランク上げ、29日生放送に注目</t>
+        </is>
+      </c>
+      <c r="E997" s="2" t="inlineStr">
+        <is>
+          <t>・佐賀集結とストーリー祭りの流れは正解
+・復刻の旧ネシハマルカーは引いておくべき
+・連道場でまとめて技ランク上げが効率的</t>
+        </is>
+      </c>
+      <c r="F997" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャキャラは難易度が高かった
+・復刻の他キャラは死になりそう
+・シングルガチャは今一つ感がある
+・Webジュエルショップ配布終了に注意</t>
+        </is>
+      </c>
+      <c r="G997" s="2" t="inlineStr">
+        <is>
+          <t>・サルーイン
+・暦読み編ストーリー
+・旧ネシハマルカー復刻
+・連道場
+・Webジュエルショップ終了</t>
+        </is>
+      </c>
+      <c r="H997" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I997" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=edZoig0Yx6k</t>
+        </is>
+      </c>
+      <c r="J997" s="2" t="inlineStr">
+        <is>
+          <t>edZoig0Yx6k</t>
+        </is>
+      </c>
+      <c r="K997" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T01:23:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B998" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C998" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　制圧戦！激闘のライブ配信！　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D998" s="2" t="inlineStr">
+        <is>
+          <t>制圧戦と幻想水滸伝スターリープのライブ配信
+紋章編集めや新規郎の塔などを進行
+サルーインは様子見、視聴者と雑談交流</t>
+        </is>
+      </c>
+      <c r="E998" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープの初見が面白い
+・幻想石がたくさんもらえる
+・チケットガチャでSSR確定が出た
+・新規郎の塔で紋章片を集められる</t>
+        </is>
+      </c>
+      <c r="F998" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインは性能不明で様子見
+・新規郎の塔50回クリアは相当きつそう</t>
+        </is>
+      </c>
+      <c r="G998" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦ライブ
+・幻想水滸伝スターリープ
+・紋章強化
+・サルーイン様子見
+・視聴者交流</t>
+        </is>
+      </c>
+      <c r="H998" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I998" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=j5yCIwmPanM</t>
+        </is>
+      </c>
+      <c r="J998" s="2" t="inlineStr">
+        <is>
+          <t>j5yCIwmPanM</t>
+        </is>
+      </c>
+      <c r="K998" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T01:23:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B999" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C999" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今回はシングルガチャ！ 8月14日更新情報まとめ【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D999" s="2" t="inlineStr">
+        <is>
+          <t>8/14更新はサルイン編シングルガチャ開催
+サルーイン/フレイヤ/巻き火がピックアップ
+ターミン編復刻や螺旋590追加も</t>
+        </is>
+      </c>
+      <c r="E999" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインは気になる性能
+・ログボや育成応援で3000ジュエル配布
+・Web配布のSSカバー人間は取っておくべき</t>
+        </is>
+      </c>
+      <c r="F999" s="2" t="inlineStr">
+        <is>
+          <t>・フレイヤは前回自分で状態異常になり使いづらかった
+・今回はシングルガチャのみ
+・Webジュエルショップ配布が8月下旬終了で注意</t>
+        </is>
+      </c>
+      <c r="G999" s="2" t="inlineStr">
+        <is>
+          <t>・サルイン編ガチャ
+・ボックスガチャ
+・ターミン復刻
+・螺旋回廊590追加
+・Webショップ終了</t>
+        </is>
+      </c>
+      <c r="H999" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I999" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Fd1XwlNUMT4</t>
+        </is>
+      </c>
+      <c r="J999" s="2" t="inlineStr">
+        <is>
+          <t>Fd1XwlNUMT4</t>
+        </is>
+      </c>
+      <c r="K999" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T01:23:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1000" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1000" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ここにきて大本命キャラが登場！大注目の最新情報をチェク！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1000" s="2" t="inlineStr">
+        <is>
+          <t>メインストーリー第7話でサルーインが主役登場
+サルイン編シングルガチャ、復刻ターミンも
+サルーインはぶっ壊れ性能を警戒</t>
+        </is>
+      </c>
+      <c r="E1000" s="2" t="inlineStr">
+        <is>
+          <t>・復刻ターミンネシハマルカーは今でも非常に強い
+・レイドで時短でき現役
+・シングルガチャで来たのは優しい
+・ログボ3000ジュエルはありがたい</t>
+        </is>
+      </c>
+      <c r="F1000" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインはぶっ壊れ性能で怖い
+・イベントは当たり障りなく早く終わってほしい
+・Web配布終了に注意
+・予想（佐賀後半）は外れた</t>
+        </is>
+      </c>
+      <c r="G1000" s="2" t="inlineStr">
+        <is>
+          <t>・サルーイン主役
+・メインストーリー第7話
+・サルイン編ガチャ
+・ターミン復刻
+・螺旋590追加</t>
+        </is>
+      </c>
+      <c r="H1000" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1000" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8_osxVrowKc</t>
+        </is>
+      </c>
+      <c r="J1000" s="2" t="inlineStr">
+        <is>
+          <t>8_osxVrowKc</t>
+        </is>
+      </c>
+      <c r="K1000" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T01:23:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1001" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1001" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ガチャ終了間近！結局どのキャラ引くべきか！リアルクィーン&amp;ジニーガチャ最終キャラランキング！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1001" s="2" t="inlineStr">
+        <is>
+          <t>終了間近ガチャキャラを最終ランク評価
+シグナスが星3で汎用性最高おすすめ
+他は条件付きで活躍の星2評価</t>
+        </is>
+      </c>
+      <c r="E1001" s="2" t="inlineStr">
+        <is>
+          <t>・シグナスは汎用性高くHP/BP回復でき星3
+・ジニーは冷続でOD火力アップが優秀
+・リアルクイーンは打熱火力支援ができる
+・シグナスの技マシンがシンプルに強い</t>
+        </is>
+      </c>
+      <c r="F1001" s="2" t="inlineStr">
+        <is>
+          <t>・ジニーは追撃や技1/2の火力が低い
+・ピンクパンチは自身が女性で恩恵を受けられず編成難度高い
+・アデルは陰トレンドで直近は活躍機会少ない
+・リアルクイーンは技3使用時に味方が代償ダメージ</t>
+        </is>
+      </c>
+      <c r="G1001" s="2" t="inlineStr">
+        <is>
+          <t>・最終キャラ評価
+・シグナス星3
+・幻想上ネ攻略
+・属性別おすすめ
+・星ランク付け</t>
+        </is>
+      </c>
+      <c r="H1001" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1001" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9JItWUOzQeQ</t>
+        </is>
+      </c>
+      <c r="J1001" s="2" t="inlineStr">
+        <is>
+          <t>9JItWUOzQeQ</t>
+        </is>
+      </c>
+      <c r="K1001" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T01:23:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1002" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1002" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】2026年8月上旬ガチャ総まとめ！全12スタイル引くべきスタイルランキング！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1002" s="2" t="inlineStr">
+        <is>
+          <t>8月上旬実装12スタイルをティアランク評価
+ターミンが最高ランク、シャムマベルがA
+コッペパンは無人島特攻でジュラ個人S評価</t>
+        </is>
+      </c>
+      <c r="E1002" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンはバランス良く軸になる最高ランク
+・シャムマベルは属性縛りなく扱いやすくA
+・コッペパンは無人島で特攻級のS評価
+・シグナスは陰属性強化に売っ付け</t>
+        </is>
+      </c>
+      <c r="F1002" s="2" t="inlineStr">
+        <is>
+          <t>・アレツはサポート皆無で火ダメ軽減0%
+・シム飯シは軽減30%で高難度は心もとない
+・ピンクパンチは女性優遇環境で使われなさそう
+・アデルは死一戦継承できないとパワー不足</t>
+        </is>
+      </c>
+      <c r="G1002" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ総まとめランキング
+・ターミン最高ランク
+・シャムマベルA
+・ダークホース枠
+・無人島特攻コッペパン</t>
+        </is>
+      </c>
+      <c r="H1002" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1002" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=O0wKbt2B7Kk</t>
+        </is>
+      </c>
+      <c r="J1002" s="2" t="inlineStr">
+        <is>
+          <t>O0wKbt2B7Kk</t>
+        </is>
+      </c>
+      <c r="K1002" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T01:23:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1003" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1003" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】佐賀県コラボ 全制圧-ターミン・ネシハマルカー-レイド速報!!まさかのキャラが大活躍!!最速は1:52!?とりあえず周回編成3種紹介!!【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1003" s="2" t="inlineStr">
+        <is>
+          <t>佐賀コラボ最終レイドのターミンネシハマルカー解説
+豪毅50・眠り有効で高速周回編成3種を紹介
+最速1分52秒、ビクトール軸などを解説</t>
+        </is>
+      </c>
+      <c r="E1003" s="2" t="inlineStr">
+        <is>
+          <t>・豪毅が50でダメージが通りやすい
+・眠りが非常に有効で時短できる
+・ビクトール軸で最速1:52を達成
+・ビクトールなしでも安定して800億可能</t>
+        </is>
+      </c>
+      <c r="F1003" s="2" t="inlineStr">
+        <is>
+          <t>・開始時にBP減少があり編成メンバーが限られる
+・ビクトールのランダム要素で戦闘時間がブレる
+・自由枠を取ると眠り付与を諦め時間が伸びる</t>
+        </is>
+      </c>
+      <c r="G1003" s="2" t="inlineStr">
+        <is>
+          <t>・佐賀コラボ制圧戦
+・レイド周回編成
+・眠り付与
+・ビクトール軸
+・800億トータルダメージ</t>
+        </is>
+      </c>
+      <c r="H1003" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1003" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=t4ydyOIbxc8</t>
+        </is>
+      </c>
+      <c r="J1003" s="2" t="inlineStr">
+        <is>
+          <t>t4ydyOIbxc8</t>
+        </is>
+      </c>
+      <c r="K1003" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T01:23:20Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1003"/>
+  <dimension ref="A1:K1023"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -66225,6 +66225,1292 @@
         </is>
       </c>
     </row>
+    <row r="1004">
+      <c r="A1004" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1004" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1004" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】凌駕「サルーイン×こよみ徹底比較」神威から神威が出る最強アタッカー!!取り回しをシミュレーション　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1004" s="2" t="inlineStr">
+        <is>
+          <t>サルーインとこよみを火力・取り回しで徹底比較。
+長期戦はサルーインが明確に上、3ターンまでは拮抗。
+総合はこよみだがイン染めならサルーイン優位。</t>
+        </is>
+      </c>
+      <c r="E1004" s="2" t="inlineStr">
+        <is>
+          <t>・戦闘が長引くほどサルーインのダメージが上回る
+・防御ダウンでループ＆重ねがけが可能
+・火力ソースとしてはサルーインに軍配
+・安定感のある火力でレイド精度が上がりそう</t>
+        </is>
+      </c>
+      <c r="F1004" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインのイン縛りは取り回しが悪い
+・エクストラの数値担保はこよみに分がある
+・防御が30%しかなく編成バランスに難</t>
+        </is>
+      </c>
+      <c r="G1004" s="2" t="inlineStr">
+        <is>
+          <t>・サルーイン
+・こよみ比較
+・陰属性火力
+・リキャスト運用
+・高難度評価SS</t>
+        </is>
+      </c>
+      <c r="H1004" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1004" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OlP7IfizWak</t>
+        </is>
+      </c>
+      <c r="J1004" s="2" t="inlineStr">
+        <is>
+          <t>OlP7IfizWak</t>
+        </is>
+      </c>
+      <c r="K1004" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1005" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1005" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「難解」3体優先度まとめ!!永久OD満タンと簡易版マイス!?フレイヤ&amp;解呪に回復にBPに…便利な陰陽師マキビ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1005" s="2" t="inlineStr">
+        <is>
+          <t>フレイヤ・マキビ・アレスの3体性能をまとめ評価。
+フレイヤはOD満タ、マキビは便利枠だが数値低め。
+プラチナ級性能でシングルは引かなくてよい。</t>
+        </is>
+      </c>
+      <c r="E1005" s="2" t="inlineStr">
+        <is>
+          <t>・フレイヤのOD1.5倍とOD満タは有効
+・マキビは状態異常解除で便利
+・マキビは手持ちが少ないプレイヤーの心強い枠</t>
+        </is>
+      </c>
+      <c r="F1005" s="2" t="inlineStr">
+        <is>
+          <t>・フレイヤは火力サポートの数値が低くおまけ程度
+・マキビは尖った部分がなく汎用止まり
+・プラチナに生きそびれた性能でひどいガチャ
+・引かなくても良いガチャの立ち位置</t>
+        </is>
+      </c>
+      <c r="G1005" s="2" t="inlineStr">
+        <is>
+          <t>・フレイヤ
+・マキビ
+・OD満タン
+・陰陽師
+・プラチナガチャ</t>
+        </is>
+      </c>
+      <c r="H1005" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1005" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Qp5Zwu9HEQQ</t>
+        </is>
+      </c>
+      <c r="J1005" s="2" t="inlineStr">
+        <is>
+          <t>Qp5Zwu9HEQQ</t>
+        </is>
+      </c>
+      <c r="K1005" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1006" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1006" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「3体のみ引け」週間ランキング!!ターミン編VSサルーイン→9体3ガチャランキング!!最新スタイルの最強を決める比較検討会→2026年8月15日版　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1006" s="2" t="inlineStr">
+        <is>
+          <t>既存9スタイルを3ガチャ週間ランキングで比較。
+接待されるのはサルーイン・こよみ・コッペパン・ターミンのみ。
+引くべきはこの層だけで他は待機推奨。</t>
+        </is>
+      </c>
+      <c r="E1006" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンは召喚継承で相互作用が強く1位
+・コッペパンは瀕死シナジーで唯一性が高い
+・サルーインは編成が揃えば強い</t>
+        </is>
+      </c>
+      <c r="F1006" s="2" t="inlineStr">
+        <is>
+          <t>・マキビ・アレスは浮上できない壁がありビリ
+・プラチナっぽい2体は弱い
+・資源像3体はウェポンや対応力がなく物足りない
+・サルーイン一点抜きは急ぐ必要なし</t>
+        </is>
+      </c>
+      <c r="G1006" s="2" t="inlineStr">
+        <is>
+          <t>・週間ランキング
+・3ガチャ比較
+・ターミン
+・コッペパン
+・引き手順</t>
+        </is>
+      </c>
+      <c r="H1006" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1006" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TMdX0l1Bl_I</t>
+        </is>
+      </c>
+      <c r="J1006" s="2" t="inlineStr">
+        <is>
+          <t>TMdX0l1Bl_I</t>
+        </is>
+      </c>
+      <c r="K1006" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B1007" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1007" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　SSR（配布キャラ以外）禁止縛りでストーリーどこまで行けるのか挑戦！2章0話から（ボスのみ）　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1007" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRSでサルーインのレイド周回性能を検証配信。
+カルテットは想定より速く2分前後で周回可能。
+ターミン枠や育成枠を交えた最速編成を模索。</t>
+        </is>
+      </c>
+      <c r="E1007" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインは想定より速く火力も高い
+・ターミン杖ポコで10秒安定周回が可能
+・コッペパン＋サルーインが今回のレイドで好相性</t>
+        </is>
+      </c>
+      <c r="F1007" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインは防御面が心配
+・カルテットのモーションがやや遅い
+・シム飯では育成枠2体が厳しい</t>
+        </is>
+      </c>
+      <c r="G1007" s="2" t="inlineStr">
+        <is>
+          <t>・サルーイン検証
+・レイド周回
+・カムイ継承
+・ターミン編成
+・セフェルマルカー</t>
+        </is>
+      </c>
+      <c r="H1007" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1007" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KHkEAwZHGAw</t>
+        </is>
+      </c>
+      <c r="J1007" s="2" t="inlineStr">
+        <is>
+          <t>KHkEAwZHGAw</t>
+        </is>
+      </c>
+      <c r="K1007" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B1008" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1008" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　関門：シュウザー最新版　零姫編成とサライ小ネタ有２編成を紹介</t>
+        </is>
+      </c>
+      <c r="D1008" s="2" t="inlineStr">
+        <is>
+          <t>関門シューザーの安定2編成を紹介。
+最新レイ姫技3で13秒の高速周回を実現。
+サイ人系で冷を2回目に確定させ12秒編成。</t>
+        </is>
+      </c>
+      <c r="E1008" s="2" t="inlineStr">
+        <is>
+          <t>・レイ姫技3で速度が安定した
+・人系変更で冷が確定し安定した</t>
+        </is>
+      </c>
+      <c r="F1008" s="2" t="inlineStr">
+        <is>
+          <t>・以前のサイ編成はムラがあった</t>
+        </is>
+      </c>
+      <c r="G1008" s="2" t="inlineStr">
+        <is>
+          <t>・関門シューザー
+・レイ姫編成
+・高速周回
+・人系
+・サライ小ネタ</t>
+        </is>
+      </c>
+      <c r="H1008" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1008" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PMO3vWfLitA</t>
+        </is>
+      </c>
+      <c r="J1008" s="2" t="inlineStr">
+        <is>
+          <t>PMO3vWfLitA</t>
+        </is>
+      </c>
+      <c r="K1008" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1009" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1009" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　SSR（配布キャラ以外）禁止縛りでストーリーどこまで行けるのか挑戦！2章1話から（ボスのみ）　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1009" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープをSSR禁止縛りで2章1話から攻略。
+学園編の永血杯ストーリーを進めボス戦を撃破。
+SR108勝とSRで縛りでも十分戦えると実感。</t>
+        </is>
+      </c>
+      <c r="E1009" s="2" t="inlineStr">
+        <is>
+          <t>・SR108勝とSRで縛りでもなんとかなる
+・サイドストーリーもちゃんと作り込まれている</t>
+        </is>
+      </c>
+      <c r="F1009" s="2" t="inlineStr">
+        <is>
+          <t>・第一試練の敵が強くパーティ強化が必要
+・ボス戦は経験値が上がらず面倒</t>
+        </is>
+      </c>
+      <c r="G1009" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープ
+・SSR禁止縛り
+・永血杯
+・学園ストーリー
+・ボス攻略</t>
+        </is>
+      </c>
+      <c r="H1009" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1009" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gkpejYPULI0</t>
+        </is>
+      </c>
+      <c r="J1009" s="2" t="inlineStr">
+        <is>
+          <t>gkpejYPULI0</t>
+        </is>
+      </c>
+      <c r="K1009" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1010" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1010" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始316日目記録　悲願　一つの夢が達成</t>
+        </is>
+      </c>
+      <c r="D1010" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣プレイ316日目の記録報告。
+特別市場で全国制圧の空白を全て埋め悲願達成。
+開発・制圧率・武将育成の今後の目標を語る。</t>
+        </is>
+      </c>
+      <c r="E1010" s="2" t="inlineStr">
+        <is>
+          <t>・特別市場が短縮効果で非常に便利だった
+・全国の空白が無くなり嬉しい
+・前田利家の戦法ゲージ上昇が良さそう</t>
+        </is>
+      </c>
+      <c r="F1010" s="2" t="inlineStr">
+        <is>
+          <t>・列伝イベントで特性を上げきれず火力不足
+・軍列リーグで勝てず不甲斐ない結果
+・開発の日数がかかりすぎる</t>
+        </is>
+      </c>
+      <c r="G1010" s="2" t="inlineStr">
+        <is>
+          <t>・信長の野望出陣
+・全国制圧率
+・特別市場
+・天下布武
+・制圧率目標</t>
+        </is>
+      </c>
+      <c r="H1010" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1010" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mtlS0WgbTDE</t>
+        </is>
+      </c>
+      <c r="J1010" s="2" t="inlineStr">
+        <is>
+          <t>mtlS0WgbTDE</t>
+        </is>
+      </c>
+      <c r="K1010" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1011" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1011" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】火力は攻撃型なみ！？アルトロンの火力を確認してみた 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D1011" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナルのアルトロンの火力をエイジ2と比較検証。
+支援型ながら攻撃型並みの火力を叩き出す高性能。
+2種デバフ持ちで専用機チームとの同時運用が強力。</t>
+        </is>
+      </c>
+      <c r="E1011" s="2" t="inlineStr">
+        <is>
+          <t>・アルトロンは支援型なのに攻撃型並みの火力
+・2種類のデバフを入れつつ高火力で殴れて使い勝手が良い
+・エイジ2とデバフが被らず同時運用が非常に強い
+・専用機が今めちゃめちゃ強くなった</t>
+        </is>
+      </c>
+      <c r="F1011" s="2" t="inlineStr">
+        <is>
+          <t>・EX武装の射程が4と短いのが気になる
+・1.5周年前のインフレ具合に期待半分・不安半分</t>
+        </is>
+      </c>
+      <c r="G1011" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・アルトロン
+・火力比較
+・エイジ2
+・専用機シナジー</t>
+        </is>
+      </c>
+      <c r="H1011" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1011" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZD80qX17YMo</t>
+        </is>
+      </c>
+      <c r="J1011" s="2" t="inlineStr">
+        <is>
+          <t>ZD80qX17YMo</t>
+        </is>
+      </c>
+      <c r="K1011" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:37Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1012" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1012" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ゆるして『こよみ編 第7話 前編 公開記念 Romancing祭 サルーイン編』【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1012" s="2" t="inlineStr">
+        <is>
+          <t>サルーイン編シングルガチャを70連で挑戦。
+前回の引きの悪さで萎え気味、深追いせず撤退。
+陰属性サポートのフレイヤ・音名字で終了。</t>
+        </is>
+      </c>
+      <c r="E1012" s="2" t="inlineStr">
+        <is>
+          <t>・初手クチャーは安心感がある
+・フレイヤは今の環境なら全然いい</t>
+        </is>
+      </c>
+      <c r="F1012" s="2" t="inlineStr">
+        <is>
+          <t>・前回シム周辺の引きが悪くて萎えた
+・音名字は陰属性サポートで微妙</t>
+        </is>
+      </c>
+      <c r="G1012" s="2" t="inlineStr">
+        <is>
+          <t>・サルーイン編ガチャ
+・シングルガチャ
+・70連
+・フレイヤ
+・撤退</t>
+        </is>
+      </c>
+      <c r="H1012" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1012" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qOgZqll52v8</t>
+        </is>
+      </c>
+      <c r="J1012" s="2" t="inlineStr">
+        <is>
+          <t>qOgZqll52v8</t>
+        </is>
+      </c>
+      <c r="K1012" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1013" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1013" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ゆるして『Romancing祭 サルーイン編』#ロマンシングサガリ・ユニバース ＃Shorts</t>
+        </is>
+      </c>
+      <c r="D1013" s="2" t="inlineStr">
+        <is>
+          <t>サルーイン編シングルガチャを70連で挑戦（Shorts）。
+前回の引きの悪さで萎え気味、深追いせず撤退。
+陰属性サポートのフレイヤ・音名字で終了。</t>
+        </is>
+      </c>
+      <c r="E1013" s="2" t="inlineStr">
+        <is>
+          <t>・初手クチャーは安心感がある
+・フレイヤは今の環境なら全然いい</t>
+        </is>
+      </c>
+      <c r="F1013" s="2" t="inlineStr">
+        <is>
+          <t>・前回シム周辺の引きが悪くて萎えた
+・音名字は陰属性サポートで微妙</t>
+        </is>
+      </c>
+      <c r="G1013" s="2" t="inlineStr">
+        <is>
+          <t>・サルーイン編ガチャ
+・Shorts
+・70連
+・フレイヤ
+・撤退</t>
+        </is>
+      </c>
+      <c r="H1013" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1013" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rrsA7vEmY5s</t>
+        </is>
+      </c>
+      <c r="J1013" s="2" t="inlineStr">
+        <is>
+          <t>rrsA7vEmY5s</t>
+        </is>
+      </c>
+      <c r="K1013" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1014" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1014" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】最強の陰火力検証！サルーイン、シウグナス、新ターミン、オーバーソウルこよみ！驚きの結果に【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1014" s="2" t="inlineStr">
+        <is>
+          <t>サルーイン・シウグナス・ターミン等で陰火力を検証。
+聖王のアビス2ターンとセフィルマルカーで速攻。
+結局こよみの方が使いやすいという結論。</t>
+        </is>
+      </c>
+      <c r="E1014" s="2" t="inlineStr">
+        <is>
+          <t>・シウグナスが結構強く安定する
+・サルーインは火力全振りで超火力が出る
+・LP回復のサポートが優秀</t>
+        </is>
+      </c>
+      <c r="F1014" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインは防御が低く落ちやすい
+・ボードゲージが低く前段が足りない
+・サルーインはサポートも火力だけで辛い
+・防御軽減が下がると結構きつい</t>
+        </is>
+      </c>
+      <c r="G1014" s="2" t="inlineStr">
+        <is>
+          <t>・陰火力検証
+・聖王のアビス
+・セフィルマルカー
+・シウグナス
+・防御軽減不足</t>
+        </is>
+      </c>
+      <c r="H1014" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1014" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4yK-K7O-wL4</t>
+        </is>
+      </c>
+      <c r="J1014" s="2" t="inlineStr">
+        <is>
+          <t>4yK-K7O-wL4</t>
+        </is>
+      </c>
+      <c r="K1014" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1015" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1015" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】サルーイン期待通りの超火力構成！３人まとめて性能確認【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1015" s="2" t="inlineStr">
+        <is>
+          <t>サルーイン・フレイヤ・マキビの3体性能を確認。
+サルーインはヒット数多く自前2.75倍で100億超。
+万能こよみに対しサルーインは継続火力型。</t>
+        </is>
+      </c>
+      <c r="E1015" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインは結構強くレイドで活躍しそう
+・フレイヤの状態解除持ち技は優秀
+・マキビは防御ゲージMAXで解除・回復付きが優秀</t>
+        </is>
+      </c>
+      <c r="F1015" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインは防御力が低い
+・フレイヤは体術枠で裁判と被り出番が微妙
+・マキビはエクストラ1.5倍で火力が出ない</t>
+        </is>
+      </c>
+      <c r="G1015" s="2" t="inlineStr">
+        <is>
+          <t>・サルーイン性能
+・フレイヤ
+・マキビ
+・カムイ継承
+・レイド運用</t>
+        </is>
+      </c>
+      <c r="H1015" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1015" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DhSplcJ2GOE</t>
+        </is>
+      </c>
+      <c r="J1015" s="2" t="inlineStr">
+        <is>
+          <t>DhSplcJ2GOE</t>
+        </is>
+      </c>
+      <c r="K1015" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1016" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1016" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】オーバーソウルサルーインガチャ【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1016" s="2" t="inlineStr">
+        <is>
+          <t>オーバーソウルのサルーインガチャを実演する動画。
+字幕がほぼ取得できず内容の詳細は不明。
+タイトルからサルーイン狙いのガチャ配信。</t>
+        </is>
+      </c>
+      <c r="E1016" s="2" t="inlineStr"/>
+      <c r="F1016" s="2" t="inlineStr"/>
+      <c r="G1016" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインガチャ
+・オーバーソウル</t>
+        </is>
+      </c>
+      <c r="H1016" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1016" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uhmocwx3G-8</t>
+        </is>
+      </c>
+      <c r="J1016" s="2" t="inlineStr">
+        <is>
+          <t>uhmocwx3G-8</t>
+        </is>
+      </c>
+      <c r="K1016" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1017" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C1017" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみ編 第7話 前編 公開記念Sガチャ🐈</t>
+        </is>
+      </c>
+      <c r="D1017" s="2" t="inlineStr">
+        <is>
+          <t>サルーイン狙いのSガチャ配信、なかなか出ず苦戦。
+サルーインは高火力、フレイヤは可、音名字は弱い評価。
+視聴者と回線やパチスロ雑談で盛り上がる。</t>
+        </is>
+      </c>
+      <c r="E1017" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインは火力が高く強い
+・サルーインは自己バフが強く豪体環境で際立つ
+・フレイヤは体力精神低下でワンチャン使える</t>
+        </is>
+      </c>
+      <c r="F1017" s="2" t="inlineStr">
+        <is>
+          <t>・音名字マキビはプラチケレベルで弱い
+・ガチャが渋く欲しいものが当たらない
+・記憶再戦が1つしかなく不便
+・サルーイン一点狙いでジュエルを浪費</t>
+        </is>
+      </c>
+      <c r="G1017" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインガチャ
+・天井
+・フレイヤ
+・音名字マキビ
+・雑談配信</t>
+        </is>
+      </c>
+      <c r="H1017" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I1017" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=oDLbSahxMSU</t>
+        </is>
+      </c>
+      <c r="J1017" s="2" t="inlineStr">
+        <is>
+          <t>oDLbSahxMSU</t>
+        </is>
+      </c>
+      <c r="K1017" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1018" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1018" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】間違えちゃダメ！現状の注意点と新イベント最速周回を解説【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1018" s="2" t="inlineStr">
+        <is>
+          <t>暦読み編ストーリーイベントの周回と注意点を解説。
+ボックスは10まで、以降は制圧戦周回がおすすめ。
+覚醒の羽衣など復刻進化素材の取り逃しに注意。</t>
+        </is>
+      </c>
+      <c r="E1018" s="2" t="inlineStr">
+        <is>
+          <t>・ボックスガチャは3000ジュエル入りでおいしい
+・通常攻撃で誰でも11秒周回できる
+・制圧戦を残してくれてありがたい</t>
+        </is>
+      </c>
+      <c r="F1018" s="2" t="inlineStr">
+        <is>
+          <t>・記憶再戦に籠りきりは非推奨で制圧戦に戻るべき
+・進化素材は期間を逃すと取れなくなる注意</t>
+        </is>
+      </c>
+      <c r="G1018" s="2" t="inlineStr">
+        <is>
+          <t>・ストーリーイベント
+・ボックスガチャ
+・11秒周回
+・制圧戦
+・進化素材</t>
+        </is>
+      </c>
+      <c r="H1018" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1018" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FC9nnDh8i-g</t>
+        </is>
+      </c>
+      <c r="J1018" s="2" t="inlineStr">
+        <is>
+          <t>FC9nnDh8i-g</t>
+        </is>
+      </c>
+      <c r="K1018" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1019" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1019" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】超火力アタッカー爆誕！大注目のサルーイン編ガチャを性能チェック！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1019" s="2" t="inlineStr">
+        <is>
+          <t>サルーイン・フレイヤ・マキビの性能を詳細チェック。
+フレイヤは無条件OD満タ＆1.5倍で当たり枠。
+サルーインは絆暦みに並ぶ超火力アタッカー。</t>
+        </is>
+      </c>
+      <c r="E1019" s="2" t="inlineStr">
+        <is>
+          <t>・フレイヤは味方全員が常にOD＆1.5倍で優秀
+・サルーインは瞬間火力なら暦みを超える超アタッカー
+・サルーインの防御ダウン12ターンが強力
+・マキビは貴重な陰属性サポーター</t>
+        </is>
+      </c>
+      <c r="F1019" s="2" t="inlineStr">
+        <is>
+          <t>・マキビはエクストラを持たずサポート枠として使いにくい
+・サルーインは防御が低くサポートは火力寄り
+・サルーインは全体攻撃に乏しい</t>
+        </is>
+      </c>
+      <c r="G1019" s="2" t="inlineStr">
+        <is>
+          <t>・性能チェック
+・サルーイン
+・フレイヤ
+・マキビ
+・カムイ継承</t>
+        </is>
+      </c>
+      <c r="H1019" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1019" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tA00BhmY1_Y</t>
+        </is>
+      </c>
+      <c r="J1019" s="2" t="inlineStr">
+        <is>
+          <t>tA00BhmY1_Y</t>
+        </is>
+      </c>
+      <c r="K1019" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1020" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1020" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】サルーイン能力値早見表〜飯綱こよみを超える ~壊れ‼️【我は…最強ﾅﾘ…】</t>
+        </is>
+      </c>
+      <c r="D1020" s="2" t="inlineStr">
+        <is>
+          <t>サルーインの能力値早見表を居戸/中長期で作成。
+火力サポートしながら本人火力も爆発する壊れ性能。
+こよみに匹敵し陰弱点の高難度で最強タッグ。</t>
+        </is>
+      </c>
+      <c r="E1020" s="2" t="inlineStr">
+        <is>
+          <t>・攻撃強化がターン頭からカンストする
+・1人で火力バフをカンストさせる
+・こよみに匹敵する超火力
+・こよみと組めば陰弱点高難度でやばい</t>
+        </is>
+      </c>
+      <c r="F1020" s="2" t="inlineStr"/>
+      <c r="G1020" s="2" t="inlineStr">
+        <is>
+          <t>・能力値早見表
+・ダークボルテージ
+・陰属性25行動
+・居戸運用
+・こよみ比較</t>
+        </is>
+      </c>
+      <c r="H1020" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1020" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Sd3zaKebJ9A</t>
+        </is>
+      </c>
+      <c r="J1020" s="2" t="inlineStr">
+        <is>
+          <t>Sd3zaKebJ9A</t>
+        </is>
+      </c>
+      <c r="K1020" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1021" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1021" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベント解説 注意点 11秒周回編成の紹介【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1021" s="2" t="inlineStr">
+        <is>
+          <t>新イベントの解説と注意点を紹介する動画。
+11秒周回編成を紹介している。
+字幕が音楽主体で内容の詳細は取得できず。</t>
+        </is>
+      </c>
+      <c r="E1021" s="2" t="inlineStr"/>
+      <c r="F1021" s="2" t="inlineStr"/>
+      <c r="G1021" s="2" t="inlineStr">
+        <is>
+          <t>・新イベント
+・11秒周回
+・編成紹介</t>
+        </is>
+      </c>
+      <c r="H1021" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1021" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PBU34vuNDhM</t>
+        </is>
+      </c>
+      <c r="J1021" s="2" t="inlineStr">
+        <is>
+          <t>PBU34vuNDhM</t>
+        </is>
+      </c>
+      <c r="K1021" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1022" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1022" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】佐賀県コラボ 制圧戦-ターミン・ネシハマルカー- 新サルーインの技ランク上げ用＆神威が無い人用【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1022" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県コラボ制圧戦ターミンの周回編成を紹介。
+新サルーインの技ランク上げ用・神威が無い人向け。
+字幕がほぼ取得できず詳細は不明。</t>
+        </is>
+      </c>
+      <c r="E1022" s="2" t="inlineStr"/>
+      <c r="F1022" s="2" t="inlineStr"/>
+      <c r="G1022" s="2" t="inlineStr">
+        <is>
+          <t>・佐賀県コラボ
+・制圧戦
+・ターミン周回
+・技ランク上げ</t>
+        </is>
+      </c>
+      <c r="H1022" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1022" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WydNoxY0JJE</t>
+        </is>
+      </c>
+      <c r="J1022" s="2" t="inlineStr">
+        <is>
+          <t>WydNoxY0JJE</t>
+        </is>
+      </c>
+      <c r="K1022" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1023" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1023" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】佐賀県コラボ 制圧戦-ターミン・ネシハマルカー-新サルーインを使ってみた!!完全自由枠1か2を取りつつ安定して高速周回編成の紹介!!【ロマンシング サガ リ・ユニバース】【レイド】</t>
+        </is>
+      </c>
+      <c r="D1023" s="2" t="inlineStr">
+        <is>
+          <t>佐賀県コラボ制圧戦でサルーインの複数編成を紹介。
+技2とカムイを比較、速さは技2でダメージはカムイ。
+自由枠を確保しつつ2分台で安定高速周回。</t>
+        </is>
+      </c>
+      <c r="E1023" s="2" t="inlineStr">
+        <is>
+          <t>・新速人系で眠りが確実に入りダメージが安定
+・自由枠を確保しつつ高速周回できる</t>
+        </is>
+      </c>
+      <c r="F1023" s="2" t="inlineStr">
+        <is>
+          <t>・記憶再戦はターミン最速編成のままが効率的との結論</t>
+        </is>
+      </c>
+      <c r="G1023" s="2" t="inlineStr">
+        <is>
+          <t>・佐賀県コラボ制圧戦
+・サルーイン編成
+・技2vsカムイ
+・自由枠確保
+・眠り付与</t>
+        </is>
+      </c>
+      <c r="H1023" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1023" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ij0nWfkmlTs</t>
+        </is>
+      </c>
+      <c r="J1023" s="2" t="inlineStr">
+        <is>
+          <t>ij0nWfkmlTs</t>
+        </is>
+      </c>
+      <c r="K1023" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15T01:09:18Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1023"/>
+  <dimension ref="A1:K1035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -67511,6 +67511,825 @@
         </is>
       </c>
     </row>
+    <row r="1024">
+      <c r="A1024" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1024" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1024" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「ガチャ沼」タマゴローは何を引いた!?止まらないすり抜けに抗う術を教えてください…　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1024" s="2" t="inlineStr">
+        <is>
+          <t>ガチャ配信、目的のコッペパンとターミンは確保
+すり抜け連発で天井到達、ジュエルを大量消費
+サルーインは天井行きで見送り寄りの検討</t>
+        </is>
+      </c>
+      <c r="E1024" s="2" t="inlineStr">
+        <is>
+          <t>・目的のコッペパンとターミンの2体を確保できた
+・サルーインは高難度で全力維持でき魅力的
+・プラチナ級の2体だと評価</t>
+        </is>
+      </c>
+      <c r="F1024" s="2" t="inlineStr">
+        <is>
+          <t>・すり抜けが止まらず天井まで到達
+・リアルクイーンは全く欲しくないのに絡む
+・少し欲しいだけのガチャで高くついた</t>
+        </is>
+      </c>
+      <c r="G1024" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ沼
+・すり抜け
+・天井
+・コッペパン確保
+・ターミン確保
+・サルーイン見送り</t>
+        </is>
+      </c>
+      <c r="H1024" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1024" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PMYBOsFEQiI</t>
+        </is>
+      </c>
+      <c r="J1024" s="2" t="inlineStr">
+        <is>
+          <t>PMYBOsFEQiI</t>
+        </is>
+      </c>
+      <c r="K1024" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16T01:08:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B1025" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1025" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】これで「中難度」銃!!看破する何通りかのギミック活用方法→追憶の幻闘場ウンディーネ&amp;ボルカノ→棍棒&amp;体術　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1025" s="2" t="inlineStr">
+        <is>
+          <t>追憶の幻闘場ウンディーネ&amp;ボルカノを攻略
+片方を封じ片方を速攻で倒すのがセオリー
+棍棒・体術で安定してクリア</t>
+        </is>
+      </c>
+      <c r="E1025" s="2" t="inlineStr">
+        <is>
+          <t>・熱チームはBP切れなければ安定して運を止められる
+・棍棒はお玉でボルカノを封殺でき楽勝
+・体術はぶっ飛ばして即終了</t>
+        </is>
+      </c>
+      <c r="F1025" s="2" t="inlineStr">
+        <is>
+          <t>・ウンディーネの間接防御が厄介でダメージが通りづらい
+・LP攻撃のタイムリミットと敵のスタンが脅威</t>
+        </is>
+      </c>
+      <c r="G1025" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場攻略
+・ウンディーネ
+・ボルカノ
+・棍棒
+・体術
+・ギミック活用</t>
+        </is>
+      </c>
+      <c r="H1025" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1025" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=f_Stbw8QHnM</t>
+        </is>
+      </c>
+      <c r="J1025" s="2" t="inlineStr">
+        <is>
+          <t>f_Stbw8QHnM</t>
+        </is>
+      </c>
+      <c r="K1025" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16T01:08:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B1026" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1026" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネやりながら雑談</t>
+        </is>
+      </c>
+      <c r="D1026" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナルをプレイしつつ雑談配信
+SDガンダム外伝やバーサルナイトを語る
+チケットガシャは将軍すり抜けで不発</t>
+        </is>
+      </c>
+      <c r="E1026" s="2" t="inlineStr">
+        <is>
+          <t>・SDガンダムイベントの作り込みが半端ない
+・EX武装の演出がめちゃくちゃ凝っている
+・国産ソシャゲで珍しくセルラン上位を取る好調
+・参戦作品の弾が実質無限なのが強み</t>
+        </is>
+      </c>
+      <c r="F1026" s="2" t="inlineStr">
+        <is>
+          <t>・ガイデン3のお知らせがなかなか来ない
+・チケットガシャで将軍がすり抜け
+・今回のガチャはSSRが全然いなかった
+・ガンダム名が初見で読めないネーミング</t>
+        </is>
+      </c>
+      <c r="G1026" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・SDガンダム外伝
+・バーサルナイト
+・チケットガシャ
+・参戦作品</t>
+        </is>
+      </c>
+      <c r="H1026" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1026" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6TdElIlv1xc</t>
+        </is>
+      </c>
+      <c r="J1026" s="2" t="inlineStr">
+        <is>
+          <t>6TdElIlv1xc</t>
+        </is>
+      </c>
+      <c r="K1026" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16T01:08:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1027" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1027" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】バーサル騎士 チケットガシャ ※配信切り抜き 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D1027" s="2" t="inlineStr">
+        <is>
+          <t>バーサル騎士チケットガシャの切り抜き
+URは出るがユニットもサポーターもすり抜け
+将軍は出ずも見所だけはあった</t>
+        </is>
+      </c>
+      <c r="E1027" s="2" t="inlineStr">
+        <is>
+          <t>・URは一応引けた
+・何も出ないよりは見所があった</t>
+        </is>
+      </c>
+      <c r="F1027" s="2" t="inlineStr">
+        <is>
+          <t>・ユニットもサポーターもどちらもすり抜け
+・狙いの将軍が出ない
+・SSRすらほぼいなかった</t>
+        </is>
+      </c>
+      <c r="G1027" s="2" t="inlineStr">
+        <is>
+          <t>・バーサル騎士
+・チケットガシャ
+・UR
+・すり抜け
+・SDガンダム</t>
+        </is>
+      </c>
+      <c r="H1027" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1027" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9S3Zw30lneY</t>
+        </is>
+      </c>
+      <c r="J1027" s="2" t="inlineStr">
+        <is>
+          <t>9S3Zw30lneY</t>
+        </is>
+      </c>
+      <c r="K1027" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16T01:08:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1028" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1028" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】サルーインVS新旧ターミン 4大ガチャランキング引くべき優先度考察【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1028" s="2" t="inlineStr">
+        <is>
+          <t>サルーイン編と復刻ターミン編の4大ガチャ優先度考察
+1位はターミン&amp;コッペパンで独走状態
+サルーインはバランス良く外れなし</t>
+        </is>
+      </c>
+      <c r="E1028" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンとコッペパンが頭一つ抜けて強い
+・サルーインはバランスが良く外れがない
+・シャムマベルが1点だけ抜けて強い
+・コッペパンは無人島特攻で火力にびっくり</t>
+        </is>
+      </c>
+      <c r="F1028" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインは防御軽減30%しかなく簡単にワンパンされる
+・マキビ・フレイヤは他で代用でき使い所が不明確
+・キューターミンは復刻で出ないリスクがある</t>
+        </is>
+      </c>
+      <c r="G1028" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ優先度
+・サルーイン
+・新旧ターミン
+・コッペパン
+・シャムマベル
+・陰属性編成</t>
+        </is>
+      </c>
+      <c r="H1028" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1028" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HrL7lgt1euE</t>
+        </is>
+      </c>
+      <c r="J1028" s="2" t="inlineStr">
+        <is>
+          <t>HrL7lgt1euE</t>
+        </is>
+      </c>
+      <c r="K1028" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16T01:08:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1029" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1029" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】サルーイン届くかSSS！？旧ターミン参戦の大波乱開幕★最新キャラランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1029" s="2" t="inlineStr">
+        <is>
+          <t>サルーイン・マキビ・フレイヤ＋ターミンのキャラランク評価
+サルーインは特殊戦力Sの火力枠
+暦読みとサルーイン択なら暦読みを推奨</t>
+        </is>
+      </c>
+      <c r="E1029" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインはトリプルS特戦力の火力枠
+・フレイヤは全体OD満タンでき優秀
+・マキビは状態異常解除持ちで完成されたスタイル
+・現状はコッペパンが一番強い評価</t>
+        </is>
+      </c>
+      <c r="F1029" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインは防御軽減30%でインフレに飲まれる懸念
+・マキビはファストなくBP回復も控えめでS止まり
+・フレイヤは防御軽減50%と低め
+・キューターミンは来週消える、迷うならスルー</t>
+        </is>
+      </c>
+      <c r="G1029" s="2" t="inlineStr">
+        <is>
+          <t>・キャラランキング
+・サルーイン
+・マキビ
+・フレイヤ
+・暦読み
+・特殊戦力</t>
+        </is>
+      </c>
+      <c r="H1029" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1029" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=U2ZCl3EeaRI</t>
+        </is>
+      </c>
+      <c r="J1029" s="2" t="inlineStr">
+        <is>
+          <t>U2ZCl3EeaRI</t>
+        </is>
+      </c>
+      <c r="K1029" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16T01:08:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B1030" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1030" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはり1位のあのキャラに！最新版確保優先度ランキング【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1030" s="2" t="inlineStr">
+        <is>
+          <t>8月最新の確保優先度ランキングを発表
+最優先はなし、実質1位はシグナス
+インフレが落ち着き焦り不要の狭の時期</t>
+        </is>
+      </c>
+      <c r="E1030" s="2" t="inlineStr">
+        <is>
+          <t>・シグナスはサポート能力が化け物級で優秀
+・ブラッドサマーナイトは技マシンとして価値が高い
+・インフレが落ち着きジュエルを貯めやすい良い時期</t>
+        </is>
+      </c>
+      <c r="F1030" s="2" t="inlineStr">
+        <is>
+          <t>・最優先に置けるほどのキャラはいない
+・螺旋回廊は難易度の割に報酬がしょぼい
+・洋属性編成は組むハードルが高く必須でない
+・レイ姫など陰属性はもうお腹いっぱい</t>
+        </is>
+      </c>
+      <c r="G1030" s="2" t="inlineStr">
+        <is>
+          <t>・確保優先度
+・シグナス
+・ジニ
+・螺旋回廊
+・インフレ落ち着き
+・狭の時期</t>
+        </is>
+      </c>
+      <c r="H1030" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1030" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FMtBwynHjU4</t>
+        </is>
+      </c>
+      <c r="J1030" s="2" t="inlineStr">
+        <is>
+          <t>FMtBwynHjU4</t>
+        </is>
+      </c>
+      <c r="K1030" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16T01:08:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1031" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1031" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】誰でも激ウマな周回が可能に！？制圧戦の真のパラダイスを大紹介！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1031" s="2" t="inlineStr">
+        <is>
+          <t>制圧戦の高速・育成周回パラダイスを大紹介
+コッペパン全滅周回は8秒で育成枠を量産
+明日サルーインガチャライブを告知</t>
+        </is>
+      </c>
+      <c r="E1031" s="2" t="inlineStr">
+        <is>
+          <t>・コッペパン全滅周回は8秒で1日1.2万周でき破格
+・育成枠1周回でも1日2万周でソウルアビリティ量産
+・ビクトール編成は最速49秒も可能
+・クラウドレルムのマップの作り込みが素敵</t>
+        </is>
+      </c>
+      <c r="F1031" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトールがいないと編成が制限される
+・Sレイ姫だと先制を取られ眠らせ損なうことがある</t>
+        </is>
+      </c>
+      <c r="G1031" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦
+・高速周回
+・コッペパン全滅周回
+・育成枠周回
+・ビクトール
+・ガチャライブ告知</t>
+        </is>
+      </c>
+      <c r="H1031" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1031" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ppfumKptMkU</t>
+        </is>
+      </c>
+      <c r="J1031" s="2" t="inlineStr">
+        <is>
+          <t>ppfumKptMkU</t>
+        </is>
+      </c>
+      <c r="K1031" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16T01:08:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1032" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1032" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】あのキャラはやはり当たり？サルーインガチャ性能チェック&amp;キャラランク評価【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1032" s="2" t="inlineStr">
+        <is>
+          <t>サルーイン・フレイヤ・マキビの性能チェックとランク評価
+3体とも使い所ありだが全員星2評価
+足りない戦力を補う目的なら引き推奨</t>
+        </is>
+      </c>
+      <c r="E1032" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインは火力と陰バフのサポートを両立し優秀
+・フレイヤは味方OD満タン支援ができ丸
+・マキビは火ダメ軽減率が高く螺旋・討伐で安定
+・暦みを持っていない人にはサルーインがおすすめ</t>
+        </is>
+      </c>
+      <c r="F1032" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインは陰変成が前提でどのPTにも入れにくく星2
+・フレイヤは1.75倍が1ターンのみでぶっ飛んだ性能ではない
+・マキビはシグナスと役割が被り複数体は不要
+・3体とも最優先ではない</t>
+        </is>
+      </c>
+      <c r="G1032" s="2" t="inlineStr">
+        <is>
+          <t>・性能チェック
+・キャラランク
+・サルーイン
+・フレイヤ
+・マキビ
+・陰属性</t>
+        </is>
+      </c>
+      <c r="H1032" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1032" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=I2SkJ_Wt900</t>
+        </is>
+      </c>
+      <c r="J1032" s="2" t="inlineStr">
+        <is>
+          <t>I2SkJ_Wt900</t>
+        </is>
+      </c>
+      <c r="K1032" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16T01:08:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B1033" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1033" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】リアルクィーン能力値早見表 ~きめ細かな【数値】を算出‼️クィーンの強さはいかに⁉️</t>
+        </is>
+      </c>
+      <c r="D1033" s="2" t="inlineStr">
+        <is>
+          <t>リアルクイーンの能力値早見表を作成・考察
+打熱アタッカー兼デバッファーで技3火力が破壊的
+ジュエル余裕あれば欲しい1体</t>
+        </is>
+      </c>
+      <c r="E1033" s="2" t="inlineStr">
+        <is>
+          <t>・技3の単体火力がトリプルS以上33ヒットで破壊的
+・短期決戦も長期戦も回復・サポートもこなせる
+・ジュエルに余裕があるなら欲しい1体</t>
+        </is>
+      </c>
+      <c r="F1033" s="2" t="inlineStr">
+        <is>
+          <t>・技3は代償ダメージ30%が入るのが厄介
+・能力値の算出がアナログ手法で大変だった</t>
+        </is>
+      </c>
+      <c r="G1033" s="2" t="inlineStr">
+        <is>
+          <t>・リアルクイーン
+・能力値早見表
+・打熱アタッカー
+・デバッファー
+・夏祭りガチャ</t>
+        </is>
+      </c>
+      <c r="H1033" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1033" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=N6f9x5jHuBE</t>
+        </is>
+      </c>
+      <c r="J1033" s="2" t="inlineStr">
+        <is>
+          <t>N6f9x5jHuBE</t>
+        </is>
+      </c>
+      <c r="K1033" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16T01:08:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1034" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1034" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】ちゃむのゲリラガチャ配信【ある意味…過去1番の配信に…】…2つもやらかしてもうた…😨</t>
+        </is>
+      </c>
+      <c r="D1034" s="2" t="inlineStr">
+        <is>
+          <t>サルーイン1点狙いのゲリラガチャ配信
+1連目で神引き成功も育成でやらかす
+スタイルLv9仕様を誤りフルスペック化</t>
+        </is>
+      </c>
+      <c r="E1034" s="2" t="inlineStr">
+        <is>
+          <t>・1連目でサルーインを神引き成功
+・フルスペックのサルーインで思いっきりレイドを楽しめる
+・仲間考案の編成がビクトール&amp;ターミンを1分53秒で回せて魅力的</t>
+        </is>
+      </c>
+      <c r="F1034" s="2" t="inlineStr">
+        <is>
+          <t>・スタイルレベル9で止める仕様を間違えフルスペックにしてしまった
+・1配信で2つもやらかしてしまった</t>
+        </is>
+      </c>
+      <c r="G1034" s="2" t="inlineStr">
+        <is>
+          <t>・ゲリラガチャ
+・サルーイン1点狙い
+・神引き
+・スタイルレベル
+・やらかし
+・レイド編成</t>
+        </is>
+      </c>
+      <c r="H1034" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1034" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_OOhVrAKHoM</t>
+        </is>
+      </c>
+      <c r="J1034" s="2" t="inlineStr">
+        <is>
+          <t>_OOhVrAKHoM</t>
+        </is>
+      </c>
+      <c r="K1034" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16T01:08:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B1035" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1035" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「サルーイン 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1035" s="2" t="inlineStr">
+        <is>
+          <t>サルーイン編ガチャのスタイル考察とランク付け
+サルーインは残属性アタッカーでA-評価
+フレイヤB＋・マキビB＋で意外と使える</t>
+        </is>
+      </c>
+      <c r="E1035" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインは威力S以上40ヒットで豪体を貫く火力
+・マキビは火ダメ88%軽減で陰属性の穴を埋められる
+・フレイヤは常時OD満タン付与のサポートが魅力
+・カムイ無吸自在は継承優先度が高い</t>
+        </is>
+      </c>
+      <c r="F1035" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインは火ダメ軽減30%と心もとない
+・残は既にスター選手揃いでサルーイン不在でも何とかなる
+・フレイヤは軽減50%で高難度だと差し替えられる懸念
+・斧・小剣が実装されず武器種が先週と丸被り</t>
+        </is>
+      </c>
+      <c r="G1035" s="2" t="inlineStr">
+        <is>
+          <t>・スタイル考察
+・ランク付け
+・サルーイン
+・フレイヤ
+・マキビ
+・継承候補</t>
+        </is>
+      </c>
+      <c r="H1035" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1035" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7LIb995Rndg</t>
+        </is>
+      </c>
+      <c r="J1035" s="2" t="inlineStr">
+        <is>
+          <t>7LIb995Rndg</t>
+        </is>
+      </c>
+      <c r="K1035" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16T01:08:30Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1035"/>
+  <dimension ref="A1:K1044"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -68330,6 +68330,602 @@
         </is>
       </c>
     </row>
+    <row r="1036">
+      <c r="A1036" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1036" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1036" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】フルオート「必勝法」43層アレツ/44層シムメシュ!!安定と早さを両立し頂を目指せ　2026年8月17日/第4回復刻雲上の無尽塔　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1036" s="2" t="inlineStr">
+        <is>
+          <t>復刻・雲上の無尽塔43層アレツ/44層シムメシュをフルオート攻略
+ベアのパリー＆ダムド原巻きでファスト安定、瀕死恩恵を最大化
+12%回避を仕込みつつ約2時間で自動討伐</t>
+        </is>
+      </c>
+      <c r="E1036" s="2" t="inlineStr">
+        <is>
+          <t>・フルオートで放置OK・安定周回できる
+・ベアのパリーで守り面は自由に選べる
+・瀕死恩恵で火力を最大化できる
+・約2時間で自動討伐と速い</t>
+        </is>
+      </c>
+      <c r="F1036" s="2" t="inlineStr">
+        <is>
+          <t>・気絶や5ターン全滅LP99など事故要素に注意
+・女神編成は横切られやすく不向きかも</t>
+        </is>
+      </c>
+      <c r="G1036" s="2" t="inlineStr">
+        <is>
+          <t>・雲上の無尽塔
+・フルオート周回
+・43層アレツ
+・44層シムメシュ
+・瀕死運用
+・回避12%</t>
+        </is>
+      </c>
+      <c r="H1036" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1036" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ckTWaLX3HAM</t>
+        </is>
+      </c>
+      <c r="J1036" s="2" t="inlineStr">
+        <is>
+          <t>ckTWaLX3HAM</t>
+        </is>
+      </c>
+      <c r="K1036" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17T11:14:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1037" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1037" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　SSR（配布キャラ以外）禁止縛りでストーリーどこまで行けるのか挑戦！2章3話から（ボスのみ）　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1037" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープをSSR禁止縛りでストーリー攻略するライブ配信
+2章から5章の永血杯（学園編）をボス戦中心に進行
+リセマラは回復キャラ推奨、まれ仲間化で幻装石を貯める</t>
+        </is>
+      </c>
+      <c r="E1037" s="2" t="inlineStr">
+        <is>
+          <t>・回復キャラ（ジン）が行動毎12.5%回復で強力
+・きつい戦闘がかえって楽しいと好評
+・まれ（人魚）仲間化で幻装石が貯まる
+・108星の無料配布キャラが優秀</t>
+        </is>
+      </c>
+      <c r="F1037" s="2" t="inlineStr">
+        <is>
+          <t>・SSR禁止だとボスがかなりきつい
+・土系キャラが少なく編成が偏る
+・メンテ緊急復帰で進行中の戦闘が消えた</t>
+        </is>
+      </c>
+      <c r="G1037" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープ
+・SSR禁止縛り
+・ストーリー攻略
+・リセマラ回復
+・限界突破
+・永血杯</t>
+        </is>
+      </c>
+      <c r="H1037" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1037" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3QAohSAS4Vk</t>
+        </is>
+      </c>
+      <c r="J1037" s="2" t="inlineStr">
+        <is>
+          <t>3QAohSAS4Vk</t>
+        </is>
+      </c>
+      <c r="K1037" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17T11:14:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1038" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1038" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SR 騎士ガルバルディβ 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1038" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSR騎士ガルバルディβの武装アニメを紹介
+戦闘ボイスと武装演出のみの短尺ショート
+セリフ以外の解説はなし</t>
+        </is>
+      </c>
+      <c r="E1038" s="2" t="inlineStr"/>
+      <c r="F1038" s="2" t="inlineStr"/>
+      <c r="G1038" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・騎士ガルバルディβ
+・武装アニメ
+・ショート動画</t>
+        </is>
+      </c>
+      <c r="H1038" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1038" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cqAd8GXRCK4</t>
+        </is>
+      </c>
+      <c r="J1038" s="2" t="inlineStr">
+        <is>
+          <t>cqAd8GXRCK4</t>
+        </is>
+      </c>
+      <c r="K1038" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17T11:14:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B1039" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1039" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】超鬼門幻闘場！杖/斧/弓/槍◆実況解説後半戦【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1039" s="2" t="inlineStr">
+        <is>
+          <t>超鬼門幻闘場ゴルカノの杖/斧/弓/槍を後半戦で実況解説
+斧と弓が特に難関、槍はコーデア＆ウコンで安定攻略
+ボルカノのポーション割りとEF2倍を軸に各属性クリア</t>
+        </is>
+      </c>
+      <c r="E1039" s="2" t="inlineStr">
+        <is>
+          <t>・エリスが刺さって強く火力が伸びる
+・ウコンが優秀で今回の突枠にハマる
+・スターギャルは貫通火力で取って良かった
+・槍はコーデア＆ウコンで安定して倒せる</t>
+        </is>
+      </c>
+      <c r="F1039" s="2" t="inlineStr">
+        <is>
+          <t>・斧と弓がかなりきつく心折れかけた
+・高難度すぎて欲しい武器が取れずストレス
+・報酬が威力80止まりで見合わない
+・運営は早く次のコンテンツを作るべき</t>
+        </is>
+      </c>
+      <c r="G1039" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場ゴルカノ
+・杖斧弓槍
+・ボルカノ
+・EF2倍
+・高難度攻略
+・ポーション割り</t>
+        </is>
+      </c>
+      <c r="H1039" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1039" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kkJM00cga3A</t>
+        </is>
+      </c>
+      <c r="J1039" s="2" t="inlineStr">
+        <is>
+          <t>kkJM00cga3A</t>
+        </is>
+      </c>
+      <c r="K1039" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17T11:14:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1040" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1040" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】サルーインvsロマバカ3でガチャライブ！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1040" s="2" t="inlineStr">
+        <is>
+          <t>サルーインガチャをゲスト（アルベルト役声優ら）と回すエンタメライブ
+三蔵は12連でサルーイン、さらにフレイヤ・マキビト・レイ姫を好調に確保
+トーク主体のロマバカ3としての初ライブ配信</t>
+        </is>
+      </c>
+      <c r="E1040" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインを12連で早期確保
+・フレイヤは全員1ターン目からOD発動でレアな性能
+・マキビトも確保し確保優先度動画に繋がる
+・ゲストトークで終始盛り上がる配信</t>
+        </is>
+      </c>
+      <c r="F1040" s="2" t="inlineStr">
+        <is>
+          <t>・フレイヤはサポーター役で必須級ではない
+・ガチャ演出が渋く天井近くまで出ない場面もあった</t>
+        </is>
+      </c>
+      <c r="G1040" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインガチャ
+・ガチャライブ
+・フレイヤ
+・マキビト確保
+・ゲストコラボ</t>
+        </is>
+      </c>
+      <c r="H1040" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1040" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RDpM5uN6yqY</t>
+        </is>
+      </c>
+      <c r="J1040" s="2" t="inlineStr">
+        <is>
+          <t>RDpM5uN6yqY</t>
+        </is>
+      </c>
+      <c r="K1040" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17T11:14:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B1041" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1041" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】これは無視できない性能が！？リアルクィーン&amp;ジニーガチャ性能チェック・キャラランク付け【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1041" s="2" t="inlineStr">
+        <is>
+          <t>追加6キャラ（リアルクイーン・ジニー他）のガチャ性能をチェック＆ランク付け
+シグナスは攻防・回復・デバフをこなし汎用性が最も高い
+属性・編成条件が強く先週のウコン/エリスより優先度は低め</t>
+        </is>
+      </c>
+      <c r="E1041" s="2" t="inlineStr">
+        <is>
+          <t>・シグナスは汎用性が高く技3が良い技マシン
+・ジニーは冷属性＆OD満タ運用で現闘上でも使える
+・つきは術敵に刺さり幻闘場で活躍
+・アデルは残用アタッカーでレイド相性が良い</t>
+        </is>
+      </c>
+      <c r="F1041" s="2" t="inlineStr">
+        <is>
+          <t>・各キャラともBP周りが足りず味方支援が必要
+・リアルクイーン等は打熱編成など条件が強い
+・ピンクパンチの性別不明編成は難易度が高い
+・総じて先週のウコン/エリス編より優先度は低い</t>
+        </is>
+      </c>
+      <c r="G1041" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ性能考察
+・リアルクイーン
+・ジニー
+・シグナス
+・つき
+・優先度評価</t>
+        </is>
+      </c>
+      <c r="H1041" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1041" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=s-UD7_0uuLU</t>
+        </is>
+      </c>
+      <c r="J1041" s="2" t="inlineStr">
+        <is>
+          <t>s-UD7_0uuLU</t>
+        </is>
+      </c>
+      <c r="K1041" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17T11:14:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1042" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1042" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】4手編成~6位の立ち回り~第132回教授のペットの井戸【先週の振り返り】</t>
+        </is>
+      </c>
+      <c r="D1042" s="2" t="inlineStr">
+        <is>
+          <t>教授のペットの井戸で6位を取った4手編成と立ち回りを解説
+小ターミン・リラ・サイバ・アレツ・ヒューズ構成で得点を狙う
+ヒューズはODオフの通常攻撃で追撃を止め減点を回避</t>
+        </is>
+      </c>
+      <c r="E1042" s="2" t="inlineStr">
+        <is>
+          <t>・4手クリアで6位の好成績
+・ODオフ通常攻撃で減点を回避し得点UP
+・他の井戸でも使える立ち回り</t>
+        </is>
+      </c>
+      <c r="F1042" s="2" t="inlineStr"/>
+      <c r="G1042" s="2" t="inlineStr">
+        <is>
+          <t>・教授のペットの井戸
+・4手編成
+・6位立ち回り
+・ヒューズ追撃
+・OD調整
+・得点稼ぎ</t>
+        </is>
+      </c>
+      <c r="H1042" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1042" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CL5vmfyWDNI</t>
+        </is>
+      </c>
+      <c r="J1042" s="2" t="inlineStr">
+        <is>
+          <t>CL5vmfyWDNI</t>
+        </is>
+      </c>
+      <c r="K1042" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17T11:14:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1043" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1043" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第133回~カン＝ケルゥの井戸~楽しい2ターン井戸が帰ってきた╰(*´︶`*)╯♡最適キャラ19体&amp;パーティ6編成考察</t>
+        </is>
+      </c>
+      <c r="D1043" s="2" t="inlineStr">
+        <is>
+          <t>8/17開始カン＝ケルゥの井戸を実装前に徹底考察（最適19体＆6編成）
+突・冷弱点で単体アタッカーが活躍、好評の2ターンクリア井戸
+サ・ジェラール・ドールら候補が豊富で正解編成の予想が難しい</t>
+        </is>
+      </c>
+      <c r="E1043" s="2" t="inlineStr">
+        <is>
+          <t>・2ターンクリアの井戸で好評・楽しみ
+・弱い井戸への要望で2ヶ月スパン復刻
+・サが2ターン目に特に強い
+・候補アタッカーが豊富で幅広い編成が可能</t>
+        </is>
+      </c>
+      <c r="F1043" s="2" t="inlineStr">
+        <is>
+          <t>・アタッカーの選択肢が多く正解編成の予想が難しい</t>
+        </is>
+      </c>
+      <c r="G1043" s="2" t="inlineStr">
+        <is>
+          <t>・カン＝ケルゥの井戸
+・2ターンクリア
+・突冷弱点
+・最適19体
+・編成6種
+・置物ランキング</t>
+        </is>
+      </c>
+      <c r="H1043" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1043" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PQSyMwXkSNU</t>
+        </is>
+      </c>
+      <c r="J1043" s="2" t="inlineStr">
+        <is>
+          <t>PQSyMwXkSNU</t>
+        </is>
+      </c>
+      <c r="K1043" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17T11:14:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1044" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1044" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】8/21までのオススメの記憶再戦と自動再戦 井戸もやってみました 私の記憶再戦の詳細 ターミン1:47【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1044" s="2" t="inlineStr">
+        <is>
+          <t>8/21までのおすすめ記憶再戦・自動再戦の周回先を解説
+覚醒の歯衣は最大進化必須だがドロップが渋く制圧戦レイド推奨
+第132回挑戦の井戸は5手・100位以内狙いの編成を紹介</t>
+        </is>
+      </c>
+      <c r="E1044" s="2" t="inlineStr">
+        <is>
+          <t>・覚醒の歯衣は最大進化で強力な手防具になる
+・制圧戦レイドは魂ひらめき＆宝箱が豪華でおすすめ
+・万額集会は成長判定回数が優秀</t>
+        </is>
+      </c>
+      <c r="F1044" s="2" t="inlineStr">
+        <is>
+          <t>・覚醒の歯衣の進化素材ドロップが渋く約11日かかる
+・現行イベントの周回は意味が薄い
+・フリークエスト・連磨の遺跡は今回優先度が低い
+・育成プラス自動再戦は回る意味がない</t>
+        </is>
+      </c>
+      <c r="G1044" s="2" t="inlineStr">
+        <is>
+          <t>・記憶再戦
+・自動再戦
+・覚醒の歯衣
+・制圧戦レイド
+・万額集会
+・第132回井戸</t>
+        </is>
+      </c>
+      <c r="H1044" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1044" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JKXMpIslh5U</t>
+        </is>
+      </c>
+      <c r="J1044" s="2" t="inlineStr">
+        <is>
+          <t>JKXMpIslh5U</t>
+        </is>
+      </c>
+      <c r="K1044" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17T11:14:01Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1044"/>
+  <dimension ref="A1:K1052"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -68926,6 +68926,505 @@
         </is>
       </c>
     </row>
+    <row r="1045">
+      <c r="A1045" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B1045" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1045" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　サルーイン編ガチャ引くぞぉ！　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1045" s="2" t="inlineStr">
+        <is>
+          <t>タイトルはサルーイン編ガチャだが実際は幻想水滸伝スターリープの雑談配信。
+ソロで気軽に遊べてハマる面白さと視聴者と語る。
+主人公やSSRの強さ、育成方針を実プレイで解説。</t>
+        </is>
+      </c>
+      <c r="E1045" s="2" t="inlineStr">
+        <is>
+          <t>・スターリープはソロで気軽に遊べてハマるほど面白い
+・主人公が強く横攻撃が使いやすい
+・SSRは素の耐久値が高く強い</t>
+        </is>
+      </c>
+      <c r="F1045" s="2" t="inlineStr">
+        <is>
+          <t>・Rは火力が低く弱い
+・ミニゲームが難しく転水・物が苦手
+・SSRは覚醒に時間がかかり先にSR/Sを育てた方が良い</t>
+        </is>
+      </c>
+      <c r="G1045" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープ
+・ライブ配信
+・主人公
+・SSR
+・育成方針</t>
+        </is>
+      </c>
+      <c r="H1045" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1045" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CUuVfCbpYA4</t>
+        </is>
+      </c>
+      <c r="J1045" s="2" t="inlineStr">
+        <is>
+          <t>CUuVfCbpYA4</t>
+        </is>
+      </c>
+      <c r="K1045" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18T01:16:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B1046" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1046" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR報酬多め！外伝Ⅲアルガス騎士団の報酬内容を確認 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1046" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネ外伝Ⅲアルガス騎士団の報酬ユニット確認Short。
+SSRが4体ずつと報酬多め、各性能を短評。
+放術士ニューガンダムが最も使い勝手良さそう。</t>
+        </is>
+      </c>
+      <c r="E1046" s="2" t="inlineStr">
+        <is>
+          <t>・SSR報酬が4体ずつと多くお得
+・放術士ニューは支援回数が増え使い勝手良さそう
+・剣士ゼタは耐久型でマップ兵器持ち</t>
+        </is>
+      </c>
+      <c r="F1046" s="2" t="inlineStr">
+        <is>
+          <t>・需要団定(ジオング)は防御も回数増加もなく最も微妙
+・人気のアレックスが報酬に入っていない</t>
+        </is>
+      </c>
+      <c r="G1046" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・アルガス騎士団
+・SSR報酬
+・ニューガンダム</t>
+        </is>
+      </c>
+      <c r="H1046" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1046" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FfNx1fA58oc</t>
+        </is>
+      </c>
+      <c r="J1046" s="2" t="inlineStr">
+        <is>
+          <t>FfNx1fA58oc</t>
+        </is>
+      </c>
+      <c r="K1046" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18T01:16:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B1047" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1047" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SR 剣士ゲルググ 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1047" s="2" t="inlineStr">
+        <is>
+          <t>GジェネのSR剣士ゲルググ武装アニメShort。
+短い戦闘ボイスと武装演出のみ。
+解説なしの演出紹介動画。</t>
+        </is>
+      </c>
+      <c r="E1047" s="2" t="inlineStr"/>
+      <c r="F1047" s="2" t="inlineStr"/>
+      <c r="G1047" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・SR剣士ゲルググ
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H1047" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1047" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FfT3UQ1xrWA</t>
+        </is>
+      </c>
+      <c r="J1047" s="2" t="inlineStr">
+        <is>
+          <t>FfT3UQ1xrWA</t>
+        </is>
+      </c>
+      <c r="K1047" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18T01:16:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B1048" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1048" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR トールギス 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1048" s="2" t="inlineStr">
+        <is>
+          <t>GジェネのSSRトールギス武装アニメShort。
+戦闘ボイスと武装演出のみで構成。
+性能解説はなく演出鑑賞向けの短尺動画。</t>
+        </is>
+      </c>
+      <c r="E1048" s="2" t="inlineStr"/>
+      <c r="F1048" s="2" t="inlineStr"/>
+      <c r="G1048" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・SSRトールギス
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H1048" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1048" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MrdeU62lg4g</t>
+        </is>
+      </c>
+      <c r="J1048" s="2" t="inlineStr">
+        <is>
+          <t>MrdeU62lg4g</t>
+        </is>
+      </c>
+      <c r="K1048" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18T01:16:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B1049" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1049" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR報酬多め！外伝Ⅲアルガス騎士団！ 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D1049" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネ外伝Ⅲアルガス騎士団の予告と報酬を解説。
+SSR報酬が多くニューガンダムが最も使い勝手良い。
+需要団定は微妙、ガイデン4実装は年内厳しそう。</t>
+        </is>
+      </c>
+      <c r="E1049" s="2" t="inlineStr">
+        <is>
+          <t>・SSRユニット報酬が多くしっかり入手したい
+・放術士ニューが支援回数増加で一番使い勝手良い
+・ナイトガンダム外伝の作り込みが毎回すごい</t>
+        </is>
+      </c>
+      <c r="F1049" s="2" t="inlineStr">
+        <is>
+          <t>・需要団定(ジオング)は防御不可で最も微妙そう
+・アレックスが今回の報酬に未収録
+・ラストのガイデン4は年内実装が難しそう</t>
+        </is>
+      </c>
+      <c r="G1049" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・アルガス騎士団
+・SSR報酬
+・ニューガンダム
+・ガイデン4</t>
+        </is>
+      </c>
+      <c r="H1049" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1049" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pV-42EoPkGI</t>
+        </is>
+      </c>
+      <c r="J1049" s="2" t="inlineStr">
+        <is>
+          <t>pV-42EoPkGI</t>
+        </is>
+      </c>
+      <c r="K1049" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18T01:16:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B1050" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1050" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはり神は強かった！！この2人一緒に使ったらやばいぞ！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1050" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRSサルーインを制圧戦周回で実戦検証。
+ヒット数が多く高火力、こよみと組むと化ける。
+レイドでは過剰火力になるほどの性能。</t>
+        </is>
+      </c>
+      <c r="E1050" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインはヒット数が多く長期戦でも火力を維持
+・こよみと一緒に使うと火力が化ける
+・全て技運用でカ門武器が使える点がプラス
+・制圧戦の集会周回で早速大活躍</t>
+        </is>
+      </c>
+      <c r="F1050" s="2" t="inlineStr">
+        <is>
+          <t>・レイド基準では過剰火力になりオーバーキル気味
+・単発火力とエクストラボースは暦みの方が上
+・エクストラフォース付き武器が実装されず残念</t>
+        </is>
+      </c>
+      <c r="G1050" s="2" t="inlineStr">
+        <is>
+          <t>・ロマサガRS
+・サルーイン
+・こよみ
+・制圧戦
+・周回</t>
+        </is>
+      </c>
+      <c r="H1050" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1050" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qLEQdbkhPDo</t>
+        </is>
+      </c>
+      <c r="J1050" s="2" t="inlineStr">
+        <is>
+          <t>qLEQdbkhPDo</t>
+        </is>
+      </c>
+      <c r="K1050" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18T01:16:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B1051" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1051" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第133回~カン＝ケルゥの井戸~ランキング100位に入ろう‼️【パーティと立ち回りを紹介】</t>
+        </is>
+      </c>
+      <c r="D1051" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRSカン=ケルゥの井戸ランキング100位攻略。
+暦み・トーマス・ターミン・裁判で21手クリア編成を紹介。
+立ち回り次第で15手上位も狙える難関コンテンツ。</t>
+        </is>
+      </c>
+      <c r="E1051" s="2" t="inlineStr">
+        <is>
+          <t>・暦み+トーマス+ターミン編成で井戸21手クリア可能
+・キャラ替えと特殊立ち回りで15手・8位圏も到達</t>
+        </is>
+      </c>
+      <c r="F1051" s="2" t="inlineStr">
+        <is>
+          <t>・トップの1ターン26手は高い魂とアビリティ必須の境地
+・15手は立ち回りが特殊で頭をフル回転させる必要</t>
+        </is>
+      </c>
+      <c r="G1051" s="2" t="inlineStr">
+        <is>
+          <t>・ロマサガRS
+・カン=ケルゥの井戸
+・ランキング
+・21手
+・立ち回り</t>
+        </is>
+      </c>
+      <c r="H1051" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1051" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9LfIQZNVpro</t>
+        </is>
+      </c>
+      <c r="J1051" s="2" t="inlineStr">
+        <is>
+          <t>9LfIQZNVpro</t>
+        </is>
+      </c>
+      <c r="K1051" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18T01:16:15Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B1052" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1052" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新サルーイン 継承無し 改良版!! ターミンレイド 自由枠1 2:03【ロマンシング サガ リ・ユニバース】【制圧戦】【周回】</t>
+        </is>
+      </c>
+      <c r="D1052" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS新サルーインのターミンレイド周回。
+継承無しの改良版編成で自由枠1、2分03秒。
+字幕はほぼ無く周回動作の実演が中心。</t>
+        </is>
+      </c>
+      <c r="E1052" s="2" t="inlineStr">
+        <is>
+          <t>・新サルーインは継承無しでもレイド周回で機能する</t>
+        </is>
+      </c>
+      <c r="F1052" s="2" t="inlineStr"/>
+      <c r="G1052" s="2" t="inlineStr">
+        <is>
+          <t>・ロマサガRS
+・新サルーイン
+・ターミンレイド
+・周回
+・制圧戦</t>
+        </is>
+      </c>
+      <c r="H1052" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1052" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Vevq43phmHU</t>
+        </is>
+      </c>
+      <c r="J1052" s="2" t="inlineStr">
+        <is>
+          <t>Vevq43phmHU</t>
+        </is>
+      </c>
+      <c r="K1052" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18T01:16:15Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1052"/>
+  <dimension ref="A1:K1061"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -69425,6 +69425,582 @@
         </is>
       </c>
     </row>
+    <row r="1053">
+      <c r="A1053" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1053" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1053" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「新ドット」新キャラ!?不遇シリーズ救済とストーリー続きのガチャ予想!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1053" s="2" t="inlineStr">
+        <is>
+          <t>新ドット新キャラの登場を予想するガチャ考察
+不遇シリーズ救済に期待
+ストーリー続きの実装も予想</t>
+        </is>
+      </c>
+      <c r="E1053" s="2" t="inlineStr"/>
+      <c r="F1053" s="2" t="inlineStr"/>
+      <c r="G1053" s="2" t="inlineStr">
+        <is>
+          <t>・新ドット
+・新キャラ予想
+・不遇シリーズ救済
+・ストーリー続き
+・ガチャ予想</t>
+        </is>
+      </c>
+      <c r="H1053" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1053" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6W2KcAi1W30</t>
+        </is>
+      </c>
+      <c r="J1053" s="2" t="inlineStr">
+        <is>
+          <t>6W2KcAi1W30</t>
+        </is>
+      </c>
+      <c r="K1053" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19T01:09:05.106931+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B1054" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1054" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　SSR（配布キャラ以外）禁止縛りでストーリーどこまで行けるのか挑戦！2章5話から（ボスのみ）　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1054" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープをSSR禁止縛りで挑戦配信
+ボス戦は火力が足りず術系編成が有効と実感
+ロマサガは無人島が長く平日は厳しいと本音も</t>
+        </is>
+      </c>
+      <c r="E1054" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープが面白くハマっている
+・主人公キャラが強い
+・連携・受け流しのアクションが楽しい</t>
+        </is>
+      </c>
+      <c r="F1054" s="2" t="inlineStr">
+        <is>
+          <t>・ボスの回復が早く火力が足りない
+・序盤は術系を入れないと厳しい
+・ロマサガ無人島は長くて単調、平日は眠くて無理</t>
+        </is>
+      </c>
+      <c r="G1054" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープ
+・SSR禁止縛り
+・ボス攻略
+・術系編成
+・ロマサガ雑談</t>
+        </is>
+      </c>
+      <c r="H1054" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1054" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=02v0CF7H7LY</t>
+        </is>
+      </c>
+      <c r="J1054" s="2" t="inlineStr">
+        <is>
+          <t>02v0CF7H7LY</t>
+        </is>
+      </c>
+      <c r="K1054" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19T01:09:05.106931+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B1055" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1055" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　幻闘：ウンディーネ&amp;ボルカノ　全武器種制覇　激闘の全貌を一挙公開</t>
+        </is>
+      </c>
+      <c r="D1055" s="2" t="inlineStr">
+        <is>
+          <t>幻闘ウンディーネ&amp;ボルカノを全武器種で制覇
+3ター目のコーション解除と短期決戦が攻略の鍵
+剣と斧はきつく体験は最新キャラで比較的余裕</t>
+        </is>
+      </c>
+      <c r="E1055" s="2" t="inlineStr">
+        <is>
+          <t>・体験は最新キャラが多く比較的余裕でクリア
+・暦みはダメージが圧倒的で2ターン撃破
+・剣は木8サラのMVP活躍で突破</t>
+        </is>
+      </c>
+      <c r="F1055" s="2" t="inlineStr">
+        <is>
+          <t>・剣と斧はかなりきつい戦い
+・ウンディーネのスタンが厄介で被弾すると崩れる
+・直接攻撃が無くカウンターが機能しにくい
+・斧は熱用意ができず火力ゴリ押しになった</t>
+        </is>
+      </c>
+      <c r="G1055" s="2" t="inlineStr">
+        <is>
+          <t>・ウンディーネ&amp;ボルカノ幻闘
+・全武器種制覇
+・コーション解除
+・短期決戦
+・スタン対策</t>
+        </is>
+      </c>
+      <c r="H1055" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1055" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hgPQUY-zqM</t>
+        </is>
+      </c>
+      <c r="J1055" s="2" t="inlineStr">
+        <is>
+          <t>7hgPQUY-zqM</t>
+        </is>
+      </c>
+      <c r="K1055" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19T01:09:05.106931+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1056" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1056" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR 剣士ゼータガンダム 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1056" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナルのショート動画
+SSR剣士ゼータガンダムの武装アニメを紹介
+決め台詞と必殺演出をピックアップ</t>
+        </is>
+      </c>
+      <c r="E1056" s="2" t="inlineStr"/>
+      <c r="F1056" s="2" t="inlineStr"/>
+      <c r="G1056" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・SSRゼータガンダム
+・武装アニメ
+・ショート</t>
+        </is>
+      </c>
+      <c r="H1056" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1056" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FCd-hbA6Tes</t>
+        </is>
+      </c>
+      <c r="J1056" s="2" t="inlineStr">
+        <is>
+          <t>FCd-hbA6Tes</t>
+        </is>
+      </c>
+      <c r="K1056" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19T01:09:05.106931+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1057" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C1057" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】制圧戦が忙しくて何かやってます</t>
+        </is>
+      </c>
+      <c r="D1057" s="2" t="inlineStr">
+        <is>
+          <t>制圧戦を回しながらの雑談ライブ配信
+倍率周回と即死周回の効率や魂ひらめきを検証
+ターミンレイドの高ダメージ周回も話題に</t>
+        </is>
+      </c>
+      <c r="E1057" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンはダメージが桁違いに出て周回が速い
+・最大倍率で回すのが総合効率は良さそう</t>
+        </is>
+      </c>
+      <c r="F1057" s="2" t="inlineStr">
+        <is>
+          <t>・倍率と魂ひらめき率の関係がはっきりせず検証が難しい
+・即死周回とダメージ周回どちらが得か人により分かれる</t>
+        </is>
+      </c>
+      <c r="G1057" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦
+・周回効率
+・魂ひらめき
+・ターミンレイド
+・成長判定</t>
+        </is>
+      </c>
+      <c r="H1057" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I1057" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Eob8pFtktnk</t>
+        </is>
+      </c>
+      <c r="J1057" s="2" t="inlineStr">
+        <is>
+          <t>Eob8pFtktnk</t>
+        </is>
+      </c>
+      <c r="K1057" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19T01:09:05.106931+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B1058" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C1058" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ウンディーネ＆ボルカノ幻闘</t>
+        </is>
+      </c>
+      <c r="D1058" s="2" t="inlineStr">
+        <is>
+          <t>ウンディーネ&amp;ボルカノ幻闘ガチャを引いて性能確認
+パメラは8回攻撃は強いが前パメラ必須で完全体になりにくい
+武器も微妙で今回は見送りと判断</t>
+        </is>
+      </c>
+      <c r="E1058" s="2" t="inlineStr">
+        <is>
+          <t>・パメラの8回攻撃と弱体化効果は強力
+・シグナスやライムは当たりで強い
+・暦読み・サイバーと影属性の相性が良い</t>
+        </is>
+      </c>
+      <c r="F1058" s="2" t="inlineStr">
+        <is>
+          <t>・パメラは前スタイルが無いと完全体にならず微妙
+・武器性能も若干微妙
+・前回エレノアよりインパクトが薄く今回は見送り</t>
+        </is>
+      </c>
+      <c r="G1058" s="2" t="inlineStr">
+        <is>
+          <t>・ウンディーネ&amp;ボルカノ幻闘
+・パメラ性能
+・武器評価
+・シグナス
+・ライム</t>
+        </is>
+      </c>
+      <c r="H1058" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I1058" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jB1RcPVS-x0</t>
+        </is>
+      </c>
+      <c r="J1058" s="2" t="inlineStr">
+        <is>
+          <t>jB1RcPVS-x0</t>
+        </is>
+      </c>
+      <c r="K1058" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19T01:09:05.106931+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1059" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1059" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こんなこと初めてです！最新版の確保ランキングでまさかの事態が発生！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1059" s="2" t="inlineStr">
+        <is>
+          <t>8/18最新の確保優先度ランキングを解説
+コッぺパンを最優先、復刻ターミンを異例の最優先2位に
+新ターミン・サルインも優先で高評価</t>
+        </is>
+      </c>
+      <c r="E1059" s="2" t="inlineStr">
+        <is>
+          <t>・コッぺパンは無人島・瀕死・集回で必須級の最優先
+・復刻ターミンはレイド/高難度で新版より使え偉い
+・サルインは純アタッカーとして最強格
+・国ターミンは回復・BP・カウンターが優秀</t>
+        </is>
+      </c>
+      <c r="F1059" s="2" t="inlineStr">
+        <is>
+          <t>・純アタッカーはインフレですぐ型落ちする
+・復刻を最優先に置くのは異例で悩ましい
+・ターミネシマルカ新版は必須とまでは言えない</t>
+        </is>
+      </c>
+      <c r="G1059" s="2" t="inlineStr">
+        <is>
+          <t>・確保優先度
+・コッぺパン最優先
+・復刻ターミン
+・サルイン
+・レイド適性</t>
+        </is>
+      </c>
+      <c r="H1059" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1059" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SuWgMWt9xrc</t>
+        </is>
+      </c>
+      <c r="J1059" s="2" t="inlineStr">
+        <is>
+          <t>SuWgMWt9xrc</t>
+        </is>
+      </c>
+      <c r="K1059" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19T01:09:05.106931+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1060" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1060" s="2" t="inlineStr">
+        <is>
+          <t>【イジゲンノモリ】ドラゴンクエストアイランド体験記〜ちゃむと嫁は…クリア出来るのか？【淡路島~イジゲンノモリ~】</t>
+        </is>
+      </c>
+      <c r="D1060" s="2" t="inlineStr">
+        <is>
+          <t>淡路島イジゲンノモリのドラクエアイランド体験記
+嫁と協力して謎解きと戦闘を進めクリア
+ラスボスを倒し世界に平和が訪れる</t>
+        </is>
+      </c>
+      <c r="E1060" s="2" t="inlineStr">
+        <is>
+          <t>・キラーマシンの演出が最高で盛り上がる
+・夫婦での協力プレイが楽しい
+・ラスボス撃破でクリアの達成感</t>
+        </is>
+      </c>
+      <c r="F1060" s="2" t="inlineStr">
+        <is>
+          <t>・順番や宝箱の鍵で迷い進行に手間取った
+・森の場所が分かりにくかった</t>
+        </is>
+      </c>
+      <c r="G1060" s="2" t="inlineStr">
+        <is>
+          <t>・ドラクエアイランド
+・イジゲンノモリ
+・淡路島
+・体験施設
+・ラスボス撃破</t>
+        </is>
+      </c>
+      <c r="H1060" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1060" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8vUk1Cx7PtI</t>
+        </is>
+      </c>
+      <c r="J1060" s="2" t="inlineStr">
+        <is>
+          <t>8vUk1Cx7PtI</t>
+        </is>
+      </c>
+      <c r="K1060" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19T01:09:05.106931+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1061" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1061" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【追い追いガチャ動画】ピンクのコがほしぃ～よ【No.630】</t>
+        </is>
+      </c>
+      <c r="D1061" s="2" t="inlineStr">
+        <is>
+          <t>夏祭りガチャでピンクパンチ狙いの追い追いガチャ
+天井まで回して無事ピンクパンチを確保
+2人とも天井到達で確率収束を実感</t>
+        </is>
+      </c>
+      <c r="E1061" s="2" t="inlineStr">
+        <is>
+          <t>・ピンクパンチが可愛く無事確保できた
+・ジニーやシグナスも道中で当たった</t>
+        </is>
+      </c>
+      <c r="F1061" s="2" t="inlineStr">
+        <is>
+          <t>・なかなか出ず引きの流れが死んでいた
+・結局2人とも天井まで行き渋い結果
+・リアルクイーン編に回す余裕が無かった</t>
+        </is>
+      </c>
+      <c r="G1061" s="2" t="inlineStr">
+        <is>
+          <t>・夏祭りガチャ
+・ピンクパンチ
+・天井到達
+・追い追いガチャ
+・ジニー狙い</t>
+        </is>
+      </c>
+      <c r="H1061" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I1061" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=p2iGrHiSpko</t>
+        </is>
+      </c>
+      <c r="J1061" s="2" t="inlineStr">
+        <is>
+          <t>p2iGrHiSpko</t>
+        </is>
+      </c>
+      <c r="K1061" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19T01:09:05.106931+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="video_log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="video_log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'video_log'!$A$1:$K$1</definedName>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1061"/>
+  <dimension ref="A1:K1071"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -70001,6 +70001,661 @@
         </is>
       </c>
     </row>
+    <row r="1062">
+      <c r="A1062" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1062" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1062" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】オート放置「1回で終わらせたい」45層ノーア/46層シャムマベル!!当時のギミックを思い出して　2026年8月19日/第4回復刻雲上の無尽塔　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1062" s="2" t="inlineStr">
+        <is>
+          <t>復刻雲上の無尽塔45層ノーア・46層シャムマベルのオート攻略解説
+ノーアは関節ギミック(5発)対応、リバイバ装備で耐久重視が基本
+シャムマベルは眠り→混乱コンボが脅威、ファスト継承と状態異常解除が鍵</t>
+        </is>
+      </c>
+      <c r="E1062" s="2" t="inlineStr">
+        <is>
+          <t>・ノーアははまれば楽勝
+・ワントップアタッカー編成のトレンドに合致
+・リバイバ装備で序盤を耐えやすい</t>
+        </is>
+      </c>
+      <c r="F1062" s="2" t="inlineStr">
+        <is>
+          <t>・シャムマベルの眠り→混乱コンボは全滅級
+・不明なエラーによる復帰不可が厄介
+・魔王の鎧は手動がだるい</t>
+        </is>
+      </c>
+      <c r="G1062" s="2" t="inlineStr">
+        <is>
+          <t>・雲上の無尽塔
+・ノーア攻略
+・シャムマベル攻略
+・関節ギミック
+・状態異常対策
+・ワントップ編成</t>
+        </is>
+      </c>
+      <c r="H1062" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1062" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Pcz8TWRoYsM</t>
+        </is>
+      </c>
+      <c r="J1062" s="2" t="inlineStr">
+        <is>
+          <t>Pcz8TWRoYsM</t>
+        </is>
+      </c>
+      <c r="K1062" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T01:58:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1063" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1063" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋590階ドグラ&amp;ウィッチ「ギミック解明速報」なぜやられた!?早期決着と立ち回り徹底解説　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1063" s="2" t="inlineStr">
+        <is>
+          <t>螺旋590階ドグラ&amp;ウィッチのギミック解明速報
+奥のドグラをスナイプで先に倒すのが早期決着の鍵
+ウィッチは動きが速くODデバフで封殺、状態異常解除で対応</t>
+        </is>
+      </c>
+      <c r="E1063" s="2" t="inlineStr">
+        <is>
+          <t>・全体攻撃も有効
+・簡単そうで早期決着が可能
+・ブーケなど全体デバフが有効</t>
+        </is>
+      </c>
+      <c r="F1063" s="2" t="inlineStr">
+        <is>
+          <t>・ドグラレーザーの割合ダメージが脅威
+・対策なしだと運ゲーになりやすい</t>
+        </is>
+      </c>
+      <c r="G1063" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋590階
+・ドグラ攻略
+・ウィッチ対策
+・デバフ封殺
+・早期決着</t>
+        </is>
+      </c>
+      <c r="H1063" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1063" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hfhuYX6quz4</t>
+        </is>
+      </c>
+      <c r="J1063" s="2" t="inlineStr">
+        <is>
+          <t>hfhuYX6quz4</t>
+        </is>
+      </c>
+      <c r="K1063" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T01:58:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1064" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1064" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　螺旋回廊590　7ターン　最速攻略</t>
+        </is>
+      </c>
+      <c r="D1064" s="2" t="inlineStr">
+        <is>
+          <t>螺旋回廊590階ドグラ&amp;ウィッチを7ターンで最速攻略
+西王・コッペパン・暦み・黒エ・裁判編成でオーバードライブ主体
+HP調整しつつ後ろから倒し状態異常を回避するのが要点</t>
+        </is>
+      </c>
+      <c r="E1064" s="2" t="inlineStr">
+        <is>
+          <t>・コッペパンで火力が大きく上がる
+・ODの5連携が状態異常回避に楽
+・デバフを入れると状態異常が入らず安定</t>
+        </is>
+      </c>
+      <c r="F1064" s="2" t="inlineStr">
+        <is>
+          <t>・状態異常→追撃で落とされるのが最も厄介
+・すごい悪習の40%割合ダメージが地味に痛い
+・コッペパンは瀕死で1位になりやすく注意</t>
+        </is>
+      </c>
+      <c r="G1064" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋590階
+・7ターン攻略
+・OD主体編成
+・デバフ対策
+・火力調整</t>
+        </is>
+      </c>
+      <c r="H1064" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1064" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YRPqXI8nh4o</t>
+        </is>
+      </c>
+      <c r="J1064" s="2" t="inlineStr">
+        <is>
+          <t>YRPqXI8nh4o</t>
+        </is>
+      </c>
+      <c r="K1064" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T01:58:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B1065" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1065" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　SSR（配布キャラ以外）禁止縛りでストーリーどこまで行けるのか挑戦！2章5話から（ボスのみ）　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1065" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープをSSR(配布以外)禁止縛りで実況配信
+2章5話からボス戦中心にストーリー攻略を進行
+レベル・火力不足でボスが強く苦戦する展開</t>
+        </is>
+      </c>
+      <c r="E1065" s="2" t="inlineStr">
+        <is>
+          <t>・ゴ王(ゴオウ)は硬く育てれば耐えられそう
+・三輪点(3輪点)のボスが強敵として印象的
+・視聴者と盛り上がりながらの配信</t>
+        </is>
+      </c>
+      <c r="F1065" s="2" t="inlineStr">
+        <is>
+          <t>・レベル・火力不足でボスに勝てない
+・被弾(避弾)が大きく防具でも耐えられない
+・回復・スタミナ剤が尽きて周回がきつい</t>
+        </is>
+      </c>
+      <c r="G1065" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープ
+・SSR禁止縛り
+・ストーリー攻略
+・ボス戦
+・育成不足</t>
+        </is>
+      </c>
+      <c r="H1065" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1065" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YT3WDx2cYr8</t>
+        </is>
+      </c>
+      <c r="J1065" s="2" t="inlineStr">
+        <is>
+          <t>YT3WDx2cYr8</t>
+        </is>
+      </c>
+      <c r="K1065" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T01:58:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1066" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1066" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR 闘士ダブルゼータガンダム 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1066" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSSR闘士ダブルゼータの武装アニメ紹介
+セリフ付きの武装カットイン演出を短尺ショートで披露
+実際の戦闘演出をコンパクトに確認できる内容</t>
+        </is>
+      </c>
+      <c r="E1066" s="2" t="inlineStr"/>
+      <c r="F1066" s="2" t="inlineStr"/>
+      <c r="G1066" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ダブルゼータ
+・武装アニメ
+・SSR演出</t>
+        </is>
+      </c>
+      <c r="H1066" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1066" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Fla4uSqVG3w</t>
+        </is>
+      </c>
+      <c r="J1066" s="2" t="inlineStr">
+        <is>
+          <t>Fla4uSqVG3w</t>
+        </is>
+      </c>
+      <c r="K1066" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T01:58:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1067" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1067" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】外伝Ⅲムシャゴーストステージ攻略 ※限定無し 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D1067" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナル外伝Ⅲ隠しステージ「武者ゴースト」を限定なしで攻略
+ナイトガンダム固定枠+アルガス騎士団ユニットで挑戦
+2回撃破必要・射程4以上100%軽減など厄介ギミックを解説</t>
+        </is>
+      </c>
+      <c r="E1067" s="2" t="inlineStr">
+        <is>
+          <t>・オートチャンスステップ持ちダブルゼータが優秀
+・剣士ゼータの反撃時防御で味方を守れる
+・無凸でも同じ立ち回りでクリア可能</t>
+        </is>
+      </c>
+      <c r="F1067" s="2" t="inlineStr">
+        <is>
+          <t>・HP回復して2回倒す必要があり面倒
+・射程4以上100%軽減で近づかないと通らない
+・ネモのマップ兵器は運ゲーで下ぶれる</t>
+        </is>
+      </c>
+      <c r="G1067" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・武者ゴースト
+・限定なし攻略
+・チャンスステップ
+・支援防御</t>
+        </is>
+      </c>
+      <c r="H1067" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1067" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VUrUUtn-BpE</t>
+        </is>
+      </c>
+      <c r="J1067" s="2" t="inlineStr">
+        <is>
+          <t>VUrUUtn-BpE</t>
+        </is>
+      </c>
+      <c r="K1067" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T01:58:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1068" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1068" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】次のガチャが非常にヤバい予感...！？後編ガチャを徹底予想した結果に大注目【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1068" s="2" t="inlineStr">
+        <is>
+          <t>8月21日開始の暦み編第7話後編ガチャを徹底予想
+シェリル編とチアキ編のダブルガチャが本命と予想
+シェリル・ワグナス・エミリア/チアキ・バーニー・教授を候補に挙げる</t>
+        </is>
+      </c>
+      <c r="E1068" s="2" t="inlineStr">
+        <is>
+          <t>・チアキはキャラが立って人気が出そう
+・ワグナス復刻は次ガチャ実装の伏線と推測</t>
+        </is>
+      </c>
+      <c r="F1068" s="2" t="inlineStr">
+        <is>
+          <t>・ストーリーガチャの予想は非常に難しい
+・エミリア予想はコスプレ連想で根拠が薄い</t>
+        </is>
+      </c>
+      <c r="G1068" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ予想
+・暦み編第7話
+・シェリル編
+・チアキ編
+・ダブルガチャ</t>
+        </is>
+      </c>
+      <c r="H1068" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1068" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C7gWL1ROVkE</t>
+        </is>
+      </c>
+      <c r="J1068" s="2" t="inlineStr">
+        <is>
+          <t>C7gWL1ROVkE</t>
+        </is>
+      </c>
+      <c r="K1068" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T01:58:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1069" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1069" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ヴィクトール無しのレイド最強キャラランキング&amp;ティア表で徹底解説！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1069" s="2" t="inlineStr">
+        <is>
+          <t>ビクトール未所持ユーザー視点のレイド最強キャラをティア表で解説
+暦み・木ハ・コッペパン・ビンセントが唯一性の高い最高評価
+ビクトールの強さを分析し次に狙うべきキャラの基準を提示</t>
+        </is>
+      </c>
+      <c r="E1069" s="2" t="inlineStr">
+        <is>
+          <t>・暦みはウィーク無視の火力で唯一性が高い
+・コッペパンの瀕死運用で周回時短ができる
+・ビンセントの順位付与で味方全体を強化
+・ミーティアの最大BP増加がBPギミックに有効</t>
+        </is>
+      </c>
+      <c r="F1069" s="2" t="inlineStr">
+        <is>
+          <t>・木ハはウィーク前提で条件次第で火力が落ちる
+・サはウィーク付与しないと優先度が下がる
+・ノエルは行動数が多くなりがちなのが惜しい</t>
+        </is>
+      </c>
+      <c r="G1069" s="2" t="inlineStr">
+        <is>
+          <t>・レイドティア表
+・ビクトール未所持
+・唯一性
+・火力バフ
+・制圧戦</t>
+        </is>
+      </c>
+      <c r="H1069" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1069" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=K1NF4730rA0</t>
+        </is>
+      </c>
+      <c r="J1069" s="2" t="inlineStr">
+        <is>
+          <t>K1NF4730rA0</t>
+        </is>
+      </c>
+      <c r="K1069" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T01:58:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1070" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1070" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】〜19手100位〜第133回カン＝ケルゥの井戸~編成と立ち回りを紹介</t>
+        </is>
+      </c>
+      <c r="D1070" s="2" t="inlineStr">
+        <is>
+          <t>カン＝ケルゥの井戸ランキング100位圏内の19手編成を紹介
+暦み・トーマス・ビクトール・エイト・裁判の5人編成
+ダメージがギリギリでシビアな立ち回りが要求される</t>
+        </is>
+      </c>
+      <c r="E1070" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトールの無限バリィが強力
+・投稿者は現在15手15位まで到達
+・トーマスのバーストランサーで高ヒット</t>
+        </is>
+      </c>
+      <c r="F1070" s="2" t="inlineStr">
+        <is>
+          <t>・19手はダメージがギリギリでシビア
+・1位の1ターン25手は次元が違う強さ</t>
+        </is>
+      </c>
+      <c r="G1070" s="2" t="inlineStr">
+        <is>
+          <t>・カンケルゥの井戸
+・19手編成
+・ランキング100位
+・立ち回り解説</t>
+        </is>
+      </c>
+      <c r="H1070" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1070" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4XW2CJAT67I</t>
+        </is>
+      </c>
+      <c r="J1070" s="2" t="inlineStr">
+        <is>
+          <t>4XW2CJAT67I</t>
+        </is>
+      </c>
+      <c r="K1070" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T01:58:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1071" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1071" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋回廊590階「ドグラ」を攻略！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1071" s="2" t="inlineStr">
+        <is>
+          <t>螺旋回廊590階ドグラをサガ3ボスとして攻略解説
+ウィッチの状態異常・先制とドグラの割合ダメージが脅威
+ターン終了時に状態異常解除できる再来サが特攻級</t>
+        </is>
+      </c>
+      <c r="E1071" s="2" t="inlineStr">
+        <is>
+          <t>・再来サが今回の特攻スタイルで安定
+・サは全体攻撃かつ両方の弱点を突ける
+・クラウドシフトで先制しやすい</t>
+        </is>
+      </c>
+      <c r="F1071" s="2" t="inlineStr">
+        <is>
+          <t>・ウィッチの状態異常ばらまきが厄介
+・HP回復不可フィールドが厄介
+・弱点属性がバラバラで対応が面倒</t>
+        </is>
+      </c>
+      <c r="G1071" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋590階
+・ドグラ攻略
+・ウィッチ対策
+・再来サ
+・状態異常解除
+・クラウドシフト</t>
+        </is>
+      </c>
+      <c r="H1071" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1071" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YkJR429xhew</t>
+        </is>
+      </c>
+      <c r="J1071" s="2" t="inlineStr">
+        <is>
+          <t>YkJR429xhew</t>
+        </is>
+      </c>
+      <c r="K1071" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T01:58:21Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="video_log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="video_log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'video_log'!$A$1:$K$1</definedName>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1071"/>
+  <dimension ref="A1:K1080"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -70656,6 +70656,581 @@
         </is>
       </c>
     </row>
+    <row r="1072">
+      <c r="A1072" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1072" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1072" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「厄襲来」黒薔薇&amp;黒T260G!!決してガン〇ムコラボではない祭り前夜祭ガチャお知らせ読んでいこう　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1072" s="2" t="inlineStr">
+        <is>
+          <t>厄襲来、黒薔薇姫と黒T260Gが登場するお知らせ確認回。
+イベントはストーリー＋制圧戦のみで報酬はセンジュエル止まり。
+新キャラ性能は皇帝女とロボが強く皇帝男は弱いと予想。</t>
+        </is>
+      </c>
+      <c r="E1072" s="2" t="inlineStr">
+        <is>
+          <t>・皇帝女は無難に強いと予想
+・ロボ（T260G）はめちゃくちゃ強いと予想
+・更新があるだけありがたい週</t>
+        </is>
+      </c>
+      <c r="F1072" s="2" t="inlineStr">
+        <is>
+          <t>・皇帝男はめちゃくちゃ弱いと予想
+・制圧戦の報酬はセンジュエルのみ
+・黒薔薇姫の性能は普通と予想</t>
+        </is>
+      </c>
+      <c r="G1072" s="2" t="inlineStr">
+        <is>
+          <t>・厄襲来
+・黒薔薇姫
+・黒T260G
+・制圧戦
+・性能予想</t>
+        </is>
+      </c>
+      <c r="H1072" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1072" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9ZPzu64Ud84</t>
+        </is>
+      </c>
+      <c r="J1072" s="2" t="inlineStr">
+        <is>
+          <t>9ZPzu64Ud84</t>
+        </is>
+      </c>
+      <c r="K1072" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21T01:06:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1073" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1073" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　SSR（配布キャラ以外）禁止縛りでストーリーどこまで行けるのか挑戦！2章5話から（ボスのみ）　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1073" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープをSSR禁止縛りで進める雑談配信。
+育成を進めボス（ギルガメシュ等）に再挑戦し手応えを確認。
+合間にロマサガRSの黒薔薇姫・T260G実装を話題に。</t>
+        </is>
+      </c>
+      <c r="E1073" s="2" t="inlineStr">
+        <is>
+          <t>・育成したらだいぶ楽になった
+・タイムのガチャは回復もできて良い
+・白薔薇の新スタイルが欲しい</t>
+        </is>
+      </c>
+      <c r="F1073" s="2" t="inlineStr">
+        <is>
+          <t>・ボスが結構きつかった
+・毎日同じボスはさすがに疲れる</t>
+        </is>
+      </c>
+      <c r="G1073" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープ
+・SSR禁止縛り
+・ボス攻略
+・育成
+・雑談配信</t>
+        </is>
+      </c>
+      <c r="H1073" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1073" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XJrzoBd8F4g</t>
+        </is>
+      </c>
+      <c r="J1073" s="2" t="inlineStr">
+        <is>
+          <t>XJrzoBd8F4g</t>
+        </is>
+      </c>
+      <c r="K1073" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21T01:06:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1074" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1074" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】遂に白薔薇とT260Gの厄版実装！8月21日更新情報まとめ 【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1074" s="2" t="inlineStr">
+        <is>
+          <t>8月21日更新の暦読み編第7話後編公開記念情報まとめ。
+白薔薇姫アビス編とT260Gアビス編の新ガチャが登場。
+体験スタイルが強く無償100連以上ありがっつり回す方針。</t>
+        </is>
+      </c>
+      <c r="E1074" s="2" t="inlineStr">
+        <is>
+          <t>・最近の体験スタイルはめちゃくちゃ強い
+・無償ジュエルが100連以上ありお得
+・白バラとT260G、最終工程が欲しい</t>
+        </is>
+      </c>
+      <c r="F1074" s="2" t="inlineStr">
+        <is>
+          <t>・前回は早期撤退でガチャ動画0点だった（自虐）
+・遠征の草原がなくなる（元々一番弱い場所）</t>
+        </is>
+      </c>
+      <c r="G1074" s="2" t="inlineStr">
+        <is>
+          <t>・8月21日更新
+・白薔薇姫アビス
+・T260Gアビス
+・体験スタイル
+・ガチャ予定</t>
+        </is>
+      </c>
+      <c r="H1074" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1074" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6agJLYdHuSE</t>
+        </is>
+      </c>
+      <c r="J1074" s="2" t="inlineStr">
+        <is>
+          <t>6agJLYdHuSE</t>
+        </is>
+      </c>
+      <c r="K1074" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21T01:06:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1075" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1075" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR 法術士ニューガンダム 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1075" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナルの法術士ニューガンダム武装アニメ紹介。
+Shorts形式で必殺技演出を短くピックアップ。
+セリフ演出中心の短尺クリップ。</t>
+        </is>
+      </c>
+      <c r="E1075" s="2" t="inlineStr"/>
+      <c r="F1075" s="2" t="inlineStr"/>
+      <c r="G1075" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・法術士ニューガンダム
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H1075" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1075" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=U6Yi4KaczSo</t>
+        </is>
+      </c>
+      <c r="J1075" s="2" t="inlineStr">
+        <is>
+          <t>U6Yi4KaczSo</t>
+        </is>
+      </c>
+      <c r="K1075" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21T01:06:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1076" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1076" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】アビス＆最終皇帝男女とか！びっくりして動画とりましたわ【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1076" s="2" t="inlineStr">
+        <is>
+          <t>予定外だが人選に驚き白薔薇・T260G実装を急遽動画化。
+白薔薇・黒薔薇・オルロワージ・タイム等キャラの魅力を語る。
+給料日直前にいいガチャが来たと期待を語る回。</t>
+        </is>
+      </c>
+      <c r="E1076" s="2" t="inlineStr">
+        <is>
+          <t>・キャラが魅力的で動画を撮る気になった
+・T260Gアビスがめちゃくちゃ欲しい
+・オルロワージは最近強めで期待
+・給料日直前にいいガチャが来た</t>
+        </is>
+      </c>
+      <c r="F1076" s="2" t="inlineStr">
+        <is>
+          <t>・黒薔薇の顔（アイシャドウ）が黒すぎる（半分ネタ）</t>
+        </is>
+      </c>
+      <c r="G1076" s="2" t="inlineStr">
+        <is>
+          <t>・アビス実装
+・最終皇帝男女
+・タイム
+・オルロワージ
+・キャラ魅力語り</t>
+        </is>
+      </c>
+      <c r="H1076" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1076" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=svcL_X7_ZgI</t>
+        </is>
+      </c>
+      <c r="J1076" s="2" t="inlineStr">
+        <is>
+          <t>svcL_X7_ZgI</t>
+        </is>
+      </c>
+      <c r="K1076" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21T01:06:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1077" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1077" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】あの新キャラたちがまさかの大活躍！？螺旋回廊590階に早速挑戦した結果...【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1077" s="2" t="inlineStr">
+        <is>
+          <t>螺旋回廊590階に早速挑戦しギミックを解説する攻略回。
+HP回復禁止＋状態異常主体でダメージブロックと解除が鍵。
+ガチャ産マキビ等の解除役が親切設計で活躍する。</t>
+        </is>
+      </c>
+      <c r="E1077" s="2" t="inlineStr">
+        <is>
+          <t>・月給7500ジュエルがありがたい
+・マキビをガチャに置く親切設計
+・そこまで難易度は高くない</t>
+        </is>
+      </c>
+      <c r="F1077" s="2" t="inlineStr">
+        <is>
+          <t>・回復禁止ギミックが厄介
+・状態異常でただ追い詰められる
+・全体攻撃対策にダメージブロックが要る</t>
+        </is>
+      </c>
+      <c r="G1077" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋回廊590階
+・回復禁止ギミック
+・状態異常
+・マキビ
+・解除役</t>
+        </is>
+      </c>
+      <c r="H1077" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1077" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bQl7fxQ1f7k</t>
+        </is>
+      </c>
+      <c r="J1077" s="2" t="inlineStr">
+        <is>
+          <t>bQl7fxQ1f7k</t>
+        </is>
+      </c>
+      <c r="K1077" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21T01:06:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1078" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1078" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】まさかの超豪華メンツ！遂に黒薔薇姫がやってきた！！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1078" s="2" t="inlineStr">
+        <is>
+          <t>諦めていた黒薔薇姫が遂に来たお知らせを確認する回。
+白薔薇アビス・T260G・皇帝男オルロワージの豪華ガチャ。
+アビス各キャラのスタイルイラストを絶賛する。</t>
+        </is>
+      </c>
+      <c r="E1078" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャのメンツが豪華で興奮する
+・白薔薇アビスのイラストが良すぎる
+・T260Gアビスのイラストがお気に入り
+・白薔薇前スタイルは今も必須級で強い</t>
+        </is>
+      </c>
+      <c r="F1078" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇は過去に剣スタイルがあり別武器が欲しかった</t>
+        </is>
+      </c>
+      <c r="G1078" s="2" t="inlineStr">
+        <is>
+          <t>・黒薔薇姫
+・白薔薇アビス
+・T260Gアビス
+・オルロワージ
+・スタイルイラスト</t>
+        </is>
+      </c>
+      <c r="H1078" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1078" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=l5u9Ho7C0Ts</t>
+        </is>
+      </c>
+      <c r="J1078" s="2" t="inlineStr">
+        <is>
+          <t>l5u9Ho7C0Ts</t>
+        </is>
+      </c>
+      <c r="K1078" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21T01:06:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1079" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1079" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】コッペパン使って瀕死戦法でやってみた！螺旋回廊590階攻略【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1079" s="2" t="inlineStr">
+        <is>
+          <t>螺旋回廊590階をコッペパンの瀕死戦法で攻略する動画。
+回復禁止環境を逆手にHP調整で立ち回る構成。
+BGM主体で戦闘映像を見せる回。</t>
+        </is>
+      </c>
+      <c r="E1079" s="2" t="inlineStr">
+        <is>
+          <t>・コッペパンの瀕死戦法で590階を攻略できた</t>
+        </is>
+      </c>
+      <c r="F1079" s="2" t="inlineStr"/>
+      <c r="G1079" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋回廊590階
+・コッペパン
+・瀕死戦法
+・攻略</t>
+        </is>
+      </c>
+      <c r="H1079" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1079" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LcfXrmxht9A</t>
+        </is>
+      </c>
+      <c r="J1079" s="2" t="inlineStr">
+        <is>
+          <t>LcfXrmxht9A</t>
+        </is>
+      </c>
+      <c r="K1079" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21T01:06:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1080" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1080" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【ガチャ動画】佐賀コラボわくわく♪【No.631】</t>
+        </is>
+      </c>
+      <c r="D1080" s="2" t="inlineStr">
+        <is>
+          <t>佐賀コラボガチャをコッペパンとアレツ狙いで回す動画。
+子どもと一緒にわいわい単発連発で挑戦する回。
+20連でコッペパンとアレツの両お目当てを引き当てる。</t>
+        </is>
+      </c>
+      <c r="E1080" s="2" t="inlineStr">
+        <is>
+          <t>・20連でお目当て2体を両方引けた
+・耐えてから引いたのが良かった
+・佐賀コラボがわくわくして楽しい</t>
+        </is>
+      </c>
+      <c r="F1080" s="2" t="inlineStr">
+        <is>
+          <t>・ジュエル残量が少なく不安だった</t>
+        </is>
+      </c>
+      <c r="G1080" s="2" t="inlineStr">
+        <is>
+          <t>・佐賀コラボ
+・ガチャ動画
+・コッペパン
+・アレツ
+・親子配信</t>
+        </is>
+      </c>
+      <c r="H1080" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I1080" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Q6aK7fJ4w7w</t>
+        </is>
+      </c>
+      <c r="J1080" s="2" t="inlineStr">
+        <is>
+          <t>Q6aK7fJ4w7w</t>
+        </is>
+      </c>
+      <c r="K1080" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21T01:06:58Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1080"/>
+  <dimension ref="A1:K1098"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -71231,6 +71231,1193 @@
         </is>
       </c>
     </row>
+    <row r="1081">
+      <c r="A1081" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1081" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1081" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】6体ランキング!!引き方迷子…「完全置物」ダメブロEXタイム&amp;熱のあらゆるエクストラを網羅するサブアタッカーオルロワージュ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1081" s="2" t="inlineStr">
+        <is>
+          <t>タイムは完全置物型サポだがダメブロ半端で総合評価B
+オルロワージュはサブアタッカーとして優秀だが手間と狭さが難点
+無人島延長戦向けで今回スタイル全般に決め手なし</t>
+        </is>
+      </c>
+      <c r="E1081" s="2" t="inlineStr">
+        <is>
+          <t>・タイムはダメブロで守れODサプライヤーとして条件次第で出番あり
+・オルロワージュは属性因卒SSで数値高くサブアタッカー優秀
+・オルロワージュはボルカノより全般的に優秀</t>
+        </is>
+      </c>
+      <c r="F1081" s="2" t="inlineStr">
+        <is>
+          <t>・タイムの中途半端なダメブロで全てが無用化
+・タイムは総合B、動かない条件が整わないと弱い
+・オルロワージュは手間がかかり有効範囲が狭く取り回し悪い
+・今回のスタイルは決め手のウェポンがなく全般に微妙</t>
+        </is>
+      </c>
+      <c r="G1081" s="2" t="inlineStr">
+        <is>
+          <t>・タイム性能考察
+・オルロワージュ考察
+・ダメブロ延長戦
+・エクストラOD
+・置物サポート</t>
+        </is>
+      </c>
+      <c r="H1081" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1081" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RF6wUpFA7x8</t>
+        </is>
+      </c>
+      <c r="J1081" s="2" t="inlineStr">
+        <is>
+          <t>RF6wUpFA7x8</t>
+        </is>
+      </c>
+      <c r="K1081" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1082" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1082" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「無敵4ターン」延長戦を殴りまくれT260G&amp;「全ステバフ1000%」行ける白薔薇姫の全方位火力サポート　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1082" s="2" t="inlineStr">
+        <is>
+          <t>T260Gは無敵4ターン延長戦特化で特攻SSだが総合B
+白薔薇姫は全捨1000%級ステバフで総合Sの高水準
+白薔薇姫は属性縛りと被りやすさが惜しい点</t>
+        </is>
+      </c>
+      <c r="E1082" s="2" t="inlineStr">
+        <is>
+          <t>・T260Gは無人島ダメブロ延長戦で非常に有効、特攻SS
+・白薔薇姫は全捨900%級の爆裂ステバフが魅力で安定
+・白薔薇姫は防御82%と複数属性カバーで総合S</t>
+        </is>
+      </c>
+      <c r="F1082" s="2" t="inlineStr">
+        <is>
+          <t>・T260Gは通常戦での必要性が薄く総合B
+・白薔薇姫は被りやすいエクストラで全力を出しにくい
+・白薔薇姫は属性縛りが面倒で特攻性がないのが惜しい</t>
+        </is>
+      </c>
+      <c r="G1082" s="2" t="inlineStr">
+        <is>
+          <t>・T260G性能
+・白薔薇姫性能
+・無敵4ターン
+・全捨バフ
+・属性縛り</t>
+        </is>
+      </c>
+      <c r="H1082" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1082" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jMuVXwF4QqY</t>
+        </is>
+      </c>
+      <c r="J1082" s="2" t="inlineStr">
+        <is>
+          <t>jMuVXwF4QqY</t>
+        </is>
+      </c>
+      <c r="K1082" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1083" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1083" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「未来に託す継承」最終皇帝女&amp;聖王に次ぐ「全体全ステデバフ」最終皇帝男　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1083" s="2" t="inlineStr">
+        <is>
+          <t>最終皇帝女は上ぶれ依存で火力A・総合Cの技マシン用途
+最終皇帝男は全体全ステデバフが有効で総合A
+技マシン狙いは可能だが本体活用は絶望的</t>
+        </is>
+      </c>
+      <c r="E1083" s="2" t="inlineStr">
+        <is>
+          <t>・最終皇帝男は全捨415%級デバフで環境でもかなり高い
+・最終皇帝男は天秤持ちで螺旋特攻もあり総合A
+・最終皇帝女はエクストラウィーク1.5倍の技マシンとして便利</t>
+        </is>
+      </c>
+      <c r="F1083" s="2" t="inlineStr">
+        <is>
+          <t>・最終皇帝女は上ぶれ依存で火力が安定せず総合C
+・最終皇帝女の技マシンもアドバンテージは小さい
+・両者とも本体活用はかなり絶望的</t>
+        </is>
+      </c>
+      <c r="G1083" s="2" t="inlineStr">
+        <is>
+          <t>・最終皇帝女考察
+・最終皇帝男考察
+・全体デバフ
+・継承技マシン
+・螺旋特攻</t>
+        </is>
+      </c>
+      <c r="H1083" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1083" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yz0bRMl0XRg</t>
+        </is>
+      </c>
+      <c r="J1083" s="2" t="inlineStr">
+        <is>
+          <t>yz0bRMl0XRg</t>
+        </is>
+      </c>
+      <c r="K1083" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1084" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1084" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Wガチャをぶん回した結果、、、！？ #2 『Romancing祭 白薔薇姫厄編＆T260G厄編』＃Shorts</t>
+        </is>
+      </c>
+      <c r="D1084" s="2" t="inlineStr">
+        <is>
+          <t>Wガチャ実況#2、白薔薇姫が第1希望で出て一安心
+最初の10連は出ず50連ごときでは出ない渋さ
+無償も使いこの引き次第では追い課金の流れ</t>
+        </is>
+      </c>
+      <c r="E1084" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇姫が第1希望で早めに出て良かった
+・今のヤンデレ風白薔薇姫のビジュアルが良い</t>
+        </is>
+      </c>
+      <c r="F1084" s="2" t="inlineStr">
+        <is>
+          <t>・最初の10連は出ず渋い
+・50連程度では出ないゲームになりすぎと不満
+・白薔薇姫の後が振るわず追い課金の懸念</t>
+        </is>
+      </c>
+      <c r="G1084" s="2" t="inlineStr">
+        <is>
+          <t>・Wガチャ実況
+・白薔薇姫
+・アセルスアビス
+・無償ジュエル
+・追い課金</t>
+        </is>
+      </c>
+      <c r="H1084" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1084" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0N0AA3Y8dp8</t>
+        </is>
+      </c>
+      <c r="J1084" s="2" t="inlineStr">
+        <is>
+          <t>0N0AA3Y8dp8</t>
+        </is>
+      </c>
+      <c r="K1084" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1085" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1085" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Wガチャをぶん回した結果、、、！？ #1 『Romancing祭 白薔薇姫厄編＆T260G厄編』＃Shorts</t>
+        </is>
+      </c>
+      <c r="D1085" s="2" t="inlineStr">
+        <is>
+          <t>Wガチャ実況#1、優勝ジュエルから回すも全く出ない
+SS率高いのに全部すり抜けで流れが悪い
+ラインナップは良いが引きでテンション下がる</t>
+        </is>
+      </c>
+      <c r="E1085" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャのキャラのラインナップにテンションが上がった</t>
+        </is>
+      </c>
+      <c r="F1085" s="2" t="inlineStr">
+        <is>
+          <t>・優勝ジュエルで回すも何も出ず引きが悪い
+・SS率が高いのに全部すり抜け
+・良い引きの後すぐ悪くなる仕様に不満</t>
+        </is>
+      </c>
+      <c r="G1085" s="2" t="inlineStr">
+        <is>
+          <t>・Wガチャ実況
+・白薔薇姫
+・T260G
+・すり抜け
+・確定枠</t>
+        </is>
+      </c>
+      <c r="H1085" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1085" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0eI_VD1rhzE</t>
+        </is>
+      </c>
+      <c r="J1085" s="2" t="inlineStr">
+        <is>
+          <t>0eI_VD1rhzE</t>
+        </is>
+      </c>
+      <c r="K1085" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1086" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1086" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Wガチャをぶん回した結果、、、！？ #4 『Romancing祭 白薔薇姫厄編＆T260G厄編』＃Shorts</t>
+        </is>
+      </c>
+      <c r="D1086" s="2" t="inlineStr">
+        <is>
+          <t>Wガチャ実況#4、心折れる引きでオルロワージュ被り
+やっとSSも目当ての2体が出ず萎える
+最終皇帝かT260Gが出ないとコンプ不可</t>
+        </is>
+      </c>
+      <c r="E1086" s="2" t="inlineStr">
+        <is>
+          <t>・片方は2体出た</t>
+        </is>
+      </c>
+      <c r="F1086" s="2" t="inlineStr">
+        <is>
+          <t>・引きがむちゃくちゃで心が折れた
+・2枚抜き狙いで被って萎える
+・目当ての2体が出ずコンプに課金が必要で不満</t>
+        </is>
+      </c>
+      <c r="G1086" s="2" t="inlineStr">
+        <is>
+          <t>・Wガチャ実況
+・オルロワージュ
+・最終皇帝
+・コンプリート
+・被り</t>
+        </is>
+      </c>
+      <c r="H1086" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1086" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3GNn1u0ITSk</t>
+        </is>
+      </c>
+      <c r="J1086" s="2" t="inlineStr">
+        <is>
+          <t>3GNn1u0ITSk</t>
+        </is>
+      </c>
+      <c r="K1086" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1087" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1087" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Wガチャをぶん回した結果、、、！？ #5 『Romancing祭 白薔薇姫厄編＆T260G厄編』＃Shorts</t>
+        </is>
+      </c>
+      <c r="D1087" s="2" t="inlineStr">
+        <is>
+          <t>Wガチャ実況#5、天井近くステップ7でギリギリ確保
+黒いロボT260Gはかっこよくスキン価値も高い
+引きは悪すぎたが最終的にコンプ達成</t>
+        </is>
+      </c>
+      <c r="E1087" s="2" t="inlineStr">
+        <is>
+          <t>・T260Gの黒いボディがかっこよくスキン価値も高い
+・ステップ7で無事お目当てを確保しコンプ達成</t>
+        </is>
+      </c>
+      <c r="F1087" s="2" t="inlineStr">
+        <is>
+          <t>・今回は引きが悪すぎた
+・確定枠頼みでギリギリの綱渡りだった</t>
+        </is>
+      </c>
+      <c r="G1087" s="2" t="inlineStr">
+        <is>
+          <t>・Wガチャ実況
+・天井ステップ7
+・T260G
+・確定枠
+・コンプ達成</t>
+        </is>
+      </c>
+      <c r="H1087" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1087" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=P0ZfQ-xLReM</t>
+        </is>
+      </c>
+      <c r="J1087" s="2" t="inlineStr">
+        <is>
+          <t>P0ZfQ-xLReM</t>
+        </is>
+      </c>
+      <c r="K1087" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1088" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1088" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Wガチャをぶん回した結果、、、！？『Romancing祭 白薔薇姫厄編＆T260G厄編』【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1088" s="2" t="inlineStr">
+        <is>
+          <t>み城のWガチャ本編、白薔薇姫厄編とT260G厄編を回す
+引きが悪くコンプするつもりはなかったが結果的にコンプ
+目当ては確保でき最終的には良かったと総括</t>
+        </is>
+      </c>
+      <c r="E1088" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャのキャラのラインナップにテンションが上がった
+・お目当てをゲットでき最終的には良かった
+・T260Gの黒いロボがかっこよくスキン価値も高い</t>
+        </is>
+      </c>
+      <c r="F1088" s="2" t="inlineStr">
+        <is>
+          <t>・引きが悪すぎて演出もひどく文句しか出ない
+・SS率が高いのに全部すり抜け
+・課金した分の対価が欲しいという不満</t>
+        </is>
+      </c>
+      <c r="G1088" s="2" t="inlineStr">
+        <is>
+          <t>・Wガチャ本編
+・白薔薇姫厄編
+・T260G厄編
+・最終皇帝
+・コンプ</t>
+        </is>
+      </c>
+      <c r="H1088" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1088" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pFMqErR4IKQ</t>
+        </is>
+      </c>
+      <c r="J1088" s="2" t="inlineStr">
+        <is>
+          <t>pFMqErR4IKQ</t>
+        </is>
+      </c>
+      <c r="K1088" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1089" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1089" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Wガチャをぶん回した結果、、、！？ #3 『Romancing祭 白薔薇姫厄編＆T260G厄編』＃Shorts</t>
+        </is>
+      </c>
+      <c r="D1089" s="2" t="inlineStr">
+        <is>
+          <t>Wガチャ実況#3、演出も出目も終わっていてひどい
+下ぶれが早すぎて喋ることもなくなる惨状
+リアクションも取れないほどのクソ引き</t>
+        </is>
+      </c>
+      <c r="E1089" s="2" t="inlineStr"/>
+      <c r="F1089" s="2" t="inlineStr">
+        <is>
+          <t>・演出がひどく爆発演出も出ない
+・下ぶれが早すぎて文句しか出ない
+・出目が悪くリアクションも取れない</t>
+        </is>
+      </c>
+      <c r="G1089" s="2" t="inlineStr">
+        <is>
+          <t>・Wガチャ実況
+・演出批判
+・下ぶれ
+・T260G
+・すり抜け</t>
+        </is>
+      </c>
+      <c r="H1089" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1089" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=q8icEhYmP0g</t>
+        </is>
+      </c>
+      <c r="J1089" s="2" t="inlineStr">
+        <is>
+          <t>q8icEhYmP0g</t>
+        </is>
+      </c>
+      <c r="K1089" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1090" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1090" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ゲキ遅！！６人全員性能確認★尖がりすぎるアビス２人【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1090" s="2" t="inlineStr">
+        <is>
+          <t>つむつむの6体性能確認、尖りすぎるアビス2人が注目
+白薔薇姫は使いやすく最終皇帝女は技マシン超まし評価
+最終皇帝男はワザマシンが半端なく強い印象</t>
+        </is>
+      </c>
+      <c r="E1090" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇姫は使えそうで欲しい、原産系より火力高め
+・最終皇帝男のワザマシンのバフが半端なく強い
+・オルロワージュは継承すると強そう
+・T260Gは4ターン火力とかっこよさで欲しい</t>
+        </is>
+      </c>
+      <c r="F1090" s="2" t="inlineStr">
+        <is>
+          <t>・タイムはフズしかなくコース級で微妙
+・最終皇帝女はゴリゴリのアタッカーで技マシン用途どまり
+・T260Gは4ターン限定で使いどころが限られる</t>
+        </is>
+      </c>
+      <c r="G1090" s="2" t="inlineStr">
+        <is>
+          <t>・6体性能確認
+・白薔薇姫
+・最終皇帝男女
+・オルロワージュ継承
+・T260G4ターン火力</t>
+        </is>
+      </c>
+      <c r="H1090" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1090" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2JNwpauVe-I</t>
+        </is>
+      </c>
+      <c r="J1090" s="2" t="inlineStr">
+        <is>
+          <t>2JNwpauVe-I</t>
+        </is>
+      </c>
+      <c r="K1090" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1091" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1091" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】前回ガチャ動画1分→今回20分越え超次元ガチャバトルに突入【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1091" s="2" t="inlineStr">
+        <is>
+          <t>つむつむのガチャ実況、白薔薇姫が本命で神引き狙い
+白薔薇姫オルロT260G最終皇帝男を無事獲得
+悪い顔の白薔薇姫イラストに大興奮</t>
+        </is>
+      </c>
+      <c r="E1091" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇姫は火力とサポート両立で本命
+・目当てを一通り引けて神引き
+・白薔薇姫の悪い顔のイラストが最高
+・T260Gのファンネル演出がかっこいい</t>
+        </is>
+      </c>
+      <c r="F1091" s="2" t="inlineStr">
+        <is>
+          <t>・無償ですり抜けが多く一時期は渋かった
+・最終皇帝男は継承技マシン程度の扱い</t>
+        </is>
+      </c>
+      <c r="G1091" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ実況
+・白薔薇姫
+・オルロワージュ
+・T260G
+・神引き</t>
+        </is>
+      </c>
+      <c r="H1091" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1091" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k-G6OPyY3N4</t>
+        </is>
+      </c>
+      <c r="J1091" s="2" t="inlineStr">
+        <is>
+          <t>k-G6OPyY3N4</t>
+        </is>
+      </c>
+      <c r="K1091" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1092" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1092" s="2" t="inlineStr">
+        <is>
+          <t>#ロマサガrs  了解！トランザム！</t>
+        </is>
+      </c>
+      <c r="D1092" s="2" t="inlineStr">
+        <is>
+          <t>T260Gのトランザム演出を試して超火力に大興奮
+GNソードやVマMAXの演出がかっこいい
+行動回数を意識した多め行動で真価を発揮</t>
+        </is>
+      </c>
+      <c r="E1092" s="2" t="inlineStr">
+        <is>
+          <t>・T260Gのトランザムが超火力でやばい
+・GNソードやVマMAXの演出がかっこいい</t>
+        </is>
+      </c>
+      <c r="F1092" s="2" t="inlineStr"/>
+      <c r="G1092" s="2" t="inlineStr">
+        <is>
+          <t>・T260Gトランザム
+・超火力
+・演出
+・行動回数</t>
+        </is>
+      </c>
+      <c r="H1092" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1092" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=v8KwW4O4S7I</t>
+        </is>
+      </c>
+      <c r="J1092" s="2" t="inlineStr">
+        <is>
+          <t>v8KwW4O4S7I</t>
+        </is>
+      </c>
+      <c r="K1092" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1093" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1093" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】想像以上！3人同時に使ったらやばかった【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1093" s="2" t="inlineStr">
+        <is>
+          <t>白薔薇姫オルロT260Gの3人同時運用が想像以上に強い
+黒薔薇姫とオルロワージュの相性が抜群
+バフ量過多で一度失敗も行動回数調整で解決</t>
+        </is>
+      </c>
+      <c r="E1093" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇姫オルロT260Gの3人は相性抜群で強い
+・黒薔薇姫とオルロワージュの相性が良く即死級
+・弱点をつけた黒薔薇姫の火力がやばい</t>
+        </is>
+      </c>
+      <c r="F1093" s="2" t="inlineStr">
+        <is>
+          <t>・バフ量が多すぎて一度編成が失敗した
+・キャラ育成がまだ終わっておらず雑編成だった</t>
+        </is>
+      </c>
+      <c r="G1093" s="2" t="inlineStr">
+        <is>
+          <t>・3人同時運用
+・黒薔薇姫
+・オルロワージュ相性
+・トランザム
+・バフ量調整</t>
+        </is>
+      </c>
+      <c r="H1093" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1093" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zeS_2xMYsro</t>
+        </is>
+      </c>
+      <c r="J1093" s="2" t="inlineStr">
+        <is>
+          <t>zeS_2xMYsro</t>
+        </is>
+      </c>
+      <c r="K1093" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1094" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C1094" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみ編 第7話 後編 公開記念Wガチャ★★螺旋は！？</t>
+        </is>
+      </c>
+      <c r="D1094" s="2" t="inlineStr">
+        <is>
+          <t>もんでるのWガチャ配信、性能を見て全体的にがっかり
+オルロは縛りきつく女帝はゴミ、タイムは最低評価
+サルインの方が良く今回は次のガチャ見て判断</t>
+        </is>
+      </c>
+      <c r="E1094" s="2" t="inlineStr">
+        <is>
+          <t>・最終皇帝男はデバフしつつ火力も出て悪くない
+・T260Gのファンネル演出とガンダム感がやばい
+・白薔薇姫は軽減82%と波紋攻撃で悪くはない</t>
+        </is>
+      </c>
+      <c r="F1094" s="2" t="inlineStr">
+        <is>
+          <t>・オルロワージュは縛りきつく新しさもなく使わない
+・最終皇帝女帝は弱くゴミすぎて泣ける
+・タイムは今回最低評価、2ターンに1回ダメブロが不満
+・全体的に魅力がなくどれも引きたくない
+・豪体環境ではサルインの方が最強クラスで優秀</t>
+        </is>
+      </c>
+      <c r="G1094" s="2" t="inlineStr">
+        <is>
+          <t>・Wガチャ配信
+・オルロワージュ
+・最終皇帝女帝
+・タイム評価
+・サルイン比較</t>
+        </is>
+      </c>
+      <c r="H1094" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I1094" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gx1hoio0mZU</t>
+        </is>
+      </c>
+      <c r="J1094" s="2" t="inlineStr">
+        <is>
+          <t>gx1hoio0mZU</t>
+        </is>
+      </c>
+      <c r="K1094" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B1095" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1095" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】全員尖りまくりな超特化型ガチャ！？T260G【厄】編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1095" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーのT260G編性能チェック、全員超特化型
+タイムは攻撃せぬ置物、女帝は純アタッカー兼技マシン
+T260Gは短期決戦特化で使いこなしが難しい</t>
+        </is>
+      </c>
+      <c r="E1095" s="2" t="inlineStr">
+        <is>
+          <t>・タイムは攻撃しないためレイドや無人島のタイム短縮に有用
+・最終皇帝女の技マシンが超優秀で今後も刺さる
+・T260GはVドーム中かなりの火力で全体単体どちらも強い</t>
+        </is>
+      </c>
+      <c r="F1095" s="2" t="inlineStr">
+        <is>
+          <t>・タイムはぶっ壊れではなくエクストラフォースがない
+・最終皇帝女はサポート性能ゼロの純アタッカー
+・T260GはVエンドで4ターン後に使い物にならなくなる
+・T260Gは使いこなすのがかなり難しい</t>
+        </is>
+      </c>
+      <c r="G1095" s="2" t="inlineStr">
+        <is>
+          <t>・T260G編チェック
+・タイム
+・最終皇帝女
+・置物サポート
+・短期決戦</t>
+        </is>
+      </c>
+      <c r="H1095" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1095" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B4-Rygxr7Zo</t>
+        </is>
+      </c>
+      <c r="J1095" s="2" t="inlineStr">
+        <is>
+          <t>B4-Rygxr7Zo</t>
+        </is>
+      </c>
+      <c r="K1095" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1096" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1096" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはり話題の黒薔薇姫は強力！？白薔薇姫【厄】編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1096" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーの白薔薇姫編チェック、話題の黒薔薇姫は強力
+オルロは待機型で継承必須、最終皇帝男は邪魔性能
+白薔薇姫は強いが陰属性飽和で必須ではない</t>
+        </is>
+      </c>
+      <c r="E1096" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇姫は剣アタッカー兼サポートで軽減も高く強力
+・オルロワージュは熱陰編成なら非常に優秀なサポーター
+・最終皇帝男の技マシンは今後の継承用に良い</t>
+        </is>
+      </c>
+      <c r="F1096" s="2" t="inlineStr">
+        <is>
+          <t>・オルロワージュは待機型で継承必須、属性も絞られる
+・最終皇帝男はシンプルな性能で無理して取る感じではない
+・白薔薇姫は陰属性キャラが飽和しており必須案件ではない</t>
+        </is>
+      </c>
+      <c r="G1096" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇姫編チェック
+・オルロワージュ
+・最終皇帝男
+・黒薔薇姫
+・陰属性飽和</t>
+        </is>
+      </c>
+      <c r="H1096" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1096" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DjRhCZynXrU</t>
+        </is>
+      </c>
+      <c r="J1096" s="2" t="inlineStr">
+        <is>
+          <t>DjRhCZynXrU</t>
+        </is>
+      </c>
+      <c r="K1096" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1097" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1097" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】白薔薇姫〔厄〕能力値早見表〜待ちわびた私の…能力…とくと見よ‼️</t>
+        </is>
+      </c>
+      <c r="D1097" s="2" t="inlineStr">
+        <is>
+          <t>チャムの白薔薇姫〔厄〕能力値早見表、期待以上の性能
+編成難易度が優しく軽減82%・術91%と高水準
+サイバーと比較しても遜色なく獲得必須と評価</t>
+        </is>
+      </c>
+      <c r="E1097" s="2" t="inlineStr">
+        <is>
+          <t>・編成難易度が優しく斬パーティ因卒だけで機能
+・味方軽減82%・術軽減91%とめちゃくちゃ高い
+・攻撃強化やデバフ量が高く本人火力もアタッカー級
+・高難度も井戸も獲得必須の性能</t>
+        </is>
+      </c>
+      <c r="F1097" s="2" t="inlineStr">
+        <is>
+          <t>・エクストラフォースはサイバーに軍配が上がる</t>
+        </is>
+      </c>
+      <c r="G1097" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇姫早見表
+・編成難易度
+・軽減82%
+・デバフ性能
+・サイバー比較</t>
+        </is>
+      </c>
+      <c r="H1097" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1097" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CGOxvPM6tfM</t>
+        </is>
+      </c>
+      <c r="J1097" s="2" t="inlineStr">
+        <is>
+          <t>CGOxvPM6tfM</t>
+        </is>
+      </c>
+      <c r="K1097" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1098" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1098" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベント解説 注意点 11秒周回編成の紹介【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1098" s="2" t="inlineStr">
+        <is>
+          <t>暦読み編後編イベント解説と11秒周回編成の紹介
+交換書で必要分を取り切ったら制圧戦へ移行推奨
+武器連磨はアビリティ追加待ちで保留が無難</t>
+        </is>
+      </c>
+      <c r="E1098" s="2" t="inlineStr">
+        <is>
+          <t>・交換書で必要なものを取り切れば効率的に終えられる
+・11秒周回編成でスケット等を効率周回できる</t>
+        </is>
+      </c>
+      <c r="F1098" s="2" t="inlineStr">
+        <is>
+          <t>・覚醒の鎧素材は今回だけでは集めきれない
+・進化の奇跡位置のためだけに残るのは非推奨
+・武器連磨は28日のアビリティ追加待ちで今やると損の可能性</t>
+        </is>
+      </c>
+      <c r="G1098" s="2" t="inlineStr">
+        <is>
+          <t>・イベント解説
+・11秒周回編成
+・覚醒の鎧進化素材
+・制圧戦
+・武器連磨</t>
+        </is>
+      </c>
+      <c r="H1098" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1098" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xNd8AGJGh88</t>
+        </is>
+      </c>
+      <c r="J1098" s="2" t="inlineStr">
+        <is>
+          <t>xNd8AGJGh88</t>
+        </is>
+      </c>
+      <c r="K1098" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22T05:22:35Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1098"/>
+  <dimension ref="A1:K1108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72418,6 +72418,663 @@
         </is>
       </c>
     </row>
+    <row r="1099">
+      <c r="A1099" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B1099" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1099" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「陰独占!?」激動8月最新Tier発表!!ドラクエコラボ以後の上位41体の環境変化を調査　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1099" s="2" t="inlineStr">
+        <is>
+          <t>8月最新の環境ティアを上位41体で整理
+属性縛りは終焉、仕上がったスタイルを狙え
+9月の祭り前、すぐ引かず引きつけて回す</t>
+        </is>
+      </c>
+      <c r="E1099" s="2" t="inlineStr">
+        <is>
+          <t>・コッぺパンは環境を変えた汎用性と唯一性
+・サルーインは再来のダメブロまでカバー
+・過動は無人島で塗り替えられない耐久
+・ビクトールは捨てどころなしの好スタイル</t>
+        </is>
+      </c>
+      <c r="F1099" s="2" t="inlineStr">
+        <is>
+          <t>・女神やミスリードは環境から消える直前
+・エミリア型は普通に殴った方が早い
+・ウンディネやミドは使用期限切れ
+・デスマシーンは単体ボス多く出番少ない</t>
+        </is>
+      </c>
+      <c r="G1099" s="2" t="inlineStr">
+        <is>
+          <t>・環境ティア表
+・属性縛りの終焉
+・コッぺパン
+・ターミン
+・9月の祭り</t>
+        </is>
+      </c>
+      <c r="H1099" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1099" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vCxA8DxZbzw</t>
+        </is>
+      </c>
+      <c r="J1099" s="2" t="inlineStr">
+        <is>
+          <t>vCxA8DxZbzw</t>
+        </is>
+      </c>
+      <c r="K1099" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24T05:44:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B1100" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1100" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　3章0話クリア達成　次戦に向けて　キャラ育成していこう！　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1100" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープ3章0話クリア後の育成配信
+SSR以外を中心に育成し土属性の弱さに苦戦
+アンティ（螺旋回路的コンテンツ）に挑戦</t>
+        </is>
+      </c>
+      <c r="E1100" s="2" t="inlineStr">
+        <is>
+          <t>・リアンやスケットが強い
+・SSRを入れると戦闘がだいぶ楽
+・面白くてハマっているゲーム</t>
+        </is>
+      </c>
+      <c r="F1100" s="2" t="inlineStr">
+        <is>
+          <t>・土属性キャラが圧倒的に弱い
+・序盤は素早さが遅いとネック
+・ペーターやおじいちゃんは行動が遅い</t>
+        </is>
+      </c>
+      <c r="G1100" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープ
+・キャラ育成
+・土属性が弱い
+・リアン
+・スケット
+・アンティの塔</t>
+        </is>
+      </c>
+      <c r="H1100" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1_gKdi_lRdw</t>
+        </is>
+      </c>
+      <c r="J1100" s="2" t="inlineStr">
+        <is>
+          <t>1_gKdi_lRdw</t>
+        </is>
+      </c>
+      <c r="K1100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24T05:44:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B1101" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1101" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始324日目記録　念願　また一歩前進へ</t>
+        </is>
+      </c>
+      <c r="D1101" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣プレイ324日目の進捗報告
+新規5武将入手、島津義弘のバフに期待
+特別市場と開発で進捗が大きく前進</t>
+        </is>
+      </c>
+      <c r="E1101" s="2" t="inlineStr">
+        <is>
+          <t>・島津義弘は攻撃上昇と会心率上昇のバフで当たり
+・松は戦法威力加算で戦力が変わった
+・特別市場は移転制限なしで非常に便利</t>
+        </is>
+      </c>
+      <c r="F1101" s="2" t="inlineStr">
+        <is>
+          <t>・開発の整備枠が時間かかりレベルが上がりづらい
+・バフが足りず火力を出し切れない</t>
+        </is>
+      </c>
+      <c r="G1101" s="2" t="inlineStr">
+        <is>
+          <t>・信長の野望出陣
+・武将入手
+・島津義弘
+・特別市場
+・開発レベル
+・3周年</t>
+        </is>
+      </c>
+      <c r="H1101" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jQDklXcm10w</t>
+        </is>
+      </c>
+      <c r="J1101" s="2" t="inlineStr">
+        <is>
+          <t>jQDklXcm10w</t>
+        </is>
+      </c>
+      <c r="K1101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24T05:44:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B1102" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1102" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SR 騎士バウ 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1102" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSR騎士バウ武装アニメ
+武装演出を収録したShorts動画
+字幕情報はごく僅か</t>
+        </is>
+      </c>
+      <c r="E1102" s="2" t="inlineStr"/>
+      <c r="F1102" s="2" t="inlineStr"/>
+      <c r="G1102" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・騎士バウ
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H1102" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JBDcxCUas2s</t>
+        </is>
+      </c>
+      <c r="J1102" s="2" t="inlineStr">
+        <is>
+          <t>JBDcxCUas2s</t>
+        </is>
+      </c>
+      <c r="K1102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24T05:44:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B1103" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1103" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】SSS環境支配級変動！最新キャラランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1103" s="2" t="inlineStr">
+        <is>
+          <t>日曜恒例の最新キャラランキング配信
+環境支配級にコッぺパンとターミンを追加
+白バラSS、オルロワ・最終工程女はS評価</t>
+        </is>
+      </c>
+      <c r="E1103" s="2" t="inlineStr">
+        <is>
+          <t>・コッぺパンはどこでも使えるバランスブレイカー級
+・オルロワは継承で9回行動しSS級
+・白バラ姫は文句なしの性能
+・T260Gは4ターン無双の火力</t>
+        </is>
+      </c>
+      <c r="F1103" s="2" t="inlineStr">
+        <is>
+          <t>・タイムは自身が殴れず2.25倍まで3ターンで遅い
+・最終工程男は防御軽減なくエクストラフォース欲しい
+・ピンクパンチは女性編成と噛み合わず降格</t>
+        </is>
+      </c>
+      <c r="G1103" s="2" t="inlineStr">
+        <is>
+          <t>・最新キャラランキング
+・環境支配級
+・コッぺパン
+・オルロワーズ
+・白バラ姫
+・タイム</t>
+        </is>
+      </c>
+      <c r="H1103" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pdzjI68I92k</t>
+        </is>
+      </c>
+      <c r="J1103" s="2" t="inlineStr">
+        <is>
+          <t>pdzjI68I92k</t>
+        </is>
+      </c>
+      <c r="K1103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24T05:44:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B1104" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1104" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】オルロワ＆タイム検証動画★リスナーリクエストvol1【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1104" s="2" t="inlineStr">
+        <is>
+          <t>リスナー要望でオルロワ＆タイムを検証
+ドラクエサルインは因列でオルロワと好相性
+タイムは幻統上の火力ピースとして優秀</t>
+        </is>
+      </c>
+      <c r="E1104" s="2" t="inlineStr">
+        <is>
+          <t>・ドラクエサルインはオルロワと相性最高で白醒推奨
+・タイムの2.25倍エクストラフォースが魅力
+・リラが思った以上に強かった</t>
+        </is>
+      </c>
+      <c r="F1104" s="2" t="inlineStr">
+        <is>
+          <t>・水属性の攻撃陣や体への対処が課題</t>
+        </is>
+      </c>
+      <c r="G1104" s="2" t="inlineStr">
+        <is>
+          <t>・オルロワーズ
+・ドラクエサルイン
+・タイム
+・幻の統べる者
+・リラ</t>
+        </is>
+      </c>
+      <c r="H1104" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vklJSNsme_8</t>
+        </is>
+      </c>
+      <c r="J1104" s="2" t="inlineStr">
+        <is>
+          <t>vklJSNsme_8</t>
+        </is>
+      </c>
+      <c r="K1104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24T05:44:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B1105" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1105" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはりあの2キャラがダントツの当たり！？最新版確保優先度ランキング【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1105" s="2" t="inlineStr">
+        <is>
+          <t>現行ガチャの確保優先度ランキング
+最優先はコッぺパンとターミンネシマルカ
+8/28生放送と大型イベント前で引き時が難しい</t>
+        </is>
+      </c>
+      <c r="E1105" s="2" t="inlineStr">
+        <is>
+          <t>・コッぺパンは無人島で最優先級の性能
+・サルインは癖がなく単純に使いやすい
+・フレイヤは属性不問で汎用性が高い
+・オルロワはサポーター最強格</t>
+        </is>
+      </c>
+      <c r="F1105" s="2" t="inlineStr">
+        <is>
+          <t>・T260Gは3〜4ターン限定でピンポイントすぎる
+・最終工程女はスタンバイ3で使いにくい
+・マキビは高難度対応だが使う場面が少ない</t>
+        </is>
+      </c>
+      <c r="G1105" s="2" t="inlineStr">
+        <is>
+          <t>・確保優先度
+・コッぺパン
+・オルロワーズ
+・白原姫アビス
+・大型イベント前</t>
+        </is>
+      </c>
+      <c r="H1105" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x9_Z6M_fRfY</t>
+        </is>
+      </c>
+      <c r="J1105" s="2" t="inlineStr">
+        <is>
+          <t>x9_Z6M_fRfY</t>
+        </is>
+      </c>
+      <c r="K1105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24T05:44:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B1106" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1106" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第134回アウラウネたちの井戸 ~9体井戸考察 ~活躍必須キャラ19体&amp;ベスト6編成紹介</t>
+        </is>
+      </c>
+      <c r="D1106" s="2" t="inlineStr">
+        <is>
+          <t>8/24開始の第134回アウラウネの井戸を考察
+打・陰の全体アタッカーが乏しく編成難航
+活躍必須19体とベスト6編成を紹介</t>
+        </is>
+      </c>
+      <c r="E1106" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズは今回ほぼ必須のアタッカー
+・アレツは範囲攻撃豊富で手数少ない
+・黒エは陰属性全体アタッカーの第一人者</t>
+        </is>
+      </c>
+      <c r="F1106" s="2" t="inlineStr">
+        <is>
+          <t>・交代とHP強化で短期アタッカーは難しい
+・打・陰の全体アタッカーがかなり乏しい
+・敵の強さ不明で編成がかなり迷う</t>
+        </is>
+      </c>
+      <c r="G1106" s="2" t="inlineStr">
+        <is>
+          <t>・アウラウネの井戸
+・打属性弱点
+・9体井戸
+・ヒューズ
+・黒エ
+・編成考察</t>
+        </is>
+      </c>
+      <c r="H1106" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RdzdNGt44tA</t>
+        </is>
+      </c>
+      <c r="J1106" s="2" t="inlineStr">
+        <is>
+          <t>RdzdNGt44tA</t>
+        </is>
+      </c>
+      <c r="K1106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24T05:44:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B1107" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1107" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】カン＝ケルゥの井戸〜1ターンクリアの軌跡‼️【8位の編成と立ち回りをきめ細かく紹介】</t>
+        </is>
+      </c>
+      <c r="D1107" s="2" t="inlineStr">
+        <is>
+          <t>カンケルゥの井戸で8位の1ターンクリア編成紹介
+サイバ暦みヒューズターミンサの全員フルスペック
+各キャラの追撃発動条件と立ち回りを解説</t>
+        </is>
+      </c>
+      <c r="E1107" s="2" t="inlineStr">
+        <is>
+          <t>・全員フルスペックで技術魂が噛み合う1ターン編成</t>
+        </is>
+      </c>
+      <c r="F1107" s="2" t="inlineStr">
+        <is>
+          <t>・自分の魂はまだ育成が必要なキャラも多い</t>
+        </is>
+      </c>
+      <c r="G1107" s="2" t="inlineStr">
+        <is>
+          <t>・カンケルゥの井戸
+・1ターンクリア
+・8位編成
+・追撃発動条件
+・継承</t>
+        </is>
+      </c>
+      <c r="H1107" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=prRyqc2PyV8</t>
+        </is>
+      </c>
+      <c r="J1107" s="2" t="inlineStr">
+        <is>
+          <t>prRyqc2PyV8</t>
+        </is>
+      </c>
+      <c r="K1107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24T05:44:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B1108" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1108" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「T260G[厄] 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1108" s="2" t="inlineStr">
+        <is>
+          <t>ロマフェスT260Gアビス編3体の性能考察
+T260GアビスはB+、最終工程女はC評価
+タイムはサポート特化でB+評価</t>
+        </is>
+      </c>
+      <c r="E1108" s="2" t="inlineStr">
+        <is>
+          <t>・T260Gアビスの4ターン無敵は唯一性がありB+
+・タイムは置き物・レイド・幻統上で活躍しそうB+</t>
+        </is>
+      </c>
+      <c r="F1108" s="2" t="inlineStr">
+        <is>
+          <t>・T260Gは代償ダメージと発動条件で扱いづらい
+・最終工程女は火ダメ軽減0・単体火力低めでC評価
+・タイムは火力0で手数不足の場面あり</t>
+        </is>
+      </c>
+      <c r="G1108" s="2" t="inlineStr">
+        <is>
+          <t>・T260Gアビス
+・最終工程女
+・タイム
+・ランク付け
+・4ターン無敵</t>
+        </is>
+      </c>
+      <c r="H1108" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ilepb6FQgz8</t>
+        </is>
+      </c>
+      <c r="J1108" s="2" t="inlineStr">
+        <is>
+          <t>ilepb6FQgz8</t>
+        </is>
+      </c>
+      <c r="K1108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24T05:44:00Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1108"/>
+  <dimension ref="A1:K1118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -73075,6 +73075,682 @@
         </is>
       </c>
     </row>
+    <row r="1109">
+      <c r="A1109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1109" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1109" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「最弱月」〇〇前は超不遇!!月刊不遇&amp;MVPランキング!!2026年2月振り返り→全くインフレしない1ヶ月　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1109" s="2" t="inlineStr">
+        <is>
+          <t>2026年2月は大決戦祭前で全くインフレしない不遇月。
+ほとんどが置き物運用で必須級スタイルはゼロ。
+決戦祭前月のガチャは外れになりやすいと考察。</t>
+        </is>
+      </c>
+      <c r="E1109" s="2" t="inlineStr">
+        <is>
+          <t>・げさん/黒バラは全ステバフ爆裂で強力
+・リラは唯一聞きづらさがあった
+・ディーバは隙のない作り
+・ウンディネは仕上がった副属性
+・8月ガチャは思い切って引いてよし</t>
+        </is>
+      </c>
+      <c r="F1109" s="2" t="inlineStr">
+        <is>
+          <t>・2月スタイルは記憶に残らない置き物ばかり
+・シェラハが毎回弱い
+・エリザベートは強くなる要素なし
+・無限バフスタイルが全く使えず
+・決戦祭前月のガチャは外れやすい
+・9月の祭りはパッとしない可能性</t>
+        </is>
+      </c>
+      <c r="G1109" s="2" t="inlineStr">
+        <is>
+          <t>・2月不遇月振り返り
+・決戦祭前は外れ
+・月刊MVP
+・置き物スタイル
+・黒バラ原型げさん</t>
+        </is>
+      </c>
+      <c r="H1109" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KeedVjHIMww</t>
+        </is>
+      </c>
+      <c r="J1109" s="2" t="inlineStr">
+        <is>
+          <t>KeedVjHIMww</t>
+        </is>
+      </c>
+      <c r="K1109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:08:48Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B1110" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1110" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「終了直前でスルー」週間ランキング!!厄編VSターミン編→15体5ガチャランキング!!最新スタイルの最強を決める比較検討会→2026年8月23日版　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1110" s="2" t="inlineStr">
+        <is>
+          <t>最新15体5ガチャの相対ランキング比較検討会。
+ターミン&amp;コッペパンは取得推奨、白薔薇姫は無人島用。
+サルウインだけ終了直前で決断が必要。</t>
+        </is>
+      </c>
+      <c r="E1110" s="2" t="inlineStr">
+        <is>
+          <t>・コッペパンは長期戦・無人島で強い
+・ターミンは総合力で軍配・編成の締めに便利
+・白薔薇姫は高ステバフで早抜け対応
+・ノアは天品持ちで無人島適正
+・アレツは連打力が結構強い</t>
+        </is>
+      </c>
+      <c r="F1110" s="2" t="inlineStr">
+        <is>
+          <t>・フレイヤ&amp;マキビはプラチナ級で性能が渋い
+・タイム君は攻撃せずメリット薄い
+・最終工程さんはアタッカーとして成り立たない
+・汎用性だけで上位にすると結局使われない
+・シャムマベルは必然性がなく出番待ち</t>
+        </is>
+      </c>
+      <c r="G1110" s="2" t="inlineStr">
+        <is>
+          <t>・週間比較検討会
+・サルウイン決断
+・ターミン/コッペパン推奨
+・白薔薇姫は無人島用
+・フレイヤ/マキビ最下</t>
+        </is>
+      </c>
+      <c r="H1110" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TuiXmLulyBU</t>
+        </is>
+      </c>
+      <c r="J1110" s="2" t="inlineStr">
+        <is>
+          <t>TuiXmLulyBU</t>
+        </is>
+      </c>
+      <c r="K1110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:08:48Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1111" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1111" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　激つよ3章0話　108星で挑む　乱凛天撃破！　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1111" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープ3章0話の乱凛天3体を討伐。
+限定SSR不使用・通常攻撃主体でノックダウンを狙う。
+青龍を温存し全体攻撃を凌ぐ攻略。</t>
+        </is>
+      </c>
+      <c r="E1111" s="2" t="inlineStr">
+        <is>
+          <t>・通常攻撃主体だと格段に倒しやすい
+・限定SSR無しでもクリア可能
+・青龍を温存して全体攻撃を凌げる</t>
+        </is>
+      </c>
+      <c r="F1111" s="2" t="inlineStr">
+        <is>
+          <t>・乱凛天は3章0話で序盤最難関
+・ランの攻撃5回無効化が厄介
+・リンリの反撃75%で奥義に注意
+・ランの火ダメ無効化が面倒</t>
+        </is>
+      </c>
+      <c r="G1111" s="2" t="inlineStr">
+        <is>
+          <t>・幻水スターリープ
+・3章0話乱凛天
+・通常攻撃主体攻略
+・限定SSR不使用
+・ノックダウン狙い</t>
+        </is>
+      </c>
+      <c r="H1111" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SD9tFi3J1qA</t>
+        </is>
+      </c>
+      <c r="J1111" s="2" t="inlineStr">
+        <is>
+          <t>SD9tFi3J1qA</t>
+        </is>
+      </c>
+      <c r="K1111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:08:48Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1112" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1112" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SR 闘士ドライセン 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1112" s="2" t="inlineStr">
+        <is>
+          <t>GジェネエターナルのSR闘士ドライセン武装アニメ紹介Short。
+ボイス付きの武装モーション演出を短尺で披露。
+#Shorts の演出クリップ。</t>
+        </is>
+      </c>
+      <c r="E1112" s="2" t="inlineStr"/>
+      <c r="F1112" s="2" t="inlineStr"/>
+      <c r="G1112" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・闘士ドライセン
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H1112" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NKRKXB46g6M</t>
+        </is>
+      </c>
+      <c r="J1112" s="2" t="inlineStr">
+        <is>
+          <t>NKRKXB46g6M</t>
+        </is>
+      </c>
+      <c r="K1112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:08:48Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B1113" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1113" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今やるべきことはこれだ！新イベントの確認と絶対に忘れてはいけない注意喚起！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1113" s="2" t="inlineStr">
+        <is>
+          <t>継承の代償後編イベントと制圧戦の同時開催を解説。
+進化素材や専用装備の取り逃し注意喚起が主眼。
+制圧戦周回と11秒周回のやり方も紹介。</t>
+        </is>
+      </c>
+      <c r="E1113" s="2" t="inlineStr">
+        <is>
+          <t>・制圧戦はダントツで周回価値が高くお得
+・老前シバルツは強力な闇剣でサラ/白バラ対応
+・11秒周回はブルーのライトボールで誰でも可能
+・コッペパンで高速育成できる制圧戦</t>
+        </is>
+      </c>
+      <c r="F1113" s="2" t="inlineStr">
+        <is>
+          <t>・覚醒の歯ご進化素材は今逃すと入手困難
+・資源像専用装備の最大進化を忘れがち
+・ボックスガチャパネル交換を忘れやすい
+・進化素材はロマンシングショップに並ばない</t>
+        </is>
+      </c>
+      <c r="G1113" s="2" t="inlineStr">
+        <is>
+          <t>・継承の代償後編
+・制圧戦推奨
+・進化素材取り逃し注意
+・老前シバルツ闇剣
+・11秒周回</t>
+        </is>
+      </c>
+      <c r="H1113" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0Ok9fw1KXG4</t>
+        </is>
+      </c>
+      <c r="J1113" s="2" t="inlineStr">
+        <is>
+          <t>0Ok9fw1KXG4</t>
+        </is>
+      </c>
+      <c r="K1113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:08:48Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1114" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1114" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】本物の人気ランキングがここに暴かれる！？公式のアンケートを徹底的に深掘りしていくぜ！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1114" s="2" t="inlineStr">
+        <is>
+          <t>公式生放送No.53の人気キャラアンケートを深掘り解析。
+1位最終皇帝女・2位男でロマサガ2人気が鮮明。
+GBサガキャラの根強い人気も浮き彫りに。</t>
+        </is>
+      </c>
+      <c r="E1114" s="2" t="inlineStr">
+        <is>
+          <t>・最終皇帝女/男がトップで嬉しい結果
+・ロマサガ2の人気の高さが証明された
+・キアは周回力とキャラ立ちで人気
+・GBサガキャラへの愛が根強い</t>
+        </is>
+      </c>
+      <c r="F1114" s="2" t="inlineStr">
+        <is>
+          <t>・人気キャラ優先でガチャ実装が偏る傾向
+・糸けんは実装に難しい要素が多い</t>
+        </is>
+      </c>
+      <c r="G1114" s="2" t="inlineStr">
+        <is>
+          <t>・公式アンケート解析
+・人気キャラ1-15位
+・ロマサガ2人気
+・GBサガの根強さ
+・ガチャ実装傾向</t>
+        </is>
+      </c>
+      <c r="H1114" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kkMxro1-6AI</t>
+        </is>
+      </c>
+      <c r="J1114" s="2" t="inlineStr">
+        <is>
+          <t>kkMxro1-6AI</t>
+        </is>
+      </c>
+      <c r="K1114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:08:48Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B1115" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1115" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ついに実装厄キャラ2体引くべき？白薔薇姫厄&amp;T260G厄ガチャ性能チェック&amp;キャラランク評価【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1115" s="2" t="inlineStr">
+        <is>
+          <t>厄ガチャ6スタイルの性能を詳細考察&amp;ランク付け。
+白薔薇姫アビスを星3、最終皇帝男/T260Gを星2評価。
+オルロワージュは代用可で星1に。</t>
+        </is>
+      </c>
+      <c r="E1115" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇姫アビスは高難度/レイド/周回で万能の星3
+・白薔薇姫は火ダメ軽減82%と高い
+・最終皇帝男はデバフと術2の全体火力が優秀
+・T260Gは4ターン無敵の唯一性が魅力
+・体力精神デバフ持ちは今貴重</t>
+        </is>
+      </c>
+      <c r="F1115" s="2" t="inlineStr">
+        <is>
+          <t>・最終皇帝女はアビリティに魅力なく星2
+・オルロワージュは本体だけなら代用可能で星1
+・タイムはエクストラフォースが被りやすい
+・T260Gは長期戦で強化切れ後に弱体化
+・オルロワージュは術さがスタンバイで所速が遅い</t>
+        </is>
+      </c>
+      <c r="G1115" s="2" t="inlineStr">
+        <is>
+          <t>・厄キャラ性能考察
+・白薔薇姫アビス星3
+・T260Gアビス星2
+・デバフ性能重視
+・キャラランク付け</t>
+        </is>
+      </c>
+      <c r="H1115" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PlssmrPT8uY</t>
+        </is>
+      </c>
+      <c r="J1115" s="2" t="inlineStr">
+        <is>
+          <t>PlssmrPT8uY</t>
+        </is>
+      </c>
+      <c r="K1115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:08:48Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1116" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1116" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】100位以内に入ろう‼️【12手クリア編成】第134回アルラウネたちの井戸~編成と立ち回りを徹底的に‼️</t>
+        </is>
+      </c>
+      <c r="D1116" s="2" t="inlineStr">
+        <is>
+          <t>第134回アルラウネの井戸ランキング100位以内向け編成紹介。
+ヒューズ・ターミン軸で3ターン12手94万点(80位級)。
+投稿者本人は2ターン運用で56位。</t>
+        </is>
+      </c>
+      <c r="E1116" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンの資源召喚が編成の要
+・3ターン12手で94万点(80位級)を実現</t>
+        </is>
+      </c>
+      <c r="F1116" s="2" t="inlineStr">
+        <is>
+          <t>・追撃の発動順がずれるとやり直しになる
+・20ヒットが揃わないと12クリア不可で注意</t>
+        </is>
+      </c>
+      <c r="G1116" s="2" t="inlineStr">
+        <is>
+          <t>・アルラウネの井戸
+・12手クリア編成
+・ランキング100位
+・3ターン運用
+・ターミン資源召喚</t>
+        </is>
+      </c>
+      <c r="H1116" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vLv4pa5gEHo</t>
+        </is>
+      </c>
+      <c r="J1116" s="2" t="inlineStr">
+        <is>
+          <t>vLv4pa5gEHo</t>
+        </is>
+      </c>
+      <c r="K1116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:08:48Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1117" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1117" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】2026年8月下旬ガチャ総まとめ！全12スタイル引くべきスタイルランキング！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1117" s="2" t="inlineStr">
+        <is>
+          <t>8月下旬実装ガチャ全12スタイルのティアランク総まとめ。
+ターミンをS、サルーイン/白薔薇姫アビスをA評価。
+コッペパンとT260Gは特別枠で紹介。</t>
+        </is>
+      </c>
+      <c r="E1117" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンは総合力でS評価
+・サルーインは40ヒットの火力おばけ
+・白薔薇姫アビスは総合力に優れた万能スタイル
+・コッペパンはSでも良い特別枠
+・タイムは置き物/レイドで活躍しそう</t>
+        </is>
+      </c>
+      <c r="F1117" s="2" t="inlineStr">
+        <is>
+          <t>・最終皇帝女はあえて弱く作られた性能
+・オルロワージュは所速が遅く微妙
+・T260Gは長期戦で強化切れ後に使い物にならない
+・フレイヤは火ダメ軽減50%が気になる</t>
+        </is>
+      </c>
+      <c r="G1117" s="2" t="inlineStr">
+        <is>
+          <t>・8月下旬ティアランク
+・ターミンS評価
+・サルーインA評価
+・白薔薇姫アビスA
+・コッペパン特別枠</t>
+        </is>
+      </c>
+      <c r="H1117" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=V1PzPxnP88E</t>
+        </is>
+      </c>
+      <c r="J1117" s="2" t="inlineStr">
+        <is>
+          <t>V1PzPxnP88E</t>
+        </is>
+      </c>
+      <c r="K1117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:08:48Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B1118" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1118" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「白薔薇姫[厄] 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1118" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭 白薔薇姫アビス編3スタイルの考察&amp;ランク付け。
+白薔薇姫アビスをA、最終皇帝男/オルロワージュをB評価。
+ザ熱属性パーティーでの運用が鍵。</t>
+        </is>
+      </c>
+      <c r="E1118" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇姫アビスは万能でA評価
+・白薔薇姫は火ダメ82%軽減で高難度採用可
+・最終皇帝男は体験のジャマで貴重
+・オルロワージュは火ダメ87%軽減が高い</t>
+        </is>
+      </c>
+      <c r="F1118" s="2" t="inlineStr">
+        <is>
+          <t>・最終皇帝男は火力/軽減率がもう一声欲しい
+・オルロワージュはアタッカー性能が微妙で所速遅い
+・オルロワージュは巻き尾と役割が被る
+・白薔薇姫はザ熱で固めないと効果が落ちる</t>
+        </is>
+      </c>
+      <c r="G1118" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇姫アビス編考察
+・白薔薇姫A評価
+・最終皇帝男B評価
+・オルロワージュB評価
+・ザ熱属性パーティー</t>
+        </is>
+      </c>
+      <c r="H1118" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vfnuacnjhcY</t>
+        </is>
+      </c>
+      <c r="J1118" s="2" t="inlineStr">
+        <is>
+          <t>vfnuacnjhcY</t>
+        </is>
+      </c>
+      <c r="K1118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25T01:08:48Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1118"/>
+  <dimension ref="A1:K1126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -73751,6 +73751,525 @@
         </is>
       </c>
     </row>
+    <row r="1119">
+      <c r="A1119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B1119" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1119" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】公式「ネタバレ」物語は新展開!!そのストーリーに絡むのは美しい美女か美少女かそれとも婆か!?加速するロマサガRS四半期祭開始!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1119" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS四半期祭が開始と告知。
+公式ネタバレPVで新展開の物語を予告。
+音楽中心で解説音声はほぼ無し。</t>
+        </is>
+      </c>
+      <c r="E1119" s="2" t="inlineStr"/>
+      <c r="F1119" s="2" t="inlineStr"/>
+      <c r="G1119" s="2" t="inlineStr">
+        <is>
+          <t>・四半期祭開始
+・新ストーリー予告
+・公式PV</t>
+        </is>
+      </c>
+      <c r="H1119" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pG0JlWqbEFY</t>
+        </is>
+      </c>
+      <c r="J1119" s="2" t="inlineStr">
+        <is>
+          <t>pG0JlWqbEFY</t>
+        </is>
+      </c>
+      <c r="K1119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26T01:32:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B1120" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1120" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　いい井戸ぉう　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1120" s="2" t="inlineStr">
+        <is>
+          <t>井戸イベントの2ターンクリアに挑戦。
+無料配布モニカが追撃運ゲで大暴れし100位入り。
+来週のジュエルビースト編成を考察。</t>
+        </is>
+      </c>
+      <c r="E1120" s="2" t="inlineStr">
+        <is>
+          <t>・今回の井戸はよくできていて非常に面白い
+・無料配布モニカが追撃運ゲで大火力・100位入り
+・ターミン・ヒューズ編成が強力
+・来週のリキャスト/スタンバイ解除ギミックが面白そう</t>
+        </is>
+      </c>
+      <c r="F1120" s="2" t="inlineStr">
+        <is>
+          <t>・井戸の2ターンクリアは非常に難しい
+・T260Gの3ターン始動は遅く使いづらい
+・新キャラ不在でログイン離れが進んでいる
+・メインストーリーが単調な周回になりがち</t>
+        </is>
+      </c>
+      <c r="G1120" s="2" t="inlineStr">
+        <is>
+          <t>・井戸2ターンクリア
+・モニカ活躍
+・ランキング100位
+・ジュエルビースト考察
+・来週の環境</t>
+        </is>
+      </c>
+      <c r="H1120" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Euz2syxpTS0</t>
+        </is>
+      </c>
+      <c r="J1120" s="2" t="inlineStr">
+        <is>
+          <t>Euz2syxpTS0</t>
+        </is>
+      </c>
+      <c r="K1120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26T01:32:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B1121" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1121" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　こよみ編後編　イベント見て行こう！　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1121" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープでメインの3章0話をクリア。
+ガチャでランが4枚引け覚醒で大幅強化。
+塔登りやキャラ育成を進める配信。</t>
+        </is>
+      </c>
+      <c r="E1121" s="2" t="inlineStr">
+        <is>
+          <t>・SSRなしでもメインストーリーをクリアできる
+・ランが4枚引けて大量覚醒で強力に
+・フレンドのゲオルグ・機下が非常に強い
+・色々考えられてよくできた楽しいゲーム</t>
+        </is>
+      </c>
+      <c r="F1121" s="2" t="inlineStr">
+        <is>
+          <t>・SSRと下位キャラの火力差が非常に大きい
+・上位の塔は耐久力不足で厳しい
+・同キャラ被りはパーティーに入れられず不便</t>
+        </is>
+      </c>
+      <c r="G1121" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープ
+・3章0話クリア
+・ガチャでラン複数
+・塔登り
+・キャラ育成</t>
+        </is>
+      </c>
+      <c r="H1121" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IwjPAA5_jio</t>
+        </is>
+      </c>
+      <c r="J1121" s="2" t="inlineStr">
+        <is>
+          <t>IwjPAA5_jio</t>
+        </is>
+      </c>
+      <c r="K1121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26T01:32:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B1122" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1122" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　3章0話クリア達成　次戦に向けて　キャラ育成していこう！　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1122" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープの3章0話クリアを目指す。
+料理・釣りミニゲームやキャラ育成を進める。
+明日8/26からのイベント・新ガチャに期待。</t>
+        </is>
+      </c>
+      <c r="E1122" s="2" t="inlineStr">
+        <is>
+          <t>・釣りミニゲームがスマホゲーとは思えないほど面白い
+・やり込み要素が多く楽しい
+・フレンドで借りたゲオルグが非常に強い</t>
+        </is>
+      </c>
+      <c r="F1122" s="2" t="inlineStr">
+        <is>
+          <t>・特定バトルは火属性キャラがいないと厳しい
+・上位帯はレベルが上がりにくく育成が大変
+・タンク役がいないと苦戦する</t>
+        </is>
+      </c>
+      <c r="G1122" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープ
+・3章0話
+・釣りミニゲーム
+・キャラ育成
+・新イベント・ガチャ</t>
+        </is>
+      </c>
+      <c r="H1122" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=elt2NtcKqAc</t>
+        </is>
+      </c>
+      <c r="J1122" s="2" t="inlineStr">
+        <is>
+          <t>elt2NtcKqAc</t>
+        </is>
+      </c>
+      <c r="K1122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26T01:32:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B1123" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1123" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】アビスVS佐賀！5大ガチャランキング引くべき優先順位考察【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1123" s="2" t="inlineStr">
+        <is>
+          <t>サガコラボ含む5大ガチャの引く優先順位を考察。
+1位ターミン、コペパンは別枠で最優先評価。
+今は盛り上がりの谷、必須以外は石温存推奨。</t>
+        </is>
+      </c>
+      <c r="E1123" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンは超火力で属性編成が環境特級
+・コペパンは無人島特攻で唯一性が高く最優先
+・白腹姫は組み合わせ次第で100億超の火力
+・サルーインは自前エクストラフォースで優秀</t>
+        </is>
+      </c>
+      <c r="F1123" s="2" t="inlineStr">
+        <is>
+          <t>・T260Gは3ターン発動が遅く使いにくい
+・シムメシは防御レゾ0でゴリ押し向け
+・今は盛り上がりの谷でジュエル温存推奨
+・螺旋590は式が低く過去キャラでも順応可</t>
+        </is>
+      </c>
+      <c r="G1123" s="2" t="inlineStr">
+        <is>
+          <t>・5大ガチャ優先順位
+・サガコラボ
+・ターミン最評価
+・コペパン最優先
+・螺旋回廊590</t>
+        </is>
+      </c>
+      <c r="H1123" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PIOwZY08UTw</t>
+        </is>
+      </c>
+      <c r="J1123" s="2" t="inlineStr">
+        <is>
+          <t>PIOwZY08UTw</t>
+        </is>
+      </c>
+      <c r="K1123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26T01:32:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B1124" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1124" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】結局サルーインガチャ引く？スルー？微課金目線の最終ジャッジ！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1124" s="2" t="inlineStr">
+        <is>
+          <t>サルーインガチャを微課金目線で最終判断。
+3体とも粒揃いだが代用可能で全スルー結論。
+週末生放送・大型イベント前でジュエル温存推奨。</t>
+        </is>
+      </c>
+      <c r="E1124" s="2" t="inlineStr">
+        <is>
+          <t>・3体とも性能は粒揃いで引いても後悔しにくい
+・サルーインは火力・全体火力バフが優秀
+・マキビは状態異常回復まで汎用性が高い
+・初心者・復帰勢にはサルーイン確保がおすすめ</t>
+        </is>
+      </c>
+      <c r="F1124" s="2" t="inlineStr">
+        <is>
+          <t>・フレイヤは打熱編成限定で代用可、スルー
+・マキビは大体が効き唯一性が低い
+・サルーインも暦みで代用でき活躍期間が短そう
+・今使うより生放送後まで温存が無難</t>
+        </is>
+      </c>
+      <c r="G1124" s="2" t="inlineStr">
+        <is>
+          <t>・サルーインガチャ
+・微課金目線
+・キャラ最終評価
+・ジュエル温存</t>
+        </is>
+      </c>
+      <c r="H1124" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BrIxIqeHKpI</t>
+        </is>
+      </c>
+      <c r="J1124" s="2" t="inlineStr">
+        <is>
+          <t>BrIxIqeHKpI</t>
+        </is>
+      </c>
+      <c r="K1124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26T01:32:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1125" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1125" s="2" t="inlineStr">
+        <is>
+          <t>ちゃむのYouTubeガチャ生配信~取ったキャラで~井戸TOPを狙う‼️</t>
+        </is>
+      </c>
+      <c r="D1125" s="2" t="inlineStr">
+        <is>
+          <t>T260G狙いのガチャ生配信で神引き連発。
+白腹姫も確保でき大満足の引きに。
+来週スタンバイ制限無効でT260Gに期待。</t>
+        </is>
+      </c>
+      <c r="E1125" s="2" t="inlineStr">
+        <is>
+          <t>・2週連続の神引きでT260G・白腹姫を確保
+・来週のスタンバイ制限無効でT260Gが刺さりそう
+・白腹姫はオルロワージョンも強く2ターン目から強力</t>
+        </is>
+      </c>
+      <c r="F1125" s="2" t="inlineStr">
+        <is>
+          <t>・T260Gのスタンバイ3ターンは通常の井戸では活躍しづらい
+・井戸編成の操作に手間取り最適解が見えにくい</t>
+        </is>
+      </c>
+      <c r="G1125" s="2" t="inlineStr">
+        <is>
+          <t>・T260Gガチャ
+・白腹姫確保
+・神引き2連発
+・井戸TOP狙い
+・ジュエルビースト予想</t>
+        </is>
+      </c>
+      <c r="H1125" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VU-BC4mqhsA</t>
+        </is>
+      </c>
+      <c r="J1125" s="2" t="inlineStr">
+        <is>
+          <t>VU-BC4mqhsA</t>
+        </is>
+      </c>
+      <c r="K1125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26T01:32:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1126" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1126" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】TIME〜2:09〜レイド残り2日‼️井戸1位狙う編成【自由枠①】〜Now or never〜</t>
+        </is>
+      </c>
+      <c r="D1126" s="2" t="inlineStr">
+        <is>
+          <t>レイド終盤、最短2分9秒の周回編成を紹介。
+暦み・サルーインを育てつつ井戸1位を狙う。
+自由枠は好きなキャラで魂をひらめかせる。</t>
+        </is>
+      </c>
+      <c r="E1126" s="2" t="inlineStr">
+        <is>
+          <t>・最短2分9秒で1日約600周でき効率的
+・暦み・ターミン・T260Gが井戸で大活躍中</t>
+        </is>
+      </c>
+      <c r="F1126" s="2" t="inlineStr"/>
+      <c r="G1126" s="2" t="inlineStr">
+        <is>
+          <t>・レイド最短周回
+・井戸1位狙い
+・暦み・サルーイン育成
+・シリーズフォースひらめき</t>
+        </is>
+      </c>
+      <c r="H1126" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qr6PlY4CuuI</t>
+        </is>
+      </c>
+      <c r="J1126" s="2" t="inlineStr">
+        <is>
+          <t>qr6PlY4CuuI</t>
+        </is>
+      </c>
+      <c r="K1126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26T01:32:39Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1126"/>
+  <dimension ref="A1:K1134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -74270,6 +74270,539 @@
         </is>
       </c>
     </row>
+    <row r="1127">
+      <c r="A1127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1127" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1127" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】黒薔薇「最強テンプレ」白薔薇姫取説&amp;お供四選!!斬熱陰を活かせる高難度最強取り回しお仲間&amp;おすすめ編成とは!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1127" s="2" t="inlineStr">
+        <is>
+          <t>白薔薇姫の性能とお供・編成を徹底解説
+全ステバフばら撒きで開幕から高バフ
+斬熱陰3属性対応で立ち回りが簡単</t>
+        </is>
+      </c>
+      <c r="E1127" s="2" t="inlineStr">
+        <is>
+          <t>・全ステバフばら撒きが環境トップ性能
+・防御82%で主流75%より頭一つ抜ける
+・PP自己完結で立ち回りが簡単
+・3属性カバーで汎用性が高い</t>
+        </is>
+      </c>
+      <c r="F1127" s="2" t="inlineStr">
+        <is>
+          <t>・討伐・螺旋向けで無人島は別物
+・半年前の原産と同性能と言うと地味</t>
+        </is>
+      </c>
+      <c r="G1127" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇姫
+・全ステバフばら撒き
+・斬熱陰3属性
+・おすすめ編成
+・高難度</t>
+        </is>
+      </c>
+      <c r="H1127" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IjlT12cIHig</t>
+        </is>
+      </c>
+      <c r="J1127" s="2" t="inlineStr">
+        <is>
+          <t>IjlT12cIHig</t>
+        </is>
+      </c>
+      <c r="K1127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27T01:37:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1128" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1128" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】佐賀県が「塩対応」ロマンシング佐賀県コラボ〇〇で超話題に　#ロマサガRS　#ロマ佐賀</t>
+        </is>
+      </c>
+      <c r="D1128" s="2" t="inlineStr">
+        <is>
+          <t>ロマンシング佐賀県コラボが今年も開幕
+ロックブーケのラーメンがXで大バズり
+「塩対応されたい」と性癖に刺さり話題</t>
+        </is>
+      </c>
+      <c r="E1128" s="2" t="inlineStr">
+        <is>
+          <t>・ロックブーケは圧倒的人気キャラ
+・原さのドット絵書き下ろし等で気合十分
+・ラーメンがシンプルに美味しいと好評</t>
+        </is>
+      </c>
+      <c r="F1128" s="2" t="inlineStr"/>
+      <c r="G1128" s="2" t="inlineStr">
+        <is>
+          <t>・ロマ佐賀コラボ
+・ロックブーケ
+・塩対応ラーメン
+・X話題</t>
+        </is>
+      </c>
+      <c r="H1128" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sm4GdJ6Sz0k</t>
+        </is>
+      </c>
+      <c r="J1128" s="2" t="inlineStr">
+        <is>
+          <t>sm4GdJ6Sz0k</t>
+        </is>
+      </c>
+      <c r="K1128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27T01:37:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1129" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1129" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】8月末は虚無期間？ 9月のアップデート情報！ 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D1129" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナル9月アップデート情報
+8月末は復刻中心で虚無寄りの控えめ内容
+9月下旬に1.5周年直前ロードマップ配信</t>
+        </is>
+      </c>
+      <c r="E1129" s="2" t="inlineStr">
+        <is>
+          <t>・マスターリーグは低レア活躍で楽しい
+・お任せ装備やミッションフィルターが便利
+・Z/ZZの性能調整はありがたい
+・1.5周年は大きく期待できそう</t>
+        </is>
+      </c>
+      <c r="F1129" s="2" t="inlineStr">
+        <is>
+          <t>・8月末〜9月中旬は虚無期間になりそう
+・回想追加なしでボリューム控えめ
+・ダブルZは枠が少なく攻略が大変
+・月末ガチャで誰が来るか読めない</t>
+        </is>
+      </c>
+      <c r="G1129" s="2" t="inlineStr">
+        <is>
+          <t>・9月アップデート
+・1.5周年
+・Wイベント
+・強敵集来ネティクス
+・ZZ性能調整</t>
+        </is>
+      </c>
+      <c r="H1129" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TH0VkTL6xXQ</t>
+        </is>
+      </c>
+      <c r="J1129" s="2" t="inlineStr">
+        <is>
+          <t>TH0VkTL6xXQ</t>
+        </is>
+      </c>
+      <c r="K1129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27T01:37:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1130" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1130" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネやりながら雑談</t>
+        </is>
+      </c>
+      <c r="D1130" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネをプレイしながら参戦・実装予想を雑談
+脱出機能の後付けはURでは難しいと考察
+覚醒ユニコーンの支援発動が弱いと不満</t>
+        </is>
+      </c>
+      <c r="E1130" s="2" t="inlineStr">
+        <is>
+          <t>・ユニットのデザインがよくできている
+・シードは映画バズで今後の展開に期待
+・ビルド系はベース機体が使え意外と重要</t>
+        </is>
+      </c>
+      <c r="F1130" s="2" t="inlineStr">
+        <is>
+          <t>・覚醒ユニコーンの支援3回発動が全然行かない
+・UIが横に長すぎて使いづらい
+・ダブルZは編成バランスが悪い
+・ガチャ演出中のロードが気になる</t>
+        </is>
+      </c>
+      <c r="G1130" s="2" t="inlineStr">
+        <is>
+          <t>・参戦・実装予想
+・脱出機能
+・覚醒ユニコーン
+・ビルドシリーズ
+・昔のGジェネ</t>
+        </is>
+      </c>
+      <c r="H1130" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_6-FJGZeLmk</t>
+        </is>
+      </c>
+      <c r="J1130" s="2" t="inlineStr">
+        <is>
+          <t>_6-FJGZeLmk</t>
+        </is>
+      </c>
+      <c r="K1130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27T01:37:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1131" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C1131" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】雑談となんかやってます！</t>
+        </is>
+      </c>
+      <c r="D1131" s="2" t="inlineStr">
+        <is>
+          <t>排水習得を狙い周回しながらの雑談配信
+8/28の火の羽新キャラをアルカイザー等と予想
+株・米価・物流賃金など世間話も多め</t>
+        </is>
+      </c>
+      <c r="E1131" s="2" t="inlineStr">
+        <is>
+          <t>・サルインは天井クラスの火力で強い
+・ウイルはコラボ唯一の大当たりで貴重
+・白薔薇・黒薔薇など効果大キャラを評価</t>
+        </is>
+      </c>
+      <c r="F1131" s="2" t="inlineStr">
+        <is>
+          <t>・レイドでアビリティ未習得のバグ疑い損失
+・ルビーを超えるキャラが欲しく頭打ち感
+・気ハは魂覚えても高難度で使わない
+・ラウンド系アビリティはいらない</t>
+        </is>
+      </c>
+      <c r="G1131" s="2" t="inlineStr">
+        <is>
+          <t>・排水周回
+・8/28火の羽新キャラ予想
+・サルイン
+・株・投資
+・物価・賃金雑談</t>
+        </is>
+      </c>
+      <c r="H1131" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I1131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3xTBv6bV-80</t>
+        </is>
+      </c>
+      <c r="J1131" s="2" t="inlineStr">
+        <is>
+          <t>3xTBv6bV-80</t>
+        </is>
+      </c>
+      <c r="K1131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27T01:37:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1132" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1132" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】激ヤバな公式情報に気付いてしまった！次の公式生放送は大盛り上がりの予感！！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1132" s="2" t="inlineStr">
+        <is>
+          <t>8/28公式生放送54の内容を予想する動画
+公式Xの羽・フェニックス演出からポルカ示唆
+初の8スタイル新発生ガチャ再来を大胆予想</t>
+        </is>
+      </c>
+      <c r="E1132" s="2" t="inlineStr">
+        <is>
+          <t>・メインストーリー続編と新機能情報に期待
+・森沢さんイラストで大型の予感
+・新発生ガチャなら初期勢は胸熱</t>
+        </is>
+      </c>
+      <c r="F1132" s="2" t="inlineStr">
+        <is>
+          <t>・1.5周年直前で回しづらいタイミング</t>
+        </is>
+      </c>
+      <c r="G1132" s="2" t="inlineStr">
+        <is>
+          <t>・8/28公式生放送54
+・予想動画
+・フェニックス/羽演出
+・ポルカ
+・新発生ガチャ</t>
+        </is>
+      </c>
+      <c r="H1132" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mu7wLnz290k</t>
+        </is>
+      </c>
+      <c r="J1132" s="2" t="inlineStr">
+        <is>
+          <t>mu7wLnz290k</t>
+        </is>
+      </c>
+      <c r="K1132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27T01:37:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1133" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1133" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】〜T260G〔厄〕能力値早見表〜スタンバイ無効❗️井戸で大活躍‼️斬熱陰~超強力リスキーアタッカー</t>
+        </is>
+      </c>
+      <c r="D1133" s="2" t="inlineStr">
+        <is>
+          <t>T260Gアビスの能力値早見表をまとめた
+3〜6ターンが急行動46ヒットで強力
+来週の井戸ジュエルビーストに刺さる予感</t>
+        </is>
+      </c>
+      <c r="E1133" s="2" t="inlineStr">
+        <is>
+          <t>・3〜6ターンの威力が高くやばい
+・来週のスタンバイ井戸に刺さりそう
+・自由があれば取って損なし超おすすめ</t>
+        </is>
+      </c>
+      <c r="F1133" s="2" t="inlineStr">
+        <is>
+          <t>・代償ダメージや能力剥がれのデメリット大
+・7ターン以降は使い物にならない前半型
+・井戸では代償ダメージが減点対象の懸念</t>
+        </is>
+      </c>
+      <c r="G1133" s="2" t="inlineStr">
+        <is>
+          <t>・T260Gアビス
+・能力値早見表
+・スタンバイターン
+・井戸/ジュエルビースト
+・斬熱陰</t>
+        </is>
+      </c>
+      <c r="H1133" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RSEOA7Ip1nA</t>
+        </is>
+      </c>
+      <c r="J1133" s="2" t="inlineStr">
+        <is>
+          <t>RSEOA7Ip1nA</t>
+        </is>
+      </c>
+      <c r="K1133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27T01:37:08Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1134" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1134" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみ編 第7話 後編ガチャを考察する配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D1134" s="2" t="inlineStr">
+        <is>
+          <t>こよみ編アビスガチャ6体を視聴者と考察
+白薔薇姫はバランス良くA評価で押し
+T260Gは唯一性でB、最終皇女は弱くC評価</t>
+        </is>
+      </c>
+      <c r="E1134" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇姫はバランス良く火ダメ82%軽減でA
+・最終皇帝男は体術の邪魔役で優秀
+・T260Gは4ターン無敵で悪さしそう唯一性高い
+・タイムは置き物・レイド性能が良い</t>
+        </is>
+      </c>
+      <c r="F1134" s="2" t="inlineStr">
+        <is>
+          <t>・最終皇女は威力Eで弱くC評価
+・オルロアージュは条件が厳しく継承前提
+・T260Gは代償ダメージが痛い
+・タイムは火ダメ軽減50%で高難度は不安</t>
+        </is>
+      </c>
+      <c r="G1134" s="2" t="inlineStr">
+        <is>
+          <t>・アビスガチャ6体考察
+・白薔薇姫
+・T260G
+・最終皇帝男
+・幻統ディーネボルカ対策</t>
+        </is>
+      </c>
+      <c r="H1134" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=safG_DNgvEY</t>
+        </is>
+      </c>
+      <c r="J1134" s="2" t="inlineStr">
+        <is>
+          <t>safG_DNgvEY</t>
+        </is>
+      </c>
+      <c r="K1134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27T01:37:08Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1134"/>
+  <dimension ref="A1:K1151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -74803,6 +74803,1099 @@
         </is>
       </c>
     </row>
+    <row r="1135">
+      <c r="A1135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1135" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1135" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「唯一無二の解除」兼サブアタッカーリズ&amp;「陰冷リラ型」イーヴリン#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1135" s="2" t="inlineStr">
+        <is>
+          <t>復刻ガチャのリズとイーヴリンをテキスト評価。
+リズは環境最高峰の防御とバフ解除が魅力だが火力不足。
+イーヴリンは防御は高いが起用機会がなく総合B。</t>
+        </is>
+      </c>
+      <c r="E1135" s="2" t="inlineStr">
+        <is>
+          <t>・リズの防御は環境最高峰
+・リズは攻撃を当てずバフ解除可能
+・イーヴリンの防御数値は強め</t>
+        </is>
+      </c>
+      <c r="F1135" s="2" t="inlineStr">
+        <is>
+          <t>・リズは火力不足でアタッカー不向き
+・リズはヒートダウンで火力マイナス
+・イーヴリンはエクストラばら撒きが無く起用機会なし
+・イーヴリンは総合評価B止まり</t>
+        </is>
+      </c>
+      <c r="G1135" s="2" t="inlineStr">
+        <is>
+          <t>・リズ性能評価
+・イーヴリン評価
+・防御・バフ解除
+・アタッカー火力</t>
+        </is>
+      </c>
+      <c r="H1135" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=eR0zZCAsC0A</t>
+        </is>
+      </c>
+      <c r="J1135" s="2" t="inlineStr">
+        <is>
+          <t>eR0zZCAsC0A</t>
+        </is>
+      </c>
+      <c r="K1135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1136" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1136" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】闘者の関門「アイツ1択」アラケスギミック解明速報!!下振れを〇〇でカバーせよ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1136" s="2" t="inlineStr">
+        <is>
+          <t>闘者の関門アラケスのギミックを解明する速報。
+攻略は「アイツ1択」と断言。
+下振れをカバーする立ち回りを解説。</t>
+        </is>
+      </c>
+      <c r="E1136" s="2" t="inlineStr">
+        <is>
+          <t>・特定キャラで安定攻略できる</t>
+        </is>
+      </c>
+      <c r="F1136" s="2" t="inlineStr">
+        <is>
+          <t>・下振れのリスクがある</t>
+        </is>
+      </c>
+      <c r="G1136" s="2" t="inlineStr">
+        <is>
+          <t>・アラケス攻略
+・ギミック解明速報
+・下振れ対策</t>
+        </is>
+      </c>
+      <c r="H1136" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iSuroh4AwrQ</t>
+        </is>
+      </c>
+      <c r="J1136" s="2" t="inlineStr">
+        <is>
+          <t>iSuroh4AwrQ</t>
+        </is>
+      </c>
+      <c r="K1136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1137" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1137" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始329日目記録　快挙　ありがとう3周年</t>
+        </is>
+      </c>
+      <c r="D1137" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣プレイ329日目の進捗報告。
+3周年イベントと新武将・課金パックを確認。
+タップ範囲拡張マスが快適と絶賛。</t>
+        </is>
+      </c>
+      <c r="E1137" s="2" t="inlineStr">
+        <is>
+          <t>・タップ範囲拡張マスが快適で神機能
+・3周年ガチャ・報酬が豪華
+・織田信長の性能がめちゃくちゃ強い
+・松姫の武系回復要員が助かる
+・浅井長政の鉄砲特攻が面白い</t>
+        </is>
+      </c>
+      <c r="F1137" s="2" t="inlineStr">
+        <is>
+          <t>・沖縄は島が離れ移動が大変
+・共闘は回復重視で火力不足だった
+・課金誘導が露骨で悩ましい</t>
+        </is>
+      </c>
+      <c r="G1137" s="2" t="inlineStr">
+        <is>
+          <t>・信長の野望出陣
+・3周年イベント
+・新武将入手
+・タップ範囲拡張
+・課金パック</t>
+        </is>
+      </c>
+      <c r="H1137" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=G6r3mXbTyX0</t>
+        </is>
+      </c>
+      <c r="J1137" s="2" t="inlineStr">
+        <is>
+          <t>G6r3mXbTyX0</t>
+        </is>
+      </c>
+      <c r="K1137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1138" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1138" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】とりま40連『Abyssal Circus 開幕記念 Romancing祭』【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1138" s="2" t="inlineStr">
+        <is>
+          <t>アビサルサーカス開幕記念ロマンシング祭を40連ガチャ。
+ジュエル不足でリズ編中心に挑戦。
+40連で無事リズを入手でき満足。</t>
+        </is>
+      </c>
+      <c r="E1138" s="2" t="inlineStr">
+        <is>
+          <t>・40連でリズが出て良かった
+・弓のバルドは貴重</t>
+        </is>
+      </c>
+      <c r="F1138" s="2" t="inlineStr">
+        <is>
+          <t>・ジュエル不足で40連しか回せない
+・ポルカは出なかった</t>
+        </is>
+      </c>
+      <c r="G1138" s="2" t="inlineStr">
+        <is>
+          <t>・ロマンシング祭ガチャ
+・リズ編40連
+・ポルカ編</t>
+        </is>
+      </c>
+      <c r="H1138" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Jpr5Ra2_3Ig</t>
+        </is>
+      </c>
+      <c r="J1138" s="2" t="inlineStr">
+        <is>
+          <t>Jpr5Ra2_3Ig</t>
+        </is>
+      </c>
+      <c r="K1138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1139" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1139" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】とりま40連『Abyssal Circus 開幕記念 Romancing祭』#ロマンシングサガリ・ユニバース ＃Shorts</t>
+        </is>
+      </c>
+      <c r="D1139" s="2" t="inlineStr">
+        <is>
+          <t>ロマンシング祭を40連引くショート版。
+ジュエル不足でリズ編を優先。
+40連でリズが出て良かったと締め。</t>
+        </is>
+      </c>
+      <c r="E1139" s="2" t="inlineStr">
+        <is>
+          <t>・40連でリズが出て良かった
+・弓のバルドは貴重</t>
+        </is>
+      </c>
+      <c r="F1139" s="2" t="inlineStr">
+        <is>
+          <t>・ジュエル不足で40連のみ
+・ポルカは出なかった</t>
+        </is>
+      </c>
+      <c r="G1139" s="2" t="inlineStr">
+        <is>
+          <t>・ロマンシング祭ガチャ
+・リズ編40連
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H1139" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Rsx-tPpDB4A</t>
+        </is>
+      </c>
+      <c r="J1139" s="2" t="inlineStr">
+        <is>
+          <t>Rsx-tPpDB4A</t>
+        </is>
+      </c>
+      <c r="K1139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1140" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1140" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】神引きはもうおわり。確率の収束が襲いかかる【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1140" s="2" t="inlineStr">
+        <is>
+          <t>第1部主人公ガチャをポルカ・ブラウニー狙いで実況。
+ポルカとブラウニーの2枚抜きに成功。
+その後は渋く確率収束を実感。</t>
+        </is>
+      </c>
+      <c r="E1140" s="2" t="inlineStr">
+        <is>
+          <t>・ポルカとブラウニーの2枚抜き成功
+・ポルカは弱点火力が高く硬くなる</t>
+        </is>
+      </c>
+      <c r="F1140" s="2" t="inlineStr">
+        <is>
+          <t>・途中から引きが渋く苦戦
+・来週のガチャの方が強そう</t>
+        </is>
+      </c>
+      <c r="G1140" s="2" t="inlineStr">
+        <is>
+          <t>・主人公ガチャ
+・ポルカ・ブラウニー狙い
+・2枚抜き
+・確率収束</t>
+        </is>
+      </c>
+      <c r="H1140" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8N4UI3_1Evw</t>
+        </is>
+      </c>
+      <c r="J1140" s="2" t="inlineStr">
+        <is>
+          <t>8N4UI3_1Evw</t>
+        </is>
+      </c>
+      <c r="K1140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1141" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1141" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】帰ってきた第一部主人公軍団6人全員性能確認【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1141" s="2" t="inlineStr">
+        <is>
+          <t>復刻した第1部主人公6人の性能を確認。
+ポルカはサポーターで防御強化がガチガチに硬い。
+リズはアタッカーで弱点時4.5倍の高火力。</t>
+        </is>
+      </c>
+      <c r="E1141" s="2" t="inlineStr">
+        <is>
+          <t>・ポルカは全体防御を95%まで盛れ激硬
+・リズは弱点時4.5倍の高火力
+・リズは最初から防御強化75%持ち</t>
+        </is>
+      </c>
+      <c r="F1141" s="2" t="inlineStr">
+        <is>
+          <t>・ポルカは火力が思ったより出ない
+・リズはブリザードのヒット数が伸び悩む</t>
+        </is>
+      </c>
+      <c r="G1141" s="2" t="inlineStr">
+        <is>
+          <t>・主人公6人性能確認
+・ポルカ(サポーター)
+・リズ(アタッカー)
+・防御強化</t>
+        </is>
+      </c>
+      <c r="H1141" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Bk-_BVTR3_M</t>
+        </is>
+      </c>
+      <c r="J1141" s="2" t="inlineStr">
+        <is>
+          <t>Bk-_BVTR3_M</t>
+        </is>
+      </c>
+      <c r="K1141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1142" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1142" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】神アプデ＆新イベント！確認しながら優先順位を整理！今やることは一択【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1142" s="2" t="inlineStr">
+        <is>
+          <t>神アプデと新イベントの優先順位を整理。
+アビサルサーカスの記憶再戦を最優先と推奨。
+連魔一括化など神アプデを高評価。</t>
+        </is>
+      </c>
+      <c r="E1142" s="2" t="inlineStr">
+        <is>
+          <t>・連魔一括化アプデが便利
+・アビサルサーカスの防具は今しか取れず優秀
+・コッペパン(ダメブロ靴)で周回が高速</t>
+        </is>
+      </c>
+      <c r="F1142" s="2" t="inlineStr">
+        <is>
+          <t>・魂の祠は敵がインフレ無しで今は不要
+・武器連魔はやり込まなくても問題ない</t>
+        </is>
+      </c>
+      <c r="G1142" s="2" t="inlineStr">
+        <is>
+          <t>・イベント優先順位
+・アビサルサーカス
+・記憶再戦
+・連魔一括化アプデ
+・ロマパス</t>
+        </is>
+      </c>
+      <c r="H1142" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GqjvMlEHssk</t>
+        </is>
+      </c>
+      <c r="J1142" s="2" t="inlineStr">
+        <is>
+          <t>GqjvMlEHssk</t>
+        </is>
+      </c>
+      <c r="K1142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1143" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1143" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ソシャゲ配信者の苦悩・悩み・願望【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1143" s="2" t="inlineStr">
+        <is>
+          <t>ゲームと関係ない配信者の人生・仕事の話。
+出張続きで動画本数が半減しショックと吐露。
+大きい仕事が片付いたらゆっくり配信したい。</t>
+        </is>
+      </c>
+      <c r="E1143" s="2" t="inlineStr">
+        <is>
+          <t>・ロマサガは大好きで配信が楽しい</t>
+        </is>
+      </c>
+      <c r="F1143" s="2" t="inlineStr">
+        <is>
+          <t>・出張続きで多忙
+・動画本数が44本から22本に半減
+・ゲームをやる時間がない</t>
+        </is>
+      </c>
+      <c r="G1143" s="2" t="inlineStr">
+        <is>
+          <t>・配信者の苦悩
+・仕事との両立
+・動画本数半減
+・今後の願望</t>
+        </is>
+      </c>
+      <c r="H1143" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tDYRQHFsHwk</t>
+        </is>
+      </c>
+      <c r="J1143" s="2" t="inlineStr">
+        <is>
+          <t>tDYRQHFsHwk</t>
+        </is>
+      </c>
+      <c r="K1143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1144" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C1144" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】😻アビサルサーカスロマンシングWガチャ😻</t>
+        </is>
+      </c>
+      <c r="D1144" s="2" t="inlineStr">
+        <is>
+          <t>メンテ明け直後にアビサルサーカスのWガチャ生配信。
+8周年カウントダウン88日ログボを紹介。
+サガレコ(BGM再生)など新機能を確認。</t>
+        </is>
+      </c>
+      <c r="E1144" s="2" t="inlineStr">
+        <is>
+          <t>・サガレコで好きな曲をBGM再生できる
+・8周年ログボが豪華(計8.8万ジュエル)</t>
+        </is>
+      </c>
+      <c r="F1144" s="2" t="inlineStr">
+        <is>
+          <t>・88日連続ログイン必須で1日逃すと損
+・先制装備の作り直しが1番痛い</t>
+        </is>
+      </c>
+      <c r="G1144" s="2" t="inlineStr">
+        <is>
+          <t>・Wガチャ生配信
+・8周年カウントダウン
+・88日ログボ
+・サガレコ機能
+・ポルカ</t>
+        </is>
+      </c>
+      <c r="H1144" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I1144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AZN2wJUdlTg</t>
+        </is>
+      </c>
+      <c r="J1144" s="2" t="inlineStr">
+        <is>
+          <t>AZN2wJUdlTg</t>
+        </is>
+      </c>
+      <c r="K1144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1145" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1145" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】メンテ明けに突撃！公式生放送直後のガチャライブ！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1145" s="2" t="inlineStr">
+        <is>
+          <t>公式生放送直後のメンテ明けガチャ生配信。
+自身の事前予想が当たったと大盛り上がり。
+リズやサガレコ・連魔アプデを絶賛。</t>
+        </is>
+      </c>
+      <c r="E1145" s="2" t="inlineStr">
+        <is>
+          <t>・サガレコのバックグラウンド再生が素晴らしい
+・連魔アプデでまとめ強化可能に
+・リズがアタッカーとして注目
+・戦闘が快適になった</t>
+        </is>
+      </c>
+      <c r="F1145" s="2" t="inlineStr"/>
+      <c r="G1145" s="2" t="inlineStr">
+        <is>
+          <t>・メンテ明けガチャライブ
+・公式予想的中
+・リズ
+・サガレコ機能
+・連魔アプデ</t>
+        </is>
+      </c>
+      <c r="H1145" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vG9bMv5w2V0</t>
+        </is>
+      </c>
+      <c r="J1145" s="2" t="inlineStr">
+        <is>
+          <t>vG9bMv5w2V0</t>
+        </is>
+      </c>
+      <c r="K1145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1146" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1146" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】最初に取るべきキャラは誰だ！？最新の視聴メダルキャラのおすすめ大紹介！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1146" s="2" t="inlineStr">
+        <is>
+          <t>視聴メダル交換所のおすすめキャラを解説。
+エルマンは配布相応で好きな人向け。
+クーンは味方に解除を配れる点が優秀。</t>
+        </is>
+      </c>
+      <c r="E1146" s="2" t="inlineStr">
+        <is>
+          <t>・クーンは味方全体に解除を配布でき螺旋回廊で有用
+・クーンはBPを多く配れる</t>
+        </is>
+      </c>
+      <c r="F1146" s="2" t="inlineStr">
+        <is>
+          <t>・エルマンは火力低く配布相応で弱い
+・クーン自体の攻撃性能は平凡</t>
+        </is>
+      </c>
+      <c r="G1146" s="2" t="inlineStr">
+        <is>
+          <t>・視聴メダル交換
+・エルマン評価
+・クーン評価
+・メリッサ</t>
+        </is>
+      </c>
+      <c r="H1146" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wZXNbyZcKLg</t>
+        </is>
+      </c>
+      <c r="J1146" s="2" t="inlineStr">
+        <is>
+          <t>wZXNbyZcKLg</t>
+        </is>
+      </c>
+      <c r="K1146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1147" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1147" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】シムメシュ&amp;ターミンガチャの最後に引くべきキャラを決めます【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1147" s="2" t="inlineStr">
+        <is>
+          <t>シムメシュ&amp;ターミンガチャの最終判断動画。
+ターミンとコッペパンが当たりで引く価値大。
+シムメシュ・ノーア・アレツはスルー推奨。</t>
+        </is>
+      </c>
+      <c r="E1147" s="2" t="inlineStr">
+        <is>
+          <t>・ターミンは唯一性が高く将来性◎
+・コッペパンは瀕死維持が初で無人島・レイドで活躍
+・シャムマベルは弓の幻闘場で貴重</t>
+        </is>
+      </c>
+      <c r="F1147" s="2" t="inlineStr">
+        <is>
+          <t>・シムメシュは代用が多くスルー
+・ノーアは魅力薄くスルー
+・アレツは入れ替わり激しくスルー</t>
+        </is>
+      </c>
+      <c r="G1147" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ最終判断
+・ターミン(引くべき)
+・コッペパン(引くべき)
+・シムメシュ/ノーア/アレツ(スルー)
+・シャムマベル(検討)</t>
+        </is>
+      </c>
+      <c r="H1147" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zjaikSwnK_8</t>
+        </is>
+      </c>
+      <c r="J1147" s="2" t="inlineStr">
+        <is>
+          <t>zjaikSwnK_8</t>
+        </is>
+      </c>
+      <c r="K1147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1148" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1148" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】【育成＋】EX1.こよみを止めろ！〜育成2枠〜自動周回：15秒‼️</t>
+        </is>
+      </c>
+      <c r="D1148" s="2" t="inlineStr">
+        <is>
+          <t>EX1「こよみを止めろ」の自動周回編成を紹介。
+ビクトール・裁判・AJ固定+育成2枠構成。
+15秒で回せる育成周回編成を解説。</t>
+        </is>
+      </c>
+      <c r="E1148" s="2" t="inlineStr">
+        <is>
+          <t>・育成枠2枠でも15秒で自動周回可能</t>
+        </is>
+      </c>
+      <c r="F1148" s="2" t="inlineStr"/>
+      <c r="G1148" s="2" t="inlineStr">
+        <is>
+          <t>・自動周回編成
+・こよみを止めろEX1
+・育成2枠
+・15秒周回</t>
+        </is>
+      </c>
+      <c r="H1148" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=l3pJjCinN-Q</t>
+        </is>
+      </c>
+      <c r="J1148" s="2" t="inlineStr">
+        <is>
+          <t>l3pJjCinN-Q</t>
+        </is>
+      </c>
+      <c r="K1148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1149" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1149" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】生放送終わりの最速でガチャ考察する配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D1149" s="2" t="inlineStr">
+        <is>
+          <t>公式生放送直後の最速ガチャ考察生配信。
+復刻の主人公ラインナップに懐かしさを実感。
+サガレコや連魔アプデ、魂の祠を確認。</t>
+        </is>
+      </c>
+      <c r="E1149" s="2" t="inlineStr">
+        <is>
+          <t>・サガレコが目玉機能
+・88の日は報酬が豪華
+・ポルカのバフ量がえぐい</t>
+        </is>
+      </c>
+      <c r="F1149" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場で斧スタイルが1ヶ月来ず救済に不満
+・9月より8月の幻闘場を救済してほしい</t>
+        </is>
+      </c>
+      <c r="G1149" s="2" t="inlineStr">
+        <is>
+          <t>・最速ガチャ考察
+・復刻主人公ガチャ
+・サガレコ
+・連魔アプデ
+・幻闘場</t>
+        </is>
+      </c>
+      <c r="H1149" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8UhzfK1Da-k</t>
+        </is>
+      </c>
+      <c r="J1149" s="2" t="inlineStr">
+        <is>
+          <t>8UhzfK1Da-k</t>
+        </is>
+      </c>
+      <c r="K1149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1150" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1150" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】幻闘場対策！能力アップ解除持ちスタイル一挙紹介【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1150" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月の幻闘場新強敵に向けた事前対策動画。
+能力アップ解除持ちスタイルを武器種別に紹介。
+槍・大剣は候補が少なく苦しいと指摘。</t>
+        </is>
+      </c>
+      <c r="E1150" s="2" t="inlineStr">
+        <is>
+          <t>・剣・体術・斧・大剣は解除候補が多く安心
+・T260Gは視聴で誰でも入手でき候補になる</t>
+        </is>
+      </c>
+      <c r="F1150" s="2" t="inlineStr">
+        <is>
+          <t>・大剣は解除候補が少なくきつい
+・槍は案外きつく苦しい武器種
+・証券は実装数が少なく戦力不足の懸念</t>
+        </is>
+      </c>
+      <c r="G1150" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場9月対策
+・能力アップ解除
+・武器種別スタイル紹介
+・継承運用</t>
+        </is>
+      </c>
+      <c r="H1150" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=v9_8_KDHv5o</t>
+        </is>
+      </c>
+      <c r="J1150" s="2" t="inlineStr">
+        <is>
+          <t>v9_8_KDHv5o</t>
+        </is>
+      </c>
+      <c r="K1150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1151" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1151" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】闘者の関門-アラケス-周回編成8種紹介 置き物ランキング有り 最速は6秒【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1151" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月アラケスの周回編成8種を紹介。
+弱点は斬、先制されるためOD攻撃推奨。
+最速はビクトール技3の6秒編成。</t>
+        </is>
+      </c>
+      <c r="E1151" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトール編成は最速6秒で周回可能
+・素早さバフがあればファスト技でも先行されない</t>
+        </is>
+      </c>
+      <c r="F1151" s="2" t="inlineStr">
+        <is>
+          <t>・素早さバフが足りないとファストでも先行される</t>
+        </is>
+      </c>
+      <c r="G1151" s="2" t="inlineStr">
+        <is>
+          <t>・アラケス周回編成
+・置き物ランキング
+・最速6秒
+・OD先制対策
+・素早さバフ</t>
+        </is>
+      </c>
+      <c r="H1151" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=blYYDfEVDrc</t>
+        </is>
+      </c>
+      <c r="J1151" s="2" t="inlineStr">
+        <is>
+          <t>blYYDfEVDrc</t>
+        </is>
+      </c>
+      <c r="K1151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29T01:10:16Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1151"/>
+  <dimension ref="A1:K1166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -75896,6 +75896,985 @@
         </is>
       </c>
     </row>
+    <row r="1152">
+      <c r="A1152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1152" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1152" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】6体ランキング!!「真っ当に斬雷」アタッカーマドレーンのついでにサポート&amp;「熱Weak」を究めたポルカの強力な火力サポート!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1152" s="2" t="inlineStr">
+        <is>
+          <t>マドレーンはマス型セミアタッカーで総合評価Bと微妙
+ポルカは熱ウィーク編成の攻防上げが優秀で属性SS
+両者ともエクストラ倍率やBP周りに不満が残る</t>
+        </is>
+      </c>
+      <c r="E1152" s="2" t="inlineStr">
+        <is>
+          <t>・ポルカは熱ウィーク編成で攻防上げが優秀(属性SS)
+・ポルカは防御バフ99%到達で非常に硬い
+・マドレーンも雷が刺さる敵ならアタッカーで役立つ</t>
+        </is>
+      </c>
+      <c r="F1152" s="2" t="inlineStr">
+        <is>
+          <t>・マドレーンは総合評価Bでアタッカーとして別段強くない
+・マドレーンはBP不足・消費BP増加で使いづらい
+・ポルカのエクストラOD1.75倍がせこくナーフ気味</t>
+        </is>
+      </c>
+      <c r="G1152" s="2" t="inlineStr">
+        <is>
+          <t>・マドレーン評価
+・ポルカ評価
+・マス型
+・熱ウィーク編成
+・エクストラOD
+・消費BP</t>
+        </is>
+      </c>
+      <c r="H1152" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=64WCix8HpsI</t>
+        </is>
+      </c>
+      <c r="J1152" s="2" t="inlineStr">
+        <is>
+          <t>64WCix8HpsI</t>
+        </is>
+      </c>
+      <c r="K1152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:11:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1153" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1153" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「伏兵」回避&amp;火力強化ヴァルドーの強さ&amp;槍部隊圧倒的進化で追憶が変わるようせいブラウニー　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1153" s="2" t="inlineStr">
+        <is>
+          <t>ヴァルドーは回避と火力サポートを両立し総合A
+妖精ブラウニーは槍特化で追憶の価値が向上し総合B
+どちらも尖った特攻性で槍/回避編成向け</t>
+        </is>
+      </c>
+      <c r="E1153" s="2" t="inlineStr">
+        <is>
+          <t>・ヴァルドーはエクストラOD1.75倍継続が強み
+・ヴァルドーは高めの火力バフと強力な捨てバフを持つ
+・ブラウニーは槍編成強化で追憶の活躍が期待できる</t>
+        </is>
+      </c>
+      <c r="F1153" s="2" t="inlineStr">
+        <is>
+          <t>・ヴァルドーの2弾被弾はパーティー全体にマイナス
+・攻防上げだけのスタイルは環境に必要ない
+・ブラウニーは多彩な回避も1つしか持ち込めない</t>
+        </is>
+      </c>
+      <c r="G1153" s="2" t="inlineStr">
+        <is>
+          <t>・ヴァルドー評価
+・ブラウニー評価
+・回避性能
+・槍編成
+・エクストラOD
+・追憶</t>
+        </is>
+      </c>
+      <c r="H1153" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rpL6u-6rQcc</t>
+        </is>
+      </c>
+      <c r="J1153" s="2" t="inlineStr">
+        <is>
+          <t>rpL6u-6rQcc</t>
+        </is>
+      </c>
+      <c r="K1153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:11:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1154" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1154" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SR カオスガンダム 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1154" s="2" t="inlineStr">
+        <is>
+          <t>SRカオスガンダムの武装アニメ紹介ショート
+戦闘ボイスのみで解説やレビューは無し
+Gジェネエターナルの武装演出を見せる動画</t>
+        </is>
+      </c>
+      <c r="E1154" s="2" t="inlineStr"/>
+      <c r="F1154" s="2" t="inlineStr"/>
+      <c r="G1154" s="2" t="inlineStr">
+        <is>
+          <t>・カオスガンダム
+・武装アニメ
+・ショート動画
+・Gジェネエターナル</t>
+        </is>
+      </c>
+      <c r="H1154" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BWGlkCdFYv4</t>
+        </is>
+      </c>
+      <c r="J1154" s="2" t="inlineStr">
+        <is>
+          <t>BWGlkCdFYv4</t>
+        </is>
+      </c>
+      <c r="K1154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:11:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1155" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1155" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】FA百式改が限定！8月31日ガシャ予告  『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D1155" s="2" t="inlineStr">
+        <is>
+          <t>8/31ガシャでFA百式改が限定実装(攻撃型)
+Vガンダムサード実装＆ゼータが初復刻
+百式改単体なら見送り、ゼータ混在で悩み中</t>
+        </is>
+      </c>
+      <c r="E1155" s="2" t="inlineStr">
+        <is>
+          <t>・FA百式改が限定ユニットなのはすごい
+・ゼータ初復刻で未入手勢に再入手機会</t>
+        </is>
+      </c>
+      <c r="F1155" s="2" t="inlineStr">
+        <is>
+          <t>・百式改だけなら引かなくてもいいと様子見
+・性能公開待ちで引くか悩ましい</t>
+        </is>
+      </c>
+      <c r="G1155" s="2" t="inlineStr">
+        <is>
+          <t>・FA百式改
+・8/31ガシャ予告
+・ゼータ初復刻
+・限定ユニット
+・Vガンダムサード</t>
+        </is>
+      </c>
+      <c r="H1155" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FopqOJd5T6M</t>
+        </is>
+      </c>
+      <c r="J1155" s="2" t="inlineStr">
+        <is>
+          <t>FopqOJd5T6M</t>
+        </is>
+      </c>
+      <c r="K1155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:11:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1156" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1156" s="2" t="inlineStr">
+        <is>
+          <t>【タガタメ】まさかの展開！？9月1日に重大発表！『誰ガ為のアルケミスト』</t>
+        </is>
+      </c>
+      <c r="D1156" s="2" t="inlineStr">
+        <is>
+          <t>タガタメが終了2年後に重大発表を予告
+9/1劇場版無料配信のラストで発表
+新作か買い切り復活か、投稿者は買い切り希望</t>
+        </is>
+      </c>
+      <c r="E1156" s="2" t="inlineStr">
+        <is>
+          <t>・サービス終了から動きがあるのは嬉しい
+・買い切りゲーで自由に遊べる方が嬉しい</t>
+        </is>
+      </c>
+      <c r="F1156" s="2" t="inlineStr">
+        <is>
+          <t>・新作スマホゲーは今の時世で生き残るのが難しそう</t>
+        </is>
+      </c>
+      <c r="G1156" s="2" t="inlineStr">
+        <is>
+          <t>・タガタメ
+・重大発表
+・9/1配信
+・新作予想
+・買い切りゲー</t>
+        </is>
+      </c>
+      <c r="H1156" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jJ0OvMkVSVI</t>
+        </is>
+      </c>
+      <c r="J1156" s="2" t="inlineStr">
+        <is>
+          <t>jJ0OvMkVSVI</t>
+        </is>
+      </c>
+      <c r="K1156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:11:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1157" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1157" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】FA百式改が限定！8月31日ガシャ予告  ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1157" s="2" t="inlineStr">
+        <is>
+          <t>8/31ガシャでFA百式改が限定実装(攻撃型)
+Vガンダムサード実装＆ゼータが初復刻
+百式改単体なら見送り、ゼータ混在で悩み中</t>
+        </is>
+      </c>
+      <c r="E1157" s="2" t="inlineStr">
+        <is>
+          <t>・FA百式改が限定ユニットなのはすごい
+・ゼータ初復刻で未入手勢に再入手機会</t>
+        </is>
+      </c>
+      <c r="F1157" s="2" t="inlineStr">
+        <is>
+          <t>・百式改だけなら引かなくてもいいと様子見
+・性能公開待ちで引くか悩ましい</t>
+        </is>
+      </c>
+      <c r="G1157" s="2" t="inlineStr">
+        <is>
+          <t>・FA百式改
+・8/31ガシャ予告
+・ゼータ初復刻
+・限定ユニット
+・ショート動画</t>
+        </is>
+      </c>
+      <c r="H1157" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wat4oOfB52Q</t>
+        </is>
+      </c>
+      <c r="J1157" s="2" t="inlineStr">
+        <is>
+          <t>wat4oOfB52Q</t>
+        </is>
+      </c>
+      <c r="K1157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:11:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1158" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1158" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】インフレカウントダウン開始！最新キャラランキング★くるぞ・・くるぞ！！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1158" s="2" t="inlineStr">
+        <is>
+          <t>週次キャラランキング、8周年前で冷静に評価
+ポルカSS・ブラウニーSS幻闘、リズはS
+バルドはA(無人島特化)、マドレーンは優先度低め</t>
+        </is>
+      </c>
+      <c r="E1158" s="2" t="inlineStr">
+        <is>
+          <t>・ポルカは弱点取れば全体防御99%で環境トップ級のSS
+・ブラウニーは槍幻闘の新水準・エクストラ2倍で強力なSS
+・リズは霊雷で神聖ターミ編成に入れられ強い</t>
+        </is>
+      </c>
+      <c r="F1158" s="2" t="inlineStr">
+        <is>
+          <t>・マドレーンはBP増加デメリットが邪魔で優先度低い
+・バルドは2回避弾で存在意義が無くなり無人島特化
+・必須級キャラは不在で8周年に温存推奨</t>
+        </is>
+      </c>
+      <c r="G1158" s="2" t="inlineStr">
+        <is>
+          <t>・キャラランキング
+・ポルカSS
+・ブラウニーSS
+・リズ評価
+・バルドA
+・8周年前温存</t>
+        </is>
+      </c>
+      <c r="H1158" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rsBhfqXqH44</t>
+        </is>
+      </c>
+      <c r="J1158" s="2" t="inlineStr">
+        <is>
+          <t>rsBhfqXqH44</t>
+        </is>
+      </c>
+      <c r="K1158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:11:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1159" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1159" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】最後の総括で緊急情報！6大ガチャランキング引くべき優先順位考察【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1159" s="2" t="inlineStr">
+        <is>
+          <t>6大ガチャの引くべき優先順位を考察
+1位白姫編、2位ポルカ編、3位リズ編
+必須級不在で来週の周年ガチャに温存推奨</t>
+        </is>
+      </c>
+      <c r="E1159" s="2" t="inlineStr">
+        <is>
+          <t>・ポルカ&amp;ブラウニーはどこかの幻闘上で使える(2位)
+・T260Gはタイムバフで現頭上に刺さる
+・オルロワージ&amp;白バラは防御80%超えで硬い(1位)</t>
+        </is>
+      </c>
+      <c r="F1159" s="2" t="inlineStr">
+        <is>
+          <t>・63連ガチャは無料分だけでいい(暦み無くインフレ落ち)
+・必須級スタイルは不在でトリプレ入りする子はいない
+・焦らず来週再来週の周年ガチャに石を温存すべき</t>
+        </is>
+      </c>
+      <c r="G1159" s="2" t="inlineStr">
+        <is>
+          <t>・6大ガチャランキング
+・白姫編1位
+・ポルカ編2位
+・リズ編3位
+・63連は最下位
+・8周年温存</t>
+        </is>
+      </c>
+      <c r="H1159" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wACqF_GxvMQ</t>
+        </is>
+      </c>
+      <c r="J1159" s="2" t="inlineStr">
+        <is>
+          <t>wACqF_GxvMQ</t>
+        </is>
+      </c>
+      <c r="K1159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:11:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1160" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1160" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ちょっと待った！！絶対損する63連ガチャの回し方！！プレゼンします【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1160" s="2" t="inlineStr">
+        <is>
+          <t>63連ガチャの天井交換は損する場合ありと注意
+年末更新で2025年分が天井交換可能になる
+今は交換せず8周年に向け石を温存推奨</t>
+        </is>
+      </c>
+      <c r="E1160" s="2" t="inlineStr">
+        <is>
+          <t>・年末更新で白バラやルクス大エンチャント等が交換可能でお得
+・過去の優秀スタイルが揃ういいガチャ</t>
+        </is>
+      </c>
+      <c r="F1160" s="2" t="inlineStr">
+        <is>
+          <t>・本当に必要なスタイルが無い限り天井交換すべきでない(損する)
+・今は交換せず年末・8周年まで待つべき</t>
+        </is>
+      </c>
+      <c r="G1160" s="2" t="inlineStr">
+        <is>
+          <t>・63連ガチャ
+・天井交換の注意
+・年末更新
+・白バラ交換
+・8周年温存</t>
+        </is>
+      </c>
+      <c r="H1160" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x9BVx91cVh4</t>
+        </is>
+      </c>
+      <c r="J1160" s="2" t="inlineStr">
+        <is>
+          <t>x9BVx91cVh4</t>
+        </is>
+      </c>
+      <c r="K1160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:11:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1161" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1161" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】最強の初代ヒロイン復活なるか！？リズ編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1161" s="2" t="inlineStr">
+        <is>
+          <t>リズ編3人(リズ/マドレーン/バルド)の性能チェック
+バルドは冷属性サポーター、リズは短期火力が抜群
+マドレーンはマス型で優先度低、急ぎ引く必要なし</t>
+        </is>
+      </c>
+      <c r="E1161" s="2" t="inlineStr">
+        <is>
+          <t>・バルドは冷属性編成で優秀なサポーター・攻撃避ければ強い
+・リズは冷ムで短期火力が抜群に高く火ダメ軽減も優秀
+・リズのディスペルアタックはバフ重複する敵に有効</t>
+        </is>
+      </c>
+      <c r="F1161" s="2" t="inlineStr">
+        <is>
+          <t>・マドレーンはマス型で消費BP増加が痛く優先度低い
+・リズは水流ライジンのヒートダウンで永続火力ダウンが大きい
+・バルドは2回被弾で式が消え条件作りが簡単でない</t>
+        </is>
+      </c>
+      <c r="G1161" s="2" t="inlineStr">
+        <is>
+          <t>・リズ編性能
+・バルド評価
+・マドレーン評価
+・リズ評価
+・冷属性編成
+・無人島</t>
+        </is>
+      </c>
+      <c r="H1161" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3ETMmkhA8m4</t>
+        </is>
+      </c>
+      <c r="J1161" s="2" t="inlineStr">
+        <is>
+          <t>3ETMmkhA8m4</t>
+        </is>
+      </c>
+      <c r="K1161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:11:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1162" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1162" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】帰ってきた初代主人公たちの実力は如何に！？ポルカ編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1162" s="2" t="inlineStr">
+        <is>
+          <t>ポルカ編3人(ブラウニー/イーブリン/ポルカ)の性能チェック
+ブラウニーはケルビン上位互換で当たり、槍幻闘のエース
+イーブリンとポルカは条件次第、急ぎ引く必要なし</t>
+        </is>
+      </c>
+      <c r="E1162" s="2" t="inlineStr">
+        <is>
+          <t>・妖精ブラウニーはケルビン上位互換で槍幻闘のエース・一番の当たり
+・イーブリンは陰/冷アタッカーで1発の火力が高い(最大4.5倍)
+・ポルカは熱属性弱点編成で条件が揃えばかなり強力</t>
+        </is>
+      </c>
+      <c r="F1162" s="2" t="inlineStr">
+        <is>
+          <t>・イーブリンはヒット数が少なく総ダメージが伸びにくい
+・ポルカは熱属性＋弱点前提で使用ハードルが高い
+・第1弾ガチャは無理して引く性能でなく様子見でOK</t>
+        </is>
+      </c>
+      <c r="G1162" s="2" t="inlineStr">
+        <is>
+          <t>・ポルカ編性能
+・ブラウニー評価
+・イーブリン評価
+・ポルカ評価
+・ケルビン上位互換
+・熱属性編成</t>
+        </is>
+      </c>
+      <c r="H1162" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=G7_99948joY</t>
+        </is>
+      </c>
+      <c r="J1162" s="2" t="inlineStr">
+        <is>
+          <t>G7_99948joY</t>
+        </is>
+      </c>
+      <c r="K1162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:11:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1163" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1163" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】超重要な注意喚起！これマジで間違えると詰みます...！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1163" s="2" t="inlineStr">
+        <is>
+          <t>アビサルサーカスの新イベントは進化手順に要注意
+メインだけ回すと副防具進化素材が足りず積む
+EX1を解放し周回、暦み専用の強力な神楽鈴を確保</t>
+        </is>
+      </c>
+      <c r="E1163" s="2" t="inlineStr">
+        <is>
+          <t>・神楽鈴はエクストラフォース1.5倍＋1ターン目ダメブロで暦みが大幅強化
+・ビクトール瀕死周回で11秒の高速周回が可能
+・開催期間18日と長めで正しく進めれば間に合う</t>
+        </is>
+      </c>
+      <c r="F1163" s="2" t="inlineStr">
+        <is>
+          <t>・メインだけ周回すると素材が膨大で積む(通常場所だと約10年)
+・進化素材はショップに追加されず逃すと復刻まで悔しい思い
+・イベント手順が非常に大変で放置すると間に合わない</t>
+        </is>
+      </c>
+      <c r="G1163" s="2" t="inlineStr">
+        <is>
+          <t>・アビサルサーカス
+・神楽鈴
+・副防具進化
+・EX周回
+・ビクトール瀕死周回
+・注意喚起</t>
+        </is>
+      </c>
+      <c r="H1163" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TIF-TisKsk0</t>
+        </is>
+      </c>
+      <c r="J1163" s="2" t="inlineStr">
+        <is>
+          <t>TIF-TisKsk0</t>
+        </is>
+      </c>
+      <c r="K1163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:11:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1164" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1164" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ポルカ&amp;リズガチャ性能チェック！全6体のキャラランク評価＆徹底解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1164" s="2" t="inlineStr">
+        <is>
+          <t>ポルカ&amp;リズガチャ全6体をテキスト評価
+ポルカ/イーブリン/ブラウニー/リズが星2
+マドレーン・バルドは星1、即引く壊れは不在</t>
+        </is>
+      </c>
+      <c r="E1164" s="2" t="inlineStr">
+        <is>
+          <t>・ブラウニーはリンクアビ強化版で火力・軽減が順当強化(場合により星3)
+・リズは霊雷の貴重な弓アタッカーでバフ解除も優秀
+・ポルカは幻闘上で90%超軽減を維持しやすい</t>
+        </is>
+      </c>
+      <c r="F1164" s="2" t="inlineStr">
+        <is>
+          <t>・マドレーンは初代から本質変わらず引きたい魅力が薄い(星1)
+・バルドは敵の攻撃依存で条件後のバフも冷続限定で限定的(星1)
+・ポルカはウィーク維持できないと持ち味が弱くなる</t>
+        </is>
+      </c>
+      <c r="G1164" s="2" t="inlineStr">
+        <is>
+          <t>・全6体ランク
+・ポルカ星2
+・リズ星2
+・ブラウニー星2
+・マドレーン星1
+・バルド星1</t>
+        </is>
+      </c>
+      <c r="H1164" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zu43TvAEj9I</t>
+        </is>
+      </c>
+      <c r="J1164" s="2" t="inlineStr">
+        <is>
+          <t>zu43TvAEj9I</t>
+        </is>
+      </c>
+      <c r="K1164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:11:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1165" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1165" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】SS3体確定！63連ガチャで当たり＆天井交換でのオススメスタイル紹介【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1165" s="2" t="inlineStr">
+        <is>
+          <t>SS3体確定63連ガチャの当たり＆天井交換候補紹介
+弓のアイス/シャムマベルやマイス、西洋等が高評価
+無料2回＋2万7千ジュエルで天井交換が可能</t>
+        </is>
+      </c>
+      <c r="E1165" s="2" t="inlineStr">
+        <is>
+          <t>・大決戦アイスは汎用性の高い弓でボルカノ幻闘に特攻
+・記憶の記録マイスはOD1.75倍で今なら補助が揃い交換候補上位
+・イシスはウィーク周回で最終ダメージ2倍の破格性能</t>
+        </is>
+      </c>
+      <c r="F1165" s="2" t="inlineStr">
+        <is>
+          <t>・記憶の記録マイスは条件が難しく扱いにくい
+・ポルカ・加藤は無人島特化で汎用ユーザーには優先度低い
+・愛紗/ボルス/猿は天井してまで引く必要はない</t>
+        </is>
+      </c>
+      <c r="G1165" s="2" t="inlineStr">
+        <is>
+          <t>・63連ガチャ
+・天井交換候補
+・弓スタイル
+・マイス
+・幻闘上特化
+・無人島スタイル</t>
+        </is>
+      </c>
+      <c r="H1165" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jWyZMWYPim0</t>
+        </is>
+      </c>
+      <c r="J1165" s="2" t="inlineStr">
+        <is>
+          <t>jWyZMWYPim0</t>
+        </is>
+      </c>
+      <c r="K1165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:11:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B1166" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1166" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベント解説 注意しないと後悔案件有り!!EX1.こよみの周回編成の紹介も!!【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1166" s="2" t="inlineStr">
+        <is>
+          <t>新イベント(暦みEX)の解説と注意喚起動画
+EX1こよみの周回編成も紹介
+※自動字幕が正しく取得できず詳細は要確認</t>
+        </is>
+      </c>
+      <c r="E1166" s="2" t="inlineStr"/>
+      <c r="F1166" s="2" t="inlineStr"/>
+      <c r="G1166" s="2" t="inlineStr">
+        <is>
+          <t>・新イベント解説
+・暦みEX1
+・周回編成
+・注意喚起</t>
+        </is>
+      </c>
+      <c r="H1166" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ihNZihZ0mzE</t>
+        </is>
+      </c>
+      <c r="J1166" s="2" t="inlineStr">
+        <is>
+          <t>ihNZihZ0mzE</t>
+        </is>
+      </c>
+      <c r="K1166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T01:11:17Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1166"/>
+  <dimension ref="A1:K1187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -76875,6 +76875,1387 @@
         </is>
       </c>
     </row>
+    <row r="1167">
+      <c r="A1167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1167" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1167" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「絶対スルー推奨」週間ランキング!!厄編VSポルカ&amp;リズ編→12体4ガチャランキング!!最新スタイルの最強を決める比較検討会→2026年8月30日版　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1167" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭のスタイルを厳選視点で評価
+1位はロボ、最新版無人島編成での活躍に期待
+他はほぼスルー推奨、黒バラは保険で確保</t>
+        </is>
+      </c>
+      <c r="E1167" s="2" t="inlineStr">
+        <is>
+          <t>・ロボは最新版無人島で活躍期待の堂々1位
+・黒バラは前捨て1000%級に仕上げる唯一性
+・パセは槍編成で今月の特攻スタイル
+・バルドの回避性能は環境随一でぶっ壊れ級</t>
+        </is>
+      </c>
+      <c r="F1167" s="2" t="inlineStr">
+        <is>
+          <t>・タマ君は性能がゲーム特性と全く合わず弱い
+・リズは謎のナーフで技5回限定＋回復なし
+・ポルカはエクストラ強化が1ターンのみのナーフ
+・大半のスタイルはスルー推奨</t>
+        </is>
+      </c>
+      <c r="G1167" s="2" t="inlineStr">
+        <is>
+          <t>・週間ランキング
+・スタイル評価
+・ロボ(無人島)
+・黒バラ
+・ガチャ厳選</t>
+        </is>
+      </c>
+      <c r="H1167" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Cq9WFmMPMXE</t>
+        </is>
+      </c>
+      <c r="J1167" s="2" t="inlineStr">
+        <is>
+          <t>Cq9WFmMPMXE</t>
+        </is>
+      </c>
+      <c r="K1167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:34:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1168" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1168" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「これで全力か?」アビスに引き込まれたタマゴロー…消える直前の「厄」ガチャから何を狙う!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1168" s="2" t="inlineStr">
+        <is>
+          <t>厄ガチャを引くコント調のガチャ実況
+黒バラ狙いだが皇帝強化は見送り
+継承の隙間がなく気楽に回す</t>
+        </is>
+      </c>
+      <c r="E1168" s="2" t="inlineStr">
+        <is>
+          <t>・プルが早く引けて1つスキップできた</t>
+        </is>
+      </c>
+      <c r="F1168" s="2" t="inlineStr">
+        <is>
+          <t>・皇帝のチョイパワーアップは回せず諦め
+・強いスタイルが来ず使用シーンが限られる</t>
+        </is>
+      </c>
+      <c r="G1168" s="2" t="inlineStr">
+        <is>
+          <t>・厄ガチャ
+・黒バラ狙い
+・ガチャ実況
+・皇帝強化見送り</t>
+        </is>
+      </c>
+      <c r="H1168" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dKyJNjDGdOI</t>
+        </is>
+      </c>
+      <c r="J1168" s="2" t="inlineStr">
+        <is>
+          <t>dKyJNjDGdOI</t>
+        </is>
+      </c>
+      <c r="K1168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:34:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1169" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1169" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　生放送同時視聴　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1169" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープを同時視聴しながらの雑談配信
+ガチャを引かず育成で戦闘力33万まで強化
+ロマサガRSは井戸と幻闘場が楽しみでモチベは維持</t>
+        </is>
+      </c>
+      <c r="E1169" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャを引かず育成でも戦闘力33万まで伸ばせた
+・RSは記憶再戦をやり込め井戸・幻闘場が楽しみ
+・お酒の勢いで引いたパセが化け物級に強かった</t>
+        </is>
+      </c>
+      <c r="F1169" s="2" t="inlineStr">
+        <is>
+          <t>・W6の108星ワイス上げがきつい
+・弱点を突けないボスで攻略が難しい
+・過去にイベントがしょぼくモチベが落ち配信をやめかけた</t>
+        </is>
+      </c>
+      <c r="G1169" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸スターリープ
+・同時視聴配信
+・育成方針
+・RSモチベーション
+・雑談</t>
+        </is>
+      </c>
+      <c r="H1169" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XxGdJU-XoLo</t>
+        </is>
+      </c>
+      <c r="J1169" s="2" t="inlineStr">
+        <is>
+          <t>XxGdJU-XoLo</t>
+        </is>
+      </c>
+      <c r="K1169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:41:52Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1170" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1170" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】豊臣１体どれ選ぶ？　選択　後悔しない箱</t>
+        </is>
+      </c>
+      <c r="D1170" s="2" t="inlineStr">
+        <is>
+          <t>豊臣SSR有効箱の1体選定を考察
+20体を兵科・配置別に評価
+おすすめは石田三成やねね、秀長</t>
+        </is>
+      </c>
+      <c r="E1170" s="2" t="inlineStr">
+        <is>
+          <t>・石田三成は強化70%＋会心上昇で弓サポートが優秀
+・ねねは覚醒で攻撃・兵法上昇が付き鉄砲サポートが高性能
+・豊臣秀長は弓の最強格デバフキャラ
+・20体から1体選べる仕様が嬉しい</t>
+        </is>
+      </c>
+      <c r="F1170" s="2" t="inlineStr">
+        <is>
+          <t>・ねねは1段階上げても回復しか伸びず悩ましい
+・豊臣秀吉は火力がそこまで高くない
+・自身は覚醒が進んでおらず使えるキャラが限られる</t>
+        </is>
+      </c>
+      <c r="G1170" s="2" t="inlineStr">
+        <is>
+          <t>・豊臣有効箱
+・1体選定
+・兵科別評価
+・おすすめ武将</t>
+        </is>
+      </c>
+      <c r="H1170" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mdcb4L4bZa8</t>
+        </is>
+      </c>
+      <c r="J1170" s="2" t="inlineStr">
+        <is>
+          <t>mdcb4L4bZa8</t>
+        </is>
+      </c>
+      <c r="K1170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:35:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1171" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1171" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】火力高めの恒常支援！Ｄガンダム・サードの性能 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1171" s="2" t="inlineStr">
+        <is>
+          <t>Dガンダム・サードの性能を確認
+支援型で射程1-5と使いやすい
+避弾しなければ支援火力が上昇</t>
+        </is>
+      </c>
+      <c r="E1171" s="2" t="inlineStr">
+        <is>
+          <t>・EX武装射程1-5が現状一番使いやすい
+・デバフ防御25%減も使いやすい
+・支援火力は高めの印象</t>
+        </is>
+      </c>
+      <c r="F1171" s="2" t="inlineStr">
+        <is>
+          <t>・無理して取る必要は今回ない</t>
+        </is>
+      </c>
+      <c r="G1171" s="2" t="inlineStr">
+        <is>
+          <t>・Dガンダム・サード
+・支援型
+・ダリー
+・ガチャ性能</t>
+        </is>
+      </c>
+      <c r="H1171" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Rwy-ywmsMfo</t>
+        </is>
+      </c>
+      <c r="J1171" s="2" t="inlineStr">
+        <is>
+          <t>Rwy-ywmsMfo</t>
+        </is>
+      </c>
+      <c r="K1171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:34:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1172" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1172" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】Zに上方修正有！8月31日ガシャの性能確認 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D1172" s="2" t="inlineStr">
+        <is>
+          <t>8月31日ガチャ実装ユニットの性能を確認
+FA百式改・Zガンダム復刻などを解説
+1.5周年前で今回はスルー予定</t>
+        </is>
+      </c>
+      <c r="E1172" s="2" t="inlineStr">
+        <is>
+          <t>・FA百式改は戦うほど強くなり脱出機能持ち
+・Zガンダムは上方修正でクリ率10%＆タグ追加
+・ブライトは不闘複屈初のHP回復URで嬉しい枠</t>
+        </is>
+      </c>
+      <c r="F1172" s="2" t="inlineStr">
+        <is>
+          <t>・FA百式改のスキルがフォースガードで攻撃型と噛み合わない
+・1.5周年直前なので今回のガチャはスルー</t>
+        </is>
+      </c>
+      <c r="G1172" s="2" t="inlineStr">
+        <is>
+          <t>・8月31日ガチャ
+・FA百式改
+・Zガンダム復刻
+・上方修正
+・スルー判断</t>
+        </is>
+      </c>
+      <c r="H1172" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ccodwjs1qfM</t>
+        </is>
+      </c>
+      <c r="J1172" s="2" t="inlineStr">
+        <is>
+          <t>ccodwjs1qfM</t>
+        </is>
+      </c>
+      <c r="K1172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:34:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1173" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1173" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】攻撃するたび火力アップ！FA百式改の性能 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1173" s="2" t="inlineStr">
+        <is>
+          <t>FA百式改の性能を確認
+攻撃型で戦うほど攻撃力が上昇
+脱出機能で1回やられても場に残れる</t>
+        </is>
+      </c>
+      <c r="E1173" s="2" t="inlineStr">
+        <is>
+          <t>・戦うほど攻撃力が最大20%上昇
+・脱出機能で1回やられても残れる
+・チャンスステップ2回でエウゴ強化</t>
+        </is>
+      </c>
+      <c r="F1173" s="2" t="inlineStr">
+        <is>
+          <t>・スキルがフォースガードで攻撃型と噛み合わない</t>
+        </is>
+      </c>
+      <c r="G1173" s="2" t="inlineStr">
+        <is>
+          <t>・FA百式改
+・攻撃型
+・クアトロ
+・チャンスステップ</t>
+        </is>
+      </c>
+      <c r="H1173" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=erdIrTQLqoc</t>
+        </is>
+      </c>
+      <c r="J1173" s="2" t="inlineStr">
+        <is>
+          <t>erdIrTQLqoc</t>
+        </is>
+      </c>
+      <c r="K1173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:34:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1174" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1174" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SR アビスガンダム 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1174" s="2" t="inlineStr">
+        <is>
+          <t>アビスガンダムの武装アニメを紹介
+SRユニットの演出ショート
+セリフ演出のみで解説なし</t>
+        </is>
+      </c>
+      <c r="E1174" s="2" t="inlineStr"/>
+      <c r="F1174" s="2" t="inlineStr"/>
+      <c r="G1174" s="2" t="inlineStr">
+        <is>
+          <t>・アビスガンダム
+・武装アニメ
+・SRユニット</t>
+        </is>
+      </c>
+      <c r="H1174" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=eudEavmE8SA</t>
+        </is>
+      </c>
+      <c r="J1174" s="2" t="inlineStr">
+        <is>
+          <t>eudEavmE8SA</t>
+        </is>
+      </c>
+      <c r="K1174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:34:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1175" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1175" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】EX周回14編成！最速10秒★コメント欄に編成代用相談可【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1175" s="2" t="inlineStr">
+        <is>
+          <t>EX周回の高速編成を14種紹介
+ビクトールなし編成も多数共有
+最速10秒でEX1・2を周回</t>
+        </is>
+      </c>
+      <c r="E1175" s="2" t="inlineStr">
+        <is>
+          <t>・最速10秒でワンパン周回が可能
+・ビクトールなしでも回せる編成が豊富
+・コッぺパンが非常に優秀
+・EX2は元気玉が210と一気に増えてお得</t>
+        </is>
+      </c>
+      <c r="F1175" s="2" t="inlineStr">
+        <is>
+          <t>・育成不足だとワンパンできず粘りが必要
+・リアルクイーンはオーバードライブで連撃暴発の注意点</t>
+        </is>
+      </c>
+      <c r="G1175" s="2" t="inlineStr">
+        <is>
+          <t>・EX周回
+・14編成
+・ビクトールなし
+・最速10秒
+・元気玉</t>
+        </is>
+      </c>
+      <c r="H1175" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3rb7YPRLByc</t>
+        </is>
+      </c>
+      <c r="J1175" s="2" t="inlineStr">
+        <is>
+          <t>3rb7YPRLByc</t>
+        </is>
+      </c>
+      <c r="K1175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:35:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1176" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1176" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみEX3の注意点！ターニングポイント【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1176" s="2" t="inlineStr">
+        <is>
+          <t>こよみEX3の注意点を解説
+進化素材が増えるので早めの解放推奨
+EX4は味方ワンパンの可能性</t>
+        </is>
+      </c>
+      <c r="E1176" s="2" t="inlineStr">
+        <is>
+          <t>・EX3は進化ドロップ素材が増えるので早めが得
+・コッぺパンが優秀で11秒周回
+・EX4はさらにワンパンしやすくなりそう</t>
+        </is>
+      </c>
+      <c r="F1176" s="2" t="inlineStr">
+        <is>
+          <t>・EX3をワンパンできず何度も失敗する場面あり
+・ノーマルクエストでは進化素材が落ちない注意</t>
+        </is>
+      </c>
+      <c r="G1176" s="2" t="inlineStr">
+        <is>
+          <t>・こよみEX3
+・進化素材
+・EX高速周回
+・コッぺパン
+・ターニングポイント</t>
+        </is>
+      </c>
+      <c r="H1176" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D09ayvBfqlI</t>
+        </is>
+      </c>
+      <c r="J1176" s="2" t="inlineStr">
+        <is>
+          <t>D09ayvBfqlI</t>
+        </is>
+      </c>
+      <c r="K1176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:35:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1177" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1177" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】最近始めた人もEX高速周回！まだあきらめない引くべきガチャと編成方法解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1177" s="2" t="inlineStr">
+        <is>
+          <t>最近始めた人向けにEX高速周回の編成を解説
+引くべきは白黒バラ・260G・AJ・雪だるま
+38秒で周回可能</t>
+        </is>
+      </c>
+      <c r="E1177" s="2" t="inlineStr">
+        <is>
+          <t>・白姫260Gオルロアージュは高難度で強く今後も使える
+・黒バラは今回本当に高性能
+・最新ガチャ3人＋AJ雪だるまはお得な編成
+・石が豊富な始めたばかりの人はやる価値あり</t>
+        </is>
+      </c>
+      <c r="F1177" s="2" t="inlineStr">
+        <is>
+          <t>・天井まで回しても目当てが1体も出ない覚悟が必要
+・ノーマルクエストでは進化素材が落ちず強アクセを持てない
+・EX4まで素材集めは今の石を投資する必要あり</t>
+        </is>
+      </c>
+      <c r="G1177" s="2" t="inlineStr">
+        <is>
+          <t>・初心者向け
+・引くべきガチャ
+・白黒バラ
+・AJ・雪だるま
+・38秒周回</t>
+        </is>
+      </c>
+      <c r="H1177" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=a5lnMiMoX1Y</t>
+        </is>
+      </c>
+      <c r="J1177" s="2" t="inlineStr">
+        <is>
+          <t>a5lnMiMoX1Y</t>
+        </is>
+      </c>
+      <c r="K1177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:35:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1178" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1178" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】これは絶対に全員把握すべき！過去最大級の神アプデがやってきました【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1178" s="2" t="inlineStr">
+        <is>
+          <t>過去最大級の神アプデ内容を総まとめ
+サガレコや一括連磨、武器連磨強化が目玉
+8周年に向け盛り上がる要素多数</t>
+        </is>
+      </c>
+      <c r="E1178" s="2" t="inlineStr">
+        <is>
+          <t>・サガレコは楽曲聞き放題＋バックグラウンド再生で神機能
+・一括連磨でまとめて連磨可能になり快適
+・武器連磨が単体800%まで対応し大幅強化
+・8周年88日前からログボが配られ嬉しい</t>
+        </is>
+      </c>
+      <c r="F1178" s="2" t="inlineStr">
+        <is>
+          <t>・魂の正域の即帰チケットは2000枚で1周分と消費が重すぎる
+・Webショップへの誘導が露骨で運営の事情を感じる</t>
+        </is>
+      </c>
+      <c r="G1178" s="2" t="inlineStr">
+        <is>
+          <t>・サガレコ
+・一括連磨
+・武器連磨強化
+・ソウルアビリティ
+・8周年カウントダウン</t>
+        </is>
+      </c>
+      <c r="H1178" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QBWK5SX_wgg</t>
+        </is>
+      </c>
+      <c r="J1178" s="2" t="inlineStr">
+        <is>
+          <t>QBWK5SX_wgg</t>
+        </is>
+      </c>
+      <c r="K1178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:39:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1179" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1179" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】誰がこの結果予想できた！？最新版確保優先度ランキング【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1179" s="2" t="inlineStr">
+        <is>
+          <t>8月31日最新版の確保優先度ランキング
+最優先は復刻AJで置き物として今も最強
+新キャラは思ったほど強くない</t>
+        </is>
+      </c>
+      <c r="E1179" s="2" t="inlineStr">
+        <is>
+          <t>・AJは復刻でも置き物1位で使わない日はない
+・オルロアージュ・白バラは高評価で高難度に強い
+・妖精ブラウニーは満足度が高く当たり枠
+・復刻でも価値が残るのはいい流れ</t>
+        </is>
+      </c>
+      <c r="F1179" s="2" t="inlineStr">
+        <is>
+          <t>・ポルカ編・リズ編の新キャラは思ったほど強くない
+・T260アビスは3〜4ターン限定でピーキーすぎ使い所がない
+・バルドはレゾナンスパでしか使えず活躍場所がない
+・最終皇帝女は過去の最終皇帝より物足りない</t>
+        </is>
+      </c>
+      <c r="G1179" s="2" t="inlineStr">
+        <is>
+          <t>・確保優先度
+・AJ最優先
+・オルロアージュ・白バラ
+・ポルカ編・リズ編
+・T260アビス</t>
+        </is>
+      </c>
+      <c r="H1179" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TbAusE6iTP8</t>
+        </is>
+      </c>
+      <c r="J1179" s="2" t="inlineStr">
+        <is>
+          <t>TbAusE6iTP8</t>
+        </is>
+      </c>
+      <c r="K1179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:39:17Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1180" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1180" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】【生声解説】第135回ジュエルビーストの井戸~螺旋の~強敵❗️スタンバイターン＋リキャスト無効‼️大活躍28体特集‼️</t>
+        </is>
+      </c>
+      <c r="D1180" s="2" t="inlineStr">
+        <is>
+          <t>第135回ジュエルビーストの井戸を生声で考察
+スタンバイ＋リキャスト無効で活躍する28体を紹介
+残属性弱点、3ターン以内決着が鍵</t>
+        </is>
+      </c>
+      <c r="E1180" s="2" t="inlineStr">
+        <is>
+          <t>・アレツはスタンバイ無効で最初から52連チャンと強力
+・アセルスは5手60ヒット連発で大注目
+・白バラ姫アビスは陰属性強化で使えそう
+・雪だるまのエクストラフォース2.5倍連発が面白そう</t>
+        </is>
+      </c>
+      <c r="F1180" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋560回では宝石のきらめきで一気に弱体化し全滅
+・コッぺパンは代償ダメージがきつく井戸では厳しい
+・熱霊雷陰属性で攻撃すると敵火力が上がり危険</t>
+        </is>
+      </c>
+      <c r="G1180" s="2" t="inlineStr">
+        <is>
+          <t>・ジュエルビースト井戸
+・スタンバイ・リキャスト無効
+・残属性弱点
+・活躍28体
+・おすすめ編成6種</t>
+        </is>
+      </c>
+      <c r="H1180" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YRkp0fVYzj0</t>
+        </is>
+      </c>
+      <c r="J1180" s="2" t="inlineStr">
+        <is>
+          <t>YRkp0fVYzj0</t>
+        </is>
+      </c>
+      <c r="K1180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:40:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1181" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1181" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】【超強敵】ジュエルビーストの井戸〜ギミックと対策を考察〜これでアナタもクリアだ‼️</t>
+        </is>
+      </c>
+      <c r="D1181" s="2" t="inlineStr">
+        <is>
+          <t>ジュエルビースト井戸のギミックと対策を考察
+鬼畜な強さで全滅者続出、クリアのヒントを解説
+カウンター回避とダメブロ対策が鍵</t>
+        </is>
+      </c>
+      <c r="E1181" s="2" t="inlineStr">
+        <is>
+          <t>・ダメブロ付与・回避付与・エマ系が火力対策に大変有効
+・残属性が絡めばクリアは問題ない
+・前捨てデバフキャラで攻守を弱体化するのが良い</t>
+        </is>
+      </c>
+      <c r="F1181" s="2" t="inlineStr">
+        <is>
+          <t>・鬼畜な強さで多くのプレイヤーが全滅する
+・熱霊雷陰属性のアタッカーは敵火力を上げるので危険
+・2ターン目のビーストタックルは直接攻撃だとカウンター被弾</t>
+        </is>
+      </c>
+      <c r="G1181" s="2" t="inlineStr">
+        <is>
+          <t>・ギミック対策
+・カウンター回避
+・ダメブロ・回避付与
+・属性の注意
+・早期決着</t>
+        </is>
+      </c>
+      <c r="H1181" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fw0uF1L4R3k</t>
+        </is>
+      </c>
+      <c r="J1181" s="2" t="inlineStr">
+        <is>
+          <t>fw0uF1L4R3k</t>
+        </is>
+      </c>
+      <c r="K1181" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:40:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1182" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1182" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】スタンバイターンキャラ21体・リキャストターンキャラ11体〜全32体〜徹底考察‼️【ジュエルビーストの井戸実装でスタンバイターンリキャストターン無効来る‼️】</t>
+        </is>
+      </c>
+      <c r="D1182" s="2" t="inlineStr">
+        <is>
+          <t>スタンバイ・リキャスト無効で輝く全32体を徹底考察
+スタンバイ21体・リキャスト11体を評価
+ジュエルビースト実装に合わせた特別評価</t>
+        </is>
+      </c>
+      <c r="E1182" s="2" t="inlineStr">
+        <is>
+          <t>・アレツは52ヒット技がいきなり放て激強
+・タイムはスタンバイ外れれば高難度・井戸・レイドで使える
+・タコジは冷続強化2倍付与で好スタイル
+・白姫アビスは2ター目から最大1200%バフで優秀</t>
+        </is>
+      </c>
+      <c r="F1182" s="2" t="inlineStr">
+        <is>
+          <t>・雪だるまタックルは今の環境では強くない
+・グレイはスタンバイ抜きでも使いづらい
+・サルインは他に強力な継承技がありそこまで使わない</t>
+        </is>
+      </c>
+      <c r="G1182" s="2" t="inlineStr">
+        <is>
+          <t>・スタンバイ21体
+・リキャスト11体
+・全32体評価
+・無効時の特別評価
+・継承技</t>
+        </is>
+      </c>
+      <c r="H1182" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=n4KX_VHpatg</t>
+        </is>
+      </c>
+      <c r="J1182" s="2" t="inlineStr">
+        <is>
+          <t>n4KX_VHpatg</t>
+        </is>
+      </c>
+      <c r="K1182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:40:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1183" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1183" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「リズ 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1183" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭リズ編の3スタイルを考察・ランク付け
+リズは短期火力型でA-、バルドB+、マドレンB
+開催期間が長くジバート待ちで急がない推奨</t>
+        </is>
+      </c>
+      <c r="E1183" s="2" t="inlineStr">
+        <is>
+          <t>・リズは5回まで超火力の弓アタッカーで幻闘場3ヶ月連続活躍の可能性
+・リズは9月幻闘場で特攻スタイルの可能性が高い
+・バルドは冷続パの余ダメ底上げ役で尖った性能
+・マドレンは味方OD攻撃を1.75倍にする強力効果</t>
+        </is>
+      </c>
+      <c r="F1183" s="2" t="inlineStr">
+        <is>
+          <t>・リズは5回打ち終わると2400%余ダメ低下でアタッカー不能
+・バルドはマイターン避弾1回以内が難しく安定しない
+・マドレンはBP+5デメリットが重く剣スタイルで需要は微妙</t>
+        </is>
+      </c>
+      <c r="G1183" s="2" t="inlineStr">
+        <is>
+          <t>・リズ編考察
+・リズリンウッド
+・バルド
+・マドレン
+・ランク付け</t>
+        </is>
+      </c>
+      <c r="H1183" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7KjnjTUiryc</t>
+        </is>
+      </c>
+      <c r="J1183" s="2" t="inlineStr">
+        <is>
+          <t>7KjnjTUiryc</t>
+        </is>
+      </c>
+      <c r="K1183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:40:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1184" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1184" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「ポルカ 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1184" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭ポルカ編の3スタイルを考察・ランク付け
+ポルカB+、槍のブラウニー(パセ)A-、イーブリンB
+開催期間が長く後続ガチャを見て判断推奨</t>
+        </is>
+      </c>
+      <c r="E1184" s="2" t="inlineStr">
+        <is>
+          <t>・ポルカはウィーク前提で最大99.76%の脅威的火ダメ軽減
+・ブラウニーは槍5人で攻撃倍率2倍＋OD常時満タで優秀
+・ブラウニーはケルビンの代わりで半年〜1年幻闘場で使えそう
+・イーブリンは火ダメ87%軽減で冷続サポーター採用圏内</t>
+        </is>
+      </c>
+      <c r="F1184" s="2" t="inlineStr">
+        <is>
+          <t>・ポルカは熱・残弱点かつ先制条件が要る特化型で万能でない
+・ブラウニーは槍人数が減ると効果激減で高難度は使いづらい
+・イーブリンはヒット数が少なく火力はそこそこ</t>
+        </is>
+      </c>
+      <c r="G1184" s="2" t="inlineStr">
+        <is>
+          <t>・ポルカ編考察
+・ポルカリンウッド
+・ブラウニー(パセ)
+・イーブリン
+・ランク付け</t>
+        </is>
+      </c>
+      <c r="H1184" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MZRN8KPlzLU</t>
+        </is>
+      </c>
+      <c r="J1184" s="2" t="inlineStr">
+        <is>
+          <t>MZRN8KPlzLU</t>
+        </is>
+      </c>
+      <c r="K1184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:40:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1185" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1185" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】斧・銃・小剣の幻闘場を頑張る配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D1185" s="2" t="inlineStr">
+        <is>
+          <t>斧・銃・小剣の幻闘場に挑む生配信
+小剣14証券は3までクリア、5は届かず辛い
+パセ確保やリズ評価、進化強化の雑談も</t>
+        </is>
+      </c>
+      <c r="E1185" s="2" t="inlineStr">
+        <is>
+          <t>・パセ(ブラウニー)は槍大＋OD満タ＋火ダメ軽減で絶対当たりの確保案件
+・リズは短期火力でレイドや周回にも使えそう
+・進化強化で暦読み・槍が大幅強化され強い
+・上10証券は3〜4ならクリアしやすい</t>
+        </is>
+      </c>
+      <c r="F1185" s="2" t="inlineStr">
+        <is>
+          <t>・小剣14証券は5がクリアできず辛い
+・8周年ミッションが複雑で技術ランクアップ8回など面倒
+・武器連磨のオールサガ300は微妙で使い所を選ぶ
+・マカ＆つきは防御面が変わらず引いた人が報われない</t>
+        </is>
+      </c>
+      <c r="G1185" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場挑戦
+・小剣14証券
+・パセ(ブラウニー)確保
+・武器連磨
+・8周年ミッション</t>
+        </is>
+      </c>
+      <c r="H1185" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xMDxmlioIEc</t>
+        </is>
+      </c>
+      <c r="J1185" s="2" t="inlineStr">
+        <is>
+          <t>xMDxmlioIEc</t>
+        </is>
+      </c>
+      <c r="K1185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:41:52Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B1186" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1186" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベント EX2.仲間と共に EX1との違いを解説 周回編成16種紹介!!10秒〜17秒 自由枠有りの編成もあります!!【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1186" s="2" t="inlineStr">
+        <is>
+          <t>新イベントEX2の周回編成を16種紹介
+EX1との違いを解説、EX2の方が周回しやすい
+10〜17秒、自由枠ありの編成も</t>
+        </is>
+      </c>
+      <c r="E1186" s="2" t="inlineStr">
+        <is>
+          <t>・EX2はドロップ量が増え周回しやすい
+・最速10秒の高速編成を多数紹介
+・自由枠ありの編成もあり代用しやすい</t>
+        </is>
+      </c>
+      <c r="F1186" s="2" t="inlineStr">
+        <is>
+          <t>・力姫ラス図のSS化に必要な同向はEX1では落ちずEX2以降のみ</t>
+        </is>
+      </c>
+      <c r="G1186" s="2" t="inlineStr">
+        <is>
+          <t>・EX2周回
+・編成16種
+・EX1との違い
+・10〜17秒
+・自由枠あり</t>
+        </is>
+      </c>
+      <c r="H1186" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B4ijM7RmIio</t>
+        </is>
+      </c>
+      <c r="J1186" s="2" t="inlineStr">
+        <is>
+          <t>B4ijM7RmIio</t>
+        </is>
+      </c>
+      <c r="K1186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:40:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1187" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1187" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベント [EX3.新たな星と] EX1と2と3の違いの解説 周回編成26種紹介!!9秒〜14秒【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1187" s="2" t="inlineStr">
+        <is>
+          <t>新イベントEX3の周回編成を26種紹介
+EX1・2・3の違いを解説
+9〜14秒の高速周回編成</t>
+        </is>
+      </c>
+      <c r="E1187" s="2" t="inlineStr">
+        <is>
+          <t>・9〜14秒の高速周回編成を多数紹介</t>
+        </is>
+      </c>
+      <c r="F1187" s="2" t="inlineStr"/>
+      <c r="G1187" s="2" t="inlineStr">
+        <is>
+          <t>・EX3周回
+・編成26種
+・EX違い解説
+・高速周回</t>
+        </is>
+      </c>
+      <c r="H1187" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=erPm55O5H6I</t>
+        </is>
+      </c>
+      <c r="J1187" s="2" t="inlineStr">
+        <is>
+          <t>erPm55O5H6I</t>
+        </is>
+      </c>
+      <c r="K1187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31T13:34:26Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1187"/>
+  <dimension ref="A1:K1211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -78256,6 +78256,1576 @@
         </is>
       </c>
     </row>
+    <row r="1188">
+      <c r="A1188" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1188" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1188" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ジャミル超強化で「弓/必勝立ち回り」&amp;「メンツ豊富」な杖なのに勝てないのは〇〇が当たらないから　追憶の幻闘場トゥ・クアイ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1188" s="2" t="inlineStr">
+        <is>
+          <t>弓は最難だが最新リズでジャミルを維持し安定攻略。
+杖は火力十分だが敵の術回避で苦戦、ODデバフ解除で対応。
+敵の高バフ直後にデバフを当てるのが攻略の鍵。</t>
+        </is>
+      </c>
+      <c r="E1188" s="2" t="inlineStr">
+        <is>
+          <t>・リズは単体強化＋回復で耐久が成立し必須級
+・ジャミル超強化で弓がかなりやりやすい
+・アイスのアローシャワーが必須の動き</t>
+        </is>
+      </c>
+      <c r="F1188" s="2" t="inlineStr">
+        <is>
+          <t>・弓は最難関
+・敵の術が当たらないバグったステータス
+・強化破りされるとバフが消え1ター目に戻る</t>
+        </is>
+      </c>
+      <c r="G1188" s="2" t="inlineStr">
+        <is>
+          <t>・追憶の幻闘場トゥ・クアイ
+・弓/杖攻略
+・ジャミル
+・リズ
+・バフ解除</t>
+        </is>
+      </c>
+      <c r="H1188" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Judr9TllL0A</t>
+        </is>
+      </c>
+      <c r="J1188" s="2" t="inlineStr">
+        <is>
+          <t>Judr9TllL0A</t>
+        </is>
+      </c>
+      <c r="K1188" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1189" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1189" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】難関「槍/必勝立ち回り」ハンニバルにかけろ&amp;「バフ解除豊富」な小剣をどう扱う!?　追憶の幻闘場トゥ・クアイ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1189" s="2" t="inlineStr">
+        <is>
+          <t>槍は難関だがハンニバルが刺さる編成を紹介。
+小剣はバフ解除豊富だがメンツは強くない。
+敵HPが一定以下でバフ入りすぎ判定のデスコンボに注意。</t>
+        </is>
+      </c>
+      <c r="E1189" s="2" t="inlineStr">
+        <is>
+          <t>・難関の槍にハンニバルが刺さる
+・ジェラールの火力が飛び抜けている
+・西王のデバフがダメージアップに有効</t>
+        </is>
+      </c>
+      <c r="F1189" s="2" t="inlineStr">
+        <is>
+          <t>・敵HPゾーンでバフ解除・スタンのデスコンボ
+・小剣はメンツが強くない
+・確定行動でなく調整が難しい</t>
+        </is>
+      </c>
+      <c r="G1189" s="2" t="inlineStr">
+        <is>
+          <t>・トゥ・クアイ
+・槍/小剣攻略
+・ハンニバル
+・バフ解除
+・敵HPゾーン</t>
+        </is>
+      </c>
+      <c r="H1189" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vUJ8BfXm_e4</t>
+        </is>
+      </c>
+      <c r="J1189" s="2" t="inlineStr">
+        <is>
+          <t>vUJ8BfXm_e4</t>
+        </is>
+      </c>
+      <c r="K1189" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1190" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1190" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】勝ち筋掴め「真・ギミック解明」体術/銃/棍棒/斧まとめて4パターン攻略!!　追憶の幻闘場トゥ・クアイ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1190" s="2" t="inlineStr">
+        <is>
+          <t>速報から状況が変わりあっさり倒せる新立ち回り。
+敵の高バフ直後にデバフを打ち込むのが重要。
+HPは低く立ち回り次第でアタッカー不要。</t>
+        </is>
+      </c>
+      <c r="E1190" s="2" t="inlineStr">
+        <is>
+          <t>・見た目強いがHP低くめちゃくちゃ弱い
+・バフ解除薬の優先度が高い
+・成熟した立ち回りなら早く倒せる</t>
+        </is>
+      </c>
+      <c r="F1190" s="2" t="inlineStr">
+        <is>
+          <t>・スタンで無理やり3ターンに収める運ゲー
+・ナ払いが鬱陶しい
+・バフ解除いないとダメージ通らない</t>
+        </is>
+      </c>
+      <c r="G1190" s="2" t="inlineStr">
+        <is>
+          <t>・トゥ・クアイ
+・体術/銃/棍棒/斧
+・バフ解除薬
+・立ち回り
+・魂アビ</t>
+        </is>
+      </c>
+      <c r="H1190" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zwuTgIfzBrI</t>
+        </is>
+      </c>
+      <c r="J1190" s="2" t="inlineStr">
+        <is>
+          <t>zwuTgIfzBrI</t>
+        </is>
+      </c>
+      <c r="K1190" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1191" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1191" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　幻闘：トゥ・クアイ　挑戦　全武器種制覇なるか！　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1191" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場トゥ・クアイを全武器種制覇に挑む生配信。
+術が当たらず特に弓が最難、リズで攻略。
+新速人会編成とアップ解除3体が有効。</t>
+        </is>
+      </c>
+      <c r="E1191" s="2" t="inlineStr">
+        <is>
+          <t>・視聴者提案の編成が天才的でリズが強い
+・ウコムの火力がバグってる
+・新速人会が便利で井戸攻略が活きた</t>
+        </is>
+      </c>
+      <c r="F1191" s="2" t="inlineStr">
+        <is>
+          <t>・術が当たらず弓が一番きつい
+・アップ解除がないと厳しい
+・来月の幻闘も難しそう</t>
+        </is>
+      </c>
+      <c r="G1191" s="2" t="inlineStr">
+        <is>
+          <t>・トゥ・クアイ全武器制覇
+・生配信
+・弓が最難
+・リズ
+・ウコム</t>
+        </is>
+      </c>
+      <c r="H1191" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hnDRyKZOg0U</t>
+        </is>
+      </c>
+      <c r="J1191" s="2" t="inlineStr">
+        <is>
+          <t>hnDRyKZOg0U</t>
+        </is>
+      </c>
+      <c r="K1191" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1192" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1192" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始335日目記録　突撃　衝撃の展開　新イベントの結果はいかに</t>
+        </is>
+      </c>
+      <c r="D1192" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣プレイ335日目の記録動画。
+新武将8体を入手し課金13.5万円で織田信長を100連ゲット。
+無凸でも火力が高く山形・内藤戦を突破。</t>
+        </is>
+      </c>
+      <c r="E1192" s="2" t="inlineStr">
+        <is>
+          <t>・織田信長は無凸でも火力がやばい
+・北条氏康がバフ要員として優秀
+・徳川イエアスは統率高く内政向き</t>
+        </is>
+      </c>
+      <c r="F1192" s="2" t="inlineStr">
+        <is>
+          <t>・北条氏康は耐久できず使いにくい
+・課金13.5万円が痛い
+・本多忠勝1体だと壁が足りず壊滅</t>
+        </is>
+      </c>
+      <c r="G1192" s="2" t="inlineStr">
+        <is>
+          <t>・信長の野望出陣
+・335日目
+・織田信長
+・課金
+・徳川編成</t>
+        </is>
+      </c>
+      <c r="H1192" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kosoi3pXIYo</t>
+        </is>
+      </c>
+      <c r="J1192" s="2" t="inlineStr">
+        <is>
+          <t>kosoi3pXIYo</t>
+        </is>
+      </c>
+      <c r="K1192" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1193" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1193" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　幻闘:トゥ・クアイ　フルオート1ターン</t>
+        </is>
+      </c>
+      <c r="D1193" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場トゥ・クアイをフルオートで体験攻略。
+最初にアップ解除しないと攻撃が通らない。
+HP約20億で武器によってはかなりきつい。</t>
+        </is>
+      </c>
+      <c r="E1193" s="2" t="inlineStr">
+        <is>
+          <t>・火力高い武器ならフルオートで倒せる
+・カウンターキャラが使えそう
+・アップ解除である程度耐えられる</t>
+        </is>
+      </c>
+      <c r="F1193" s="2" t="inlineStr">
+        <is>
+          <t>・アップ解除しないと攻撃が通らない
+・15回まで体力上昇でダメージ通らない場合あり
+・防御75-80ないと厳しい</t>
+        </is>
+      </c>
+      <c r="G1193" s="2" t="inlineStr">
+        <is>
+          <t>・トゥ・クアイ
+・フルオート
+・アップ解除
+・カウンターキャラ
+・防御</t>
+        </is>
+      </c>
+      <c r="H1193" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=o9qxJKQt6lI</t>
+        </is>
+      </c>
+      <c r="J1193" s="2" t="inlineStr">
+        <is>
+          <t>o9qxJKQt6lI</t>
+        </is>
+      </c>
+      <c r="K1193" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1194" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1194" s="2" t="inlineStr">
+        <is>
+          <t>【タガタメ】タガタメ新作ゲーム！タガマス発表！『誰ガ為のアルケミスト』</t>
+        </is>
+      </c>
+      <c r="D1194" s="2" t="inlineStr">
+        <is>
+          <t>タガタメ新作「タガマス」ポートマスターズが発表。
+リアルタイムバトルRPGで事前登録が近日開始。
+URウロボロスが初手配布でもらえる。</t>
+        </is>
+      </c>
+      <c r="E1194" s="2" t="inlineStr">
+        <is>
+          <t>・URウロボロスが初手で配布はお得
+・イラストが動くようになった
+・SSR以上確定チケットなど報酬が充実</t>
+        </is>
+      </c>
+      <c r="F1194" s="2" t="inlineStr">
+        <is>
+          <t>・ゲーム性がまだ分からない
+・プロローグがいきなりクライマックスすぎる
+・タイプの意味合いが不明で分かりにくい</t>
+        </is>
+      </c>
+      <c r="G1194" s="2" t="inlineStr">
+        <is>
+          <t>・タガタメ新作
+・タガマス
+・事前登録
+・ウロボロス配布
+・タイプ/ロール</t>
+        </is>
+      </c>
+      <c r="H1194" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qLQaDptgKGs</t>
+        </is>
+      </c>
+      <c r="J1194" s="2" t="inlineStr">
+        <is>
+          <t>qLQaDptgKGs</t>
+        </is>
+      </c>
+      <c r="K1194" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1195" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1195" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】錬磨注意点！後になって後悔しても遅いので話を聞いてみてください【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1195" s="2" t="inlineStr">
+        <is>
+          <t>新しい武器錬磨は必要な分だけやるべきと助言。
+なんとなくやると石・素材が枯渇し後悔する。
+イベント配布素材で試すのがおすすめ。</t>
+        </is>
+      </c>
+      <c r="E1195" s="2" t="inlineStr">
+        <is>
+          <t>・錬磨は簡単にまとめてやれるようになった
+・イベント配布素材なら気軽に使える
+・やってみると楽しくハマる</t>
+        </is>
+      </c>
+      <c r="F1195" s="2" t="inlineStr">
+        <is>
+          <t>・なんとなくやると素材が枯渇し後悔
+・100%程度の伸びで意味を感じなかった
+・上げた水準を下げるのは大変</t>
+        </is>
+      </c>
+      <c r="G1195" s="2" t="inlineStr">
+        <is>
+          <t>・武器錬磨
+・素材枯渇
+・錬磨注意
+・全体攻撃
+・リサギ精神</t>
+        </is>
+      </c>
+      <c r="H1195" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HB9DV9nPPIM</t>
+        </is>
+      </c>
+      <c r="J1195" s="2" t="inlineStr">
+        <is>
+          <t>HB9DV9nPPIM</t>
+        </is>
+      </c>
+      <c r="K1195" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1196" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1196" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】幻闘場全編成＆ギミック代用考察トゥクアイ編【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1196" s="2" t="inlineStr">
+        <is>
+          <t>トゥ・クアイ全武器種の編成とギミックを解説。
+バフ解除必須でコンボと弓が最難、体術は簡単。
+2ターン想定で武器ごとの攻略難易度を紹介。</t>
+        </is>
+      </c>
+      <c r="E1196" s="2" t="inlineStr">
+        <is>
+          <t>・トゥ・クアイは出来がよく面白いボス
+・暦みがいると楽にクリアしやすい
+・イスカンダールが吸ってくれて剣が安定</t>
+        </is>
+      </c>
+      <c r="F1196" s="2" t="inlineStr">
+        <is>
+          <t>・コンボはSランクでめちゃくちゃ難しい
+・弓は精神高すぎて術が当たらない
+・リズ・アイスがいないと弓はきつい</t>
+        </is>
+      </c>
+      <c r="G1196" s="2" t="inlineStr">
+        <is>
+          <t>・トゥ・クアイ全編成
+・ギミック解説
+・バフ解除
+・難易度評価
+・リズ/アイス</t>
+        </is>
+      </c>
+      <c r="H1196" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ii9BwayvRn4</t>
+        </is>
+      </c>
+      <c r="J1196" s="2" t="inlineStr">
+        <is>
+          <t>ii9BwayvRn4</t>
+        </is>
+      </c>
+      <c r="K1196" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1197" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C1197" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】幻闘やってます</t>
+        </is>
+      </c>
+      <c r="D1197" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場を大剣中心に攻略する雑談生配信。
+UI変更やダメージ表記の重さに不満が続出。
+今月のロマパスは両方スルー予定。</t>
+        </is>
+      </c>
+      <c r="E1197" s="2" t="inlineStr">
+        <is>
+          <t>・リズがいればギミック突破しやすそう
+・無敵のラゼムがいい味を出す
+・EX真剣勝負で周回が楽になる</t>
+        </is>
+      </c>
+      <c r="F1197" s="2" t="inlineStr">
+        <is>
+          <t>・今月のロマパスは両方スルー
+・UI変更でウェブショップに飛べず不便
+・ダメージ最新表記はアプリが重くなる</t>
+        </is>
+      </c>
+      <c r="G1197" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場
+・生配信
+・ロマパススルー
+・UI変更不満
+・リズ</t>
+        </is>
+      </c>
+      <c r="H1197" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I1197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EEpi70liGgs</t>
+        </is>
+      </c>
+      <c r="J1197" s="2" t="inlineStr">
+        <is>
+          <t>EEpi70liGgs</t>
+        </is>
+      </c>
+      <c r="K1197" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1198" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1198" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】作るだけで大幅に強くなる神錬磨！？新しくなった武器錬磨を徹底解説【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1198" s="2" t="inlineStr">
+        <is>
+          <t>新しくなった武器錬磨のおすすめを徹底解説。
+看門・幻闘武器には錬磨不可、能力プラスが汎用性高くおすすめ。
+最優先はエクストラフォース付き武器の強化。</t>
+        </is>
+      </c>
+      <c r="E1198" s="2" t="inlineStr">
+        <is>
+          <t>・能力プラスが汎用性高く一番おすすめ
+・エクストラフォース付き武器が最優先で偉い
+・一括錬磨は便利な新機能</t>
+        </is>
+      </c>
+      <c r="F1198" s="2" t="inlineStr">
+        <is>
+          <t>・看門・幻闘武器には錬磨がつけられない
+・オールサガプラスは大して強くない
+・一括錬磨マックスは素材が一瞬で枯渇する</t>
+        </is>
+      </c>
+      <c r="G1198" s="2" t="inlineStr">
+        <is>
+          <t>・武器錬磨解説
+・能力プラス
+・エクストラフォース
+・味方威力プラス
+・看門武器</t>
+        </is>
+      </c>
+      <c r="H1198" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GOhbi0HrFE0</t>
+        </is>
+      </c>
+      <c r="J1198" s="2" t="inlineStr">
+        <is>
+          <t>GOhbi0HrFE0</t>
+        </is>
+      </c>
+      <c r="K1198" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1199" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1199" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今の主役はこのキャラたちだ！能力アップ持ちのスタイルを一挙大紹介！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1199" s="2" t="inlineStr">
+        <is>
+          <t>強敵トゥ・クアイに必須の能力アップ解除持ちを一挙紹介。
+技術で64スタイル＋アビリティ15と数は多い。
+弓は武器技に解除がなくリズが必須級。</t>
+        </is>
+      </c>
+      <c r="E1199" s="2" t="inlineStr">
+        <is>
+          <t>・配布リベルの男女だけで剣がいける
+・絶望の歌が斧ですごく便利
+・リズがいると弓の難易度が一気に下がる</t>
+        </is>
+      </c>
+      <c r="F1199" s="2" t="inlineStr">
+        <is>
+          <t>・弓は武器技に解除がなくリズがいないと厳しい
+・今回のトガはここ最近で相当難しい
+・術は当たりづらく火力も相当要求される</t>
+        </is>
+      </c>
+      <c r="G1199" s="2" t="inlineStr">
+        <is>
+          <t>・能力アップ解除
+・スタイル一覧
+・トゥ・クアイ
+・リズリンウッド
+・配布リベル</t>
+        </is>
+      </c>
+      <c r="H1199" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Q8cAGj8qe5w</t>
+        </is>
+      </c>
+      <c r="J1199" s="2" t="inlineStr">
+        <is>
+          <t>Q8cAGj8qe5w</t>
+        </is>
+      </c>
+      <c r="K1199" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1200" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1200" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】これが今のロマサガRSの最強の配布キャラ！？周回で困ってる人全員集合！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1200" s="2" t="inlineStr">
+        <is>
+          <t>今のロマサガRS最強の配布キャラはアレツと紹介。
+アビサルサーカス周回で1手クリアできる周回性能。
+武器錬磨でエクストラフォースの価値が急上昇。</t>
+        </is>
+      </c>
+      <c r="E1200" s="2" t="inlineStr">
+        <is>
+          <t>・配布アレツは周回で最強で1番強い
+・20ヒット必殺でエフェクトも早い
+・能力プラス582の腕力で火力が漏れる</t>
+        </is>
+      </c>
+      <c r="F1200" s="2" t="inlineStr">
+        <is>
+          <t>・アレツのソウルレベルが低いと弱い
+・エクストラフォース足りないと1手で無理
+・EX1が一番時間がかかる</t>
+        </is>
+      </c>
+      <c r="G1200" s="2" t="inlineStr">
+        <is>
+          <t>・配布アレツ
+・アビサルサーカス周回
+・エクストラフォース
+・20ヒット必殺技
+・ビクトール代用</t>
+        </is>
+      </c>
+      <c r="H1200" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xGc0INdSM4I</t>
+        </is>
+      </c>
+      <c r="J1200" s="2" t="inlineStr">
+        <is>
+          <t>xGc0INdSM4I</t>
+        </is>
+      </c>
+      <c r="K1200" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1201" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1201" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】幻闘場トゥクアイ攻略を一気に楽に！安定攻略&amp;ギミック解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1201" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場トゥクアイの安定攻略とギミックを解説。
+敵はウィークEF2倍持ちで蒸気バフをループさせる。
+バフ解除役を1・4-5に置くと攻略が楽。</t>
+        </is>
+      </c>
+      <c r="E1201" s="2" t="inlineStr">
+        <is>
+          <t>・バフ解除役を配置すると攻略が楽になる</t>
+        </is>
+      </c>
+      <c r="F1201" s="2" t="inlineStr">
+        <is>
+          <t>・敵の体制バフが高くバフ解除ないとダメージ通らない</t>
+        </is>
+      </c>
+      <c r="G1201" s="2" t="inlineStr">
+        <is>
+          <t>・トゥクアイ
+・ギミック解説
+・バフ解除
+・ウィークEF2倍
+・蒸気ループ</t>
+        </is>
+      </c>
+      <c r="H1201" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6Wh-gckrUs8</t>
+        </is>
+      </c>
+      <c r="J1201" s="2" t="inlineStr">
+        <is>
+          <t>6Wh-gckrUs8</t>
+        </is>
+      </c>
+      <c r="K1201" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1202" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1202" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】9月ロマンシングパスは本当に買うべきか？上級・通常パスオススメか判断！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1202" s="2" t="inlineStr">
+        <is>
+          <t>9月ロマパスの上級・通常の性能をチェック。
+上級の魔女の娘は残雷の火力バッファーで買っても良い様子見。
+通常パスは条件が厳しくスルー予定。</t>
+        </is>
+      </c>
+      <c r="E1202" s="2" t="inlineStr">
+        <is>
+          <t>・魔女の娘は開幕火力バフ＆最大BP増加が優秀
+・気発と相性が良く周回適性が高い
+・付与するエクストラフォースが被らない</t>
+        </is>
+      </c>
+      <c r="F1202" s="2" t="inlineStr">
+        <is>
+          <t>・通常パスは行動後防御強化が1回分しか入らず残念
+・ODやファスト先行が必要で条件が厳しい
+・魔女の娘は付与側がやや弱い気がする</t>
+        </is>
+      </c>
+      <c r="G1202" s="2" t="inlineStr">
+        <is>
+          <t>・9月ロマンシングパス
+・魔女の娘
+・火力バッファー
+・通常パス
+・気発相性</t>
+        </is>
+      </c>
+      <c r="H1202" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VBmJn48aaQs</t>
+        </is>
+      </c>
+      <c r="J1202" s="2" t="inlineStr">
+        <is>
+          <t>VBmJn48aaQs</t>
+        </is>
+      </c>
+      <c r="K1202" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1203" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1203" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】白薔薇姫厄&amp;T260G厄ガチャの最後に引くべきキャラを決めます【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1203" s="2" t="inlineStr">
+        <is>
+          <t>白薔薇姫厄とT260G厄ガチャの最終判断動画。
+どちらも代用が多く基本スルー濃厚。
+引くなら白薔薇姫アビスが一番の当たり。</t>
+        </is>
+      </c>
+      <c r="E1203" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇姫アビスは癖がなく使いやすい
+・タイムは開幕大量バフでレイド時短に貢献
+・初心者・復帰勢には白薔薇姫アビスがおすすめ</t>
+        </is>
+      </c>
+      <c r="F1203" s="2" t="inlineStr">
+        <is>
+          <t>・両ガチャとも代用が多く基本スルー
+・T260Gの4ターン火力は使う場面がほぼない
+・最終皇帝勢は世代交代に飲まれやすい</t>
+        </is>
+      </c>
+      <c r="G1203" s="2" t="inlineStr">
+        <is>
+          <t>・白薔薇姫厄
+・T260G厄
+・ガチャ判断
+・スルー濃厚
+・9月ガチャ温存</t>
+        </is>
+      </c>
+      <c r="H1203" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VRxwJ-djsKc</t>
+        </is>
+      </c>
+      <c r="J1203" s="2" t="inlineStr">
+        <is>
+          <t>VRxwJ-djsKc</t>
+        </is>
+      </c>
+      <c r="K1203" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1204" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1204" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】幻闘場:トゥ・クアイ【剣:レベル5】〜井戸流2ターン攻略編成〜</t>
+        </is>
+      </c>
+      <c r="D1204" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場トゥ・クアイ剣レベル5の井戸流2ターン攻略編成。
+剣での2ターンクリア編成を紹介する短尺動画。
+※字幕が自動生成で内容の読み取りは限定的。</t>
+        </is>
+      </c>
+      <c r="E1204" s="2" t="inlineStr"/>
+      <c r="F1204" s="2" t="inlineStr"/>
+      <c r="G1204" s="2" t="inlineStr">
+        <is>
+          <t>・トゥ・クアイ
+・剣レベル5
+・井戸流
+・2ターン攻略
+・編成紹介</t>
+        </is>
+      </c>
+      <c r="H1204" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C9hIBIfqTVo</t>
+        </is>
+      </c>
+      <c r="J1204" s="2" t="inlineStr">
+        <is>
+          <t>C9hIBIfqTVo</t>
+        </is>
+      </c>
+      <c r="K1204" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1205" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1205" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】幻闘場:トゥ・クアイ【大剣:レベル5】〜井戸流:1ターン攻略編成‼️</t>
+        </is>
+      </c>
+      <c r="D1205" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場トゥ・クアイ大剣レベル5の井戸流1ターン攻略編成。
+オトマン・暦み・ビクトル・サルーイン・ニトの編成。
+新速人会で1ターンクリアを狙う。</t>
+        </is>
+      </c>
+      <c r="E1205" s="2" t="inlineStr"/>
+      <c r="F1205" s="2" t="inlineStr"/>
+      <c r="G1205" s="2" t="inlineStr">
+        <is>
+          <t>・トゥ・クアイ
+・大剣レベル5
+・井戸流1ターン
+・オトマン/暦み/ビクトル
+・新速人会</t>
+        </is>
+      </c>
+      <c r="H1205" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=G6NLUuIIoPA</t>
+        </is>
+      </c>
+      <c r="J1205" s="2" t="inlineStr">
+        <is>
+          <t>G6NLUuIIoPA</t>
+        </is>
+      </c>
+      <c r="K1205" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1206" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1206" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】幻闘場：トゥ・クアイ【杖：レベル5】〜2ターンクリア編成〜</t>
+        </is>
+      </c>
+      <c r="D1206" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場トゥ・クアイ杖レベル5の2ターンクリア編成を紹介。
+ロックブーケのバフ解除役を先に動かすのが鍵。
+新ターミン・はまるか等がいればクリア可能。</t>
+        </is>
+      </c>
+      <c r="E1206" s="2" t="inlineStr">
+        <is>
+          <t>・新ターミン・はまるか・はるかがいればクリアできる
+・ロックブーケのダークスフィアで解除できる</t>
+        </is>
+      </c>
+      <c r="F1206" s="2" t="inlineStr">
+        <is>
+          <t>・ダークスフィアが当たりにくく数回散らす必要がある</t>
+        </is>
+      </c>
+      <c r="G1206" s="2" t="inlineStr">
+        <is>
+          <t>・トゥ・クアイ
+・杖レベル5
+・2ターン編成
+・ロックブーケ
+・バフ解除</t>
+        </is>
+      </c>
+      <c r="H1206" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GYMpCt7-_1Q</t>
+        </is>
+      </c>
+      <c r="J1206" s="2" t="inlineStr">
+        <is>
+          <t>GYMpCt7-_1Q</t>
+        </is>
+      </c>
+      <c r="K1206" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1207" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1207" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】幻闘場：トゥ・クアイ【体術:レベル5】〜2ターンクリア編成〜</t>
+        </is>
+      </c>
+      <c r="D1207" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場トゥ・クアイ体術レベル5の2ターンクリア編成を紹介。
+人間女のバフ解除役＋アタッカーで構成。
+能力アップ解除役と火力キャラが充実し比較的簡単。</t>
+        </is>
+      </c>
+      <c r="E1207" s="2" t="inlineStr">
+        <is>
+          <t>・体術は能力アップ解除役が多く比較的簡単
+・火力キャラ・サポーターが充実
+・装備はこのメンツなら何でも大丈夫</t>
+        </is>
+      </c>
+      <c r="F1207" s="2" t="inlineStr"/>
+      <c r="G1207" s="2" t="inlineStr">
+        <is>
+          <t>・トゥ・クアイ
+・体術レベル5
+・2ターン編成
+・人間女
+・バフ解除</t>
+        </is>
+      </c>
+      <c r="H1207" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QtaMdO71NGg</t>
+        </is>
+      </c>
+      <c r="J1207" s="2" t="inlineStr">
+        <is>
+          <t>QtaMdO71NGg</t>
+        </is>
+      </c>
+      <c r="K1207" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1208" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1208" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】幻闘武器進化‼️徹底考察‼️〜10の武器種の【優先度】〜アタッカー83体紹介〜</t>
+        </is>
+      </c>
+      <c r="D1208" s="2" t="inlineStr">
+        <is>
+          <t>幻闘武器の進化はエクストラフォース1.5倍付与が目玉。
+全武器種のアタッカー83体を比較し優先度を考察。
+おすすめは剣か体術、チャムは体術を選択。</t>
+        </is>
+      </c>
+      <c r="E1208" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘武器はエクストラフォース1.5倍付与とど偉い効果
+・剣・体術は強アタッカーが揃い最有力
+・体術は井戸で毎週活躍するキャラが多い</t>
+        </is>
+      </c>
+      <c r="F1208" s="2" t="inlineStr">
+        <is>
+          <t>・月に1つしか強化できず選択ミスで1ヶ月後悔
+・コンボ・斧は球がおらず最後まで選ばれない
+・証券はサポーター気質が多くアタッカーが物足りない</t>
+        </is>
+      </c>
+      <c r="G1208" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘武器進化
+・エクストラフォース1.5倍
+・アタッカー83体
+・武器種優先度
+・剣/体術</t>
+        </is>
+      </c>
+      <c r="H1208" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=l9JXnqUsr5k</t>
+        </is>
+      </c>
+      <c r="J1208" s="2" t="inlineStr">
+        <is>
+          <t>l9JXnqUsr5k</t>
+        </is>
+      </c>
+      <c r="K1208" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1209" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1209" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【ガチャ動画】最遅！？サルーインガチャ！なんかごめん【No.633】</t>
+        </is>
+      </c>
+      <c r="D1209" s="2" t="inlineStr">
+        <is>
+          <t>黒薔薇/白薔薇姫ガチャをフレイヤー狙いで実況。
+フレイヤーやハンニバル、まきびなどを確保。
+安定演出で複数体を引き当てる。</t>
+        </is>
+      </c>
+      <c r="E1209" s="2" t="inlineStr">
+        <is>
+          <t>・フレイヤーを確保でき流れが良い
+・安定演出で2体以上引けた
+・まきび・マイアなど良キャラが来た</t>
+        </is>
+      </c>
+      <c r="F1209" s="2" t="inlineStr">
+        <is>
+          <t>・ペットガチャが悪くないのに全然出ない
+・ピックアップが1体も来ないのはもったいない</t>
+        </is>
+      </c>
+      <c r="G1209" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ実況
+・黒薔薇/白薔薇姫
+・フレイヤー確保
+・サルーイン
+・くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="H1209" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I1209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kSutYTIrsXw</t>
+        </is>
+      </c>
+      <c r="J1209" s="2" t="inlineStr">
+        <is>
+          <t>kSutYTIrsXw</t>
+        </is>
+      </c>
+      <c r="K1209" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1210" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1210" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】いともたやすく行われる幻闘場攻略配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D1210" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場トゥ・クアイを武器種ごとに攻略する生配信。
+体術は簡単だが証券・弓は解除と火力が問われ苦戦。
+斧はじじ（薬王）が活躍、弓はリズ不足が課題。</t>
+        </is>
+      </c>
+      <c r="E1210" s="2" t="inlineStr">
+        <is>
+          <t>・体術はバカでも勝てる強い武器
+・斧はじじ（薬王）が匠に活躍
+・コンボはゴリラ編成が最強で1周ムーブで勝てる</t>
+        </is>
+      </c>
+      <c r="F1210" s="2" t="inlineStr">
+        <is>
+          <t>・弓はリズ未所持できつく取っておくべきだった
+・証券はサポーター気質で火力が出しにくい
+・斧が2ヶ月連続でゼロスタイル</t>
+        </is>
+      </c>
+      <c r="G1210" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場攻略
+・生配信
+・体術/証券/弓/斧
+・バフ解除
+・リズ未所持</t>
+        </is>
+      </c>
+      <c r="H1210" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JsB4bD6hmfs</t>
+        </is>
+      </c>
+      <c r="J1210" s="2" t="inlineStr">
+        <is>
+          <t>JsB4bD6hmfs</t>
+        </is>
+      </c>
+      <c r="K1210" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1211" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1211" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベント[EX4.全員集結] ヤバい事実が発覚… EX4解放後の次のイベントまでの過ごし方を解説します【ロマンシング サガ リ・ユニバース】【周回】【編成】</t>
+        </is>
+      </c>
+      <c r="D1211" s="2" t="inlineStr">
+        <is>
+          <t>アビサルサーカスEX4全員集結の解説と過ごし方。
+戦闘は7秒自動勝利だが力姫錬装の素材集めが問題。
+最大進化に55万個・約1週間の周回が必要。</t>
+        </is>
+      </c>
+      <c r="E1211" s="2" t="inlineStr">
+        <is>
+          <t>・EX4は7秒自動勝利で判定3回のパラダイス
+・力姫を最大進化させると非常に強力な装備
+・ドロップ2倍で錬磨の遺跡も魅力</t>
+        </is>
+      </c>
+      <c r="F1211" s="2" t="inlineStr">
+        <is>
+          <t>・最大進化に55万個・約1週間かかる
+・旨みがフリークエストと大差なく交換所も無い
+・錬磨2倍の餌の前でEX4に籠らせる強い意思を感じる</t>
+        </is>
+      </c>
+      <c r="G1211" s="2" t="inlineStr">
+        <is>
+          <t>・アビサルサーカスEX4
+・自動勝利
+・力姫カグラスズ進化
+・素材周回
+・レマの遺跡</t>
+        </is>
+      </c>
+      <c r="H1211" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3MkrwkDNTsU</t>
+        </is>
+      </c>
+      <c r="J1211" s="2" t="inlineStr">
+        <is>
+          <t>3MkrwkDNTsU</t>
+        </is>
+      </c>
+      <c r="K1211" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T01:58:56Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1211"/>
+  <dimension ref="A1:K1213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -79826,6 +79826,146 @@
         </is>
       </c>
     </row>
+    <row r="1212">
+      <c r="A1212" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1212" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1212" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】男女「性能格差」限定超えた!?リベル男女の性能詳細!!&amp;追憶の幻闘場トゥクアイ以外に使い道は?使い方取り合い説明書　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1212" s="2" t="inlineStr">
+        <is>
+          <t>配布リベル男女の性能を詳細比較・評価
+女は無難な個人性能でA、男はサブアタッカーでB評価
+限定より強い唯一性はあるが数値は土平均を少し下回る</t>
+        </is>
+      </c>
+      <c r="E1212" s="2" t="inlineStr">
+        <is>
+          <t>・女はレジスト防御50%・回避37%と防御が優秀
+・配布ながら唯一性ある術で限定より強い場面も
+・男は火力バフ680%・火力捨て90%でまともな火力
+・2人並べればマイターンOD満タを構築可能</t>
+        </is>
+      </c>
+      <c r="F1212" s="2" t="inlineStr">
+        <is>
+          <t>・エクストラ以外は無難止まりで数値は土平均少し下
+・男の全体火力サポートはバフが弱め
+・男女で奇数偶数がチグハグ、今後の限定ガチャが苦しい懸念
+・継承候補の術産も確実なプラスではなく必須ではない</t>
+        </is>
+      </c>
+      <c r="G1212" s="2" t="inlineStr">
+        <is>
+          <t>・リベル男女性能
+・限定との比較
+・高難度評価
+・マイターンOD
+・術産継承
+・追憶トゥクアイ</t>
+        </is>
+      </c>
+      <c r="H1212" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yYx47ZpXHMs</t>
+        </is>
+      </c>
+      <c r="J1212" s="2" t="inlineStr">
+        <is>
+          <t>yYx47ZpXHMs</t>
+        </is>
+      </c>
+      <c r="K1212" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T11:08:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1213" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1213" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】あの追憶トゥ・クアイもぶっ壊す！配布リベルがめちゃくちゃ強かった！！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1213" s="2" t="inlineStr">
+        <is>
+          <t>Webジュエルショップで無料入手の配布リベル男女を解説
+男アタッカー2.5倍・女サポーター2.0倍、セットで毎ターン全員OD
+追憶トゥクアイの能力アップ解除役として大活躍する強配布</t>
+        </is>
+      </c>
+      <c r="E1213" s="2" t="inlineStr">
+        <is>
+          <t>・Webジュエルショップで無料入手できてお得
+・配布なのに超強く変えが効かない性能
+・男女セットで毎ターン全員オーバードライブ可能
+・能力アップ解除持ちで追憶トゥクアイ攻略に大活躍
+・育成ハードルが低く技マシンとしても価値が高い</t>
+        </is>
+      </c>
+      <c r="F1213" s="2" t="inlineStr">
+        <is>
+          <t>・術は精神参照で解除しないと当たらずトゥクアイが難関
+・解除役1人だと命中が心もとない
+・幻闘場トゥクアイ以外では使い所が少なめ</t>
+        </is>
+      </c>
+      <c r="G1213" s="2" t="inlineStr">
+        <is>
+          <t>・配布リベル入手法
+・男女セット運用
+・追撃・OD性能
+・トゥクアイ攻略
+・能力アップ解除
+・術命中の仕組み</t>
+        </is>
+      </c>
+      <c r="H1213" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=upVUnroscvQ</t>
+        </is>
+      </c>
+      <c r="J1213" s="2" t="inlineStr">
+        <is>
+          <t>upVUnroscvQ</t>
+        </is>
+      </c>
+      <c r="K1213" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T11:08:56Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1213"/>
+  <dimension ref="A1:K1224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -79966,6 +79966,712 @@
         </is>
       </c>
     </row>
+    <row r="1214">
+      <c r="A1214" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1214" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1214" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみ「第二形態」!?親友のギャルも含めて第2弾1日早く予想開始!!その前に俺達を頼むよ…　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1214" s="2" t="inlineStr">
+        <is>
+          <t>暦み編第2弾ガチャを1日早く予想開始
+16日メンテ後TGSでロマサ新作発表を予測
+第2弾はストーリー準拠の8星ダブルガチャが濃厚</t>
+        </is>
+      </c>
+      <c r="E1214" s="2" t="inlineStr">
+        <is>
+          <t>・8周年に向け祭りの盛り上がりに期待</t>
+        </is>
+      </c>
+      <c r="F1214" s="2" t="inlineStr">
+        <is>
+          <t>・立ち絵フラグ乱発など出しすぎ問題を懸念</t>
+        </is>
+      </c>
+      <c r="G1214" s="2" t="inlineStr">
+        <is>
+          <t>・第2弾ガチャ予想
+・ガチャ日程
+・TGS新作発表
+・ダブルガチャ
+・こよみ第二形態</t>
+        </is>
+      </c>
+      <c r="H1214" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BRVDQgY9DdM</t>
+        </is>
+      </c>
+      <c r="J1214" s="2" t="inlineStr">
+        <is>
+          <t>BRVDQgY9DdM</t>
+        </is>
+      </c>
+      <c r="K1214" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05T02:32:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1215" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1215" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】63連ガチャ「真の当たり」とは!?狙うべき最強八選!!タイプ別にランキング　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1215" s="2" t="inlineStr">
+        <is>
+          <t>無料で回せる63連ガチャの当たりをタイプ別に解説
+イシスが総合使用回数で頭一つ抜けて最強
+今は引く理由がなく無料分だけ回すのを推奨</t>
+        </is>
+      </c>
+      <c r="E1215" s="2" t="inlineStr">
+        <is>
+          <t>・イシスは立ち上がり早く制圧戦で最強
+・マイスは半年前でもまだ現役
+・リラは唯一性の高い連打追撃が強い</t>
+        </is>
+      </c>
+      <c r="F1215" s="2" t="inlineStr">
+        <is>
+          <t>・雪だ系はエクストラ以外の出力が弱く必須でない
+・AJは全体攻撃追撃主流で機能しなくなった
+・デスマシーンは倒すべき敵がいない</t>
+        </is>
+      </c>
+      <c r="G1215" s="2" t="inlineStr">
+        <is>
+          <t>・63連ガチャ
+・タイプ別当たり
+・イシス最強
+・ガチャ厳選
+・無料周回</t>
+        </is>
+      </c>
+      <c r="H1215" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=W9ksDp2zqyY</t>
+        </is>
+      </c>
+      <c r="J1215" s="2" t="inlineStr">
+        <is>
+          <t>W9ksDp2zqyY</t>
+        </is>
+      </c>
+      <c r="K1215" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05T02:32:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1216" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1216" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】特別黄金茶会　新規入手の方必見！　1000武将確認</t>
+        </is>
+      </c>
+      <c r="D1216" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣の特別黄金茶会パックの1戦武将を全確認
+始めたてでも使える速戦力キャラを性能面から吟味
+おすすめは明智光秀・真田幸村・上杉謙信ら</t>
+        </is>
+      </c>
+      <c r="E1216" s="2" t="inlineStr">
+        <is>
+          <t>・真田幸村は覚醒なしでも再起バフで強い
+・上杉謙信はバフ入るアタッカーで価値高い
+・明智光秀はイベント上位が使う優秀バフ</t>
+        </is>
+      </c>
+      <c r="F1216" s="2" t="inlineStr">
+        <is>
+          <t>・北条など家染め前提のバフ量が不明で不安
+・全部取ると約7万コ番必要で負担大
+・武田系は武田染め必須がきつい</t>
+        </is>
+      </c>
+      <c r="G1216" s="2" t="inlineStr">
+        <is>
+          <t>・黄金茶会パック
+・1戦武将
+・武将性能
+・覚醒
+・おすすめ武将</t>
+        </is>
+      </c>
+      <c r="H1216" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gz-HorhUIG8</t>
+        </is>
+      </c>
+      <c r="J1216" s="2" t="inlineStr">
+        <is>
+          <t>gz-HorhUIG8</t>
+        </is>
+      </c>
+      <c r="K1216" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05T02:32:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1217" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1217" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SRキュベレイMkｰⅡ(プルツー専用機) 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1217" s="2" t="inlineStr">
+        <is>
+          <t>SRキュベレイMk-II（プルツー専用機）の武装アニメ紹介ショート
+プルツーのセリフと共に武装演出を披露
+短尺のShorts動画</t>
+        </is>
+      </c>
+      <c r="E1217" s="2" t="inlineStr"/>
+      <c r="F1217" s="2" t="inlineStr"/>
+      <c r="G1217" s="2" t="inlineStr">
+        <is>
+          <t>・キュベレイMk-II
+・プルツー専用機
+・武装アニメ
+・Gジェネエターナル
+・ショート</t>
+        </is>
+      </c>
+      <c r="H1217" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CPPbq9iyXbo</t>
+        </is>
+      </c>
+      <c r="J1217" s="2" t="inlineStr">
+        <is>
+          <t>CPPbq9iyXbo</t>
+        </is>
+      </c>
+      <c r="K1217" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05T02:32:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1218" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1218" s="2" t="inlineStr">
+        <is>
+          <t>見た目のカスタマイズも可能！発売日アナウンストレーラーから見る新情報を確認！『GUNDAM ROGUE ORBIT』</t>
+        </is>
+      </c>
+      <c r="D1218" s="2" t="inlineStr">
+        <is>
+          <t>ガンダム新作ローグオビットの発売日が2027年3月5日に決定
+トレーラーから見た目カスタマイズなど新情報を確認
+機体・キャラ追加も進み続報に期待</t>
+        </is>
+      </c>
+      <c r="E1218" s="2" t="inlineStr">
+        <is>
+          <t>・見た目を大きく変えられるカスタマイズが面白そう
+・モビルスーツが多数登場しそうで良い
+・2027年発売で思ったより早い</t>
+        </is>
+      </c>
+      <c r="F1218" s="2" t="inlineStr">
+        <is>
+          <t>・MODスキンが有料DLC販売されそうな懸念
+・中身と見た目を別設定できると嬉しいが不明</t>
+        </is>
+      </c>
+      <c r="G1218" s="2" t="inlineStr">
+        <is>
+          <t>・ガンダムローグオビット
+・発売日発表
+・見た目カスタマイズ
+・MODスキン
+・新モビルスーツ</t>
+        </is>
+      </c>
+      <c r="H1218" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TEaXERvSG0g</t>
+        </is>
+      </c>
+      <c r="J1218" s="2" t="inlineStr">
+        <is>
+          <t>TEaXERvSG0g</t>
+        </is>
+      </c>
+      <c r="K1218" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05T02:32:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1219" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C1219" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】イベント完全に出遅れた、幻闘やってます、途中からP雑談</t>
+        </is>
+      </c>
+      <c r="D1219" s="2" t="inlineStr">
+        <is>
+          <t>イベントに出遅れEX周回と幻闘トゥクアイに苦戦する配信
+X4周回が7秒で終わる高効率と知り慌ててEX解放
+後半はパチンコ・スロットの雑談に脱線</t>
+        </is>
+      </c>
+      <c r="E1219" s="2" t="inlineStr">
+        <is>
+          <t>・X4は5人誰でも育成でき6〜7秒で終わる高効率
+・ロマサガ3リメイクに期待</t>
+        </is>
+      </c>
+      <c r="F1219" s="2" t="inlineStr">
+        <is>
+          <t>・EX3到達に1日半かかり要求周回数がきつい
+・メインばかり回してEX解放が出遅れた</t>
+        </is>
+      </c>
+      <c r="G1219" s="2" t="inlineStr">
+        <is>
+          <t>・イベント出遅れ
+・EX周回
+・幻闘トゥクアイ
+・X4周回
+・パチスロ雑談</t>
+        </is>
+      </c>
+      <c r="H1219" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I1219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=p61Vcl-pIRw</t>
+        </is>
+      </c>
+      <c r="J1219" s="2" t="inlineStr">
+        <is>
+          <t>p61Vcl-pIRw</t>
+        </is>
+      </c>
+      <c r="K1219" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05T02:32:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B1220" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1220" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】マジで全員要注目！今気をつけるべき重要な注意点を大紹介！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1220" s="2" t="inlineStr">
+        <is>
+          <t>8周年で見逃しやすい重要ポイントを注意喚起
+88日ログボや遠征ソウルピース・週末クエストの回収を推奨
+Webジュエルショップ登録やリポスト企画も忘れず</t>
+        </is>
+      </c>
+      <c r="E1220" s="2" t="inlineStr">
+        <is>
+          <t>・88日ログボで8000ジュエルが太っ腹
+・EX4は5枠育成で1周3回抽選と激熱
+・リポストで全員2000ジュエルもらえる</t>
+        </is>
+      </c>
+      <c r="F1220" s="2" t="inlineStr">
+        <is>
+          <t>・お知らせを開くユーザーが1〜2割で告知が地味
+・Webショップのメール登録につまずく人が多い</t>
+        </is>
+      </c>
+      <c r="G1220" s="2" t="inlineStr">
+        <is>
+          <t>・8周年注意点
+・88日ログボ
+・ソウルピース遠征
+・EX周回
+・Webジュエルショップ</t>
+        </is>
+      </c>
+      <c r="H1220" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1wcerLRg1HE</t>
+        </is>
+      </c>
+      <c r="J1220" s="2" t="inlineStr">
+        <is>
+          <t>1wcerLRg1HE</t>
+        </is>
+      </c>
+      <c r="K1220" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05T02:32:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1221" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1221" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】幻闘場：トゥ・クアイ【銃：レベル5】〜4ターンクリア編成〜</t>
+        </is>
+      </c>
+      <c r="D1221" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場トゥクアイ銃レベル5の4ターンクリア編成を紹介
+T260Gとメイレンでバフのダブル解除役を担当
+新速人・浮気武器で強化なしでもギリギリ攻略</t>
+        </is>
+      </c>
+      <c r="E1221" s="2" t="inlineStr">
+        <is>
+          <t>・T260Gとメイレンのダブル解除で安定攻略
+・強化・防具を揃えれば楽勝</t>
+        </is>
+      </c>
+      <c r="F1221" s="2" t="inlineStr">
+        <is>
+          <t>・無強化だとギリギリのクリアで安定しない</t>
+        </is>
+      </c>
+      <c r="G1221" s="2" t="inlineStr">
+        <is>
+          <t>・トゥクアイ銃Lv5
+・4ターンクリア編成
+・T260G
+・バフ解除
+・新速人</t>
+        </is>
+      </c>
+      <c r="H1221" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=N7rk12kEeMA</t>
+        </is>
+      </c>
+      <c r="J1221" s="2" t="inlineStr">
+        <is>
+          <t>N7rk12kEeMA</t>
+        </is>
+      </c>
+      <c r="K1221" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05T02:32:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1222" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1222" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】能力アップ（UP）解除キャラ全集【幻闘場：トゥ・クアイ対策】剣6・大剣3・槍5・斧5・棍棒3杖13・小剣11・銃3・弓5・体術20</t>
+        </is>
+      </c>
+      <c r="D1222" s="2" t="inlineStr">
+        <is>
+          <t>幻闘トゥクアイ対策に全武器種の能力アップ解除持ちキャラをまとめ
+解説なしでスクショ用の一覧画像を提示
+急ぎ調査のため抜けはコメントで補完依頼</t>
+        </is>
+      </c>
+      <c r="E1222" s="2" t="inlineStr">
+        <is>
+          <t>・全武器種の解除持ちを一覧化して対策に便利</t>
+        </is>
+      </c>
+      <c r="F1222" s="2" t="inlineStr">
+        <is>
+          <t>・急ぎ調査で抜けキャラの可能性あり</t>
+        </is>
+      </c>
+      <c r="G1222" s="2" t="inlineStr">
+        <is>
+          <t>・能力アップ解除
+・トゥクアイ対策
+・全武器種一覧
+・スクショ用
+・キャラまとめ</t>
+        </is>
+      </c>
+      <c r="H1222" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vW4N1FerkAA</t>
+        </is>
+      </c>
+      <c r="J1222" s="2" t="inlineStr">
+        <is>
+          <t>vW4N1FerkAA</t>
+        </is>
+      </c>
+      <c r="K1222" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05T02:32:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1223" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1223" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【ガチャ動画】実は追ってたT260G厄！！「アンリィ!!」復活計画も…！？【No.635】</t>
+        </is>
+      </c>
+      <c r="D1223" s="2" t="inlineStr">
+        <is>
+          <t>T260G厄を狙って50連ガチャに挑戦する雑談ガチャ配信
+相性が悪く50連で目当てが何も出ず
+アンリィの代わりになる母系キャラ探しで盛り上がる</t>
+        </is>
+      </c>
+      <c r="E1223" s="2" t="inlineStr">
+        <is>
+          <t>・ロボ系スタイルの見た目がかっこいい
+・9月お祭りでジュエル追加配布に期待</t>
+        </is>
+      </c>
+      <c r="F1223" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャの相性が悪く50連で何も出ず
+・クーンが301回引いても出ない渋さ</t>
+        </is>
+      </c>
+      <c r="G1223" s="2" t="inlineStr">
+        <is>
+          <t>・T260G厄ガチャ
+・50連
+・ガチャ渋い
+・アンリィ復活計画
+・雑談</t>
+        </is>
+      </c>
+      <c r="H1223" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I1223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hkvOQLvZrME</t>
+        </is>
+      </c>
+      <c r="J1223" s="2" t="inlineStr">
+        <is>
+          <t>hkvOQLvZrME</t>
+        </is>
+      </c>
+      <c r="K1223" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05T02:32:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B1224" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1224" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベント 諦めるのまだ早い!? ガチャ限1+配布4人 周回編成の紹介!!【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1224" s="2" t="inlineStr">
+        <is>
+          <t>アビッサルサーカス周回をガチャ限1＋配布4人の編成で紹介
+再現性重視でAJ・アレツ・ビンセント・リベル男女を採用
+EX1〜3それぞれの技・人系設定を解説</t>
+        </is>
+      </c>
+      <c r="E1224" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ限1＋配布で再現性の高い周回編成
+・ロマンシングショップやジュエルショップで揃えやすい</t>
+        </is>
+      </c>
+      <c r="F1224" s="2" t="inlineStr">
+        <is>
+          <t>・求められる周回数が想像以上に厳しい
+・ドロップ追加で集めやすくなることに期待（現状不満）</t>
+        </is>
+      </c>
+      <c r="G1224" s="2" t="inlineStr">
+        <is>
+          <t>・アビッサルサーカス周回
+・再現性重視編成
+・配布キャラ活用
+・AJ
+・リベル男女</t>
+        </is>
+      </c>
+      <c r="H1224" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=I753on-4kIM</t>
+        </is>
+      </c>
+      <c r="J1224" s="2" t="inlineStr">
+        <is>
+          <t>I753on-4kIM</t>
+        </is>
+      </c>
+      <c r="K1224" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05T02:32:26Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1224"/>
+  <dimension ref="A1:K1233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -80672,6 +80672,605 @@
         </is>
       </c>
     </row>
+    <row r="1225">
+      <c r="A1225" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1225" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1225" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】リズ取説「10月も接待」唯一無二!!リズを活かせる取り回し&amp;性能をわかりやすく取り扱い説明書にまとめ!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1225" s="2" t="inlineStr">
+        <is>
+          <t>リズは対特攻兵器として作られた霊アタッカー
+高防御と攻撃毎バフ解除で唯一無二の性能
+10月接待級で螺旋や運カノ向けの追目線評価</t>
+        </is>
+      </c>
+      <c r="E1225" s="2" t="inlineStr">
+        <is>
+          <t>・リーサル打切り最終ヒットに463%の高火力
+・攻撃ごとにバフ解除できる唯一無二の性能
+・全体防御86%到達＋レジスト回避37%で硬い
+・短めの螺旋で最優先の霊アタッカー
+・極勝回復付きで回復役も兼ねる</t>
+        </is>
+      </c>
+      <c r="F1225" s="2" t="inlineStr">
+        <is>
+          <t>・火力補正値220%と控えめでメリット薄い
+・立ち上がりが遅く3ターン目から本気
+・霊夢攻撃無効は特合には刺さらない
+・厳選・高難度勢にはあまり必要ない</t>
+        </is>
+      </c>
+      <c r="G1225" s="2" t="inlineStr">
+        <is>
+          <t>・霊アタッカー
+・リズ性能
+・攻撃毎バフ解除
+・全体防御86%
+・極勝回復
+・3ヶ月連続接待</t>
+        </is>
+      </c>
+      <c r="H1225" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OAmtoOojh7E</t>
+        </is>
+      </c>
+      <c r="J1225" s="2" t="inlineStr">
+        <is>
+          <t>OAmtoOojh7E</t>
+        </is>
+      </c>
+      <c r="K1225" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T03:04:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1226" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1226" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　幻闘：トゥ・クアイ　全武器種制覇　激闘の全貌を一挙公開</t>
+        </is>
+      </c>
+      <c r="D1226" s="2" t="inlineStr">
+        <is>
+          <t>幻闘トゥ・クアイを全武器種でクリア紹介
+術解除役2体かデバフ・カウンターが攻略の鍵
+各武器の編成と立ち回りを一挙公開</t>
+        </is>
+      </c>
+      <c r="E1226" s="2" t="inlineStr">
+        <is>
+          <t>・イスカンダルは攻撃を集め回数を減らせ優秀
+・白姫は圧倒的火力で貢献
+・ヒューズの火力がえぐい
+・ミドが証券で高火力＆防御に貢献
+・ウコムが槍で高火力を出す</t>
+        </is>
+      </c>
+      <c r="F1226" s="2" t="inlineStr">
+        <is>
+          <t>・術が当たらず解除できないのが厄介
+・絶望の歌の回数制限で事故ると耐久不能
+・証券と弓は長期戦できつい
+・HP半分以降の発狂で攻撃回数増加に注意</t>
+        </is>
+      </c>
+      <c r="G1226" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘トゥ・クアイ
+・全武器種制覇
+・術解除役2体
+・カウンター活用
+・精神デバフ
+・発狂対策</t>
+        </is>
+      </c>
+      <c r="H1226" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=I7EpBmnXhig</t>
+        </is>
+      </c>
+      <c r="J1226" s="2" t="inlineStr">
+        <is>
+          <t>I7EpBmnXhig</t>
+        </is>
+      </c>
+      <c r="K1226" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T03:04:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1227" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1227" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SR スーパーガンダム 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1227" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナルのスーパーガンダム武装アニメ
+SR機体の武装演出を短尺Shortsで紹介
+字幕情報が乏しく詳細な評価はなし</t>
+        </is>
+      </c>
+      <c r="E1227" s="2" t="inlineStr"/>
+      <c r="F1227" s="2" t="inlineStr"/>
+      <c r="G1227" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・スーパーガンダム
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H1227" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=n3MtaT1nGxI</t>
+        </is>
+      </c>
+      <c r="J1227" s="2" t="inlineStr">
+        <is>
+          <t>n3MtaT1nGxI</t>
+        </is>
+      </c>
+      <c r="K1227" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T03:04:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1228" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1228" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】真ポルカVS最終皇帝女！最強防御軸はどっちだ★プレゼン【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1228" s="2" t="inlineStr">
+        <is>
+          <t>真ポルカと最終皇帝女の防御軽減を比較
+ポルカは弱点条件付きだが手軽に高軽減
+条件が揃えばポルカが使いやすいと結論</t>
+        </is>
+      </c>
+      <c r="E1228" s="2" t="inlineStr">
+        <is>
+          <t>・ポルカは全員3回行動で99.5%軽減が簡単
+・最終皇帝女は青天井で最大95%軽減
+・イスカンダル＋最終皇帝女の裏技が強力</t>
+        </is>
+      </c>
+      <c r="F1228" s="2" t="inlineStr">
+        <is>
+          <t>・ポルカは弱点をつかないと無意味
+・ポルカは自分が最初に動く必要がある
+・最終皇帝女は行動回数少ないと無意味</t>
+        </is>
+      </c>
+      <c r="G1228" s="2" t="inlineStr">
+        <is>
+          <t>・防御軽減比較
+・真ポルカ
+・最終皇帝女
+・ルクスオーバーエンチャント
+・イスカンダル
+・弱点必須</t>
+        </is>
+      </c>
+      <c r="H1228" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Hwh1SSNUr3A</t>
+        </is>
+      </c>
+      <c r="J1228" s="2" t="inlineStr">
+        <is>
+          <t>Hwh1SSNUr3A</t>
+        </is>
+      </c>
+      <c r="K1228" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T03:04:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1229" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1229" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】真の最強はだれだ！2026年上半期SSS評価限定Tier表★大英傑全員集合【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1229" s="2" t="inlineStr">
+        <is>
+          <t>2026年上半期トリプルS限定の最強Tier表
+感覚評価でゴッド〜Cにランク付けして解説
+1位はビクトールで今年の環境の顔と評価</t>
+        </is>
+      </c>
+      <c r="E1229" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトールは生涯無双級で今の環境の顔
+・裁判はどの編成にも入る全員キャラ
+・サイバは全体攻撃＋艦体で万能
+・ルクスオーバーエンチャントはチート級
+・お玉はバラマキ＋2ターンデバフで強い</t>
+        </is>
+      </c>
+      <c r="F1229" s="2" t="inlineStr">
+        <is>
+          <t>・アイスは1.75倍割りが増え相対的に低下
+・グレイはデメリット薄れ今使う機会なし
+・マルチウェポンは時代が変わりB評価</t>
+        </is>
+      </c>
+      <c r="G1229" s="2" t="inlineStr">
+        <is>
+          <t>・上半期Tier表
+・SSS限定
+・ビクトール1位
+・セブンナイツ
+・ルクスオーバーエンチャント
+・感覚評価</t>
+        </is>
+      </c>
+      <c r="H1229" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LySGEog0LwA</t>
+        </is>
+      </c>
+      <c r="J1229" s="2" t="inlineStr">
+        <is>
+          <t>LySGEog0LwA</t>
+        </is>
+      </c>
+      <c r="K1229" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T03:04:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B1230" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1230" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】この2人がいたら難易度激変！？追憶の幻闘場「トゥ・クアイ」大剣＆斧を解説【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1230" s="2" t="inlineStr">
+        <is>
+          <t>追憶の幻闘場トゥ・クアイの体術と斧を解説
+最終皇帝女がいれば体術は全武器で最も楽
+斧は西王アビスとの相性が抜群で安定する</t>
+        </is>
+      </c>
+      <c r="E1230" s="2" t="inlineStr">
+        <is>
+          <t>・最終皇帝女のオールODで体術が一番楽
+・斧は西王アビスがいれば苦戦しない
+・ハーディは追憶で強力なキャラ
+・インフレ側が有利でいつか必ず勝てる</t>
+        </is>
+      </c>
+      <c r="F1230" s="2" t="inlineStr">
+        <is>
+          <t>・斧は全武器で貧弱寄りになりやすい
+・西王アビスなしだとレベル5はきつい
+・先月の運ネ&amp;ボルカノの方が難しかった</t>
+        </is>
+      </c>
+      <c r="G1230" s="2" t="inlineStr">
+        <is>
+          <t>・追憶トゥ・クアイ
+・体術/斧攻略
+・最終皇帝女
+・西王アビス
+・武器連魔
+・やれる所までやる</t>
+        </is>
+      </c>
+      <c r="H1230" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Gy9fNT06Vew</t>
+        </is>
+      </c>
+      <c r="J1230" s="2" t="inlineStr">
+        <is>
+          <t>Gy9fNT06Vew</t>
+        </is>
+      </c>
+      <c r="K1230" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T03:04:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1231" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1231" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】遂に大本命のジョー＆バートがやってくる！？9月8日のガチャを徹底予想した結果がヤバすぎた...【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1231" s="2" t="inlineStr">
+        <is>
+          <t>9月8日ガチャの登場キャラを徹底予想
+ジョ＆バートら後半6人が来ると予想
+前回予想は新発生6人を全正解と報告</t>
+        </is>
+      </c>
+      <c r="E1231" s="2" t="inlineStr">
+        <is>
+          <t>・ストーリーが今めちゃくちゃ熱い
+・ジョはロマサガRSの主人公級の特別枠
+・第2弾はジョ＆バートでやばいガチャ</t>
+        </is>
+      </c>
+      <c r="F1231" s="2" t="inlineStr"/>
+      <c r="G1231" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ予想
+・9月8日
+・ジョ&amp;バート
+・新発生12人
+・前回全正解
+・視聴者予想発表</t>
+        </is>
+      </c>
+      <c r="H1231" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VldpRaMLl5I</t>
+        </is>
+      </c>
+      <c r="J1231" s="2" t="inlineStr">
+        <is>
+          <t>VldpRaMLl5I</t>
+        </is>
+      </c>
+      <c r="K1231" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T03:04:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1232" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1232" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】ジュエルビーストの井戸【盗賊ギルド特別編成】〜TOP20位編成〜</t>
+        </is>
+      </c>
+      <c r="D1232" s="2" t="inlineStr">
+        <is>
+          <t>ジュエルビーストの井戸ベスト編成を紹介
+雪だるま暦み等で3ターン44手・初日2位
+防具の工夫と立ち回りを詳細に解説</t>
+        </is>
+      </c>
+      <c r="E1232" s="2" t="inlineStr">
+        <is>
+          <t>・盗賊ギルドが初日123独占した強力編成
+・雪だるまで横1列攻撃を受け切れる好編成
+・最終日に仲間が37手3位を達成</t>
+        </is>
+      </c>
+      <c r="F1232" s="2" t="inlineStr">
+        <is>
+          <t>・カムイが先に出ず45手になる不安定さ</t>
+        </is>
+      </c>
+      <c r="G1232" s="2" t="inlineStr">
+        <is>
+          <t>・ジュエルビースト井戸
+・3ターン44手編成
+・盗賊ギルド
+・雪だるま
+・防具工夫
+・TOP20編成</t>
+        </is>
+      </c>
+      <c r="H1232" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FUOipSw-PL0</t>
+        </is>
+      </c>
+      <c r="J1232" s="2" t="inlineStr">
+        <is>
+          <t>FUOipSw-PL0</t>
+        </is>
+      </c>
+      <c r="K1232" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T03:04:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1233" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1233" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第136回鋼鉄兵たちの井戸【過去最強の7人衆】1ターンで倒し切る編成‼️厳選24体‼️</t>
+        </is>
+      </c>
+      <c r="D1233" s="2" t="inlineStr">
+        <is>
+          <t>第136回鋼鉄兵の井戸クリア編成を事前考察
+ヒューズら全体攻撃・雷・関節キャラが活躍予想
+1ターンクリア狙いの編成6パターン紹介</t>
+        </is>
+      </c>
+      <c r="E1233" s="2" t="inlineStr">
+        <is>
+          <t>・ヒューズは雷＆関節で今回一番人気のアタッカー
+・ターミンシはHP高い敵で必ず活躍する
+・コム彼の爆発力に期待</t>
+        </is>
+      </c>
+      <c r="F1233" s="2" t="inlineStr">
+        <is>
+          <t>・約2ヶ月ぶりで強化控えめの可能性
+・高難度2回目で鬼畜な強さの懸念
+・開始OD満タンを考慮し忘れた編成あり</t>
+        </is>
+      </c>
+      <c r="G1233" s="2" t="inlineStr">
+        <is>
+          <t>・鋼鉄兵の井戸
+・クリア編成予想
+・ヒューズ
+・全体攻撃
+・デバフ必須
+・バフや/魂アビランキング</t>
+        </is>
+      </c>
+      <c r="H1233" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=a8at9UAa16Q</t>
+        </is>
+      </c>
+      <c r="J1233" s="2" t="inlineStr">
+        <is>
+          <t>a8at9UAa16Q</t>
+        </is>
+      </c>
+      <c r="K1233" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T03:04:25Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1233"/>
+  <dimension ref="A1:K1242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -81271,6 +81271,600 @@
         </is>
       </c>
     </row>
+    <row r="1234">
+      <c r="A1234" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1234" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1234" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ギミック解明速報「〇〇の方が厄介」防御ゲーでゴリ押し不可能…トゥ・クアイそれぞれの対処法を剣と大剣で解説→追憶の幻闘場　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1234" s="2" t="inlineStr">
+        <is>
+          <t>幻闘トゥ・クアイは高防御でステバフ解除が攻略の鍵
+防御をガチガチに固めればアタッカー不要で撃破可能
+熱属性・カウンター・OD必中が有効な対処法</t>
+        </is>
+      </c>
+      <c r="E1234" s="2" t="inlineStr">
+        <is>
+          <t>・HPが低くバフ解除だけで倒せる
+・防御を固めればアタッカー不要
+・熱(ホルカ・アウナス)が刺さる
+・カウンターで連撃を止められる</t>
+        </is>
+      </c>
+      <c r="F1234" s="2" t="inlineStr">
+        <is>
+          <t>・敵の火力・防御が非常に高い
+・バフ解除の先制と防御編成が両立しづらい
+・必中や折り込みが必須で耐えづらい</t>
+        </is>
+      </c>
+      <c r="G1234" s="2" t="inlineStr">
+        <is>
+          <t>・ギミック解明
+・ステバフ解除
+・防御編成
+・カウンター
+・熱属性
+・追憶の幻闘場</t>
+        </is>
+      </c>
+      <c r="H1234" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0nRmLhsb-3Y</t>
+        </is>
+      </c>
+      <c r="J1234" s="2" t="inlineStr">
+        <is>
+          <t>0nRmLhsb-3Y</t>
+        </is>
+      </c>
+      <c r="K1234" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1235" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1235" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「爽快」満額井戸!!勝手知ったる鋼鉄兵をなぎ倒す　#ロマサガRS　#タマ井戸</t>
+        </is>
+      </c>
+      <c r="D1235" s="2" t="inlineStr">
+        <is>
+          <t>決戦兵器ヒューズ無しでも満額タマ井戸を周回
+ブーケ等で鋼鉄兵を気持ちよくなぎ倒す
+月曜昼ランクイン、先週の移戸報酬も回収</t>
+        </is>
+      </c>
+      <c r="E1235" s="2" t="inlineStr">
+        <is>
+          <t>・ブーケ・再で気持ちよく倒せる
+・満額で爽快な周回</t>
+        </is>
+      </c>
+      <c r="F1235" s="2" t="inlineStr">
+        <is>
+          <t>・決戦兵器ヒューズが手元にいない</t>
+        </is>
+      </c>
+      <c r="G1235" s="2" t="inlineStr">
+        <is>
+          <t>・タマ井戸
+・満額
+・鋼鉄兵
+・ランキング
+・YouTubeショート</t>
+        </is>
+      </c>
+      <c r="H1235" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KtsAL2yho3U</t>
+        </is>
+      </c>
+      <c r="J1235" s="2" t="inlineStr">
+        <is>
+          <t>KtsAL2yho3U</t>
+        </is>
+      </c>
+      <c r="K1235" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1236" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1236" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「最新お知らせ」ガッチガチの6体!!いやダーハオいずこへwアビサルサーカス第2弾と合わせてこよみイゴマールも来たぞぉ!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1236" s="2" t="inlineStr">
+        <is>
+          <t>アビサルサーカス第2弾と交換所追加が継続
+連達多数で不遇スタイルの強化に期待
+イゴマール暦みは未実装、TGSで新作情報期待</t>
+        </is>
+      </c>
+      <c r="E1236" s="2" t="inlineStr">
+        <is>
+          <t>・交換所・センジュエルが追加
+・連達多数で不遇スタイル救済に期待
+・新作情報がどこかで絡む期待</t>
+        </is>
+      </c>
+      <c r="F1236" s="2" t="inlineStr">
+        <is>
+          <t>・ダーハオはこのメンツに混ぜられない
+・暦み不在なのに神村鈴を期待させられる</t>
+        </is>
+      </c>
+      <c r="G1236" s="2" t="inlineStr">
+        <is>
+          <t>・最新お知らせ
+・アビサルサーカス第2弾
+・連達追加
+・交換所追加
+・TGS
+・新作情報</t>
+        </is>
+      </c>
+      <c r="H1236" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sDc0rcGwY-0</t>
+        </is>
+      </c>
+      <c r="J1236" s="2" t="inlineStr">
+        <is>
+          <t>sDc0rcGwY-0</t>
+        </is>
+      </c>
+      <c r="K1236" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1237" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1237" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　幻闘：トゥ・クアイ　挑戦　全武器種制覇なるか！　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1237" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープの新イベントに挑戦する配信
+2章でレベル上げ不可など仕様が分かりにくく賛否
+メインストーリーは高評価だが新イベントは微妙評価</t>
+        </is>
+      </c>
+      <c r="E1237" s="2" t="inlineStr">
+        <is>
+          <t>・メインストーリーイベントはめちゃくちゃ面白かった
+・クリアで工場キャラのピースがもらえる</t>
+        </is>
+      </c>
+      <c r="F1237" s="2" t="inlineStr">
+        <is>
+          <t>・2章でレベル上げ不可の謎仕様
+・弱点がつけず武器強化しかできない
+・新イベントは微妙で失敗気味
+・ストーリーが薄く何をやるか分かりにくい</t>
+        </is>
+      </c>
+      <c r="G1237" s="2" t="inlineStr">
+        <is>
+          <t>・幻想水滸伝スターリープ
+・新イベント
+・強敵周回
+・仕様の分かりにくさ
+・メインストーリー</t>
+        </is>
+      </c>
+      <c r="H1237" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cRtabv8aXVc</t>
+        </is>
+      </c>
+      <c r="J1237" s="2" t="inlineStr">
+        <is>
+          <t>cRtabv8aXVc</t>
+        </is>
+      </c>
+      <c r="K1237" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1238" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1238" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】R メタス 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1238" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナルの武装アニメ紹介ショート
+Rメタスの武装演出をピックアップ
+短尺のアニメーション見せ動画</t>
+        </is>
+      </c>
+      <c r="E1238" s="2" t="inlineStr"/>
+      <c r="F1238" s="2" t="inlineStr"/>
+      <c r="G1238" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・メタス
+・武装アニメ
+・ショート動画</t>
+        </is>
+      </c>
+      <c r="H1238" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=247KaeVxovw</t>
+        </is>
+      </c>
+      <c r="J1238" s="2" t="inlineStr">
+        <is>
+          <t>247KaeVxovw</t>
+        </is>
+      </c>
+      <c r="K1238" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1239" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1239" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新ジョーは欲しい！9月8日更新情報まとめ 【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1239" s="2" t="inlineStr">
+        <is>
+          <t>9/8開始アビサルサーカス第2弾の更新情報まとめ
+ガチャは上編ジ・バート編で両方回す予定
+討伐クエスト暦みとの戦いと連動報酬も追加</t>
+        </is>
+      </c>
+      <c r="E1239" s="2" t="inlineStr">
+        <is>
+          <t>・交換所報酬が追加されありがたい
+・ジは絶対取る、ゼノンも欲しい
+・イゴマール暦みは実装されたら超強い期待
+・ロマンシングで交換所全交換できる</t>
+        </is>
+      </c>
+      <c r="F1239" s="2" t="inlineStr">
+        <is>
+          <t>・バートは自分は出づらい
+・前回のポルカガチャはもう回さない</t>
+        </is>
+      </c>
+      <c r="G1239" s="2" t="inlineStr">
+        <is>
+          <t>・9/8更新情報
+・アビサルサーカス第2弾
+・ロマフェス上/バート編
+・討伐クエスト暦み
+・交換所追加
+・ゼノン</t>
+        </is>
+      </c>
+      <c r="H1239" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lUS1-iuo2DM</t>
+        </is>
+      </c>
+      <c r="J1239" s="2" t="inlineStr">
+        <is>
+          <t>lUS1-iuo2DM</t>
+        </is>
+      </c>
+      <c r="K1239" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1240" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1240" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】来るか？！熱冷の時代！！ジョー＆バートガチャ覇権の予感【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1240" s="2" t="inlineStr">
+        <is>
+          <t>アビサルサーカス第2弾のジ・バートガチャに期待
+追撃連達でジの大幅強化を予想
+討伐クエストで新キャラ性能を試したい</t>
+        </is>
+      </c>
+      <c r="E1240" s="2" t="inlineStr">
+        <is>
+          <t>・バートの技がかっこよく強い期待
+・無銘双剣熱化が強く追撃に期待
+・オッドサークル防御強化で強化期待
+・ジは環境を長く引っ張った実績
+・討伐クエストは性能測定に良い</t>
+        </is>
+      </c>
+      <c r="F1240" s="2" t="inlineStr">
+        <is>
+          <t>・敵がインフレせず高難度が物足りない
+・ゼノンは連撃周回キャラで期待薄</t>
+        </is>
+      </c>
+      <c r="G1240" s="2" t="inlineStr">
+        <is>
+          <t>・アビサルサーカス第2弾
+・ジ&amp;バートガチャ
+・熱冷編成
+・連達追撃
+・討伐クエスト
+・ゼノン/玄龍</t>
+        </is>
+      </c>
+      <c r="H1240" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A2k85YEhe3M</t>
+        </is>
+      </c>
+      <c r="J1240" s="2" t="inlineStr">
+        <is>
+          <t>A2k85YEhe3M</t>
+        </is>
+      </c>
+      <c r="K1240" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1241" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1241" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ジョーに大幅強化の予兆あり！？大本命襲来で大興奮の最新情報を確認！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1241" s="2" t="inlineStr">
+        <is>
+          <t>アビサルサーカス第2弾で大本命ジ登場に大興奮
+フランベソルベ連達追加でジ大幅強化を予想
+副防具周回と5枠育成イベントも好評</t>
+        </is>
+      </c>
+      <c r="E1241" s="2" t="inlineStr">
+        <is>
+          <t>・フランベソルベ連達でジ大幅パワーアップ期待
+・副防具周回でき5枠育成・3倍で激美味しい
+・ログボ3000ジュエルとバナーが熱い
+・予想が2連続的中</t>
+        </is>
+      </c>
+      <c r="F1241" s="2" t="inlineStr">
+        <is>
+          <t>・討伐クエストの暦みは敵として結構強そう</t>
+        </is>
+      </c>
+      <c r="G1241" s="2" t="inlineStr">
+        <is>
+          <t>・アビサルサーカス第2弾
+・ジ登場
+・フランベソルベ連達
+・ロマフェス上/バート編
+・討伐クエスト暦み
+・予想的中</t>
+        </is>
+      </c>
+      <c r="H1241" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ASk9qQspNU8</t>
+        </is>
+      </c>
+      <c r="J1241" s="2" t="inlineStr">
+        <is>
+          <t>ASk9qQspNU8</t>
+        </is>
+      </c>
+      <c r="K1241" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1242" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1242" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Abyssal Circusは今が稼ぎ時！育成編成で周回効率が激変します【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1242" s="2" t="inlineStr">
+        <is>
+          <t>アビサルサーカスEX4は攻撃不要で5枠全育成可能
+成長判定3倍で周回育成効率が激変する
+暦み専用副防具の最大進化が最優先事項</t>
+        </is>
+      </c>
+      <c r="E1242" s="2" t="inlineStr">
+        <is>
+          <t>・5枠全育成でき成長判定3倍で効率抜群
+・副防具最大進化でEXフォース1.5倍・ダメブロ
+・記憶再戦と自動再戦のダブル育成が有効
+・攻撃不要でキャラ次第の周回差がない</t>
+        </is>
+      </c>
+      <c r="F1242" s="2" t="inlineStr">
+        <is>
+          <t>・EX4到達まで時間がかかる
+・進化素材を取り損ねると最大進化不可
+・副防具は暦み以外に装備するとデバフ</t>
+        </is>
+      </c>
+      <c r="G1242" s="2" t="inlineStr">
+        <is>
+          <t>・アビサルサーカスEX4
+・育成周回
+・暦み専用副防具
+・成長判定3倍
+・記憶再戦/自動再戦
+・ロール別育成</t>
+        </is>
+      </c>
+      <c r="H1242" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TxswAsIkhZU</t>
+        </is>
+      </c>
+      <c r="J1242" s="2" t="inlineStr">
+        <is>
+          <t>TxswAsIkhZU</t>
+        </is>
+      </c>
+      <c r="K1242" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08T01:07:05Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1242"/>
+  <dimension ref="A1:K1261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -81865,6 +81865,1251 @@
         </is>
       </c>
     </row>
+    <row r="1243">
+      <c r="A1243" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1243" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1243" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】6体ランキング「気絶前提」シンドゥの怒涛のエクストラ〇〇倍&amp;ゼノンが鬼八に!?突陽火力のトップアタッカー　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1243" s="2" t="inlineStr">
+        <is>
+          <t>新ガチャ6体のガチャ性能をランキング解説
+シンドゥは気絶前提でエクストラ3.25倍のみ
+火力はゼノン・バートランドが優秀でバート編推奨</t>
+        </is>
+      </c>
+      <c r="E1243" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノンはエクストラ5倍永続で火力SS
+・バートランドはトップクラスのアタッカー
+・バートランドのエクストラばら撒きが圧倒的に高い
+・ブリザードフォースは有用</t>
+        </is>
+      </c>
+      <c r="F1243" s="2" t="inlineStr">
+        <is>
+          <t>・シンドゥはエクストラ3.25倍しか残らず見た目ほど強くない
+・シンドゥは中期戦で火力もバフもなさすぎる
+・ゼノンは13ターン目から戦えなくなる</t>
+        </is>
+      </c>
+      <c r="G1243" s="2" t="inlineStr">
+        <is>
+          <t>・シンドゥ性能
+・ゼノン火力
+・バートランド
+・エクストラフォース
+・ガチャ優先度</t>
+        </is>
+      </c>
+      <c r="H1243" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GOOw0HDvXJU</t>
+        </is>
+      </c>
+      <c r="J1243" s="2" t="inlineStr">
+        <is>
+          <t>GOOw0HDvXJU</t>
+        </is>
+      </c>
+      <c r="K1243" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1244" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1244" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】会心「53連打」熱冷アタッカー玄竜&amp;防御99%!?とんでもない刺さり方をするかもしれない氷雪　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1244" s="2" t="inlineStr">
+        <is>
+          <t>玄竜と氷雪の熱冷アタッカー性能を解説
+玄竜はエクストラ3.5倍で現環境に強い良スタイル
+氷雪は防御99%のカウンター型でハマれば刺さる</t>
+        </is>
+      </c>
+      <c r="E1244" s="2" t="inlineStr">
+        <is>
+          <t>・玄竜はまともな熱アタッカーで現環境にない枠で強い
+・玄竜は近年出たアタッカーの中で1番良い
+・氷雪は防御99%近くで短期で倒しきる硬さ
+・氷雪はハマればとんでもなく刺さる</t>
+        </is>
+      </c>
+      <c r="F1244" s="2" t="inlineStr">
+        <is>
+          <t>・バートランドは熱が弱い絶妙なバランスがきつい
+・氷雪はリラがあれば必要ないスタイル
+・全体攻撃の熱はエレノアで足りることが多い</t>
+        </is>
+      </c>
+      <c r="G1244" s="2" t="inlineStr">
+        <is>
+          <t>・玄竜性能
+・氷雪(標絶)
+・熱冷アタッカー
+・カウンター
+・防御性能</t>
+        </is>
+      </c>
+      <c r="H1244" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=anJlsxfzv3c</t>
+        </is>
+      </c>
+      <c r="J1244" s="2" t="inlineStr">
+        <is>
+          <t>anJlsxfzv3c</t>
+        </is>
+      </c>
+      <c r="K1244" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1245" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1245" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみとの戦いギミック解明速報「周回一周で」完了!!ロマンシング一発で大幅時短!!すぐ終わらせて神楽鈴完成させたら〇〇に籠るんだ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1245" s="2" t="inlineStr">
+        <is>
+          <t>こよみ討伐はロマンシング1回で交換所完了
+状態異常解除を優先し黒バで火力を安定させる
+23ターン超で確定気絶・全滅技に注意</t>
+        </is>
+      </c>
+      <c r="E1245" s="2" t="inlineStr">
+        <is>
+          <t>・ロマンシング1回でOKで大幅時短
+・難度は低く適当に殴っても倒せる
+・黒バを置くと火力がかなり安定</t>
+        </is>
+      </c>
+      <c r="F1245" s="2" t="inlineStr">
+        <is>
+          <t>・23ターン超で確定気絶・確定全滅技が飛んでくる
+・バフ・デバフがターン終了時に消滅するので解除必須</t>
+        </is>
+      </c>
+      <c r="G1245" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ討伐
+・周回時短
+・状態異常解除
+・ギミック解説
+・リバイバル</t>
+        </is>
+      </c>
+      <c r="H1245" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dmg0KZXG7jo</t>
+        </is>
+      </c>
+      <c r="J1245" s="2" t="inlineStr">
+        <is>
+          <t>dmg0KZXG7jo</t>
+        </is>
+      </c>
+      <c r="K1245" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1246" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1246" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「継承も徹底解説」ジョー&amp;バートランド→今まさに使う状態異常対策とエクストラ置物&amp;斬陰の天井がさらに高く!!火力最高峰バートランド　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1246" s="2" t="inlineStr">
+        <is>
+          <t>ジョーとバートランドの継承含め徹底解説
+ジョーは守り特化で状態異常体制がコンセプト
+バートランドは無名双剣で火力最高峰の尖った火力</t>
+        </is>
+      </c>
+      <c r="E1246" s="2" t="inlineStr">
+        <is>
+          <t>・バートランドは残力7倍に迫り環境最上位の火力
+・バートランドのエクストラ2.5倍は現環境トップに有効
+・ジョーの状態異常体制アップは唯一無二
+・過去2体の中では1番よくできている</t>
+        </is>
+      </c>
+      <c r="F1246" s="2" t="inlineStr">
+        <is>
+          <t>・ジョーは中途半端な火力や守りで出番が微妙
+・バートランドは効果1ターンという絶妙なナーフ
+・ジョーは昔のスタイルのままで残念
+・バートランドは無名双剣ないとアタッカー起用なし</t>
+        </is>
+      </c>
+      <c r="G1246" s="2" t="inlineStr">
+        <is>
+          <t>・ジョー継承
+・バートランド火力
+・状態異常体制
+・エクストラ2.5倍
+・無名双剣</t>
+        </is>
+      </c>
+      <c r="H1246" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=v0wua1XgHZs</t>
+        </is>
+      </c>
+      <c r="J1246" s="2" t="inlineStr">
+        <is>
+          <t>v0wua1XgHZs</t>
+        </is>
+      </c>
+      <c r="K1246" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1247" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1247" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　明日新イベント更新！　お知らせチェックしていこう！　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1247" s="2" t="inlineStr">
+        <is>
+          <t>新イベント前の雑談配信でガチャとこよみ討伐を語る
+原流とゼノンが人気でリズを最優先で狙う声
+こよみ討伐は火力戦で状態異常解除だけ注意</t>
+        </is>
+      </c>
+      <c r="E1247" s="2" t="inlineStr">
+        <is>
+          <t>・原流は火力がすごく井戸で刺さる
+・ゼノンは攻防どちらもやばい修羅場
+・こよみ討伐は弱体破りもなくぬるい
+・聖王が状態異常解除で強い</t>
+        </is>
+      </c>
+      <c r="F1247" s="2" t="inlineStr">
+        <is>
+          <t>・ジョー・バートランドは継承(形状)ないと微妙
+・ゼノンは体術で欲しかったが惜しい
+・ガチャの取りこぼしが最近多い</t>
+        </is>
+      </c>
+      <c r="G1247" s="2" t="inlineStr">
+        <is>
+          <t>・雑談配信
+・ガチャ相談
+・原流・ゼノン
+・こよみ討伐
+・リズ狙い</t>
+        </is>
+      </c>
+      <c r="H1247" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7VBdOMkT7CM</t>
+        </is>
+      </c>
+      <c r="J1247" s="2" t="inlineStr">
+        <is>
+          <t>7VBdOMkT7CM</t>
+        </is>
+      </c>
+      <c r="K1247" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1248" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1248" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ジョー狙って有償ガチャ！『Abyssal Circus 開幕記念 Romancing祭ジョー編＆バートランド編』【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1248" s="2" t="inlineStr">
+        <is>
+          <t>ジョー狙いで有償ロマンシングフェスを実践
+すり抜け多発もジョー・バート・ゼノンを確保
+神龍以外の欲しい枠は綺麗に揃い撤退</t>
+        </is>
+      </c>
+      <c r="E1248" s="2" t="inlineStr">
+        <is>
+          <t>・欲しい枠のバート・ゼノンが揃った
+・無償ジュエルを温存でき次に回せる</t>
+        </is>
+      </c>
+      <c r="F1248" s="2" t="inlineStr">
+        <is>
+          <t>・すり抜けが多くSS自体が出にくかった
+・ゼノンは防御強化系が一切ない点が気になる</t>
+        </is>
+      </c>
+      <c r="G1248" s="2" t="inlineStr">
+        <is>
+          <t>・有償ガチャ
+・ジョー編
+・バートランド編
+・すり抜け
+・引き結果</t>
+        </is>
+      </c>
+      <c r="H1248" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cs0erfWWmfs</t>
+        </is>
+      </c>
+      <c r="J1248" s="2" t="inlineStr">
+        <is>
+          <t>cs0erfWWmfs</t>
+        </is>
+      </c>
+      <c r="K1248" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1249" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1249" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】本命はこっちか！6人性能解説！スーパー性能ひっさげて復活！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1249" s="2" t="inlineStr">
+        <is>
+          <t>新ガチャ6人の性能を配信で一気に解説
+ゼノンは突用の超アタッカーで今回の目玉
+シンドゥは無人島向けダメブロ量産が使い道</t>
+        </is>
+      </c>
+      <c r="E1249" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノンは突用の超アタッカーで今回1番欲しい
+・シンドゥはダメブロを敵の数だけ継続でき無人島向け
+・バートランドは100億以上出せる継続火力
+・原流も火力が出る</t>
+        </is>
+      </c>
+      <c r="F1249" s="2" t="inlineStr">
+        <is>
+          <t>・ジョーはアタッカー性能はあんまりで飛び抜けてない
+・ジョーはフランベソルベ継承しないと火力が伸びない
+・シンドゥの500回攻撃の用途は無人島限定</t>
+        </is>
+      </c>
+      <c r="G1249" s="2" t="inlineStr">
+        <is>
+          <t>・6人性能解説
+・ゼノン超火力
+・シンドゥ無人島
+・バートランド
+・ジョー継承</t>
+        </is>
+      </c>
+      <c r="H1249" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7YQXT3dNyKE</t>
+        </is>
+      </c>
+      <c r="J1249" s="2" t="inlineStr">
+        <is>
+          <t>7YQXT3dNyKE</t>
+        </is>
+      </c>
+      <c r="K1249" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1250" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1250" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】慟哭から始まるコンビニダッシュ！一体いつから神引きすると錯覚した？220連越Wガチャ【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1250" s="2" t="inlineStr">
+        <is>
+          <t>バート・ゼノン狙いで220連超のWガチャに挑戦
+すり抜け連発で2万円課金の大勝負に
+上編でジョーが出ず終始苦戦した引き</t>
+        </is>
+      </c>
+      <c r="E1250" s="2" t="inlineStr">
+        <is>
+          <t>・バートランド編は104連で片方コンプできた</t>
+        </is>
+      </c>
+      <c r="F1250" s="2" t="inlineStr">
+        <is>
+          <t>・すり抜けが30連続くなど引きが渋い
+・上編でジョーが全く出ず爆死
+・2万円課金する羽目になった</t>
+        </is>
+      </c>
+      <c r="G1250" s="2" t="inlineStr">
+        <is>
+          <t>・Wガチャ
+・220連
+・すり抜け
+・2万円課金
+・ジョー狙い</t>
+        </is>
+      </c>
+      <c r="H1250" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AskKap1uVYM</t>
+        </is>
+      </c>
+      <c r="J1250" s="2" t="inlineStr">
+        <is>
+          <t>AskKap1uVYM</t>
+        </is>
+      </c>
+      <c r="K1250" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1251" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1251" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】完全体バートランド！もう遅い！！鞘から剣を抜いちまったからな。。闇夜凶葬刃！！！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1251" s="2" t="inlineStr">
+        <is>
+          <t>完全体バートランドをこよみ戦で試し切り
+無名双剣劣化ループでダメージ90億を記録
+3ターン撃破ならこよみ本体火力が上と評価</t>
+        </is>
+      </c>
+      <c r="E1251" s="2" t="inlineStr">
+        <is>
+          <t>・バートランドは無名双剣劣化ループで90億の火力
+・1ターン目に最大技を撃つとダメブロを奪える</t>
+        </is>
+      </c>
+      <c r="F1251" s="2" t="inlineStr">
+        <is>
+          <t>・3ターン撃破ならこよみ本体の方が火力上
+・バートランドは3ターンに1回でもたつく</t>
+        </is>
+      </c>
+      <c r="G1251" s="2" t="inlineStr">
+        <is>
+          <t>・バートランド試し切り
+・無名双剣劣化
+・こよみ戦
+・ダメージ検証
+・過去技名紹介</t>
+        </is>
+      </c>
+      <c r="H1251" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=csmck0Zy8Hs</t>
+        </is>
+      </c>
+      <c r="J1251" s="2" t="inlineStr">
+        <is>
+          <t>csmck0Zy8Hs</t>
+        </is>
+      </c>
+      <c r="K1251" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1252" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C1252" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】アビサルサーカス第二弾ガチャ！🎪後半雑談タイム</t>
+        </is>
+      </c>
+      <c r="D1252" s="2" t="inlineStr">
+        <is>
+          <t>アビサルサーカス第二弾ガチャ後半は雑談中心
+原流はダブルウィークで幻統では強いと評価
+ゼノンやシンドゥの性能にも軽く触れる</t>
+        </is>
+      </c>
+      <c r="E1252" s="2" t="inlineStr">
+        <is>
+          <t>・原流は幻統(両属性)なら確実に強い
+・ゼノンはユニゾンブレスで火力がすぐ最大値</t>
+        </is>
+      </c>
+      <c r="F1252" s="2" t="inlineStr">
+        <is>
+          <t>・原流はダブルウィークで普通の敵だと片方しか刺さらない
+・情報が出ておらず能力次第</t>
+        </is>
+      </c>
+      <c r="G1252" s="2" t="inlineStr">
+        <is>
+          <t>・第二弾ガチャ
+・雑談配信
+・原流ダブルウィーク
+・ゼノン
+・パチスロ話</t>
+        </is>
+      </c>
+      <c r="H1252" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I1252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1kpRZ3RE2jI</t>
+        </is>
+      </c>
+      <c r="J1252" s="2" t="inlineStr">
+        <is>
+          <t>1kpRZ3RE2jI</t>
+        </is>
+      </c>
+      <c r="K1252" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1253" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1253" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】最強のジョーが帰還！？大注目のジョー編ガチャ性能チェック！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1253" s="2" t="inlineStr">
+        <is>
+          <t>ジョー編3人(ジョー・原流・シンドゥ)を性能チェック
+ジョーは精神500回が必要な極端なサポーター
+原流はOD満タン維持の純粋な超火力アタッカー</t>
+        </is>
+      </c>
+      <c r="E1253" s="2" t="inlineStr">
+        <is>
+          <t>・ジョーは最終ダメ2.5〜3倍の高いエクストラフォース
+・原流はOD常時満タンで超火力アタッカー
+・シンドゥの連撃チャンスは上ぶれ36ヒット</t>
+        </is>
+      </c>
+      <c r="F1253" s="2" t="inlineStr">
+        <is>
+          <t>・ジョーは精神500回使い切りが非常に大変
+・ジョーは置き物的でなく使いやすくはない
+・シンドゥの5〜36ヒットはギャンブル性が高すぎる</t>
+        </is>
+      </c>
+      <c r="G1253" s="2" t="inlineStr">
+        <is>
+          <t>・ジョー救世子
+・精神500回
+・エクストラフォース
+・原流アタッカー
+・シンドゥ</t>
+        </is>
+      </c>
+      <c r="H1253" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=siaOp4ejJqw</t>
+        </is>
+      </c>
+      <c r="J1253" s="2" t="inlineStr">
+        <is>
+          <t>siaOp4ejJqw</t>
+        </is>
+      </c>
+      <c r="K1253" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1254" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1254" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】実はこちらにも注目キャラが！？バートランド編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1254" s="2" t="inlineStr">
+        <is>
+          <t>バートランド編(ゼノン・バート・原流標絶)を性能チェック
+ゼノンは気発と同型の突用純アタッカー
+バートランドは挑発カウンター持ちの超硬ディフェンダー</t>
+        </is>
+      </c>
+      <c r="E1254" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノンは弱点ODで6倍相当の超火力
+・バートランドは常時87.5%以上の超防御
+・バートランドは直接も間接も実質カウンターできる</t>
+        </is>
+      </c>
+      <c r="F1254" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノンは13ターン以上のバトルで全く使えない
+・ゼノンは追撃なしで気発同様エフェクト速度次第</t>
+        </is>
+      </c>
+      <c r="G1254" s="2" t="inlineStr">
+        <is>
+          <t>・バートランド編
+・ゼノン突用
+・気発同型
+・カウンター
+・ディフェンダー</t>
+        </is>
+      </c>
+      <c r="H1254" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zqLPoKf332g</t>
+        </is>
+      </c>
+      <c r="J1254" s="2" t="inlineStr">
+        <is>
+          <t>zqLPoKf332g</t>
+        </is>
+      </c>
+      <c r="K1254" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1255" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1255" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】鋼鉄兵たちの井戸~爽快~100位編成‼️</t>
+        </is>
+      </c>
+      <c r="D1255" s="2" t="inlineStr">
+        <is>
+          <t>鋼鉄兵たちの井戸で100位以内の編成を紹介
+ヒューズ・エリス主体の1ターン4手構成
+4手で約70位、装備はそこまでシビアでない</t>
+        </is>
+      </c>
+      <c r="E1255" s="2" t="inlineStr">
+        <is>
+          <t>・4手クリアで装備はそこまでシビアでなくても大丈夫
+・ヒューズ・エリスが井戸の主力アタッカー</t>
+        </is>
+      </c>
+      <c r="F1255" s="2" t="inlineStr">
+        <is>
+          <t>・3手クリアはかなり苦戦する
+・さらに上位は新しい連撃や良い魂が必要</t>
+        </is>
+      </c>
+      <c r="G1255" s="2" t="inlineStr">
+        <is>
+          <t>・鋼鉄兵の井戸
+・100位編成
+・1ターン4手
+・ヒューズ/エリス
+・ランキング</t>
+        </is>
+      </c>
+      <c r="H1255" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KjkPBzp5lFY</t>
+        </is>
+      </c>
+      <c r="J1255" s="2" t="inlineStr">
+        <is>
+          <t>KjkPBzp5lFY</t>
+        </is>
+      </c>
+      <c r="K1255" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1256" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1256" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】ゼノン能力値早見表【鬼八をも超えるポテンシャル✨】鬼八の能力値早見表と並べて⭐️数値を徹底比較⭐️</t>
+        </is>
+      </c>
+      <c r="D1256" s="2" t="inlineStr">
+        <is>
+          <t>ゼノンの能力値早見表を鬼八と徹底比較
+エクストラ6倍・24ヒットで後発ゼノンが優位
+12ターン限定だが少手数運用で非常に強い</t>
+        </is>
+      </c>
+      <c r="E1256" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノンはエクストラ6倍・火力バフ900%でかなり強い
+・後発で地震火力・耐久・技威力が鬼八超え
+・少手数やレイドタイムアタックでかなりの強さ</t>
+        </is>
+      </c>
+      <c r="F1256" s="2" t="inlineStr">
+        <is>
+          <t>・12ターン以上の長期戦には不向き
+・突用属性のため汎用性は鬼八に分がありそう</t>
+        </is>
+      </c>
+      <c r="G1256" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノン能力値
+・鬼八比較
+・エクストラ6倍
+・24ヒット
+・タイムアタック</t>
+        </is>
+      </c>
+      <c r="H1256" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=f8GH8Qcpd90</t>
+        </is>
+      </c>
+      <c r="J1256" s="2" t="inlineStr">
+        <is>
+          <t>f8GH8Qcpd90</t>
+        </is>
+      </c>
+      <c r="K1256" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1257" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1257" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】玄竜能力値早見表【アセルス越えの~超火力‼️】~アセルスの能力値早見表と比較しての検証考察</t>
+        </is>
+      </c>
+      <c r="D1257" s="2" t="inlineStr">
+        <is>
+          <t>玄竜の能力値早見表をアセルスと比較検証
+トリプルS45〜53ヒットの飛び抜けた火力
+短期も中長期も火力維持できる当たりキャラ</t>
+        </is>
+      </c>
+      <c r="E1257" s="2" t="inlineStr">
+        <is>
+          <t>・玄竜はトリプルS53ヒットの超火力でやばい
+・アセルスより短期も中長期も火力を維持できる
+・エクストラ3倍と火力バフもしっかり付く
+・今回の玄竜は当たり</t>
+        </is>
+      </c>
+      <c r="F1257" s="2" t="inlineStr">
+        <is>
+          <t>・ウィーク(弱点)を取れない場所では火力が半減近くまで落ちる</t>
+        </is>
+      </c>
+      <c r="G1257" s="2" t="inlineStr">
+        <is>
+          <t>・玄竜能力値
+・アセルス比較
+・トリプルS連打
+・エクストラ3倍
+・火力維持</t>
+        </is>
+      </c>
+      <c r="H1257" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kCSTEqfQF44</t>
+        </is>
+      </c>
+      <c r="J1257" s="2" t="inlineStr">
+        <is>
+          <t>kCSTEqfQF44</t>
+        </is>
+      </c>
+      <c r="K1257" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1258" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1258" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】討伐クエスト「こよみ」Romancingを攻略！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1258" s="2" t="inlineStr">
+        <is>
+          <t>討伐クエストこよみ(ヨマール)Romancingを攻略
+形態で属性変化、規則の力上昇に対策が必要
+4ターン以内に火力ゴリ押しで撃破する作戦</t>
+        </is>
+      </c>
+      <c r="E1258" s="2" t="inlineStr">
+        <is>
+          <t>・こよみの超火力を利用し4ターン以内に決着できる
+・西王・アビスで上がった能力を解除して安定</t>
+        </is>
+      </c>
+      <c r="F1258" s="2" t="inlineStr">
+        <is>
+          <t>・規則1の力上昇を放置すると耐えられない
+・4ター目のハンズ4は全体気絶で回避手段不明
+・ミスフォーチンの状態異常で戦線離脱の危険</t>
+        </is>
+      </c>
+      <c r="G1258" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ討伐
+・ヨマール
+・形態変化
+・全体気絶ギミック
+・火力ゴリ押し</t>
+        </is>
+      </c>
+      <c r="H1258" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BfcEX8VQt_4</t>
+        </is>
+      </c>
+      <c r="J1258" s="2" t="inlineStr">
+        <is>
+          <t>BfcEX8VQt_4</t>
+        </is>
+      </c>
+      <c r="K1258" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1259" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1259" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「こよみとの戦い」解説 Romancing 最短2ターン編成、安定3ターン編成　クリア出来ない人向けの解説【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1259" s="2" t="inlineStr">
+        <is>
+          <t>こよみとの戦いを最短2ターン・安定3ターン編成で解説
+交換所アイテムは9月18日まで、難易度別に効率を提示
+クリア不可なら副防具強化を最優先にと助言</t>
+        </is>
+      </c>
+      <c r="E1259" s="2" t="inlineStr">
+        <is>
+          <t>・安定3ターン編成なら状態異常解除薬で安定できる
+・ロマンシング1回で交換所を取り切れる効率の良さ</t>
+        </is>
+      </c>
+      <c r="F1259" s="2" t="inlineStr">
+        <is>
+          <t>・連携攻撃でペナルティウォールのダメブロ15回を貼られる
+・ハンズ4の全体気絶など危険技が多い
+・クリアできないなら交換書を諦める選択もあり</t>
+        </is>
+      </c>
+      <c r="G1259" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ解説
+・2ターン/3ターン編成
+・交換所期限
+・弱点ターン変化
+・副防具優先</t>
+        </is>
+      </c>
+      <c r="H1259" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=109bBWVuVEk</t>
+        </is>
+      </c>
+      <c r="J1259" s="2" t="inlineStr">
+        <is>
+          <t>109bBWVuVEk</t>
+        </is>
+      </c>
+      <c r="K1259" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1260" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1260" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】超絶注意喚起!!周回場所マジで気をつけて!!知らないとマジで後悔します!!【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1260" s="2" t="inlineStr">
+        <is>
+          <t>周回場所に関する超絶注意喚起の動画
+知らないと後悔する周回先の落とし穴を警告
+(字幕取得不良のため詳細は動画本編を参照)</t>
+        </is>
+      </c>
+      <c r="E1260" s="2" t="inlineStr"/>
+      <c r="F1260" s="2" t="inlineStr">
+        <is>
+          <t>・知らないと後悔する周回場所があると警告</t>
+        </is>
+      </c>
+      <c r="G1260" s="2" t="inlineStr">
+        <is>
+          <t>・周回注意喚起
+・周回場所
+・こよみ関連
+・注意喚起</t>
+        </is>
+      </c>
+      <c r="H1260" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7UYqSdIRQ08</t>
+        </is>
+      </c>
+      <c r="J1260" s="2" t="inlineStr">
+        <is>
+          <t>7UYqSdIRQ08</t>
+        </is>
+      </c>
+      <c r="K1260" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1261" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1261" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】超絶注意喚起!!こよみ副防具進化後の周回先はガチで気をつけて!!【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1261" s="2" t="inlineStr">
+        <is>
+          <t>こよみ副防具進化後の周回先を注意喚起
+進化後の周回場所選びに落とし穴があると警告
+(字幕取得不良のため詳細は動画本編を参照)</t>
+        </is>
+      </c>
+      <c r="E1261" s="2" t="inlineStr"/>
+      <c r="F1261" s="2" t="inlineStr">
+        <is>
+          <t>・副防具進化後の周回先を間違えると危険と警告</t>
+        </is>
+      </c>
+      <c r="G1261" s="2" t="inlineStr">
+        <is>
+          <t>・副防具進化
+・周回先注意
+・こよみ
+・注意喚起</t>
+        </is>
+      </c>
+      <c r="H1261" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qOkJHZ7jezI</t>
+        </is>
+      </c>
+      <c r="J1261" s="2" t="inlineStr">
+        <is>
+          <t>qOkJHZ7jezI</t>
+        </is>
+      </c>
+      <c r="K1261" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09T01:15:39Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1261"/>
+  <dimension ref="A1:K1271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -83110,6 +83110,659 @@
         </is>
       </c>
     </row>
+    <row r="1262">
+      <c r="A1262" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1262" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1262" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】引くべき「1ガチャ」週間ランキング!!ジョー&amp;バートランドVSポルカ&amp;リズ編→12体4ガチャランキング!!最新スタイルの最強を決める比較検討会→2026年9月10日版　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1262" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭のガチャ4種を並べて比較検討
+ゼノン・バートランド・原竜が高評価で確保優先
+後半戦の無人島/高難度に向け石を蓄えるべき</t>
+        </is>
+      </c>
+      <c r="E1262" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノンは与ダメ分野で飛び抜け確保優先度高め
+・バートランドは無名双剣継承で環境トップ級
+・原竜は熱の唯一性が高く現環境最高
+・バートのカースドカルテッド12ヒットが爽快
+・リズはここ数体で一番の出来</t>
+        </is>
+      </c>
+      <c r="F1262" s="2" t="inlineStr">
+        <is>
+          <t>・ジは置物として便利な程度で他は弱い
+・熱弱点4体編成自体が強くない
+・リラのコピーは基本性能のみで継承差が歴然
+・ノエルはライバル多く優先度が下がっている</t>
+        </is>
+      </c>
+      <c r="G1262" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ優先度
+・4ガチャ比較
+・ゼノン
+・バートランド
+・原竜
+・リズ</t>
+        </is>
+      </c>
+      <c r="H1262" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gza3-1N9VwY</t>
+        </is>
+      </c>
+      <c r="J1262" s="2" t="inlineStr">
+        <is>
+          <t>gza3-1N9VwY</t>
+        </is>
+      </c>
+      <c r="K1262" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11T02:57:04Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1263" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1263" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】3周年SSR1000 友好箱　武将確認　新規入手の方必見！　1000武将確認</t>
+        </is>
+      </c>
+      <c r="D1263" s="2" t="inlineStr">
+        <is>
+          <t>3周年SSR1000友好箱の交換候補武将を1体ずつ解説
+本多忠勝・毛利元就・井伊直政・竹中半兵衛・豊臣秀吉など
+タンク/デバフ/切り込みなど役割別に性能を紹介</t>
+        </is>
+      </c>
+      <c r="E1263" s="2" t="inlineStr">
+        <is>
+          <t>・本多忠勝は被ダメが相手の強化に影響されずタンク役として優秀
+・毛利元就のデバフは味方全体に付与され勢力戦で強力
+・豊臣秀吉は戦法速度低下とゲージ増加で強い
+・井伊直政は初動の貫通確定が強力な切り込み隊長</t>
+        </is>
+      </c>
+      <c r="F1263" s="2" t="inlineStr">
+        <is>
+          <t>・毛利元就は覚醒5段階まで育てないと落ちやすい
+・井伊直政は中盤以降バフがないと火力が厳しい
+・竹中半兵衛は未所持で効果量がピンと来ない</t>
+        </is>
+      </c>
+      <c r="G1263" s="2" t="inlineStr">
+        <is>
+          <t>・3周年友好箱
+・武将交換候補
+・本多忠勝
+・豊臣秀吉
+・デバフ性能</t>
+        </is>
+      </c>
+      <c r="H1263" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=H4qnVbOor7E</t>
+        </is>
+      </c>
+      <c r="J1263" s="2" t="inlineStr">
+        <is>
+          <t>H4qnVbOor7E</t>
+        </is>
+      </c>
+      <c r="K1263" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11T02:57:04Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1264" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1264" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始343日目記録　猛将　衝撃の展開　今回の主役は筆頭武将</t>
+        </is>
+      </c>
+      <c r="D1264" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣343日目の現状とイベント進捗を報告
+新規6武将を入手し織田信長や毛利元就を育成
+勢力戦や長篠レイドで報酬狙いランク維持</t>
+        </is>
+      </c>
+      <c r="E1264" s="2" t="inlineStr">
+        <is>
+          <t>・織田信長は火力もダメージ軽減もあり生き残りやすく優秀
+・明智光秀は無凸でもバフが乗り戦法ゲージ低下が強力
+・生駒は回復間隔が短く回復要因として活躍</t>
+        </is>
+      </c>
+      <c r="F1264" s="2" t="inlineStr">
+        <is>
+          <t>・毛利元就は育成不足で落ちやすく特性も上げ切れていない
+・明智・真田幸村は凸しないと厳しい
+・経験部が周年イベントでだいぶ枯渇した</t>
+        </is>
+      </c>
+      <c r="G1264" s="2" t="inlineStr">
+        <is>
+          <t>・343日目記録
+・新規武将6体
+・織田信長
+・毛利元就
+・勢力戦/レイド</t>
+        </is>
+      </c>
+      <c r="H1264" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ef4xLwBQITA</t>
+        </is>
+      </c>
+      <c r="J1264" s="2" t="inlineStr">
+        <is>
+          <t>ef4xLwBQITA</t>
+        </is>
+      </c>
+      <c r="K1264" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11T02:57:04Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1265" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1265" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR ガンダムMkｰⅣ 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1265" s="2" t="inlineStr">
+        <is>
+          <t>SSRガンダムMk-Ⅳの武装アニメ紹介Shorts
+台詞のみで性能解説はなし
+Gジェネエターナルの短尺動画</t>
+        </is>
+      </c>
+      <c r="E1265" s="2" t="inlineStr"/>
+      <c r="F1265" s="2" t="inlineStr"/>
+      <c r="G1265" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・ガンダムMk-Ⅳ
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H1265" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ExXCBcjxjg8</t>
+        </is>
+      </c>
+      <c r="J1265" s="2" t="inlineStr">
+        <is>
+          <t>ExXCBcjxjg8</t>
+        </is>
+      </c>
+      <c r="K1265" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11T02:57:04Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1266" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1266" s="2" t="inlineStr">
+        <is>
+          <t>【RS3R】遂に来た！ロマサガ3リメイク発表！！【ロマンシングサガ3デスティニーユナイテッド】</t>
+        </is>
+      </c>
+      <c r="D1266" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガ3リメイク発表内容を主人公・システム面から確認
+2リメイクベースにフリーシナリオや極意化を実装
+マスコンバット・トレードも続投し2027年2月発売</t>
+        </is>
+      </c>
+      <c r="E1266" s="2" t="inlineStr">
+        <is>
+          <t>・2リメイク譲りの綺麗なグラとテンポの良さに期待
+・フリーシナリオが冒険記で分かりやすくなった
+・キャラごと固有モーションで妖精なども可愛い
+・マスコンバットのグラが豪快になった</t>
+        </is>
+      </c>
+      <c r="F1266" s="2" t="inlineStr">
+        <is>
+          <t>・コマンダーモード記載がなくサラの最終戦参加が不安
+・サラや少年など育てる意味の薄いキャラの救済が気になる
+・略称が「デサガ」だと響きが良くない</t>
+        </is>
+      </c>
+      <c r="G1266" s="2" t="inlineStr">
+        <is>
+          <t>・ロマサガ3リメイク
+・8人主人公/フリーシナリオ
+・タイムラインバトル
+・マスコンバット/トレード
+・固有モーション</t>
+        </is>
+      </c>
+      <c r="H1266" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=h2u_XaUtArs</t>
+        </is>
+      </c>
+      <c r="J1266" s="2" t="inlineStr">
+        <is>
+          <t>h2u_XaUtArs</t>
+        </is>
+      </c>
+      <c r="K1266" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11T02:57:04Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1267" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1267" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】小剣を救ってみせる、、超本気ゼノン！こうやって使うんだぁぁぁぁぁ！！！！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1267" s="2" t="inlineStr">
+        <is>
+          <t>ゼノン(小剣)で高難度戦を3ターン攻略に挑戦
+何度も全滅しつつ成功パターンを解説
+ロマサガ3リメイク発表への雑談も長め</t>
+        </is>
+      </c>
+      <c r="E1267" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノンがいればシャトリスで組みクリアできる
+・エクストラフォース1.75倍持ちがいると火力が段違い
+・サルゴンは器用でOD加速もでき優秀</t>
+        </is>
+      </c>
+      <c r="F1267" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノン単体では2ターン攻略は無理で3ターンかかる
+・残攻線が5ヒットでバフを消され事故りやすい
+・2発来ると耐えられず何度も死に戻り</t>
+        </is>
+      </c>
+      <c r="G1267" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノン
+・小剣/斬アタッカー
+・3ターン攻略
+・オーバードライブ
+・成功パターン</t>
+        </is>
+      </c>
+      <c r="H1267" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sAkAYG-mej0</t>
+        </is>
+      </c>
+      <c r="J1267" s="2" t="inlineStr">
+        <is>
+          <t>sAkAYG-mej0</t>
+        </is>
+      </c>
+      <c r="K1267" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11T02:57:04Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1268" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1268" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガ3リメイク】あの名作がリメイク！ロマサガ3リメイクの現状判明している内容まとめ【ロマンシング サガ3デスティニーユナイテッド】</t>
+        </is>
+      </c>
+      <c r="D1268" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガ3リメイク「デスティニーユナイテッド」判明情報を総まとめ
+2027年2月発売、リベサガのたけP・ジーン開発
+マスコンバットやトレードも進化して続投</t>
+        </is>
+      </c>
+      <c r="E1268" s="2" t="inlineStr">
+        <is>
+          <t>・リベサガと同じたけP・ジーン開発で期待大
+・マスコンバット・トレードが進化して続投
+・伊藤賢治の楽曲が約2倍の大ボリューム
+・原曲とアレンジをいつでも切替可能
+・フリーシナリオ健在で遊び応え十分</t>
+        </is>
+      </c>
+      <c r="F1268" s="2" t="inlineStr"/>
+      <c r="G1268" s="2" t="inlineStr">
+        <is>
+          <t>・ロマサガ3リメイク
+・2027年2月発売
+・タイムラインバトル
+・マスコンバット/トレード
+・豪華キャスト
+・極意化</t>
+        </is>
+      </c>
+      <c r="H1268" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ffl-OTfKOzM</t>
+        </is>
+      </c>
+      <c r="J1268" s="2" t="inlineStr">
+        <is>
+          <t>ffl-OTfKOzM</t>
+        </is>
+      </c>
+      <c r="K1268" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11T02:57:04Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1269" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1269" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】ちゃむのYouTubeガチャ配信【間違いなく~つぎの○○で大活躍〜】〜今宵も~神引きの剣捌きが咲き乱れ〜✨</t>
+        </is>
+      </c>
+      <c r="D1269" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガ3リメイク発表に触れつつガチャ録画配信
+バートランド編でゼノンなど狙い60連
+上編でもスーパーアタッカーを60連で確保</t>
+        </is>
+      </c>
+      <c r="E1269" s="2" t="inlineStr">
+        <is>
+          <t>・バートランドは斬突アタッカー多い今の時代に活躍
+・ロマサガ3リメイクのコレクターズEd買いたいほど楽しみ
+・カウンタースタイルはどこかで必ず使える</t>
+        </is>
+      </c>
+      <c r="F1269" s="2" t="inlineStr">
+        <is>
+          <t>・バートランド編は40連すり抜けでピックなしと渋い
+・ゼノンは井戸で活躍しうるが必須でなく悩む</t>
+        </is>
+      </c>
+      <c r="G1269" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ配信
+・ロマサガ3リメイク
+・バートランド
+・ゼノン
+・神引き</t>
+        </is>
+      </c>
+      <c r="H1269" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=T3xTj1veqL8</t>
+        </is>
+      </c>
+      <c r="J1269" s="2" t="inlineStr">
+        <is>
+          <t>T3xTj1veqL8</t>
+        </is>
+      </c>
+      <c r="K1269" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11T02:57:04Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1270" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1270" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「バートランド 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1270" s="2" t="inlineStr">
+        <is>
+          <t>Romancing祭バートランド編3体の性能を考察・ランク付け
+バートランドは継承込A-、氷結ちゃんはB評価
+ゼノンは攻撃倍率6倍の超火力アタッカーでB+</t>
+        </is>
+      </c>
+      <c r="E1270" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノンは攻撃倍率6倍でレイド/高難度に採用でき隙間需要が高い
+・バートランドは無名双剣継承で環境トップ級かつ能力バフ優秀
+・氷結ちゃんはストック型リベンジャーが地味に輝く可能性</t>
+        </is>
+      </c>
+      <c r="F1270" s="2" t="inlineStr">
+        <is>
+          <t>・バートランドは前作暦み編がないと厳しく継承必須
+・氷結ちゃんは条件が噛み合わないと汎用性低め
+・ゼノンは13ター目以降使い物にならずサポート乏しい
+・バートランドの火ダメ軽減50%が物足りない</t>
+        </is>
+      </c>
+      <c r="G1270" s="2" t="inlineStr">
+        <is>
+          <t>・バートランド編考察
+・バートランド
+・原竜/氷結ちゃん
+・ゼノン
+・ランク付け</t>
+        </is>
+      </c>
+      <c r="H1270" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MJ5308oT0II</t>
+        </is>
+      </c>
+      <c r="J1270" s="2" t="inlineStr">
+        <is>
+          <t>MJ5308oT0II</t>
+        </is>
+      </c>
+      <c r="K1270" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11T02:57:04Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1271" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1271" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】討伐クエスト「こよみとの戦い」リクエストがあった編成3種類 ロマンシングクリアの詳細を解説!!【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1271" s="2" t="inlineStr">
+        <is>
+          <t>討伐「こよみとの戦い」の視聴者リクエスト編成を3種紹介
+暦み覚醒を軸に継承・並び順・装備を解説
+西王アビスやコッペパンで状態異常/生存を確保</t>
+        </is>
+      </c>
+      <c r="E1271" s="2" t="inlineStr">
+        <is>
+          <t>・暦みを最左に置く並び順で確保を安定維持できる
+・西王アビスで状態異常回避と3ター目生存が可能</t>
+        </is>
+      </c>
+      <c r="F1271" s="2" t="inlineStr"/>
+      <c r="G1271" s="2" t="inlineStr">
+        <is>
+          <t>・こよみとの戦い
+・討伐クエスト
+・編成3種
+・継承
+・並び順</t>
+        </is>
+      </c>
+      <c r="H1271" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NjVioNNDq4U</t>
+        </is>
+      </c>
+      <c r="J1271" s="2" t="inlineStr">
+        <is>
+          <t>NjVioNNDq4U</t>
+        </is>
+      </c>
+      <c r="K1271" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11T02:57:04Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1271"/>
+  <dimension ref="A1:K1283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -83763,6 +83763,788 @@
         </is>
       </c>
     </row>
+    <row r="1272">
+      <c r="A1272" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1272" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1272" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ますます「一択」忘れずにせんせい週末限定クエスト補充!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1272" s="2" t="inlineStr">
+        <is>
+          <t>週末限定クエスト補充・攻略の短編動画。
+字幕がほぼ取得できず詳細は不明。
+「一択」編成を推奨する内容とみられる。</t>
+        </is>
+      </c>
+      <c r="E1272" s="2" t="inlineStr"/>
+      <c r="F1272" s="2" t="inlineStr"/>
+      <c r="G1272" s="2" t="inlineStr">
+        <is>
+          <t>・週末限定クエスト
+・一択編成</t>
+        </is>
+      </c>
+      <c r="H1272" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JLYnoCeJNz8</t>
+        </is>
+      </c>
+      <c r="J1272" s="2" t="inlineStr">
+        <is>
+          <t>JLYnoCeJNz8</t>
+        </is>
+      </c>
+      <c r="K1272" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:09:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1273" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1273" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガ3R】「意外」デスサガ声優の共通点!!主人公8人中 鬼〇の刃が…名探〇プリキュアが…!?ロマサガ3リメイクの発売を待て!!　#ロマサガ3R　#デスサガ</t>
+        </is>
+      </c>
+      <c r="D1273" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガ3リメイクはフルボイス化が最大の変更点。
+主人公8人の担当声優を実力派中心に紹介。
+名探偵プリキュア出演者が多くプリキュア化と話題。</t>
+        </is>
+      </c>
+      <c r="E1273" s="2" t="inlineStr">
+        <is>
+          <t>・フルボイス化で豪華声優陣に期待
+・カタリナ役 瀬戸麻沙美ははまり役
+・日野聡のミカエルなど実力派揃い
+・アーミック役 小安のボイスが楽しみ</t>
+        </is>
+      </c>
+      <c r="F1273" s="2" t="inlineStr">
+        <is>
+          <t>・モニカの兄はRSでガチャに全く出ず不遇</t>
+        </is>
+      </c>
+      <c r="G1273" s="2" t="inlineStr">
+        <is>
+          <t>・ロマサガ3R
+・フルボイス
+・声優紹介
+・主人公8人</t>
+        </is>
+      </c>
+      <c r="H1273" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qpCKESk3F1c</t>
+        </is>
+      </c>
+      <c r="J1273" s="2" t="inlineStr">
+        <is>
+          <t>qpCKESk3F1c</t>
+        </is>
+      </c>
+      <c r="K1273" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:09:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1274" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1274" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ロマサガ3R始動!?「ロマサガ2R比較」TGSは!?11月発売日記念は!?新キャラプレイアブルは!?デスサガガチャ襲来解明速報　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1274" s="2" t="inlineStr">
+        <is>
+          <t>TGS・ロマサガ3R発売を控えRSのガチャ展開を予想。
+過去のリベサガ時は何も出なかったが主人公実装に期待。
+何もしなければやばい運営と苦言も呈する。</t>
+        </is>
+      </c>
+      <c r="E1274" s="2" t="inlineStr">
+        <is>
+          <t>・主人公8人をこの機に実装する流れに期待</t>
+        </is>
+      </c>
+      <c r="F1274" s="2" t="inlineStr">
+        <is>
+          <t>・リベサガ時は新作発表でも何も出さなかった
+・TGS直前で何もしなければ運営としてやばい</t>
+        </is>
+      </c>
+      <c r="G1274" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ予想
+・ロマサガ3R
+・TGS
+・主人公8人実装
+・発売日記念</t>
+        </is>
+      </c>
+      <c r="H1274" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yT8Js4wUWc0</t>
+        </is>
+      </c>
+      <c r="J1274" s="2" t="inlineStr">
+        <is>
+          <t>yT8Js4wUWc0</t>
+        </is>
+      </c>
+      <c r="K1274" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:09:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1275" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1275" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】00Fのイベント詳細来たので確認 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1275" s="2" t="inlineStr">
+        <is>
+          <t>ガンダムWFイベントが9月17日開催と判明。
+報酬はラジエル・アストレアF2など事前情報通り。
+ガチャはUR版や新規ダブルZ系の可能性を予想。</t>
+        </is>
+      </c>
+      <c r="E1275" s="2" t="inlineStr">
+        <is>
+          <t>・ヒサ・フェルミは支援防御回数が多く使いやすい
+・アストレアF2は範囲広めのマップ兵器持ち</t>
+        </is>
+      </c>
+      <c r="F1275" s="2" t="inlineStr">
+        <is>
+          <t>・フォン・スパークはチャンスステップが増えず残念
+・イベント開催が予想より先で少し遅い</t>
+        </is>
+      </c>
+      <c r="G1275" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・WFイベント
+・報酬ユニット
+・ガチャ予想</t>
+        </is>
+      </c>
+      <c r="H1275" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7PpICyors2w</t>
+        </is>
+      </c>
+      <c r="J1275" s="2" t="inlineStr">
+        <is>
+          <t>7PpICyors2w</t>
+        </is>
+      </c>
+      <c r="K1275" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:09:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1276" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1276" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】00Fのイベント詳細来たので確認 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D1276" s="2" t="inlineStr">
+        <is>
+          <t>ガンダムWFイベントが9月17日開催と判明し詳細確認。
+報酬ユニット・キャラは事前情報通りの内容。
+ガチャはZ系補強など複数の可能性を考察。</t>
+        </is>
+      </c>
+      <c r="E1276" s="2" t="inlineStr">
+        <is>
+          <t>・ヒサ・フェルミは支援防御回数が多く使いやすい
+・アストレアF2は範囲広めのマップ兵器持ち</t>
+        </is>
+      </c>
+      <c r="F1276" s="2" t="inlineStr">
+        <is>
+          <t>・フォン・スパークはチャンスステップが増えず残念
+・イベント開催が予想より先で少し遅い</t>
+        </is>
+      </c>
+      <c r="G1276" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・WFイベント
+・報酬ユニット
+・ガチャ予想</t>
+        </is>
+      </c>
+      <c r="H1276" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=htqgv65mLPM</t>
+        </is>
+      </c>
+      <c r="J1276" s="2" t="inlineStr">
+        <is>
+          <t>htqgv65mLPM</t>
+        </is>
+      </c>
+      <c r="K1276" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:09:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1277" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1277" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】これが【今の】現実・・ゼノン確保前の注意事項を共有【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1277" s="2" t="inlineStr">
+        <is>
+          <t>ゼノン確保前の注意喚起、小剣編成を劇的には楽にしない。
+体術と違い小剣は全体フォース配布が乏しく火力が出にくい。
+ゼノンは防御ゲージが低くギミック対応で落ちやすい。</t>
+        </is>
+      </c>
+      <c r="E1277" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノンは刺さる場面ではしっかり刺さる
+・バートランドは使い所がある評価</t>
+        </is>
+      </c>
+      <c r="F1277" s="2" t="inlineStr">
+        <is>
+          <t>・小剣編成の難易度を簡単にはしない
+・ゼノンは防御ゲージが低く落ちやすい
+・小剣は全体エクストラフォース配布役が不在</t>
+        </is>
+      </c>
+      <c r="G1277" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノン
+・小剣編成
+・こよみとの戦い
+・確保前注意
+・ギミック対応</t>
+        </is>
+      </c>
+      <c r="H1277" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DYV9-oI9_A0</t>
+        </is>
+      </c>
+      <c r="J1277" s="2" t="inlineStr">
+        <is>
+          <t>DYV9-oI9_A0</t>
+        </is>
+      </c>
+      <c r="K1277" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:09:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1278" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1278" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】全コンプ済★最新ガチャランキング引くべき優先順位考察【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1278" s="2" t="inlineStr">
+        <is>
+          <t>今回6ガチャを順位付けし、1位はバートランド編。
+暦読み・幸持ちの雑員加速に噛み合い魅力的と評価。
+全体的にSS級の環境支配キャラはいない印象。</t>
+        </is>
+      </c>
+      <c r="E1278" s="2" t="inlineStr">
+        <is>
+          <t>・バートランド編は絆を2.5倍にでき暦読みと好相性
+・上編ジョは超強力火力の大当たり枠
+・ポルカは全体耐久を圧倒的に強化
+・ゼノンはスコアアタックに刺さる</t>
+        </is>
+      </c>
+      <c r="F1278" s="2" t="inlineStr">
+        <is>
+          <t>・ディラ編は今取らなくてよい・最近使わない
+・ポルカは弱点必須で使いづらい
+・シドゥの500ヒットは実用性が乏しい
+・環境を支配するSS級キャラは不在</t>
+        </is>
+      </c>
+      <c r="G1278" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャランキング
+・バートランド編
+・上編
+・63連ガチャ
+・特定条件活躍</t>
+        </is>
+      </c>
+      <c r="H1278" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lIN0yFvZUi4</t>
+        </is>
+      </c>
+      <c r="J1278" s="2" t="inlineStr">
+        <is>
+          <t>lIN0yFvZUi4</t>
+        </is>
+      </c>
+      <c r="K1278" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:09:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1279" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1279" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】まさかのキャラが第1位！最新版確保優先度ランキング【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1279" s="2" t="inlineStr">
+        <is>
+          <t>確保優先度、最優先は該当なしで悩ましい結果。
+優先高は原流1位、次いでジョ・バート・ブラウニー・ゼノン。
+暦読み編キャラの方が環境上位と分析する。</t>
+        </is>
+      </c>
+      <c r="E1279" s="2" t="inlineStr">
+        <is>
+          <t>・原流は1・2ターン目とも火力が高く周回向き
+・ジョは絆アビ2つ持ちで熱パに好相性
+・ブラウニーは強欲の原頭上で貴重な戦力
+・ゼノンは弱点つければレイドで活躍</t>
+        </is>
+      </c>
+      <c r="F1279" s="2" t="inlineStr">
+        <is>
+          <t>・最優先に置ける性能のキャラはいない
+・バートランドは継承がほぼ必須
+・原流標節はディフェンダーで使い所がない
+・ポルカ編は暦読み編より一段下の性能</t>
+        </is>
+      </c>
+      <c r="G1279" s="2" t="inlineStr">
+        <is>
+          <t>・確保優先度
+・原流1位
+・ジョ
+・ゼノン
+・暦読み編</t>
+        </is>
+      </c>
+      <c r="H1279" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=03STS-yFlJ8</t>
+        </is>
+      </c>
+      <c r="J1279" s="2" t="inlineStr">
+        <is>
+          <t>03STS-yFlJ8</t>
+        </is>
+      </c>
+      <c r="K1279" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:09:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1280" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1280" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】結局このメンツが強過ぎなのよ...！現状最強レベルの編成でこよみとの戦いに挑戦【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1280" s="2" t="inlineStr">
+        <is>
+          <t>こよみとの戦いロマンシングに暦読み最強編成でオート挑戦。
+暦読み・サイバー・コッぺパンが環境トップと再認識。
+オートでも余裕でクリア、報酬の少なさには苦言。</t>
+        </is>
+      </c>
+      <c r="E1280" s="2" t="inlineStr">
+        <is>
+          <t>・コッぺパンは補助サポーターとして非常に優秀
+・サライは1ターン目から高火力
+・暦読み・サイバーは環境トップの強さ
+・サイバーの状態異常解除が有用</t>
+        </is>
+      </c>
+      <c r="F1280" s="2" t="inlineStr">
+        <is>
+          <t>・報酬のジュエル500・ソウルピース100は少ない
+・オート時はダメージが足りず倒せない場合がある</t>
+        </is>
+      </c>
+      <c r="G1280" s="2" t="inlineStr">
+        <is>
+          <t>・こよみとの戦い
+・暦読み編成
+・オートクリア
+・コッぺパン
+・環境トップ</t>
+        </is>
+      </c>
+      <c r="H1280" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=28QY6GPX6rY</t>
+        </is>
+      </c>
+      <c r="J1280" s="2" t="inlineStr">
+        <is>
+          <t>28QY6GPX6rY</t>
+        </is>
+      </c>
+      <c r="K1280" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:09:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1281" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1281" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】これがあれば開幕から術が当たる！幻闘場トゥクアイ杖の戦録ギミック対策【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1281" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場トゥクアイ杖の戦録ギミックを実戦で対策。
+術は当たらず技やODで必中を取る必要がある。
+追撃・解除薬とターミンのゴリ押しでクリア。</t>
+        </is>
+      </c>
+      <c r="E1281" s="2" t="inlineStr">
+        <is>
+          <t>・ODや技なら必中で当てられる
+・ターミンの火力でゴリ押しクリアできた
+・黒バラを連れて行って正解だった</t>
+        </is>
+      </c>
+      <c r="F1281" s="2" t="inlineStr">
+        <is>
+          <t>・通常の術は当たらず対策が必要
+・デバフが効きにくく難しい</t>
+        </is>
+      </c>
+      <c r="G1281" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場
+・トゥクアイ
+・杖の戦録
+・ギミック対策
+・術無効</t>
+        </is>
+      </c>
+      <c r="H1281" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zUEaJ3ESCQ8</t>
+        </is>
+      </c>
+      <c r="J1281" s="2" t="inlineStr">
+        <is>
+          <t>zUEaJ3ESCQ8</t>
+        </is>
+      </c>
+      <c r="K1281" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:09:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1282" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1282" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第137回シグフレイたちの井戸【ギミック・アビリティ・攻撃】〜攻略法を徹底解説〜ランキング上位を目指そう‼️</t>
+        </is>
+      </c>
+      <c r="D1282" s="2" t="inlineStr">
+        <is>
+          <t>9月14日実装シグフレイの井戸を実装前に考察。
+全員術士で挑む初の井戸でギミックが多彩。
+術全体アタッカーとバッファーの総合力が問われる。</t>
+        </is>
+      </c>
+      <c r="E1282" s="2" t="inlineStr">
+        <is>
+          <t>・全員術士という初の井戸で編成が楽しい
+・術師の総合力が問われる面白いステージ
+・ターミン・黒原姫・サイバーなどが活躍思想</t>
+        </is>
+      </c>
+      <c r="F1282" s="2" t="inlineStr">
+        <is>
+          <t>・引用元の螺旋1570回はかなりの強敵
+・突属性は無効化され採用しづらい
+・最後の抵抗でバフを剥がされ厄介</t>
+        </is>
+      </c>
+      <c r="G1282" s="2" t="inlineStr">
+        <is>
+          <t>・シグフレイの井戸
+・第137回
+・術士編成
+・ギミック考察
+・螺旋1570回</t>
+        </is>
+      </c>
+      <c r="H1282" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UYZ1yXhdG_0</t>
+        </is>
+      </c>
+      <c r="J1282" s="2" t="inlineStr">
+        <is>
+          <t>UYZ1yXhdG_0</t>
+        </is>
+      </c>
+      <c r="K1282" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:09:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1283" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1283" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】2026年9月上旬ガチャ総まとめ！全12スタイル引くべきスタイルランキング！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1283" s="2" t="inlineStr">
+        <is>
+          <t>9月上旬ガチャをティアランク付け、S評価は該当なし。
+A評価はリズ、原流やゼノンはダークホース枠。
+ブラウニーは幻闘場特化で実質A級と高評価。</t>
+        </is>
+      </c>
+      <c r="E1283" s="2" t="inlineStr">
+        <is>
+          <t>・リズは短期決戦・レイドで超火力を出せA評価
+・ゼノンは攻撃倍率6倍でレイドで活躍
+・ブラウニーは半年〜1年使える幻闘場特化
+・イーブリンは火ダメ87%軽減が優秀</t>
+        </is>
+      </c>
+      <c r="F1283" s="2" t="inlineStr">
+        <is>
+          <t>・抜けて強いS評価スタイルは今はいない
+・リズは長期戦では火力が失速
+・ゼノンは13ターン目以降使い物にならない
+・バートランドは前の暦読み編がないと厳しい</t>
+        </is>
+      </c>
+      <c r="G1283" s="2" t="inlineStr">
+        <is>
+          <t>・ティアランク
+・ガチャ総まとめ
+・リズA評価
+・S該当なし
+・ブラウニー</t>
+        </is>
+      </c>
+      <c r="H1283" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-ZIiMV-DA8Y</t>
+        </is>
+      </c>
+      <c r="J1283" s="2" t="inlineStr">
+        <is>
+          <t>-ZIiMV-DA8Y</t>
+        </is>
+      </c>
+      <c r="K1283" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:09:07Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1283"/>
+  <dimension ref="A1:K1299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -84545,6 +84545,1113 @@
         </is>
       </c>
     </row>
+    <row r="1284">
+      <c r="A1284" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1284" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1284" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】バートランド取説「最強×最強」こよみ&amp;サルーイン比較とバート軸編成2種!!斬陰熱冷を活かせるまたは活かせない高難度&amp;無尽塔お仲間は誰!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1284" s="2" t="inlineStr">
+        <is>
+          <t>バートランドの性能を斬・熱冷で要点解説。
+継承無名双剣の残編成が本命、暦みが短期の相棒。
+熱冷運用は原流と組む時のみで汎用性は低い。</t>
+        </is>
+      </c>
+      <c r="E1284" s="2" t="inlineStr">
+        <is>
+          <t>・無名双剣継承で装備込み暦みを超える火力
+・味方全体にODザイン2.5倍ばら撒きが強力
+・長期戦で確実に暦みを上回る残部隊
+・原流とはまれば1ターン最大恩恵でベストパートナー
+・ODゲージ55%補填が有用</t>
+        </is>
+      </c>
+      <c r="F1284" s="2" t="inlineStr">
+        <is>
+          <t>・リキャスト3ターンが惜しい
+・熱冷運用は火力が出ず活躍機会ほぼ無し
+・無名双剣か怪獣継承がないと使い勝手が悪い
+・熱冷は副属性が広がる見込みなく不遇</t>
+        </is>
+      </c>
+      <c r="G1284" s="2" t="inlineStr">
+        <is>
+          <t>・バートランド性能
+・無名双剣継承
+・残編成
+・暦み/サルーイン比較
+・熱冷運用
+・ODゲージ補填</t>
+        </is>
+      </c>
+      <c r="H1284" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Vbs2cjdO-5M</t>
+        </is>
+      </c>
+      <c r="J1284" s="2" t="inlineStr">
+        <is>
+          <t>Vbs2cjdO-5M</t>
+        </is>
+      </c>
+      <c r="K1284" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1285" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1285" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始343日目記録　猛将　今回の主役は筆頭武将！</t>
+        </is>
+      </c>
+      <c r="D1285" s="2" t="inlineStr">
+        <is>
+          <t>出陣343日目、周年で新規武将6体を追加。
+織田信長や柴田勝家の育成方針とイベント報告。
+ガチャで柴田勝家を50連50%で無事引き当て。</t>
+        </is>
+      </c>
+      <c r="E1285" s="2" t="inlineStr">
+        <is>
+          <t>・織田信長は火力も軽減もあり生き残りやすい
+・明智光秀は無凸でもバフとゲージ低下が優秀
+・モリ元就はデバフ枠として貴重
+・柴田勝家は保湿で攻撃を集め軽減も高い
+・本多小松はタンク完成系に最適</t>
+        </is>
+      </c>
+      <c r="F1285" s="2" t="inlineStr">
+        <is>
+          <t>・明智光秀は3凸しないと厳しい
+・モリ元就は未育成で落ちやすい
+・柴田勝家は5凸しないとダメ向けできず育成難易度が高い
+・特性素材が全然足りない
+・徳川家は復勝・より持ちが少ない</t>
+        </is>
+      </c>
+      <c r="G1285" s="2" t="inlineStr">
+        <is>
+          <t>・新規武将6体
+・織田信長
+・明智光秀
+・柴田勝家ガチャ
+・勢力戦/列伝
+・徳川家育成</t>
+        </is>
+      </c>
+      <c r="H1285" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WblRvSY5jmo</t>
+        </is>
+      </c>
+      <c r="J1285" s="2" t="inlineStr">
+        <is>
+          <t>WblRvSY5jmo</t>
+        </is>
+      </c>
+      <c r="K1285" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1286" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1286" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　討伐：飯綱こよみ　最大の壁４ターンを乗り越えて勝利を掴み取る</t>
+        </is>
+      </c>
+      <c r="D1286" s="2" t="inlineStr">
+        <is>
+          <t>討伐こよみを火力控えめ編成で長期戦攻略。
+4ターン目の気絶とダメブロ15回対策が鍵。
+ダメブロ活用と白薔薇姫のガード超極で完勝。</t>
+        </is>
+      </c>
+      <c r="E1286" s="2" t="inlineStr">
+        <is>
+          <t>・ダメブロの効果が高く有効
+・白薔薇姫のガードアップ超極が大きい
+・弱点つけない暦みでも最高火力
+・ターミンの資源継承が有効</t>
+        </is>
+      </c>
+      <c r="F1286" s="2" t="inlineStr">
+        <is>
+          <t>・暦みが弱点入らず厄介
+・5ターン目以降の能力バフ上昇で硬くなる
+・火力低いと15ターン強制終了リスク
+・カウンターすると敵の防御強化が上がる
+・火力が全然通らず苦戦</t>
+        </is>
+      </c>
+      <c r="G1286" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ討伐
+・4ターン気絶対策
+・ダメブロ15回
+・状態異常対策
+・白薔薇姫ガード
+・暦みアタッカー</t>
+        </is>
+      </c>
+      <c r="H1286" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=i_93SpxN-yA</t>
+        </is>
+      </c>
+      <c r="J1286" s="2" t="inlineStr">
+        <is>
+          <t>i_93SpxN-yA</t>
+        </is>
+      </c>
+      <c r="K1286" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1287" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1287" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネやりながら雑談</t>
+        </is>
+      </c>
+      <c r="D1287" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナルを遊びつつ雑談配信。
+1.5周年はVガンダム参戦がほぼ確定。
+年明けのゲーム発売ラッシュとロマサガ3も話題。</t>
+        </is>
+      </c>
+      <c r="E1287" s="2" t="inlineStr">
+        <is>
+          <t>・チャレンジ配布ユニットは毎回優秀で強い
+・ダブルZチャレンジがなんとかなり安心
+・1.5周年キャンペーンは消費半減で回りやすい
+・三日月(ミカ)はチャンスステップ多く優秀</t>
+        </is>
+      </c>
+      <c r="F1287" s="2" t="inlineStr">
+        <is>
+          <t>・URのEX武装は必中で回避が死んでいる
+・パイロットの性能がついてこない
+・攻撃型が限定に寄りすぎ
+・ゼクアインが弱い
+・ダブルZはキャラが少ない</t>
+        </is>
+      </c>
+      <c r="G1287" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・1.5周年Vガンダム
+・チャレンジ機体
+・ローグオービット
+・ロマサガ3リメイク
+・課金調整</t>
+        </is>
+      </c>
+      <c r="H1287" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NKmliJNMMWk</t>
+        </is>
+      </c>
+      <c r="J1287" s="2" t="inlineStr">
+        <is>
+          <t>NKmliJNMMWk</t>
+        </is>
+      </c>
+      <c r="K1287" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1288" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1288" s="2" t="inlineStr">
+        <is>
+          <t>【RS3R】仲間の自由度は？コマンダーは？公式生放送情報まとめ【ロマンシングサガ3デスティニーユナイテッド】</t>
+        </is>
+      </c>
+      <c r="D1288" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガ3リメイクの公式生放送情報まとめ。
+カタリナ加入可、パーティー編成の自由度が大幅向上。
+コマンダーはなし、術は購入から閃き習得に変更。</t>
+        </is>
+      </c>
+      <c r="E1288" s="2" t="inlineStr">
+        <is>
+          <t>・主人公問わず全キャラ仲間にでき編成自由度が高い
+・セーブポイントで自由に再編成可能
+・固有装備が意味のあるものに
+・術が強化される
+・弱かった術も使い道あり</t>
+        </is>
+      </c>
+      <c r="F1288" s="2" t="inlineStr">
+        <is>
+          <t>・コマンダーモードはなし
+・暗闇の迷宮は削除
+・術が購入式でなく閃き型になり自由度減
+・ひらめき適正は確率差として残る</t>
+        </is>
+      </c>
+      <c r="G1288" s="2" t="inlineStr">
+        <is>
+          <t>・RS3リメイク
+・カタリナ加入
+・編成自由度
+・コマンダー廃止
+・術強化
+・隠しダンジョン</t>
+        </is>
+      </c>
+      <c r="H1288" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UgA96ueu1fA</t>
+        </is>
+      </c>
+      <c r="J1288" s="2" t="inlineStr">
+        <is>
+          <t>UgA96ueu1fA</t>
+        </is>
+      </c>
+      <c r="K1288" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1289" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1289" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】1.5周年はVガンダムで確定！？特設サイト＆インタビュー記事を確認 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D1289" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナル1.5周年の特設サイトを確認。
+参戦記念作品はVガンダムでほぼ確定。
+Eシミュレーター第2弾など運営の対応を評価。</t>
+        </is>
+      </c>
+      <c r="E1289" s="2" t="inlineStr">
+        <is>
+          <t>・運営がユーザーの声によく耳を傾けている
+・Eシミュレーター第2弾が前倒しで期待
+・ガシャクロス光の騎士編も確実に来る</t>
+        </is>
+      </c>
+      <c r="F1289" s="2" t="inlineStr">
+        <is>
+          <t>・キャラクターSSPは現状予定なし
+・ジークアクス・劇場版シードは1.5周年ではなさそう
+・ビルド系はメインステージ参戦せずストーリーイベント止まり</t>
+        </is>
+      </c>
+      <c r="G1289" s="2" t="inlineStr">
+        <is>
+          <t>・1.5周年Vガンダム確定
+・特設サイト
+・Eシミュレーター第2弾
+・ガシャクロス4章
+・キャラSSP</t>
+        </is>
+      </c>
+      <c r="H1289" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=peFsh5ea42U</t>
+        </is>
+      </c>
+      <c r="J1289" s="2" t="inlineStr">
+        <is>
+          <t>peFsh5ea42U</t>
+        </is>
+      </c>
+      <c r="K1289" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1290" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1290" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】瞬間火力最強をきめようか。。超パワーゲンちゃん★次元が違いすぎる件【ロマンシングサガリユニバース】【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1290" s="2" t="inlineStr">
+        <is>
+          <t>原流とアセルスの火力を実機で比較検証。
+弱点つけなくても編成で軽く火力を出せると解説。
+原流が圧倒的火力でアセルス超え、評価を改める。</t>
+        </is>
+      </c>
+      <c r="E1290" s="2" t="inlineStr">
+        <is>
+          <t>・原流は1ターン目から火力が出て編成の幅が広い
+・原流はエクストラ乗せヒットが下がらず強力
+・アセルスはパークワンド等で2ターン目に爆発
+・熱冷逆転時の原流はやばい火力</t>
+        </is>
+      </c>
+      <c r="F1290" s="2" t="inlineStr">
+        <is>
+          <t>・原流もアセルスも弱点つけないとエクストラ乗らず1億止まり
+・アセルスは2ターン目に化けるが原流に届かない
+・アセルスの汎用性が原流の登場で少し減った</t>
+        </is>
+      </c>
+      <c r="G1290" s="2" t="inlineStr">
+        <is>
+          <t>・原流vsアセルス
+・弱点なし火力
+・編成火力
+・バートランド併用
+・YouTube収益変化</t>
+        </is>
+      </c>
+      <c r="H1290" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4vuZhIXkm4c</t>
+        </is>
+      </c>
+      <c r="J1290" s="2" t="inlineStr">
+        <is>
+          <t>4vuZhIXkm4c</t>
+        </is>
+      </c>
+      <c r="K1290" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1291" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1291" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】全コンプ済！最新キャラランキング★王者陰斬ＶＳ新星熱冷主人公軍団【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1291" s="2" t="inlineStr">
+        <is>
+          <t>全コンプ済みで最新キャラをTierランク付け。
+残環境は不動、ジョーS・原流SS・新ドゥーA評価。
+バートは無名双剣継承込みでSS、ゼノンもSS。</t>
+        </is>
+      </c>
+      <c r="E1291" s="2" t="inlineStr">
+        <is>
+          <t>・原流は弱点つけると破壊力えげつない
+・ゼノンは1回行動超火力で証券唯一無二
+・バートは3ターンに1回2.5倍が強い
+・継承込みバートはSS級評価</t>
+        </is>
+      </c>
+      <c r="F1291" s="2" t="inlineStr">
+        <is>
+          <t>・ジョーは器用貧乏でアタッカー物足りない
+・新ドゥーは500ヒット条件が尖りすぎ使いづらい
+・ポルカは編成が面倒でS止まり
+・新ドゥーは無人島適正も怖い</t>
+        </is>
+      </c>
+      <c r="G1291" s="2" t="inlineStr">
+        <is>
+          <t>・キャラランキング
+・残環境不動
+・原流SS評価
+・バートランド継承
+・ゼノンSS
+・所持率アンケート</t>
+        </is>
+      </c>
+      <c r="H1291" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=l3Pe6nSutTc</t>
+        </is>
+      </c>
+      <c r="J1291" s="2" t="inlineStr">
+        <is>
+          <t>l3Pe6nSutTc</t>
+        </is>
+      </c>
+      <c r="K1291" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1292" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C1292" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】こよみとの闘い！と🎪</t>
+        </is>
+      </c>
+      <c r="D1292" s="2" t="inlineStr">
+        <is>
+          <t>雑談しつつ暦み討伐とアビサルサーカスを消化。
+原流を入れると火力激増で3ターン討伐が可能に。
+魂アビ排水は運次第で全然覚えず苦戦。</t>
+        </is>
+      </c>
+      <c r="E1292" s="2" t="inlineStr">
+        <is>
+          <t>・原流を入れると火力が段違いで楽勝
+・原流はアセルスを超えるダメージ
+・げんちゃんは弱点あれば強力
+・RS3リメイクのミニゲーム(トレード)に期待</t>
+        </is>
+      </c>
+      <c r="F1292" s="2" t="inlineStr">
+        <is>
+          <t>・暦みは弱点つけず動けないと厳しい
+・魂アビ排水が全然覚えられず討伐も失敗
+・アビサルサーカスは目玉が弱くインパクト不足
+・ロマサガRSはインフレがひどい</t>
+        </is>
+      </c>
+      <c r="G1292" s="2" t="inlineStr">
+        <is>
+          <t>・こよみ討伐
+・原流火力
+・魂アビ排水
+・RS3リメイク雑談
+・パチスロ/株談義</t>
+        </is>
+      </c>
+      <c r="H1292" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I1292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=oOSfpCzAY7U</t>
+        </is>
+      </c>
+      <c r="J1292" s="2" t="inlineStr">
+        <is>
+          <t>oOSfpCzAY7U</t>
+        </is>
+      </c>
+      <c r="K1292" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1293" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1293" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガ3リメイク】衝撃の新情報アリ！公式生放送で発表された内容を大紹介【ロマンシング サガ3デスティニーユナイテッド】</t>
+        </is>
+      </c>
+      <c r="D1293" s="2" t="inlineStr">
+        <is>
+          <t>RS3リメイク公式生放送の新情報を大紹介。
+全キャラ仲間化・カタリナ加入で編成自由度向上。
+術は閃き習得に変更、マスコンバット等も継続。</t>
+        </is>
+      </c>
+      <c r="E1293" s="2" t="inlineStr">
+        <is>
+          <t>・どの主人公でも全キャラ仲間にできる
+・セーブポイントでLP/BP全回復&amp;仲間交代可能
+・マスコンバットが見やすく改善
+・トレードにODゲージ新要素で戦略的に
+・サラが大事なバトルでも使える</t>
+        </is>
+      </c>
+      <c r="F1293" s="2" t="inlineStr">
+        <is>
+          <t>・コマンダーモードはなし
+・王家の指輪の金策は不可に
+・暗闇の迷宮は削除
+・技術の王冠システムは廃止</t>
+        </is>
+      </c>
+      <c r="G1293" s="2" t="inlineStr">
+        <is>
+          <t>・RS3リメイク
+・カタリナ仲間化
+・術閃き習得
+・セーブ回復/交代
+・マスコンバット/トレード
+・新キャラ示唆</t>
+        </is>
+      </c>
+      <c r="H1293" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CrekX_POvBI</t>
+        </is>
+      </c>
+      <c r="J1293" s="2" t="inlineStr">
+        <is>
+          <t>CrekX_POvBI</t>
+        </is>
+      </c>
+      <c r="K1293" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1294" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1294" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】小剣の救世主！幻闘場ウンディーネ&amp;ボルカノ小剣の戦録3ターン攻略【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1294" s="2" t="inlineStr">
+        <is>
+          <t>幻闘場小剣ウンディーネ&amp;ボルカノを3ターン攻略。
+ゼノンの火力で220億出し証券コンプリート。
+イリスのルミナスフォースで生存を確保。</t>
+        </is>
+      </c>
+      <c r="E1294" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノンの火力が正義で220億出る
+・イリスのルミナスフォースで生存確定
+・ネオンの天品持ちが偉い</t>
+        </is>
+      </c>
+      <c r="F1294" s="2" t="inlineStr"/>
+      <c r="G1294" s="2" t="inlineStr">
+        <is>
+          <t>・幻闘場小剣
+・ウンディーネ&amp;ボルカノ
+・ゼノン火力
+・3ターン攻略
+・証券コンプ</t>
+        </is>
+      </c>
+      <c r="H1294" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=up-yrSRdIyM</t>
+        </is>
+      </c>
+      <c r="J1294" s="2" t="inlineStr">
+        <is>
+          <t>up-yrSRdIyM</t>
+        </is>
+      </c>
+      <c r="K1294" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1295" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1295" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ジョー&amp;バートランドガチャ性能チェック！全6体のキャラランク評価＆徹底解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1295" s="2" t="inlineStr">
+        <is>
+          <t>新ガチャ全6体の性能とランクを声付き解説。
+ゼノンが証券の貴重な火力枠で個人的注目キャラ。
+ジョーは高難度向け、新ドゥーは500ヒット条件。</t>
+        </is>
+      </c>
+      <c r="E1295" s="2" t="inlineStr">
+        <is>
+          <t>・ジョーは2種の絆で高難度に重宝
+・原流は火力ヒット数稼げる熱アタッカー
+・ゼノンは証券の貴重な火力枠でアタッカー性能ピカイチ
+・バートはジョーとの相性抜群</t>
+        </is>
+      </c>
+      <c r="F1295" s="2" t="inlineStr">
+        <is>
+          <t>・原流は条件厳しく使う場所を選ぶ
+・新ドゥーは500ヒットが局所的で星1
+・バートはユニーク性が薄い
+・ゼノンは弱点がはっきりしている</t>
+        </is>
+      </c>
+      <c r="G1295" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ6体性能
+・ジョー星3
+・原流星2
+・新ドゥー星1
+・バート星2
+・ゼノン注目</t>
+        </is>
+      </c>
+      <c r="H1295" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xtgQHSKWFvo</t>
+        </is>
+      </c>
+      <c r="J1295" s="2" t="inlineStr">
+        <is>
+          <t>xtgQHSKWFvo</t>
+        </is>
+      </c>
+      <c r="K1295" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1296" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1296" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】ジョー能力値早見表~【2パターンの早見表を~比較】ありゃ~😳貴女も~○○で大活躍しますのん？</t>
+        </is>
+      </c>
+      <c r="D1296" s="2" t="inlineStr">
+        <is>
+          <t>第2弾ガチャのジョー能力値を2パターンで比較。
+フランソルベプラス継承で強力な熱アタッカーに。
+状態異常体制付与で周回アタッカーも可能。</t>
+        </is>
+      </c>
+      <c r="E1296" s="2" t="inlineStr">
+        <is>
+          <t>・フランソルベプラス継承で全体クアトロエス連打が強力
+・熱冷用フォース1.5倍で火力貢献大
+・状態異常体制極大でスタン対策になる
+・周回アタッカーとしても使える</t>
+        </is>
+      </c>
+      <c r="F1296" s="2" t="inlineStr">
+        <is>
+          <t>・素の遺灰戦術は追撃が弱く今の時代に合わない
+・熱冷術が術算1回でもったいない
+・シグフレイの直接攻撃でスタンを食らう懸念</t>
+        </is>
+      </c>
+      <c r="G1296" s="2" t="inlineStr">
+        <is>
+          <t>・ジョー能力値
+・フランソルベプラス継承
+・熱冷サポート
+・状態異常体制
+・周回運用</t>
+        </is>
+      </c>
+      <c r="H1296" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_fl7SzInQ-c</t>
+        </is>
+      </c>
+      <c r="J1296" s="2" t="inlineStr">
+        <is>
+          <t>_fl7SzInQ-c</t>
+        </is>
+      </c>
+      <c r="K1296" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1297" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1297" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【ガチャ動画】やはり単発・・・！！【No.636】</t>
+        </is>
+      </c>
+      <c r="D1297" s="2" t="inlineStr">
+        <is>
+          <t>アビサルサーカスガチャでブラウニー狙いの実況。
+100連で出ず単発切り替えでSS2体を引き当て。
+1800ジュエル温存で感動のフィナーレ。</t>
+        </is>
+      </c>
+      <c r="E1297" s="2" t="inlineStr">
+        <is>
+          <t>・単発切り替えでブラウニー2体ゲット
+・1800ジュエル温存できてお得
+・すり抜けなく綺麗に獲得できた</t>
+        </is>
+      </c>
+      <c r="F1297" s="2" t="inlineStr">
+        <is>
+          <t>・100連物センサーで目当てが出ず
+・ブラウニーとの相性が悪いガチャ
+・10連だとジュエルの無駄が出る懸念</t>
+        </is>
+      </c>
+      <c r="G1297" s="2" t="inlineStr">
+        <is>
+          <t>・アビサルサーカスガチャ
+・ブラウニー狙い
+・単発引き
+・SS2体獲得
+・ジュエル温存</t>
+        </is>
+      </c>
+      <c r="H1297" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I1297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qGeoAS5Zn_A</t>
+        </is>
+      </c>
+      <c r="J1297" s="2" t="inlineStr">
+        <is>
+          <t>qGeoAS5Zn_A</t>
+        </is>
+      </c>
+      <c r="K1297" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1298" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1298" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「ジョー 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1298" s="2" t="inlineStr">
+        <is>
+          <t>ロマンシングフェス上編3体のスタイルを考察評価。
+ジョーは万能B、原流は火力特化B+、新ドゥーはB。
+継承や条件次第で評価が変わる尖った性能。</t>
+        </is>
+      </c>
+      <c r="E1298" s="2" t="inlineStr">
+        <is>
+          <t>・ジョーは軽減・状態異常対策要因として心強い
+・原流はユニゾンブレス53ヒットが強力でレイド/高難度に使える
+・新ドゥーは500ヒット後2.75〜3.25倍の脅威の火力</t>
+        </is>
+      </c>
+      <c r="F1298" s="2" t="inlineStr">
+        <is>
+          <t>・ジョーは器用貧乏でサポも火力も中途半端
+・原流は火ダメ軽減0でウィーク条件が必要
+・新ドゥーは500ヒット条件が高く序盤活躍しない
+・超高難度は年2〜3回しかなく重要度は落ちる</t>
+        </is>
+      </c>
+      <c r="G1298" s="2" t="inlineStr">
+        <is>
+          <t>・ジョー考察B
+・原流B+
+・新ドゥーB
+・火ダメ軽減
+・継承候補
+・高難度適性</t>
+        </is>
+      </c>
+      <c r="H1298" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SjkzLQW_rkQ</t>
+        </is>
+      </c>
+      <c r="J1298" s="2" t="inlineStr">
+        <is>
+          <t>SjkzLQW_rkQ</t>
+        </is>
+      </c>
+      <c r="K1298" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1299" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1299" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Abyssal Circus第二弾ガチャ考察する配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D1299" s="2" t="inlineStr">
+        <is>
+          <t>第2弾ガチャ全6体を視聴者と考察する生配信。
+リズ(弓)が頭一つ抜けて引き推奨と結論。
+バートは前スタイル継承必須、単体では弱いと辛口評価。</t>
+        </is>
+      </c>
+      <c r="E1299" s="2" t="inlineStr">
+        <is>
+          <t>・リズは硬く火力もあり弓枠で頭抜けて優秀
+・ゼノンは証券で1年使える貴重な火力
+・原流はジョーより火力ロマンあり
+・こよみ討伐にリズが刺さる</t>
+        </is>
+      </c>
+      <c r="F1299" s="2" t="inlineStr">
+        <is>
+          <t>・ジョーは器用貧乏で焦って取る必要なし
+・バートは前スタイル継承ないと使い道なく単体では弱すぎ
+・新ドゥーはダメブロ1ターンで無人島も微妙
+・上編ガチャは目玉なくインパクト不足
+・アビサルサーカスの周回がきつすぎる</t>
+        </is>
+      </c>
+      <c r="G1299" s="2" t="inlineStr">
+        <is>
+          <t>・第2弾ガチャ考察
+・リズ弓推奨
+・ゼノン証券
+・バート継承必須
+・暦み討伐ギミック
+・武器バランス</t>
+        </is>
+      </c>
+      <c r="H1299" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kpBBiM6MaQ4</t>
+        </is>
+      </c>
+      <c r="J1299" s="2" t="inlineStr">
+        <is>
+          <t>kpBBiM6MaQ4</t>
+        </is>
+      </c>
+      <c r="K1299" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:13:02Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1299"/>
+  <dimension ref="A1:K1308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -85652,6 +85652,588 @@
         </is>
       </c>
     </row>
+    <row r="1300">
+      <c r="A1300" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1300" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1300" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「布石」限定ダーハオと魔女の娘のシナジー!?雷の新たな道を切り開くロマンシングパス配布→2026年9月　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1300" s="2" t="inlineStr">
+        <is>
+          <t>限定ダーハオの性能をロマンシングパス視点で検証
+エクストラOD雷1.5倍が軸だが発動条件が厳しい
+総合評価Cでパス購入は見送りと結論</t>
+        </is>
+      </c>
+      <c r="E1300" s="2" t="inlineStr">
+        <is>
+          <t>・メインウェポンのBP補填で味方全体が動きやすい
+・バトル開始時BP+10と最大BP+10が便利</t>
+        </is>
+      </c>
+      <c r="F1300" s="2" t="inlineStr">
+        <is>
+          <t>・個人性能は特徴がなく火力補正値もほぼ無し
+・継承しても効果が半分しか乗らない
+・雷編成・雷OD・BP補填の3条件同時成立はほぼ0
+・総合評価Cの古い性能でパスは買えないと判断</t>
+        </is>
+      </c>
+      <c r="G1300" s="2" t="inlineStr">
+        <is>
+          <t>・限定ダーハオ
+・ロマンシングパス
+・雷OD編成
+・BP補填
+・高難度評価C</t>
+        </is>
+      </c>
+      <c r="H1300" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-Ja7d96YcSc</t>
+        </is>
+      </c>
+      <c r="J1300" s="2" t="inlineStr">
+        <is>
+          <t>-Ja7d96YcSc</t>
+        </is>
+      </c>
+      <c r="K1300" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1301" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1301" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】井戸シグフレイ「あの術師」初の活躍!?ギミックおさらい速報で満額クリア目指せ　#ロマサガRS　2026年9月14日</t>
+        </is>
+      </c>
+      <c r="D1301" s="2" t="inlineStr">
+        <is>
+          <t>井戸シグフレイのギミックをおさらいし満額を狙う
+全体術で殴りシグフレイを同着で倒すのが要点
+エレノアと西王のデバフが刺さり満額達成</t>
+        </is>
+      </c>
+      <c r="E1301" s="2" t="inlineStr">
+        <is>
+          <t>・エレノアが非常に強く編成の主力
+・西王のデバフでシグフレイのEF攻撃をノーダメ化</t>
+        </is>
+      </c>
+      <c r="F1301" s="2" t="inlineStr">
+        <is>
+          <t>・シグフレイの無限エンハンスで長期戦は難易度高め
+・打突無効カウンターがあり打属性は持たせない方が良い</t>
+        </is>
+      </c>
+      <c r="G1301" s="2" t="inlineStr">
+        <is>
+          <t>・井戸シグフレイ
+・ギミック解説
+・満額クリア
+・貫通有効
+・同着撃破</t>
+        </is>
+      </c>
+      <c r="H1301" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C1PaB2a4_OQ</t>
+        </is>
+      </c>
+      <c r="J1301" s="2" t="inlineStr">
+        <is>
+          <t>C1PaB2a4_OQ</t>
+        </is>
+      </c>
+      <c r="K1301" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1302" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1302" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】どれ選ぶ？　織田有効箱　後悔する前に！</t>
+        </is>
+      </c>
+      <c r="D1302" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣3周年SSR有効箱の選択を解説
+鉄砲・足軽・弓の候補8体を性能比較
+筆者はタン波(鉄砲)と細川藤(足軽)を最有力に選定</t>
+        </is>
+      </c>
+      <c r="E1302" s="2" t="inlineStr">
+        <is>
+          <t>・タン波(鉄砲)は係数・兵数上昇で耐久強化に有効
+・細川藤孝は戦法ゲージ15%上げと軽減が優秀
+・森吉は寄唯一で覚醒5会心70%が強力
+・佐々成政は兵上昇で火力期待値が高い</t>
+        </is>
+      </c>
+      <c r="F1302" s="2" t="inlineStr">
+        <is>
+          <t>・佐々成政は覚醒機会が来ず現状取得が難しい
+・タン波(弓)は火力バフ要因として物足りない
+・戦力14万で停滞し耐久編成が課題</t>
+        </is>
+      </c>
+      <c r="G1302" s="2" t="inlineStr">
+        <is>
+          <t>・有効箱3周年
+・織田武将
+・鉄砲/足軽/弓
+・戦法ゲージ
+・兵数・係数</t>
+        </is>
+      </c>
+      <c r="H1302" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=84xzWEayPoE</t>
+        </is>
+      </c>
+      <c r="J1302" s="2" t="inlineStr">
+        <is>
+          <t>84xzWEayPoE</t>
+        </is>
+      </c>
+      <c r="K1302" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1303" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1303" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】これがRS現在の最強編成候補！陰斬＆＋１system★こよみも聖王もダメージ０！全部２ターンで消えてしまう。【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1303" s="2" t="inlineStr">
+        <is>
+          <t>現環境の螺旋向け最強編成候補を実戦で紹介
+暦読み・裁判・コテパン軸にバートランド継承を検証
+バートランドは編成適応力が高くSS評価</t>
+        </is>
+      </c>
+      <c r="E1303" s="2" t="inlineStr">
+        <is>
+          <t>・バートランドは編成適応力が高く総合SS評価
+・マギアコントラリア継承でアセルスのBP不足を補える
+・原流(げちゃん)がハマると1人600億級の火力
+・白バラ・T260と相性が良く火力が伸びる</t>
+        </is>
+      </c>
+      <c r="F1303" s="2" t="inlineStr">
+        <is>
+          <t>・バートランド入り編成は火力不足で2ターンに工夫が必要
+・アセルスはBPが少なく手数当たり火力が伸びにくい
+・敵の豪体持ちは低威力技が通らずダメージが出ない</t>
+        </is>
+      </c>
+      <c r="G1303" s="2" t="inlineStr">
+        <is>
+          <t>・最強編成候補
+・バートランド
+・暦読み・裁判・コテパン
+・マギアコントラリア
+・2ターンクリア</t>
+        </is>
+      </c>
+      <c r="H1303" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8sP90xGVDEE</t>
+        </is>
+      </c>
+      <c r="J1303" s="2" t="inlineStr">
+        <is>
+          <t>8sP90xGVDEE</t>
+        </is>
+      </c>
+      <c r="K1303" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1304" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1304" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】重要事項！ちゃんねるから今後のおしらせ【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1304" s="2" t="inlineStr">
+        <is>
+          <t>チャンネルの動画スケジュール変更と新企画を告知
+ガチャ終了前にリスナー参加型アンケートを実施
+集計結果とコメントを2日前に動画で発表</t>
+        </is>
+      </c>
+      <c r="E1304" s="2" t="inlineStr">
+        <is>
+          <t>・アンケート企画に93%が見たいと好反応
+・みんなの確保率が確保判断の参考になる</t>
+        </is>
+      </c>
+      <c r="F1304" s="2" t="inlineStr"/>
+      <c r="G1304" s="2" t="inlineStr">
+        <is>
+          <t>・新企画告知
+・参加型アンケート
+・ガチャ確保判断
+・スケジュール変更
+・雷バートガチャ</t>
+        </is>
+      </c>
+      <c r="H1304" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=E3NbVMsW1mg</t>
+        </is>
+      </c>
+      <c r="J1304" s="2" t="inlineStr">
+        <is>
+          <t>E3NbVMsW1mg</t>
+        </is>
+      </c>
+      <c r="K1304" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1305" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1305" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今かなり美味しい期間って気付いてる？この時期にやるべきことを徹底解説！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1305" s="2" t="inlineStr">
+        <is>
+          <t>今は育成が捗る美味しい期間と徹底解説
+アビサルサーカス周回でこよみ副防具と道場チケット確保が最優先
+武器の連携アビリティのひらめきも狙い目</t>
+        </is>
+      </c>
+      <c r="E1305" s="2" t="inlineStr">
+        <is>
+          <t>・イベクエEX4は1周で3回分の育成判定が美味しい
+・こよみ副防具は最大強化で1.5フォース＆ダメブロック
+・毎日500枚の道場チケットは貴重で必ず集めるべき
+・武器連携アビリティは弱い武器の底上げに有効</t>
+        </is>
+      </c>
+      <c r="F1305" s="2" t="inlineStr">
+        <is>
+          <t>・記憶再生の場所切り替えが面倒でチケット取り逃しに注意
+・道場チケットは苦戦武器以外に無駄使いしない方が良い</t>
+        </is>
+      </c>
+      <c r="G1305" s="2" t="inlineStr">
+        <is>
+          <t>・育成の好機
+・アビサルサーカス周回
+・こよみ副防具
+・道場チケット500枚
+・武器ソウルアビリティ</t>
+        </is>
+      </c>
+      <c r="H1305" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lVR-HERr7u0</t>
+        </is>
+      </c>
+      <c r="J1305" s="2" t="inlineStr">
+        <is>
+          <t>lVR-HERr7u0</t>
+        </is>
+      </c>
+      <c r="K1305" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1306" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1306" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】シグフレイ解体新書【シグフレイたちの井戸】【螺旋570階シグフレイ】のアビリティ・ギミックを解説‼️</t>
+        </is>
+      </c>
+      <c r="D1306" s="2" t="inlineStr">
+        <is>
+          <t>井戸シグフレイと螺旋570階の攻略を徹底解説
+弱点は斬＋熱(メイン)・陰(手下)、全体術と同着撃破が基本
+技をシグフレイに当てすぎると全滅リスク大</t>
+        </is>
+      </c>
+      <c r="E1306" s="2" t="inlineStr">
+        <is>
+          <t>・全体術＋斬熱要因で効率よく攻略できる
+・裁判のデバフを戦闘手下に入れ火力を伸ばせる</t>
+        </is>
+      </c>
+      <c r="F1306" s="2" t="inlineStr">
+        <is>
+          <t>・技100%カットの大義の鎧いで技攻撃が通らない
+・シグフレイへの技は術師の反攻で強化され全滅を招く
+・誰か倒れるとバフ全解除で同着撃破がシビア
+・井戸は螺旋570階よりさらに強くなる見込み</t>
+        </is>
+      </c>
+      <c r="G1306" s="2" t="inlineStr">
+        <is>
+          <t>・シグフレイ解体新書
+・螺旋570階
+・斬・熱・陰弱点
+・全体術編成
+・同着撃破ギミック</t>
+        </is>
+      </c>
+      <c r="H1306" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EQxgFZindUU</t>
+        </is>
+      </c>
+      <c r="J1306" s="2" t="inlineStr">
+        <is>
+          <t>EQxgFZindUU</t>
+        </is>
+      </c>
+      <c r="K1306" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1307" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1307" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】【難関‼️】ジュエルビーストの井戸〜100位編成を紹介〜</t>
+        </is>
+      </c>
+      <c r="D1307" s="2" t="inlineStr">
+        <is>
+          <t>ジュエルビーストの井戸100位編成を紹介
+ナレーションなしBGMのみの実戦映像
+字幕からは編成の詳細を読み取れず</t>
+        </is>
+      </c>
+      <c r="E1307" s="2" t="inlineStr"/>
+      <c r="F1307" s="2" t="inlineStr"/>
+      <c r="G1307" s="2" t="inlineStr">
+        <is>
+          <t>・ジュエルビーストの井戸
+・100位編成
+・実戦映像
+・BGMのみ</t>
+        </is>
+      </c>
+      <c r="H1307" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JzeoDZ98W1E</t>
+        </is>
+      </c>
+      <c r="J1307" s="2" t="inlineStr">
+        <is>
+          <t>JzeoDZ98W1E</t>
+        </is>
+      </c>
+      <c r="K1307" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1308" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1308" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】追憶の幻闘場「トゥ・クアイ」ギミック解説・攻略！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1308" s="2" t="inlineStr">
+        <is>
+          <t>9月実装の追憶の幻闘場トゥ・クアイを攻略解説
+体力・精神・腕力バフの解除が攻略の鍵
+ファストとディレイ2パターンの排除が厄介</t>
+        </is>
+      </c>
+      <c r="E1308" s="2" t="inlineStr">
+        <is>
+          <t>・バンピとアデルの解除役2人で両パターンに対応
+・能力解除さえできれば一定の武器士で攻略可能</t>
+        </is>
+      </c>
+      <c r="F1308" s="2" t="inlineStr">
+        <is>
+          <t>・ラウンド毎の体力・精神自己回復で火力が通りにくい
+・2ターン目の攻撃が痛く光の壁など対策が要る
+・武器士によっては初月クリアできない難易度</t>
+        </is>
+      </c>
+      <c r="G1308" s="2" t="inlineStr">
+        <is>
+          <t>・トゥ・クアイ
+・追憶の幻闘場
+・能力アップ解除
+・ファスト/ディレイ
+・武器種兼編成</t>
+        </is>
+      </c>
+      <c r="H1308" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zprP_YlEpcw</t>
+        </is>
+      </c>
+      <c r="J1308" s="2" t="inlineStr">
+        <is>
+          <t>zprP_YlEpcw</t>
+        </is>
+      </c>
+      <c r="K1308" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14T01:08:26Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1308"/>
+  <dimension ref="A1:K1316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -86234,6 +86234,523 @@
         </is>
       </c>
     </row>
+    <row r="1309">
+      <c r="A1309" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1309" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1309" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「鬼八を超える逸材」!?ゼノンと鬼八を徹底比較して現環境における手持ちアタッカーバランスを整えろ　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1309" s="2" t="inlineStr">
+        <is>
+          <t>ゼノンと気端(鬼八)のスタイル性能を徹底比較
+大枠ではゼノンが優位、防御と瞬発力で勝る
+手薄な突属性の穴を埋める便利枠でお得</t>
+        </is>
+      </c>
+      <c r="E1309" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノンは防御レジスト50%+回避37%で気端に大差
+・スタンバイ4ターン技の瞬発力が高い
+・活動限界12ターンで実用上十分
+・手薄な突属性の穴を埋められる
+・ガチャでバートランドも拾える良ガチャ</t>
+        </is>
+      </c>
+      <c r="F1309" s="2" t="inlineStr">
+        <is>
+          <t>・気端は不具合でため活動限界が延長中(想定外)
+・気端は防御レジスト50%のみで高難度に不利
+・防御ダウンはおまけ要素で差を感じにくい</t>
+        </is>
+      </c>
+      <c r="G1309" s="2" t="inlineStr">
+        <is>
+          <t>・ゼノンvs気端
+・スタイル性能比較
+・突属性
+・エクストラ倍率
+・バートランド</t>
+        </is>
+      </c>
+      <c r="H1309" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YmFCneEo_-8</t>
+        </is>
+      </c>
+      <c r="J1309" s="2" t="inlineStr">
+        <is>
+          <t>YmFCneEo_-8</t>
+        </is>
+      </c>
+      <c r="K1309" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15T01:32:44Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1310" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1310" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　もうい井戸ぉ〜！　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1310" s="2" t="inlineStr">
+        <is>
+          <t>井戸(幻闘場)の各ステージ攻略を試行錯誤する配信
+敵の体力精神バフ解除が鍵、OD使用は非推奨と判明
+デバフ・カウンター活用で剣や体術等をクリア</t>
+        </is>
+      </c>
+      <c r="E1310" s="2" t="inlineStr">
+        <is>
+          <t>・カウンターキャラが有効で立ち回りが安定
+・新速人回が調整しやすく使える</t>
+        </is>
+      </c>
+      <c r="F1310" s="2" t="inlineStr">
+        <is>
+          <t>・敵の体力精神が高く術・技が当たらない
+・オーバードライブが使いにくい仕様
+・解除やデバフキャラがいないと厳しい難易度</t>
+        </is>
+      </c>
+      <c r="G1310" s="2" t="inlineStr">
+        <is>
+          <t>・井戸攻略
+・配信
+・体力精神バフ解除
+・OD非推奨
+・デバフ活用</t>
+        </is>
+      </c>
+      <c r="H1310" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=idYAxF8O9dE</t>
+        </is>
+      </c>
+      <c r="J1310" s="2" t="inlineStr">
+        <is>
+          <t>idYAxF8O9dE</t>
+        </is>
+      </c>
+      <c r="K1310" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15T01:32:44Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B1311" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1311" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　新イベント更新！　Wガチャ　見て行こう！　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1311" s="2" t="inlineStr">
+        <is>
+          <t>新イベント更新とWガチャを回す雑談配信
+井戸が高難度で4ターン80万点が限界と苦戦
+Wガチャで原流・ゼノン確保、リズを狙いたい</t>
+        </is>
+      </c>
+      <c r="E1311" s="2" t="inlineStr">
+        <is>
+          <t>・原流を確保できて嬉しい
+・サイバー投入で火力が大きく伸びる</t>
+        </is>
+      </c>
+      <c r="F1311" s="2" t="inlineStr">
+        <is>
+          <t>・井戸が高難度で3ターンはジがいないと厳しい
+・技が当たらず火力が追いつかない
+・ルージュは火力が低め</t>
+        </is>
+      </c>
+      <c r="G1311" s="2" t="inlineStr">
+        <is>
+          <t>・新イベント
+・Wガチャ
+・井戸高難度
+・原流・ゼノン
+・ロマサガ3</t>
+        </is>
+      </c>
+      <c r="H1311" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tUF62nMoob8</t>
+        </is>
+      </c>
+      <c r="J1311" s="2" t="inlineStr">
+        <is>
+          <t>tUF62nMoob8</t>
+        </is>
+      </c>
+      <c r="K1311" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15T01:32:44Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1312" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1312" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　新イベント更新！徹底調査！　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1312" s="2" t="inlineStr">
+        <is>
+          <t>新イベント更新内容を徹底調査する雑談配信
+新ガチャ(ポルカ編・リズ編)や魂の正域道場を確認
+63連ガチャ無料2回とインペリアルサガ男女無料配布が目玉</t>
+        </is>
+      </c>
+      <c r="E1312" s="2" t="inlineStr">
+        <is>
+          <t>・63連ガチャが無料2回できるのが大きい
+・インペリアルサガのリベル男女が無料配布
+・サルーインが強力で確保して良かった
+・妖精は幻闘場要因として良い</t>
+        </is>
+      </c>
+      <c r="F1312" s="2" t="inlineStr">
+        <is>
+          <t>・今回のガチャキャラは弱め・普通と感じる
+・アビリティ説明が長く読む気がしない
+・魂ピース集めが課金前提できつい</t>
+        </is>
+      </c>
+      <c r="G1312" s="2" t="inlineStr">
+        <is>
+          <t>・新イベント調査
+・新ガチャ
+・魂の正域道場
+・63連ガチャ
+・22周年ジュエル</t>
+        </is>
+      </c>
+      <c r="H1312" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wQprLHleGvU</t>
+        </is>
+      </c>
+      <c r="J1312" s="2" t="inlineStr">
+        <is>
+          <t>wQprLHleGvU</t>
+        </is>
+      </c>
+      <c r="K1312" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15T01:33:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1313" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1313" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】やはり次はロマサガ3リメイクガチャがくる！？9月16日の新ガチャを徹底予想【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1313" s="2" t="inlineStr">
+        <is>
+          <t>三蔵による9月16日新ガチャ内容の徹底予想
+デス発売決定ガチャではなくストーリー内実装と予想
+ミカエル等ロマサガ3主人公6人の登場を予想</t>
+        </is>
+      </c>
+      <c r="E1313" s="2" t="inlineStr"/>
+      <c r="F1313" s="2" t="inlineStr">
+        <is>
+          <t>・ミカエルは17ヶ月未実装で待たされすぎと指摘</t>
+        </is>
+      </c>
+      <c r="G1313" s="2" t="inlineStr">
+        <is>
+          <t>・新ガチャ予想
+・ロマサガ3リメイク
+・旧発生
+・9月16日
+・主人公6人</t>
+        </is>
+      </c>
+      <c r="H1313" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=S-qX1VFgYcQ</t>
+        </is>
+      </c>
+      <c r="J1313" s="2" t="inlineStr">
+        <is>
+          <t>S-qX1VFgYcQ</t>
+        </is>
+      </c>
+      <c r="K1313" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15T01:32:44Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1314" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1314" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】シグフレイたちの井戸：⭐️超難関~100位編成⭐️</t>
+        </is>
+      </c>
+      <c r="D1314" s="2" t="inlineStr">
+        <is>
+          <t>第137回シグフレイたちの井戸100位以内編成紹介
+サイバ等5名の4ターン85手ノーダメージ編成
+術継承変更で55位・27位まで狙える</t>
+        </is>
+      </c>
+      <c r="E1314" s="2" t="inlineStr">
+        <is>
+          <t>・マイターンODが安定して打てる好編成
+・ポルカのダメブロでノーダメ立ち回り可能
+・術継承変更で順位を大きく伸ばせる</t>
+        </is>
+      </c>
+      <c r="F1314" s="2" t="inlineStr">
+        <is>
+          <t>・3ターン目のロベ打ちの呪でターミンの属性が無効化される</t>
+        </is>
+      </c>
+      <c r="G1314" s="2" t="inlineStr">
+        <is>
+          <t>・シグフレイの井戸
+・100位編成
+・ノーダメージ
+・マイターンOD
+・4ターン85手</t>
+        </is>
+      </c>
+      <c r="H1314" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lVbS71YuMsI</t>
+        </is>
+      </c>
+      <c r="J1314" s="2" t="inlineStr">
+        <is>
+          <t>lVbS71YuMsI</t>
+        </is>
+      </c>
+      <c r="K1314" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15T01:32:44Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1315" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1315" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【ガチャ動画】玄ちゃんを待ちきれなくて【No.638】</t>
+        </is>
+      </c>
+      <c r="D1315" s="2" t="inlineStr">
+        <is>
+          <t>玄ちゃん(ダブルガチャ分裂)狙いのガチャ実況
+待ち切れず事前30連、さらに単発10連を追加
+結局すり抜けリズのみで玄ちゃん確保できず</t>
+        </is>
+      </c>
+      <c r="E1315" s="2" t="inlineStr"/>
+      <c r="F1315" s="2" t="inlineStr">
+        <is>
+          <t>・9000ジュエルしかなく天井まで届かない
+・回しても玄ちゃんが出ずすり抜けリズのみ</t>
+        </is>
+      </c>
+      <c r="G1315" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ実況
+・玄ちゃん
+・ダブルガチャ
+・単発10連
+・すり抜け</t>
+        </is>
+      </c>
+      <c r="H1315" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I1315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kpfoNSnVPnc</t>
+        </is>
+      </c>
+      <c r="J1315" s="2" t="inlineStr">
+        <is>
+          <t>kpfoNSnVPnc</t>
+        </is>
+      </c>
+      <c r="K1315" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15T01:32:44Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1316" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1316" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】要注意!!意外と取ってない人いるかも!?9月16日の12時まで!!ついでに[闘者の関門-シュウザー-]の最速更新!!【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1316" s="2" t="inlineStr">
+        <is>
+          <t>見落としがちな上限突破ミッションを注意喚起
+9月16日12時まで、実行で3000ジュエル獲得
+闘者の関門シューザーをジョーで最速8秒に更新</t>
+        </is>
+      </c>
+      <c r="E1316" s="2" t="inlineStr">
+        <is>
+          <t>・ジョーはフランベソルベプラス継承で最速8秒を実現
+・追撃順を固定しない方が速い</t>
+        </is>
+      </c>
+      <c r="F1316" s="2" t="inlineStr">
+        <is>
+          <t>・上限突破ミッションは見落としジュエル未受取になりがち</t>
+        </is>
+      </c>
+      <c r="G1316" s="2" t="inlineStr">
+        <is>
+          <t>・ミッション注意
+・3000ジュエル
+・闘者の関門シューザー
+・最速更新
+・ジョー</t>
+        </is>
+      </c>
+      <c r="H1316" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=90WY84P-dtA</t>
+        </is>
+      </c>
+      <c r="J1316" s="2" t="inlineStr">
+        <is>
+          <t>90WY84P-dtA</t>
+        </is>
+      </c>
+      <c r="K1316" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15T01:32:44Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1316"/>
+  <dimension ref="A1:K1326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -86751,6 +86751,653 @@
         </is>
       </c>
     </row>
+    <row r="1317">
+      <c r="A1317" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1317" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1317" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「やっぱりな…」ロマサガ3予想完全終了で当面デスサガ関連は来ないことが確定!?最新お知らせ読んでいこー!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1317" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガ3関連は11月発売日記念まで来ないと確定。
+ミンストレル第1弾で来週はホーク・フバーラのダブルガチャ。
+ストーリー全編後編は16/25/30日、鍛錬は日曜開始。</t>
+        </is>
+      </c>
+      <c r="E1317" s="2" t="inlineStr">
+        <is>
+          <t>・前回いまいちを受けやたら強いミルザはあるかも
+・記念日に千ジュエル配布</t>
+        </is>
+      </c>
+      <c r="F1317" s="2" t="inlineStr">
+        <is>
+          <t>・シングルガチャは性能いまいちのケースが多い
+・前回のミルザはいまいちだった
+・連達は少なめ</t>
+        </is>
+      </c>
+      <c r="G1317" s="2" t="inlineStr">
+        <is>
+          <t>・ロマサガ3予想終了
+・ミンストレル第1弾
+・ストーリー配信日程
+・ダブルガチャ予告
+・記念日ジュエル</t>
+        </is>
+      </c>
+      <c r="H1317" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YzVj6aOB8sI</t>
+        </is>
+      </c>
+      <c r="J1317" s="2" t="inlineStr">
+        <is>
+          <t>YzVj6aOB8sI</t>
+        </is>
+      </c>
+      <c r="K1317" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T01:08:10Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1318" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1318" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】第137回：シグフレイたちの井戸　満額報酬　強敵どう倒す？</t>
+        </is>
+      </c>
+      <c r="D1318" s="2" t="inlineStr">
+        <is>
+          <t>シグフレイ井戸の満額報酬(約82万)クリア編成を紹介。
+バルテルミ・サイバー・ルージュ・ターミン・白バラで4ターン。
+技被弾で敵強化、撃破で能力解除される厄介な仕様。</t>
+        </is>
+      </c>
+      <c r="E1318" s="2" t="inlineStr">
+        <is>
+          <t>・バルテルミがいると火力がかなり出る
+・サイバーを入れると火力が伸びる</t>
+        </is>
+      </c>
+      <c r="F1318" s="2" t="inlineStr">
+        <is>
+          <t>・シグフレイがめちゃくちゃ強い
+・敵撃破で能力解除され火力が下がるのが厄介
+・最上位は無理な参考編成
+・使えるキャラがかなり絞られ厳しい</t>
+        </is>
+      </c>
+      <c r="G1318" s="2" t="inlineStr">
+        <is>
+          <t>・シグフレイ井戸
+・満額報酬80万
+・クリア編成
+・オーバードライブ
+・能力解除ギミック</t>
+        </is>
+      </c>
+      <c r="H1318" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=e_rPPVidQaU</t>
+        </is>
+      </c>
+      <c r="J1318" s="2" t="inlineStr">
+        <is>
+          <t>e_rPPVidQaU</t>
+        </is>
+      </c>
+      <c r="K1318" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T01:08:10Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1319" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1319" s="2" t="inlineStr">
+        <is>
+          <t>【GジェネET】限定無し！9月17日ガシャ予告 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D1319" s="2" t="inlineStr">
+        <is>
+          <t>9月17日ガシャ予告を確認、内容は限定なし。
+アバランチアストレアF(耐久型)とスノ(攻撃型)が恒常追加。
+1.5周年直前のためスルー・様子見が無難。</t>
+        </is>
+      </c>
+      <c r="E1319" s="2" t="inlineStr"/>
+      <c r="F1319" s="2" t="inlineStr">
+        <is>
+          <t>・限定なしなので基本スルー推奨
+・1.5周年直前で様子見の方がいい</t>
+        </is>
+      </c>
+      <c r="G1319" s="2" t="inlineStr">
+        <is>
+          <t>・9/17ガシャ予告
+・限定なし
+・耐久型/攻撃型
+・1.5周年前
+・スルー推奨</t>
+        </is>
+      </c>
+      <c r="H1319" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LSM-4nwwEpk</t>
+        </is>
+      </c>
+      <c r="J1319" s="2" t="inlineStr">
+        <is>
+          <t>LSM-4nwwEpk</t>
+        </is>
+      </c>
+      <c r="K1319" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T01:08:10Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1320" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1320" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ミルザのイラスト凄くね？9月16日更新情報まとめ【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1320" s="2" t="inlineStr">
+        <is>
+          <t>9/16更新のミンストレルノイズ全編と新ガチャを紹介。
+アルベルト編でミルザが剣の通常スタイルで新登場、絵が豪華。
+シングルで回しやすく、HP目安5450・3000ジュエル配布。</t>
+        </is>
+      </c>
+      <c r="E1320" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザのイラストが豪華で高級感が半端ない
+・シングルガチャで回しやすい
+・ミルザと斧の愛紗が欲しい
+・3000ジュエル配布</t>
+        </is>
+      </c>
+      <c r="F1320" s="2" t="inlineStr">
+        <is>
+          <t>・シングルガチャは性能が怖そうと不安</t>
+        </is>
+      </c>
+      <c r="G1320" s="2" t="inlineStr">
+        <is>
+          <t>・ミンストレルノイズ全編
+・ミルザ新スタイル
+・イラスト豪華
+・シングルガチャ
+・復刻最終皇帝女</t>
+        </is>
+      </c>
+      <c r="H1320" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OIqbSCFrWPQ</t>
+        </is>
+      </c>
+      <c r="J1320" s="2" t="inlineStr">
+        <is>
+          <t>OIqbSCFrWPQ</t>
+        </is>
+      </c>
+      <c r="K1320" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T01:08:10Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1321" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1321" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SR 強化型ZZガンダム 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1321" s="2" t="inlineStr">
+        <is>
+          <t>SR強化型ZZガンダムの武装アニメを見せるShorts。
+戦闘ボイスのみで解説はなし。
+Gジェネエターナルの武装演出紹介。</t>
+        </is>
+      </c>
+      <c r="E1321" s="2" t="inlineStr"/>
+      <c r="F1321" s="2" t="inlineStr"/>
+      <c r="G1321" s="2" t="inlineStr">
+        <is>
+          <t>・強化型ZZガンダム
+・武装アニメ
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H1321" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=juutS41HcyU</t>
+        </is>
+      </c>
+      <c r="J1321" s="2" t="inlineStr">
+        <is>
+          <t>juutS41HcyU</t>
+        </is>
+      </c>
+      <c r="K1321" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T01:08:10Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1322" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1322" s="2" t="inlineStr">
+        <is>
+          <t>【GジェネET】限定無し！9月17日ガシャ予告 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1322" s="2" t="inlineStr">
+        <is>
+          <t>9月17日ガシャ予告の限定なしをShortsで確認。
+アバランチアストレアF(耐久型)とスノ(攻撃型)が恒常追加。
+1.5周年前でスルー・様子見が無難。</t>
+        </is>
+      </c>
+      <c r="E1322" s="2" t="inlineStr"/>
+      <c r="F1322" s="2" t="inlineStr">
+        <is>
+          <t>・限定なしなので基本スルー推奨
+・1.5周年直前で様子見の方がいい</t>
+        </is>
+      </c>
+      <c r="G1322" s="2" t="inlineStr">
+        <is>
+          <t>・9/17ガシャ予告
+・限定なし
+・耐久型/攻撃型
+・スルー推奨</t>
+        </is>
+      </c>
+      <c r="H1322" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vND-erG0uzs</t>
+        </is>
+      </c>
+      <c r="J1322" s="2" t="inlineStr">
+        <is>
+          <t>vND-erG0uzs</t>
+        </is>
+      </c>
+      <c r="K1322" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T01:08:10Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1323" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1323" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】どういうことだってばよ、、公式最新情報確認【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1323" s="2" t="inlineStr">
+        <is>
+          <t>ミンストレルノイズ第1弾の不穏なバナーを考察。
+アルベルトの剣が闇色で闇落ち直前、愛紗が中立に見える。
+復刻は最終皇帝女編、愛紗の斧やアイスの使い道を語る。</t>
+        </is>
+      </c>
+      <c r="E1323" s="2" t="inlineStr">
+        <is>
+          <t>・愛紗は斧で幻闘場で使える
+・アイスはギミック対応でまだ使える
+・ビューネは無人島で使える</t>
+        </is>
+      </c>
+      <c r="F1323" s="2" t="inlineStr">
+        <is>
+          <t>・アルベルトが闇落ちしそうで心配
+・アイスは豪体増加で火力が落ち片落ち気味
+・バナーが禍々しくどちらが悪役か分かりづらい</t>
+        </is>
+      </c>
+      <c r="G1323" s="2" t="inlineStr">
+        <is>
+          <t>・ミンストレルノイズ全編
+・アルベルト闇落ち考察
+・ストーリー考察
+・復刻最終皇帝女
+・愛紗の斧</t>
+        </is>
+      </c>
+      <c r="H1323" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MoXX_wkWtkg</t>
+        </is>
+      </c>
+      <c r="J1323" s="2" t="inlineStr">
+        <is>
+          <t>MoXX_wkWtkg</t>
+        </is>
+      </c>
+      <c r="K1323" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T01:08:10Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1324" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1324" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】棍棒、体術、銃を攻略！追憶の幻闘場トゥ・クアイレベル5クリア編成を紹介！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1324" s="2" t="inlineStr">
+        <is>
+          <t>追憶の幻闘場トゥ・クアイLv5を打属性で攻略。
+棍棒コンボ・体術・銃の3種を能力アップ解除軸で挑戦。
+おたま・ヒューズ・ビンセントの高火力が光る。</t>
+        </is>
+      </c>
+      <c r="E1324" s="2" t="inlineStr">
+        <is>
+          <t>・おたまが攻撃されるほど追撃を稼ぎ強すぎる
+・体術は超絶簡単でサイバーが強い
+・ヒューズのリーサルトリガプラスがえぐい
+・ビンセントや裁判が壊れ性能</t>
+        </is>
+      </c>
+      <c r="F1324" s="2" t="inlineStr">
+        <is>
+          <t>・棍棒コンボが一番難しい
+・全体スタンやナギ払いが厄介でリタイア発生
+・おたまがいないとかなり厳しい
+・銃は手持ち次第で厳しい</t>
+        </is>
+      </c>
+      <c r="G1324" s="2" t="inlineStr">
+        <is>
+          <t>・追憶の幻闘場
+・トゥ・クアイLv5
+・打属性攻略
+・おたま強い
+・ヒューズ・ビンセント
+・能力アップ解除</t>
+        </is>
+      </c>
+      <c r="H1324" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=__NkD7Ng3oA</t>
+        </is>
+      </c>
+      <c r="J1324" s="2" t="inlineStr">
+        <is>
+          <t>__NkD7Ng3oA</t>
+        </is>
+      </c>
+      <c r="K1324" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T01:08:10Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1325" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1325" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】重大な告知あり！衝撃的なガチャが実装されたのでさっそくお知らせを確認【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1325" s="2" t="inlineStr">
+        <is>
+          <t>9/16実装の主役はまさかのアルベルトと衝撃告知。
+声優浦田さんの誕生日と重なり同日20時に記念ライブ配信。
+シングルガチャ・復刻最終皇帝女、予想は歴代最低の的中率。</t>
+        </is>
+      </c>
+      <c r="E1325" s="2" t="inlineStr">
+        <is>
+          <t>・アルベルト実装と声優誕生日が重なり大盛り上がり
+・3000ジュエルのログボが嬉しい
+・エサガ記念で1000ジュエル配布
+・シングルで比較的優しいガチャ</t>
+        </is>
+      </c>
+      <c r="F1325" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ予想が歴代最低クラスの的中率
+・シングルだが性能が怖そう
+・24日18時更新の意図が謎</t>
+        </is>
+      </c>
+      <c r="G1325" s="2" t="inlineStr">
+        <is>
+          <t>・アルベルト実装
+・浦田さん誕生日ライブ
+・ノイズ第1弾
+・シングルガチャ
+・予想大外れ
+・螺旋回廊600層</t>
+        </is>
+      </c>
+      <c r="H1325" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=c11UG22Kx7o</t>
+        </is>
+      </c>
+      <c r="J1325" s="2" t="inlineStr">
+        <is>
+          <t>c11UG22Kx7o</t>
+        </is>
+      </c>
+      <c r="K1325" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T01:08:10Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1326" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1326" s="2" t="inlineStr">
+        <is>
+          <t>ちゃむのYouTube生配信（ガチャ&amp;シグフレイ井戸配信）~TOP10を狙う！(◎_◎;)</t>
+        </is>
+      </c>
+      <c r="D1326" s="2" t="inlineStr">
+        <is>
+          <t>ガチャ生配信でジを狙い、天井コンプまで到達。
+フランベソルベ+連達で全体クワトロ化しシグフレイ井戸に刺さる。
+井戸TOP10狙いは3ターンできずBP・防具調整が課題。</t>
+        </is>
+      </c>
+      <c r="E1326" s="2" t="inlineStr">
+        <is>
+          <t>・ジがシグフレイ井戸に刺さり活躍
+・フランベソルベ+の連達で全体6連化
+・最後の新龍で天井コンプできた
+・ジは継承技も恵まれ集会でも使える</t>
+        </is>
+      </c>
+      <c r="F1326" s="2" t="inlineStr">
+        <is>
+          <t>・3ターンクリアできずBP不足で失敗
+・初見で防具の微調整が必要
+・かぶりが多かった
+・術師を揃えるのが難しい</t>
+        </is>
+      </c>
+      <c r="G1326" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ生配信
+・ジ狙い
+・フランベソルベ+
+・シグフレイ井戸TOP10
+・天井コンプ
+・術師編成</t>
+        </is>
+      </c>
+      <c r="H1326" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9JcuboEohO8</t>
+        </is>
+      </c>
+      <c r="J1326" s="2" t="inlineStr">
+        <is>
+          <t>9JcuboEohO8</t>
+        </is>
+      </c>
+      <c r="K1326" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16T01:08:10Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1326"/>
+  <dimension ref="A1:K1338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -87398,6 +87398,816 @@
         </is>
       </c>
     </row>
+    <row r="1327">
+      <c r="A1327" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1327" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1327" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「再考&amp;絶対待機」週間ランキング!!ジョー&amp;バートランドVSミルザ→15体5ガチャランキング!!最新スタイルの最強を決める比較検討会→2026年9月17日版　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1327" s="2" t="inlineStr">
+        <is>
+          <t>ミルザ追加で斬陽の比較検討ランキングを更新した回。
+バートランド・ゼノン・ミルザが上位で王族/斬陽が主軸。
+主人公狙いなら弓強化含め月末まで絶対待機を推奨。</t>
+        </is>
+      </c>
+      <c r="E1327" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザはエクストラ2倍が強力で1位評価
+・バートランドは環境最上位編成をさらに強化
+・ゼノンは汎用性が高く無人島・制圧線で優秀
+・アルベルトはバランス良い中堅アタッカー
+・原流は属性内の強さが抜きん出る</t>
+        </is>
+      </c>
+      <c r="F1327" s="2" t="inlineStr">
+        <is>
+          <t>・マドレーン・イーブリンは使用可能性ほぼ0
+・ポルカは熱縛り編成しか組めず弱い
+・要属性はミルザ引いてもアルベルト不要なほど格差
+・今は回すガチャが少ない</t>
+        </is>
+      </c>
+      <c r="G1327" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザ追加
+・週間ランキング
+・斬陽アタッカー
+・ガチャ引き方
+・螺旋回廊</t>
+        </is>
+      </c>
+      <c r="H1327" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EfheElr0eec</t>
+        </is>
+      </c>
+      <c r="J1327" s="2" t="inlineStr">
+        <is>
+          <t>EfheElr0eec</t>
+        </is>
+      </c>
+      <c r="K1327" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T01:12:32.456517+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1328" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1328" s="2" t="inlineStr">
+        <is>
+          <t>【幻想水滸伝　スターリープ】　普遍の間46F　無課金5体編成で挑む！選ぶのはこの助っ人！　【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1328" s="2" t="inlineStr">
+        <is>
+          <t>幻想水滸伝スターリープ普遍の間46Fに無課金5体で挑戦。
+敵の瀕死回復と2段階バフが厄介で水弱点を突いて攻略。
+借りた助っ人「上位」とスケットを駆使しクリア成功。</t>
+        </is>
+      </c>
+      <c r="E1328" s="2" t="inlineStr">
+        <is>
+          <t>・借りた助っ人「上位」がめちゃくちゃ強い
+・スケットがフル覚醒で頼れる
+・1体ずつ倒せば怖くない安定攻略
+・新ガチャキャラは非常に強い</t>
+        </is>
+      </c>
+      <c r="F1328" s="2" t="inlineStr">
+        <is>
+          <t>・敵の瀕死回復と2段階バフが厄介
+・自軍の装備が不足しギリギリの戦い
+・横(サポート)キャラが手薄で不足</t>
+        </is>
+      </c>
+      <c r="G1328" s="2" t="inlineStr">
+        <is>
+          <t>・普遍の間46F
+・無課金5体編成
+・水弱点
+・助っ人上位
+・スケット活用</t>
+        </is>
+      </c>
+      <c r="H1328" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=oPUtVjseSgU</t>
+        </is>
+      </c>
+      <c r="J1328" s="2" t="inlineStr">
+        <is>
+          <t>oPUtVjseSgU</t>
+        </is>
+      </c>
+      <c r="K1328" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T01:12:32.456517+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1329" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1329" s="2" t="inlineStr">
+        <is>
+          <t>【GジェネET】ガンダムとの戦いを！ スサノオの性能確認 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1329" s="2" t="inlineStr">
+        <is>
+          <t>GジェネETのスサノオのEX性能を確認する動画。
+対ガンダム特化で防御力減少を重ね大ダメージを狙える。
+射程は短くチャンスステップ+1もない対ガンダム型。</t>
+        </is>
+      </c>
+      <c r="E1329" s="2" t="inlineStr">
+        <is>
+          <t>・対ガンダムなら防御減少で大ダメージが出せる
+・ミスター武士のアビは特別機体不要で発動
+・テンション条件が比較的発動させやすい</t>
+        </is>
+      </c>
+      <c r="F1329" s="2" t="inlineStr">
+        <is>
+          <t>・EX武装が射程1-3と短い
+・倒しきれないとテンション低下に注意
+・チャンスステップ+1がなく1回のみ
+・対ガンダム以外の用途が乏しい</t>
+        </is>
+      </c>
+      <c r="G1329" s="2" t="inlineStr">
+        <is>
+          <t>・スサノオ
+・対ガンダム特化
+・EX武装
+・射程短め
+・ミスター武士</t>
+        </is>
+      </c>
+      <c r="H1329" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3dDQVsxo2mQ</t>
+        </is>
+      </c>
+      <c r="J1329" s="2" t="inlineStr">
+        <is>
+          <t>3dDQVsxo2mQ</t>
+        </is>
+      </c>
+      <c r="K1329" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T01:12:32.456517+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1330" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1330" s="2" t="inlineStr">
+        <is>
+          <t>【GジェネET】攻撃性能高めな耐久型  アヴァランチアストレアの性能確認 ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1330" s="2" t="inlineStr">
+        <is>
+          <t>アヴァランチアストレア(耐久型・向上)の性能を確認。
+攻撃時に自己バフがかかる新しい耐久型の方向性。
+射程短め・支援防御1回のみで無理に追う必要なし。</t>
+        </is>
+      </c>
+      <c r="E1330" s="2" t="inlineStr">
+        <is>
+          <t>・攻撃力25%減少と物理パワー減少を持つ
+・自分から攻撃するとバフがかかる新方向性
+・相手の反撃にも支援防御が可能</t>
+        </is>
+      </c>
+      <c r="F1330" s="2" t="inlineStr">
+        <is>
+          <t>・射程が全体的に短い
+・支援防御が1回しかできない
+・向上ユニットなので無理に追う必要はない</t>
+        </is>
+      </c>
+      <c r="G1330" s="2" t="inlineStr">
+        <is>
+          <t>・アヴァランチアストレア
+・耐久型
+・自己攻撃バフ
+・射程短め
+・フォンスパーク</t>
+        </is>
+      </c>
+      <c r="H1330" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D50bxf99vrU</t>
+        </is>
+      </c>
+      <c r="J1330" s="2" t="inlineStr">
+        <is>
+          <t>D50bxf99vrU</t>
+        </is>
+      </c>
+      <c r="K1330" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T01:12:32.456517+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1331" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1331" s="2" t="inlineStr">
+        <is>
+          <t>【GジェネET】アヴァランチアストレア＆スサノオの性能確認 『SDガンダムGジェネレーションエターナル』</t>
+        </is>
+      </c>
+      <c r="D1331" s="2" t="inlineStr">
+        <is>
+          <t>明日実装のアストレアとスサノオの性能を確認する動画。
+耐久型は自己攻撃バフ、スサノオは対ガンダム特化。
+1.5周年直前で今回のガチャは無理に回さなくてよい。</t>
+        </is>
+      </c>
+      <c r="E1331" s="2" t="inlineStr">
+        <is>
+          <t>・スサノオは対ガンダムで大ダメージ
+・アストレアは攻撃デバフと自己バフを持つ
+・WO系で固めるとサポーターがそこそこ強い</t>
+        </is>
+      </c>
+      <c r="F1331" s="2" t="inlineStr">
+        <is>
+          <t>・両機とも射程が短い
+・支援防御・チャンスステップが1回のみ
+・サポーターはスキルがエネルギー回復で微妙
+・1.5周年直前で今回のガチャは見送り推奨</t>
+        </is>
+      </c>
+      <c r="G1331" s="2" t="inlineStr">
+        <is>
+          <t>・アヴァランチアストレア
+・スサノオ
+・対ガンダム
+・向上ユニット
+・ガチャ見送り</t>
+        </is>
+      </c>
+      <c r="H1331" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=W1svLjs68us</t>
+        </is>
+      </c>
+      <c r="J1331" s="2" t="inlineStr">
+        <is>
+          <t>W1svLjs68us</t>
+        </is>
+      </c>
+      <c r="K1331" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T01:12:32.456517+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1332" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1332" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】とりま有償ガチャ『ロマンシング・サガ ミンストレル・ノイズ公開記念 Romancing祭 アルベルト編』【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1332" s="2" t="inlineStr">
+        <is>
+          <t>ロマンシング祭アルベルト編を有償ガチャ中心に実践。
+愛紗・ミルザ・アルベルト狙いでステップを回す。
+有償ガチャだけで狙い3体が揃う神引きに成功。</t>
+        </is>
+      </c>
+      <c r="E1332" s="2" t="inlineStr">
+        <is>
+          <t>・有償ガチャだけで狙いの3体が揃い神引き
+・愛紗は能力アップ解除で幻統上に刺さる
+・無償ジュエルを温存でき次に余裕</t>
+        </is>
+      </c>
+      <c r="F1332" s="2" t="inlineStr">
+        <is>
+          <t>・確定枠以外のすり抜けが微妙続き
+・ムクチャーが最後まで出なかった</t>
+        </is>
+      </c>
+      <c r="G1332" s="2" t="inlineStr">
+        <is>
+          <t>・ロマンシング祭
+・有償ガチャ
+・アルベルト
+・ミルザ
+・愛紗</t>
+        </is>
+      </c>
+      <c r="H1332" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=j7xC7-FeONM</t>
+        </is>
+      </c>
+      <c r="J1332" s="2" t="inlineStr">
+        <is>
+          <t>j7xC7-FeONM</t>
+        </is>
+      </c>
+      <c r="K1332" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T01:12:32.456517+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1333" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1333" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】引く！！絶対に欲しい陽ガチャ！！決死のアルベルト編を回す【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1333" s="2" t="inlineStr">
+        <is>
+          <t>陽ガチャ「決死のアルベルト編」を配信で回す。
+最優先はミルザでAJ似の優秀な性能と高評価。
+91連でアルベルト・愛紗は出たがミルザだけ出ず。</t>
+        </is>
+      </c>
+      <c r="E1333" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザは4コード以下バフ+王族2倍で優秀
+・久々の分かりやすい当たりキャラ
+・愛紗のクリアアックスはバフ消しで刺さる</t>
+        </is>
+      </c>
+      <c r="F1333" s="2" t="inlineStr">
+        <is>
+          <t>・91連でミルザだけ出ない渋い引き
+・クロス爆発しないとSSも来ないジンクス
+・石が少なく天井狙いがきつい
+・運営の提供がひどいと不満</t>
+        </is>
+      </c>
+      <c r="G1333" s="2" t="inlineStr">
+        <is>
+          <t>・決死のアルベルト編
+・ミルザ最優先
+・ガチャ配信
+・王族2倍
+・天井狙い</t>
+        </is>
+      </c>
+      <c r="H1333" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KEmQ34EGtQs</t>
+        </is>
+      </c>
+      <c r="J1333" s="2" t="inlineStr">
+        <is>
+          <t>KEmQ34EGtQs</t>
+        </is>
+      </c>
+      <c r="K1333" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T01:12:32.456517+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1334" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1334" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】ミルザ能力値早見表‼️最強斬陽パーティ完成‼️最強の斬陽パーティラインナップ紹介</t>
+        </is>
+      </c>
+      <c r="D1334" s="2" t="inlineStr">
+        <is>
+          <t>ミルザの能力値早見表と最強斬陽パーティを紹介。
+アウェイファクターを4回に抑えるのが運用の肝。
+要属性エクストラ2倍と全体OD満タンが強力。</t>
+        </is>
+      </c>
+      <c r="E1334" s="2" t="inlineStr">
+        <is>
+          <t>・要属性エクストラフォース常時2倍が強い
+・全員マイターンOD満タンが強力
+・体力精神デバフ90%も付与
+・アルベルト・ビクトール等と組み最強斬陽時代</t>
+        </is>
+      </c>
+      <c r="F1334" s="2" t="inlineStr">
+        <is>
+          <t>・5回攻撃キャラを入れると効果が発動しない
+・条件に合う4行動要属性アタッカーが少ない</t>
+        </is>
+      </c>
+      <c r="G1334" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザ能力値
+・斬陽パーティ
+・アウェイファクター
+・エクストラ2倍
+・4行動キャラ</t>
+        </is>
+      </c>
+      <c r="H1334" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=l4h1DE2KUaM</t>
+        </is>
+      </c>
+      <c r="J1334" s="2" t="inlineStr">
+        <is>
+          <t>l4h1DE2KUaM</t>
+        </is>
+      </c>
+      <c r="K1334" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T01:12:32.456517+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1335" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1335" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】アルベルト能力値早見表【2T毎なら…身を削って…闘います】斬陽アタッカーね異端王子‼️</t>
+        </is>
+      </c>
+      <c r="D1335" s="2" t="inlineStr">
+        <is>
+          <t>アルベルトの能力値早見表を短期戦想定で解説。
+2ターンごとにトータル50ヒットの爆発火力。
+自己バフと敵デバフで味方の火力貢献も高い。</t>
+        </is>
+      </c>
+      <c r="E1335" s="2" t="inlineStr">
+        <is>
+          <t>・技2で追撃込み50ヒットの爆発火力
+・攻撃ごとにバフ蓄積で凄まじい威力
+・エクストラフォース1.5倍で味方貢献
+・体力精神デバフ525%も強力</t>
+        </is>
+      </c>
+      <c r="F1335" s="2" t="inlineStr">
+        <is>
+          <t>・2ターンに1回しか打てない
+・技発動時に45%の代償ダメージを受ける
+・BPが2ほど足りない</t>
+        </is>
+      </c>
+      <c r="G1335" s="2" t="inlineStr">
+        <is>
+          <t>・アルベルト能力値
+・短期戦運用
+・50ヒット
+・エクストラフォース
+・味方火力貢献</t>
+        </is>
+      </c>
+      <c r="H1335" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mGcW_K2h8J8</t>
+        </is>
+      </c>
+      <c r="J1335" s="2" t="inlineStr">
+        <is>
+          <t>mGcW_K2h8J8</t>
+        </is>
+      </c>
+      <c r="K1335" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T01:12:32.456517+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1336" s="2" t="inlineStr">
+        <is>
+          <t>くんちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1336" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】【ガチャ動画】手が勝手に引いちゃうときあるよね【No.639】</t>
+        </is>
+      </c>
+      <c r="D1336" s="2" t="inlineStr">
+        <is>
+          <t>勢いで追加10連を回す家族実況のガチャ動画。
+子どもとお菓子屋さんごっこを交え和やかに進行。
+ちょい足しの10連で狙いのキャラを引き当てる。</t>
+        </is>
+      </c>
+      <c r="E1336" s="2" t="inlineStr">
+        <is>
+          <t>・ちょい足しの10連で狙いキャラが出た
+・家族で楽しむ和やかな雰囲気</t>
+        </is>
+      </c>
+      <c r="F1336" s="2" t="inlineStr">
+        <is>
+          <t>・別のガチャは30連引いても何も出なかった</t>
+        </is>
+      </c>
+      <c r="G1336" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャ動画
+・追加10連
+・家族実況
+・ちょい足し
+・お菓子屋さんごっこ</t>
+        </is>
+      </c>
+      <c r="H1336" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, ガチャ</t>
+        </is>
+      </c>
+      <c r="I1336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mDO48cIS8js</t>
+        </is>
+      </c>
+      <c r="J1336" s="2" t="inlineStr">
+        <is>
+          <t>mDO48cIS8js</t>
+        </is>
+      </c>
+      <c r="K1336" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T01:12:32.456517+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1337" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1337" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ロマンシング・サガ ミンストレル・ノイズ公開記念ガチャ考察する配信【生配信】</t>
+        </is>
+      </c>
+      <c r="D1337" s="2" t="inlineStr">
+        <is>
+          <t>ミンストレル・ノイズ公開記念ガチャを事前考察する配信。
+ミルザ・アルベルトは強力、愛紗はシフ待ちで判断推奨。
+多数回すも大爆死でアルベルトとミルザのみ確保。</t>
+        </is>
+      </c>
+      <c r="E1337" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザは要属性を2倍にでき尖った強さ
+・アルベルトは高火力で評価を上げてよい
+・ミルザは置き物・レイド適性も高く腐りにくい
+・愛紗は幻統上で使え外れがないガチャ</t>
+        </is>
+      </c>
+      <c r="F1337" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザは4回以下・要属性でないと火力が出ず将来性に不安
+・愛紗は総合力が低く現場特攻のみ
+・ガチャは大爆死でアルベルトばかり被る
+・ログイン不具合等の運営対応に不満</t>
+        </is>
+      </c>
+      <c r="G1337" s="2" t="inlineStr">
+        <is>
+          <t>・ミンストレルノイズ
+・ガチャ考察
+・ミルザ評価
+・アルベルト評価
+・愛紗はシフ待ち</t>
+        </is>
+      </c>
+      <c r="H1337" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=V5aPNqIfVnQ</t>
+        </is>
+      </c>
+      <c r="J1337" s="2" t="inlineStr">
+        <is>
+          <t>V5aPNqIfVnQ</t>
+        </is>
+      </c>
+      <c r="K1337" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T01:12:32.456517+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1338" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1338" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今やるべき事を間違えるな!!新イベント解説【ロマンシング サガ リ・ユニバース】</t>
+        </is>
+      </c>
+      <c r="D1338" s="2" t="inlineStr">
+        <is>
+          <t>ミンストレル・ノイズ前編の新イベントを解説。
+ボックスガチャ周回で必要素材とチケットを回収。
+焦って周回不要、魂ひらめきは連磨の遺跡を推奨。</t>
+        </is>
+      </c>
+      <c r="E1338" s="2" t="inlineStr">
+        <is>
+          <t>・配布副防具は開幕OD満タンで星4強化推奨
+・2倍ドロップ中の連磨の遺跡がおすすめ
+・20日に螺旋回廊の追加給料が来る</t>
+        </is>
+      </c>
+      <c r="F1338" s="2" t="inlineStr">
+        <is>
+          <t>・今回のイベントは焦って周回する意味がほぼない
+・2ラウンドで判定回数ボーナスもない
+・レリックアクセ目的での周回価値は低い</t>
+        </is>
+      </c>
+      <c r="G1338" s="2" t="inlineStr">
+        <is>
+          <t>・新イベント解説
+・ボックスガチャ
+・記憶再戦
+・魂のひらめき
+・配布副防具</t>
+        </is>
+      </c>
+      <c r="H1338" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wnbm6_-4Tsc</t>
+        </is>
+      </c>
+      <c r="J1338" s="2" t="inlineStr">
+        <is>
+          <t>wnbm6_-4Tsc</t>
+        </is>
+      </c>
+      <c r="K1338" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T01:12:32.456517+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1338"/>
+  <dimension ref="A1:K1347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -88208,6 +88208,613 @@
         </is>
       </c>
     </row>
+    <row r="1339">
+      <c r="A1339" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1339" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1339" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ミルザ取説「最強お供」お供七選!!継承含めた性能深掘り&amp;絶対的主戦場は〇〇〇!!アルベルトとのシナジー有用性を熟考！5行動以上陽は不要!?　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1339" s="2" t="inlineStr">
+        <is>
+          <t>ミルザの性能を継承・主戦場まで深掘り解説
+レフティフォーク継承の3.75倍火力が本命
+ビクトール・アルベルトがベストパートナー</t>
+        </is>
+      </c>
+      <c r="E1339" s="2" t="inlineStr">
+        <is>
+          <t>・レフティフォーク継承で3.75倍火力は強い
+・棒立ち75%防御などAJに無い耐久面が有用
+・4行動以下全体エクストラ2倍が強力
+・ビクトールとのシナジーが最上位クラス
+・OD満タ維持の瞬発力ある戦い方が強い</t>
+        </is>
+      </c>
+      <c r="F1339" s="2" t="inlineStr">
+        <is>
+          <t>・銀行山継承は防御上げが微妙で基本不要
+・個人火力バフは控えめでダメージ伸びない
+・光属性用スタイルは編成が発展途上で腐る可能性</t>
+        </is>
+      </c>
+      <c r="G1339" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザ性能
+・レフティフォーク継承
+・制圧戦
+・ビクトール
+・アルベルト
+・光属性編成</t>
+        </is>
+      </c>
+      <c r="H1339" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8D7UIOna8xM</t>
+        </is>
+      </c>
+      <c r="J1339" s="2" t="inlineStr">
+        <is>
+          <t>8D7UIOna8xM</t>
+        </is>
+      </c>
+      <c r="K1339" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:05:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1340" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1340" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】プレイ開始350日目記録　良弟 　今回の主役は補佐武将！</t>
+        </is>
+      </c>
+      <c r="D1340" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣プレイ350日目の現状報告
+柴田勝家が大活躍しSSRは10体に増加
+全国制圧率5.4%と各イベント成果を報告</t>
+        </is>
+      </c>
+      <c r="E1340" s="2" t="inlineStr">
+        <is>
+          <t>・柴田勝家のタオ特性がめちゃくちゃ強い
+・浅井など徳川系の回復キャラが貴重で戦力
+・長野の戦い4177位で目標をクリア</t>
+        </is>
+      </c>
+      <c r="F1340" s="2" t="inlineStr">
+        <is>
+          <t>・SSR10体で育成が大変になってきた
+・宮城の制圧率0.4%が取れるか心配
+・名当タがまだ400で武器不足</t>
+        </is>
+      </c>
+      <c r="G1340" s="2" t="inlineStr">
+        <is>
+          <t>・信長の野望出陣
+・350日記録
+・柴田勝家
+・制圧率
+・イベント成果
+・3周年</t>
+        </is>
+      </c>
+      <c r="H1340" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y-avoYP2UrQ</t>
+        </is>
+      </c>
+      <c r="J1340" s="2" t="inlineStr">
+        <is>
+          <t>y-avoYP2UrQ</t>
+        </is>
+      </c>
+      <c r="K1340" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:05:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1341" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1341" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネエターナル】SSR ガンダムアストレア タイプF2 武装アニメ ＃Shorts ＃ジージェネエターナル</t>
+        </is>
+      </c>
+      <c r="D1341" s="2" t="inlineStr">
+        <is>
+          <t>ガンダムアストレアF2の武装アニメ紹介Shorts
+SSRユニットの武器演出を見せる短尺映像
+実況コメントなしの映像クリップ</t>
+        </is>
+      </c>
+      <c r="E1341" s="2" t="inlineStr"/>
+      <c r="F1341" s="2" t="inlineStr"/>
+      <c r="G1341" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・アストレアF2
+・武装アニメ
+・SSR
+・Shorts</t>
+        </is>
+      </c>
+      <c r="H1341" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bsDxE5el-G4</t>
+        </is>
+      </c>
+      <c r="J1341" s="2" t="inlineStr">
+        <is>
+          <t>bsDxE5el-G4</t>
+        </is>
+      </c>
+      <c r="K1341" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:05:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1342" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1342" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】今話題沸騰のミルザ検定！（4回行動以下）Tier表にて合格者を発表する【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1342" s="2" t="inlineStr">
+        <is>
+          <t>ミルザ検定(4回行動以下)合格者をTier表で発表
+火力は1人出せれば十分で光属性偏重は不要
+ビクトール・ゼノン・アルベルトが特に優秀</t>
+        </is>
+      </c>
+      <c r="E1342" s="2" t="inlineStr">
+        <is>
+          <t>・ビクトールは継続火力優秀でアルベルト級
+・ゼノンは1回行動で確実に刺さる
+・アルベルトは50ヒットで300億出せる
+・光属性に偏らせず強スタイルで十分</t>
+        </is>
+      </c>
+      <c r="F1342" s="2" t="inlineStr">
+        <is>
+          <t>・光属性に絞ると回復が足りなくなる
+・レオンはインフレに飲まれ厳しい
+・5回行動キャラは検定不合格で使えない</t>
+        </is>
+      </c>
+      <c r="G1342" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザ検定
+・4回行動
+・Tier表
+・ビクトール
+・ゼノン
+・光属性編成</t>
+        </is>
+      </c>
+      <c r="H1342" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3nPJhOMH0CA</t>
+        </is>
+      </c>
+      <c r="J1342" s="2" t="inlineStr">
+        <is>
+          <t>3nPJhOMH0CA</t>
+        </is>
+      </c>
+      <c r="K1342" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:05:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1343" s="2" t="inlineStr">
+        <is>
+          <t>もんでる</t>
+        </is>
+      </c>
+      <c r="C1343" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ロマンシング・サガ ミンストレル・ノイズ公開記念ガチャ🎪</t>
+        </is>
+      </c>
+      <c r="D1343" s="2" t="inlineStr">
+        <is>
+          <t>記念ガチャを引きながらキャラ性能を実況
+アルベルトは2ター1回残用の爆火力で優秀
+愛紗は幻級上特化、ミルザは英雄の構え継承推奨</t>
+        </is>
+      </c>
+      <c r="E1343" s="2" t="inlineStr">
+        <is>
+          <t>・アルベルトの火力がやばいと高評価
+・愛紗は幻級上でかなり強い
+・ミルザ置き物には英雄の構え継承が良い
+・イベント1ヶ月延長は良い対応</t>
+        </is>
+      </c>
+      <c r="F1343" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザの技3は術で超弱い
+・500チケット終了しチケット延長なしが残念
+・魂アビは無価値なものが多すぎる
+・ガチャ単発ですり抜けて悔しい</t>
+        </is>
+      </c>
+      <c r="G1343" s="2" t="inlineStr">
+        <is>
+          <t>・記念ガチャ
+・アルベルト
+・ミルザ
+・愛紗
+・英雄の構え継承
+・500チケット終了</t>
+        </is>
+      </c>
+      <c r="H1343" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, 攻略実況</t>
+        </is>
+      </c>
+      <c r="I1343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iWiKy6_6x8Q</t>
+        </is>
+      </c>
+      <c r="J1343" s="2" t="inlineStr">
+        <is>
+          <t>iWiKy6_6x8Q</t>
+        </is>
+      </c>
+      <c r="K1343" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:05:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1344" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1344" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】知らないと大きく差が付く重大要素！今本当に周回すべき場所を教えます！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1344" s="2" t="inlineStr">
+        <is>
+          <t>アビサル延長で周回先を間違えるなと警鐘
+今は連マの遺跡2倍(10/1まで)が最優先
+暦み副防具未完成の人だけアビサルを回るべき</t>
+        </is>
+      </c>
+      <c r="E1344" s="2" t="inlineStr">
+        <is>
+          <t>・連マ遺跡2倍は貴重で今の最優先
+・アビサル延長は神楽ズ未完成者には神展開
+・ボックスガチャは半日で終わる手軽さ</t>
+        </is>
+      </c>
+      <c r="F1344" s="2" t="inlineStr">
+        <is>
+          <t>・アビサル延長で周回先を間違える人が多い
+・連マ2倍キャンペーンはめったに来ない
+・武器連マ素材はパス課金でも足りない
+・ミンストレルノイズは周回旨みが薄い</t>
+        </is>
+      </c>
+      <c r="G1344" s="2" t="inlineStr">
+        <is>
+          <t>・周回優先度
+・アビサルサーカス延長
+・連マ遺跡2倍
+・暦み副防具
+・ミンストレルノイズ
+・11秒周回</t>
+        </is>
+      </c>
+      <c r="H1344" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0BQ730AcBOo</t>
+        </is>
+      </c>
+      <c r="J1344" s="2" t="inlineStr">
+        <is>
+          <t>0BQ730AcBOo</t>
+        </is>
+      </c>
+      <c r="K1344" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:05:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1345" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1345" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】アルベルトガチャ性能チェック！全3体のキャラランク評価＆徹底解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1345" s="2" t="inlineStr">
+        <is>
+          <t>アルベルト・ミルザ・愛紗3体の性能とランク付け
+アルベルトは2ター周期の残用高火力アタッカー
+ミルザが当たり候補で要編成のインフラ級</t>
+        </is>
+      </c>
+      <c r="E1345" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザが1番の当たり候補で要編成のインフラ
+・アルベルトは追撃だけでSSS35ヒットの火力
+・愛紗は幻級上突破に嬉しい特攻性能
+・ミルザの避弾HP回復付与はユニークな性能</t>
+        </is>
+      </c>
+      <c r="F1345" s="2" t="inlineStr">
+        <is>
+          <t>・アルベルトは術運用時に火力落ちるのが懸念
+・アルベルトは火力以外目立たず初動星2評価
+・愛紗は主戦場が幻級上に限られ星2評価</t>
+        </is>
+      </c>
+      <c r="G1345" s="2" t="inlineStr">
+        <is>
+          <t>・アルベルト
+・ミルザ
+・愛紗
+・キャラランク
+・残用火力
+・幻級上特攻</t>
+        </is>
+      </c>
+      <c r="H1345" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uSN7fFugCvc</t>
+        </is>
+      </c>
+      <c r="J1345" s="2" t="inlineStr">
+        <is>
+          <t>uSN7fFugCvc</t>
+        </is>
+      </c>
+      <c r="K1345" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:05:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1346" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1346" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】Romancing祭「アルベルト 編」スタイル考察＆性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1346" s="2" t="inlineStr">
+        <is>
+          <t>アルベルト・ミルザ・愛紗の性能考察とランク付け
+アルベルトは2ター周期50ヒットの残用高火力
+ミルザは要属性火力底上げ役でA-評価</t>
+        </is>
+      </c>
+      <c r="E1346" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザは要属性2倍+OD満タが破格でA-
+・ミルザの避弾HP極小回復はヒーラー機能
+・アルベルトは2ター毎50ヒットの高火力でB+
+・愛紗はトークアイのバフ解除に有効</t>
+        </is>
+      </c>
+      <c r="F1346" s="2" t="inlineStr">
+        <is>
+          <t>・アルベルトは技のBP17が重くBP枯渇しやすい
+・アルベルトは技50ヒットで自身45%代償ダメ
+・ミルザは5回行動アタッカーと噛み合わない
+・愛紗は火軽減67%で物足りない</t>
+        </is>
+      </c>
+      <c r="G1346" s="2" t="inlineStr">
+        <is>
+          <t>・アルベルト
+・ミルザ
+・愛紗
+・BP問題
+・幻級上特攻
+・ランク付け</t>
+        </is>
+      </c>
+      <c r="H1346" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yv2qpWA6scQ</t>
+        </is>
+      </c>
+      <c r="J1346" s="2" t="inlineStr">
+        <is>
+          <t>yv2qpWA6scQ</t>
+        </is>
+      </c>
+      <c r="K1346" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:05:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1347" s="2" t="inlineStr">
+        <is>
+          <t>RS 周回チャンネル</t>
+        </is>
+      </c>
+      <c r="C1347" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】え？期間延長!?神対応!!これは優先順位が変わって来ます!!詳しく解説します【ロマンシング サガ リ・ユニバース】【新イベント】【周回編成】</t>
+        </is>
+      </c>
+      <c r="D1347" s="2" t="inlineStr">
+        <is>
+          <t>不具合対応でイベント・ガチャの期間が延長
+アビサルサーカスが10/24まで延長は神対応
+暦みの副防具の最大進化が最優先</t>
+        </is>
+      </c>
+      <c r="E1347" s="2" t="inlineStr">
+        <is>
+          <t>・アビサルサーカス1ヶ月超延長は神対応
+・暦み副防具はEF50%付与など非常に強力
+・副防具進化は2〜3日で終わる手軽さ
+・連マ遺跡ドロップ2倍も来ている</t>
+        </is>
+      </c>
+      <c r="F1347" s="2" t="inlineStr">
+        <is>
+          <t>・魂のひらめき道場チケットは延長されず残念</t>
+        </is>
+      </c>
+      <c r="G1347" s="2" t="inlineStr">
+        <is>
+          <t>・期間延長
+・アビサルサーカス
+・暦み副防具
+・記憶再戦
+・優先順位
+・連マ遺跡2倍</t>
+        </is>
+      </c>
+      <c r="H1347" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 周回, レイド編成</t>
+        </is>
+      </c>
+      <c r="I1347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LzS5l3FFvrs</t>
+        </is>
+      </c>
+      <c r="J1347" s="2" t="inlineStr">
+        <is>
+          <t>LzS5l3FFvrs</t>
+        </is>
+      </c>
+      <c r="K1347" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:05:39Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1347"/>
+  <dimension ref="A1:K1355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -88815,6 +88815,546 @@
         </is>
       </c>
     </row>
+    <row r="1348">
+      <c r="A1348" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1348" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1348" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】◯行動させる!?「有力」新A.J.型ミルザ速報!!エクストラ数値も強化され陽全てを引き上げる　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1348" s="2" t="inlineStr">
+        <is>
+          <t>新ミルザは火力2.75倍、FT4継承一択
+4行動以内で味方に用エクストラ2倍付与
+属性SS/総合A、用環境の主役級</t>
+        </is>
+      </c>
+      <c r="E1348" s="2" t="inlineStr">
+        <is>
+          <t>・火力補正2.75倍でサブアタッカー優秀
+・用エクストラ2倍はAJより数値が高い
+・防御75%と安定し回復ばらまきも有用
+・ビクトール・ゼノンと好相性で用環境主役</t>
+        </is>
+      </c>
+      <c r="F1348" s="2" t="inlineStr">
+        <is>
+          <t>・用縛り・4行動以内の制約がきつい
+・恩恵パートナーがビクトール・ゼノン程度
+・リアム等は行動調整で恩恵が外れいまいち</t>
+        </is>
+      </c>
+      <c r="G1348" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザ性能
+・4行動以内縛り
+・用エクストラ2倍
+・FT4継承
+・高難度評価</t>
+        </is>
+      </c>
+      <c r="H1348" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tOqtV6FYghs</t>
+        </is>
+      </c>
+      <c r="J1348" s="2" t="inlineStr">
+        <is>
+          <t>tOqtV6FYghs</t>
+        </is>
+      </c>
+      <c r="K1348" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T01:07:34Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1349" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1349" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】3体ランキング!!「超鉄壁」なのに50連打するアルベルトがさらにエクストラフォースまで&amp;33連サブアタッカーアイシャの新たな力　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1349" s="2" t="inlineStr">
+        <is>
+          <t>アイシャはマスコット寄り、クリアアックスが便利で総合B
+アルベルトは超鉄壁アタッカー、汎用S/総合A
+ミルザだけ確保し即撤退推奨</t>
+        </is>
+      </c>
+      <c r="E1349" s="2" t="inlineStr">
+        <is>
+          <t>・アルベルトは防御96%超鉄壁で汎用S
+・アイシャのクリアアックスがバフ管理に便利
+・アルベルトはミルザと相性抜群</t>
+        </is>
+      </c>
+      <c r="F1349" s="2" t="inlineStr">
+        <is>
+          <t>・アイシャはマスコット性能で火力補正いまいち
+・アルベルトは英雄の構えの面倒さと代償ダメが難点
+・ミルザ以外は必然性なく確保不要</t>
+        </is>
+      </c>
+      <c r="G1349" s="2" t="inlineStr">
+        <is>
+          <t>・アイシャ性能
+・アルベルト性能
+・クリアアックス
+・超鉄壁防御
+・確保優先度</t>
+        </is>
+      </c>
+      <c r="H1349" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ud_mgm4JI7U</t>
+        </is>
+      </c>
+      <c r="J1349" s="2" t="inlineStr">
+        <is>
+          <t>ud_mgm4JI7U</t>
+        </is>
+      </c>
+      <c r="K1349" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T01:07:34Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1350" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1350" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】まさか「ここ」も眼中に!?「周回乱立」最適解の育成&amp;周回とは→記憶再戦/自動再戦のあらゆるパターンを網羅しそこじゃないと気付けるお手伝い!!　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1350" s="2" t="inlineStr">
+        <is>
+          <t>記憶再戦は祠周回で武器の魂アビ取得が最優先
+連魔遺跡2倍はスルー、連魔は必須でなくなった
+魂アビだけ限定性、他はいつでも良い</t>
+        </is>
+      </c>
+      <c r="E1350" s="2" t="inlineStr">
+        <is>
+          <t>・祠の魂アビは今後の高難度・追で大きな助け
+・育成判定ボーナス3回は今しかない好機
+・パス購入なら連魔は必要時に作ればよい</t>
+        </is>
+      </c>
+      <c r="F1350" s="2" t="inlineStr">
+        <is>
+          <t>・連魔遺跡2倍はしょぼいドロップでスルー推奨
+・瀕死や数百%・HP満タの差はほぼ誤差
+・育成上限周回は暇な時で足り不急</t>
+        </is>
+      </c>
+      <c r="G1350" s="2" t="inlineStr">
+        <is>
+          <t>・記憶再戦
+・自動再戦
+・魂アビ
+・連魔遺跡2倍
+・技ランク上げ道場</t>
+        </is>
+      </c>
+      <c r="H1350" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wJ2bjrL1P6g</t>
+        </is>
+      </c>
+      <c r="J1350" s="2" t="inlineStr">
+        <is>
+          <t>wJ2bjrL1P6g</t>
+        </is>
+      </c>
+      <c r="K1350" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T01:07:34Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1351" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1351" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】久々の引き得ガチャきたる★７大ガチャランキング引きべく優先順位考察【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1351" s="2" t="inlineStr">
+        <is>
+          <t>★7ガチャ7個到来、優先順位をランキングで考察
+無人島特攻のリズが一番人気、ブラウニーも高評価
+63年ガチャや不人気枠は完全スルー推奨</t>
+        </is>
+      </c>
+      <c r="E1351" s="2" t="inlineStr">
+        <is>
+          <t>・リズは無人島に刺さり一番人気
+・ブラウニーは槍幻統SSの壊れ性能
+・ボルカは全体90%台の耐久で最強の壁
+・アイスは弓の最急手で優秀</t>
+        </is>
+      </c>
+      <c r="F1351" s="2" t="inlineStr">
+        <is>
+          <t>・63年ガチャは新キャラ優位で引かない方がいい
+・バルドは優先度低く8割弱がスルー
+・マドレーンは80%が完全スルー
+・リズも火力は微妙でサポーター寄り</t>
+        </is>
+      </c>
+      <c r="G1351" s="2" t="inlineStr">
+        <is>
+          <t>・★7ガチャ7個
+・ガチャ優先順位
+・リズ無人島特攻
+・ブラウニー槍SS
+・視聴者アンケート</t>
+        </is>
+      </c>
+      <c r="H1351" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Is83nEf8Lac</t>
+        </is>
+      </c>
+      <c r="J1351" s="2" t="inlineStr">
+        <is>
+          <t>Is83nEf8Lac</t>
+        </is>
+      </c>
+      <c r="K1351" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T01:07:34Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1352" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1352" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】陽リーダー＆斬陽超アタッカー登場！アルベルト編解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1352" s="2" t="inlineStr">
+        <is>
+          <t>アルベルトは斬陽超アタッカー、技で150億級の火力
+ミルザはAJ逆パターン、用特化で汎用性は低め
+ミルザとアルベルトは一緒に使う設計</t>
+        </is>
+      </c>
+      <c r="E1352" s="2" t="inlineStr">
+        <is>
+          <t>・アルベルトは50ヒットで150億級の超火力
+・ミルザとアルベルトの相性が抜群
+・アイシャはボルカ・通に特攻できる</t>
+        </is>
+      </c>
+      <c r="F1352" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザは用毒性だけで汎用性は高くない
+・アルベルトの2キャスト弱い時はあまり強くない
+・アイシャはクリア済みなら不要</t>
+        </is>
+      </c>
+      <c r="G1352" s="2" t="inlineStr">
+        <is>
+          <t>・アルベルト超火力
+・ミルザAJ逆
+・アイシャ幻統特攻
+・ガチャ優先
+・陽属性編成</t>
+        </is>
+      </c>
+      <c r="H1352" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zkWG0OzCzNg</t>
+        </is>
+      </c>
+      <c r="J1352" s="2" t="inlineStr">
+        <is>
+          <t>zkWG0OzCzNg</t>
+        </is>
+      </c>
+      <c r="K1352" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T01:07:34Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1353" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1353" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】緊急動画！昨日の動画でサンゾーまさかの怒られる？【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1353" s="2" t="inlineStr">
+        <is>
+          <t>前回の連魔遺跡推しに視聴者から多数の指摘
+進化素材の存在を伝え忘れたと謝罪
+結論は好きなものを回せ、自身は連魔重視</t>
+        </is>
+      </c>
+      <c r="E1353" s="2" t="inlineStr">
+        <is>
+          <t>・連魔素材2倍は年1回級の激レア機会
+・追加された追の武器が看板武器級に強い
+・連魔強化で戦力が跳ね上がる
+・熱量あるコメントに感謝</t>
+        </is>
+      </c>
+      <c r="F1353" s="2" t="inlineStr">
+        <is>
+          <t>・進化素材を前回伝え忘れたのは自分のミス
+・ソウルピース・連魔素材は課金差がつき安売りされない
+・進化強化は属性体制だけで急ぐ必要はない</t>
+        </is>
+      </c>
+      <c r="G1353" s="2" t="inlineStr">
+        <is>
+          <t>・連魔の遺跡2倍
+・進化素材
+・ミンサガノイズ
+・ソウルピース
+・追の現状武器</t>
+        </is>
+      </c>
+      <c r="H1353" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6oNZfLMcbTg</t>
+        </is>
+      </c>
+      <c r="J1353" s="2" t="inlineStr">
+        <is>
+          <t>6oNZfLMcbTg</t>
+        </is>
+      </c>
+      <c r="K1353" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T01:07:34Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1354" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1354" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】実は隠れた大当たりキャラが存在！アルベルト編ガチャ性能チェック【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1354" s="2" t="inlineStr">
+        <is>
+          <t>新ガチャ3体の性能をチェック
+一番の当たりはミルザ、用属性編成の必須級
+アルベルトは50ヒットの斬用超アタッカー</t>
+        </is>
+      </c>
+      <c r="E1354" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザは用属性編成の必須級で高難度適性も高い
+・アルベルトは50ヒットで火ダメ軽減87.5%と硬い
+・アイシャのクリアアックスは斧未所持者の救済</t>
+        </is>
+      </c>
+      <c r="F1354" s="2" t="inlineStr">
+        <is>
+          <t>・アイシャは斧サポーターで西王持ちには不要気味
+・アルベルトはシャイニングスラッシュで最大HP45%消費
+・初行線中を使うと火力が出ない</t>
+        </is>
+      </c>
+      <c r="G1354" s="2" t="inlineStr">
+        <is>
+          <t>・アイシャ斬熱斧
+・ミルザ性能
+・アルベルト超アタッカー
+・クリアアックス
+・用属性編成</t>
+        </is>
+      </c>
+      <c r="H1354" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kEomJ_SxJ9A</t>
+        </is>
+      </c>
+      <c r="J1354" s="2" t="inlineStr">
+        <is>
+          <t>kEomJ_SxJ9A</t>
+        </is>
+      </c>
+      <c r="K1354" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T01:07:34Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1355" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1355" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】ミルザと相性のよい5回未満・4回以下の攻撃回数を持つ陽スタイルを一挙紹介！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1355" s="2" t="inlineStr">
+        <is>
+          <t>ミルザは4回以下攻撃の陽スタイルの最終ダメージ2倍
+対象スタイルを一挙紹介
+アルベルト・ゼノン・ビクトールと組ませるのが熱い</t>
+        </is>
+      </c>
+      <c r="E1355" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザは対象スタイルの最終ダメージを2倍にする爆発力
+・アルベルト・ビクトール・ゼノンとの相性が特に熱い
+・ジーンは限定でなく誰でも取得でき貴重</t>
+        </is>
+      </c>
+      <c r="F1355" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザの恩恵は付与条件に癖があり4回以内制限がきつい
+・リアムは5ターンに1度5回攻撃で恩恵外れ対象外
+・アーニャン・ゼノンは武器縛りで相性いまいちな面</t>
+        </is>
+      </c>
+      <c r="G1355" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザ相性
+・4回以下攻撃
+・陽スタイル紹介
+・最終ダメージ2倍
+・おすすめ編成</t>
+        </is>
+      </c>
+      <c r="H1355" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CctKfCkl6wM</t>
+        </is>
+      </c>
+      <c r="J1355" s="2" t="inlineStr">
+        <is>
+          <t>CctKfCkl6wM</t>
+        </is>
+      </c>
+      <c r="K1355" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T01:07:34Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/video_log.xlsx
+++ b/video_log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1355"/>
+  <dimension ref="A1:K1369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -89355,6 +89355,935 @@
         </is>
       </c>
     </row>
+    <row r="1356">
+      <c r="A1356" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1356" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1356" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】「注意」順番に周回場所こなしましょう→防具の強化素材お忘れなく　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1356" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRSの周回攻略ショート動画
+周回は決められた順番でこなすべきと注意喚起
+防具の強化素材の取り忘れに気をつけて</t>
+        </is>
+      </c>
+      <c r="E1356" s="2" t="inlineStr"/>
+      <c r="F1356" s="2" t="inlineStr">
+        <is>
+          <t>・周回の順番を間違えると非効率になる
+・防具強化素材を取り忘れやすい</t>
+        </is>
+      </c>
+      <c r="G1356" s="2" t="inlineStr">
+        <is>
+          <t>・周回順序
+・防具強化素材
+・注意喚起
+・ショート動画</t>
+        </is>
+      </c>
+      <c r="H1356" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IB3v3hAUHv4</t>
+        </is>
+      </c>
+      <c r="J1356" s="2" t="inlineStr">
+        <is>
+          <t>IB3v3hAUHv4</t>
+        </is>
+      </c>
+      <c r="K1356" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:08:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1357" s="2" t="inlineStr">
+        <is>
+          <t>タマゴローRS</t>
+        </is>
+      </c>
+      <c r="C1357" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋600階「最新陽無し」ミルザ&amp;アルベルト不要!!アディリスのギミック解明速報!!完全陽属性無し編成も解説　#ロマサガRS</t>
+        </is>
+      </c>
+      <c r="D1357" s="2" t="inlineStr">
+        <is>
+          <t>螺旋600階アディリスのギミックを速報解説
+属性多段ヒット約50発で偶数ターンのデスコンボを封殺
+陽属性なしは回避カウンター編成で対応可能</t>
+        </is>
+      </c>
+      <c r="E1357" s="2" t="inlineStr">
+        <is>
+          <t>・ウィクトール&amp;リアムのペアで問題なく対応できる
+・属性最低限2体＋強キャラ混成で攻略可能</t>
+        </is>
+      </c>
+      <c r="F1357" s="2" t="inlineStr">
+        <is>
+          <t>・頭痛技を打ちすぎると大ダメージを受ける
+・HPが0になっても半分回復し厄介
+・陽属性なし編成だと難易度が高い</t>
+        </is>
+      </c>
+      <c r="G1357" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋600階
+・アディリス
+・ギミック解明
+・属性多段ヒット
+・陽属性なし編成</t>
+        </is>
+      </c>
+      <c r="H1357" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, レイド, ガチャ, 速報</t>
+        </is>
+      </c>
+      <c r="I1357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=g-jMZ_w1DOA</t>
+        </is>
+      </c>
+      <c r="J1357" s="2" t="inlineStr">
+        <is>
+          <t>g-jMZ_w1DOA</t>
+        </is>
+      </c>
+      <c r="K1357" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:08:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1358" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1358" s="2" t="inlineStr">
+        <is>
+          <t>【信長の野望出陣】どれ選ぶ？　列伝報酬３周年友好箱　後悔する前に！</t>
+        </is>
+      </c>
+      <c r="D1358" s="2" t="inlineStr">
+        <is>
+          <t>信長の野望出陣・3周年友好箱の交換キャラを解説
+900/850/800部将を1体ずつ性能評価
+斎藤・北条・武田信玄など気少価値の高いキャラを紹介</t>
+        </is>
+      </c>
+      <c r="E1358" s="2" t="inlineStr">
+        <is>
+          <t>・斎藤俊光は気少価値が高く候補
+・北条は武将を固めると連携率が上がり強い
+・武田信玄は覚醒後火ダメ軽減60%で強力
+・池田常は速度低下軽減が大きい</t>
+        </is>
+      </c>
+      <c r="F1358" s="2" t="inlineStr">
+        <is>
+          <t>・本多忠勝は攻撃間隔が長く評価しづらい
+・どれも一長一短で交換に悩む</t>
+        </is>
+      </c>
+      <c r="G1358" s="2" t="inlineStr">
+        <is>
+          <t>・信長の野望出陣
+・3周年友好箱
+・列伝報酬
+・中交換キャラ選び
+・部将評価</t>
+        </is>
+      </c>
+      <c r="H1358" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=c0PNJ-BEdy0</t>
+        </is>
+      </c>
+      <c r="J1358" s="2" t="inlineStr">
+        <is>
+          <t>c0PNJ-BEdy0</t>
+        </is>
+      </c>
+      <c r="K1358" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:08:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1359" s="2" t="inlineStr">
+        <is>
+          <t>あんずもん</t>
+        </is>
+      </c>
+      <c r="C1359" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】　井戸やっていこう！　Interesting games from Japan【初見さん大歓迎】</t>
+        </is>
+      </c>
+      <c r="D1359" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS配信でアルベルト達の新キャラ性能を検証
+アルベルトはビクトールと組むと火力・デバフ両取り
+ミルザは置物性能が高くゼノンと好相性</t>
+        </is>
+      </c>
+      <c r="E1359" s="2" t="inlineStr">
+        <is>
+          <t>・アルベルトはビクトールと組むと強くレイド向き
+・ミルザは置き物要因として優秀で回復も可能
+・ミルザはゼノンと相性抜群</t>
+        </is>
+      </c>
+      <c r="F1359" s="2" t="inlineStr">
+        <is>
+          <t>・愛紗はBP減少が2ターンしかなく微妙
+・アルベルトは自傷ダメージ・回復の手間がある
+・ミルザは追撃4回までに抑える縛りがある</t>
+        </is>
+      </c>
+      <c r="G1359" s="2" t="inlineStr">
+        <is>
+          <t>・井戸配信
+・アルベルト評価
+・ミルザ評価
+・愛紗評価
+・ガチャ考察</t>
+        </is>
+      </c>
+      <c r="H1359" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ライブ配信, コミュニティ</t>
+        </is>
+      </c>
+      <c r="I1359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x9eJVRxUrDo</t>
+        </is>
+      </c>
+      <c r="J1359" s="2" t="inlineStr">
+        <is>
+          <t>x9eJVRxUrDo</t>
+        </is>
+      </c>
+      <c r="K1359" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:08:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1360" s="2" t="inlineStr">
+        <is>
+          <t>明星ch</t>
+        </is>
+      </c>
+      <c r="C1360" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネやりながら雑談</t>
+        </is>
+      </c>
+      <c r="D1360" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナルをプレイしながら今後の参戦予想を雑談
+ファースト外伝URが多く他作品の追加を期待
+運営の細かいアップデート対応を評価</t>
+        </is>
+      </c>
+      <c r="E1360" s="2" t="inlineStr">
+        <is>
+          <t>・運営がユーザー意見を聞いて細かくアップデートしてくれる
+・天井やガチャペースがそこまでキツくない
+・セルラン1位を取れた</t>
+        </is>
+      </c>
+      <c r="F1360" s="2" t="inlineStr">
+        <is>
+          <t>・ファースト外伝URが多すぎてバランスが偏る
+・ダブルZ系がキャラ性能不足でしわ寄せが来ている
+・連動配布SSRは使いどころが少ない
+・飛行ユニットが水陸ステージで沈むなど仕様に不満</t>
+        </is>
+      </c>
+      <c r="G1360" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・参戦予想
+・ファースト外伝
+・ダブルZ
+・運営アップデート</t>
+        </is>
+      </c>
+      <c r="H1360" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ショート, 混合チャンネル</t>
+        </is>
+      </c>
+      <c r="I1360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3ZdzGWTTaTw</t>
+        </is>
+      </c>
+      <c r="J1360" s="2" t="inlineStr">
+        <is>
+          <t>3ZdzGWTTaTw</t>
+        </is>
+      </c>
+      <c r="K1360" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:08:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1361" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1361" s="2" t="inlineStr">
+        <is>
+          <t>【Gジェネ】SSP化＆SP化＆UR凸公開★全コンテンツクリアで1.5周年突入！【ジージェネエターナル】</t>
+        </is>
+      </c>
+      <c r="D1361" s="2" t="inlineStr">
+        <is>
+          <t>Gジェネエターナル1.5周年に無課金プレイ状況を公開
+F91ツインヴェスターは102連でようやく入手
+F系IFシナリオが最高でシーマ様の活躍が心に残る</t>
+        </is>
+      </c>
+      <c r="E1361" s="2" t="inlineStr">
+        <is>
+          <t>・F系のIFシナリオが最高だった
+・F91ツインヴェスターは1回で大ダメージ使いやすい
+・メティオSSPが超強い
+・リーオーガンダムのネティックスが意外と強い</t>
+        </is>
+      </c>
+      <c r="F1361" s="2" t="inlineStr">
+        <is>
+          <t>・F91が102連まで出ず結構きつかった
+・ダブルオーライザー・ウイングゼロカスタムが出ず苦労
+・サポーターがなかなか揃わない
+・ネオジオングを間違えて2体監凸してしまった</t>
+        </is>
+      </c>
+      <c r="G1361" s="2" t="inlineStr">
+        <is>
+          <t>・Gジェネエターナル
+・1.5周年
+・無課金
+・ユニット凸状況
+・SSP化/SP化</t>
+        </is>
+      </c>
+      <c r="H1361" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QP5_tMZ_NHQ</t>
+        </is>
+      </c>
+      <c r="J1361" s="2" t="inlineStr">
+        <is>
+          <t>QP5_tMZ_NHQ</t>
+        </is>
+      </c>
+      <c r="K1361" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:08:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1362" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1362" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋600階3ターンfinish★神速でギミック＆編成解説【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1362" s="2" t="inlineStr">
+        <is>
+          <t>螺旋600階アディリスを3ターンで撃破し編成解説
+陽属性編成＋ミルザの毒特攻でギミック攻略
+アルベルトとゼノンのダブルアタッカーが最大火力</t>
+        </is>
+      </c>
+      <c r="E1362" s="2" t="inlineStr">
+        <is>
+          <t>・3ターンクリアは最速級で気持ちいい
+・アルベルトのシャイニングスラッシュが凄まじい火力
+・ミルザは技中心運用で絶対落ちない安定感</t>
+        </is>
+      </c>
+      <c r="F1362" s="2" t="inlineStr">
+        <is>
+          <t>・術ダメージを与えると反撃されNG
+・HP回復と割合ダメージが厄介
+・ミルザがいないと毒ギミックがきつい</t>
+        </is>
+      </c>
+      <c r="G1362" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋600階
+・アディリス
+・3ターンクリア
+・陽属性編成
+・毒特攻ミルザ</t>
+        </is>
+      </c>
+      <c r="H1362" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SQl9sNtyYvw</t>
+        </is>
+      </c>
+      <c r="J1362" s="2" t="inlineStr">
+        <is>
+          <t>SQl9sNtyYvw</t>
+        </is>
+      </c>
+      <c r="K1362" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:08:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1363" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1363" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】久々にやばいやつ来た！！身構えている時には強キャラは来ないものだ・・最新キャラランキング【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1363" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS最新キャラランキングで6人を評価
+ミルザはトリプルSで環境を作る置物性能
+アルベルトは50ヒットの強力アタッカーでSS</t>
+        </is>
+      </c>
+      <c r="E1363" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザはトリプルSで前期トップクラスの置物性能
+・アルベルトは50ヒットで自己バフも高く強力
+・アイス&amp;リズは2人揃うとSSでボルカノ攻略が簡単
+・サイバー・コッペパン・ミルザのシステムが完成度高い</t>
+        </is>
+      </c>
+      <c r="F1363" s="2" t="inlineStr">
+        <is>
+          <t>・ビューネは無人島特化で高難度では使わない
+・愛紗は上位SS/トリプルS勢には及ばない
+・ミルザは防御系現率が低いので注意
+・復刻に石を使うよりミルザガチャ推奨</t>
+        </is>
+      </c>
+      <c r="G1363" s="2" t="inlineStr">
+        <is>
+          <t>・キャラランキング
+・ミルザ評価
+・アルベルト評価
+・リズ/アイス
+・復刻キャラ</t>
+        </is>
+      </c>
+      <c r="H1363" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=W0Se9zb2UPM</t>
+        </is>
+      </c>
+      <c r="J1363" s="2" t="inlineStr">
+        <is>
+          <t>W0Se9zb2UPM</t>
+        </is>
+      </c>
+      <c r="K1363" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:08:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1364" s="2" t="inlineStr">
+        <is>
+          <t>つむつむちゃんねる●ゲーム考察専門</t>
+        </is>
+      </c>
+      <c r="C1364" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】リズ確保率はまさかの〇〇%！？マドレーン・ヴァルドーの評価とスルー率も徹底分析！【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1364" s="2" t="inlineStr">
+        <is>
+          <t>日編ガチャのアンケート集計で確保率を分析
+リズは確保率40%で断トツ人気、最終50%予想
+マドレーンとバルドはスルー率8割超で不人気</t>
+        </is>
+      </c>
+      <c r="E1364" s="2" t="inlineStr">
+        <is>
+          <t>・リズは弓の追加補強・デバフ解除で確保優先度が高い
+・リズは今も普通に強い</t>
+        </is>
+      </c>
+      <c r="F1364" s="2" t="inlineStr">
+        <is>
+          <t>・マドレーンは全体消費BP+5のデメリットで83%スルー
+・バルドは対象武器種の層が厚く使いづらい
+・マドレーンは9ヶ月前の性能で魅力に欠ける</t>
+        </is>
+      </c>
+      <c r="G1364" s="2" t="inlineStr">
+        <is>
+          <t>・ガチャアンケート
+・リズ確保率40%
+・マドレーン/バルド
+・スルー率分析
+・参加型企画</t>
+        </is>
+      </c>
+      <c r="H1364" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能考察, ランキング</t>
+        </is>
+      </c>
+      <c r="I1364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=eKLNYeNvyuM</t>
+        </is>
+      </c>
+      <c r="J1364" s="2" t="inlineStr">
+        <is>
+          <t>eKLNYeNvyuM</t>
+        </is>
+      </c>
+      <c r="K1364" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:08:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1365" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1365" s="2" t="inlineStr">
+        <is>
+          <t>収録でいつも大暴走するサンゾー！困り果てた2人からまさかの提案が…！？【TARLESS X（ターレスエックス）】【PR】</t>
+        </is>
+      </c>
+      <c r="D1365" s="2" t="inlineStr">
+        <is>
+          <t>ゲーミング電子タバコTARLESS XをPRで紹介
+3シーン対応の6フレーバーを実際に試飲
+RGB搭載の変形式デザインと割引コードを紹介</t>
+        </is>
+      </c>
+      <c r="E1365" s="2" t="inlineStr">
+        <is>
+          <t>・フレーバーの再現度が高く美味しい
+・RGBイルミネーションと変形式デザインがかっこいい
+・ブーストモードでしっかり目覚め切り替わる
+・1本で約4000回吸えてコスパが良い</t>
+        </is>
+      </c>
+      <c r="F1365" s="2" t="inlineStr"/>
+      <c r="G1365" s="2" t="inlineStr">
+        <is>
+          <t>・TARLESS X
+・ゲーミング電子タバコ
+・6フレーバー試飲
+・ニコチンタールゼロ
+・PR</t>
+        </is>
+      </c>
+      <c r="H1365" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IK0jGjfmZ2I</t>
+        </is>
+      </c>
+      <c r="J1365" s="2" t="inlineStr">
+        <is>
+          <t>IK0jGjfmZ2I</t>
+        </is>
+      </c>
+      <c r="K1365" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:08:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1366" s="2" t="inlineStr">
+        <is>
+          <t>サンゾーGAMES</t>
+        </is>
+      </c>
+      <c r="C1366" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】遂に最優先キャラが登場！最新版確保優先度ランキング【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1366" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS確保優先度ランキング最新版を発表
+ミルザが最優先で環境を作る系キャラと評価
+アルベルトはミルザとセットで超強力アタッカー</t>
+        </is>
+      </c>
+      <c r="E1366" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザは環境を作る系で使い回しが良い最優先
+・アルベルトは2ターン50ヒットの強力アタッカー
+・リズは薄い弓のアタッカーで追の特攻になり優秀
+・ガチャ期間延長でじっくり選べてありがたい</t>
+        </is>
+      </c>
+      <c r="F1366" s="2" t="inlineStr">
+        <is>
+          <t>・アルベルトはミルザがいないと優先度が下がる
+・ポルカは弱点つき前提で汎用性が低い
+・井戸は報酬がなく動画にしづらい</t>
+        </is>
+      </c>
+      <c r="G1366" s="2" t="inlineStr">
+        <is>
+          <t>・確保優先度ランキング
+・ミルザ最優先
+・アルベルト/原流
+・追目線重視
+・螺旋回廊重要度</t>
+        </is>
+      </c>
+      <c r="H1366" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 攻略全般</t>
+        </is>
+      </c>
+      <c r="I1366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=P9b6zk-ZOyY</t>
+        </is>
+      </c>
+      <c r="J1366" s="2" t="inlineStr">
+        <is>
+          <t>P9b6zk-ZOyY</t>
+        </is>
+      </c>
+      <c r="K1366" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:08:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1367" s="2" t="inlineStr">
+        <is>
+          <t>あっきゃんGAMES</t>
+        </is>
+      </c>
+      <c r="C1367" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】新イベントよりこっち！新規勢はAbyssal Circusで育成を優先すべき理由【ロマンシングサガリユニバース】</t>
+        </is>
+      </c>
+      <c r="D1367" s="2" t="inlineStr">
+        <is>
+          <t>新規勢は新イベントよりアビサルサーカスの育成を優先
+報酬を取り切ったらアビサルサーカスに戻るのが推奨
+EX4バトルの成長判定3倍で育成効率が高い</t>
+        </is>
+      </c>
+      <c r="E1367" s="2" t="inlineStr">
+        <is>
+          <t>・アビサルサーカスは成長判定3倍で育成効率が高い
+・育成編成の自由度が広い
+・イベント延長で育成チャンスが増えありがたい</t>
+        </is>
+      </c>
+      <c r="F1367" s="2" t="inlineStr">
+        <is>
+          <t>・新イベントのステップ21以降の報酬は旨みがない
+・育成プラスの育成上限はアビサルサーカスが低い</t>
+        </is>
+      </c>
+      <c r="G1367" s="2" t="inlineStr">
+        <is>
+          <t>・アビサルサーカス
+・育成優先
+・新規/復帰勢向け
+・成長判定3倍
+・育成プラス上限</t>
+        </is>
+      </c>
+      <c r="H1367" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 初心者向け, 攻略解説, ショート</t>
+        </is>
+      </c>
+      <c r="I1367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=J8FYrixgI7U</t>
+        </is>
+      </c>
+      <c r="J1367" s="2" t="inlineStr">
+        <is>
+          <t>J8FYrixgI7U</t>
+        </is>
+      </c>
+      <c r="K1367" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:08:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1368" s="2" t="inlineStr">
+        <is>
+          <t>tyamu</t>
+        </is>
+      </c>
+      <c r="C1368" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガrs】第138回カラミティの井戸【超難解】ギミック検証 ~厳選27キャラ・8パーティ紹介（斬熱冷弱点）</t>
+        </is>
+      </c>
+      <c r="D1368" s="2" t="inlineStr">
+        <is>
+          <t>第138回カラミティ(空道)の井戸を実装前に徹底考察
+斬・熱・冷の3弱点で編成予想が難しい井戸
+ミルザが置物ランキング1位に初登場と紹介</t>
+        </is>
+      </c>
+      <c r="E1368" s="2" t="inlineStr">
+        <is>
+          <t>・斬弱点で選択肢が幅広く楽しい井戸
+・ミルザが置物キャラのトップを更新
+・げちゃん軸の熱冷編成が強力</t>
+        </is>
+      </c>
+      <c r="F1368" s="2" t="inlineStr">
+        <is>
+          <t>・弱点が3つで編成予想が非常に難しい
+・コーション発動後の発狂モードが脅威
+・1ターン移動だとギミックが無意味になり2ターンを希望</t>
+        </is>
+      </c>
+      <c r="G1368" s="2" t="inlineStr">
+        <is>
+          <t>・カラミティの井戸
+・空道
+・斬熱冷弱点
+・ギミック検証
+・27キャラ8パーティ</t>
+        </is>
+      </c>
+      <c r="H1368" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, 性能確認, 早見表</t>
+        </is>
+      </c>
+      <c r="I1368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SIaiT0V4ZjQ</t>
+        </is>
+      </c>
+      <c r="J1368" s="2" t="inlineStr">
+        <is>
+          <t>SIaiT0V4ZjQ</t>
+        </is>
+      </c>
+      <c r="K1368" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:08:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1369" s="2" t="inlineStr">
+        <is>
+          <t>ジュラのサガちゃんねる</t>
+        </is>
+      </c>
+      <c r="C1369" s="2" t="inlineStr">
+        <is>
+          <t>【ロマサガRS】螺旋回廊600階「アディリス」を攻略！【ロマンシング サガ リユニバース】</t>
+        </is>
+      </c>
+      <c r="D1369" s="2" t="inlineStr">
+        <is>
+          <t>螺旋回廊600階アディリスを陽属性編成で攻略
+コーションは2ターンで90ヒット以上与えて割る必要あり
+発狂前に火力で押し切るのが攻略セオリー</t>
+        </is>
+      </c>
+      <c r="E1369" s="2" t="inlineStr">
+        <is>
+          <t>・ミルザ・アルベルト・ゼノンは今ガチャで引けて揃えやすい
+・火力で押し切れば攻略は楽
+・9月中は救済スタイルを引けるチャンス</t>
+        </is>
+      </c>
+      <c r="F1369" s="2" t="inlineStr">
+        <is>
+          <t>・弱点が陽属性単体で非常に狭い
+・LP6ダメージの凶悪技で一撃離脱の危険
+・ドラゴンハートで50%回復し逆転負けの危険
+・割合ダメージと毒でパーティ崩壊しやすい</t>
+        </is>
+      </c>
+      <c r="G1369" s="2" t="inlineStr">
+        <is>
+          <t>・螺旋600階
+・アディリス
+・陽属性弱点
+・コーション90ヒット
+・要属性編成</t>
+        </is>
+      </c>
+      <c r="H1369" s="2" t="inlineStr">
+        <is>
+          <t>ロマサガRS, ガチャ, ランキング</t>
+        </is>
+      </c>
+      <c r="I1369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dNexJRuzbBU</t>
+        </is>
+      </c>
+      <c r="J1369" s="2" t="inlineStr">
+        <is>
+          <t>dNexJRuzbBU</t>
+        </is>
+      </c>
+      <c r="K1369" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20T01:08:07Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
